--- a/POD_2026-27_11-5-2026.xlsx
+++ b/POD_2026-27_11-5-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://urjc-my.sharepoint.com/personal/esther_garcia_urjc_es/Documents/Documentos/POD 2026-27/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="246" documentId="11_79C815625599F410B0C00D3910C611C600045ACD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2D0E621-6565-43F1-9346-97ED23F19677}"/>
+  <xr:revisionPtr revIDLastSave="256" documentId="11_79C815625599F410B0C00D3910C611C600045ACD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3AD332FC-B50A-4C47-B94B-6FBC3EE4469D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2917" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2926" uniqueCount="491">
   <si>
     <t>POD_2026-27_11-5-2026</t>
   </si>
@@ -1070,6 +1070,9 @@
     <t>G_IMAT_EXT822_I_1A(M) (2030004), G_IMAT-IORG_EXT822_I_1A(M) (2122003), G_IMAT-IORG_1A(M) (2419001)</t>
   </si>
   <si>
+    <t>Javier Pello</t>
+  </si>
+  <si>
     <t>L=&gt;(09:00-11:00)[28/09/26, 19/10/26, 26/10/26, 23/11/26], J=&gt;(09:00-11:00)[05/11/26, 03/12/26], M=&gt;(09:00-11:00)[01/12/26]</t>
   </si>
   <si>
@@ -1358,7 +1361,13 @@
     <t>G_IQ_EXT822_I_1A(M) (2143007), G_IQ-IAMB_EXT822_I_1A(M) (2226009), G_IQ-IAMB_1A(M) (2416006), G_IQ-IORG_EXT822_I__1A(M) (2121008), G_IQ-IORG_1A(M) (2414006)</t>
   </si>
   <si>
+    <t>Javier Pello (24)</t>
+  </si>
+  <si>
     <t>L=&gt;(09:00-10:00)[08/02/27, 15/02/27, 22/02/27, 01/03/27, 15/03/27, 05/04/27, 19/04/27, 26/04/27, 03/05/27], V=&gt;(09:00-10:00)[05/03/27], J=&gt;(09:00-10:00)[01/04/27, 29/04/27]</t>
+  </si>
+  <si>
+    <t>Javier Pello (6)</t>
   </si>
   <si>
     <t>M=&gt;(13:00-14:00)[09/02/27, 16/02/27, 23/02/27, 02/03/27, 09/03/27, 16/03/27, 06/04/27, 20/04/27, 27/04/27, 04/05/27], V=&gt;(09:00-10:00)[02/04/27, 30/04/27]</t>
@@ -1869,7 +1878,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R244"/>
+  <dimension ref="A1:R252"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -9242,6 +9251,9 @@
       <c r="M158" t="s">
         <v>27</v>
       </c>
+      <c r="N158" t="s">
+        <v>344</v>
+      </c>
       <c r="P158" t="s">
         <v>28</v>
       </c>
@@ -9281,13 +9293,16 @@
         <v>42</v>
       </c>
       <c r="K159" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L159" t="s">
         <v>343</v>
       </c>
       <c r="M159" t="s">
         <v>27</v>
+      </c>
+      <c r="N159" t="s">
+        <v>344</v>
       </c>
       <c r="P159" t="s">
         <v>28</v>
@@ -9328,13 +9343,16 @@
         <v>42</v>
       </c>
       <c r="K160" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L160" t="s">
         <v>343</v>
       </c>
       <c r="M160" t="s">
         <v>27</v>
+      </c>
+      <c r="N160" t="s">
+        <v>344</v>
       </c>
       <c r="P160" t="s">
         <v>28</v>
@@ -9375,10 +9393,10 @@
         <v>42</v>
       </c>
       <c r="K161" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L161" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M161" t="s">
         <v>27</v>
@@ -9422,10 +9440,10 @@
         <v>42</v>
       </c>
       <c r="K162" t="s">
+        <v>349</v>
+      </c>
+      <c r="L162" t="s">
         <v>348</v>
-      </c>
-      <c r="L162" t="s">
-        <v>347</v>
       </c>
       <c r="M162" t="s">
         <v>27</v>
@@ -9469,10 +9487,10 @@
         <v>42</v>
       </c>
       <c r="K163" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L163" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M163" t="s">
         <v>27</v>
@@ -9516,16 +9534,16 @@
         <v>25</v>
       </c>
       <c r="K164" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L164" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M164" t="s">
         <v>27</v>
       </c>
       <c r="N164" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P164" t="s">
         <v>28</v>
@@ -9566,16 +9584,16 @@
         <v>25</v>
       </c>
       <c r="K165" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L165" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M165" t="s">
         <v>27</v>
       </c>
       <c r="N165" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P165" t="s">
         <v>28</v>
@@ -9616,13 +9634,13 @@
         <v>25</v>
       </c>
       <c r="K166" t="s">
+        <v>357</v>
+      </c>
+      <c r="M166" t="s">
+        <v>27</v>
+      </c>
+      <c r="N166" t="s">
         <v>356</v>
-      </c>
-      <c r="M166" t="s">
-        <v>27</v>
-      </c>
-      <c r="N166" t="s">
-        <v>355</v>
       </c>
       <c r="P166" t="s">
         <v>28</v>
@@ -9636,7 +9654,7 @@
         <v>2401001</v>
       </c>
       <c r="B167" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C167" t="s">
         <v>157</v>
@@ -9663,10 +9681,10 @@
         <v>25</v>
       </c>
       <c r="K167" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L167" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M167" t="s">
         <v>27</v>
@@ -9683,7 +9701,7 @@
         <v>2401001</v>
       </c>
       <c r="B168" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C168" t="s">
         <v>157</v>
@@ -9710,10 +9728,10 @@
         <v>25</v>
       </c>
       <c r="K168" t="s">
+        <v>361</v>
+      </c>
+      <c r="L168" t="s">
         <v>360</v>
-      </c>
-      <c r="L168" t="s">
-        <v>359</v>
       </c>
       <c r="M168" t="s">
         <v>27</v>
@@ -9730,7 +9748,7 @@
         <v>2401001</v>
       </c>
       <c r="B169" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C169" t="s">
         <v>157</v>
@@ -9757,10 +9775,10 @@
         <v>25</v>
       </c>
       <c r="K169" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L169" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M169" t="s">
         <v>27</v>
@@ -9777,7 +9795,7 @@
         <v>2401007</v>
       </c>
       <c r="B170" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C170" t="s">
         <v>157</v>
@@ -9804,10 +9822,10 @@
         <v>25</v>
       </c>
       <c r="K170" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L170" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M170" t="s">
         <v>27</v>
@@ -9824,7 +9842,7 @@
         <v>2401007</v>
       </c>
       <c r="B171" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C171" t="s">
         <v>157</v>
@@ -9851,10 +9869,10 @@
         <v>25</v>
       </c>
       <c r="K171" t="s">
+        <v>365</v>
+      </c>
+      <c r="L171" t="s">
         <v>364</v>
-      </c>
-      <c r="L171" t="s">
-        <v>363</v>
       </c>
       <c r="M171" t="s">
         <v>27</v>
@@ -9871,7 +9889,7 @@
         <v>2401007</v>
       </c>
       <c r="B172" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C172" t="s">
         <v>157</v>
@@ -9898,10 +9916,10 @@
         <v>25</v>
       </c>
       <c r="K172" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L172" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M172" t="s">
         <v>27</v>
@@ -9918,7 +9936,7 @@
         <v>2401013</v>
       </c>
       <c r="B173" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C173" t="s">
         <v>157</v>
@@ -9930,7 +9948,7 @@
         <v>21</v>
       </c>
       <c r="F173" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G173" t="s">
         <v>40</v>
@@ -9945,16 +9963,16 @@
         <v>42</v>
       </c>
       <c r="K173" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L173" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M173" t="s">
         <v>27</v>
       </c>
       <c r="N173" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="P173" t="s">
         <v>28</v>
@@ -9968,7 +9986,7 @@
         <v>2401013</v>
       </c>
       <c r="B174" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C174" t="s">
         <v>157</v>
@@ -9980,7 +9998,7 @@
         <v>21</v>
       </c>
       <c r="F174" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G174" t="s">
         <v>40</v>
@@ -9995,16 +10013,16 @@
         <v>42</v>
       </c>
       <c r="K174" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L174" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M174" t="s">
         <v>27</v>
       </c>
       <c r="N174" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="P174" t="s">
         <v>28</v>
@@ -10018,7 +10036,7 @@
         <v>2401013</v>
       </c>
       <c r="B175" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C175" t="s">
         <v>157</v>
@@ -10030,7 +10048,7 @@
         <v>21</v>
       </c>
       <c r="F175" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G175" t="s">
         <v>40</v>
@@ -10045,16 +10063,16 @@
         <v>42</v>
       </c>
       <c r="K175" t="s">
+        <v>373</v>
+      </c>
+      <c r="L175" t="s">
+        <v>369</v>
+      </c>
+      <c r="M175" t="s">
+        <v>27</v>
+      </c>
+      <c r="N175" t="s">
         <v>372</v>
-      </c>
-      <c r="L175" t="s">
-        <v>368</v>
-      </c>
-      <c r="M175" t="s">
-        <v>27</v>
-      </c>
-      <c r="N175" t="s">
-        <v>371</v>
       </c>
       <c r="P175" t="s">
         <v>28</v>
@@ -10068,7 +10086,7 @@
         <v>2401018</v>
       </c>
       <c r="B176" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C176" t="s">
         <v>157</v>
@@ -10080,7 +10098,7 @@
         <v>35</v>
       </c>
       <c r="F176" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G176" t="s">
         <v>40</v>
@@ -10095,10 +10113,10 @@
         <v>42</v>
       </c>
       <c r="K176" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L176" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M176" t="s">
         <v>27</v>
@@ -10115,7 +10133,7 @@
         <v>2401018</v>
       </c>
       <c r="B177" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C177" t="s">
         <v>157</v>
@@ -10127,7 +10145,7 @@
         <v>35</v>
       </c>
       <c r="F177" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G177" t="s">
         <v>40</v>
@@ -10142,10 +10160,10 @@
         <v>42</v>
       </c>
       <c r="K177" t="s">
+        <v>377</v>
+      </c>
+      <c r="L177" t="s">
         <v>376</v>
-      </c>
-      <c r="L177" t="s">
-        <v>375</v>
       </c>
       <c r="M177" t="s">
         <v>27</v>
@@ -10162,7 +10180,7 @@
         <v>2401018</v>
       </c>
       <c r="B178" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C178" t="s">
         <v>157</v>
@@ -10174,7 +10192,7 @@
         <v>35</v>
       </c>
       <c r="F178" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G178" t="s">
         <v>40</v>
@@ -10183,16 +10201,16 @@
         <v>4</v>
       </c>
       <c r="I178" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="J178" t="s">
         <v>42</v>
       </c>
       <c r="K178" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L178" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M178" t="s">
         <v>27</v>
@@ -10209,7 +10227,7 @@
         <v>2401018</v>
       </c>
       <c r="B179" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C179" t="s">
         <v>157</v>
@@ -10221,7 +10239,7 @@
         <v>35</v>
       </c>
       <c r="F179" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G179" t="s">
         <v>40</v>
@@ -10236,10 +10254,10 @@
         <v>42</v>
       </c>
       <c r="K179" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L179" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M179" t="s">
         <v>27</v>
@@ -10256,7 +10274,7 @@
         <v>2401018</v>
       </c>
       <c r="B180" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C180" t="s">
         <v>157</v>
@@ -10268,7 +10286,7 @@
         <v>35</v>
       </c>
       <c r="F180" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G180" t="s">
         <v>40</v>
@@ -10277,16 +10295,16 @@
         <v>4</v>
       </c>
       <c r="I180" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="J180" t="s">
         <v>42</v>
       </c>
       <c r="K180" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L180" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M180" t="s">
         <v>27</v>
@@ -10303,7 +10321,7 @@
         <v>2401018</v>
       </c>
       <c r="B181" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C181" t="s">
         <v>157</v>
@@ -10315,7 +10333,7 @@
         <v>35</v>
       </c>
       <c r="F181" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G181" t="s">
         <v>40</v>
@@ -10324,16 +10342,16 @@
         <v>4</v>
       </c>
       <c r="I181" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J181" t="s">
         <v>42</v>
       </c>
       <c r="K181" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L181" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M181" t="s">
         <v>27</v>
@@ -10350,7 +10368,7 @@
         <v>2401018</v>
       </c>
       <c r="B182" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C182" t="s">
         <v>157</v>
@@ -10362,7 +10380,7 @@
         <v>35</v>
       </c>
       <c r="F182" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G182" t="s">
         <v>40</v>
@@ -10371,16 +10389,16 @@
         <v>4</v>
       </c>
       <c r="I182" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J182" t="s">
         <v>42</v>
       </c>
       <c r="K182" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L182" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M182" t="s">
         <v>27</v>
@@ -10397,7 +10415,7 @@
         <v>2402003</v>
       </c>
       <c r="B183" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C183" t="s">
         <v>157</v>
@@ -10424,10 +10442,10 @@
         <v>25</v>
       </c>
       <c r="K183" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L183" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M183" t="s">
         <v>27</v>
@@ -10447,7 +10465,7 @@
         <v>2402003</v>
       </c>
       <c r="B184" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C184" t="s">
         <v>157</v>
@@ -10474,10 +10492,10 @@
         <v>25</v>
       </c>
       <c r="K184" t="s">
+        <v>390</v>
+      </c>
+      <c r="L184" t="s">
         <v>389</v>
-      </c>
-      <c r="L184" t="s">
-        <v>388</v>
       </c>
       <c r="M184" t="s">
         <v>27</v>
@@ -10497,7 +10515,7 @@
         <v>2402003</v>
       </c>
       <c r="B185" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C185" t="s">
         <v>157</v>
@@ -10524,10 +10542,10 @@
         <v>25</v>
       </c>
       <c r="K185" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L185" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M185" t="s">
         <v>27</v>
@@ -10547,7 +10565,7 @@
         <v>2402008</v>
       </c>
       <c r="B186" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C186" t="s">
         <v>157</v>
@@ -10574,16 +10592,16 @@
         <v>25</v>
       </c>
       <c r="K186" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L186" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M186" t="s">
         <v>27</v>
       </c>
       <c r="N186" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="P186" t="s">
         <v>28</v>
@@ -10597,7 +10615,7 @@
         <v>2402008</v>
       </c>
       <c r="B187" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C187" t="s">
         <v>157</v>
@@ -10624,16 +10642,16 @@
         <v>25</v>
       </c>
       <c r="K187" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L187" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M187" t="s">
         <v>27</v>
       </c>
       <c r="N187" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="P187" t="s">
         <v>28</v>
@@ -10647,7 +10665,7 @@
         <v>2402008</v>
       </c>
       <c r="B188" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C188" t="s">
         <v>157</v>
@@ -10674,16 +10692,16 @@
         <v>25</v>
       </c>
       <c r="K188" t="s">
+        <v>397</v>
+      </c>
+      <c r="L188" t="s">
+        <v>393</v>
+      </c>
+      <c r="M188" t="s">
+        <v>27</v>
+      </c>
+      <c r="N188" t="s">
         <v>396</v>
-      </c>
-      <c r="L188" t="s">
-        <v>392</v>
-      </c>
-      <c r="M188" t="s">
-        <v>27</v>
-      </c>
-      <c r="N188" t="s">
-        <v>395</v>
       </c>
       <c r="P188" t="s">
         <v>28</v>
@@ -10697,7 +10715,7 @@
         <v>2402015</v>
       </c>
       <c r="B189" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C189" t="s">
         <v>157</v>
@@ -10724,13 +10742,13 @@
         <v>42</v>
       </c>
       <c r="K189" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M189" t="s">
         <v>27</v>
       </c>
       <c r="N189" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P189" t="s">
         <v>28</v>
@@ -10744,7 +10762,7 @@
         <v>2402015</v>
       </c>
       <c r="B190" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C190" t="s">
         <v>157</v>
@@ -10771,13 +10789,13 @@
         <v>42</v>
       </c>
       <c r="K190" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M190" t="s">
         <v>27</v>
       </c>
       <c r="N190" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P190" t="s">
         <v>28</v>
@@ -10791,7 +10809,7 @@
         <v>2402015</v>
       </c>
       <c r="B191" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C191" t="s">
         <v>157</v>
@@ -10818,7 +10836,7 @@
         <v>42</v>
       </c>
       <c r="K191" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M191" t="s">
         <v>27</v>
@@ -10836,7 +10854,7 @@
         <v>2403004</v>
       </c>
       <c r="B192" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C192" t="s">
         <v>157</v>
@@ -10863,10 +10881,10 @@
         <v>42</v>
       </c>
       <c r="K192" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L192" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M192" t="s">
         <v>27</v>
@@ -10886,7 +10904,7 @@
         <v>2403004</v>
       </c>
       <c r="B193" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C193" t="s">
         <v>157</v>
@@ -10913,10 +10931,10 @@
         <v>42</v>
       </c>
       <c r="K193" t="s">
+        <v>406</v>
+      </c>
+      <c r="L193" t="s">
         <v>405</v>
-      </c>
-      <c r="L193" t="s">
-        <v>404</v>
       </c>
       <c r="M193" t="s">
         <v>27</v>
@@ -10936,7 +10954,7 @@
         <v>2403004</v>
       </c>
       <c r="B194" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C194" t="s">
         <v>157</v>
@@ -10963,10 +10981,10 @@
         <v>42</v>
       </c>
       <c r="K194" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L194" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M194" t="s">
         <v>27</v>
@@ -10986,7 +11004,7 @@
         <v>2403009</v>
       </c>
       <c r="B195" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C195" t="s">
         <v>157</v>
@@ -11013,10 +11031,10 @@
         <v>42</v>
       </c>
       <c r="K195" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L195" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M195" t="s">
         <v>27</v>
@@ -11033,7 +11051,7 @@
         <v>2403009</v>
       </c>
       <c r="B196" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C196" t="s">
         <v>157</v>
@@ -11060,10 +11078,10 @@
         <v>42</v>
       </c>
       <c r="K196" t="s">
+        <v>410</v>
+      </c>
+      <c r="L196" t="s">
         <v>409</v>
-      </c>
-      <c r="L196" t="s">
-        <v>408</v>
       </c>
       <c r="M196" t="s">
         <v>27</v>
@@ -11080,7 +11098,7 @@
         <v>2403009</v>
       </c>
       <c r="B197" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C197" t="s">
         <v>157</v>
@@ -11107,10 +11125,10 @@
         <v>42</v>
       </c>
       <c r="K197" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L197" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M197" t="s">
         <v>27</v>
@@ -11127,7 +11145,7 @@
         <v>2403013</v>
       </c>
       <c r="B198" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C198" t="s">
         <v>157</v>
@@ -11154,7 +11172,7 @@
         <v>25</v>
       </c>
       <c r="K198" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M198" t="s">
         <v>27</v>
@@ -11171,7 +11189,7 @@
         <v>2403013</v>
       </c>
       <c r="B199" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C199" t="s">
         <v>157</v>
@@ -11198,7 +11216,7 @@
         <v>25</v>
       </c>
       <c r="K199" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M199" t="s">
         <v>27</v>
@@ -11215,7 +11233,7 @@
         <v>2403013</v>
       </c>
       <c r="B200" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C200" t="s">
         <v>157</v>
@@ -11242,7 +11260,7 @@
         <v>25</v>
       </c>
       <c r="K200" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M200" t="s">
         <v>27</v>
@@ -11259,7 +11277,7 @@
         <v>2404001</v>
       </c>
       <c r="B201" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C201" t="s">
         <v>157</v>
@@ -11286,16 +11304,16 @@
         <v>42</v>
       </c>
       <c r="K201" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L201" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M201" t="s">
         <v>27</v>
       </c>
       <c r="N201" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="P201" t="s">
         <v>28</v>
@@ -11309,7 +11327,7 @@
         <v>2404001</v>
       </c>
       <c r="B202" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C202" t="s">
         <v>157</v>
@@ -11336,16 +11354,16 @@
         <v>42</v>
       </c>
       <c r="K202" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L202" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M202" t="s">
         <v>27</v>
       </c>
       <c r="N202" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="P202" t="s">
         <v>28</v>
@@ -11359,7 +11377,7 @@
         <v>2404001</v>
       </c>
       <c r="B203" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C203" t="s">
         <v>157</v>
@@ -11386,16 +11404,16 @@
         <v>42</v>
       </c>
       <c r="K203" t="s">
+        <v>421</v>
+      </c>
+      <c r="L203" t="s">
+        <v>417</v>
+      </c>
+      <c r="M203" t="s">
+        <v>27</v>
+      </c>
+      <c r="N203" t="s">
         <v>420</v>
-      </c>
-      <c r="L203" t="s">
-        <v>416</v>
-      </c>
-      <c r="M203" t="s">
-        <v>27</v>
-      </c>
-      <c r="N203" t="s">
-        <v>419</v>
       </c>
       <c r="P203" t="s">
         <v>28</v>
@@ -11409,7 +11427,7 @@
         <v>2404006</v>
       </c>
       <c r="B204" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C204" t="s">
         <v>157</v>
@@ -11436,16 +11454,16 @@
         <v>42</v>
       </c>
       <c r="K204" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L204" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M204" t="s">
         <v>27</v>
       </c>
       <c r="N204" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="P204" t="s">
         <v>28</v>
@@ -11459,7 +11477,7 @@
         <v>2404006</v>
       </c>
       <c r="B205" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C205" t="s">
         <v>157</v>
@@ -11486,16 +11504,16 @@
         <v>42</v>
       </c>
       <c r="K205" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L205" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M205" t="s">
         <v>27</v>
       </c>
       <c r="N205" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="P205" t="s">
         <v>28</v>
@@ -11509,7 +11527,7 @@
         <v>2404006</v>
       </c>
       <c r="B206" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C206" t="s">
         <v>157</v>
@@ -11536,16 +11554,16 @@
         <v>42</v>
       </c>
       <c r="K206" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L206" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M206" t="s">
         <v>27</v>
       </c>
       <c r="N206" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="P206" t="s">
         <v>28</v>
@@ -11559,7 +11577,7 @@
         <v>2404015</v>
       </c>
       <c r="B207" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C207" t="s">
         <v>157</v>
@@ -11571,7 +11589,7 @@
         <v>21</v>
       </c>
       <c r="F207" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G207" t="s">
         <v>40</v>
@@ -11586,13 +11604,13 @@
         <v>25</v>
       </c>
       <c r="K207" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M207" t="s">
         <v>27</v>
       </c>
       <c r="N207" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="P207" t="s">
         <v>28</v>
@@ -11606,7 +11624,7 @@
         <v>2404015</v>
       </c>
       <c r="B208" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C208" t="s">
         <v>157</v>
@@ -11618,7 +11636,7 @@
         <v>21</v>
       </c>
       <c r="F208" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G208" t="s">
         <v>40</v>
@@ -11627,19 +11645,19 @@
         <v>32</v>
       </c>
       <c r="I208" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J208" t="s">
         <v>25</v>
       </c>
       <c r="K208" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M208" t="s">
         <v>27</v>
       </c>
       <c r="N208" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="P208" t="s">
         <v>28</v>
@@ -11653,7 +11671,7 @@
         <v>2404015</v>
       </c>
       <c r="B209" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C209" t="s">
         <v>157</v>
@@ -11665,7 +11683,7 @@
         <v>21</v>
       </c>
       <c r="F209" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G209" t="s">
         <v>40</v>
@@ -11674,19 +11692,19 @@
         <v>32</v>
       </c>
       <c r="I209" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J209" t="s">
         <v>25</v>
       </c>
       <c r="K209" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M209" t="s">
         <v>27</v>
       </c>
       <c r="N209" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="P209" t="s">
         <v>28</v>
@@ -11700,7 +11718,7 @@
         <v>2405001</v>
       </c>
       <c r="B210" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C210" t="s">
         <v>157</v>
@@ -11727,13 +11745,16 @@
         <v>42</v>
       </c>
       <c r="K210" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L210" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M210" t="s">
         <v>27</v>
+      </c>
+      <c r="N210" t="s">
+        <v>344</v>
       </c>
       <c r="P210" t="s">
         <v>28</v>
@@ -11747,7 +11768,7 @@
         <v>2405001</v>
       </c>
       <c r="B211" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C211" t="s">
         <v>157</v>
@@ -11774,13 +11795,16 @@
         <v>42</v>
       </c>
       <c r="K211" t="s">
+        <v>437</v>
+      </c>
+      <c r="L211" t="s">
         <v>436</v>
       </c>
-      <c r="L211" t="s">
-        <v>435</v>
-      </c>
       <c r="M211" t="s">
         <v>27</v>
+      </c>
+      <c r="N211" t="s">
+        <v>344</v>
       </c>
       <c r="P211" t="s">
         <v>28</v>
@@ -11794,7 +11818,7 @@
         <v>2405001</v>
       </c>
       <c r="B212" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C212" t="s">
         <v>157</v>
@@ -11821,13 +11845,16 @@
         <v>42</v>
       </c>
       <c r="K212" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L212" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="M212" t="s">
         <v>27</v>
+      </c>
+      <c r="N212" t="s">
+        <v>344</v>
       </c>
       <c r="P212" t="s">
         <v>28</v>
@@ -11841,7 +11868,7 @@
         <v>2405006</v>
       </c>
       <c r="B213" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C213" t="s">
         <v>157</v>
@@ -11868,13 +11895,16 @@
         <v>42</v>
       </c>
       <c r="K213" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L213" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M213" t="s">
         <v>27</v>
+      </c>
+      <c r="N213" t="s">
+        <v>441</v>
       </c>
       <c r="P213" t="s">
         <v>28</v>
@@ -11888,7 +11918,7 @@
         <v>2405006</v>
       </c>
       <c r="B214" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C214" t="s">
         <v>157</v>
@@ -11915,13 +11945,16 @@
         <v>42</v>
       </c>
       <c r="K214" t="s">
+        <v>442</v>
+      </c>
+      <c r="L214" t="s">
         <v>440</v>
       </c>
-      <c r="L214" t="s">
-        <v>439</v>
-      </c>
       <c r="M214" t="s">
         <v>27</v>
+      </c>
+      <c r="N214" t="s">
+        <v>443</v>
       </c>
       <c r="P214" t="s">
         <v>28</v>
@@ -11935,7 +11968,7 @@
         <v>2405006</v>
       </c>
       <c r="B215" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C215" t="s">
         <v>157</v>
@@ -11962,13 +11995,16 @@
         <v>42</v>
       </c>
       <c r="K215" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="L215" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M215" t="s">
         <v>27</v>
+      </c>
+      <c r="N215" t="s">
+        <v>443</v>
       </c>
       <c r="P215" t="s">
         <v>28</v>
@@ -11982,7 +12018,7 @@
         <v>2405015</v>
       </c>
       <c r="B216" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C216" t="s">
         <v>157</v>
@@ -12009,16 +12045,16 @@
         <v>25</v>
       </c>
       <c r="K216" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="L216" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="M216" t="s">
         <v>27</v>
       </c>
       <c r="N216" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="P216" t="s">
         <v>28</v>
@@ -12032,7 +12068,7 @@
         <v>2405015</v>
       </c>
       <c r="B217" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C217" t="s">
         <v>157</v>
@@ -12059,16 +12095,16 @@
         <v>25</v>
       </c>
       <c r="K217" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="L217" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="M217" t="s">
         <v>27</v>
       </c>
       <c r="N217" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="P217" t="s">
         <v>28</v>
@@ -12082,7 +12118,7 @@
         <v>2405015</v>
       </c>
       <c r="B218" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C218" t="s">
         <v>157</v>
@@ -12109,13 +12145,13 @@
         <v>25</v>
       </c>
       <c r="K218" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="M218" t="s">
         <v>27</v>
       </c>
       <c r="N218" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="P218" t="s">
         <v>28</v>
@@ -12129,7 +12165,7 @@
         <v>2406004</v>
       </c>
       <c r="B219" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C219" t="s">
         <v>157</v>
@@ -12156,10 +12192,10 @@
         <v>25</v>
       </c>
       <c r="K219" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="L219" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="M219" t="s">
         <v>27</v>
@@ -12176,7 +12212,7 @@
         <v>2406004</v>
       </c>
       <c r="B220" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C220" t="s">
         <v>157</v>
@@ -12203,10 +12239,10 @@
         <v>25</v>
       </c>
       <c r="K220" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="L220" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="M220" t="s">
         <v>27</v>
@@ -12223,7 +12259,7 @@
         <v>2406004</v>
       </c>
       <c r="B221" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C221" t="s">
         <v>157</v>
@@ -12244,13 +12280,13 @@
         <v>8</v>
       </c>
       <c r="I221" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J221" t="s">
         <v>25</v>
       </c>
       <c r="L221" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="M221" t="s">
         <v>27</v>
@@ -12267,7 +12303,7 @@
         <v>2406004</v>
       </c>
       <c r="B222" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C222" t="s">
         <v>157</v>
@@ -12294,10 +12330,10 @@
         <v>25</v>
       </c>
       <c r="K222" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="L222" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="M222" t="s">
         <v>27</v>
@@ -12314,7 +12350,7 @@
         <v>2406004</v>
       </c>
       <c r="B223" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C223" t="s">
         <v>157</v>
@@ -12335,13 +12371,13 @@
         <v>8</v>
       </c>
       <c r="I223" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J223" t="s">
         <v>25</v>
       </c>
       <c r="L223" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="M223" t="s">
         <v>27</v>
@@ -12358,7 +12394,7 @@
         <v>2406009</v>
       </c>
       <c r="B224" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C224" t="s">
         <v>157</v>
@@ -12385,10 +12421,10 @@
         <v>25</v>
       </c>
       <c r="K224" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="L224" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="M224" t="s">
         <v>27</v>
@@ -12405,7 +12441,7 @@
         <v>2406009</v>
       </c>
       <c r="B225" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C225" t="s">
         <v>157</v>
@@ -12432,10 +12468,10 @@
         <v>25</v>
       </c>
       <c r="K225" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="L225" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="M225" t="s">
         <v>27</v>
@@ -12452,7 +12488,7 @@
         <v>2406009</v>
       </c>
       <c r="B226" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C226" t="s">
         <v>157</v>
@@ -12473,16 +12509,16 @@
         <v>8</v>
       </c>
       <c r="I226" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J226" t="s">
         <v>25</v>
       </c>
       <c r="K226" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="L226" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="M226" t="s">
         <v>27</v>
@@ -12499,7 +12535,7 @@
         <v>2406009</v>
       </c>
       <c r="B227" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C227" t="s">
         <v>157</v>
@@ -12526,10 +12562,10 @@
         <v>25</v>
       </c>
       <c r="K227" t="s">
+        <v>460</v>
+      </c>
+      <c r="L227" t="s">
         <v>457</v>
-      </c>
-      <c r="L227" t="s">
-        <v>454</v>
       </c>
       <c r="M227" t="s">
         <v>27</v>
@@ -12546,7 +12582,7 @@
         <v>2406009</v>
       </c>
       <c r="B228" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C228" t="s">
         <v>157</v>
@@ -12567,16 +12603,16 @@
         <v>8</v>
       </c>
       <c r="I228" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J228" t="s">
         <v>25</v>
       </c>
       <c r="K228" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="L228" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="M228" t="s">
         <v>27</v>
@@ -12593,7 +12629,7 @@
         <v>2406012</v>
       </c>
       <c r="B229" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C229" t="s">
         <v>157</v>
@@ -12605,7 +12641,7 @@
         <v>21</v>
       </c>
       <c r="F229" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="G229" t="s">
         <v>40</v>
@@ -12620,10 +12656,10 @@
         <v>42</v>
       </c>
       <c r="K229" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="L229" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="M229" t="s">
         <v>27</v>
@@ -12640,7 +12676,7 @@
         <v>2406012</v>
       </c>
       <c r="B230" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C230" t="s">
         <v>157</v>
@@ -12652,7 +12688,7 @@
         <v>21</v>
       </c>
       <c r="F230" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="G230" t="s">
         <v>40</v>
@@ -12661,16 +12697,16 @@
         <v>8</v>
       </c>
       <c r="I230" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="J230" t="s">
         <v>42</v>
       </c>
       <c r="K230" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="L230" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="M230" t="s">
         <v>27</v>
@@ -12687,7 +12723,7 @@
         <v>2406012</v>
       </c>
       <c r="B231" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C231" t="s">
         <v>157</v>
@@ -12699,7 +12735,7 @@
         <v>21</v>
       </c>
       <c r="F231" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="G231" t="s">
         <v>40</v>
@@ -12708,16 +12744,16 @@
         <v>8</v>
       </c>
       <c r="I231" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="J231" t="s">
         <v>42</v>
       </c>
       <c r="K231" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="L231" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="M231" t="s">
         <v>27</v>
@@ -12734,10 +12770,10 @@
         <v>2059001</v>
       </c>
       <c r="B232" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="C232" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D232" s="2">
         <v>1</v>
@@ -12761,10 +12797,10 @@
         <v>42</v>
       </c>
       <c r="K232" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="L232" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="M232" t="s">
         <v>27</v>
@@ -12781,10 +12817,10 @@
         <v>2059002</v>
       </c>
       <c r="B233" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="C233" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D233" s="2">
         <v>1</v>
@@ -12808,10 +12844,10 @@
         <v>42</v>
       </c>
       <c r="K233" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="L233" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="M233" t="s">
         <v>27</v>
@@ -12828,10 +12864,10 @@
         <v>2059006</v>
       </c>
       <c r="B234" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="C234" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D234" s="2">
         <v>1</v>
@@ -12855,10 +12891,10 @@
         <v>42</v>
       </c>
       <c r="K234" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="L234" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="M234" t="s">
         <v>27</v>
@@ -12875,10 +12911,10 @@
         <v>2140011</v>
       </c>
       <c r="B235" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="C235" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D235" s="2">
         <v>2</v>
@@ -12905,7 +12941,7 @@
         <v>159</v>
       </c>
       <c r="L235" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="M235" t="s">
         <v>27</v>
@@ -12922,10 +12958,10 @@
         <v>2390004</v>
       </c>
       <c r="B236" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C236" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D236" s="2">
         <v>1</v>
@@ -12949,10 +12985,10 @@
         <v>25</v>
       </c>
       <c r="K236" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="L236" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="M236" t="s">
         <v>27</v>
@@ -12969,10 +13005,10 @@
         <v>2390004</v>
       </c>
       <c r="B237" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C237" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D237" s="2">
         <v>1</v>
@@ -12996,10 +13032,10 @@
         <v>25</v>
       </c>
       <c r="K237" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="L237" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="M237" t="s">
         <v>27</v>
@@ -13016,10 +13052,10 @@
         <v>2390004</v>
       </c>
       <c r="B238" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C238" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D238" s="2">
         <v>1</v>
@@ -13043,10 +13079,10 @@
         <v>25</v>
       </c>
       <c r="K238" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="L238" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="M238" t="s">
         <v>27</v>
@@ -13063,10 +13099,10 @@
         <v>2390009</v>
       </c>
       <c r="B239" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C239" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D239" s="2">
         <v>1</v>
@@ -13090,10 +13126,10 @@
         <v>25</v>
       </c>
       <c r="K239" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="L239" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="M239" t="s">
         <v>27</v>
@@ -13110,10 +13146,10 @@
         <v>2390009</v>
       </c>
       <c r="B240" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C240" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D240" s="2">
         <v>1</v>
@@ -13137,10 +13173,10 @@
         <v>25</v>
       </c>
       <c r="K240" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="L240" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="M240" t="s">
         <v>27</v>
@@ -13157,10 +13193,10 @@
         <v>2390009</v>
       </c>
       <c r="B241" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C241" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D241" s="2">
         <v>1</v>
@@ -13184,10 +13220,10 @@
         <v>25</v>
       </c>
       <c r="K241" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="L241" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="M241" t="s">
         <v>27</v>
@@ -13204,10 +13240,10 @@
         <v>2390013</v>
       </c>
       <c r="B242" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C242" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D242" s="2">
         <v>2</v>
@@ -13231,7 +13267,7 @@
         <v>42</v>
       </c>
       <c r="K242" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="M242" t="s">
         <v>27</v>
@@ -13248,10 +13284,10 @@
         <v>2390013</v>
       </c>
       <c r="B243" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C243" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D243" s="2">
         <v>2</v>
@@ -13275,7 +13311,7 @@
         <v>42</v>
       </c>
       <c r="K243" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="M243" t="s">
         <v>27</v>
@@ -13292,10 +13328,10 @@
         <v>2390013</v>
       </c>
       <c r="B244" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C244" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D244" s="2">
         <v>2</v>
@@ -13319,7 +13355,7 @@
         <v>42</v>
       </c>
       <c r="K244" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="M244" t="s">
         <v>27</v>
@@ -13330,6 +13366,9 @@
       <c r="Q244" t="s">
         <v>29</v>
       </c>
+    </row>
+    <row r="252" spans="1:17" ht="15" customHeight="1">
+      <c r="L252" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/POD_2026-27_11-5-2026.xlsx
+++ b/POD_2026-27_11-5-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://urjc-my.sharepoint.com/personal/esther_garcia_urjc_es/Documents/Documentos/POD 2026-27/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="256" documentId="11_79C815625599F410B0C00D3910C611C600045ACD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3AD332FC-B50A-4C47-B94B-6FBC3EE4469D}"/>
+  <xr:revisionPtr revIDLastSave="269" documentId="11_79C815625599F410B0C00D3910C611C600045ACD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9CE8BAA4-9BC3-4CF2-9FCA-4000CC19B849}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2926" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2929" uniqueCount="494">
   <si>
     <t>POD_2026-27_11-5-2026</t>
   </si>
@@ -584,6 +584,9 @@
     <t>G_INF-ADE_1A(M) (2097015), G_INF-COMP_1A(M) (2113005), G_INF-MAT_EXT_1A(M) (2117003)</t>
   </si>
   <si>
+    <t>ÁNGEL PÉREZ (35/70)</t>
+  </si>
+  <si>
     <t>J(13:00 - 15:00), V(09:00 - 11:00)</t>
   </si>
   <si>
@@ -716,6 +719,9 @@
     <t>G_ECO-MAT_1A(M) (2299005), G_ED_PRIM-MAT_EXT_1A(M) (2178004), G_ED_PRIM-MAT_SUSP_1A(M) (2348004), G_INF-MAT_EXT_1A(M) (2117005), G_INF-MAT_1A(M) (2315003), G_MAT_EXT_I_1A(M) (2028003), G_SOFT-MAT_EXT_1A(M) (2118005), G_SOFT-MAT_1A(M) (2316003)</t>
   </si>
   <si>
+    <t>ÁNGEL PÉREZ (60/60)</t>
+  </si>
+  <si>
     <t>MATEMATICA DISCRETA</t>
   </si>
   <si>
@@ -1070,12 +1076,15 @@
     <t>G_IMAT_EXT822_I_1A(M) (2030004), G_IMAT-IORG_EXT822_I_1A(M) (2122003), G_IMAT-IORG_1A(M) (2419001)</t>
   </si>
   <si>
-    <t>Javier Pello</t>
+    <t>Javier Pello (48/48)</t>
   </si>
   <si>
     <t>L=&gt;(09:00-11:00)[28/09/26, 19/10/26, 26/10/26, 23/11/26], J=&gt;(09:00-11:00)[05/11/26, 03/12/26], M=&gt;(09:00-11:00)[01/12/26]</t>
   </si>
   <si>
+    <t>Javier Pello (12/12)</t>
+  </si>
+  <si>
     <t>L=&gt;(09:00-11:00)[05/10/26, 30/11/26], M=&gt;(09:00-11:00)[03/11/26], J=&gt;(09:00-11:00)[26/11/26, 10/12/26]</t>
   </si>
   <si>
@@ -1361,13 +1370,13 @@
     <t>G_IQ_EXT822_I_1A(M) (2143007), G_IQ-IAMB_EXT822_I_1A(M) (2226009), G_IQ-IAMB_1A(M) (2416006), G_IQ-IORG_EXT822_I__1A(M) (2121008), G_IQ-IORG_1A(M) (2414006)</t>
   </si>
   <si>
-    <t>Javier Pello (24)</t>
+    <t>Javier Pello (24/48)</t>
   </si>
   <si>
     <t>L=&gt;(09:00-10:00)[08/02/27, 15/02/27, 22/02/27, 01/03/27, 15/03/27, 05/04/27, 19/04/27, 26/04/27, 03/05/27], V=&gt;(09:00-10:00)[05/03/27], J=&gt;(09:00-10:00)[01/04/27, 29/04/27]</t>
   </si>
   <si>
-    <t>Javier Pello (6)</t>
+    <t>Javier Pello (6/12)</t>
   </si>
   <si>
     <t>M=&gt;(13:00-14:00)[09/02/27, 16/02/27, 23/02/27, 02/03/27, 09/03/27, 16/03/27, 06/04/27, 20/04/27, 27/04/27, 04/05/27], V=&gt;(09:00-10:00)[02/04/27, 30/04/27]</t>
@@ -5533,6 +5542,9 @@
       <c r="M79" t="s">
         <v>27</v>
       </c>
+      <c r="N79" t="s">
+        <v>182</v>
+      </c>
       <c r="P79" t="s">
         <v>28</v>
       </c>
@@ -5572,10 +5584,10 @@
         <v>42</v>
       </c>
       <c r="K80" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L80" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M80" t="s">
         <v>27</v>
@@ -5592,7 +5604,7 @@
         <v>2034001</v>
       </c>
       <c r="B81" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C81" t="s">
         <v>157</v>
@@ -5622,7 +5634,7 @@
         <v>177</v>
       </c>
       <c r="L81" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M81" t="s">
         <v>27</v>
@@ -5639,7 +5651,7 @@
         <v>2034002</v>
       </c>
       <c r="B82" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C82" t="s">
         <v>157</v>
@@ -5666,10 +5678,10 @@
         <v>42</v>
       </c>
       <c r="K82" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L82" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M82" t="s">
         <v>27</v>
@@ -5686,7 +5698,7 @@
         <v>2034006</v>
       </c>
       <c r="B83" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C83" t="s">
         <v>157</v>
@@ -5713,10 +5725,10 @@
         <v>42</v>
       </c>
       <c r="K83" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L83" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M83" t="s">
         <v>27</v>
@@ -5733,7 +5745,7 @@
         <v>2061001</v>
       </c>
       <c r="B84" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C84" t="s">
         <v>157</v>
@@ -5777,7 +5789,7 @@
         <v>2061002</v>
       </c>
       <c r="B85" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C85" t="s">
         <v>157</v>
@@ -5821,7 +5833,7 @@
         <v>2061006</v>
       </c>
       <c r="B86" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C86" t="s">
         <v>157</v>
@@ -5865,7 +5877,7 @@
         <v>2107013</v>
       </c>
       <c r="B87" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C87" t="s">
         <v>157</v>
@@ -5877,7 +5889,7 @@
         <v>21</v>
       </c>
       <c r="F87" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G87" t="s">
         <v>40</v>
@@ -5895,7 +5907,7 @@
         <v>159</v>
       </c>
       <c r="L87" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M87" t="s">
         <v>27</v>
@@ -5912,7 +5924,7 @@
         <v>2143016</v>
       </c>
       <c r="B88" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C88" t="s">
         <v>157</v>
@@ -5924,7 +5936,7 @@
         <v>21</v>
       </c>
       <c r="F88" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G88" t="s">
         <v>40</v>
@@ -5942,7 +5954,7 @@
         <v>159</v>
       </c>
       <c r="L88" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M88" t="s">
         <v>27</v>
@@ -5959,7 +5971,7 @@
         <v>2148011</v>
       </c>
       <c r="B89" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C89" t="s">
         <v>157</v>
@@ -5971,7 +5983,7 @@
         <v>21</v>
       </c>
       <c r="F89" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G89" t="s">
         <v>40</v>
@@ -6003,7 +6015,7 @@
         <v>2175020</v>
       </c>
       <c r="B90" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C90" t="s">
         <v>157</v>
@@ -6030,10 +6042,10 @@
         <v>25</v>
       </c>
       <c r="K90" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L90" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M90" t="s">
         <v>27</v>
@@ -6050,7 +6062,7 @@
         <v>2285005</v>
       </c>
       <c r="B91" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C91" t="s">
         <v>157</v>
@@ -6094,7 +6106,7 @@
         <v>2285006</v>
       </c>
       <c r="B92" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C92" t="s">
         <v>157</v>
@@ -6121,13 +6133,13 @@
         <v>42</v>
       </c>
       <c r="K92" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M92" t="s">
         <v>27</v>
       </c>
       <c r="N92" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P92" t="s">
         <v>28</v>
@@ -6141,7 +6153,7 @@
         <v>2285007</v>
       </c>
       <c r="B93" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C93" t="s">
         <v>157</v>
@@ -6153,7 +6165,7 @@
         <v>35</v>
       </c>
       <c r="F93" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G93" t="s">
         <v>40</v>
@@ -6168,7 +6180,7 @@
         <v>42</v>
       </c>
       <c r="K93" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M93" t="s">
         <v>27</v>
@@ -6185,7 +6197,7 @@
         <v>2286015</v>
       </c>
       <c r="B94" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C94" t="s">
         <v>157</v>
@@ -6197,7 +6209,7 @@
         <v>21</v>
       </c>
       <c r="F94" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G94" t="s">
         <v>40</v>
@@ -6229,7 +6241,7 @@
         <v>2338044</v>
       </c>
       <c r="B95" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C95" t="s">
         <v>157</v>
@@ -6273,7 +6285,7 @@
         <v>2342014</v>
       </c>
       <c r="B96" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C96" t="s">
         <v>157</v>
@@ -6285,7 +6297,7 @@
         <v>21</v>
       </c>
       <c r="F96" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G96" t="s">
         <v>40</v>
@@ -6306,7 +6318,7 @@
         <v>27</v>
       </c>
       <c r="N96" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P96" t="s">
         <v>28</v>
@@ -6320,7 +6332,7 @@
         <v>5</v>
       </c>
       <c r="B97" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C97" t="s">
         <v>157</v>
@@ -6332,7 +6344,7 @@
         <v>21</v>
       </c>
       <c r="F97" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G97" t="s">
         <v>40</v>
@@ -6347,13 +6359,13 @@
         <v>42</v>
       </c>
       <c r="K97" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M97" t="s">
         <v>27</v>
       </c>
       <c r="N97" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P97" t="s">
         <v>28</v>
@@ -6367,7 +6379,7 @@
         <v>2343027</v>
       </c>
       <c r="B98" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C98" t="s">
         <v>157</v>
@@ -6379,7 +6391,7 @@
         <v>35</v>
       </c>
       <c r="F98" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G98" t="s">
         <v>40</v>
@@ -6394,13 +6406,13 @@
         <v>25</v>
       </c>
       <c r="K98" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M98" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N98" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P98" t="s">
         <v>28</v>
@@ -6414,7 +6426,7 @@
         <v>2343027</v>
       </c>
       <c r="B99" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C99" t="s">
         <v>157</v>
@@ -6426,7 +6438,7 @@
         <v>35</v>
       </c>
       <c r="F99" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G99" t="s">
         <v>40</v>
@@ -6441,13 +6453,13 @@
         <v>25</v>
       </c>
       <c r="K99" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M99" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N99" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P99" t="s">
         <v>28</v>
@@ -6461,7 +6473,7 @@
         <v>2343027</v>
       </c>
       <c r="B100" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C100" t="s">
         <v>157</v>
@@ -6473,7 +6485,7 @@
         <v>35</v>
       </c>
       <c r="F100" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G100" t="s">
         <v>40</v>
@@ -6488,10 +6500,10 @@
         <v>25</v>
       </c>
       <c r="K100" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M100" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N100" s="3"/>
       <c r="P100" t="s">
@@ -6506,7 +6518,7 @@
         <v>2347001</v>
       </c>
       <c r="B101" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C101" t="s">
         <v>157</v>
@@ -6533,16 +6545,16 @@
         <v>42</v>
       </c>
       <c r="K101" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L101" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M101" t="s">
         <v>27</v>
       </c>
       <c r="N101" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P101" t="s">
         <v>28</v>
@@ -6556,7 +6568,7 @@
         <v>2347003</v>
       </c>
       <c r="B102" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C102" t="s">
         <v>157</v>
@@ -6586,10 +6598,13 @@
         <v>177</v>
       </c>
       <c r="L102" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M102" t="s">
         <v>27</v>
+      </c>
+      <c r="N102" t="s">
+        <v>227</v>
       </c>
       <c r="P102" t="s">
         <v>28</v>
@@ -6603,7 +6618,7 @@
         <v>2347005</v>
       </c>
       <c r="B103" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C103" t="s">
         <v>157</v>
@@ -6615,7 +6630,7 @@
         <v>21</v>
       </c>
       <c r="F103" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G103" t="s">
         <v>40</v>
@@ -6630,16 +6645,16 @@
         <v>42</v>
       </c>
       <c r="K103" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L103" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M103" t="s">
         <v>27</v>
       </c>
       <c r="N103" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="P103" t="s">
         <v>28</v>
@@ -6653,7 +6668,7 @@
         <v>2347006</v>
       </c>
       <c r="B104" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C104" t="s">
         <v>157</v>
@@ -6665,7 +6680,7 @@
         <v>35</v>
       </c>
       <c r="F104" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="G104" t="s">
         <v>40</v>
@@ -6680,13 +6695,16 @@
         <v>42</v>
       </c>
       <c r="K104" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="L104" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M104" t="s">
         <v>27</v>
+      </c>
+      <c r="N104" t="s">
+        <v>227</v>
       </c>
       <c r="P104" t="s">
         <v>28</v>
@@ -6700,7 +6718,7 @@
         <v>2347007</v>
       </c>
       <c r="B105" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C105" t="s">
         <v>157</v>
@@ -6727,16 +6745,16 @@
         <v>42</v>
       </c>
       <c r="K105" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L105" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="M105" t="s">
         <v>27</v>
       </c>
       <c r="N105" s="3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="P105" t="s">
         <v>28</v>
@@ -6750,7 +6768,7 @@
         <v>2347013</v>
       </c>
       <c r="B106" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C106" t="s">
         <v>157</v>
@@ -6762,7 +6780,7 @@
         <v>21</v>
       </c>
       <c r="F106" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="G106" t="s">
         <v>40</v>
@@ -6777,16 +6795,16 @@
         <v>42</v>
       </c>
       <c r="K106" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="L106" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="M106" t="s">
         <v>27</v>
       </c>
       <c r="N106" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P106" t="s">
         <v>28</v>
@@ -6800,7 +6818,7 @@
         <v>2347014</v>
       </c>
       <c r="B107" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C107" t="s">
         <v>157</v>
@@ -6812,7 +6830,7 @@
         <v>35</v>
       </c>
       <c r="F107" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G107" t="s">
         <v>40</v>
@@ -6827,10 +6845,10 @@
         <v>42</v>
       </c>
       <c r="K107" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L107" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="M107" t="s">
         <v>27</v>
@@ -6847,7 +6865,7 @@
         <v>2347017</v>
       </c>
       <c r="B108" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C108" t="s">
         <v>157</v>
@@ -6859,7 +6877,7 @@
         <v>35</v>
       </c>
       <c r="F108" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G108" t="s">
         <v>23</v>
@@ -6874,16 +6892,16 @@
         <v>42</v>
       </c>
       <c r="K108" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="L108" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="M108" t="s">
         <v>27</v>
       </c>
       <c r="N108" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="P108" t="s">
         <v>28</v>
@@ -6897,7 +6915,7 @@
         <v>2347030</v>
       </c>
       <c r="B109" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C109" t="s">
         <v>157</v>
@@ -6909,7 +6927,7 @@
         <v>35</v>
       </c>
       <c r="F109" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="G109" t="s">
         <v>40</v>
@@ -6924,16 +6942,16 @@
         <v>42</v>
       </c>
       <c r="K109" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L109" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="M109" t="s">
         <v>27</v>
       </c>
       <c r="N109" s="3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="P109" t="s">
         <v>28</v>
@@ -6947,7 +6965,7 @@
         <v>2347021</v>
       </c>
       <c r="B110" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C110" t="s">
         <v>157</v>
@@ -6959,7 +6977,7 @@
         <v>21</v>
       </c>
       <c r="F110" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="G110" t="s">
         <v>40</v>
@@ -6974,16 +6992,16 @@
         <v>42</v>
       </c>
       <c r="K110" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="L110" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M110" t="s">
         <v>27</v>
       </c>
       <c r="N110" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P110" t="s">
         <v>28</v>
@@ -6997,7 +7015,7 @@
         <v>2347022</v>
       </c>
       <c r="B111" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C111" t="s">
         <v>157</v>
@@ -7009,7 +7027,7 @@
         <v>21</v>
       </c>
       <c r="F111" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="G111" t="s">
         <v>40</v>
@@ -7024,16 +7042,16 @@
         <v>42</v>
       </c>
       <c r="K111" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="L111" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="M111" t="s">
         <v>27</v>
       </c>
       <c r="N111" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="O111" s="1"/>
       <c r="P111" t="s">
@@ -7048,7 +7066,7 @@
         <v>2347024</v>
       </c>
       <c r="B112" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C112" t="s">
         <v>157</v>
@@ -7060,7 +7078,7 @@
         <v>21</v>
       </c>
       <c r="F112" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="G112" t="s">
         <v>40</v>
@@ -7075,16 +7093,16 @@
         <v>42</v>
       </c>
       <c r="K112" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L112" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M112" t="s">
         <v>27</v>
       </c>
       <c r="N112" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P112" t="s">
         <v>28</v>
@@ -7098,7 +7116,7 @@
         <v>2347026</v>
       </c>
       <c r="B113" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C113" t="s">
         <v>157</v>
@@ -7110,7 +7128,7 @@
         <v>35</v>
       </c>
       <c r="F113" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="G113" t="s">
         <v>40</v>
@@ -7125,16 +7143,16 @@
         <v>42</v>
       </c>
       <c r="K113" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="L113" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M113" t="s">
         <v>27</v>
       </c>
       <c r="N113" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="P113" t="s">
         <v>28</v>
@@ -7148,7 +7166,7 @@
         <v>2347027</v>
       </c>
       <c r="B114" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C114" t="s">
         <v>157</v>
@@ -7160,7 +7178,7 @@
         <v>35</v>
       </c>
       <c r="F114" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G114" t="s">
         <v>40</v>
@@ -7175,16 +7193,16 @@
         <v>42</v>
       </c>
       <c r="K114" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L114" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="M114" t="s">
         <v>27</v>
       </c>
       <c r="N114" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="P114" t="s">
         <v>28</v>
@@ -7198,7 +7216,7 @@
         <v>2347029</v>
       </c>
       <c r="B115" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C115" t="s">
         <v>157</v>
@@ -7210,7 +7228,7 @@
         <v>35</v>
       </c>
       <c r="F115" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G115" t="s">
         <v>40</v>
@@ -7225,13 +7243,13 @@
         <v>42</v>
       </c>
       <c r="K115" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="L115" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="M115" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P115" t="s">
         <v>28</v>
@@ -7245,7 +7263,7 @@
         <v>2347031</v>
       </c>
       <c r="B116" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C116" t="s">
         <v>157</v>
@@ -7257,7 +7275,7 @@
         <v>21</v>
       </c>
       <c r="F116" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="G116" t="s">
         <v>40</v>
@@ -7272,16 +7290,16 @@
         <v>42</v>
       </c>
       <c r="K116" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L116" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="M116" t="s">
         <v>27</v>
       </c>
       <c r="N116" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="P116" t="s">
         <v>28</v>
@@ -7295,7 +7313,7 @@
         <v>2347038</v>
       </c>
       <c r="B117" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C117" t="s">
         <v>157</v>
@@ -7307,10 +7325,10 @@
         <v>21</v>
       </c>
       <c r="F117" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G117" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="H117" s="2">
         <v>60</v>
@@ -7322,16 +7340,16 @@
         <v>42</v>
       </c>
       <c r="K117" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="L117" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="M117" t="s">
         <v>27</v>
       </c>
       <c r="N117" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="P117" t="s">
         <v>28</v>
@@ -7345,7 +7363,7 @@
         <v>2361002</v>
       </c>
       <c r="B118" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C118" t="s">
         <v>157</v>
@@ -7372,7 +7390,7 @@
         <v>42</v>
       </c>
       <c r="K118" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M118" t="s">
         <v>27</v>
@@ -7389,7 +7407,7 @@
         <v>2361002</v>
       </c>
       <c r="B119" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C119" t="s">
         <v>157</v>
@@ -7416,7 +7434,7 @@
         <v>42</v>
       </c>
       <c r="K119" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="M119" t="s">
         <v>27</v>
@@ -7433,7 +7451,7 @@
         <v>2361002</v>
       </c>
       <c r="B120" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C120" t="s">
         <v>157</v>
@@ -7460,7 +7478,7 @@
         <v>42</v>
       </c>
       <c r="K120" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="M120" t="s">
         <v>27</v>
@@ -7477,7 +7495,7 @@
         <v>2361004</v>
       </c>
       <c r="B121" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C121" t="s">
         <v>157</v>
@@ -7504,7 +7522,7 @@
         <v>42</v>
       </c>
       <c r="K121" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="M121" t="s">
         <v>27</v>
@@ -7521,7 +7539,7 @@
         <v>2393002</v>
       </c>
       <c r="B122" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C122" t="s">
         <v>157</v>
@@ -7548,10 +7566,10 @@
         <v>42</v>
       </c>
       <c r="K122" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="L122" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="M122" t="s">
         <v>27</v>
@@ -7568,7 +7586,7 @@
         <v>2393002</v>
       </c>
       <c r="B123" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C123" t="s">
         <v>157</v>
@@ -7589,16 +7607,16 @@
         <v>20</v>
       </c>
       <c r="I123" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="J123" t="s">
         <v>42</v>
       </c>
       <c r="K123" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L123" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="M123" t="s">
         <v>27</v>
@@ -7615,7 +7633,7 @@
         <v>2393002</v>
       </c>
       <c r="B124" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C124" t="s">
         <v>157</v>
@@ -7636,16 +7654,16 @@
         <v>20</v>
       </c>
       <c r="I124" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="J124" t="s">
         <v>42</v>
       </c>
       <c r="K124" t="s">
+        <v>287</v>
+      </c>
+      <c r="L124" t="s">
         <v>285</v>
-      </c>
-      <c r="L124" t="s">
-        <v>283</v>
       </c>
       <c r="M124" t="s">
         <v>27</v>
@@ -7662,7 +7680,7 @@
         <v>2394004</v>
       </c>
       <c r="B125" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C125" t="s">
         <v>157</v>
@@ -7689,10 +7707,10 @@
         <v>25</v>
       </c>
       <c r="K125" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L125" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="M125" t="s">
         <v>27</v>
@@ -7709,7 +7727,7 @@
         <v>2394004</v>
       </c>
       <c r="B126" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C126" t="s">
         <v>157</v>
@@ -7736,10 +7754,10 @@
         <v>25</v>
       </c>
       <c r="K126" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="L126" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="M126" t="s">
         <v>27</v>
@@ -7756,7 +7774,7 @@
         <v>2394004</v>
       </c>
       <c r="B127" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C127" t="s">
         <v>157</v>
@@ -7783,10 +7801,10 @@
         <v>25</v>
       </c>
       <c r="K127" t="s">
+        <v>292</v>
+      </c>
+      <c r="L127" t="s">
         <v>290</v>
-      </c>
-      <c r="L127" t="s">
-        <v>288</v>
       </c>
       <c r="M127" t="s">
         <v>27</v>
@@ -7803,7 +7821,7 @@
         <v>2395003</v>
       </c>
       <c r="B128" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C128" t="s">
         <v>157</v>
@@ -7830,10 +7848,10 @@
         <v>42</v>
       </c>
       <c r="K128" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L128" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="M128" t="s">
         <v>27</v>
@@ -7850,7 +7868,7 @@
         <v>2395003</v>
       </c>
       <c r="B129" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C129" t="s">
         <v>157</v>
@@ -7877,10 +7895,10 @@
         <v>42</v>
       </c>
       <c r="K129" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="L129" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="M129" t="s">
         <v>27</v>
@@ -7897,7 +7915,7 @@
         <v>2395003</v>
       </c>
       <c r="B130" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C130" t="s">
         <v>157</v>
@@ -7924,10 +7942,10 @@
         <v>42</v>
       </c>
       <c r="K130" t="s">
+        <v>297</v>
+      </c>
+      <c r="L130" t="s">
         <v>295</v>
-      </c>
-      <c r="L130" t="s">
-        <v>293</v>
       </c>
       <c r="M130" t="s">
         <v>27</v>
@@ -7944,7 +7962,7 @@
         <v>2396001</v>
       </c>
       <c r="B131" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C131" t="s">
         <v>157</v>
@@ -7971,10 +7989,10 @@
         <v>25</v>
       </c>
       <c r="K131" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L131" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="M131" t="s">
         <v>27</v>
@@ -7991,7 +8009,7 @@
         <v>2396001</v>
       </c>
       <c r="B132" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C132" t="s">
         <v>157</v>
@@ -8018,10 +8036,10 @@
         <v>25</v>
       </c>
       <c r="K132" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="L132" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M132" t="s">
         <v>27</v>
@@ -8038,7 +8056,7 @@
         <v>2396001</v>
       </c>
       <c r="B133" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C133" t="s">
         <v>157</v>
@@ -8065,10 +8083,10 @@
         <v>25</v>
       </c>
       <c r="K133" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="L133" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M133" t="s">
         <v>27</v>
@@ -8085,7 +8103,7 @@
         <v>2397003</v>
       </c>
       <c r="B134" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C134" t="s">
         <v>157</v>
@@ -8112,10 +8130,10 @@
         <v>25</v>
       </c>
       <c r="K134" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="L134" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="M134" t="s">
         <v>27</v>
@@ -8132,7 +8150,7 @@
         <v>2397003</v>
       </c>
       <c r="B135" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C135" t="s">
         <v>157</v>
@@ -8159,10 +8177,10 @@
         <v>25</v>
       </c>
       <c r="K135" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="L135" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="M135" t="s">
         <v>27</v>
@@ -8179,7 +8197,7 @@
         <v>2397003</v>
       </c>
       <c r="B136" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C136" t="s">
         <v>157</v>
@@ -8206,10 +8224,10 @@
         <v>25</v>
       </c>
       <c r="K136" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="L136" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="M136" t="s">
         <v>27</v>
@@ -8226,7 +8244,7 @@
         <v>2397008</v>
       </c>
       <c r="B137" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C137" t="s">
         <v>157</v>
@@ -8253,10 +8271,10 @@
         <v>25</v>
       </c>
       <c r="K137" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="L137" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="M137" t="s">
         <v>27</v>
@@ -8273,7 +8291,7 @@
         <v>2397008</v>
       </c>
       <c r="B138" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C138" t="s">
         <v>157</v>
@@ -8300,10 +8318,10 @@
         <v>25</v>
       </c>
       <c r="K138" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="L138" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="M138" t="s">
         <v>27</v>
@@ -8320,7 +8338,7 @@
         <v>2397008</v>
       </c>
       <c r="B139" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C139" t="s">
         <v>157</v>
@@ -8347,10 +8365,10 @@
         <v>25</v>
       </c>
       <c r="K139" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L139" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="M139" t="s">
         <v>27</v>
@@ -8367,7 +8385,7 @@
         <v>2398001</v>
       </c>
       <c r="B140" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C140" t="s">
         <v>157</v>
@@ -8394,16 +8412,16 @@
         <v>42</v>
       </c>
       <c r="K140" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="L140" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M140" t="s">
         <v>27</v>
       </c>
       <c r="N140" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="P140" t="s">
         <v>28</v>
@@ -8417,7 +8435,7 @@
         <v>2398001</v>
       </c>
       <c r="B141" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C141" t="s">
         <v>157</v>
@@ -8444,16 +8462,16 @@
         <v>42</v>
       </c>
       <c r="K141" t="s">
+        <v>319</v>
+      </c>
+      <c r="L141" t="s">
         <v>317</v>
       </c>
-      <c r="L141" t="s">
-        <v>315</v>
-      </c>
       <c r="M141" t="s">
         <v>27</v>
       </c>
       <c r="N141" s="4" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="P141" t="s">
         <v>28</v>
@@ -8467,7 +8485,7 @@
         <v>2398001</v>
       </c>
       <c r="B142" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C142" t="s">
         <v>157</v>
@@ -8494,16 +8512,16 @@
         <v>42</v>
       </c>
       <c r="K142" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L142" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="M142" t="s">
         <v>27</v>
       </c>
       <c r="N142" s="4" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="P142" t="s">
         <v>28</v>
@@ -8517,7 +8535,7 @@
         <v>2398006</v>
       </c>
       <c r="B143" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C143" t="s">
         <v>157</v>
@@ -8544,10 +8562,10 @@
         <v>42</v>
       </c>
       <c r="K143" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L143" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="M143" t="s">
         <v>27</v>
@@ -8564,7 +8582,7 @@
         <v>2398006</v>
       </c>
       <c r="B144" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C144" t="s">
         <v>157</v>
@@ -8591,10 +8609,10 @@
         <v>42</v>
       </c>
       <c r="K144" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="L144" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="M144" t="s">
         <v>27</v>
@@ -8611,7 +8629,7 @@
         <v>2398006</v>
       </c>
       <c r="B145" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C145" t="s">
         <v>157</v>
@@ -8638,10 +8656,10 @@
         <v>42</v>
       </c>
       <c r="K145" t="s">
+        <v>325</v>
+      </c>
+      <c r="L145" t="s">
         <v>323</v>
-      </c>
-      <c r="L145" t="s">
-        <v>321</v>
       </c>
       <c r="M145" t="s">
         <v>27</v>
@@ -8658,7 +8676,7 @@
         <v>2398013</v>
       </c>
       <c r="B146" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C146" t="s">
         <v>157</v>
@@ -8670,7 +8688,7 @@
         <v>21</v>
       </c>
       <c r="F146" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G146" t="s">
         <v>23</v>
@@ -8685,10 +8703,10 @@
         <v>25</v>
       </c>
       <c r="K146" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L146" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="M146" t="s">
         <v>27</v>
@@ -8705,7 +8723,7 @@
         <v>2398013</v>
       </c>
       <c r="B147" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C147" t="s">
         <v>157</v>
@@ -8717,7 +8735,7 @@
         <v>21</v>
       </c>
       <c r="F147" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G147" t="s">
         <v>23</v>
@@ -8732,10 +8750,10 @@
         <v>25</v>
       </c>
       <c r="K147" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="L147" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="M147" t="s">
         <v>27</v>
@@ -8752,7 +8770,7 @@
         <v>2398013</v>
       </c>
       <c r="B148" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C148" t="s">
         <v>157</v>
@@ -8764,7 +8782,7 @@
         <v>21</v>
       </c>
       <c r="F148" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G148" t="s">
         <v>23</v>
@@ -8779,7 +8797,7 @@
         <v>25</v>
       </c>
       <c r="K148" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M148" t="s">
         <v>27</v>
@@ -8796,7 +8814,7 @@
         <v>2399003</v>
       </c>
       <c r="B149" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C149" t="s">
         <v>157</v>
@@ -8823,10 +8841,10 @@
         <v>42</v>
       </c>
       <c r="K149" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L149" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="M149" t="s">
         <v>27</v>
@@ -8843,7 +8861,7 @@
         <v>2399003</v>
       </c>
       <c r="B150" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C150" t="s">
         <v>157</v>
@@ -8870,10 +8888,10 @@
         <v>42</v>
       </c>
       <c r="K150" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="L150" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="M150" t="s">
         <v>27</v>
@@ -8890,7 +8908,7 @@
         <v>2399003</v>
       </c>
       <c r="B151" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C151" t="s">
         <v>157</v>
@@ -8917,10 +8935,10 @@
         <v>42</v>
       </c>
       <c r="K151" t="s">
+        <v>334</v>
+      </c>
+      <c r="L151" t="s">
         <v>332</v>
-      </c>
-      <c r="L151" t="s">
-        <v>330</v>
       </c>
       <c r="M151" t="s">
         <v>27</v>
@@ -8937,7 +8955,7 @@
         <v>2399010</v>
       </c>
       <c r="B152" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C152" t="s">
         <v>157</v>
@@ -8964,10 +8982,10 @@
         <v>42</v>
       </c>
       <c r="K152" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="L152" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="M152" t="s">
         <v>27</v>
@@ -8984,7 +9002,7 @@
         <v>2399010</v>
       </c>
       <c r="B153" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C153" t="s">
         <v>157</v>
@@ -9011,10 +9029,10 @@
         <v>42</v>
       </c>
       <c r="K153" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="L153" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="M153" t="s">
         <v>27</v>
@@ -9031,7 +9049,7 @@
         <v>2399010</v>
       </c>
       <c r="B154" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C154" t="s">
         <v>157</v>
@@ -9058,10 +9076,10 @@
         <v>42</v>
       </c>
       <c r="K154" t="s">
+        <v>338</v>
+      </c>
+      <c r="L154" t="s">
         <v>336</v>
-      </c>
-      <c r="L154" t="s">
-        <v>334</v>
       </c>
       <c r="M154" t="s">
         <v>27</v>
@@ -9078,7 +9096,7 @@
         <v>2399014</v>
       </c>
       <c r="B155" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C155" t="s">
         <v>157</v>
@@ -9105,10 +9123,10 @@
         <v>25</v>
       </c>
       <c r="K155" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L155" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="M155" t="s">
         <v>27</v>
@@ -9125,7 +9143,7 @@
         <v>2399014</v>
       </c>
       <c r="B156" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C156" t="s">
         <v>157</v>
@@ -9152,10 +9170,10 @@
         <v>25</v>
       </c>
       <c r="K156" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L156" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="M156" t="s">
         <v>27</v>
@@ -9172,7 +9190,7 @@
         <v>2399014</v>
       </c>
       <c r="B157" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C157" t="s">
         <v>157</v>
@@ -9199,7 +9217,7 @@
         <v>25</v>
       </c>
       <c r="K157" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="M157" t="s">
         <v>27</v>
@@ -9216,7 +9234,7 @@
         <v>2400003</v>
       </c>
       <c r="B158" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C158" t="s">
         <v>157</v>
@@ -9243,16 +9261,16 @@
         <v>42</v>
       </c>
       <c r="K158" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L158" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="M158" t="s">
         <v>27</v>
       </c>
       <c r="N158" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="P158" t="s">
         <v>28</v>
@@ -9266,7 +9284,7 @@
         <v>2400003</v>
       </c>
       <c r="B159" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C159" t="s">
         <v>157</v>
@@ -9293,16 +9311,16 @@
         <v>42</v>
       </c>
       <c r="K159" t="s">
+        <v>347</v>
+      </c>
+      <c r="L159" t="s">
         <v>345</v>
       </c>
-      <c r="L159" t="s">
-        <v>343</v>
-      </c>
       <c r="M159" t="s">
         <v>27</v>
       </c>
       <c r="N159" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="P159" t="s">
         <v>28</v>
@@ -9316,7 +9334,7 @@
         <v>2400003</v>
       </c>
       <c r="B160" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C160" t="s">
         <v>157</v>
@@ -9343,16 +9361,16 @@
         <v>42</v>
       </c>
       <c r="K160" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="L160" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="M160" t="s">
         <v>27</v>
       </c>
       <c r="N160" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="P160" t="s">
         <v>28</v>
@@ -9366,7 +9384,7 @@
         <v>2400008</v>
       </c>
       <c r="B161" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C161" t="s">
         <v>157</v>
@@ -9393,10 +9411,10 @@
         <v>42</v>
       </c>
       <c r="K161" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="L161" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="M161" t="s">
         <v>27</v>
@@ -9413,7 +9431,7 @@
         <v>2400008</v>
       </c>
       <c r="B162" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C162" t="s">
         <v>157</v>
@@ -9440,10 +9458,10 @@
         <v>42</v>
       </c>
       <c r="K162" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="L162" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="M162" t="s">
         <v>27</v>
@@ -9460,7 +9478,7 @@
         <v>2400008</v>
       </c>
       <c r="B163" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C163" t="s">
         <v>157</v>
@@ -9487,10 +9505,10 @@
         <v>42</v>
       </c>
       <c r="K163" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="L163" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="M163" t="s">
         <v>27</v>
@@ -9507,7 +9525,7 @@
         <v>2400012</v>
       </c>
       <c r="B164" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C164" t="s">
         <v>157</v>
@@ -9519,7 +9537,7 @@
         <v>21</v>
       </c>
       <c r="F164" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G164" t="s">
         <v>23</v>
@@ -9534,16 +9552,16 @@
         <v>25</v>
       </c>
       <c r="K164" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="L164" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="M164" t="s">
         <v>27</v>
       </c>
       <c r="N164" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="P164" t="s">
         <v>28</v>
@@ -9557,7 +9575,7 @@
         <v>2400012</v>
       </c>
       <c r="B165" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C165" t="s">
         <v>157</v>
@@ -9569,7 +9587,7 @@
         <v>21</v>
       </c>
       <c r="F165" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G165" t="s">
         <v>23</v>
@@ -9584,16 +9602,16 @@
         <v>25</v>
       </c>
       <c r="K165" s="3" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="L165" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="M165" t="s">
         <v>27</v>
       </c>
       <c r="N165" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="P165" t="s">
         <v>28</v>
@@ -9607,7 +9625,7 @@
         <v>2400012</v>
       </c>
       <c r="B166" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C166" t="s">
         <v>157</v>
@@ -9619,7 +9637,7 @@
         <v>21</v>
       </c>
       <c r="F166" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G166" t="s">
         <v>23</v>
@@ -9634,13 +9652,13 @@
         <v>25</v>
       </c>
       <c r="K166" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="M166" t="s">
         <v>27</v>
       </c>
       <c r="N166" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="P166" t="s">
         <v>28</v>
@@ -9654,7 +9672,7 @@
         <v>2401001</v>
       </c>
       <c r="B167" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C167" t="s">
         <v>157</v>
@@ -9681,10 +9699,10 @@
         <v>25</v>
       </c>
       <c r="K167" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="L167" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="M167" t="s">
         <v>27</v>
@@ -9701,7 +9719,7 @@
         <v>2401001</v>
       </c>
       <c r="B168" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C168" t="s">
         <v>157</v>
@@ -9728,10 +9746,10 @@
         <v>25</v>
       </c>
       <c r="K168" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="L168" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="M168" t="s">
         <v>27</v>
@@ -9748,7 +9766,7 @@
         <v>2401001</v>
       </c>
       <c r="B169" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C169" t="s">
         <v>157</v>
@@ -9775,10 +9793,10 @@
         <v>25</v>
       </c>
       <c r="K169" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="L169" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="M169" t="s">
         <v>27</v>
@@ -9795,7 +9813,7 @@
         <v>2401007</v>
       </c>
       <c r="B170" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C170" t="s">
         <v>157</v>
@@ -9822,10 +9840,10 @@
         <v>25</v>
       </c>
       <c r="K170" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="L170" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="M170" t="s">
         <v>27</v>
@@ -9842,7 +9860,7 @@
         <v>2401007</v>
       </c>
       <c r="B171" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C171" t="s">
         <v>157</v>
@@ -9869,10 +9887,10 @@
         <v>25</v>
       </c>
       <c r="K171" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="L171" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="M171" t="s">
         <v>27</v>
@@ -9889,7 +9907,7 @@
         <v>2401007</v>
       </c>
       <c r="B172" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C172" t="s">
         <v>157</v>
@@ -9916,10 +9934,10 @@
         <v>25</v>
       </c>
       <c r="K172" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="L172" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="M172" t="s">
         <v>27</v>
@@ -9936,7 +9954,7 @@
         <v>2401013</v>
       </c>
       <c r="B173" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C173" t="s">
         <v>157</v>
@@ -9948,7 +9966,7 @@
         <v>21</v>
       </c>
       <c r="F173" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="G173" t="s">
         <v>40</v>
@@ -9963,16 +9981,16 @@
         <v>42</v>
       </c>
       <c r="K173" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="L173" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="M173" t="s">
         <v>27</v>
       </c>
       <c r="N173" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="P173" t="s">
         <v>28</v>
@@ -9986,7 +10004,7 @@
         <v>2401013</v>
       </c>
       <c r="B174" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C174" t="s">
         <v>157</v>
@@ -9998,7 +10016,7 @@
         <v>21</v>
       </c>
       <c r="F174" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="G174" t="s">
         <v>40</v>
@@ -10013,16 +10031,16 @@
         <v>42</v>
       </c>
       <c r="K174" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="L174" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="M174" t="s">
         <v>27</v>
       </c>
       <c r="N174" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="P174" t="s">
         <v>28</v>
@@ -10036,7 +10054,7 @@
         <v>2401013</v>
       </c>
       <c r="B175" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C175" t="s">
         <v>157</v>
@@ -10048,7 +10066,7 @@
         <v>21</v>
       </c>
       <c r="F175" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="G175" t="s">
         <v>40</v>
@@ -10063,16 +10081,16 @@
         <v>42</v>
       </c>
       <c r="K175" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="L175" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="M175" t="s">
         <v>27</v>
       </c>
       <c r="N175" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="P175" t="s">
         <v>28</v>
@@ -10086,7 +10104,7 @@
         <v>2401018</v>
       </c>
       <c r="B176" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C176" t="s">
         <v>157</v>
@@ -10098,7 +10116,7 @@
         <v>35</v>
       </c>
       <c r="F176" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="G176" t="s">
         <v>40</v>
@@ -10113,10 +10131,10 @@
         <v>42</v>
       </c>
       <c r="K176" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="L176" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="M176" t="s">
         <v>27</v>
@@ -10133,7 +10151,7 @@
         <v>2401018</v>
       </c>
       <c r="B177" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C177" t="s">
         <v>157</v>
@@ -10145,7 +10163,7 @@
         <v>35</v>
       </c>
       <c r="F177" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="G177" t="s">
         <v>40</v>
@@ -10160,10 +10178,10 @@
         <v>42</v>
       </c>
       <c r="K177" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="L177" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="M177" t="s">
         <v>27</v>
@@ -10180,7 +10198,7 @@
         <v>2401018</v>
       </c>
       <c r="B178" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C178" t="s">
         <v>157</v>
@@ -10192,7 +10210,7 @@
         <v>35</v>
       </c>
       <c r="F178" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="G178" t="s">
         <v>40</v>
@@ -10201,16 +10219,16 @@
         <v>4</v>
       </c>
       <c r="I178" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="J178" t="s">
         <v>42</v>
       </c>
       <c r="K178" t="s">
+        <v>382</v>
+      </c>
+      <c r="L178" t="s">
         <v>379</v>
-      </c>
-      <c r="L178" t="s">
-        <v>376</v>
       </c>
       <c r="M178" t="s">
         <v>27</v>
@@ -10227,7 +10245,7 @@
         <v>2401018</v>
       </c>
       <c r="B179" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C179" t="s">
         <v>157</v>
@@ -10239,7 +10257,7 @@
         <v>35</v>
       </c>
       <c r="F179" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="G179" t="s">
         <v>40</v>
@@ -10254,10 +10272,10 @@
         <v>42</v>
       </c>
       <c r="K179" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="L179" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="M179" t="s">
         <v>27</v>
@@ -10274,7 +10292,7 @@
         <v>2401018</v>
       </c>
       <c r="B180" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C180" t="s">
         <v>157</v>
@@ -10286,7 +10304,7 @@
         <v>35</v>
       </c>
       <c r="F180" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="G180" t="s">
         <v>40</v>
@@ -10295,16 +10313,16 @@
         <v>4</v>
       </c>
       <c r="I180" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="J180" t="s">
         <v>42</v>
       </c>
       <c r="K180" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="L180" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="M180" t="s">
         <v>27</v>
@@ -10321,7 +10339,7 @@
         <v>2401018</v>
       </c>
       <c r="B181" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C181" t="s">
         <v>157</v>
@@ -10333,7 +10351,7 @@
         <v>35</v>
       </c>
       <c r="F181" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="G181" t="s">
         <v>40</v>
@@ -10342,16 +10360,16 @@
         <v>4</v>
       </c>
       <c r="I181" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="J181" t="s">
         <v>42</v>
       </c>
       <c r="K181" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="L181" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="M181" t="s">
         <v>27</v>
@@ -10368,7 +10386,7 @@
         <v>2401018</v>
       </c>
       <c r="B182" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C182" t="s">
         <v>157</v>
@@ -10380,7 +10398,7 @@
         <v>35</v>
       </c>
       <c r="F182" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="G182" t="s">
         <v>40</v>
@@ -10389,16 +10407,16 @@
         <v>4</v>
       </c>
       <c r="I182" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="J182" t="s">
         <v>42</v>
       </c>
       <c r="K182" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="L182" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="M182" t="s">
         <v>27</v>
@@ -10415,7 +10433,7 @@
         <v>2402003</v>
       </c>
       <c r="B183" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C183" t="s">
         <v>157</v>
@@ -10442,16 +10460,16 @@
         <v>25</v>
       </c>
       <c r="K183" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="L183" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="M183" t="s">
         <v>27</v>
       </c>
       <c r="N183" s="4" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="P183" t="s">
         <v>28</v>
@@ -10465,7 +10483,7 @@
         <v>2402003</v>
       </c>
       <c r="B184" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C184" t="s">
         <v>157</v>
@@ -10492,16 +10510,16 @@
         <v>25</v>
       </c>
       <c r="K184" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="L184" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="M184" t="s">
         <v>27</v>
       </c>
       <c r="N184" s="4" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="P184" t="s">
         <v>28</v>
@@ -10515,7 +10533,7 @@
         <v>2402003</v>
       </c>
       <c r="B185" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C185" t="s">
         <v>157</v>
@@ -10542,16 +10560,16 @@
         <v>25</v>
       </c>
       <c r="K185" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="L185" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="M185" t="s">
         <v>27</v>
       </c>
       <c r="N185" s="4" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="P185" t="s">
         <v>28</v>
@@ -10565,7 +10583,7 @@
         <v>2402008</v>
       </c>
       <c r="B186" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C186" t="s">
         <v>157</v>
@@ -10592,16 +10610,16 @@
         <v>25</v>
       </c>
       <c r="K186" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="L186" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="M186" t="s">
         <v>27</v>
       </c>
       <c r="N186" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="P186" t="s">
         <v>28</v>
@@ -10615,7 +10633,7 @@
         <v>2402008</v>
       </c>
       <c r="B187" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C187" t="s">
         <v>157</v>
@@ -10642,16 +10660,16 @@
         <v>25</v>
       </c>
       <c r="K187" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="L187" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="M187" t="s">
         <v>27</v>
       </c>
       <c r="N187" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="P187" t="s">
         <v>28</v>
@@ -10665,7 +10683,7 @@
         <v>2402008</v>
       </c>
       <c r="B188" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C188" t="s">
         <v>157</v>
@@ -10692,16 +10710,16 @@
         <v>25</v>
       </c>
       <c r="K188" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="L188" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="M188" t="s">
         <v>27</v>
       </c>
       <c r="N188" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="P188" t="s">
         <v>28</v>
@@ -10715,7 +10733,7 @@
         <v>2402015</v>
       </c>
       <c r="B189" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C189" t="s">
         <v>157</v>
@@ -10727,7 +10745,7 @@
         <v>21</v>
       </c>
       <c r="F189" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G189" t="s">
         <v>23</v>
@@ -10742,13 +10760,13 @@
         <v>42</v>
       </c>
       <c r="K189" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="M189" t="s">
         <v>27</v>
       </c>
       <c r="N189" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="P189" t="s">
         <v>28</v>
@@ -10762,7 +10780,7 @@
         <v>2402015</v>
       </c>
       <c r="B190" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C190" t="s">
         <v>157</v>
@@ -10774,7 +10792,7 @@
         <v>21</v>
       </c>
       <c r="F190" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G190" t="s">
         <v>23</v>
@@ -10789,13 +10807,13 @@
         <v>42</v>
       </c>
       <c r="K190" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="M190" t="s">
         <v>27</v>
       </c>
       <c r="N190" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="P190" t="s">
         <v>28</v>
@@ -10809,7 +10827,7 @@
         <v>2402015</v>
       </c>
       <c r="B191" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C191" t="s">
         <v>157</v>
@@ -10821,7 +10839,7 @@
         <v>21</v>
       </c>
       <c r="F191" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G191" t="s">
         <v>23</v>
@@ -10836,7 +10854,7 @@
         <v>42</v>
       </c>
       <c r="K191" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="M191" t="s">
         <v>27</v>
@@ -10854,7 +10872,7 @@
         <v>2403004</v>
       </c>
       <c r="B192" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C192" t="s">
         <v>157</v>
@@ -10881,16 +10899,16 @@
         <v>42</v>
       </c>
       <c r="K192" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="L192" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="M192" t="s">
         <v>27</v>
       </c>
       <c r="N192" s="4" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="P192" t="s">
         <v>28</v>
@@ -10904,7 +10922,7 @@
         <v>2403004</v>
       </c>
       <c r="B193" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C193" t="s">
         <v>157</v>
@@ -10931,16 +10949,16 @@
         <v>42</v>
       </c>
       <c r="K193" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="L193" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="M193" t="s">
         <v>27</v>
       </c>
       <c r="N193" s="4" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="P193" t="s">
         <v>28</v>
@@ -10954,7 +10972,7 @@
         <v>2403004</v>
       </c>
       <c r="B194" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C194" t="s">
         <v>157</v>
@@ -10981,16 +10999,16 @@
         <v>42</v>
       </c>
       <c r="K194" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="L194" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="M194" t="s">
         <v>27</v>
       </c>
       <c r="N194" s="4" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="P194" t="s">
         <v>28</v>
@@ -11004,7 +11022,7 @@
         <v>2403009</v>
       </c>
       <c r="B195" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C195" t="s">
         <v>157</v>
@@ -11031,10 +11049,10 @@
         <v>42</v>
       </c>
       <c r="K195" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="L195" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="M195" t="s">
         <v>27</v>
@@ -11051,7 +11069,7 @@
         <v>2403009</v>
       </c>
       <c r="B196" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C196" t="s">
         <v>157</v>
@@ -11078,10 +11096,10 @@
         <v>42</v>
       </c>
       <c r="K196" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="L196" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="M196" t="s">
         <v>27</v>
@@ -11098,7 +11116,7 @@
         <v>2403009</v>
       </c>
       <c r="B197" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C197" t="s">
         <v>157</v>
@@ -11125,10 +11143,10 @@
         <v>42</v>
       </c>
       <c r="K197" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="L197" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="M197" t="s">
         <v>27</v>
@@ -11145,7 +11163,7 @@
         <v>2403013</v>
       </c>
       <c r="B198" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C198" t="s">
         <v>157</v>
@@ -11157,7 +11175,7 @@
         <v>21</v>
       </c>
       <c r="F198" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G198" t="s">
         <v>23</v>
@@ -11172,7 +11190,7 @@
         <v>25</v>
       </c>
       <c r="K198" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="M198" t="s">
         <v>27</v>
@@ -11189,7 +11207,7 @@
         <v>2403013</v>
       </c>
       <c r="B199" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C199" t="s">
         <v>157</v>
@@ -11201,7 +11219,7 @@
         <v>21</v>
       </c>
       <c r="F199" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G199" t="s">
         <v>23</v>
@@ -11216,7 +11234,7 @@
         <v>25</v>
       </c>
       <c r="K199" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="M199" t="s">
         <v>27</v>
@@ -11233,7 +11251,7 @@
         <v>2403013</v>
       </c>
       <c r="B200" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C200" t="s">
         <v>157</v>
@@ -11245,7 +11263,7 @@
         <v>21</v>
       </c>
       <c r="F200" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G200" t="s">
         <v>23</v>
@@ -11260,7 +11278,7 @@
         <v>25</v>
       </c>
       <c r="K200" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="M200" t="s">
         <v>27</v>
@@ -11277,7 +11295,7 @@
         <v>2404001</v>
       </c>
       <c r="B201" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C201" t="s">
         <v>157</v>
@@ -11304,16 +11322,16 @@
         <v>42</v>
       </c>
       <c r="K201" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="L201" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="M201" t="s">
         <v>27</v>
       </c>
       <c r="N201" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="P201" t="s">
         <v>28</v>
@@ -11327,7 +11345,7 @@
         <v>2404001</v>
       </c>
       <c r="B202" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C202" t="s">
         <v>157</v>
@@ -11354,16 +11372,16 @@
         <v>42</v>
       </c>
       <c r="K202" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="L202" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="M202" t="s">
         <v>27</v>
       </c>
       <c r="N202" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="P202" t="s">
         <v>28</v>
@@ -11377,7 +11395,7 @@
         <v>2404001</v>
       </c>
       <c r="B203" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C203" t="s">
         <v>157</v>
@@ -11404,16 +11422,16 @@
         <v>42</v>
       </c>
       <c r="K203" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="L203" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="M203" t="s">
         <v>27</v>
       </c>
       <c r="N203" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="P203" t="s">
         <v>28</v>
@@ -11427,7 +11445,7 @@
         <v>2404006</v>
       </c>
       <c r="B204" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C204" t="s">
         <v>157</v>
@@ -11454,16 +11472,16 @@
         <v>42</v>
       </c>
       <c r="K204" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="L204" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="M204" t="s">
         <v>27</v>
       </c>
       <c r="N204" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="P204" t="s">
         <v>28</v>
@@ -11477,7 +11495,7 @@
         <v>2404006</v>
       </c>
       <c r="B205" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C205" t="s">
         <v>157</v>
@@ -11504,16 +11522,16 @@
         <v>42</v>
       </c>
       <c r="K205" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="L205" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="M205" t="s">
         <v>27</v>
       </c>
       <c r="N205" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="P205" t="s">
         <v>28</v>
@@ -11527,7 +11545,7 @@
         <v>2404006</v>
       </c>
       <c r="B206" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C206" t="s">
         <v>157</v>
@@ -11554,16 +11572,16 @@
         <v>42</v>
       </c>
       <c r="K206" t="s">
+        <v>429</v>
+      </c>
+      <c r="L206" t="s">
         <v>426</v>
       </c>
-      <c r="L206" t="s">
-        <v>423</v>
-      </c>
       <c r="M206" t="s">
         <v>27</v>
       </c>
       <c r="N206" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="P206" t="s">
         <v>28</v>
@@ -11577,7 +11595,7 @@
         <v>2404015</v>
       </c>
       <c r="B207" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C207" t="s">
         <v>157</v>
@@ -11589,7 +11607,7 @@
         <v>21</v>
       </c>
       <c r="F207" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="G207" t="s">
         <v>40</v>
@@ -11604,13 +11622,13 @@
         <v>25</v>
       </c>
       <c r="K207" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="M207" t="s">
         <v>27</v>
       </c>
       <c r="N207" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="P207" t="s">
         <v>28</v>
@@ -11624,7 +11642,7 @@
         <v>2404015</v>
       </c>
       <c r="B208" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C208" t="s">
         <v>157</v>
@@ -11636,7 +11654,7 @@
         <v>21</v>
       </c>
       <c r="F208" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="G208" t="s">
         <v>40</v>
@@ -11645,19 +11663,19 @@
         <v>32</v>
       </c>
       <c r="I208" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="J208" t="s">
         <v>25</v>
       </c>
       <c r="K208" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="M208" t="s">
         <v>27</v>
       </c>
       <c r="N208" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="P208" t="s">
         <v>28</v>
@@ -11671,7 +11689,7 @@
         <v>2404015</v>
       </c>
       <c r="B209" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C209" t="s">
         <v>157</v>
@@ -11683,7 +11701,7 @@
         <v>21</v>
       </c>
       <c r="F209" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="G209" t="s">
         <v>40</v>
@@ -11692,19 +11710,19 @@
         <v>32</v>
       </c>
       <c r="I209" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="J209" t="s">
         <v>25</v>
       </c>
       <c r="K209" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="M209" t="s">
         <v>27</v>
       </c>
       <c r="N209" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="P209" t="s">
         <v>28</v>
@@ -11718,7 +11736,7 @@
         <v>2405001</v>
       </c>
       <c r="B210" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C210" t="s">
         <v>157</v>
@@ -11745,16 +11763,16 @@
         <v>42</v>
       </c>
       <c r="K210" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="L210" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="M210" t="s">
         <v>27</v>
       </c>
       <c r="N210" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="P210" t="s">
         <v>28</v>
@@ -11768,7 +11786,7 @@
         <v>2405001</v>
       </c>
       <c r="B211" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C211" t="s">
         <v>157</v>
@@ -11795,16 +11813,16 @@
         <v>42</v>
       </c>
       <c r="K211" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="L211" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="M211" t="s">
         <v>27</v>
       </c>
       <c r="N211" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="P211" t="s">
         <v>28</v>
@@ -11818,7 +11836,7 @@
         <v>2405001</v>
       </c>
       <c r="B212" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C212" t="s">
         <v>157</v>
@@ -11845,16 +11863,16 @@
         <v>42</v>
       </c>
       <c r="K212" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="L212" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="M212" t="s">
         <v>27</v>
       </c>
       <c r="N212" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="P212" t="s">
         <v>28</v>
@@ -11868,7 +11886,7 @@
         <v>2405006</v>
       </c>
       <c r="B213" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C213" t="s">
         <v>157</v>
@@ -11895,16 +11913,16 @@
         <v>42</v>
       </c>
       <c r="K213" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="L213" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="M213" t="s">
         <v>27</v>
       </c>
       <c r="N213" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="P213" t="s">
         <v>28</v>
@@ -11918,7 +11936,7 @@
         <v>2405006</v>
       </c>
       <c r="B214" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C214" t="s">
         <v>157</v>
@@ -11945,16 +11963,16 @@
         <v>42</v>
       </c>
       <c r="K214" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="L214" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="M214" t="s">
         <v>27</v>
       </c>
       <c r="N214" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="P214" t="s">
         <v>28</v>
@@ -11968,7 +11986,7 @@
         <v>2405006</v>
       </c>
       <c r="B215" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C215" t="s">
         <v>157</v>
@@ -11995,16 +12013,16 @@
         <v>42</v>
       </c>
       <c r="K215" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="L215" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="M215" t="s">
         <v>27</v>
       </c>
       <c r="N215" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="P215" t="s">
         <v>28</v>
@@ -12018,7 +12036,7 @@
         <v>2405015</v>
       </c>
       <c r="B216" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C216" t="s">
         <v>157</v>
@@ -12030,7 +12048,7 @@
         <v>21</v>
       </c>
       <c r="F216" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G216" t="s">
         <v>23</v>
@@ -12045,16 +12063,16 @@
         <v>25</v>
       </c>
       <c r="K216" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="L216" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="M216" t="s">
         <v>27</v>
       </c>
       <c r="N216" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="P216" t="s">
         <v>28</v>
@@ -12068,7 +12086,7 @@
         <v>2405015</v>
       </c>
       <c r="B217" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C217" t="s">
         <v>157</v>
@@ -12080,7 +12098,7 @@
         <v>21</v>
       </c>
       <c r="F217" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G217" t="s">
         <v>23</v>
@@ -12095,16 +12113,16 @@
         <v>25</v>
       </c>
       <c r="K217" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="L217" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="M217" t="s">
         <v>27</v>
       </c>
       <c r="N217" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="P217" t="s">
         <v>28</v>
@@ -12118,7 +12136,7 @@
         <v>2405015</v>
       </c>
       <c r="B218" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C218" t="s">
         <v>157</v>
@@ -12130,7 +12148,7 @@
         <v>21</v>
       </c>
       <c r="F218" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G218" t="s">
         <v>23</v>
@@ -12145,13 +12163,13 @@
         <v>25</v>
       </c>
       <c r="K218" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="M218" t="s">
         <v>27</v>
       </c>
       <c r="N218" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="P218" t="s">
         <v>28</v>
@@ -12165,7 +12183,7 @@
         <v>2406004</v>
       </c>
       <c r="B219" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C219" t="s">
         <v>157</v>
@@ -12192,10 +12210,10 @@
         <v>25</v>
       </c>
       <c r="K219" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="L219" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="M219" t="s">
         <v>27</v>
@@ -12212,7 +12230,7 @@
         <v>2406004</v>
       </c>
       <c r="B220" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C220" t="s">
         <v>157</v>
@@ -12239,10 +12257,10 @@
         <v>25</v>
       </c>
       <c r="K220" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="L220" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="M220" t="s">
         <v>27</v>
@@ -12259,7 +12277,7 @@
         <v>2406004</v>
       </c>
       <c r="B221" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C221" t="s">
         <v>157</v>
@@ -12280,13 +12298,13 @@
         <v>8</v>
       </c>
       <c r="I221" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="J221" t="s">
         <v>25</v>
       </c>
       <c r="L221" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="M221" t="s">
         <v>27</v>
@@ -12303,7 +12321,7 @@
         <v>2406004</v>
       </c>
       <c r="B222" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C222" t="s">
         <v>157</v>
@@ -12330,10 +12348,10 @@
         <v>25</v>
       </c>
       <c r="K222" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="L222" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="M222" t="s">
         <v>27</v>
@@ -12350,7 +12368,7 @@
         <v>2406004</v>
       </c>
       <c r="B223" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C223" t="s">
         <v>157</v>
@@ -12371,13 +12389,13 @@
         <v>8</v>
       </c>
       <c r="I223" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="J223" t="s">
         <v>25</v>
       </c>
       <c r="L223" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="M223" t="s">
         <v>27</v>
@@ -12394,7 +12412,7 @@
         <v>2406009</v>
       </c>
       <c r="B224" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C224" t="s">
         <v>157</v>
@@ -12421,10 +12439,10 @@
         <v>25</v>
       </c>
       <c r="K224" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="L224" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="M224" t="s">
         <v>27</v>
@@ -12441,7 +12459,7 @@
         <v>2406009</v>
       </c>
       <c r="B225" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C225" t="s">
         <v>157</v>
@@ -12468,10 +12486,10 @@
         <v>25</v>
       </c>
       <c r="K225" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="L225" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="M225" t="s">
         <v>27</v>
@@ -12488,7 +12506,7 @@
         <v>2406009</v>
       </c>
       <c r="B226" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C226" t="s">
         <v>157</v>
@@ -12509,16 +12527,16 @@
         <v>8</v>
       </c>
       <c r="I226" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="J226" t="s">
         <v>25</v>
       </c>
       <c r="K226" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="L226" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="M226" t="s">
         <v>27</v>
@@ -12535,7 +12553,7 @@
         <v>2406009</v>
       </c>
       <c r="B227" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C227" t="s">
         <v>157</v>
@@ -12562,10 +12580,10 @@
         <v>25</v>
       </c>
       <c r="K227" t="s">
+        <v>463</v>
+      </c>
+      <c r="L227" t="s">
         <v>460</v>
-      </c>
-      <c r="L227" t="s">
-        <v>457</v>
       </c>
       <c r="M227" t="s">
         <v>27</v>
@@ -12582,7 +12600,7 @@
         <v>2406009</v>
       </c>
       <c r="B228" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C228" t="s">
         <v>157</v>
@@ -12603,16 +12621,16 @@
         <v>8</v>
       </c>
       <c r="I228" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="J228" t="s">
         <v>25</v>
       </c>
       <c r="K228" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="L228" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="M228" t="s">
         <v>27</v>
@@ -12629,7 +12647,7 @@
         <v>2406012</v>
       </c>
       <c r="B229" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C229" t="s">
         <v>157</v>
@@ -12641,7 +12659,7 @@
         <v>21</v>
       </c>
       <c r="F229" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="G229" t="s">
         <v>40</v>
@@ -12656,10 +12674,10 @@
         <v>42</v>
       </c>
       <c r="K229" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="L229" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="M229" t="s">
         <v>27</v>
@@ -12676,7 +12694,7 @@
         <v>2406012</v>
       </c>
       <c r="B230" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C230" t="s">
         <v>157</v>
@@ -12688,7 +12706,7 @@
         <v>21</v>
       </c>
       <c r="F230" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="G230" t="s">
         <v>40</v>
@@ -12697,16 +12715,16 @@
         <v>8</v>
       </c>
       <c r="I230" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="J230" t="s">
         <v>42</v>
       </c>
       <c r="K230" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="L230" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="M230" t="s">
         <v>27</v>
@@ -12723,7 +12741,7 @@
         <v>2406012</v>
       </c>
       <c r="B231" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C231" t="s">
         <v>157</v>
@@ -12735,7 +12753,7 @@
         <v>21</v>
       </c>
       <c r="F231" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="G231" t="s">
         <v>40</v>
@@ -12744,16 +12762,16 @@
         <v>8</v>
       </c>
       <c r="I231" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="J231" t="s">
         <v>42</v>
       </c>
       <c r="K231" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="L231" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="M231" t="s">
         <v>27</v>
@@ -12770,10 +12788,10 @@
         <v>2059001</v>
       </c>
       <c r="B232" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C232" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="D232" s="2">
         <v>1</v>
@@ -12797,10 +12815,10 @@
         <v>42</v>
       </c>
       <c r="K232" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="L232" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="M232" t="s">
         <v>27</v>
@@ -12817,10 +12835,10 @@
         <v>2059002</v>
       </c>
       <c r="B233" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C233" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="D233" s="2">
         <v>1</v>
@@ -12844,10 +12862,10 @@
         <v>42</v>
       </c>
       <c r="K233" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="L233" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="M233" t="s">
         <v>27</v>
@@ -12864,10 +12882,10 @@
         <v>2059006</v>
       </c>
       <c r="B234" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C234" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="D234" s="2">
         <v>1</v>
@@ -12891,10 +12909,10 @@
         <v>42</v>
       </c>
       <c r="K234" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="L234" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="M234" t="s">
         <v>27</v>
@@ -12911,10 +12929,10 @@
         <v>2140011</v>
       </c>
       <c r="B235" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C235" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="D235" s="2">
         <v>2</v>
@@ -12923,7 +12941,7 @@
         <v>21</v>
       </c>
       <c r="F235" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G235" t="s">
         <v>40</v>
@@ -12941,7 +12959,7 @@
         <v>159</v>
       </c>
       <c r="L235" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="M235" t="s">
         <v>27</v>
@@ -12958,10 +12976,10 @@
         <v>2390004</v>
       </c>
       <c r="B236" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C236" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="D236" s="2">
         <v>1</v>
@@ -12985,10 +13003,10 @@
         <v>25</v>
       </c>
       <c r="K236" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="L236" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="M236" t="s">
         <v>27</v>
@@ -13005,10 +13023,10 @@
         <v>2390004</v>
       </c>
       <c r="B237" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C237" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="D237" s="2">
         <v>1</v>
@@ -13032,10 +13050,10 @@
         <v>25</v>
       </c>
       <c r="K237" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="L237" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="M237" t="s">
         <v>27</v>
@@ -13052,10 +13070,10 @@
         <v>2390004</v>
       </c>
       <c r="B238" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C238" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="D238" s="2">
         <v>1</v>
@@ -13079,10 +13097,10 @@
         <v>25</v>
       </c>
       <c r="K238" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="L238" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="M238" t="s">
         <v>27</v>
@@ -13099,10 +13117,10 @@
         <v>2390009</v>
       </c>
       <c r="B239" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C239" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="D239" s="2">
         <v>1</v>
@@ -13126,10 +13144,10 @@
         <v>25</v>
       </c>
       <c r="K239" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="L239" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="M239" t="s">
         <v>27</v>
@@ -13146,10 +13164,10 @@
         <v>2390009</v>
       </c>
       <c r="B240" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C240" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="D240" s="2">
         <v>1</v>
@@ -13173,10 +13191,10 @@
         <v>25</v>
       </c>
       <c r="K240" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="L240" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="M240" t="s">
         <v>27</v>
@@ -13193,10 +13211,10 @@
         <v>2390009</v>
       </c>
       <c r="B241" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C241" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="D241" s="2">
         <v>1</v>
@@ -13220,10 +13238,10 @@
         <v>25</v>
       </c>
       <c r="K241" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="L241" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="M241" t="s">
         <v>27</v>
@@ -13240,10 +13258,10 @@
         <v>2390013</v>
       </c>
       <c r="B242" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C242" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="D242" s="2">
         <v>2</v>
@@ -13252,7 +13270,7 @@
         <v>21</v>
       </c>
       <c r="F242" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G242" t="s">
         <v>23</v>
@@ -13267,7 +13285,7 @@
         <v>42</v>
       </c>
       <c r="K242" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="M242" t="s">
         <v>27</v>
@@ -13284,10 +13302,10 @@
         <v>2390013</v>
       </c>
       <c r="B243" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C243" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="D243" s="2">
         <v>2</v>
@@ -13296,7 +13314,7 @@
         <v>21</v>
       </c>
       <c r="F243" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G243" t="s">
         <v>23</v>
@@ -13311,7 +13329,7 @@
         <v>42</v>
       </c>
       <c r="K243" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="M243" t="s">
         <v>27</v>
@@ -13328,10 +13346,10 @@
         <v>2390013</v>
       </c>
       <c r="B244" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C244" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="D244" s="2">
         <v>2</v>
@@ -13340,7 +13358,7 @@
         <v>21</v>
       </c>
       <c r="F244" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G244" t="s">
         <v>23</v>
@@ -13355,7 +13373,7 @@
         <v>42</v>
       </c>
       <c r="K244" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="M244" t="s">
         <v>27</v>

--- a/POD_2026-27_11-5-2026.xlsx
+++ b/POD_2026-27_11-5-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://urjc-my.sharepoint.com/personal/esther_garcia_urjc_es/Documents/Documentos/POD 2026-27/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="269" documentId="11_79C815625599F410B0C00D3910C611C600045ACD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9CE8BAA4-9BC3-4CF2-9FCA-4000CC19B849}"/>
+  <xr:revisionPtr revIDLastSave="274" documentId="11_79C815625599F410B0C00D3910C611C600045ACD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD31BD61-4F73-45ED-B163-F6590E3AC3C8}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2929" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2931" uniqueCount="495">
   <si>
     <t>POD_2026-27_11-5-2026</t>
   </si>
@@ -584,7 +584,7 @@
     <t>G_INF-ADE_1A(M) (2097015), G_INF-COMP_1A(M) (2113005), G_INF-MAT_EXT_1A(M) (2117003)</t>
   </si>
   <si>
-    <t>ÁNGEL PÉREZ (35/70)</t>
+    <t>ÁNGEL PÉREZ (35/70) (*hablar con quien coja la otra media sobre reparto temporal)</t>
   </si>
   <si>
     <t>J(13:00 - 15:00), V(09:00 - 11:00)</t>
@@ -612,6 +612,9 @@
   </si>
   <si>
     <t>(2061) GRADO EN INGENIERIA INFORMATICA SEMIPRESENCIAL (MOSTOLES)</t>
+  </si>
+  <si>
+    <t>ÁNGEL PÉREZ (0/0)</t>
   </si>
   <si>
     <t>(2107) GRADO EN INGENIERIA AMBIENTAL (MOSTOLES)</t>
@@ -5502,7 +5505,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="14.45">
+    <row r="79" spans="1:17" ht="45.75">
       <c r="A79" s="2">
         <v>2033002</v>
       </c>
@@ -5542,7 +5545,7 @@
       <c r="M79" t="s">
         <v>27</v>
       </c>
-      <c r="N79" t="s">
+      <c r="N79" s="3" t="s">
         <v>182</v>
       </c>
       <c r="P79" t="s">
@@ -5646,7 +5649,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="14.45">
+    <row r="82" spans="1:17" ht="45.75">
       <c r="A82" s="2">
         <v>2034002</v>
       </c>
@@ -5685,6 +5688,9 @@
       </c>
       <c r="M82" t="s">
         <v>27</v>
+      </c>
+      <c r="N82" s="3" t="s">
+        <v>182</v>
       </c>
       <c r="P82" t="s">
         <v>28</v>
@@ -5821,6 +5827,9 @@
       <c r="M85" t="s">
         <v>27</v>
       </c>
+      <c r="N85" t="s">
+        <v>192</v>
+      </c>
       <c r="P85" t="s">
         <v>28</v>
       </c>
@@ -5877,7 +5886,7 @@
         <v>2107013</v>
       </c>
       <c r="B87" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C87" t="s">
         <v>157</v>
@@ -5889,7 +5898,7 @@
         <v>21</v>
       </c>
       <c r="F87" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G87" t="s">
         <v>40</v>
@@ -5907,7 +5916,7 @@
         <v>159</v>
       </c>
       <c r="L87" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M87" t="s">
         <v>27</v>
@@ -5924,7 +5933,7 @@
         <v>2143016</v>
       </c>
       <c r="B88" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C88" t="s">
         <v>157</v>
@@ -5936,7 +5945,7 @@
         <v>21</v>
       </c>
       <c r="F88" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G88" t="s">
         <v>40</v>
@@ -5954,7 +5963,7 @@
         <v>159</v>
       </c>
       <c r="L88" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M88" t="s">
         <v>27</v>
@@ -5971,7 +5980,7 @@
         <v>2148011</v>
       </c>
       <c r="B89" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C89" t="s">
         <v>157</v>
@@ -5983,7 +5992,7 @@
         <v>21</v>
       </c>
       <c r="F89" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G89" t="s">
         <v>40</v>
@@ -6015,7 +6024,7 @@
         <v>2175020</v>
       </c>
       <c r="B90" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C90" t="s">
         <v>157</v>
@@ -6042,10 +6051,10 @@
         <v>25</v>
       </c>
       <c r="K90" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L90" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M90" t="s">
         <v>27</v>
@@ -6062,7 +6071,7 @@
         <v>2285005</v>
       </c>
       <c r="B91" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C91" t="s">
         <v>157</v>
@@ -6106,7 +6115,7 @@
         <v>2285006</v>
       </c>
       <c r="B92" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C92" t="s">
         <v>157</v>
@@ -6133,13 +6142,13 @@
         <v>42</v>
       </c>
       <c r="K92" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M92" t="s">
         <v>27</v>
       </c>
       <c r="N92" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P92" t="s">
         <v>28</v>
@@ -6153,7 +6162,7 @@
         <v>2285007</v>
       </c>
       <c r="B93" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C93" t="s">
         <v>157</v>
@@ -6165,7 +6174,7 @@
         <v>35</v>
       </c>
       <c r="F93" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G93" t="s">
         <v>40</v>
@@ -6180,7 +6189,7 @@
         <v>42</v>
       </c>
       <c r="K93" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M93" t="s">
         <v>27</v>
@@ -6197,7 +6206,7 @@
         <v>2286015</v>
       </c>
       <c r="B94" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C94" t="s">
         <v>157</v>
@@ -6209,7 +6218,7 @@
         <v>21</v>
       </c>
       <c r="F94" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G94" t="s">
         <v>40</v>
@@ -6241,7 +6250,7 @@
         <v>2338044</v>
       </c>
       <c r="B95" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C95" t="s">
         <v>157</v>
@@ -6285,7 +6294,7 @@
         <v>2342014</v>
       </c>
       <c r="B96" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C96" t="s">
         <v>157</v>
@@ -6297,7 +6306,7 @@
         <v>21</v>
       </c>
       <c r="F96" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G96" t="s">
         <v>40</v>
@@ -6318,7 +6327,7 @@
         <v>27</v>
       </c>
       <c r="N96" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P96" t="s">
         <v>28</v>
@@ -6332,7 +6341,7 @@
         <v>5</v>
       </c>
       <c r="B97" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C97" t="s">
         <v>157</v>
@@ -6344,7 +6353,7 @@
         <v>21</v>
       </c>
       <c r="F97" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G97" t="s">
         <v>40</v>
@@ -6359,13 +6368,13 @@
         <v>42</v>
       </c>
       <c r="K97" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M97" t="s">
         <v>27</v>
       </c>
       <c r="N97" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P97" t="s">
         <v>28</v>
@@ -6379,7 +6388,7 @@
         <v>2343027</v>
       </c>
       <c r="B98" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C98" t="s">
         <v>157</v>
@@ -6391,7 +6400,7 @@
         <v>35</v>
       </c>
       <c r="F98" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G98" t="s">
         <v>40</v>
@@ -6406,13 +6415,13 @@
         <v>25</v>
       </c>
       <c r="K98" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M98" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N98" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P98" t="s">
         <v>28</v>
@@ -6426,7 +6435,7 @@
         <v>2343027</v>
       </c>
       <c r="B99" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C99" t="s">
         <v>157</v>
@@ -6438,7 +6447,7 @@
         <v>35</v>
       </c>
       <c r="F99" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G99" t="s">
         <v>40</v>
@@ -6453,13 +6462,13 @@
         <v>25</v>
       </c>
       <c r="K99" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M99" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N99" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P99" t="s">
         <v>28</v>
@@ -6473,7 +6482,7 @@
         <v>2343027</v>
       </c>
       <c r="B100" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C100" t="s">
         <v>157</v>
@@ -6485,7 +6494,7 @@
         <v>35</v>
       </c>
       <c r="F100" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G100" t="s">
         <v>40</v>
@@ -6500,10 +6509,10 @@
         <v>25</v>
       </c>
       <c r="K100" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M100" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N100" s="3"/>
       <c r="P100" t="s">
@@ -6518,7 +6527,7 @@
         <v>2347001</v>
       </c>
       <c r="B101" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C101" t="s">
         <v>157</v>
@@ -6545,16 +6554,16 @@
         <v>42</v>
       </c>
       <c r="K101" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L101" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M101" t="s">
         <v>27</v>
       </c>
       <c r="N101" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P101" t="s">
         <v>28</v>
@@ -6568,7 +6577,7 @@
         <v>2347003</v>
       </c>
       <c r="B102" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C102" t="s">
         <v>157</v>
@@ -6598,13 +6607,13 @@
         <v>177</v>
       </c>
       <c r="L102" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M102" t="s">
         <v>27</v>
       </c>
       <c r="N102" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P102" t="s">
         <v>28</v>
@@ -6618,7 +6627,7 @@
         <v>2347005</v>
       </c>
       <c r="B103" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C103" t="s">
         <v>157</v>
@@ -6630,7 +6639,7 @@
         <v>21</v>
       </c>
       <c r="F103" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G103" t="s">
         <v>40</v>
@@ -6645,16 +6654,16 @@
         <v>42</v>
       </c>
       <c r="K103" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L103" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M103" t="s">
         <v>27</v>
       </c>
       <c r="N103" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P103" t="s">
         <v>28</v>
@@ -6668,7 +6677,7 @@
         <v>2347006</v>
       </c>
       <c r="B104" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C104" t="s">
         <v>157</v>
@@ -6680,7 +6689,7 @@
         <v>35</v>
       </c>
       <c r="F104" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G104" t="s">
         <v>40</v>
@@ -6695,16 +6704,16 @@
         <v>42</v>
       </c>
       <c r="K104" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L104" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M104" t="s">
         <v>27</v>
       </c>
       <c r="N104" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="P104" t="s">
         <v>28</v>
@@ -6718,7 +6727,7 @@
         <v>2347007</v>
       </c>
       <c r="B105" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C105" t="s">
         <v>157</v>
@@ -6748,13 +6757,13 @@
         <v>189</v>
       </c>
       <c r="L105" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M105" t="s">
         <v>27</v>
       </c>
       <c r="N105" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P105" t="s">
         <v>28</v>
@@ -6768,7 +6777,7 @@
         <v>2347013</v>
       </c>
       <c r="B106" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C106" t="s">
         <v>157</v>
@@ -6780,7 +6789,7 @@
         <v>21</v>
       </c>
       <c r="F106" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G106" t="s">
         <v>40</v>
@@ -6795,16 +6804,16 @@
         <v>42</v>
       </c>
       <c r="K106" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L106" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M106" t="s">
         <v>27</v>
       </c>
       <c r="N106" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P106" t="s">
         <v>28</v>
@@ -6818,7 +6827,7 @@
         <v>2347014</v>
       </c>
       <c r="B107" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C107" t="s">
         <v>157</v>
@@ -6830,7 +6839,7 @@
         <v>35</v>
       </c>
       <c r="F107" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G107" t="s">
         <v>40</v>
@@ -6845,10 +6854,10 @@
         <v>42</v>
       </c>
       <c r="K107" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L107" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M107" t="s">
         <v>27</v>
@@ -6865,7 +6874,7 @@
         <v>2347017</v>
       </c>
       <c r="B108" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C108" t="s">
         <v>157</v>
@@ -6877,7 +6886,7 @@
         <v>35</v>
       </c>
       <c r="F108" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G108" t="s">
         <v>23</v>
@@ -6892,16 +6901,16 @@
         <v>42</v>
       </c>
       <c r="K108" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L108" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M108" t="s">
         <v>27</v>
       </c>
       <c r="N108" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P108" t="s">
         <v>28</v>
@@ -6915,7 +6924,7 @@
         <v>2347030</v>
       </c>
       <c r="B109" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C109" t="s">
         <v>157</v>
@@ -6927,7 +6936,7 @@
         <v>35</v>
       </c>
       <c r="F109" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G109" t="s">
         <v>40</v>
@@ -6942,16 +6951,16 @@
         <v>42</v>
       </c>
       <c r="K109" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L109" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M109" t="s">
         <v>27</v>
       </c>
       <c r="N109" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P109" t="s">
         <v>28</v>
@@ -6965,7 +6974,7 @@
         <v>2347021</v>
       </c>
       <c r="B110" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C110" t="s">
         <v>157</v>
@@ -6977,7 +6986,7 @@
         <v>21</v>
       </c>
       <c r="F110" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G110" t="s">
         <v>40</v>
@@ -6992,16 +7001,16 @@
         <v>42</v>
       </c>
       <c r="K110" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L110" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M110" t="s">
         <v>27</v>
       </c>
       <c r="N110" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P110" t="s">
         <v>28</v>
@@ -7015,7 +7024,7 @@
         <v>2347022</v>
       </c>
       <c r="B111" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C111" t="s">
         <v>157</v>
@@ -7027,7 +7036,7 @@
         <v>21</v>
       </c>
       <c r="F111" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G111" t="s">
         <v>40</v>
@@ -7042,16 +7051,16 @@
         <v>42</v>
       </c>
       <c r="K111" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L111" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M111" t="s">
         <v>27</v>
       </c>
       <c r="N111" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O111" s="1"/>
       <c r="P111" t="s">
@@ -7066,7 +7075,7 @@
         <v>2347024</v>
       </c>
       <c r="B112" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C112" t="s">
         <v>157</v>
@@ -7078,7 +7087,7 @@
         <v>21</v>
       </c>
       <c r="F112" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G112" t="s">
         <v>40</v>
@@ -7093,16 +7102,16 @@
         <v>42</v>
       </c>
       <c r="K112" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L112" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M112" t="s">
         <v>27</v>
       </c>
       <c r="N112" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P112" t="s">
         <v>28</v>
@@ -7116,7 +7125,7 @@
         <v>2347026</v>
       </c>
       <c r="B113" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C113" t="s">
         <v>157</v>
@@ -7128,7 +7137,7 @@
         <v>35</v>
       </c>
       <c r="F113" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G113" t="s">
         <v>40</v>
@@ -7143,16 +7152,16 @@
         <v>42</v>
       </c>
       <c r="K113" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L113" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M113" t="s">
         <v>27</v>
       </c>
       <c r="N113" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P113" t="s">
         <v>28</v>
@@ -7166,7 +7175,7 @@
         <v>2347027</v>
       </c>
       <c r="B114" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C114" t="s">
         <v>157</v>
@@ -7178,7 +7187,7 @@
         <v>35</v>
       </c>
       <c r="F114" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G114" t="s">
         <v>40</v>
@@ -7193,16 +7202,16 @@
         <v>42</v>
       </c>
       <c r="K114" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L114" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M114" t="s">
         <v>27</v>
       </c>
       <c r="N114" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P114" t="s">
         <v>28</v>
@@ -7216,7 +7225,7 @@
         <v>2347029</v>
       </c>
       <c r="B115" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C115" t="s">
         <v>157</v>
@@ -7228,7 +7237,7 @@
         <v>35</v>
       </c>
       <c r="F115" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G115" t="s">
         <v>40</v>
@@ -7243,13 +7252,13 @@
         <v>42</v>
       </c>
       <c r="K115" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L115" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M115" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P115" t="s">
         <v>28</v>
@@ -7263,7 +7272,7 @@
         <v>2347031</v>
       </c>
       <c r="B116" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C116" t="s">
         <v>157</v>
@@ -7275,7 +7284,7 @@
         <v>21</v>
       </c>
       <c r="F116" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G116" t="s">
         <v>40</v>
@@ -7290,16 +7299,16 @@
         <v>42</v>
       </c>
       <c r="K116" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L116" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M116" t="s">
         <v>27</v>
       </c>
       <c r="N116" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P116" t="s">
         <v>28</v>
@@ -7313,7 +7322,7 @@
         <v>2347038</v>
       </c>
       <c r="B117" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C117" t="s">
         <v>157</v>
@@ -7325,10 +7334,10 @@
         <v>21</v>
       </c>
       <c r="F117" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G117" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H117" s="2">
         <v>60</v>
@@ -7340,16 +7349,16 @@
         <v>42</v>
       </c>
       <c r="K117" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L117" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M117" t="s">
         <v>27</v>
       </c>
       <c r="N117" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P117" t="s">
         <v>28</v>
@@ -7363,7 +7372,7 @@
         <v>2361002</v>
       </c>
       <c r="B118" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C118" t="s">
         <v>157</v>
@@ -7390,7 +7399,7 @@
         <v>42</v>
       </c>
       <c r="K118" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M118" t="s">
         <v>27</v>
@@ -7407,7 +7416,7 @@
         <v>2361002</v>
       </c>
       <c r="B119" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C119" t="s">
         <v>157</v>
@@ -7434,7 +7443,7 @@
         <v>42</v>
       </c>
       <c r="K119" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M119" t="s">
         <v>27</v>
@@ -7451,7 +7460,7 @@
         <v>2361002</v>
       </c>
       <c r="B120" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C120" t="s">
         <v>157</v>
@@ -7478,7 +7487,7 @@
         <v>42</v>
       </c>
       <c r="K120" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M120" t="s">
         <v>27</v>
@@ -7495,7 +7504,7 @@
         <v>2361004</v>
       </c>
       <c r="B121" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C121" t="s">
         <v>157</v>
@@ -7522,7 +7531,7 @@
         <v>42</v>
       </c>
       <c r="K121" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M121" t="s">
         <v>27</v>
@@ -7539,7 +7548,7 @@
         <v>2393002</v>
       </c>
       <c r="B122" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C122" t="s">
         <v>157</v>
@@ -7566,10 +7575,10 @@
         <v>42</v>
       </c>
       <c r="K122" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L122" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M122" t="s">
         <v>27</v>
@@ -7586,7 +7595,7 @@
         <v>2393002</v>
       </c>
       <c r="B123" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C123" t="s">
         <v>157</v>
@@ -7607,16 +7616,16 @@
         <v>20</v>
       </c>
       <c r="I123" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J123" t="s">
         <v>42</v>
       </c>
       <c r="K123" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L123" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M123" t="s">
         <v>27</v>
@@ -7633,7 +7642,7 @@
         <v>2393002</v>
       </c>
       <c r="B124" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C124" t="s">
         <v>157</v>
@@ -7654,16 +7663,16 @@
         <v>20</v>
       </c>
       <c r="I124" t="s">
+        <v>287</v>
+      </c>
+      <c r="J124" t="s">
+        <v>42</v>
+      </c>
+      <c r="K124" t="s">
+        <v>288</v>
+      </c>
+      <c r="L124" t="s">
         <v>286</v>
-      </c>
-      <c r="J124" t="s">
-        <v>42</v>
-      </c>
-      <c r="K124" t="s">
-        <v>287</v>
-      </c>
-      <c r="L124" t="s">
-        <v>285</v>
       </c>
       <c r="M124" t="s">
         <v>27</v>
@@ -7680,7 +7689,7 @@
         <v>2394004</v>
       </c>
       <c r="B125" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C125" t="s">
         <v>157</v>
@@ -7707,10 +7716,10 @@
         <v>25</v>
       </c>
       <c r="K125" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L125" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M125" t="s">
         <v>27</v>
@@ -7727,7 +7736,7 @@
         <v>2394004</v>
       </c>
       <c r="B126" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C126" t="s">
         <v>157</v>
@@ -7754,10 +7763,10 @@
         <v>25</v>
       </c>
       <c r="K126" t="s">
+        <v>292</v>
+      </c>
+      <c r="L126" t="s">
         <v>291</v>
-      </c>
-      <c r="L126" t="s">
-        <v>290</v>
       </c>
       <c r="M126" t="s">
         <v>27</v>
@@ -7774,7 +7783,7 @@
         <v>2394004</v>
       </c>
       <c r="B127" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C127" t="s">
         <v>157</v>
@@ -7801,10 +7810,10 @@
         <v>25</v>
       </c>
       <c r="K127" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L127" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M127" t="s">
         <v>27</v>
@@ -7821,7 +7830,7 @@
         <v>2395003</v>
       </c>
       <c r="B128" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C128" t="s">
         <v>157</v>
@@ -7848,10 +7857,10 @@
         <v>42</v>
       </c>
       <c r="K128" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L128" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M128" t="s">
         <v>27</v>
@@ -7868,7 +7877,7 @@
         <v>2395003</v>
       </c>
       <c r="B129" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C129" t="s">
         <v>157</v>
@@ -7895,10 +7904,10 @@
         <v>42</v>
       </c>
       <c r="K129" t="s">
+        <v>297</v>
+      </c>
+      <c r="L129" t="s">
         <v>296</v>
-      </c>
-      <c r="L129" t="s">
-        <v>295</v>
       </c>
       <c r="M129" t="s">
         <v>27</v>
@@ -7915,7 +7924,7 @@
         <v>2395003</v>
       </c>
       <c r="B130" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C130" t="s">
         <v>157</v>
@@ -7942,10 +7951,10 @@
         <v>42</v>
       </c>
       <c r="K130" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L130" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M130" t="s">
         <v>27</v>
@@ -7962,7 +7971,7 @@
         <v>2396001</v>
       </c>
       <c r="B131" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C131" t="s">
         <v>157</v>
@@ -7989,10 +7998,10 @@
         <v>25</v>
       </c>
       <c r="K131" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L131" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M131" t="s">
         <v>27</v>
@@ -8009,7 +8018,7 @@
         <v>2396001</v>
       </c>
       <c r="B132" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C132" t="s">
         <v>157</v>
@@ -8036,10 +8045,10 @@
         <v>25</v>
       </c>
       <c r="K132" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L132" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M132" t="s">
         <v>27</v>
@@ -8056,7 +8065,7 @@
         <v>2396001</v>
       </c>
       <c r="B133" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C133" t="s">
         <v>157</v>
@@ -8083,10 +8092,10 @@
         <v>25</v>
       </c>
       <c r="K133" t="s">
+        <v>304</v>
+      </c>
+      <c r="L133" t="s">
         <v>303</v>
-      </c>
-      <c r="L133" t="s">
-        <v>302</v>
       </c>
       <c r="M133" t="s">
         <v>27</v>
@@ -8103,7 +8112,7 @@
         <v>2397003</v>
       </c>
       <c r="B134" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C134" t="s">
         <v>157</v>
@@ -8130,10 +8139,10 @@
         <v>25</v>
       </c>
       <c r="K134" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L134" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M134" t="s">
         <v>27</v>
@@ -8150,7 +8159,7 @@
         <v>2397003</v>
       </c>
       <c r="B135" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C135" t="s">
         <v>157</v>
@@ -8177,10 +8186,10 @@
         <v>25</v>
       </c>
       <c r="K135" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L135" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M135" t="s">
         <v>27</v>
@@ -8197,7 +8206,7 @@
         <v>2397003</v>
       </c>
       <c r="B136" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C136" t="s">
         <v>157</v>
@@ -8224,10 +8233,10 @@
         <v>25</v>
       </c>
       <c r="K136" t="s">
+        <v>310</v>
+      </c>
+      <c r="L136" t="s">
         <v>309</v>
-      </c>
-      <c r="L136" t="s">
-        <v>308</v>
       </c>
       <c r="M136" t="s">
         <v>27</v>
@@ -8244,7 +8253,7 @@
         <v>2397008</v>
       </c>
       <c r="B137" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C137" t="s">
         <v>157</v>
@@ -8271,10 +8280,10 @@
         <v>25</v>
       </c>
       <c r="K137" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L137" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M137" t="s">
         <v>27</v>
@@ -8291,7 +8300,7 @@
         <v>2397008</v>
       </c>
       <c r="B138" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C138" t="s">
         <v>157</v>
@@ -8318,10 +8327,10 @@
         <v>25</v>
       </c>
       <c r="K138" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L138" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M138" t="s">
         <v>27</v>
@@ -8338,7 +8347,7 @@
         <v>2397008</v>
       </c>
       <c r="B139" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C139" t="s">
         <v>157</v>
@@ -8365,10 +8374,10 @@
         <v>25</v>
       </c>
       <c r="K139" t="s">
+        <v>315</v>
+      </c>
+      <c r="L139" t="s">
         <v>314</v>
-      </c>
-      <c r="L139" t="s">
-        <v>313</v>
       </c>
       <c r="M139" t="s">
         <v>27</v>
@@ -8385,7 +8394,7 @@
         <v>2398001</v>
       </c>
       <c r="B140" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C140" t="s">
         <v>157</v>
@@ -8412,16 +8421,16 @@
         <v>42</v>
       </c>
       <c r="K140" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L140" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M140" t="s">
         <v>27</v>
       </c>
       <c r="N140" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P140" t="s">
         <v>28</v>
@@ -8435,7 +8444,7 @@
         <v>2398001</v>
       </c>
       <c r="B141" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C141" t="s">
         <v>157</v>
@@ -8462,16 +8471,16 @@
         <v>42</v>
       </c>
       <c r="K141" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L141" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M141" t="s">
         <v>27</v>
       </c>
       <c r="N141" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P141" t="s">
         <v>28</v>
@@ -8485,7 +8494,7 @@
         <v>2398001</v>
       </c>
       <c r="B142" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C142" t="s">
         <v>157</v>
@@ -8512,16 +8521,16 @@
         <v>42</v>
       </c>
       <c r="K142" t="s">
+        <v>322</v>
+      </c>
+      <c r="L142" t="s">
+        <v>318</v>
+      </c>
+      <c r="M142" t="s">
+        <v>27</v>
+      </c>
+      <c r="N142" s="4" t="s">
         <v>321</v>
-      </c>
-      <c r="L142" t="s">
-        <v>317</v>
-      </c>
-      <c r="M142" t="s">
-        <v>27</v>
-      </c>
-      <c r="N142" s="4" t="s">
-        <v>320</v>
       </c>
       <c r="P142" t="s">
         <v>28</v>
@@ -8535,7 +8544,7 @@
         <v>2398006</v>
       </c>
       <c r="B143" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C143" t="s">
         <v>157</v>
@@ -8562,10 +8571,10 @@
         <v>42</v>
       </c>
       <c r="K143" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L143" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M143" t="s">
         <v>27</v>
@@ -8582,7 +8591,7 @@
         <v>2398006</v>
       </c>
       <c r="B144" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C144" t="s">
         <v>157</v>
@@ -8609,10 +8618,10 @@
         <v>42</v>
       </c>
       <c r="K144" t="s">
+        <v>325</v>
+      </c>
+      <c r="L144" t="s">
         <v>324</v>
-      </c>
-      <c r="L144" t="s">
-        <v>323</v>
       </c>
       <c r="M144" t="s">
         <v>27</v>
@@ -8629,7 +8638,7 @@
         <v>2398006</v>
       </c>
       <c r="B145" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C145" t="s">
         <v>157</v>
@@ -8656,10 +8665,10 @@
         <v>42</v>
       </c>
       <c r="K145" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L145" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M145" t="s">
         <v>27</v>
@@ -8676,7 +8685,7 @@
         <v>2398013</v>
       </c>
       <c r="B146" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C146" t="s">
         <v>157</v>
@@ -8688,7 +8697,7 @@
         <v>21</v>
       </c>
       <c r="F146" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G146" t="s">
         <v>23</v>
@@ -8703,10 +8712,10 @@
         <v>25</v>
       </c>
       <c r="K146" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L146" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M146" t="s">
         <v>27</v>
@@ -8723,7 +8732,7 @@
         <v>2398013</v>
       </c>
       <c r="B147" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C147" t="s">
         <v>157</v>
@@ -8735,7 +8744,7 @@
         <v>21</v>
       </c>
       <c r="F147" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G147" t="s">
         <v>23</v>
@@ -8750,10 +8759,10 @@
         <v>25</v>
       </c>
       <c r="K147" t="s">
+        <v>329</v>
+      </c>
+      <c r="L147" t="s">
         <v>328</v>
-      </c>
-      <c r="L147" t="s">
-        <v>327</v>
       </c>
       <c r="M147" t="s">
         <v>27</v>
@@ -8770,7 +8779,7 @@
         <v>2398013</v>
       </c>
       <c r="B148" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C148" t="s">
         <v>157</v>
@@ -8782,7 +8791,7 @@
         <v>21</v>
       </c>
       <c r="F148" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G148" t="s">
         <v>23</v>
@@ -8797,7 +8806,7 @@
         <v>25</v>
       </c>
       <c r="K148" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M148" t="s">
         <v>27</v>
@@ -8814,7 +8823,7 @@
         <v>2399003</v>
       </c>
       <c r="B149" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C149" t="s">
         <v>157</v>
@@ -8841,10 +8850,10 @@
         <v>42</v>
       </c>
       <c r="K149" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L149" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M149" t="s">
         <v>27</v>
@@ -8861,7 +8870,7 @@
         <v>2399003</v>
       </c>
       <c r="B150" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C150" t="s">
         <v>157</v>
@@ -8888,10 +8897,10 @@
         <v>42</v>
       </c>
       <c r="K150" t="s">
+        <v>334</v>
+      </c>
+      <c r="L150" t="s">
         <v>333</v>
-      </c>
-      <c r="L150" t="s">
-        <v>332</v>
       </c>
       <c r="M150" t="s">
         <v>27</v>
@@ -8908,7 +8917,7 @@
         <v>2399003</v>
       </c>
       <c r="B151" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C151" t="s">
         <v>157</v>
@@ -8935,10 +8944,10 @@
         <v>42</v>
       </c>
       <c r="K151" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L151" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M151" t="s">
         <v>27</v>
@@ -8955,7 +8964,7 @@
         <v>2399010</v>
       </c>
       <c r="B152" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C152" t="s">
         <v>157</v>
@@ -8982,10 +8991,10 @@
         <v>42</v>
       </c>
       <c r="K152" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L152" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M152" t="s">
         <v>27</v>
@@ -9002,7 +9011,7 @@
         <v>2399010</v>
       </c>
       <c r="B153" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C153" t="s">
         <v>157</v>
@@ -9029,10 +9038,10 @@
         <v>42</v>
       </c>
       <c r="K153" t="s">
+        <v>338</v>
+      </c>
+      <c r="L153" t="s">
         <v>337</v>
-      </c>
-      <c r="L153" t="s">
-        <v>336</v>
       </c>
       <c r="M153" t="s">
         <v>27</v>
@@ -9049,7 +9058,7 @@
         <v>2399010</v>
       </c>
       <c r="B154" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C154" t="s">
         <v>157</v>
@@ -9076,10 +9085,10 @@
         <v>42</v>
       </c>
       <c r="K154" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L154" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M154" t="s">
         <v>27</v>
@@ -9096,7 +9105,7 @@
         <v>2399014</v>
       </c>
       <c r="B155" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C155" t="s">
         <v>157</v>
@@ -9123,10 +9132,10 @@
         <v>25</v>
       </c>
       <c r="K155" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L155" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M155" t="s">
         <v>27</v>
@@ -9143,7 +9152,7 @@
         <v>2399014</v>
       </c>
       <c r="B156" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C156" t="s">
         <v>157</v>
@@ -9170,10 +9179,10 @@
         <v>25</v>
       </c>
       <c r="K156" t="s">
+        <v>342</v>
+      </c>
+      <c r="L156" t="s">
         <v>341</v>
-      </c>
-      <c r="L156" t="s">
-        <v>340</v>
       </c>
       <c r="M156" t="s">
         <v>27</v>
@@ -9190,7 +9199,7 @@
         <v>2399014</v>
       </c>
       <c r="B157" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C157" t="s">
         <v>157</v>
@@ -9217,7 +9226,7 @@
         <v>25</v>
       </c>
       <c r="K157" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M157" t="s">
         <v>27</v>
@@ -9234,7 +9243,7 @@
         <v>2400003</v>
       </c>
       <c r="B158" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C158" t="s">
         <v>157</v>
@@ -9261,16 +9270,16 @@
         <v>42</v>
       </c>
       <c r="K158" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L158" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M158" t="s">
         <v>27</v>
       </c>
       <c r="N158" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P158" t="s">
         <v>28</v>
@@ -9284,7 +9293,7 @@
         <v>2400003</v>
       </c>
       <c r="B159" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C159" t="s">
         <v>157</v>
@@ -9311,16 +9320,16 @@
         <v>42</v>
       </c>
       <c r="K159" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L159" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M159" t="s">
         <v>27</v>
       </c>
       <c r="N159" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P159" t="s">
         <v>28</v>
@@ -9334,7 +9343,7 @@
         <v>2400003</v>
       </c>
       <c r="B160" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C160" t="s">
         <v>157</v>
@@ -9361,16 +9370,16 @@
         <v>42</v>
       </c>
       <c r="K160" t="s">
+        <v>350</v>
+      </c>
+      <c r="L160" t="s">
+        <v>346</v>
+      </c>
+      <c r="M160" t="s">
+        <v>27</v>
+      </c>
+      <c r="N160" t="s">
         <v>349</v>
-      </c>
-      <c r="L160" t="s">
-        <v>345</v>
-      </c>
-      <c r="M160" t="s">
-        <v>27</v>
-      </c>
-      <c r="N160" t="s">
-        <v>348</v>
       </c>
       <c r="P160" t="s">
         <v>28</v>
@@ -9384,7 +9393,7 @@
         <v>2400008</v>
       </c>
       <c r="B161" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C161" t="s">
         <v>157</v>
@@ -9411,10 +9420,10 @@
         <v>42</v>
       </c>
       <c r="K161" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L161" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M161" t="s">
         <v>27</v>
@@ -9431,7 +9440,7 @@
         <v>2400008</v>
       </c>
       <c r="B162" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C162" t="s">
         <v>157</v>
@@ -9458,10 +9467,10 @@
         <v>42</v>
       </c>
       <c r="K162" t="s">
+        <v>353</v>
+      </c>
+      <c r="L162" t="s">
         <v>352</v>
-      </c>
-      <c r="L162" t="s">
-        <v>351</v>
       </c>
       <c r="M162" t="s">
         <v>27</v>
@@ -9478,7 +9487,7 @@
         <v>2400008</v>
       </c>
       <c r="B163" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C163" t="s">
         <v>157</v>
@@ -9505,10 +9514,10 @@
         <v>42</v>
       </c>
       <c r="K163" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L163" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M163" t="s">
         <v>27</v>
@@ -9525,7 +9534,7 @@
         <v>2400012</v>
       </c>
       <c r="B164" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C164" t="s">
         <v>157</v>
@@ -9537,7 +9546,7 @@
         <v>21</v>
       </c>
       <c r="F164" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G164" t="s">
         <v>23</v>
@@ -9552,16 +9561,16 @@
         <v>25</v>
       </c>
       <c r="K164" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L164" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M164" t="s">
         <v>27</v>
       </c>
       <c r="N164" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="P164" t="s">
         <v>28</v>
@@ -9575,7 +9584,7 @@
         <v>2400012</v>
       </c>
       <c r="B165" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C165" t="s">
         <v>157</v>
@@ -9587,7 +9596,7 @@
         <v>21</v>
       </c>
       <c r="F165" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G165" t="s">
         <v>23</v>
@@ -9602,16 +9611,16 @@
         <v>25</v>
       </c>
       <c r="K165" s="3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L165" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M165" t="s">
         <v>27</v>
       </c>
       <c r="N165" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P165" t="s">
         <v>28</v>
@@ -9625,7 +9634,7 @@
         <v>2400012</v>
       </c>
       <c r="B166" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C166" t="s">
         <v>157</v>
@@ -9637,7 +9646,7 @@
         <v>21</v>
       </c>
       <c r="F166" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G166" t="s">
         <v>23</v>
@@ -9652,13 +9661,13 @@
         <v>25</v>
       </c>
       <c r="K166" t="s">
+        <v>361</v>
+      </c>
+      <c r="M166" t="s">
+        <v>27</v>
+      </c>
+      <c r="N166" t="s">
         <v>360</v>
-      </c>
-      <c r="M166" t="s">
-        <v>27</v>
-      </c>
-      <c r="N166" t="s">
-        <v>359</v>
       </c>
       <c r="P166" t="s">
         <v>28</v>
@@ -9672,7 +9681,7 @@
         <v>2401001</v>
       </c>
       <c r="B167" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C167" t="s">
         <v>157</v>
@@ -9699,10 +9708,10 @@
         <v>25</v>
       </c>
       <c r="K167" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L167" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M167" t="s">
         <v>27</v>
@@ -9719,7 +9728,7 @@
         <v>2401001</v>
       </c>
       <c r="B168" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C168" t="s">
         <v>157</v>
@@ -9746,10 +9755,10 @@
         <v>25</v>
       </c>
       <c r="K168" t="s">
+        <v>365</v>
+      </c>
+      <c r="L168" t="s">
         <v>364</v>
-      </c>
-      <c r="L168" t="s">
-        <v>363</v>
       </c>
       <c r="M168" t="s">
         <v>27</v>
@@ -9766,7 +9775,7 @@
         <v>2401001</v>
       </c>
       <c r="B169" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C169" t="s">
         <v>157</v>
@@ -9793,10 +9802,10 @@
         <v>25</v>
       </c>
       <c r="K169" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L169" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M169" t="s">
         <v>27</v>
@@ -9813,7 +9822,7 @@
         <v>2401007</v>
       </c>
       <c r="B170" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C170" t="s">
         <v>157</v>
@@ -9840,10 +9849,10 @@
         <v>25</v>
       </c>
       <c r="K170" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L170" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M170" t="s">
         <v>27</v>
@@ -9860,7 +9869,7 @@
         <v>2401007</v>
       </c>
       <c r="B171" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C171" t="s">
         <v>157</v>
@@ -9887,10 +9896,10 @@
         <v>25</v>
       </c>
       <c r="K171" t="s">
+        <v>369</v>
+      </c>
+      <c r="L171" t="s">
         <v>368</v>
-      </c>
-      <c r="L171" t="s">
-        <v>367</v>
       </c>
       <c r="M171" t="s">
         <v>27</v>
@@ -9907,7 +9916,7 @@
         <v>2401007</v>
       </c>
       <c r="B172" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C172" t="s">
         <v>157</v>
@@ -9934,10 +9943,10 @@
         <v>25</v>
       </c>
       <c r="K172" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L172" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M172" t="s">
         <v>27</v>
@@ -9954,7 +9963,7 @@
         <v>2401013</v>
       </c>
       <c r="B173" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C173" t="s">
         <v>157</v>
@@ -9966,7 +9975,7 @@
         <v>21</v>
       </c>
       <c r="F173" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="G173" t="s">
         <v>40</v>
@@ -9981,16 +9990,16 @@
         <v>42</v>
       </c>
       <c r="K173" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L173" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M173" t="s">
         <v>27</v>
       </c>
       <c r="N173" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P173" t="s">
         <v>28</v>
@@ -10004,7 +10013,7 @@
         <v>2401013</v>
       </c>
       <c r="B174" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C174" t="s">
         <v>157</v>
@@ -10016,7 +10025,7 @@
         <v>21</v>
       </c>
       <c r="F174" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="G174" t="s">
         <v>40</v>
@@ -10031,16 +10040,16 @@
         <v>42</v>
       </c>
       <c r="K174" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L174" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M174" t="s">
         <v>27</v>
       </c>
       <c r="N174" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="P174" t="s">
         <v>28</v>
@@ -10054,7 +10063,7 @@
         <v>2401013</v>
       </c>
       <c r="B175" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C175" t="s">
         <v>157</v>
@@ -10066,7 +10075,7 @@
         <v>21</v>
       </c>
       <c r="F175" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="G175" t="s">
         <v>40</v>
@@ -10081,16 +10090,16 @@
         <v>42</v>
       </c>
       <c r="K175" t="s">
+        <v>377</v>
+      </c>
+      <c r="L175" t="s">
+        <v>373</v>
+      </c>
+      <c r="M175" t="s">
+        <v>27</v>
+      </c>
+      <c r="N175" t="s">
         <v>376</v>
-      </c>
-      <c r="L175" t="s">
-        <v>372</v>
-      </c>
-      <c r="M175" t="s">
-        <v>27</v>
-      </c>
-      <c r="N175" t="s">
-        <v>375</v>
       </c>
       <c r="P175" t="s">
         <v>28</v>
@@ -10104,7 +10113,7 @@
         <v>2401018</v>
       </c>
       <c r="B176" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C176" t="s">
         <v>157</v>
@@ -10116,7 +10125,7 @@
         <v>35</v>
       </c>
       <c r="F176" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G176" t="s">
         <v>40</v>
@@ -10131,10 +10140,10 @@
         <v>42</v>
       </c>
       <c r="K176" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L176" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M176" t="s">
         <v>27</v>
@@ -10151,7 +10160,7 @@
         <v>2401018</v>
       </c>
       <c r="B177" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C177" t="s">
         <v>157</v>
@@ -10163,7 +10172,7 @@
         <v>35</v>
       </c>
       <c r="F177" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G177" t="s">
         <v>40</v>
@@ -10178,10 +10187,10 @@
         <v>42</v>
       </c>
       <c r="K177" t="s">
+        <v>381</v>
+      </c>
+      <c r="L177" t="s">
         <v>380</v>
-      </c>
-      <c r="L177" t="s">
-        <v>379</v>
       </c>
       <c r="M177" t="s">
         <v>27</v>
@@ -10198,7 +10207,7 @@
         <v>2401018</v>
       </c>
       <c r="B178" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C178" t="s">
         <v>157</v>
@@ -10210,7 +10219,7 @@
         <v>35</v>
       </c>
       <c r="F178" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G178" t="s">
         <v>40</v>
@@ -10219,16 +10228,16 @@
         <v>4</v>
       </c>
       <c r="I178" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="J178" t="s">
         <v>42</v>
       </c>
       <c r="K178" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L178" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M178" t="s">
         <v>27</v>
@@ -10245,7 +10254,7 @@
         <v>2401018</v>
       </c>
       <c r="B179" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C179" t="s">
         <v>157</v>
@@ -10257,7 +10266,7 @@
         <v>35</v>
       </c>
       <c r="F179" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G179" t="s">
         <v>40</v>
@@ -10272,10 +10281,10 @@
         <v>42</v>
       </c>
       <c r="K179" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L179" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M179" t="s">
         <v>27</v>
@@ -10292,7 +10301,7 @@
         <v>2401018</v>
       </c>
       <c r="B180" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C180" t="s">
         <v>157</v>
@@ -10304,7 +10313,7 @@
         <v>35</v>
       </c>
       <c r="F180" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G180" t="s">
         <v>40</v>
@@ -10313,16 +10322,16 @@
         <v>4</v>
       </c>
       <c r="I180" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J180" t="s">
         <v>42</v>
       </c>
       <c r="K180" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L180" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M180" t="s">
         <v>27</v>
@@ -10339,7 +10348,7 @@
         <v>2401018</v>
       </c>
       <c r="B181" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C181" t="s">
         <v>157</v>
@@ -10351,7 +10360,7 @@
         <v>35</v>
       </c>
       <c r="F181" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G181" t="s">
         <v>40</v>
@@ -10360,16 +10369,16 @@
         <v>4</v>
       </c>
       <c r="I181" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J181" t="s">
         <v>42</v>
       </c>
       <c r="K181" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L181" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M181" t="s">
         <v>27</v>
@@ -10386,7 +10395,7 @@
         <v>2401018</v>
       </c>
       <c r="B182" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C182" t="s">
         <v>157</v>
@@ -10398,7 +10407,7 @@
         <v>35</v>
       </c>
       <c r="F182" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G182" t="s">
         <v>40</v>
@@ -10407,16 +10416,16 @@
         <v>4</v>
       </c>
       <c r="I182" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J182" t="s">
         <v>42</v>
       </c>
       <c r="K182" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L182" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M182" t="s">
         <v>27</v>
@@ -10433,7 +10442,7 @@
         <v>2402003</v>
       </c>
       <c r="B183" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C183" t="s">
         <v>157</v>
@@ -10460,16 +10469,16 @@
         <v>25</v>
       </c>
       <c r="K183" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L183" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M183" t="s">
         <v>27</v>
       </c>
       <c r="N183" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P183" t="s">
         <v>28</v>
@@ -10483,7 +10492,7 @@
         <v>2402003</v>
       </c>
       <c r="B184" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C184" t="s">
         <v>157</v>
@@ -10510,16 +10519,16 @@
         <v>25</v>
       </c>
       <c r="K184" t="s">
+        <v>394</v>
+      </c>
+      <c r="L184" t="s">
         <v>393</v>
       </c>
-      <c r="L184" t="s">
-        <v>392</v>
-      </c>
       <c r="M184" t="s">
         <v>27</v>
       </c>
       <c r="N184" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P184" t="s">
         <v>28</v>
@@ -10533,7 +10542,7 @@
         <v>2402003</v>
       </c>
       <c r="B185" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C185" t="s">
         <v>157</v>
@@ -10560,16 +10569,16 @@
         <v>25</v>
       </c>
       <c r="K185" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L185" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M185" t="s">
         <v>27</v>
       </c>
       <c r="N185" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P185" t="s">
         <v>28</v>
@@ -10583,7 +10592,7 @@
         <v>2402008</v>
       </c>
       <c r="B186" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C186" t="s">
         <v>157</v>
@@ -10610,16 +10619,16 @@
         <v>25</v>
       </c>
       <c r="K186" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L186" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M186" t="s">
         <v>27</v>
       </c>
       <c r="N186" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="P186" t="s">
         <v>28</v>
@@ -10633,7 +10642,7 @@
         <v>2402008</v>
       </c>
       <c r="B187" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C187" t="s">
         <v>157</v>
@@ -10660,16 +10669,16 @@
         <v>25</v>
       </c>
       <c r="K187" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L187" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M187" t="s">
         <v>27</v>
       </c>
       <c r="N187" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="P187" t="s">
         <v>28</v>
@@ -10683,7 +10692,7 @@
         <v>2402008</v>
       </c>
       <c r="B188" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C188" t="s">
         <v>157</v>
@@ -10710,16 +10719,16 @@
         <v>25</v>
       </c>
       <c r="K188" t="s">
+        <v>401</v>
+      </c>
+      <c r="L188" t="s">
+        <v>397</v>
+      </c>
+      <c r="M188" t="s">
+        <v>27</v>
+      </c>
+      <c r="N188" t="s">
         <v>400</v>
-      </c>
-      <c r="L188" t="s">
-        <v>396</v>
-      </c>
-      <c r="M188" t="s">
-        <v>27</v>
-      </c>
-      <c r="N188" t="s">
-        <v>399</v>
       </c>
       <c r="P188" t="s">
         <v>28</v>
@@ -10733,7 +10742,7 @@
         <v>2402015</v>
       </c>
       <c r="B189" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C189" t="s">
         <v>157</v>
@@ -10745,7 +10754,7 @@
         <v>21</v>
       </c>
       <c r="F189" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G189" t="s">
         <v>23</v>
@@ -10760,13 +10769,13 @@
         <v>42</v>
       </c>
       <c r="K189" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M189" t="s">
         <v>27</v>
       </c>
       <c r="N189" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="P189" t="s">
         <v>28</v>
@@ -10780,7 +10789,7 @@
         <v>2402015</v>
       </c>
       <c r="B190" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C190" t="s">
         <v>157</v>
@@ -10792,7 +10801,7 @@
         <v>21</v>
       </c>
       <c r="F190" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G190" t="s">
         <v>23</v>
@@ -10807,13 +10816,13 @@
         <v>42</v>
       </c>
       <c r="K190" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M190" t="s">
         <v>27</v>
       </c>
       <c r="N190" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="P190" t="s">
         <v>28</v>
@@ -10827,7 +10836,7 @@
         <v>2402015</v>
       </c>
       <c r="B191" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C191" t="s">
         <v>157</v>
@@ -10839,7 +10848,7 @@
         <v>21</v>
       </c>
       <c r="F191" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G191" t="s">
         <v>23</v>
@@ -10854,7 +10863,7 @@
         <v>42</v>
       </c>
       <c r="K191" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M191" t="s">
         <v>27</v>
@@ -10872,7 +10881,7 @@
         <v>2403004</v>
       </c>
       <c r="B192" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C192" t="s">
         <v>157</v>
@@ -10899,16 +10908,16 @@
         <v>42</v>
       </c>
       <c r="K192" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L192" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M192" t="s">
         <v>27</v>
       </c>
       <c r="N192" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P192" t="s">
         <v>28</v>
@@ -10922,7 +10931,7 @@
         <v>2403004</v>
       </c>
       <c r="B193" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C193" t="s">
         <v>157</v>
@@ -10949,16 +10958,16 @@
         <v>42</v>
       </c>
       <c r="K193" t="s">
+        <v>410</v>
+      </c>
+      <c r="L193" t="s">
         <v>409</v>
       </c>
-      <c r="L193" t="s">
-        <v>408</v>
-      </c>
       <c r="M193" t="s">
         <v>27</v>
       </c>
       <c r="N193" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P193" t="s">
         <v>28</v>
@@ -10972,7 +10981,7 @@
         <v>2403004</v>
       </c>
       <c r="B194" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C194" t="s">
         <v>157</v>
@@ -10999,16 +11008,16 @@
         <v>42</v>
       </c>
       <c r="K194" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L194" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M194" t="s">
         <v>27</v>
       </c>
       <c r="N194" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P194" t="s">
         <v>28</v>
@@ -11022,7 +11031,7 @@
         <v>2403009</v>
       </c>
       <c r="B195" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C195" t="s">
         <v>157</v>
@@ -11049,10 +11058,10 @@
         <v>42</v>
       </c>
       <c r="K195" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L195" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M195" t="s">
         <v>27</v>
@@ -11069,7 +11078,7 @@
         <v>2403009</v>
       </c>
       <c r="B196" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C196" t="s">
         <v>157</v>
@@ -11096,10 +11105,10 @@
         <v>42</v>
       </c>
       <c r="K196" t="s">
+        <v>414</v>
+      </c>
+      <c r="L196" t="s">
         <v>413</v>
-      </c>
-      <c r="L196" t="s">
-        <v>412</v>
       </c>
       <c r="M196" t="s">
         <v>27</v>
@@ -11116,7 +11125,7 @@
         <v>2403009</v>
       </c>
       <c r="B197" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C197" t="s">
         <v>157</v>
@@ -11143,10 +11152,10 @@
         <v>42</v>
       </c>
       <c r="K197" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L197" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M197" t="s">
         <v>27</v>
@@ -11163,7 +11172,7 @@
         <v>2403013</v>
       </c>
       <c r="B198" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C198" t="s">
         <v>157</v>
@@ -11175,7 +11184,7 @@
         <v>21</v>
       </c>
       <c r="F198" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G198" t="s">
         <v>23</v>
@@ -11190,7 +11199,7 @@
         <v>25</v>
       </c>
       <c r="K198" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M198" t="s">
         <v>27</v>
@@ -11207,7 +11216,7 @@
         <v>2403013</v>
       </c>
       <c r="B199" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C199" t="s">
         <v>157</v>
@@ -11219,7 +11228,7 @@
         <v>21</v>
       </c>
       <c r="F199" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G199" t="s">
         <v>23</v>
@@ -11234,7 +11243,7 @@
         <v>25</v>
       </c>
       <c r="K199" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M199" t="s">
         <v>27</v>
@@ -11251,7 +11260,7 @@
         <v>2403013</v>
       </c>
       <c r="B200" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C200" t="s">
         <v>157</v>
@@ -11263,7 +11272,7 @@
         <v>21</v>
       </c>
       <c r="F200" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G200" t="s">
         <v>23</v>
@@ -11278,7 +11287,7 @@
         <v>25</v>
       </c>
       <c r="K200" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M200" t="s">
         <v>27</v>
@@ -11295,7 +11304,7 @@
         <v>2404001</v>
       </c>
       <c r="B201" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C201" t="s">
         <v>157</v>
@@ -11322,16 +11331,16 @@
         <v>42</v>
       </c>
       <c r="K201" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L201" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M201" t="s">
         <v>27</v>
       </c>
       <c r="N201" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P201" t="s">
         <v>28</v>
@@ -11345,7 +11354,7 @@
         <v>2404001</v>
       </c>
       <c r="B202" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C202" t="s">
         <v>157</v>
@@ -11372,16 +11381,16 @@
         <v>42</v>
       </c>
       <c r="K202" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L202" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M202" t="s">
         <v>27</v>
       </c>
       <c r="N202" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="P202" t="s">
         <v>28</v>
@@ -11395,7 +11404,7 @@
         <v>2404001</v>
       </c>
       <c r="B203" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C203" t="s">
         <v>157</v>
@@ -11422,16 +11431,16 @@
         <v>42</v>
       </c>
       <c r="K203" t="s">
+        <v>425</v>
+      </c>
+      <c r="L203" t="s">
+        <v>421</v>
+      </c>
+      <c r="M203" t="s">
+        <v>27</v>
+      </c>
+      <c r="N203" t="s">
         <v>424</v>
-      </c>
-      <c r="L203" t="s">
-        <v>420</v>
-      </c>
-      <c r="M203" t="s">
-        <v>27</v>
-      </c>
-      <c r="N203" t="s">
-        <v>423</v>
       </c>
       <c r="P203" t="s">
         <v>28</v>
@@ -11445,7 +11454,7 @@
         <v>2404006</v>
       </c>
       <c r="B204" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C204" t="s">
         <v>157</v>
@@ -11472,16 +11481,16 @@
         <v>42</v>
       </c>
       <c r="K204" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L204" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M204" t="s">
         <v>27</v>
       </c>
       <c r="N204" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P204" t="s">
         <v>28</v>
@@ -11495,7 +11504,7 @@
         <v>2404006</v>
       </c>
       <c r="B205" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C205" t="s">
         <v>157</v>
@@ -11522,16 +11531,16 @@
         <v>42</v>
       </c>
       <c r="K205" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L205" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M205" t="s">
         <v>27</v>
       </c>
       <c r="N205" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="P205" t="s">
         <v>28</v>
@@ -11545,7 +11554,7 @@
         <v>2404006</v>
       </c>
       <c r="B206" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C206" t="s">
         <v>157</v>
@@ -11572,16 +11581,16 @@
         <v>42</v>
       </c>
       <c r="K206" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L206" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M206" t="s">
         <v>27</v>
       </c>
       <c r="N206" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="P206" t="s">
         <v>28</v>
@@ -11595,7 +11604,7 @@
         <v>2404015</v>
       </c>
       <c r="B207" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C207" t="s">
         <v>157</v>
@@ -11607,7 +11616,7 @@
         <v>21</v>
       </c>
       <c r="F207" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="G207" t="s">
         <v>40</v>
@@ -11622,13 +11631,13 @@
         <v>25</v>
       </c>
       <c r="K207" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M207" t="s">
         <v>27</v>
       </c>
       <c r="N207" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="P207" t="s">
         <v>28</v>
@@ -11642,7 +11651,7 @@
         <v>2404015</v>
       </c>
       <c r="B208" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C208" t="s">
         <v>157</v>
@@ -11654,7 +11663,7 @@
         <v>21</v>
       </c>
       <c r="F208" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="G208" t="s">
         <v>40</v>
@@ -11663,19 +11672,19 @@
         <v>32</v>
       </c>
       <c r="I208" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J208" t="s">
         <v>25</v>
       </c>
       <c r="K208" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M208" t="s">
         <v>27</v>
       </c>
       <c r="N208" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="P208" t="s">
         <v>28</v>
@@ -11689,7 +11698,7 @@
         <v>2404015</v>
       </c>
       <c r="B209" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C209" t="s">
         <v>157</v>
@@ -11701,7 +11710,7 @@
         <v>21</v>
       </c>
       <c r="F209" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="G209" t="s">
         <v>40</v>
@@ -11710,19 +11719,19 @@
         <v>32</v>
       </c>
       <c r="I209" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="J209" t="s">
         <v>25</v>
       </c>
       <c r="K209" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M209" t="s">
         <v>27</v>
       </c>
       <c r="N209" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="P209" t="s">
         <v>28</v>
@@ -11736,7 +11745,7 @@
         <v>2405001</v>
       </c>
       <c r="B210" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C210" t="s">
         <v>157</v>
@@ -11763,16 +11772,16 @@
         <v>42</v>
       </c>
       <c r="K210" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="L210" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M210" t="s">
         <v>27</v>
       </c>
       <c r="N210" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P210" t="s">
         <v>28</v>
@@ -11786,7 +11795,7 @@
         <v>2405001</v>
       </c>
       <c r="B211" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C211" t="s">
         <v>157</v>
@@ -11813,16 +11822,16 @@
         <v>42</v>
       </c>
       <c r="K211" t="s">
+        <v>441</v>
+      </c>
+      <c r="L211" t="s">
         <v>440</v>
       </c>
-      <c r="L211" t="s">
-        <v>439</v>
-      </c>
       <c r="M211" t="s">
         <v>27</v>
       </c>
       <c r="N211" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P211" t="s">
         <v>28</v>
@@ -11836,7 +11845,7 @@
         <v>2405001</v>
       </c>
       <c r="B212" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C212" t="s">
         <v>157</v>
@@ -11863,16 +11872,16 @@
         <v>42</v>
       </c>
       <c r="K212" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L212" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M212" t="s">
         <v>27</v>
       </c>
       <c r="N212" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P212" t="s">
         <v>28</v>
@@ -11886,7 +11895,7 @@
         <v>2405006</v>
       </c>
       <c r="B213" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C213" t="s">
         <v>157</v>
@@ -11913,16 +11922,16 @@
         <v>42</v>
       </c>
       <c r="K213" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L213" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M213" t="s">
         <v>27</v>
       </c>
       <c r="N213" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="P213" t="s">
         <v>28</v>
@@ -11936,7 +11945,7 @@
         <v>2405006</v>
       </c>
       <c r="B214" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C214" t="s">
         <v>157</v>
@@ -11963,16 +11972,16 @@
         <v>42</v>
       </c>
       <c r="K214" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L214" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M214" t="s">
         <v>27</v>
       </c>
       <c r="N214" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="P214" t="s">
         <v>28</v>
@@ -11986,7 +11995,7 @@
         <v>2405006</v>
       </c>
       <c r="B215" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C215" t="s">
         <v>157</v>
@@ -12013,16 +12022,16 @@
         <v>42</v>
       </c>
       <c r="K215" t="s">
+        <v>448</v>
+      </c>
+      <c r="L215" t="s">
+        <v>444</v>
+      </c>
+      <c r="M215" t="s">
+        <v>27</v>
+      </c>
+      <c r="N215" t="s">
         <v>447</v>
-      </c>
-      <c r="L215" t="s">
-        <v>443</v>
-      </c>
-      <c r="M215" t="s">
-        <v>27</v>
-      </c>
-      <c r="N215" t="s">
-        <v>446</v>
       </c>
       <c r="P215" t="s">
         <v>28</v>
@@ -12036,7 +12045,7 @@
         <v>2405015</v>
       </c>
       <c r="B216" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C216" t="s">
         <v>157</v>
@@ -12048,7 +12057,7 @@
         <v>21</v>
       </c>
       <c r="F216" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G216" t="s">
         <v>23</v>
@@ -12063,16 +12072,16 @@
         <v>25</v>
       </c>
       <c r="K216" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L216" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M216" t="s">
         <v>27</v>
       </c>
       <c r="N216" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="P216" t="s">
         <v>28</v>
@@ -12086,7 +12095,7 @@
         <v>2405015</v>
       </c>
       <c r="B217" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C217" t="s">
         <v>157</v>
@@ -12098,7 +12107,7 @@
         <v>21</v>
       </c>
       <c r="F217" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G217" t="s">
         <v>23</v>
@@ -12113,16 +12122,16 @@
         <v>25</v>
       </c>
       <c r="K217" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L217" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M217" t="s">
         <v>27</v>
       </c>
       <c r="N217" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="P217" t="s">
         <v>28</v>
@@ -12136,7 +12145,7 @@
         <v>2405015</v>
       </c>
       <c r="B218" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C218" t="s">
         <v>157</v>
@@ -12148,7 +12157,7 @@
         <v>21</v>
       </c>
       <c r="F218" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G218" t="s">
         <v>23</v>
@@ -12163,13 +12172,13 @@
         <v>25</v>
       </c>
       <c r="K218" t="s">
+        <v>454</v>
+      </c>
+      <c r="M218" t="s">
+        <v>27</v>
+      </c>
+      <c r="N218" t="s">
         <v>453</v>
-      </c>
-      <c r="M218" t="s">
-        <v>27</v>
-      </c>
-      <c r="N218" t="s">
-        <v>452</v>
       </c>
       <c r="P218" t="s">
         <v>28</v>
@@ -12183,7 +12192,7 @@
         <v>2406004</v>
       </c>
       <c r="B219" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C219" t="s">
         <v>157</v>
@@ -12210,10 +12219,10 @@
         <v>25</v>
       </c>
       <c r="K219" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L219" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M219" t="s">
         <v>27</v>
@@ -12230,7 +12239,7 @@
         <v>2406004</v>
       </c>
       <c r="B220" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C220" t="s">
         <v>157</v>
@@ -12257,10 +12266,10 @@
         <v>25</v>
       </c>
       <c r="K220" t="s">
+        <v>458</v>
+      </c>
+      <c r="L220" t="s">
         <v>457</v>
-      </c>
-      <c r="L220" t="s">
-        <v>456</v>
       </c>
       <c r="M220" t="s">
         <v>27</v>
@@ -12277,7 +12286,7 @@
         <v>2406004</v>
       </c>
       <c r="B221" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C221" t="s">
         <v>157</v>
@@ -12298,13 +12307,13 @@
         <v>8</v>
       </c>
       <c r="I221" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J221" t="s">
         <v>25</v>
       </c>
       <c r="L221" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M221" t="s">
         <v>27</v>
@@ -12321,7 +12330,7 @@
         <v>2406004</v>
       </c>
       <c r="B222" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C222" t="s">
         <v>157</v>
@@ -12348,10 +12357,10 @@
         <v>25</v>
       </c>
       <c r="K222" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L222" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M222" t="s">
         <v>27</v>
@@ -12368,7 +12377,7 @@
         <v>2406004</v>
       </c>
       <c r="B223" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C223" t="s">
         <v>157</v>
@@ -12389,13 +12398,13 @@
         <v>8</v>
       </c>
       <c r="I223" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="J223" t="s">
         <v>25</v>
       </c>
       <c r="L223" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M223" t="s">
         <v>27</v>
@@ -12412,7 +12421,7 @@
         <v>2406009</v>
       </c>
       <c r="B224" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C224" t="s">
         <v>157</v>
@@ -12439,10 +12448,10 @@
         <v>25</v>
       </c>
       <c r="K224" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L224" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M224" t="s">
         <v>27</v>
@@ -12459,7 +12468,7 @@
         <v>2406009</v>
       </c>
       <c r="B225" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C225" t="s">
         <v>157</v>
@@ -12486,10 +12495,10 @@
         <v>25</v>
       </c>
       <c r="K225" t="s">
+        <v>462</v>
+      </c>
+      <c r="L225" t="s">
         <v>461</v>
-      </c>
-      <c r="L225" t="s">
-        <v>460</v>
       </c>
       <c r="M225" t="s">
         <v>27</v>
@@ -12506,7 +12515,7 @@
         <v>2406009</v>
       </c>
       <c r="B226" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C226" t="s">
         <v>157</v>
@@ -12527,16 +12536,16 @@
         <v>8</v>
       </c>
       <c r="I226" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J226" t="s">
         <v>25</v>
       </c>
       <c r="K226" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L226" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M226" t="s">
         <v>27</v>
@@ -12553,7 +12562,7 @@
         <v>2406009</v>
       </c>
       <c r="B227" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C227" t="s">
         <v>157</v>
@@ -12580,10 +12589,10 @@
         <v>25</v>
       </c>
       <c r="K227" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="L227" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M227" t="s">
         <v>27</v>
@@ -12600,7 +12609,7 @@
         <v>2406009</v>
       </c>
       <c r="B228" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C228" t="s">
         <v>157</v>
@@ -12621,16 +12630,16 @@
         <v>8</v>
       </c>
       <c r="I228" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="J228" t="s">
         <v>25</v>
       </c>
       <c r="K228" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L228" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M228" t="s">
         <v>27</v>
@@ -12647,7 +12656,7 @@
         <v>2406012</v>
       </c>
       <c r="B229" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C229" t="s">
         <v>157</v>
@@ -12659,7 +12668,7 @@
         <v>21</v>
       </c>
       <c r="F229" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="G229" t="s">
         <v>40</v>
@@ -12674,10 +12683,10 @@
         <v>42</v>
       </c>
       <c r="K229" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L229" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M229" t="s">
         <v>27</v>
@@ -12694,7 +12703,7 @@
         <v>2406012</v>
       </c>
       <c r="B230" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C230" t="s">
         <v>157</v>
@@ -12706,7 +12715,7 @@
         <v>21</v>
       </c>
       <c r="F230" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="G230" t="s">
         <v>40</v>
@@ -12715,16 +12724,16 @@
         <v>8</v>
       </c>
       <c r="I230" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="J230" t="s">
         <v>42</v>
       </c>
       <c r="K230" t="s">
+        <v>469</v>
+      </c>
+      <c r="L230" t="s">
         <v>468</v>
-      </c>
-      <c r="L230" t="s">
-        <v>467</v>
       </c>
       <c r="M230" t="s">
         <v>27</v>
@@ -12741,7 +12750,7 @@
         <v>2406012</v>
       </c>
       <c r="B231" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C231" t="s">
         <v>157</v>
@@ -12753,7 +12762,7 @@
         <v>21</v>
       </c>
       <c r="F231" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="G231" t="s">
         <v>40</v>
@@ -12762,16 +12771,16 @@
         <v>8</v>
       </c>
       <c r="I231" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J231" t="s">
         <v>42</v>
       </c>
       <c r="K231" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L231" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M231" t="s">
         <v>27</v>
@@ -12788,10 +12797,10 @@
         <v>2059001</v>
       </c>
       <c r="B232" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C232" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D232" s="2">
         <v>1</v>
@@ -12815,10 +12824,10 @@
         <v>42</v>
       </c>
       <c r="K232" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L232" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="M232" t="s">
         <v>27</v>
@@ -12835,10 +12844,10 @@
         <v>2059002</v>
       </c>
       <c r="B233" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C233" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D233" s="2">
         <v>1</v>
@@ -12862,10 +12871,10 @@
         <v>42</v>
       </c>
       <c r="K233" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L233" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M233" t="s">
         <v>27</v>
@@ -12882,10 +12891,10 @@
         <v>2059006</v>
       </c>
       <c r="B234" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C234" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D234" s="2">
         <v>1</v>
@@ -12909,10 +12918,10 @@
         <v>42</v>
       </c>
       <c r="K234" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="L234" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M234" t="s">
         <v>27</v>
@@ -12929,10 +12938,10 @@
         <v>2140011</v>
       </c>
       <c r="B235" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C235" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D235" s="2">
         <v>2</v>
@@ -12941,7 +12950,7 @@
         <v>21</v>
       </c>
       <c r="F235" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G235" t="s">
         <v>40</v>
@@ -12959,7 +12968,7 @@
         <v>159</v>
       </c>
       <c r="L235" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M235" t="s">
         <v>27</v>
@@ -12976,10 +12985,10 @@
         <v>2390004</v>
       </c>
       <c r="B236" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C236" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D236" s="2">
         <v>1</v>
@@ -13003,10 +13012,10 @@
         <v>25</v>
       </c>
       <c r="K236" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="L236" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M236" t="s">
         <v>27</v>
@@ -13023,10 +13032,10 @@
         <v>2390004</v>
       </c>
       <c r="B237" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C237" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D237" s="2">
         <v>1</v>
@@ -13050,10 +13059,10 @@
         <v>25</v>
       </c>
       <c r="K237" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L237" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M237" t="s">
         <v>27</v>
@@ -13070,10 +13079,10 @@
         <v>2390004</v>
       </c>
       <c r="B238" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C238" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D238" s="2">
         <v>1</v>
@@ -13097,10 +13106,10 @@
         <v>25</v>
       </c>
       <c r="K238" t="s">
+        <v>486</v>
+      </c>
+      <c r="L238" t="s">
         <v>485</v>
-      </c>
-      <c r="L238" t="s">
-        <v>484</v>
       </c>
       <c r="M238" t="s">
         <v>27</v>
@@ -13117,10 +13126,10 @@
         <v>2390009</v>
       </c>
       <c r="B239" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C239" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D239" s="2">
         <v>1</v>
@@ -13144,10 +13153,10 @@
         <v>25</v>
       </c>
       <c r="K239" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L239" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M239" t="s">
         <v>27</v>
@@ -13164,10 +13173,10 @@
         <v>2390009</v>
       </c>
       <c r="B240" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C240" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D240" s="2">
         <v>1</v>
@@ -13191,10 +13200,10 @@
         <v>25</v>
       </c>
       <c r="K240" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L240" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M240" t="s">
         <v>27</v>
@@ -13211,10 +13220,10 @@
         <v>2390009</v>
       </c>
       <c r="B241" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C241" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D241" s="2">
         <v>1</v>
@@ -13238,10 +13247,10 @@
         <v>25</v>
       </c>
       <c r="K241" t="s">
+        <v>491</v>
+      </c>
+      <c r="L241" t="s">
         <v>490</v>
-      </c>
-      <c r="L241" t="s">
-        <v>489</v>
       </c>
       <c r="M241" t="s">
         <v>27</v>
@@ -13258,10 +13267,10 @@
         <v>2390013</v>
       </c>
       <c r="B242" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C242" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D242" s="2">
         <v>2</v>
@@ -13270,7 +13279,7 @@
         <v>21</v>
       </c>
       <c r="F242" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G242" t="s">
         <v>23</v>
@@ -13285,7 +13294,7 @@
         <v>42</v>
       </c>
       <c r="K242" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M242" t="s">
         <v>27</v>
@@ -13302,10 +13311,10 @@
         <v>2390013</v>
       </c>
       <c r="B243" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C243" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D243" s="2">
         <v>2</v>
@@ -13314,7 +13323,7 @@
         <v>21</v>
       </c>
       <c r="F243" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G243" t="s">
         <v>23</v>
@@ -13329,7 +13338,7 @@
         <v>42</v>
       </c>
       <c r="K243" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M243" t="s">
         <v>27</v>
@@ -13346,10 +13355,10 @@
         <v>2390013</v>
       </c>
       <c r="B244" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C244" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D244" s="2">
         <v>2</v>
@@ -13358,7 +13367,7 @@
         <v>21</v>
       </c>
       <c r="F244" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G244" t="s">
         <v>23</v>
@@ -13373,7 +13382,7 @@
         <v>42</v>
       </c>
       <c r="K244" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M244" t="s">
         <v>27</v>

--- a/POD_2026-27_11-5-2026.xlsx
+++ b/POD_2026-27_11-5-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://urjc-my.sharepoint.com/personal/esther_garcia_urjc_es/Documents/Documentos/POD 2026-27/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="274" documentId="11_79C815625599F410B0C00D3910C611C600045ACD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD31BD61-4F73-45ED-B163-F6590E3AC3C8}"/>
+  <xr:revisionPtr revIDLastSave="284" documentId="11_79C815625599F410B0C00D3910C611C600045ACD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F3CCF80-2BEA-4692-A7E5-C7FE4DB22D11}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2931" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2935" uniqueCount="498">
   <si>
     <t>POD_2026-27_11-5-2026</t>
   </si>
@@ -194,10 +194,10 @@
     <t>V=&gt;(09:00-11:00)[11/09/26, 18/09/26, 25/09/26, 02/10/26, 09/10/26, 16/10/26, 23/10/26, 30/10/26, 06/11/26, 13/11/26, 20/11/26, 27/11/26, 11/12/26, 18/12/26], X=&gt;(11:00-13:00)[16/09/26, 30/09/26, 14/10/26, 28/10/26, 11/11/26, 25/11/26]</t>
   </si>
   <si>
-    <t>ARIEL SÁNCHEZ(22)</t>
-  </si>
-  <si>
-    <t>ARIEL SÁNCHEZ(8)</t>
+    <t>ARIEL SÁNCHEZ(22), RAZVAN IAGAR (22)</t>
+  </si>
+  <si>
+    <t>ARIEL SÁNCHEZ(8), RAZVAN IAGAR (8)</t>
   </si>
   <si>
     <t>AMPLIACION DE MATEMATICA APLICADA</t>
@@ -848,6 +848,9 @@
     <t>G_ECO-MAT_5A(M) (2299053), G_ED_PRIM-MAT_EXT_4A(M) (2178053), G_ED_PRIM-MAT_SUSP_4A(M) (2348053), G_INF-MAT_EXT_4A(M) (2117042), G_INF-MAT_4A(M) (2315046), G_MAT_EXT_I_3A(M) (2028029), G_SOFT-MAT_EXT_4A(M) (2118041), G_SOFT-MAT_4A(M) (2316046)</t>
   </si>
   <si>
+    <t>RAZVAN IAGAR (30)</t>
+  </si>
+  <si>
     <t>METODOS NUMERICOS</t>
   </si>
   <si>
@@ -962,10 +965,16 @@
     <t>G_C_EXP_EXT822_II_1A(M) (2336005), G_C_EXP_I_EXT_1A(M) (2119005)</t>
   </si>
   <si>
+    <t>RAZVAN IAGAR (48)</t>
+  </si>
+  <si>
     <t>M=&gt;(15:00-17:00)[22/09/26, 13/10/26, 27/10/26, 10/11/26, 24/11/26]</t>
   </si>
   <si>
     <t>G_C_EXP_EXT822_II_1A(M) (2336005)</t>
+  </si>
+  <si>
+    <t>RAZVAN IAGAR (12)</t>
   </si>
   <si>
     <t>M=&gt;(15:00-17:00)[06/10/26, 20/10/26, 03/11/26, 17/11/26, 01/12/26, 15/12/26]</t>
@@ -7260,6 +7269,9 @@
       <c r="M115" t="s">
         <v>219</v>
       </c>
+      <c r="N115" t="s">
+        <v>270</v>
+      </c>
       <c r="P115" t="s">
         <v>28</v>
       </c>
@@ -7284,7 +7296,7 @@
         <v>21</v>
       </c>
       <c r="F116" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G116" t="s">
         <v>40</v>
@@ -7299,10 +7311,10 @@
         <v>42</v>
       </c>
       <c r="K116" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L116" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M116" t="s">
         <v>27</v>
@@ -7334,10 +7346,10 @@
         <v>21</v>
       </c>
       <c r="F117" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G117" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H117" s="2">
         <v>60</v>
@@ -7349,10 +7361,10 @@
         <v>42</v>
       </c>
       <c r="K117" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L117" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M117" t="s">
         <v>27</v>
@@ -7372,7 +7384,7 @@
         <v>2361002</v>
       </c>
       <c r="B118" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C118" t="s">
         <v>157</v>
@@ -7399,7 +7411,7 @@
         <v>42</v>
       </c>
       <c r="K118" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M118" t="s">
         <v>27</v>
@@ -7416,7 +7428,7 @@
         <v>2361002</v>
       </c>
       <c r="B119" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C119" t="s">
         <v>157</v>
@@ -7443,7 +7455,7 @@
         <v>42</v>
       </c>
       <c r="K119" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M119" t="s">
         <v>27</v>
@@ -7460,7 +7472,7 @@
         <v>2361002</v>
       </c>
       <c r="B120" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C120" t="s">
         <v>157</v>
@@ -7487,7 +7499,7 @@
         <v>42</v>
       </c>
       <c r="K120" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M120" t="s">
         <v>27</v>
@@ -7504,7 +7516,7 @@
         <v>2361004</v>
       </c>
       <c r="B121" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C121" t="s">
         <v>157</v>
@@ -7531,7 +7543,7 @@
         <v>42</v>
       </c>
       <c r="K121" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M121" t="s">
         <v>27</v>
@@ -7548,7 +7560,7 @@
         <v>2393002</v>
       </c>
       <c r="B122" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C122" t="s">
         <v>157</v>
@@ -7575,10 +7587,10 @@
         <v>42</v>
       </c>
       <c r="K122" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L122" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M122" t="s">
         <v>27</v>
@@ -7595,7 +7607,7 @@
         <v>2393002</v>
       </c>
       <c r="B123" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C123" t="s">
         <v>157</v>
@@ -7616,16 +7628,16 @@
         <v>20</v>
       </c>
       <c r="I123" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="J123" t="s">
         <v>42</v>
       </c>
       <c r="K123" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L123" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M123" t="s">
         <v>27</v>
@@ -7642,7 +7654,7 @@
         <v>2393002</v>
       </c>
       <c r="B124" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C124" t="s">
         <v>157</v>
@@ -7663,16 +7675,16 @@
         <v>20</v>
       </c>
       <c r="I124" t="s">
+        <v>288</v>
+      </c>
+      <c r="J124" t="s">
+        <v>42</v>
+      </c>
+      <c r="K124" t="s">
+        <v>289</v>
+      </c>
+      <c r="L124" t="s">
         <v>287</v>
-      </c>
-      <c r="J124" t="s">
-        <v>42</v>
-      </c>
-      <c r="K124" t="s">
-        <v>288</v>
-      </c>
-      <c r="L124" t="s">
-        <v>286</v>
       </c>
       <c r="M124" t="s">
         <v>27</v>
@@ -7689,7 +7701,7 @@
         <v>2394004</v>
       </c>
       <c r="B125" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C125" t="s">
         <v>157</v>
@@ -7716,10 +7728,10 @@
         <v>25</v>
       </c>
       <c r="K125" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L125" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M125" t="s">
         <v>27</v>
@@ -7736,7 +7748,7 @@
         <v>2394004</v>
       </c>
       <c r="B126" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C126" t="s">
         <v>157</v>
@@ -7763,10 +7775,10 @@
         <v>25</v>
       </c>
       <c r="K126" t="s">
+        <v>293</v>
+      </c>
+      <c r="L126" t="s">
         <v>292</v>
-      </c>
-      <c r="L126" t="s">
-        <v>291</v>
       </c>
       <c r="M126" t="s">
         <v>27</v>
@@ -7783,7 +7795,7 @@
         <v>2394004</v>
       </c>
       <c r="B127" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C127" t="s">
         <v>157</v>
@@ -7810,10 +7822,10 @@
         <v>25</v>
       </c>
       <c r="K127" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L127" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M127" t="s">
         <v>27</v>
@@ -7830,7 +7842,7 @@
         <v>2395003</v>
       </c>
       <c r="B128" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C128" t="s">
         <v>157</v>
@@ -7857,10 +7869,10 @@
         <v>42</v>
       </c>
       <c r="K128" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L128" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M128" t="s">
         <v>27</v>
@@ -7877,7 +7889,7 @@
         <v>2395003</v>
       </c>
       <c r="B129" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C129" t="s">
         <v>157</v>
@@ -7904,10 +7916,10 @@
         <v>42</v>
       </c>
       <c r="K129" t="s">
+        <v>298</v>
+      </c>
+      <c r="L129" t="s">
         <v>297</v>
-      </c>
-      <c r="L129" t="s">
-        <v>296</v>
       </c>
       <c r="M129" t="s">
         <v>27</v>
@@ -7924,7 +7936,7 @@
         <v>2395003</v>
       </c>
       <c r="B130" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C130" t="s">
         <v>157</v>
@@ -7951,10 +7963,10 @@
         <v>42</v>
       </c>
       <c r="K130" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L130" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M130" t="s">
         <v>27</v>
@@ -7971,7 +7983,7 @@
         <v>2396001</v>
       </c>
       <c r="B131" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C131" t="s">
         <v>157</v>
@@ -7998,10 +8010,10 @@
         <v>25</v>
       </c>
       <c r="K131" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L131" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="M131" t="s">
         <v>27</v>
@@ -8018,7 +8030,7 @@
         <v>2396001</v>
       </c>
       <c r="B132" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C132" t="s">
         <v>157</v>
@@ -8045,10 +8057,10 @@
         <v>25</v>
       </c>
       <c r="K132" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L132" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M132" t="s">
         <v>27</v>
@@ -8065,7 +8077,7 @@
         <v>2396001</v>
       </c>
       <c r="B133" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C133" t="s">
         <v>157</v>
@@ -8092,10 +8104,10 @@
         <v>25</v>
       </c>
       <c r="K133" t="s">
+        <v>305</v>
+      </c>
+      <c r="L133" t="s">
         <v>304</v>
-      </c>
-      <c r="L133" t="s">
-        <v>303</v>
       </c>
       <c r="M133" t="s">
         <v>27</v>
@@ -8112,7 +8124,7 @@
         <v>2397003</v>
       </c>
       <c r="B134" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C134" t="s">
         <v>157</v>
@@ -8139,13 +8151,16 @@
         <v>25</v>
       </c>
       <c r="K134" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L134" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M134" t="s">
         <v>27</v>
+      </c>
+      <c r="N134" t="s">
+        <v>309</v>
       </c>
       <c r="P134" t="s">
         <v>28</v>
@@ -8159,7 +8174,7 @@
         <v>2397003</v>
       </c>
       <c r="B135" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C135" t="s">
         <v>157</v>
@@ -8186,13 +8201,16 @@
         <v>25</v>
       </c>
       <c r="K135" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="L135" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="M135" t="s">
         <v>27</v>
+      </c>
+      <c r="N135" t="s">
+        <v>312</v>
       </c>
       <c r="P135" t="s">
         <v>28</v>
@@ -8206,7 +8224,7 @@
         <v>2397003</v>
       </c>
       <c r="B136" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C136" t="s">
         <v>157</v>
@@ -8233,13 +8251,16 @@
         <v>25</v>
       </c>
       <c r="K136" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="L136" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="M136" t="s">
         <v>27</v>
+      </c>
+      <c r="N136" t="s">
+        <v>312</v>
       </c>
       <c r="P136" t="s">
         <v>28</v>
@@ -8253,7 +8274,7 @@
         <v>2397008</v>
       </c>
       <c r="B137" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C137" t="s">
         <v>157</v>
@@ -8280,10 +8301,10 @@
         <v>25</v>
       </c>
       <c r="K137" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="L137" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="M137" t="s">
         <v>27</v>
@@ -8300,7 +8321,7 @@
         <v>2397008</v>
       </c>
       <c r="B138" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C138" t="s">
         <v>157</v>
@@ -8327,10 +8348,10 @@
         <v>25</v>
       </c>
       <c r="K138" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="L138" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="M138" t="s">
         <v>27</v>
@@ -8347,7 +8368,7 @@
         <v>2397008</v>
       </c>
       <c r="B139" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C139" t="s">
         <v>157</v>
@@ -8374,10 +8395,10 @@
         <v>25</v>
       </c>
       <c r="K139" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="L139" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="M139" t="s">
         <v>27</v>
@@ -8394,7 +8415,7 @@
         <v>2398001</v>
       </c>
       <c r="B140" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C140" t="s">
         <v>157</v>
@@ -8421,16 +8442,16 @@
         <v>42</v>
       </c>
       <c r="K140" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="L140" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="M140" t="s">
         <v>27</v>
       </c>
       <c r="N140" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="P140" t="s">
         <v>28</v>
@@ -8444,7 +8465,7 @@
         <v>2398001</v>
       </c>
       <c r="B141" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C141" t="s">
         <v>157</v>
@@ -8471,16 +8492,16 @@
         <v>42</v>
       </c>
       <c r="K141" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="L141" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="M141" t="s">
         <v>27</v>
       </c>
       <c r="N141" s="4" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="P141" t="s">
         <v>28</v>
@@ -8494,7 +8515,7 @@
         <v>2398001</v>
       </c>
       <c r="B142" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C142" t="s">
         <v>157</v>
@@ -8521,16 +8542,16 @@
         <v>42</v>
       </c>
       <c r="K142" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="L142" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="M142" t="s">
         <v>27</v>
       </c>
       <c r="N142" s="4" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="P142" t="s">
         <v>28</v>
@@ -8544,7 +8565,7 @@
         <v>2398006</v>
       </c>
       <c r="B143" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C143" t="s">
         <v>157</v>
@@ -8571,10 +8592,10 @@
         <v>42</v>
       </c>
       <c r="K143" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="L143" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="M143" t="s">
         <v>27</v>
@@ -8591,7 +8612,7 @@
         <v>2398006</v>
       </c>
       <c r="B144" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C144" t="s">
         <v>157</v>
@@ -8618,10 +8639,10 @@
         <v>42</v>
       </c>
       <c r="K144" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="L144" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="M144" t="s">
         <v>27</v>
@@ -8638,7 +8659,7 @@
         <v>2398006</v>
       </c>
       <c r="B145" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C145" t="s">
         <v>157</v>
@@ -8665,10 +8686,10 @@
         <v>42</v>
       </c>
       <c r="K145" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="L145" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="M145" t="s">
         <v>27</v>
@@ -8685,7 +8706,7 @@
         <v>2398013</v>
       </c>
       <c r="B146" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C146" t="s">
         <v>157</v>
@@ -8712,10 +8733,10 @@
         <v>25</v>
       </c>
       <c r="K146" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="L146" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="M146" t="s">
         <v>27</v>
@@ -8732,7 +8753,7 @@
         <v>2398013</v>
       </c>
       <c r="B147" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C147" t="s">
         <v>157</v>
@@ -8759,10 +8780,10 @@
         <v>25</v>
       </c>
       <c r="K147" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="L147" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="M147" t="s">
         <v>27</v>
@@ -8779,7 +8800,7 @@
         <v>2398013</v>
       </c>
       <c r="B148" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C148" t="s">
         <v>157</v>
@@ -8806,7 +8827,7 @@
         <v>25</v>
       </c>
       <c r="K148" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="M148" t="s">
         <v>27</v>
@@ -8823,7 +8844,7 @@
         <v>2399003</v>
       </c>
       <c r="B149" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C149" t="s">
         <v>157</v>
@@ -8850,10 +8871,10 @@
         <v>42</v>
       </c>
       <c r="K149" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L149" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="M149" t="s">
         <v>27</v>
@@ -8870,7 +8891,7 @@
         <v>2399003</v>
       </c>
       <c r="B150" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C150" t="s">
         <v>157</v>
@@ -8897,10 +8918,10 @@
         <v>42</v>
       </c>
       <c r="K150" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="L150" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="M150" t="s">
         <v>27</v>
@@ -8917,7 +8938,7 @@
         <v>2399003</v>
       </c>
       <c r="B151" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C151" t="s">
         <v>157</v>
@@ -8944,10 +8965,10 @@
         <v>42</v>
       </c>
       <c r="K151" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="L151" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="M151" t="s">
         <v>27</v>
@@ -8964,7 +8985,7 @@
         <v>2399010</v>
       </c>
       <c r="B152" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C152" t="s">
         <v>157</v>
@@ -8991,10 +9012,10 @@
         <v>42</v>
       </c>
       <c r="K152" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="L152" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="M152" t="s">
         <v>27</v>
@@ -9011,7 +9032,7 @@
         <v>2399010</v>
       </c>
       <c r="B153" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C153" t="s">
         <v>157</v>
@@ -9038,10 +9059,10 @@
         <v>42</v>
       </c>
       <c r="K153" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="L153" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="M153" t="s">
         <v>27</v>
@@ -9058,7 +9079,7 @@
         <v>2399010</v>
       </c>
       <c r="B154" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C154" t="s">
         <v>157</v>
@@ -9085,10 +9106,10 @@
         <v>42</v>
       </c>
       <c r="K154" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="L154" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="M154" t="s">
         <v>27</v>
@@ -9105,7 +9126,7 @@
         <v>2399014</v>
       </c>
       <c r="B155" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C155" t="s">
         <v>157</v>
@@ -9132,10 +9153,10 @@
         <v>25</v>
       </c>
       <c r="K155" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="L155" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="M155" t="s">
         <v>27</v>
@@ -9152,7 +9173,7 @@
         <v>2399014</v>
       </c>
       <c r="B156" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C156" t="s">
         <v>157</v>
@@ -9179,10 +9200,10 @@
         <v>25</v>
       </c>
       <c r="K156" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="L156" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="M156" t="s">
         <v>27</v>
@@ -9199,7 +9220,7 @@
         <v>2399014</v>
       </c>
       <c r="B157" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C157" t="s">
         <v>157</v>
@@ -9226,7 +9247,7 @@
         <v>25</v>
       </c>
       <c r="K157" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="M157" t="s">
         <v>27</v>
@@ -9243,7 +9264,7 @@
         <v>2400003</v>
       </c>
       <c r="B158" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C158" t="s">
         <v>157</v>
@@ -9270,16 +9291,16 @@
         <v>42</v>
       </c>
       <c r="K158" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="L158" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="M158" t="s">
         <v>27</v>
       </c>
       <c r="N158" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="P158" t="s">
         <v>28</v>
@@ -9293,7 +9314,7 @@
         <v>2400003</v>
       </c>
       <c r="B159" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C159" t="s">
         <v>157</v>
@@ -9320,16 +9341,16 @@
         <v>42</v>
       </c>
       <c r="K159" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="L159" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="M159" t="s">
         <v>27</v>
       </c>
       <c r="N159" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="P159" t="s">
         <v>28</v>
@@ -9343,7 +9364,7 @@
         <v>2400003</v>
       </c>
       <c r="B160" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C160" t="s">
         <v>157</v>
@@ -9370,16 +9391,16 @@
         <v>42</v>
       </c>
       <c r="K160" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="L160" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="M160" t="s">
         <v>27</v>
       </c>
       <c r="N160" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="P160" t="s">
         <v>28</v>
@@ -9393,7 +9414,7 @@
         <v>2400008</v>
       </c>
       <c r="B161" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C161" t="s">
         <v>157</v>
@@ -9420,10 +9441,10 @@
         <v>42</v>
       </c>
       <c r="K161" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="L161" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="M161" t="s">
         <v>27</v>
@@ -9440,7 +9461,7 @@
         <v>2400008</v>
       </c>
       <c r="B162" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C162" t="s">
         <v>157</v>
@@ -9467,10 +9488,10 @@
         <v>42</v>
       </c>
       <c r="K162" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="L162" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="M162" t="s">
         <v>27</v>
@@ -9487,7 +9508,7 @@
         <v>2400008</v>
       </c>
       <c r="B163" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C163" t="s">
         <v>157</v>
@@ -9514,10 +9535,10 @@
         <v>42</v>
       </c>
       <c r="K163" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="L163" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="M163" t="s">
         <v>27</v>
@@ -9534,7 +9555,7 @@
         <v>2400012</v>
       </c>
       <c r="B164" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C164" t="s">
         <v>157</v>
@@ -9561,16 +9582,16 @@
         <v>25</v>
       </c>
       <c r="K164" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L164" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="M164" t="s">
         <v>27</v>
       </c>
       <c r="N164" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="P164" t="s">
         <v>28</v>
@@ -9584,7 +9605,7 @@
         <v>2400012</v>
       </c>
       <c r="B165" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C165" t="s">
         <v>157</v>
@@ -9611,16 +9632,16 @@
         <v>25</v>
       </c>
       <c r="K165" s="3" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="L165" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="M165" t="s">
         <v>27</v>
       </c>
       <c r="N165" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="P165" t="s">
         <v>28</v>
@@ -9634,7 +9655,7 @@
         <v>2400012</v>
       </c>
       <c r="B166" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C166" t="s">
         <v>157</v>
@@ -9661,13 +9682,13 @@
         <v>25</v>
       </c>
       <c r="K166" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="M166" t="s">
         <v>27</v>
       </c>
       <c r="N166" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="P166" t="s">
         <v>28</v>
@@ -9681,7 +9702,7 @@
         <v>2401001</v>
       </c>
       <c r="B167" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C167" t="s">
         <v>157</v>
@@ -9708,10 +9729,10 @@
         <v>25</v>
       </c>
       <c r="K167" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="L167" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="M167" t="s">
         <v>27</v>
@@ -9728,7 +9749,7 @@
         <v>2401001</v>
       </c>
       <c r="B168" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C168" t="s">
         <v>157</v>
@@ -9755,10 +9776,10 @@
         <v>25</v>
       </c>
       <c r="K168" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="L168" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="M168" t="s">
         <v>27</v>
@@ -9775,7 +9796,7 @@
         <v>2401001</v>
       </c>
       <c r="B169" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C169" t="s">
         <v>157</v>
@@ -9802,10 +9823,10 @@
         <v>25</v>
       </c>
       <c r="K169" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="L169" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="M169" t="s">
         <v>27</v>
@@ -9822,7 +9843,7 @@
         <v>2401007</v>
       </c>
       <c r="B170" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C170" t="s">
         <v>157</v>
@@ -9849,10 +9870,10 @@
         <v>25</v>
       </c>
       <c r="K170" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="L170" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="M170" t="s">
         <v>27</v>
@@ -9869,7 +9890,7 @@
         <v>2401007</v>
       </c>
       <c r="B171" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C171" t="s">
         <v>157</v>
@@ -9896,10 +9917,10 @@
         <v>25</v>
       </c>
       <c r="K171" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="L171" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="M171" t="s">
         <v>27</v>
@@ -9916,7 +9937,7 @@
         <v>2401007</v>
       </c>
       <c r="B172" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C172" t="s">
         <v>157</v>
@@ -9943,10 +9964,10 @@
         <v>25</v>
       </c>
       <c r="K172" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="L172" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="M172" t="s">
         <v>27</v>
@@ -9963,7 +9984,7 @@
         <v>2401013</v>
       </c>
       <c r="B173" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C173" t="s">
         <v>157</v>
@@ -9975,7 +9996,7 @@
         <v>21</v>
       </c>
       <c r="F173" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="G173" t="s">
         <v>40</v>
@@ -9990,16 +10011,16 @@
         <v>42</v>
       </c>
       <c r="K173" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="L173" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="M173" t="s">
         <v>27</v>
       </c>
       <c r="N173" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="P173" t="s">
         <v>28</v>
@@ -10013,7 +10034,7 @@
         <v>2401013</v>
       </c>
       <c r="B174" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C174" t="s">
         <v>157</v>
@@ -10025,7 +10046,7 @@
         <v>21</v>
       </c>
       <c r="F174" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="G174" t="s">
         <v>40</v>
@@ -10040,16 +10061,16 @@
         <v>42</v>
       </c>
       <c r="K174" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="L174" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="M174" t="s">
         <v>27</v>
       </c>
       <c r="N174" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="P174" t="s">
         <v>28</v>
@@ -10063,7 +10084,7 @@
         <v>2401013</v>
       </c>
       <c r="B175" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C175" t="s">
         <v>157</v>
@@ -10075,7 +10096,7 @@
         <v>21</v>
       </c>
       <c r="F175" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="G175" t="s">
         <v>40</v>
@@ -10090,16 +10111,16 @@
         <v>42</v>
       </c>
       <c r="K175" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="L175" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="M175" t="s">
         <v>27</v>
       </c>
       <c r="N175" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="P175" t="s">
         <v>28</v>
@@ -10113,7 +10134,7 @@
         <v>2401018</v>
       </c>
       <c r="B176" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C176" t="s">
         <v>157</v>
@@ -10125,7 +10146,7 @@
         <v>35</v>
       </c>
       <c r="F176" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="G176" t="s">
         <v>40</v>
@@ -10140,10 +10161,10 @@
         <v>42</v>
       </c>
       <c r="K176" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="L176" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="M176" t="s">
         <v>27</v>
@@ -10160,7 +10181,7 @@
         <v>2401018</v>
       </c>
       <c r="B177" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C177" t="s">
         <v>157</v>
@@ -10172,7 +10193,7 @@
         <v>35</v>
       </c>
       <c r="F177" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="G177" t="s">
         <v>40</v>
@@ -10187,10 +10208,10 @@
         <v>42</v>
       </c>
       <c r="K177" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="L177" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="M177" t="s">
         <v>27</v>
@@ -10207,7 +10228,7 @@
         <v>2401018</v>
       </c>
       <c r="B178" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C178" t="s">
         <v>157</v>
@@ -10219,7 +10240,7 @@
         <v>35</v>
       </c>
       <c r="F178" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="G178" t="s">
         <v>40</v>
@@ -10228,16 +10249,16 @@
         <v>4</v>
       </c>
       <c r="I178" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="J178" t="s">
         <v>42</v>
       </c>
       <c r="K178" t="s">
+        <v>386</v>
+      </c>
+      <c r="L178" t="s">
         <v>383</v>
-      </c>
-      <c r="L178" t="s">
-        <v>380</v>
       </c>
       <c r="M178" t="s">
         <v>27</v>
@@ -10254,7 +10275,7 @@
         <v>2401018</v>
       </c>
       <c r="B179" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C179" t="s">
         <v>157</v>
@@ -10266,7 +10287,7 @@
         <v>35</v>
       </c>
       <c r="F179" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="G179" t="s">
         <v>40</v>
@@ -10281,10 +10302,10 @@
         <v>42</v>
       </c>
       <c r="K179" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="L179" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="M179" t="s">
         <v>27</v>
@@ -10301,7 +10322,7 @@
         <v>2401018</v>
       </c>
       <c r="B180" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C180" t="s">
         <v>157</v>
@@ -10313,7 +10334,7 @@
         <v>35</v>
       </c>
       <c r="F180" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="G180" t="s">
         <v>40</v>
@@ -10322,16 +10343,16 @@
         <v>4</v>
       </c>
       <c r="I180" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="J180" t="s">
         <v>42</v>
       </c>
       <c r="K180" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="L180" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="M180" t="s">
         <v>27</v>
@@ -10348,7 +10369,7 @@
         <v>2401018</v>
       </c>
       <c r="B181" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C181" t="s">
         <v>157</v>
@@ -10360,7 +10381,7 @@
         <v>35</v>
       </c>
       <c r="F181" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="G181" t="s">
         <v>40</v>
@@ -10369,16 +10390,16 @@
         <v>4</v>
       </c>
       <c r="I181" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="J181" t="s">
         <v>42</v>
       </c>
       <c r="K181" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="L181" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="M181" t="s">
         <v>27</v>
@@ -10395,7 +10416,7 @@
         <v>2401018</v>
       </c>
       <c r="B182" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C182" t="s">
         <v>157</v>
@@ -10407,7 +10428,7 @@
         <v>35</v>
       </c>
       <c r="F182" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="G182" t="s">
         <v>40</v>
@@ -10416,16 +10437,16 @@
         <v>4</v>
       </c>
       <c r="I182" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="J182" t="s">
         <v>42</v>
       </c>
       <c r="K182" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="L182" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="M182" t="s">
         <v>27</v>
@@ -10442,7 +10463,7 @@
         <v>2402003</v>
       </c>
       <c r="B183" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C183" t="s">
         <v>157</v>
@@ -10469,16 +10490,16 @@
         <v>25</v>
       </c>
       <c r="K183" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="L183" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="M183" t="s">
         <v>27</v>
       </c>
       <c r="N183" s="4" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="P183" t="s">
         <v>28</v>
@@ -10492,7 +10513,7 @@
         <v>2402003</v>
       </c>
       <c r="B184" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C184" t="s">
         <v>157</v>
@@ -10519,16 +10540,16 @@
         <v>25</v>
       </c>
       <c r="K184" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="L184" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="M184" t="s">
         <v>27</v>
       </c>
       <c r="N184" s="4" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="P184" t="s">
         <v>28</v>
@@ -10542,7 +10563,7 @@
         <v>2402003</v>
       </c>
       <c r="B185" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C185" t="s">
         <v>157</v>
@@ -10569,16 +10590,16 @@
         <v>25</v>
       </c>
       <c r="K185" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="L185" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="M185" t="s">
         <v>27</v>
       </c>
       <c r="N185" s="4" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="P185" t="s">
         <v>28</v>
@@ -10592,7 +10613,7 @@
         <v>2402008</v>
       </c>
       <c r="B186" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C186" t="s">
         <v>157</v>
@@ -10619,16 +10640,16 @@
         <v>25</v>
       </c>
       <c r="K186" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="L186" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="M186" t="s">
         <v>27</v>
       </c>
       <c r="N186" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="P186" t="s">
         <v>28</v>
@@ -10642,7 +10663,7 @@
         <v>2402008</v>
       </c>
       <c r="B187" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C187" t="s">
         <v>157</v>
@@ -10669,16 +10690,16 @@
         <v>25</v>
       </c>
       <c r="K187" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="L187" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="M187" t="s">
         <v>27</v>
       </c>
       <c r="N187" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="P187" t="s">
         <v>28</v>
@@ -10692,7 +10713,7 @@
         <v>2402008</v>
       </c>
       <c r="B188" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C188" t="s">
         <v>157</v>
@@ -10719,16 +10740,16 @@
         <v>25</v>
       </c>
       <c r="K188" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="L188" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="M188" t="s">
         <v>27</v>
       </c>
       <c r="N188" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="P188" t="s">
         <v>28</v>
@@ -10742,7 +10763,7 @@
         <v>2402015</v>
       </c>
       <c r="B189" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C189" t="s">
         <v>157</v>
@@ -10769,13 +10790,13 @@
         <v>42</v>
       </c>
       <c r="K189" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="M189" t="s">
         <v>27</v>
       </c>
       <c r="N189" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="P189" t="s">
         <v>28</v>
@@ -10789,7 +10810,7 @@
         <v>2402015</v>
       </c>
       <c r="B190" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C190" t="s">
         <v>157</v>
@@ -10816,13 +10837,13 @@
         <v>42</v>
       </c>
       <c r="K190" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="M190" t="s">
         <v>27</v>
       </c>
       <c r="N190" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="P190" t="s">
         <v>28</v>
@@ -10836,7 +10857,7 @@
         <v>2402015</v>
       </c>
       <c r="B191" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C191" t="s">
         <v>157</v>
@@ -10863,7 +10884,7 @@
         <v>42</v>
       </c>
       <c r="K191" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="M191" t="s">
         <v>27</v>
@@ -10881,7 +10902,7 @@
         <v>2403004</v>
       </c>
       <c r="B192" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C192" t="s">
         <v>157</v>
@@ -10908,16 +10929,16 @@
         <v>42</v>
       </c>
       <c r="K192" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="L192" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="M192" t="s">
         <v>27</v>
       </c>
       <c r="N192" s="4" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="P192" t="s">
         <v>28</v>
@@ -10931,7 +10952,7 @@
         <v>2403004</v>
       </c>
       <c r="B193" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C193" t="s">
         <v>157</v>
@@ -10958,16 +10979,16 @@
         <v>42</v>
       </c>
       <c r="K193" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="L193" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="M193" t="s">
         <v>27</v>
       </c>
       <c r="N193" s="4" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="P193" t="s">
         <v>28</v>
@@ -10981,7 +11002,7 @@
         <v>2403004</v>
       </c>
       <c r="B194" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C194" t="s">
         <v>157</v>
@@ -11008,16 +11029,16 @@
         <v>42</v>
       </c>
       <c r="K194" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="L194" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="M194" t="s">
         <v>27</v>
       </c>
       <c r="N194" s="4" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="P194" t="s">
         <v>28</v>
@@ -11031,7 +11052,7 @@
         <v>2403009</v>
       </c>
       <c r="B195" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C195" t="s">
         <v>157</v>
@@ -11058,10 +11079,10 @@
         <v>42</v>
       </c>
       <c r="K195" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="L195" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="M195" t="s">
         <v>27</v>
@@ -11078,7 +11099,7 @@
         <v>2403009</v>
       </c>
       <c r="B196" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C196" t="s">
         <v>157</v>
@@ -11105,10 +11126,10 @@
         <v>42</v>
       </c>
       <c r="K196" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="L196" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="M196" t="s">
         <v>27</v>
@@ -11125,7 +11146,7 @@
         <v>2403009</v>
       </c>
       <c r="B197" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C197" t="s">
         <v>157</v>
@@ -11152,10 +11173,10 @@
         <v>42</v>
       </c>
       <c r="K197" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="L197" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="M197" t="s">
         <v>27</v>
@@ -11172,7 +11193,7 @@
         <v>2403013</v>
       </c>
       <c r="B198" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C198" t="s">
         <v>157</v>
@@ -11199,7 +11220,7 @@
         <v>25</v>
       </c>
       <c r="K198" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="M198" t="s">
         <v>27</v>
@@ -11216,7 +11237,7 @@
         <v>2403013</v>
       </c>
       <c r="B199" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C199" t="s">
         <v>157</v>
@@ -11243,7 +11264,7 @@
         <v>25</v>
       </c>
       <c r="K199" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="M199" t="s">
         <v>27</v>
@@ -11260,7 +11281,7 @@
         <v>2403013</v>
       </c>
       <c r="B200" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C200" t="s">
         <v>157</v>
@@ -11287,7 +11308,7 @@
         <v>25</v>
       </c>
       <c r="K200" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="M200" t="s">
         <v>27</v>
@@ -11304,7 +11325,7 @@
         <v>2404001</v>
       </c>
       <c r="B201" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C201" t="s">
         <v>157</v>
@@ -11331,16 +11352,16 @@
         <v>42</v>
       </c>
       <c r="K201" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="L201" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="M201" t="s">
         <v>27</v>
       </c>
       <c r="N201" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="P201" t="s">
         <v>28</v>
@@ -11354,7 +11375,7 @@
         <v>2404001</v>
       </c>
       <c r="B202" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C202" t="s">
         <v>157</v>
@@ -11381,16 +11402,16 @@
         <v>42</v>
       </c>
       <c r="K202" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="L202" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="M202" t="s">
         <v>27</v>
       </c>
       <c r="N202" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="P202" t="s">
         <v>28</v>
@@ -11404,7 +11425,7 @@
         <v>2404001</v>
       </c>
       <c r="B203" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C203" t="s">
         <v>157</v>
@@ -11431,16 +11452,16 @@
         <v>42</v>
       </c>
       <c r="K203" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="L203" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="M203" t="s">
         <v>27</v>
       </c>
       <c r="N203" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="P203" t="s">
         <v>28</v>
@@ -11454,7 +11475,7 @@
         <v>2404006</v>
       </c>
       <c r="B204" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C204" t="s">
         <v>157</v>
@@ -11481,16 +11502,16 @@
         <v>42</v>
       </c>
       <c r="K204" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="L204" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="M204" t="s">
         <v>27</v>
       </c>
       <c r="N204" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="P204" t="s">
         <v>28</v>
@@ -11504,7 +11525,7 @@
         <v>2404006</v>
       </c>
       <c r="B205" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C205" t="s">
         <v>157</v>
@@ -11531,16 +11552,16 @@
         <v>42</v>
       </c>
       <c r="K205" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="L205" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="M205" t="s">
         <v>27</v>
       </c>
       <c r="N205" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="P205" t="s">
         <v>28</v>
@@ -11554,7 +11575,7 @@
         <v>2404006</v>
       </c>
       <c r="B206" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C206" t="s">
         <v>157</v>
@@ -11581,16 +11602,16 @@
         <v>42</v>
       </c>
       <c r="K206" t="s">
+        <v>433</v>
+      </c>
+      <c r="L206" t="s">
         <v>430</v>
       </c>
-      <c r="L206" t="s">
-        <v>427</v>
-      </c>
       <c r="M206" t="s">
         <v>27</v>
       </c>
       <c r="N206" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="P206" t="s">
         <v>28</v>
@@ -11604,7 +11625,7 @@
         <v>2404015</v>
       </c>
       <c r="B207" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C207" t="s">
         <v>157</v>
@@ -11616,7 +11637,7 @@
         <v>21</v>
       </c>
       <c r="F207" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="G207" t="s">
         <v>40</v>
@@ -11631,13 +11652,13 @@
         <v>25</v>
       </c>
       <c r="K207" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="M207" t="s">
         <v>27</v>
       </c>
       <c r="N207" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="P207" t="s">
         <v>28</v>
@@ -11651,7 +11672,7 @@
         <v>2404015</v>
       </c>
       <c r="B208" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C208" t="s">
         <v>157</v>
@@ -11663,7 +11684,7 @@
         <v>21</v>
       </c>
       <c r="F208" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="G208" t="s">
         <v>40</v>
@@ -11672,19 +11693,19 @@
         <v>32</v>
       </c>
       <c r="I208" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="J208" t="s">
         <v>25</v>
       </c>
       <c r="K208" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="M208" t="s">
         <v>27</v>
       </c>
       <c r="N208" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="P208" t="s">
         <v>28</v>
@@ -11698,7 +11719,7 @@
         <v>2404015</v>
       </c>
       <c r="B209" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C209" t="s">
         <v>157</v>
@@ -11710,7 +11731,7 @@
         <v>21</v>
       </c>
       <c r="F209" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="G209" t="s">
         <v>40</v>
@@ -11719,19 +11740,19 @@
         <v>32</v>
       </c>
       <c r="I209" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="J209" t="s">
         <v>25</v>
       </c>
       <c r="K209" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="M209" t="s">
         <v>27</v>
       </c>
       <c r="N209" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="P209" t="s">
         <v>28</v>
@@ -11745,7 +11766,7 @@
         <v>2405001</v>
       </c>
       <c r="B210" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C210" t="s">
         <v>157</v>
@@ -11772,16 +11793,16 @@
         <v>42</v>
       </c>
       <c r="K210" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="L210" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="M210" t="s">
         <v>27</v>
       </c>
       <c r="N210" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="P210" t="s">
         <v>28</v>
@@ -11795,7 +11816,7 @@
         <v>2405001</v>
       </c>
       <c r="B211" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C211" t="s">
         <v>157</v>
@@ -11822,16 +11843,16 @@
         <v>42</v>
       </c>
       <c r="K211" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="L211" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="M211" t="s">
         <v>27</v>
       </c>
       <c r="N211" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="P211" t="s">
         <v>28</v>
@@ -11845,7 +11866,7 @@
         <v>2405001</v>
       </c>
       <c r="B212" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C212" t="s">
         <v>157</v>
@@ -11872,16 +11893,16 @@
         <v>42</v>
       </c>
       <c r="K212" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="L212" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="M212" t="s">
         <v>27</v>
       </c>
       <c r="N212" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="P212" t="s">
         <v>28</v>
@@ -11895,7 +11916,7 @@
         <v>2405006</v>
       </c>
       <c r="B213" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C213" t="s">
         <v>157</v>
@@ -11922,16 +11943,16 @@
         <v>42</v>
       </c>
       <c r="K213" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="L213" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="M213" t="s">
         <v>27</v>
       </c>
       <c r="N213" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="P213" t="s">
         <v>28</v>
@@ -11945,7 +11966,7 @@
         <v>2405006</v>
       </c>
       <c r="B214" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C214" t="s">
         <v>157</v>
@@ -11972,16 +11993,16 @@
         <v>42</v>
       </c>
       <c r="K214" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="L214" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="M214" t="s">
         <v>27</v>
       </c>
       <c r="N214" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="P214" t="s">
         <v>28</v>
@@ -11995,7 +12016,7 @@
         <v>2405006</v>
       </c>
       <c r="B215" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C215" t="s">
         <v>157</v>
@@ -12022,16 +12043,16 @@
         <v>42</v>
       </c>
       <c r="K215" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="L215" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="M215" t="s">
         <v>27</v>
       </c>
       <c r="N215" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="P215" t="s">
         <v>28</v>
@@ -12045,7 +12066,7 @@
         <v>2405015</v>
       </c>
       <c r="B216" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C216" t="s">
         <v>157</v>
@@ -12072,16 +12093,16 @@
         <v>25</v>
       </c>
       <c r="K216" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="L216" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="M216" t="s">
         <v>27</v>
       </c>
       <c r="N216" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="P216" t="s">
         <v>28</v>
@@ -12095,7 +12116,7 @@
         <v>2405015</v>
       </c>
       <c r="B217" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C217" t="s">
         <v>157</v>
@@ -12122,16 +12143,16 @@
         <v>25</v>
       </c>
       <c r="K217" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="L217" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="M217" t="s">
         <v>27</v>
       </c>
       <c r="N217" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="P217" t="s">
         <v>28</v>
@@ -12145,7 +12166,7 @@
         <v>2405015</v>
       </c>
       <c r="B218" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C218" t="s">
         <v>157</v>
@@ -12172,13 +12193,13 @@
         <v>25</v>
       </c>
       <c r="K218" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="M218" t="s">
         <v>27</v>
       </c>
       <c r="N218" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="P218" t="s">
         <v>28</v>
@@ -12192,7 +12213,7 @@
         <v>2406004</v>
       </c>
       <c r="B219" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C219" t="s">
         <v>157</v>
@@ -12219,10 +12240,10 @@
         <v>25</v>
       </c>
       <c r="K219" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="L219" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="M219" t="s">
         <v>27</v>
@@ -12239,7 +12260,7 @@
         <v>2406004</v>
       </c>
       <c r="B220" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C220" t="s">
         <v>157</v>
@@ -12266,10 +12287,10 @@
         <v>25</v>
       </c>
       <c r="K220" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="L220" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="M220" t="s">
         <v>27</v>
@@ -12286,7 +12307,7 @@
         <v>2406004</v>
       </c>
       <c r="B221" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C221" t="s">
         <v>157</v>
@@ -12307,13 +12328,13 @@
         <v>8</v>
       </c>
       <c r="I221" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="J221" t="s">
         <v>25</v>
       </c>
       <c r="L221" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="M221" t="s">
         <v>27</v>
@@ -12330,7 +12351,7 @@
         <v>2406004</v>
       </c>
       <c r="B222" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C222" t="s">
         <v>157</v>
@@ -12357,10 +12378,10 @@
         <v>25</v>
       </c>
       <c r="K222" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="L222" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="M222" t="s">
         <v>27</v>
@@ -12377,7 +12398,7 @@
         <v>2406004</v>
       </c>
       <c r="B223" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C223" t="s">
         <v>157</v>
@@ -12398,13 +12419,13 @@
         <v>8</v>
       </c>
       <c r="I223" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="J223" t="s">
         <v>25</v>
       </c>
       <c r="L223" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="M223" t="s">
         <v>27</v>
@@ -12421,7 +12442,7 @@
         <v>2406009</v>
       </c>
       <c r="B224" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C224" t="s">
         <v>157</v>
@@ -12448,10 +12469,10 @@
         <v>25</v>
       </c>
       <c r="K224" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="L224" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="M224" t="s">
         <v>27</v>
@@ -12468,7 +12489,7 @@
         <v>2406009</v>
       </c>
       <c r="B225" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C225" t="s">
         <v>157</v>
@@ -12495,10 +12516,10 @@
         <v>25</v>
       </c>
       <c r="K225" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="L225" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="M225" t="s">
         <v>27</v>
@@ -12515,7 +12536,7 @@
         <v>2406009</v>
       </c>
       <c r="B226" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C226" t="s">
         <v>157</v>
@@ -12536,16 +12557,16 @@
         <v>8</v>
       </c>
       <c r="I226" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="J226" t="s">
         <v>25</v>
       </c>
       <c r="K226" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="L226" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="M226" t="s">
         <v>27</v>
@@ -12562,7 +12583,7 @@
         <v>2406009</v>
       </c>
       <c r="B227" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C227" t="s">
         <v>157</v>
@@ -12589,10 +12610,10 @@
         <v>25</v>
       </c>
       <c r="K227" t="s">
+        <v>467</v>
+      </c>
+      <c r="L227" t="s">
         <v>464</v>
-      </c>
-      <c r="L227" t="s">
-        <v>461</v>
       </c>
       <c r="M227" t="s">
         <v>27</v>
@@ -12609,7 +12630,7 @@
         <v>2406009</v>
       </c>
       <c r="B228" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C228" t="s">
         <v>157</v>
@@ -12630,16 +12651,16 @@
         <v>8</v>
       </c>
       <c r="I228" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="J228" t="s">
         <v>25</v>
       </c>
       <c r="K228" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="L228" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="M228" t="s">
         <v>27</v>
@@ -12656,7 +12677,7 @@
         <v>2406012</v>
       </c>
       <c r="B229" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C229" t="s">
         <v>157</v>
@@ -12668,7 +12689,7 @@
         <v>21</v>
       </c>
       <c r="F229" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="G229" t="s">
         <v>40</v>
@@ -12683,10 +12704,10 @@
         <v>42</v>
       </c>
       <c r="K229" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="L229" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="M229" t="s">
         <v>27</v>
@@ -12703,7 +12724,7 @@
         <v>2406012</v>
       </c>
       <c r="B230" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C230" t="s">
         <v>157</v>
@@ -12715,7 +12736,7 @@
         <v>21</v>
       </c>
       <c r="F230" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="G230" t="s">
         <v>40</v>
@@ -12724,16 +12745,16 @@
         <v>8</v>
       </c>
       <c r="I230" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="J230" t="s">
         <v>42</v>
       </c>
       <c r="K230" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="L230" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="M230" t="s">
         <v>27</v>
@@ -12750,7 +12771,7 @@
         <v>2406012</v>
       </c>
       <c r="B231" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C231" t="s">
         <v>157</v>
@@ -12762,7 +12783,7 @@
         <v>21</v>
       </c>
       <c r="F231" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="G231" t="s">
         <v>40</v>
@@ -12771,16 +12792,16 @@
         <v>8</v>
       </c>
       <c r="I231" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="J231" t="s">
         <v>42</v>
       </c>
       <c r="K231" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="L231" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="M231" t="s">
         <v>27</v>
@@ -12797,10 +12818,10 @@
         <v>2059001</v>
       </c>
       <c r="B232" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C232" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="D232" s="2">
         <v>1</v>
@@ -12824,10 +12845,10 @@
         <v>42</v>
       </c>
       <c r="K232" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="L232" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="M232" t="s">
         <v>27</v>
@@ -12844,10 +12865,10 @@
         <v>2059002</v>
       </c>
       <c r="B233" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C233" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="D233" s="2">
         <v>1</v>
@@ -12871,10 +12892,10 @@
         <v>42</v>
       </c>
       <c r="K233" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="L233" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="M233" t="s">
         <v>27</v>
@@ -12891,10 +12912,10 @@
         <v>2059006</v>
       </c>
       <c r="B234" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C234" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="D234" s="2">
         <v>1</v>
@@ -12918,10 +12939,10 @@
         <v>42</v>
       </c>
       <c r="K234" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="L234" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="M234" t="s">
         <v>27</v>
@@ -12938,10 +12959,10 @@
         <v>2140011</v>
       </c>
       <c r="B235" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C235" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="D235" s="2">
         <v>2</v>
@@ -12968,7 +12989,7 @@
         <v>159</v>
       </c>
       <c r="L235" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="M235" t="s">
         <v>27</v>
@@ -12985,10 +13006,10 @@
         <v>2390004</v>
       </c>
       <c r="B236" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C236" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="D236" s="2">
         <v>1</v>
@@ -13012,10 +13033,10 @@
         <v>25</v>
       </c>
       <c r="K236" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="L236" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="M236" t="s">
         <v>27</v>
@@ -13032,10 +13053,10 @@
         <v>2390004</v>
       </c>
       <c r="B237" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C237" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="D237" s="2">
         <v>1</v>
@@ -13059,10 +13080,10 @@
         <v>25</v>
       </c>
       <c r="K237" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="L237" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="M237" t="s">
         <v>27</v>
@@ -13079,10 +13100,10 @@
         <v>2390004</v>
       </c>
       <c r="B238" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C238" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="D238" s="2">
         <v>1</v>
@@ -13106,10 +13127,10 @@
         <v>25</v>
       </c>
       <c r="K238" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="L238" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="M238" t="s">
         <v>27</v>
@@ -13126,10 +13147,10 @@
         <v>2390009</v>
       </c>
       <c r="B239" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C239" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="D239" s="2">
         <v>1</v>
@@ -13153,10 +13174,10 @@
         <v>25</v>
       </c>
       <c r="K239" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="L239" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="M239" t="s">
         <v>27</v>
@@ -13173,10 +13194,10 @@
         <v>2390009</v>
       </c>
       <c r="B240" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C240" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="D240" s="2">
         <v>1</v>
@@ -13200,10 +13221,10 @@
         <v>25</v>
       </c>
       <c r="K240" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="L240" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="M240" t="s">
         <v>27</v>
@@ -13220,10 +13241,10 @@
         <v>2390009</v>
       </c>
       <c r="B241" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C241" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="D241" s="2">
         <v>1</v>
@@ -13247,10 +13268,10 @@
         <v>25</v>
       </c>
       <c r="K241" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="L241" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="M241" t="s">
         <v>27</v>
@@ -13267,10 +13288,10 @@
         <v>2390013</v>
       </c>
       <c r="B242" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C242" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="D242" s="2">
         <v>2</v>
@@ -13294,7 +13315,7 @@
         <v>42</v>
       </c>
       <c r="K242" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="M242" t="s">
         <v>27</v>
@@ -13311,10 +13332,10 @@
         <v>2390013</v>
       </c>
       <c r="B243" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C243" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="D243" s="2">
         <v>2</v>
@@ -13338,7 +13359,7 @@
         <v>42</v>
       </c>
       <c r="K243" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="M243" t="s">
         <v>27</v>
@@ -13355,10 +13376,10 @@
         <v>2390013</v>
       </c>
       <c r="B244" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C244" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="D244" s="2">
         <v>2</v>
@@ -13382,7 +13403,7 @@
         <v>42</v>
       </c>
       <c r="K244" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="M244" t="s">
         <v>27</v>

--- a/POD_2026-27_11-5-2026.xlsx
+++ b/POD_2026-27_11-5-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://urjc-my.sharepoint.com/personal/esther_garcia_urjc_es/Documents/Documentos/POD 2026-27/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="284" documentId="11_79C815625599F410B0C00D3910C611C600045ACD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F3CCF80-2BEA-4692-A7E5-C7FE4DB22D11}"/>
+  <xr:revisionPtr revIDLastSave="286" documentId="11_79C815625599F410B0C00D3910C611C600045ACD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC1EC50B-635A-4EB7-A605-7DEF5A16E802}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/POD_2026-27_11-5-2026.xlsx
+++ b/POD_2026-27_11-5-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://urjc-my.sharepoint.com/personal/esther_garcia_urjc_es/Documents/Documentos/POD 2026-27/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="286" documentId="11_79C815625599F410B0C00D3910C611C600045ACD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC1EC50B-635A-4EB7-A605-7DEF5A16E802}"/>
+  <xr:revisionPtr revIDLastSave="289" documentId="11_79C815625599F410B0C00D3910C611C600045ACD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0ADBD62D-A6C4-4157-B246-38BE71564E3F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2935" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2938" uniqueCount="501">
   <si>
     <t>POD_2026-27_11-5-2026</t>
   </si>
@@ -371,6 +371,9 @@
     <t>G_AEROBIL_EXT_1A(F) (2125006), G_AERO_EXT_I_1A(F) (2151006), G_AERO_EXT822_II_1A(F) (2339006), G_TELECO-AEROESP_EXT822_1A(F) (2332006), G_TELECO-AEROESP_1A(F) (2412008), G_TRANSP_EXT822_1A(F) (2341006), G_VEHI_EXT_I_1A(F) (2284007), G_VEHI_EXT822_1A(F) (2356007)</t>
   </si>
   <si>
+    <t>MISAEL MARRIAGA (76)</t>
+  </si>
+  <si>
     <t>(2384) GRADO EN INGENIERÍA BIOMÉDICA (INGLÉS)(FUENLABRADA)</t>
   </si>
   <si>
@@ -593,6 +596,9 @@
     <t>G_INF-ADE_1A(M) (2097010)</t>
   </si>
   <si>
+    <t>MISAEL MARRIAGA (60)</t>
+  </si>
+  <si>
     <t>(2034) GRADO EN INGENIERIA DEL SOFTWARE (MOSTOLES)</t>
   </si>
   <si>
@@ -651,6 +657,9 @@
   </si>
   <si>
     <t>(2285) GRADO EN INGENIERIA DE LA CIBERSEGURIDAD (MOSTOLES)</t>
+  </si>
+  <si>
+    <t>MISAEL MARRIAGA (35) (*hablar con quien coja la otra media sobre reparto temporal)</t>
   </si>
   <si>
     <t>L(11:00 - 13:00), J(13:00 - 15:00)</t>
@@ -3941,6 +3950,9 @@
       <c r="M44" t="s">
         <v>27</v>
       </c>
+      <c r="N44" t="s">
+        <v>111</v>
+      </c>
       <c r="P44" t="s">
         <v>28</v>
       </c>
@@ -3953,7 +3965,7 @@
         <v>2384001</v>
       </c>
       <c r="B45" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C45" t="s">
         <v>44</v>
@@ -3965,7 +3977,7 @@
         <v>21</v>
       </c>
       <c r="F45" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G45" t="s">
         <v>23</v>
@@ -3980,10 +3992,10 @@
         <v>25</v>
       </c>
       <c r="K45" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L45" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M45" t="s">
         <v>27</v>
@@ -4000,7 +4012,7 @@
         <v>2384001</v>
       </c>
       <c r="B46" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C46" t="s">
         <v>44</v>
@@ -4012,7 +4024,7 @@
         <v>21</v>
       </c>
       <c r="F46" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G46" t="s">
         <v>23</v>
@@ -4021,16 +4033,16 @@
         <v>14</v>
       </c>
       <c r="I46" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J46" t="s">
         <v>25</v>
       </c>
       <c r="K46" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L46" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M46" t="s">
         <v>27</v>
@@ -4047,7 +4059,7 @@
         <v>2384001</v>
       </c>
       <c r="B47" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C47" t="s">
         <v>44</v>
@@ -4059,7 +4071,7 @@
         <v>21</v>
       </c>
       <c r="F47" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G47" t="s">
         <v>23</v>
@@ -4068,16 +4080,16 @@
         <v>14</v>
       </c>
       <c r="I47" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J47" t="s">
         <v>25</v>
       </c>
       <c r="K47" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L47" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M47" t="s">
         <v>27</v>
@@ -4094,7 +4106,7 @@
         <v>2384005</v>
       </c>
       <c r="B48" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C48" t="s">
         <v>44</v>
@@ -4106,7 +4118,7 @@
         <v>21</v>
       </c>
       <c r="F48" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G48" t="s">
         <v>23</v>
@@ -4121,10 +4133,10 @@
         <v>25</v>
       </c>
       <c r="K48" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L48" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M48" t="s">
         <v>27</v>
@@ -4141,7 +4153,7 @@
         <v>2384005</v>
       </c>
       <c r="B49" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C49" t="s">
         <v>44</v>
@@ -4153,7 +4165,7 @@
         <v>21</v>
       </c>
       <c r="F49" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G49" t="s">
         <v>23</v>
@@ -4162,16 +4174,16 @@
         <v>14</v>
       </c>
       <c r="I49" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J49" t="s">
         <v>25</v>
       </c>
       <c r="K49" t="s">
+        <v>123</v>
+      </c>
+      <c r="L49" t="s">
         <v>122</v>
-      </c>
-      <c r="L49" t="s">
-        <v>121</v>
       </c>
       <c r="M49" t="s">
         <v>27</v>
@@ -4188,7 +4200,7 @@
         <v>2384005</v>
       </c>
       <c r="B50" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C50" t="s">
         <v>44</v>
@@ -4200,7 +4212,7 @@
         <v>21</v>
       </c>
       <c r="F50" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G50" t="s">
         <v>23</v>
@@ -4209,16 +4221,16 @@
         <v>14</v>
       </c>
       <c r="I50" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J50" t="s">
         <v>25</v>
       </c>
       <c r="K50" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L50" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M50" t="s">
         <v>27</v>
@@ -4235,7 +4247,7 @@
         <v>2385001</v>
       </c>
       <c r="B51" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C51" t="s">
         <v>44</v>
@@ -4262,10 +4274,10 @@
         <v>25</v>
       </c>
       <c r="K51" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L51" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M51" t="s">
         <v>27</v>
@@ -4282,7 +4294,7 @@
         <v>2385001</v>
       </c>
       <c r="B52" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C52" t="s">
         <v>44</v>
@@ -4303,16 +4315,16 @@
         <v>14</v>
       </c>
       <c r="I52" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J52" t="s">
         <v>25</v>
       </c>
       <c r="K52" t="s">
+        <v>128</v>
+      </c>
+      <c r="L52" t="s">
         <v>127</v>
-      </c>
-      <c r="L52" t="s">
-        <v>126</v>
       </c>
       <c r="M52" t="s">
         <v>27</v>
@@ -4329,7 +4341,7 @@
         <v>2385001</v>
       </c>
       <c r="B53" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C53" t="s">
         <v>44</v>
@@ -4350,16 +4362,16 @@
         <v>14</v>
       </c>
       <c r="I53" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J53" t="s">
         <v>25</v>
       </c>
       <c r="K53" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L53" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M53" t="s">
         <v>27</v>
@@ -4376,7 +4388,7 @@
         <v>2385005</v>
       </c>
       <c r="B54" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C54" t="s">
         <v>44</v>
@@ -4403,10 +4415,10 @@
         <v>25</v>
       </c>
       <c r="K54" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L54" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M54" t="s">
         <v>27</v>
@@ -4423,7 +4435,7 @@
         <v>2385005</v>
       </c>
       <c r="B55" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C55" t="s">
         <v>44</v>
@@ -4444,16 +4456,16 @@
         <v>14</v>
       </c>
       <c r="I55" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J55" t="s">
         <v>25</v>
       </c>
       <c r="K55" t="s">
+        <v>132</v>
+      </c>
+      <c r="L55" t="s">
         <v>131</v>
-      </c>
-      <c r="L55" t="s">
-        <v>130</v>
       </c>
       <c r="M55" t="s">
         <v>27</v>
@@ -4470,7 +4482,7 @@
         <v>2385005</v>
       </c>
       <c r="B56" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C56" t="s">
         <v>44</v>
@@ -4491,16 +4503,16 @@
         <v>14</v>
       </c>
       <c r="I56" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J56" t="s">
         <v>25</v>
       </c>
       <c r="K56" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L56" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M56" t="s">
         <v>27</v>
@@ -4517,7 +4529,7 @@
         <v>2386001</v>
       </c>
       <c r="B57" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C57" t="s">
         <v>44</v>
@@ -4544,10 +4556,10 @@
         <v>42</v>
       </c>
       <c r="K57" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L57" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M57" t="s">
         <v>27</v>
@@ -4564,7 +4576,7 @@
         <v>2386001</v>
       </c>
       <c r="B58" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C58" t="s">
         <v>44</v>
@@ -4591,7 +4603,7 @@
         <v>42</v>
       </c>
       <c r="L58" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M58" t="s">
         <v>27</v>
@@ -4608,7 +4620,7 @@
         <v>2386001</v>
       </c>
       <c r="B59" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C59" t="s">
         <v>44</v>
@@ -4635,7 +4647,7 @@
         <v>42</v>
       </c>
       <c r="L59" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M59" t="s">
         <v>27</v>
@@ -4652,7 +4664,7 @@
         <v>2386001</v>
       </c>
       <c r="B60" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C60" t="s">
         <v>44</v>
@@ -4673,16 +4685,16 @@
         <v>44</v>
       </c>
       <c r="I60" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J60" t="s">
         <v>42</v>
       </c>
       <c r="K60" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L60" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M60" t="s">
         <v>27</v>
@@ -4699,7 +4711,7 @@
         <v>2386001</v>
       </c>
       <c r="B61" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C61" t="s">
         <v>44</v>
@@ -4720,13 +4732,13 @@
         <v>16</v>
       </c>
       <c r="I61" t="s">
+        <v>141</v>
+      </c>
+      <c r="J61" t="s">
+        <v>42</v>
+      </c>
+      <c r="L61" t="s">
         <v>140</v>
-      </c>
-      <c r="J61" t="s">
-        <v>42</v>
-      </c>
-      <c r="L61" t="s">
-        <v>139</v>
       </c>
       <c r="M61" t="s">
         <v>27</v>
@@ -4743,7 +4755,7 @@
         <v>2386001</v>
       </c>
       <c r="B62" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C62" t="s">
         <v>44</v>
@@ -4764,14 +4776,14 @@
         <v>16</v>
       </c>
       <c r="I62" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J62" t="s">
         <v>42</v>
       </c>
       <c r="K62" s="1"/>
       <c r="L62" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M62" t="s">
         <v>27</v>
@@ -4788,7 +4800,7 @@
         <v>2386002</v>
       </c>
       <c r="B63" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C63" t="s">
         <v>44</v>
@@ -4815,10 +4827,10 @@
         <v>42</v>
       </c>
       <c r="K63" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L63" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="M63" t="s">
         <v>27</v>
@@ -4835,7 +4847,7 @@
         <v>2386002</v>
       </c>
       <c r="B64" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C64" t="s">
         <v>44</v>
@@ -4856,22 +4868,22 @@
         <v>76</v>
       </c>
       <c r="I64" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J64" t="s">
         <v>42</v>
       </c>
       <c r="K64" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L64" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M64" t="s">
         <v>27</v>
       </c>
       <c r="N64" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P64" t="s">
         <v>28</v>
@@ -4885,7 +4897,7 @@
         <v>2387009</v>
       </c>
       <c r="B65" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C65" t="s">
         <v>44</v>
@@ -4912,10 +4924,10 @@
         <v>42</v>
       </c>
       <c r="K65" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L65" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M65" t="s">
         <v>27</v>
@@ -4932,7 +4944,7 @@
         <v>2387009</v>
       </c>
       <c r="B66" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C66" t="s">
         <v>44</v>
@@ -4959,7 +4971,7 @@
         <v>42</v>
       </c>
       <c r="L66" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M66" t="s">
         <v>27</v>
@@ -4976,7 +4988,7 @@
         <v>2387009</v>
       </c>
       <c r="B67" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C67" t="s">
         <v>44</v>
@@ -5003,7 +5015,7 @@
         <v>42</v>
       </c>
       <c r="L67" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M67" t="s">
         <v>27</v>
@@ -5020,7 +5032,7 @@
         <v>2387016</v>
       </c>
       <c r="B68" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C68" t="s">
         <v>44</v>
@@ -5047,7 +5059,7 @@
         <v>25</v>
       </c>
       <c r="K68" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M68" t="s">
         <v>27</v>
@@ -5064,7 +5076,7 @@
         <v>2387016</v>
       </c>
       <c r="B69" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C69" t="s">
         <v>44</v>
@@ -5085,7 +5097,7 @@
         <v>16</v>
       </c>
       <c r="I69" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J69" t="s">
         <v>25</v>
@@ -5105,7 +5117,7 @@
         <v>2387016</v>
       </c>
       <c r="B70" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C70" t="s">
         <v>44</v>
@@ -5126,7 +5138,7 @@
         <v>16</v>
       </c>
       <c r="I70" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J70" t="s">
         <v>25</v>
@@ -5146,10 +5158,10 @@
         <v>2265020</v>
       </c>
       <c r="B71" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C71" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D71" s="2">
         <v>2</v>
@@ -5158,7 +5170,7 @@
         <v>35</v>
       </c>
       <c r="F71" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G71" t="s">
         <v>23</v>
@@ -5173,13 +5185,13 @@
         <v>25</v>
       </c>
       <c r="K71" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M71" t="s">
         <v>27</v>
       </c>
       <c r="N71" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P71" t="s">
         <v>28</v>
@@ -5193,10 +5205,10 @@
         <v>2029018</v>
       </c>
       <c r="B72" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C72" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D72" s="2">
         <v>2</v>
@@ -5205,7 +5217,7 @@
         <v>21</v>
       </c>
       <c r="F72" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G72" t="s">
         <v>40</v>
@@ -5220,10 +5232,10 @@
         <v>25</v>
       </c>
       <c r="K72" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L72" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M72" t="s">
         <v>27</v>
@@ -5240,10 +5252,10 @@
         <v>2030013</v>
       </c>
       <c r="B73" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C73" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D73" s="2">
         <v>2</v>
@@ -5252,7 +5264,7 @@
         <v>35</v>
       </c>
       <c r="F73" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G73" t="s">
         <v>23</v>
@@ -5267,10 +5279,10 @@
         <v>25</v>
       </c>
       <c r="K73" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L73" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M73" t="s">
         <v>27</v>
@@ -5287,19 +5299,19 @@
         <v>2031001</v>
       </c>
       <c r="B74" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C74" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D74" s="2">
         <v>1</v>
       </c>
       <c r="E74" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F74" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G74" t="s">
         <v>23</v>
@@ -5331,10 +5343,10 @@
         <v>2032001</v>
       </c>
       <c r="B75" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C75" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D75" s="2">
         <v>1</v>
@@ -5343,7 +5355,7 @@
         <v>21</v>
       </c>
       <c r="F75" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G75" t="s">
         <v>23</v>
@@ -5358,10 +5370,10 @@
         <v>42</v>
       </c>
       <c r="K75" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L75" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M75" t="s">
         <v>27</v>
@@ -5378,10 +5390,10 @@
         <v>2032007</v>
       </c>
       <c r="B76" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C76" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D76" s="2">
         <v>1</v>
@@ -5405,16 +5417,16 @@
         <v>42</v>
       </c>
       <c r="K76" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L76" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M76" t="s">
         <v>27</v>
       </c>
       <c r="N76" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P76" t="s">
         <v>28</v>
@@ -5428,10 +5440,10 @@
         <v>2032009</v>
       </c>
       <c r="B77" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C77" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D77" s="2">
         <v>1</v>
@@ -5455,7 +5467,7 @@
         <v>42</v>
       </c>
       <c r="K77" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M77" t="s">
         <v>27</v>
@@ -5472,10 +5484,10 @@
         <v>2033001</v>
       </c>
       <c r="B78" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C78" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D78" s="2">
         <v>1</v>
@@ -5484,7 +5496,7 @@
         <v>21</v>
       </c>
       <c r="F78" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G78" t="s">
         <v>23</v>
@@ -5499,10 +5511,10 @@
         <v>42</v>
       </c>
       <c r="K78" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L78" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M78" t="s">
         <v>27</v>
@@ -5519,10 +5531,10 @@
         <v>2033002</v>
       </c>
       <c r="B79" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C79" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D79" s="2">
         <v>1</v>
@@ -5531,7 +5543,7 @@
         <v>21</v>
       </c>
       <c r="F79" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G79" t="s">
         <v>23</v>
@@ -5546,16 +5558,16 @@
         <v>42</v>
       </c>
       <c r="K79" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L79" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M79" t="s">
         <v>27</v>
       </c>
       <c r="N79" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P79" t="s">
         <v>28</v>
@@ -5569,10 +5581,10 @@
         <v>2033006</v>
       </c>
       <c r="B80" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C80" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D80" s="2">
         <v>1</v>
@@ -5596,13 +5608,16 @@
         <v>42</v>
       </c>
       <c r="K80" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L80" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M80" t="s">
         <v>27</v>
+      </c>
+      <c r="N80" t="s">
+        <v>186</v>
       </c>
       <c r="P80" t="s">
         <v>28</v>
@@ -5616,10 +5631,10 @@
         <v>2034001</v>
       </c>
       <c r="B81" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C81" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D81" s="2">
         <v>1</v>
@@ -5628,7 +5643,7 @@
         <v>21</v>
       </c>
       <c r="F81" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G81" t="s">
         <v>23</v>
@@ -5643,10 +5658,10 @@
         <v>42</v>
       </c>
       <c r="K81" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L81" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="M81" t="s">
         <v>27</v>
@@ -5663,10 +5678,10 @@
         <v>2034002</v>
       </c>
       <c r="B82" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C82" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D82" s="2">
         <v>1</v>
@@ -5675,7 +5690,7 @@
         <v>21</v>
       </c>
       <c r="F82" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G82" t="s">
         <v>23</v>
@@ -5690,16 +5705,16 @@
         <v>42</v>
       </c>
       <c r="K82" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="L82" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="M82" t="s">
         <v>27</v>
       </c>
       <c r="N82" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P82" t="s">
         <v>28</v>
@@ -5713,10 +5728,10 @@
         <v>2034006</v>
       </c>
       <c r="B83" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C83" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D83" s="2">
         <v>1</v>
@@ -5740,10 +5755,10 @@
         <v>42</v>
       </c>
       <c r="K83" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="L83" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="M83" t="s">
         <v>27</v>
@@ -5760,10 +5775,10 @@
         <v>2061001</v>
       </c>
       <c r="B84" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C84" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D84" s="2">
         <v>1</v>
@@ -5772,7 +5787,7 @@
         <v>21</v>
       </c>
       <c r="F84" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G84" t="s">
         <v>23</v>
@@ -5804,10 +5819,10 @@
         <v>2061002</v>
       </c>
       <c r="B85" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C85" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D85" s="2">
         <v>1</v>
@@ -5816,7 +5831,7 @@
         <v>21</v>
       </c>
       <c r="F85" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G85" t="s">
         <v>23</v>
@@ -5837,7 +5852,7 @@
         <v>27</v>
       </c>
       <c r="N85" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P85" t="s">
         <v>28</v>
@@ -5851,10 +5866,10 @@
         <v>2061006</v>
       </c>
       <c r="B86" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C86" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D86" s="2">
         <v>1</v>
@@ -5895,10 +5910,10 @@
         <v>2107013</v>
       </c>
       <c r="B87" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C87" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D87" s="2">
         <v>2</v>
@@ -5907,7 +5922,7 @@
         <v>21</v>
       </c>
       <c r="F87" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G87" t="s">
         <v>40</v>
@@ -5922,10 +5937,10 @@
         <v>25</v>
       </c>
       <c r="K87" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L87" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="M87" t="s">
         <v>27</v>
@@ -5942,10 +5957,10 @@
         <v>2143016</v>
       </c>
       <c r="B88" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C88" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D88" s="2">
         <v>2</v>
@@ -5954,7 +5969,7 @@
         <v>21</v>
       </c>
       <c r="F88" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G88" t="s">
         <v>40</v>
@@ -5969,10 +5984,10 @@
         <v>25</v>
       </c>
       <c r="K88" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L88" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="M88" t="s">
         <v>27</v>
@@ -5989,10 +6004,10 @@
         <v>2148011</v>
       </c>
       <c r="B89" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C89" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D89" s="2">
         <v>2</v>
@@ -6001,7 +6016,7 @@
         <v>21</v>
       </c>
       <c r="F89" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G89" t="s">
         <v>40</v>
@@ -6016,7 +6031,7 @@
         <v>25</v>
       </c>
       <c r="K89" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M89" t="s">
         <v>27</v>
@@ -6033,10 +6048,10 @@
         <v>2175020</v>
       </c>
       <c r="B90" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C90" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D90" s="2">
         <v>2</v>
@@ -6045,7 +6060,7 @@
         <v>35</v>
       </c>
       <c r="F90" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G90" t="s">
         <v>23</v>
@@ -6060,10 +6075,10 @@
         <v>25</v>
       </c>
       <c r="K90" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L90" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="M90" t="s">
         <v>27</v>
@@ -6075,15 +6090,15 @@
         <v>29</v>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="14.45">
+    <row r="91" spans="1:17" ht="45.75">
       <c r="A91" s="2">
         <v>2285005</v>
       </c>
       <c r="B91" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C91" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D91" s="2">
         <v>1</v>
@@ -6092,7 +6107,7 @@
         <v>21</v>
       </c>
       <c r="F91" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G91" t="s">
         <v>23</v>
@@ -6107,10 +6122,13 @@
         <v>42</v>
       </c>
       <c r="K91" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M91" t="s">
         <v>27</v>
+      </c>
+      <c r="N91" s="3" t="s">
+        <v>207</v>
       </c>
       <c r="P91" t="s">
         <v>28</v>
@@ -6124,10 +6142,10 @@
         <v>2285006</v>
       </c>
       <c r="B92" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C92" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D92" s="2">
         <v>1</v>
@@ -6151,13 +6169,13 @@
         <v>42</v>
       </c>
       <c r="K92" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="M92" t="s">
         <v>27</v>
       </c>
       <c r="N92" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="P92" t="s">
         <v>28</v>
@@ -6171,10 +6189,10 @@
         <v>2285007</v>
       </c>
       <c r="B93" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C93" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D93" s="2">
         <v>1</v>
@@ -6183,7 +6201,7 @@
         <v>35</v>
       </c>
       <c r="F93" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="G93" t="s">
         <v>40</v>
@@ -6198,7 +6216,7 @@
         <v>42</v>
       </c>
       <c r="K93" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="M93" t="s">
         <v>27</v>
@@ -6215,10 +6233,10 @@
         <v>2286015</v>
       </c>
       <c r="B94" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C94" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D94" s="2">
         <v>2</v>
@@ -6227,7 +6245,7 @@
         <v>21</v>
       </c>
       <c r="F94" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G94" t="s">
         <v>40</v>
@@ -6242,7 +6260,7 @@
         <v>25</v>
       </c>
       <c r="K94" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M94" t="s">
         <v>27</v>
@@ -6259,10 +6277,10 @@
         <v>2338044</v>
       </c>
       <c r="B95" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C95" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D95" s="2">
         <v>1</v>
@@ -6303,10 +6321,10 @@
         <v>2342014</v>
       </c>
       <c r="B96" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C96" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D96" s="2">
         <v>2</v>
@@ -6315,7 +6333,7 @@
         <v>21</v>
       </c>
       <c r="F96" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G96" t="s">
         <v>40</v>
@@ -6330,13 +6348,13 @@
         <v>42</v>
       </c>
       <c r="K96" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M96" t="s">
         <v>27</v>
       </c>
       <c r="N96" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="P96" t="s">
         <v>28</v>
@@ -6350,10 +6368,10 @@
         <v>5</v>
       </c>
       <c r="B97" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C97" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D97" s="2">
         <v>4</v>
@@ -6362,7 +6380,7 @@
         <v>21</v>
       </c>
       <c r="F97" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G97" t="s">
         <v>40</v>
@@ -6377,13 +6395,13 @@
         <v>42</v>
       </c>
       <c r="K97" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="M97" t="s">
         <v>27</v>
       </c>
       <c r="N97" s="3" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="P97" t="s">
         <v>28</v>
@@ -6397,10 +6415,10 @@
         <v>2343027</v>
       </c>
       <c r="B98" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C98" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D98" s="2">
         <v>3</v>
@@ -6409,7 +6427,7 @@
         <v>35</v>
       </c>
       <c r="F98" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="G98" t="s">
         <v>40</v>
@@ -6424,13 +6442,13 @@
         <v>25</v>
       </c>
       <c r="K98" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="M98" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="N98" s="3" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="P98" t="s">
         <v>28</v>
@@ -6444,10 +6462,10 @@
         <v>2343027</v>
       </c>
       <c r="B99" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C99" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D99" s="2">
         <v>3</v>
@@ -6456,7 +6474,7 @@
         <v>35</v>
       </c>
       <c r="F99" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="G99" t="s">
         <v>40</v>
@@ -6465,19 +6483,19 @@
         <v>6</v>
       </c>
       <c r="I99" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J99" t="s">
         <v>25</v>
       </c>
       <c r="K99" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="M99" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="N99" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="P99" t="s">
         <v>28</v>
@@ -6491,10 +6509,10 @@
         <v>2343027</v>
       </c>
       <c r="B100" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C100" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D100" s="2">
         <v>3</v>
@@ -6503,7 +6521,7 @@
         <v>35</v>
       </c>
       <c r="F100" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="G100" t="s">
         <v>40</v>
@@ -6512,16 +6530,16 @@
         <v>6</v>
       </c>
       <c r="I100" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J100" t="s">
         <v>25</v>
       </c>
       <c r="K100" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="M100" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="N100" s="3"/>
       <c r="P100" t="s">
@@ -6536,10 +6554,10 @@
         <v>2347001</v>
       </c>
       <c r="B101" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C101" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D101" s="2">
         <v>1</v>
@@ -6563,16 +6581,16 @@
         <v>42</v>
       </c>
       <c r="K101" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="L101" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="M101" t="s">
         <v>27</v>
       </c>
       <c r="N101" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="P101" t="s">
         <v>28</v>
@@ -6586,10 +6604,10 @@
         <v>2347003</v>
       </c>
       <c r="B102" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C102" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D102" s="2">
         <v>1</v>
@@ -6598,7 +6616,7 @@
         <v>21</v>
       </c>
       <c r="F102" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G102" t="s">
         <v>40</v>
@@ -6613,16 +6631,16 @@
         <v>42</v>
       </c>
       <c r="K102" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L102" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M102" t="s">
         <v>27</v>
       </c>
       <c r="N102" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="P102" t="s">
         <v>28</v>
@@ -6636,10 +6654,10 @@
         <v>2347005</v>
       </c>
       <c r="B103" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C103" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D103" s="2">
         <v>1</v>
@@ -6648,7 +6666,7 @@
         <v>21</v>
       </c>
       <c r="F103" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="G103" t="s">
         <v>40</v>
@@ -6663,16 +6681,16 @@
         <v>42</v>
       </c>
       <c r="K103" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="L103" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="M103" t="s">
         <v>27</v>
       </c>
       <c r="N103" s="3" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="P103" t="s">
         <v>28</v>
@@ -6686,10 +6704,10 @@
         <v>2347006</v>
       </c>
       <c r="B104" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C104" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D104" s="2">
         <v>1</v>
@@ -6698,7 +6716,7 @@
         <v>35</v>
       </c>
       <c r="F104" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G104" t="s">
         <v>40</v>
@@ -6713,16 +6731,16 @@
         <v>42</v>
       </c>
       <c r="K104" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="L104" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="M104" t="s">
         <v>27</v>
       </c>
       <c r="N104" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="P104" t="s">
         <v>28</v>
@@ -6736,10 +6754,10 @@
         <v>2347007</v>
       </c>
       <c r="B105" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C105" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D105" s="2">
         <v>1</v>
@@ -6763,16 +6781,16 @@
         <v>42</v>
       </c>
       <c r="K105" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="L105" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="M105" t="s">
         <v>27</v>
       </c>
       <c r="N105" s="3" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="P105" t="s">
         <v>28</v>
@@ -6786,10 +6804,10 @@
         <v>2347013</v>
       </c>
       <c r="B106" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C106" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D106" s="2">
         <v>2</v>
@@ -6798,7 +6816,7 @@
         <v>21</v>
       </c>
       <c r="F106" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="G106" t="s">
         <v>40</v>
@@ -6813,16 +6831,16 @@
         <v>42</v>
       </c>
       <c r="K106" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="L106" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="M106" t="s">
         <v>27</v>
       </c>
       <c r="N106" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="P106" t="s">
         <v>28</v>
@@ -6836,10 +6854,10 @@
         <v>2347014</v>
       </c>
       <c r="B107" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C107" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D107" s="2">
         <v>2</v>
@@ -6848,7 +6866,7 @@
         <v>35</v>
       </c>
       <c r="F107" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="G107" t="s">
         <v>40</v>
@@ -6863,10 +6881,10 @@
         <v>42</v>
       </c>
       <c r="K107" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="L107" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="M107" t="s">
         <v>27</v>
@@ -6883,10 +6901,10 @@
         <v>2347017</v>
       </c>
       <c r="B108" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C108" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D108" s="2">
         <v>2</v>
@@ -6895,7 +6913,7 @@
         <v>35</v>
       </c>
       <c r="F108" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="G108" t="s">
         <v>23</v>
@@ -6910,16 +6928,16 @@
         <v>42</v>
       </c>
       <c r="K108" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="L108" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="M108" t="s">
         <v>27</v>
       </c>
       <c r="N108" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="P108" t="s">
         <v>28</v>
@@ -6933,10 +6951,10 @@
         <v>2347030</v>
       </c>
       <c r="B109" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C109" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D109" s="2">
         <v>2</v>
@@ -6945,7 +6963,7 @@
         <v>35</v>
       </c>
       <c r="F109" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="G109" t="s">
         <v>40</v>
@@ -6960,16 +6978,16 @@
         <v>42</v>
       </c>
       <c r="K109" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="L109" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="M109" t="s">
         <v>27</v>
       </c>
       <c r="N109" s="3" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="P109" t="s">
         <v>28</v>
@@ -6983,10 +7001,10 @@
         <v>2347021</v>
       </c>
       <c r="B110" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C110" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D110" s="2">
         <v>3</v>
@@ -6995,7 +7013,7 @@
         <v>21</v>
       </c>
       <c r="F110" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="G110" t="s">
         <v>40</v>
@@ -7010,16 +7028,16 @@
         <v>42</v>
       </c>
       <c r="K110" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="L110" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="M110" t="s">
         <v>27</v>
       </c>
       <c r="N110" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="P110" t="s">
         <v>28</v>
@@ -7033,10 +7051,10 @@
         <v>2347022</v>
       </c>
       <c r="B111" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C111" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D111" s="2">
         <v>3</v>
@@ -7045,7 +7063,7 @@
         <v>21</v>
       </c>
       <c r="F111" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="G111" t="s">
         <v>40</v>
@@ -7060,16 +7078,16 @@
         <v>42</v>
       </c>
       <c r="K111" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="L111" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="M111" t="s">
         <v>27</v>
       </c>
       <c r="N111" s="3" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="O111" s="1"/>
       <c r="P111" t="s">
@@ -7084,10 +7102,10 @@
         <v>2347024</v>
       </c>
       <c r="B112" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C112" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D112" s="2">
         <v>3</v>
@@ -7096,7 +7114,7 @@
         <v>21</v>
       </c>
       <c r="F112" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="G112" t="s">
         <v>40</v>
@@ -7111,16 +7129,16 @@
         <v>42</v>
       </c>
       <c r="K112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="L112" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="M112" t="s">
         <v>27</v>
       </c>
       <c r="N112" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="P112" t="s">
         <v>28</v>
@@ -7134,10 +7152,10 @@
         <v>2347026</v>
       </c>
       <c r="B113" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C113" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D113" s="2">
         <v>3</v>
@@ -7146,7 +7164,7 @@
         <v>35</v>
       </c>
       <c r="F113" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G113" t="s">
         <v>40</v>
@@ -7161,16 +7179,16 @@
         <v>42</v>
       </c>
       <c r="K113" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="L113" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="M113" t="s">
         <v>27</v>
       </c>
       <c r="N113" s="3" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="P113" t="s">
         <v>28</v>
@@ -7184,10 +7202,10 @@
         <v>2347027</v>
       </c>
       <c r="B114" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C114" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D114" s="2">
         <v>3</v>
@@ -7196,7 +7214,7 @@
         <v>35</v>
       </c>
       <c r="F114" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="G114" t="s">
         <v>40</v>
@@ -7211,16 +7229,16 @@
         <v>42</v>
       </c>
       <c r="K114" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="L114" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="M114" t="s">
         <v>27</v>
       </c>
       <c r="N114" s="3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="P114" t="s">
         <v>28</v>
@@ -7234,10 +7252,10 @@
         <v>2347029</v>
       </c>
       <c r="B115" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C115" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D115" s="2">
         <v>3</v>
@@ -7246,7 +7264,7 @@
         <v>35</v>
       </c>
       <c r="F115" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G115" t="s">
         <v>40</v>
@@ -7261,16 +7279,16 @@
         <v>42</v>
       </c>
       <c r="K115" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="L115" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="M115" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="N115" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="P115" t="s">
         <v>28</v>
@@ -7284,10 +7302,10 @@
         <v>2347031</v>
       </c>
       <c r="B116" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C116" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D116" s="2">
         <v>4</v>
@@ -7296,7 +7314,7 @@
         <v>21</v>
       </c>
       <c r="F116" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="G116" t="s">
         <v>40</v>
@@ -7311,16 +7329,16 @@
         <v>42</v>
       </c>
       <c r="K116" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="L116" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="M116" t="s">
         <v>27</v>
       </c>
       <c r="N116" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="P116" t="s">
         <v>28</v>
@@ -7334,10 +7352,10 @@
         <v>2347038</v>
       </c>
       <c r="B117" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C117" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D117" s="2">
         <v>4</v>
@@ -7346,10 +7364,10 @@
         <v>21</v>
       </c>
       <c r="F117" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="G117" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="H117" s="2">
         <v>60</v>
@@ -7361,16 +7379,16 @@
         <v>42</v>
       </c>
       <c r="K117" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="L117" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="M117" t="s">
         <v>27</v>
       </c>
       <c r="N117" s="3" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="P117" t="s">
         <v>28</v>
@@ -7384,10 +7402,10 @@
         <v>2361002</v>
       </c>
       <c r="B118" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C118" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D118" s="2">
         <v>1</v>
@@ -7411,7 +7429,7 @@
         <v>42</v>
       </c>
       <c r="K118" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="M118" t="s">
         <v>27</v>
@@ -7428,10 +7446,10 @@
         <v>2361002</v>
       </c>
       <c r="B119" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C119" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D119" s="2">
         <v>1</v>
@@ -7455,7 +7473,7 @@
         <v>42</v>
       </c>
       <c r="K119" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="M119" t="s">
         <v>27</v>
@@ -7472,10 +7490,10 @@
         <v>2361002</v>
       </c>
       <c r="B120" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C120" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D120" s="2">
         <v>1</v>
@@ -7499,7 +7517,7 @@
         <v>42</v>
       </c>
       <c r="K120" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="M120" t="s">
         <v>27</v>
@@ -7516,10 +7534,10 @@
         <v>2361004</v>
       </c>
       <c r="B121" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C121" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D121" s="2">
         <v>1</v>
@@ -7528,7 +7546,7 @@
         <v>21</v>
       </c>
       <c r="F121" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G121" t="s">
         <v>23</v>
@@ -7543,7 +7561,7 @@
         <v>42</v>
       </c>
       <c r="K121" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="M121" t="s">
         <v>27</v>
@@ -7560,10 +7578,10 @@
         <v>2393002</v>
       </c>
       <c r="B122" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C122" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D122" s="2">
         <v>1</v>
@@ -7572,7 +7590,7 @@
         <v>21</v>
       </c>
       <c r="F122" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G122" t="s">
         <v>23</v>
@@ -7587,10 +7605,10 @@
         <v>42</v>
       </c>
       <c r="K122" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="L122" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="M122" t="s">
         <v>27</v>
@@ -7607,10 +7625,10 @@
         <v>2393002</v>
       </c>
       <c r="B123" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C123" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D123" s="2">
         <v>1</v>
@@ -7619,7 +7637,7 @@
         <v>21</v>
       </c>
       <c r="F123" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G123" t="s">
         <v>23</v>
@@ -7628,16 +7646,16 @@
         <v>20</v>
       </c>
       <c r="I123" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="J123" t="s">
         <v>42</v>
       </c>
       <c r="K123" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="L123" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="M123" t="s">
         <v>27</v>
@@ -7654,10 +7672,10 @@
         <v>2393002</v>
       </c>
       <c r="B124" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C124" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D124" s="2">
         <v>1</v>
@@ -7666,7 +7684,7 @@
         <v>21</v>
       </c>
       <c r="F124" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G124" t="s">
         <v>23</v>
@@ -7675,16 +7693,16 @@
         <v>20</v>
       </c>
       <c r="I124" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="J124" t="s">
         <v>42</v>
       </c>
       <c r="K124" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="L124" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="M124" t="s">
         <v>27</v>
@@ -7701,10 +7719,10 @@
         <v>2394004</v>
       </c>
       <c r="B125" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C125" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D125" s="2">
         <v>1</v>
@@ -7713,7 +7731,7 @@
         <v>21</v>
       </c>
       <c r="F125" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G125" t="s">
         <v>23</v>
@@ -7728,10 +7746,10 @@
         <v>25</v>
       </c>
       <c r="K125" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="L125" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="M125" t="s">
         <v>27</v>
@@ -7748,10 +7766,10 @@
         <v>2394004</v>
       </c>
       <c r="B126" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C126" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D126" s="2">
         <v>1</v>
@@ -7760,7 +7778,7 @@
         <v>21</v>
       </c>
       <c r="F126" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G126" t="s">
         <v>23</v>
@@ -7769,16 +7787,16 @@
         <v>12</v>
       </c>
       <c r="I126" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J126" t="s">
         <v>25</v>
       </c>
       <c r="K126" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="L126" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="M126" t="s">
         <v>27</v>
@@ -7795,10 +7813,10 @@
         <v>2394004</v>
       </c>
       <c r="B127" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C127" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D127" s="2">
         <v>1</v>
@@ -7807,7 +7825,7 @@
         <v>21</v>
       </c>
       <c r="F127" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G127" t="s">
         <v>23</v>
@@ -7816,16 +7834,16 @@
         <v>12</v>
       </c>
       <c r="I127" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J127" t="s">
         <v>25</v>
       </c>
       <c r="K127" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="L127" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="M127" t="s">
         <v>27</v>
@@ -7842,10 +7860,10 @@
         <v>2395003</v>
       </c>
       <c r="B128" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C128" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D128" s="2">
         <v>1</v>
@@ -7854,7 +7872,7 @@
         <v>21</v>
       </c>
       <c r="F128" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G128" t="s">
         <v>23</v>
@@ -7869,10 +7887,10 @@
         <v>42</v>
       </c>
       <c r="K128" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="L128" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="M128" t="s">
         <v>27</v>
@@ -7889,10 +7907,10 @@
         <v>2395003</v>
       </c>
       <c r="B129" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C129" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D129" s="2">
         <v>1</v>
@@ -7901,7 +7919,7 @@
         <v>21</v>
       </c>
       <c r="F129" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G129" t="s">
         <v>23</v>
@@ -7916,10 +7934,10 @@
         <v>42</v>
       </c>
       <c r="K129" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="L129" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="M129" t="s">
         <v>27</v>
@@ -7936,10 +7954,10 @@
         <v>2395003</v>
       </c>
       <c r="B130" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C130" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D130" s="2">
         <v>1</v>
@@ -7948,7 +7966,7 @@
         <v>21</v>
       </c>
       <c r="F130" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G130" t="s">
         <v>23</v>
@@ -7963,10 +7981,10 @@
         <v>42</v>
       </c>
       <c r="K130" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="L130" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="M130" t="s">
         <v>27</v>
@@ -7983,10 +8001,10 @@
         <v>2396001</v>
       </c>
       <c r="B131" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C131" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D131" s="2">
         <v>1</v>
@@ -7995,7 +8013,7 @@
         <v>21</v>
       </c>
       <c r="F131" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G131" t="s">
         <v>23</v>
@@ -8010,10 +8028,10 @@
         <v>25</v>
       </c>
       <c r="K131" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="L131" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="M131" t="s">
         <v>27</v>
@@ -8030,10 +8048,10 @@
         <v>2396001</v>
       </c>
       <c r="B132" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C132" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D132" s="2">
         <v>1</v>
@@ -8042,7 +8060,7 @@
         <v>21</v>
       </c>
       <c r="F132" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G132" t="s">
         <v>23</v>
@@ -8051,16 +8069,16 @@
         <v>20</v>
       </c>
       <c r="I132" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J132" t="s">
         <v>25</v>
       </c>
       <c r="K132" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="L132" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="M132" t="s">
         <v>27</v>
@@ -8077,10 +8095,10 @@
         <v>2396001</v>
       </c>
       <c r="B133" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C133" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D133" s="2">
         <v>1</v>
@@ -8089,7 +8107,7 @@
         <v>21</v>
       </c>
       <c r="F133" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G133" t="s">
         <v>23</v>
@@ -8098,16 +8116,16 @@
         <v>20</v>
       </c>
       <c r="I133" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J133" t="s">
         <v>25</v>
       </c>
       <c r="K133" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="L133" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="M133" t="s">
         <v>27</v>
@@ -8124,10 +8142,10 @@
         <v>2397003</v>
       </c>
       <c r="B134" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C134" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D134" s="2">
         <v>1</v>
@@ -8151,16 +8169,16 @@
         <v>25</v>
       </c>
       <c r="K134" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="L134" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="M134" t="s">
         <v>27</v>
       </c>
       <c r="N134" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="P134" t="s">
         <v>28</v>
@@ -8174,10 +8192,10 @@
         <v>2397003</v>
       </c>
       <c r="B135" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C135" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D135" s="2">
         <v>1</v>
@@ -8195,22 +8213,22 @@
         <v>12</v>
       </c>
       <c r="I135" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J135" t="s">
         <v>25</v>
       </c>
       <c r="K135" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="L135" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="M135" t="s">
         <v>27</v>
       </c>
       <c r="N135" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="P135" t="s">
         <v>28</v>
@@ -8224,10 +8242,10 @@
         <v>2397003</v>
       </c>
       <c r="B136" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C136" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D136" s="2">
         <v>1</v>
@@ -8245,22 +8263,22 @@
         <v>12</v>
       </c>
       <c r="I136" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J136" t="s">
         <v>25</v>
       </c>
       <c r="K136" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="L136" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="M136" t="s">
         <v>27</v>
       </c>
       <c r="N136" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="P136" t="s">
         <v>28</v>
@@ -8274,10 +8292,10 @@
         <v>2397008</v>
       </c>
       <c r="B137" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C137" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D137" s="2">
         <v>1</v>
@@ -8301,10 +8319,10 @@
         <v>25</v>
       </c>
       <c r="K137" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="L137" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="M137" t="s">
         <v>27</v>
@@ -8321,10 +8339,10 @@
         <v>2397008</v>
       </c>
       <c r="B138" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C138" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D138" s="2">
         <v>1</v>
@@ -8342,16 +8360,16 @@
         <v>12</v>
       </c>
       <c r="I138" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J138" t="s">
         <v>25</v>
       </c>
       <c r="K138" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="L138" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="M138" t="s">
         <v>27</v>
@@ -8368,10 +8386,10 @@
         <v>2397008</v>
       </c>
       <c r="B139" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C139" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D139" s="2">
         <v>1</v>
@@ -8389,16 +8407,16 @@
         <v>12</v>
       </c>
       <c r="I139" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J139" t="s">
         <v>25</v>
       </c>
       <c r="K139" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="L139" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="M139" t="s">
         <v>27</v>
@@ -8415,10 +8433,10 @@
         <v>2398001</v>
       </c>
       <c r="B140" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C140" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D140" s="2">
         <v>1</v>
@@ -8442,16 +8460,16 @@
         <v>42</v>
       </c>
       <c r="K140" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="L140" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="M140" t="s">
         <v>27</v>
       </c>
       <c r="N140" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="P140" t="s">
         <v>28</v>
@@ -8465,10 +8483,10 @@
         <v>2398001</v>
       </c>
       <c r="B141" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C141" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D141" s="2">
         <v>1</v>
@@ -8492,16 +8510,16 @@
         <v>42</v>
       </c>
       <c r="K141" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="L141" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="M141" t="s">
         <v>27</v>
       </c>
       <c r="N141" s="4" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="P141" t="s">
         <v>28</v>
@@ -8515,10 +8533,10 @@
         <v>2398001</v>
       </c>
       <c r="B142" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C142" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D142" s="2">
         <v>1</v>
@@ -8542,16 +8560,16 @@
         <v>42</v>
       </c>
       <c r="K142" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="L142" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="M142" t="s">
         <v>27</v>
       </c>
       <c r="N142" s="4" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="P142" t="s">
         <v>28</v>
@@ -8565,10 +8583,10 @@
         <v>2398006</v>
       </c>
       <c r="B143" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C143" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D143" s="2">
         <v>1</v>
@@ -8592,10 +8610,10 @@
         <v>42</v>
       </c>
       <c r="K143" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="L143" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="M143" t="s">
         <v>27</v>
@@ -8612,10 +8630,10 @@
         <v>2398006</v>
       </c>
       <c r="B144" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C144" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D144" s="2">
         <v>1</v>
@@ -8639,10 +8657,10 @@
         <v>42</v>
       </c>
       <c r="K144" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="L144" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="M144" t="s">
         <v>27</v>
@@ -8659,10 +8677,10 @@
         <v>2398006</v>
       </c>
       <c r="B145" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C145" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D145" s="2">
         <v>1</v>
@@ -8686,10 +8704,10 @@
         <v>42</v>
       </c>
       <c r="K145" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="L145" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="M145" t="s">
         <v>27</v>
@@ -8706,10 +8724,10 @@
         <v>2398013</v>
       </c>
       <c r="B146" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C146" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D146" s="2">
         <v>2</v>
@@ -8718,7 +8736,7 @@
         <v>21</v>
       </c>
       <c r="F146" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G146" t="s">
         <v>23</v>
@@ -8733,10 +8751,10 @@
         <v>25</v>
       </c>
       <c r="K146" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="L146" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="M146" t="s">
         <v>27</v>
@@ -8753,10 +8771,10 @@
         <v>2398013</v>
       </c>
       <c r="B147" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C147" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D147" s="2">
         <v>2</v>
@@ -8765,7 +8783,7 @@
         <v>21</v>
       </c>
       <c r="F147" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G147" t="s">
         <v>23</v>
@@ -8774,16 +8792,16 @@
         <v>20</v>
       </c>
       <c r="I147" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J147" t="s">
         <v>25</v>
       </c>
       <c r="K147" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="L147" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="M147" t="s">
         <v>27</v>
@@ -8800,10 +8818,10 @@
         <v>2398013</v>
       </c>
       <c r="B148" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C148" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D148" s="2">
         <v>2</v>
@@ -8812,7 +8830,7 @@
         <v>21</v>
       </c>
       <c r="F148" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G148" t="s">
         <v>23</v>
@@ -8821,13 +8839,13 @@
         <v>20</v>
       </c>
       <c r="I148" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J148" t="s">
         <v>25</v>
       </c>
       <c r="K148" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="M148" t="s">
         <v>27</v>
@@ -8844,10 +8862,10 @@
         <v>2399003</v>
       </c>
       <c r="B149" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C149" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D149" s="2">
         <v>1</v>
@@ -8871,10 +8889,10 @@
         <v>42</v>
       </c>
       <c r="K149" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="L149" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="M149" t="s">
         <v>27</v>
@@ -8891,10 +8909,10 @@
         <v>2399003</v>
       </c>
       <c r="B150" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C150" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D150" s="2">
         <v>1</v>
@@ -8918,10 +8936,10 @@
         <v>42</v>
       </c>
       <c r="K150" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="L150" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="M150" t="s">
         <v>27</v>
@@ -8938,10 +8956,10 @@
         <v>2399003</v>
       </c>
       <c r="B151" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C151" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D151" s="2">
         <v>1</v>
@@ -8965,10 +8983,10 @@
         <v>42</v>
       </c>
       <c r="K151" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="L151" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="M151" t="s">
         <v>27</v>
@@ -8985,10 +9003,10 @@
         <v>2399010</v>
       </c>
       <c r="B152" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C152" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D152" s="2">
         <v>1</v>
@@ -9012,10 +9030,10 @@
         <v>42</v>
       </c>
       <c r="K152" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="L152" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="M152" t="s">
         <v>27</v>
@@ -9032,10 +9050,10 @@
         <v>2399010</v>
       </c>
       <c r="B153" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C153" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D153" s="2">
         <v>1</v>
@@ -9059,10 +9077,10 @@
         <v>42</v>
       </c>
       <c r="K153" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="L153" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="M153" t="s">
         <v>27</v>
@@ -9079,10 +9097,10 @@
         <v>2399010</v>
       </c>
       <c r="B154" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C154" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D154" s="2">
         <v>1</v>
@@ -9106,10 +9124,10 @@
         <v>42</v>
       </c>
       <c r="K154" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="L154" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="M154" t="s">
         <v>27</v>
@@ -9126,10 +9144,10 @@
         <v>2399014</v>
       </c>
       <c r="B155" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C155" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D155" s="2">
         <v>2</v>
@@ -9138,7 +9156,7 @@
         <v>21</v>
       </c>
       <c r="F155" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G155" t="s">
         <v>23</v>
@@ -9153,10 +9171,10 @@
         <v>25</v>
       </c>
       <c r="K155" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="L155" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="M155" t="s">
         <v>27</v>
@@ -9173,10 +9191,10 @@
         <v>2399014</v>
       </c>
       <c r="B156" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C156" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D156" s="2">
         <v>2</v>
@@ -9185,7 +9203,7 @@
         <v>21</v>
       </c>
       <c r="F156" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G156" t="s">
         <v>23</v>
@@ -9194,16 +9212,16 @@
         <v>21</v>
       </c>
       <c r="I156" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J156" t="s">
         <v>25</v>
       </c>
       <c r="K156" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="L156" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="M156" t="s">
         <v>27</v>
@@ -9220,10 +9238,10 @@
         <v>2399014</v>
       </c>
       <c r="B157" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C157" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D157" s="2">
         <v>2</v>
@@ -9232,7 +9250,7 @@
         <v>21</v>
       </c>
       <c r="F157" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G157" t="s">
         <v>23</v>
@@ -9241,13 +9259,13 @@
         <v>21</v>
       </c>
       <c r="I157" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J157" t="s">
         <v>25</v>
       </c>
       <c r="K157" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="M157" t="s">
         <v>27</v>
@@ -9264,10 +9282,10 @@
         <v>2400003</v>
       </c>
       <c r="B158" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C158" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D158" s="2">
         <v>1</v>
@@ -9291,16 +9309,16 @@
         <v>42</v>
       </c>
       <c r="K158" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="L158" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="M158" t="s">
         <v>27</v>
       </c>
       <c r="N158" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="P158" t="s">
         <v>28</v>
@@ -9314,10 +9332,10 @@
         <v>2400003</v>
       </c>
       <c r="B159" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C159" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D159" s="2">
         <v>1</v>
@@ -9341,16 +9359,16 @@
         <v>42</v>
       </c>
       <c r="K159" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="L159" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="M159" t="s">
         <v>27</v>
       </c>
       <c r="N159" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="P159" t="s">
         <v>28</v>
@@ -9364,10 +9382,10 @@
         <v>2400003</v>
       </c>
       <c r="B160" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C160" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D160" s="2">
         <v>1</v>
@@ -9391,16 +9409,16 @@
         <v>42</v>
       </c>
       <c r="K160" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="L160" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="M160" t="s">
         <v>27</v>
       </c>
       <c r="N160" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="P160" t="s">
         <v>28</v>
@@ -9414,10 +9432,10 @@
         <v>2400008</v>
       </c>
       <c r="B161" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C161" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D161" s="2">
         <v>1</v>
@@ -9441,10 +9459,10 @@
         <v>42</v>
       </c>
       <c r="K161" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="L161" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="M161" t="s">
         <v>27</v>
@@ -9461,10 +9479,10 @@
         <v>2400008</v>
       </c>
       <c r="B162" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C162" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D162" s="2">
         <v>1</v>
@@ -9488,10 +9506,10 @@
         <v>42</v>
       </c>
       <c r="K162" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L162" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="M162" t="s">
         <v>27</v>
@@ -9508,10 +9526,10 @@
         <v>2400008</v>
       </c>
       <c r="B163" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C163" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D163" s="2">
         <v>1</v>
@@ -9535,10 +9553,10 @@
         <v>42</v>
       </c>
       <c r="K163" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="L163" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="M163" t="s">
         <v>27</v>
@@ -9555,10 +9573,10 @@
         <v>2400012</v>
       </c>
       <c r="B164" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C164" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D164" s="2">
         <v>2</v>
@@ -9567,7 +9585,7 @@
         <v>21</v>
       </c>
       <c r="F164" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G164" t="s">
         <v>23</v>
@@ -9582,16 +9600,16 @@
         <v>25</v>
       </c>
       <c r="K164" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="L164" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="M164" t="s">
         <v>27</v>
       </c>
       <c r="N164" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="P164" t="s">
         <v>28</v>
@@ -9605,10 +9623,10 @@
         <v>2400012</v>
       </c>
       <c r="B165" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C165" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D165" s="2">
         <v>2</v>
@@ -9617,7 +9635,7 @@
         <v>21</v>
       </c>
       <c r="F165" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G165" t="s">
         <v>23</v>
@@ -9626,22 +9644,22 @@
         <v>21</v>
       </c>
       <c r="I165" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J165" t="s">
         <v>25</v>
       </c>
       <c r="K165" s="3" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="L165" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="M165" t="s">
         <v>27</v>
       </c>
       <c r="N165" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="P165" t="s">
         <v>28</v>
@@ -9655,10 +9673,10 @@
         <v>2400012</v>
       </c>
       <c r="B166" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C166" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D166" s="2">
         <v>2</v>
@@ -9667,7 +9685,7 @@
         <v>21</v>
       </c>
       <c r="F166" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G166" t="s">
         <v>23</v>
@@ -9676,19 +9694,19 @@
         <v>21</v>
       </c>
       <c r="I166" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J166" t="s">
         <v>25</v>
       </c>
       <c r="K166" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="M166" t="s">
         <v>27</v>
       </c>
       <c r="N166" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="P166" t="s">
         <v>28</v>
@@ -9702,10 +9720,10 @@
         <v>2401001</v>
       </c>
       <c r="B167" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C167" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D167" s="2">
         <v>1</v>
@@ -9729,10 +9747,10 @@
         <v>25</v>
       </c>
       <c r="K167" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="L167" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="M167" t="s">
         <v>27</v>
@@ -9749,10 +9767,10 @@
         <v>2401001</v>
       </c>
       <c r="B168" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C168" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D168" s="2">
         <v>1</v>
@@ -9770,16 +9788,16 @@
         <v>12</v>
       </c>
       <c r="I168" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J168" t="s">
         <v>25</v>
       </c>
       <c r="K168" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="L168" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="M168" t="s">
         <v>27</v>
@@ -9796,10 +9814,10 @@
         <v>2401001</v>
       </c>
       <c r="B169" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C169" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D169" s="2">
         <v>1</v>
@@ -9817,16 +9835,16 @@
         <v>12</v>
       </c>
       <c r="I169" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J169" t="s">
         <v>25</v>
       </c>
       <c r="K169" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="L169" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="M169" t="s">
         <v>27</v>
@@ -9843,10 +9861,10 @@
         <v>2401007</v>
       </c>
       <c r="B170" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C170" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D170" s="2">
         <v>1</v>
@@ -9870,10 +9888,10 @@
         <v>25</v>
       </c>
       <c r="K170" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="L170" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="M170" t="s">
         <v>27</v>
@@ -9890,10 +9908,10 @@
         <v>2401007</v>
       </c>
       <c r="B171" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C171" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D171" s="2">
         <v>1</v>
@@ -9911,16 +9929,16 @@
         <v>12</v>
       </c>
       <c r="I171" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J171" t="s">
         <v>25</v>
       </c>
       <c r="K171" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="L171" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="M171" t="s">
         <v>27</v>
@@ -9937,10 +9955,10 @@
         <v>2401007</v>
       </c>
       <c r="B172" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C172" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D172" s="2">
         <v>1</v>
@@ -9958,16 +9976,16 @@
         <v>12</v>
       </c>
       <c r="I172" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J172" t="s">
         <v>25</v>
       </c>
       <c r="K172" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="L172" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="M172" t="s">
         <v>27</v>
@@ -9984,10 +10002,10 @@
         <v>2401013</v>
       </c>
       <c r="B173" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C173" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D173" s="2">
         <v>2</v>
@@ -9996,7 +10014,7 @@
         <v>21</v>
       </c>
       <c r="F173" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="G173" t="s">
         <v>40</v>
@@ -10011,16 +10029,16 @@
         <v>42</v>
       </c>
       <c r="K173" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="L173" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="M173" t="s">
         <v>27</v>
       </c>
       <c r="N173" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="P173" t="s">
         <v>28</v>
@@ -10034,10 +10052,10 @@
         <v>2401013</v>
       </c>
       <c r="B174" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C174" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D174" s="2">
         <v>2</v>
@@ -10046,7 +10064,7 @@
         <v>21</v>
       </c>
       <c r="F174" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="G174" t="s">
         <v>40</v>
@@ -10061,16 +10079,16 @@
         <v>42</v>
       </c>
       <c r="K174" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="L174" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="M174" t="s">
         <v>27</v>
       </c>
       <c r="N174" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="P174" t="s">
         <v>28</v>
@@ -10084,10 +10102,10 @@
         <v>2401013</v>
       </c>
       <c r="B175" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C175" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D175" s="2">
         <v>2</v>
@@ -10096,7 +10114,7 @@
         <v>21</v>
       </c>
       <c r="F175" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="G175" t="s">
         <v>40</v>
@@ -10111,16 +10129,16 @@
         <v>42</v>
       </c>
       <c r="K175" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="L175" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="M175" t="s">
         <v>27</v>
       </c>
       <c r="N175" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="P175" t="s">
         <v>28</v>
@@ -10134,10 +10152,10 @@
         <v>2401018</v>
       </c>
       <c r="B176" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C176" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D176" s="2">
         <v>2</v>
@@ -10146,7 +10164,7 @@
         <v>35</v>
       </c>
       <c r="F176" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="G176" t="s">
         <v>40</v>
@@ -10161,10 +10179,10 @@
         <v>42</v>
       </c>
       <c r="K176" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="L176" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="M176" t="s">
         <v>27</v>
@@ -10181,10 +10199,10 @@
         <v>2401018</v>
       </c>
       <c r="B177" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C177" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D177" s="2">
         <v>2</v>
@@ -10193,7 +10211,7 @@
         <v>35</v>
       </c>
       <c r="F177" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="G177" t="s">
         <v>40</v>
@@ -10208,10 +10226,10 @@
         <v>42</v>
       </c>
       <c r="K177" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="L177" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="M177" t="s">
         <v>27</v>
@@ -10228,10 +10246,10 @@
         <v>2401018</v>
       </c>
       <c r="B178" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C178" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D178" s="2">
         <v>2</v>
@@ -10240,7 +10258,7 @@
         <v>35</v>
       </c>
       <c r="F178" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="G178" t="s">
         <v>40</v>
@@ -10249,16 +10267,16 @@
         <v>4</v>
       </c>
       <c r="I178" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="J178" t="s">
         <v>42</v>
       </c>
       <c r="K178" t="s">
+        <v>389</v>
+      </c>
+      <c r="L178" t="s">
         <v>386</v>
-      </c>
-      <c r="L178" t="s">
-        <v>383</v>
       </c>
       <c r="M178" t="s">
         <v>27</v>
@@ -10275,10 +10293,10 @@
         <v>2401018</v>
       </c>
       <c r="B179" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C179" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D179" s="2">
         <v>2</v>
@@ -10287,7 +10305,7 @@
         <v>35</v>
       </c>
       <c r="F179" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="G179" t="s">
         <v>40</v>
@@ -10302,10 +10320,10 @@
         <v>42</v>
       </c>
       <c r="K179" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="L179" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="M179" t="s">
         <v>27</v>
@@ -10322,10 +10340,10 @@
         <v>2401018</v>
       </c>
       <c r="B180" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C180" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D180" s="2">
         <v>2</v>
@@ -10334,7 +10352,7 @@
         <v>35</v>
       </c>
       <c r="F180" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="G180" t="s">
         <v>40</v>
@@ -10343,16 +10361,16 @@
         <v>4</v>
       </c>
       <c r="I180" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="J180" t="s">
         <v>42</v>
       </c>
       <c r="K180" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="L180" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="M180" t="s">
         <v>27</v>
@@ -10369,10 +10387,10 @@
         <v>2401018</v>
       </c>
       <c r="B181" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C181" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D181" s="2">
         <v>2</v>
@@ -10381,7 +10399,7 @@
         <v>35</v>
       </c>
       <c r="F181" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="G181" t="s">
         <v>40</v>
@@ -10390,16 +10408,16 @@
         <v>4</v>
       </c>
       <c r="I181" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="J181" t="s">
         <v>42</v>
       </c>
       <c r="K181" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="L181" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="M181" t="s">
         <v>27</v>
@@ -10416,10 +10434,10 @@
         <v>2401018</v>
       </c>
       <c r="B182" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C182" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D182" s="2">
         <v>2</v>
@@ -10428,7 +10446,7 @@
         <v>35</v>
       </c>
       <c r="F182" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="G182" t="s">
         <v>40</v>
@@ -10437,16 +10455,16 @@
         <v>4</v>
       </c>
       <c r="I182" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="J182" t="s">
         <v>42</v>
       </c>
       <c r="K182" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="L182" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="M182" t="s">
         <v>27</v>
@@ -10463,10 +10481,10 @@
         <v>2402003</v>
       </c>
       <c r="B183" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C183" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D183" s="2">
         <v>1</v>
@@ -10490,16 +10508,16 @@
         <v>25</v>
       </c>
       <c r="K183" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="L183" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="M183" t="s">
         <v>27</v>
       </c>
       <c r="N183" s="4" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="P183" t="s">
         <v>28</v>
@@ -10513,10 +10531,10 @@
         <v>2402003</v>
       </c>
       <c r="B184" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C184" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D184" s="2">
         <v>1</v>
@@ -10534,22 +10552,22 @@
         <v>12</v>
       </c>
       <c r="I184" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J184" t="s">
         <v>25</v>
       </c>
       <c r="K184" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="L184" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="M184" t="s">
         <v>27</v>
       </c>
       <c r="N184" s="4" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="P184" t="s">
         <v>28</v>
@@ -10563,10 +10581,10 @@
         <v>2402003</v>
       </c>
       <c r="B185" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C185" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D185" s="2">
         <v>1</v>
@@ -10584,22 +10602,22 @@
         <v>12</v>
       </c>
       <c r="I185" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J185" t="s">
         <v>25</v>
       </c>
       <c r="K185" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="L185" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="M185" t="s">
         <v>27</v>
       </c>
       <c r="N185" s="4" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="P185" t="s">
         <v>28</v>
@@ -10613,10 +10631,10 @@
         <v>2402008</v>
       </c>
       <c r="B186" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C186" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D186" s="2">
         <v>1</v>
@@ -10640,16 +10658,16 @@
         <v>25</v>
       </c>
       <c r="K186" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="L186" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="M186" t="s">
         <v>27</v>
       </c>
       <c r="N186" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="P186" t="s">
         <v>28</v>
@@ -10663,10 +10681,10 @@
         <v>2402008</v>
       </c>
       <c r="B187" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C187" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D187" s="2">
         <v>1</v>
@@ -10684,22 +10702,22 @@
         <v>12</v>
       </c>
       <c r="I187" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J187" t="s">
         <v>25</v>
       </c>
       <c r="K187" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="L187" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="M187" t="s">
         <v>27</v>
       </c>
       <c r="N187" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="P187" t="s">
         <v>28</v>
@@ -10713,10 +10731,10 @@
         <v>2402008</v>
       </c>
       <c r="B188" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C188" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D188" s="2">
         <v>1</v>
@@ -10734,22 +10752,22 @@
         <v>12</v>
       </c>
       <c r="I188" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J188" t="s">
         <v>25</v>
       </c>
       <c r="K188" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="L188" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="M188" t="s">
         <v>27</v>
       </c>
       <c r="N188" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="P188" t="s">
         <v>28</v>
@@ -10763,10 +10781,10 @@
         <v>2402015</v>
       </c>
       <c r="B189" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C189" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D189" s="2">
         <v>2</v>
@@ -10775,7 +10793,7 @@
         <v>21</v>
       </c>
       <c r="F189" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G189" t="s">
         <v>23</v>
@@ -10790,13 +10808,13 @@
         <v>42</v>
       </c>
       <c r="K189" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="M189" t="s">
         <v>27</v>
       </c>
       <c r="N189" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="P189" t="s">
         <v>28</v>
@@ -10810,10 +10828,10 @@
         <v>2402015</v>
       </c>
       <c r="B190" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C190" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D190" s="2">
         <v>2</v>
@@ -10822,7 +10840,7 @@
         <v>21</v>
       </c>
       <c r="F190" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G190" t="s">
         <v>23</v>
@@ -10837,13 +10855,13 @@
         <v>42</v>
       </c>
       <c r="K190" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="M190" t="s">
         <v>27</v>
       </c>
       <c r="N190" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="P190" t="s">
         <v>28</v>
@@ -10857,10 +10875,10 @@
         <v>2402015</v>
       </c>
       <c r="B191" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C191" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D191" s="2">
         <v>2</v>
@@ -10869,7 +10887,7 @@
         <v>21</v>
       </c>
       <c r="F191" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G191" t="s">
         <v>23</v>
@@ -10884,7 +10902,7 @@
         <v>42</v>
       </c>
       <c r="K191" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="M191" t="s">
         <v>27</v>
@@ -10902,10 +10920,10 @@
         <v>2403004</v>
       </c>
       <c r="B192" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C192" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D192" s="2">
         <v>1</v>
@@ -10929,16 +10947,16 @@
         <v>42</v>
       </c>
       <c r="K192" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="L192" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="M192" t="s">
         <v>27</v>
       </c>
       <c r="N192" s="4" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="P192" t="s">
         <v>28</v>
@@ -10952,10 +10970,10 @@
         <v>2403004</v>
       </c>
       <c r="B193" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C193" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D193" s="2">
         <v>1</v>
@@ -10979,16 +10997,16 @@
         <v>42</v>
       </c>
       <c r="K193" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="L193" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="M193" t="s">
         <v>27</v>
       </c>
       <c r="N193" s="4" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="P193" t="s">
         <v>28</v>
@@ -11002,10 +11020,10 @@
         <v>2403004</v>
       </c>
       <c r="B194" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C194" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D194" s="2">
         <v>1</v>
@@ -11029,16 +11047,16 @@
         <v>42</v>
       </c>
       <c r="K194" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="L194" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="M194" t="s">
         <v>27</v>
       </c>
       <c r="N194" s="4" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="P194" t="s">
         <v>28</v>
@@ -11052,10 +11070,10 @@
         <v>2403009</v>
       </c>
       <c r="B195" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C195" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D195" s="2">
         <v>1</v>
@@ -11079,10 +11097,10 @@
         <v>42</v>
       </c>
       <c r="K195" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="L195" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="M195" t="s">
         <v>27</v>
@@ -11099,10 +11117,10 @@
         <v>2403009</v>
       </c>
       <c r="B196" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C196" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D196" s="2">
         <v>1</v>
@@ -11126,10 +11144,10 @@
         <v>42</v>
       </c>
       <c r="K196" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="L196" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="M196" t="s">
         <v>27</v>
@@ -11146,10 +11164,10 @@
         <v>2403009</v>
       </c>
       <c r="B197" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C197" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D197" s="2">
         <v>1</v>
@@ -11173,10 +11191,10 @@
         <v>42</v>
       </c>
       <c r="K197" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="L197" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="M197" t="s">
         <v>27</v>
@@ -11193,10 +11211,10 @@
         <v>2403013</v>
       </c>
       <c r="B198" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C198" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D198" s="2">
         <v>2</v>
@@ -11205,7 +11223,7 @@
         <v>21</v>
       </c>
       <c r="F198" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G198" t="s">
         <v>23</v>
@@ -11220,7 +11238,7 @@
         <v>25</v>
       </c>
       <c r="K198" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="M198" t="s">
         <v>27</v>
@@ -11237,10 +11255,10 @@
         <v>2403013</v>
       </c>
       <c r="B199" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C199" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D199" s="2">
         <v>2</v>
@@ -11249,7 +11267,7 @@
         <v>21</v>
       </c>
       <c r="F199" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G199" t="s">
         <v>23</v>
@@ -11258,13 +11276,13 @@
         <v>21</v>
       </c>
       <c r="I199" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J199" t="s">
         <v>25</v>
       </c>
       <c r="K199" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="M199" t="s">
         <v>27</v>
@@ -11281,10 +11299,10 @@
         <v>2403013</v>
       </c>
       <c r="B200" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C200" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D200" s="2">
         <v>2</v>
@@ -11293,7 +11311,7 @@
         <v>21</v>
       </c>
       <c r="F200" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G200" t="s">
         <v>23</v>
@@ -11302,13 +11320,13 @@
         <v>21</v>
       </c>
       <c r="I200" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J200" t="s">
         <v>25</v>
       </c>
       <c r="K200" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="M200" t="s">
         <v>27</v>
@@ -11325,10 +11343,10 @@
         <v>2404001</v>
       </c>
       <c r="B201" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C201" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D201" s="2">
         <v>1</v>
@@ -11352,16 +11370,16 @@
         <v>42</v>
       </c>
       <c r="K201" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="L201" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="M201" t="s">
         <v>27</v>
       </c>
       <c r="N201" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="P201" t="s">
         <v>28</v>
@@ -11375,10 +11393,10 @@
         <v>2404001</v>
       </c>
       <c r="B202" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C202" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D202" s="2">
         <v>1</v>
@@ -11402,16 +11420,16 @@
         <v>42</v>
       </c>
       <c r="K202" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="L202" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="M202" t="s">
         <v>27</v>
       </c>
       <c r="N202" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="P202" t="s">
         <v>28</v>
@@ -11425,10 +11443,10 @@
         <v>2404001</v>
       </c>
       <c r="B203" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C203" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D203" s="2">
         <v>1</v>
@@ -11452,16 +11470,16 @@
         <v>42</v>
       </c>
       <c r="K203" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="L203" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="M203" t="s">
         <v>27</v>
       </c>
       <c r="N203" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="P203" t="s">
         <v>28</v>
@@ -11475,10 +11493,10 @@
         <v>2404006</v>
       </c>
       <c r="B204" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C204" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D204" s="2">
         <v>1</v>
@@ -11502,16 +11520,16 @@
         <v>42</v>
       </c>
       <c r="K204" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="L204" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="M204" t="s">
         <v>27</v>
       </c>
       <c r="N204" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="P204" t="s">
         <v>28</v>
@@ -11525,10 +11543,10 @@
         <v>2404006</v>
       </c>
       <c r="B205" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C205" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D205" s="2">
         <v>1</v>
@@ -11552,16 +11570,16 @@
         <v>42</v>
       </c>
       <c r="K205" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="L205" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="M205" t="s">
         <v>27</v>
       </c>
       <c r="N205" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="P205" t="s">
         <v>28</v>
@@ -11575,10 +11593,10 @@
         <v>2404006</v>
       </c>
       <c r="B206" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C206" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D206" s="2">
         <v>1</v>
@@ -11602,16 +11620,16 @@
         <v>42</v>
       </c>
       <c r="K206" t="s">
+        <v>436</v>
+      </c>
+      <c r="L206" t="s">
         <v>433</v>
       </c>
-      <c r="L206" t="s">
-        <v>430</v>
-      </c>
       <c r="M206" t="s">
         <v>27</v>
       </c>
       <c r="N206" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="P206" t="s">
         <v>28</v>
@@ -11625,10 +11643,10 @@
         <v>2404015</v>
       </c>
       <c r="B207" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C207" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D207" s="2">
         <v>2</v>
@@ -11637,7 +11655,7 @@
         <v>21</v>
       </c>
       <c r="F207" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="G207" t="s">
         <v>40</v>
@@ -11652,13 +11670,13 @@
         <v>25</v>
       </c>
       <c r="K207" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="M207" t="s">
         <v>27</v>
       </c>
       <c r="N207" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="P207" t="s">
         <v>28</v>
@@ -11672,10 +11690,10 @@
         <v>2404015</v>
       </c>
       <c r="B208" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C208" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D208" s="2">
         <v>2</v>
@@ -11684,7 +11702,7 @@
         <v>21</v>
       </c>
       <c r="F208" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="G208" t="s">
         <v>40</v>
@@ -11693,19 +11711,19 @@
         <v>32</v>
       </c>
       <c r="I208" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="J208" t="s">
         <v>25</v>
       </c>
       <c r="K208" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="M208" t="s">
         <v>27</v>
       </c>
       <c r="N208" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="P208" t="s">
         <v>28</v>
@@ -11719,10 +11737,10 @@
         <v>2404015</v>
       </c>
       <c r="B209" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C209" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D209" s="2">
         <v>2</v>
@@ -11731,7 +11749,7 @@
         <v>21</v>
       </c>
       <c r="F209" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="G209" t="s">
         <v>40</v>
@@ -11740,19 +11758,19 @@
         <v>32</v>
       </c>
       <c r="I209" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="J209" t="s">
         <v>25</v>
       </c>
       <c r="K209" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="M209" t="s">
         <v>27</v>
       </c>
       <c r="N209" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="P209" t="s">
         <v>28</v>
@@ -11766,10 +11784,10 @@
         <v>2405001</v>
       </c>
       <c r="B210" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C210" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D210" s="2">
         <v>1</v>
@@ -11793,16 +11811,16 @@
         <v>42</v>
       </c>
       <c r="K210" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="L210" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="M210" t="s">
         <v>27</v>
       </c>
       <c r="N210" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="P210" t="s">
         <v>28</v>
@@ -11816,10 +11834,10 @@
         <v>2405001</v>
       </c>
       <c r="B211" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C211" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D211" s="2">
         <v>1</v>
@@ -11843,16 +11861,16 @@
         <v>42</v>
       </c>
       <c r="K211" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="L211" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="M211" t="s">
         <v>27</v>
       </c>
       <c r="N211" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="P211" t="s">
         <v>28</v>
@@ -11866,10 +11884,10 @@
         <v>2405001</v>
       </c>
       <c r="B212" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C212" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D212" s="2">
         <v>1</v>
@@ -11893,16 +11911,16 @@
         <v>42</v>
       </c>
       <c r="K212" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="L212" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="M212" t="s">
         <v>27</v>
       </c>
       <c r="N212" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="P212" t="s">
         <v>28</v>
@@ -11916,10 +11934,10 @@
         <v>2405006</v>
       </c>
       <c r="B213" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C213" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D213" s="2">
         <v>1</v>
@@ -11943,16 +11961,16 @@
         <v>42</v>
       </c>
       <c r="K213" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="L213" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="M213" t="s">
         <v>27</v>
       </c>
       <c r="N213" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="P213" t="s">
         <v>28</v>
@@ -11966,10 +11984,10 @@
         <v>2405006</v>
       </c>
       <c r="B214" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C214" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D214" s="2">
         <v>1</v>
@@ -11993,16 +12011,16 @@
         <v>42</v>
       </c>
       <c r="K214" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="L214" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="M214" t="s">
         <v>27</v>
       </c>
       <c r="N214" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="P214" t="s">
         <v>28</v>
@@ -12016,10 +12034,10 @@
         <v>2405006</v>
       </c>
       <c r="B215" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C215" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D215" s="2">
         <v>1</v>
@@ -12043,16 +12061,16 @@
         <v>42</v>
       </c>
       <c r="K215" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="L215" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="M215" t="s">
         <v>27</v>
       </c>
       <c r="N215" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="P215" t="s">
         <v>28</v>
@@ -12066,10 +12084,10 @@
         <v>2405015</v>
       </c>
       <c r="B216" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C216" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D216" s="2">
         <v>2</v>
@@ -12078,7 +12096,7 @@
         <v>21</v>
       </c>
       <c r="F216" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G216" t="s">
         <v>23</v>
@@ -12093,16 +12111,16 @@
         <v>25</v>
       </c>
       <c r="K216" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="L216" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="M216" t="s">
         <v>27</v>
       </c>
       <c r="N216" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="P216" t="s">
         <v>28</v>
@@ -12116,10 +12134,10 @@
         <v>2405015</v>
       </c>
       <c r="B217" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C217" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D217" s="2">
         <v>2</v>
@@ -12128,7 +12146,7 @@
         <v>21</v>
       </c>
       <c r="F217" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G217" t="s">
         <v>23</v>
@@ -12137,22 +12155,22 @@
         <v>20</v>
       </c>
       <c r="I217" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J217" t="s">
         <v>25</v>
       </c>
       <c r="K217" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="L217" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="M217" t="s">
         <v>27</v>
       </c>
       <c r="N217" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="P217" t="s">
         <v>28</v>
@@ -12166,10 +12184,10 @@
         <v>2405015</v>
       </c>
       <c r="B218" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C218" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D218" s="2">
         <v>2</v>
@@ -12178,7 +12196,7 @@
         <v>21</v>
       </c>
       <c r="F218" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G218" t="s">
         <v>23</v>
@@ -12187,19 +12205,19 @@
         <v>20</v>
       </c>
       <c r="I218" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J218" t="s">
         <v>25</v>
       </c>
       <c r="K218" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="M218" t="s">
         <v>27</v>
       </c>
       <c r="N218" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="P218" t="s">
         <v>28</v>
@@ -12213,10 +12231,10 @@
         <v>2406004</v>
       </c>
       <c r="B219" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C219" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D219" s="2">
         <v>1</v>
@@ -12240,10 +12258,10 @@
         <v>25</v>
       </c>
       <c r="K219" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="L219" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="M219" t="s">
         <v>27</v>
@@ -12260,10 +12278,10 @@
         <v>2406004</v>
       </c>
       <c r="B220" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C220" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D220" s="2">
         <v>1</v>
@@ -12281,16 +12299,16 @@
         <v>4</v>
       </c>
       <c r="I220" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J220" t="s">
         <v>25</v>
       </c>
       <c r="K220" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="L220" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="M220" t="s">
         <v>27</v>
@@ -12307,10 +12325,10 @@
         <v>2406004</v>
       </c>
       <c r="B221" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C221" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D221" s="2">
         <v>1</v>
@@ -12328,13 +12346,13 @@
         <v>8</v>
       </c>
       <c r="I221" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="J221" t="s">
         <v>25</v>
       </c>
       <c r="L221" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="M221" t="s">
         <v>27</v>
@@ -12351,10 +12369,10 @@
         <v>2406004</v>
       </c>
       <c r="B222" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C222" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D222" s="2">
         <v>1</v>
@@ -12372,16 +12390,16 @@
         <v>4</v>
       </c>
       <c r="I222" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J222" t="s">
         <v>25</v>
       </c>
       <c r="K222" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="L222" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="M222" t="s">
         <v>27</v>
@@ -12398,10 +12416,10 @@
         <v>2406004</v>
       </c>
       <c r="B223" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C223" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D223" s="2">
         <v>1</v>
@@ -12419,13 +12437,13 @@
         <v>8</v>
       </c>
       <c r="I223" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="J223" t="s">
         <v>25</v>
       </c>
       <c r="L223" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="M223" t="s">
         <v>27</v>
@@ -12442,10 +12460,10 @@
         <v>2406009</v>
       </c>
       <c r="B224" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C224" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D224" s="2">
         <v>1</v>
@@ -12469,10 +12487,10 @@
         <v>25</v>
       </c>
       <c r="K224" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="L224" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="M224" t="s">
         <v>27</v>
@@ -12489,10 +12507,10 @@
         <v>2406009</v>
       </c>
       <c r="B225" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C225" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D225" s="2">
         <v>1</v>
@@ -12510,16 +12528,16 @@
         <v>4</v>
       </c>
       <c r="I225" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J225" t="s">
         <v>25</v>
       </c>
       <c r="K225" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="L225" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="M225" t="s">
         <v>27</v>
@@ -12536,10 +12554,10 @@
         <v>2406009</v>
       </c>
       <c r="B226" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C226" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D226" s="2">
         <v>1</v>
@@ -12557,16 +12575,16 @@
         <v>8</v>
       </c>
       <c r="I226" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="J226" t="s">
         <v>25</v>
       </c>
       <c r="K226" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="L226" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="M226" t="s">
         <v>27</v>
@@ -12583,10 +12601,10 @@
         <v>2406009</v>
       </c>
       <c r="B227" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C227" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D227" s="2">
         <v>1</v>
@@ -12604,16 +12622,16 @@
         <v>4</v>
       </c>
       <c r="I227" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J227" t="s">
         <v>25</v>
       </c>
       <c r="K227" t="s">
+        <v>470</v>
+      </c>
+      <c r="L227" t="s">
         <v>467</v>
-      </c>
-      <c r="L227" t="s">
-        <v>464</v>
       </c>
       <c r="M227" t="s">
         <v>27</v>
@@ -12630,10 +12648,10 @@
         <v>2406009</v>
       </c>
       <c r="B228" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C228" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D228" s="2">
         <v>1</v>
@@ -12651,16 +12669,16 @@
         <v>8</v>
       </c>
       <c r="I228" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="J228" t="s">
         <v>25</v>
       </c>
       <c r="K228" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="L228" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="M228" t="s">
         <v>27</v>
@@ -12677,10 +12695,10 @@
         <v>2406012</v>
       </c>
       <c r="B229" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C229" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D229" s="2">
         <v>2</v>
@@ -12689,7 +12707,7 @@
         <v>21</v>
       </c>
       <c r="F229" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="G229" t="s">
         <v>40</v>
@@ -12704,10 +12722,10 @@
         <v>42</v>
       </c>
       <c r="K229" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="L229" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="M229" t="s">
         <v>27</v>
@@ -12724,10 +12742,10 @@
         <v>2406012</v>
       </c>
       <c r="B230" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C230" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D230" s="2">
         <v>2</v>
@@ -12736,7 +12754,7 @@
         <v>21</v>
       </c>
       <c r="F230" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="G230" t="s">
         <v>40</v>
@@ -12745,16 +12763,16 @@
         <v>8</v>
       </c>
       <c r="I230" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="J230" t="s">
         <v>42</v>
       </c>
       <c r="K230" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="L230" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="M230" t="s">
         <v>27</v>
@@ -12771,10 +12789,10 @@
         <v>2406012</v>
       </c>
       <c r="B231" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C231" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D231" s="2">
         <v>2</v>
@@ -12783,7 +12801,7 @@
         <v>21</v>
       </c>
       <c r="F231" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="G231" t="s">
         <v>40</v>
@@ -12792,16 +12810,16 @@
         <v>8</v>
       </c>
       <c r="I231" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="J231" t="s">
         <v>42</v>
       </c>
       <c r="K231" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="L231" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="M231" t="s">
         <v>27</v>
@@ -12818,10 +12836,10 @@
         <v>2059001</v>
       </c>
       <c r="B232" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C232" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="D232" s="2">
         <v>1</v>
@@ -12830,7 +12848,7 @@
         <v>21</v>
       </c>
       <c r="F232" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G232" t="s">
         <v>23</v>
@@ -12845,10 +12863,10 @@
         <v>42</v>
       </c>
       <c r="K232" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="L232" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="M232" t="s">
         <v>27</v>
@@ -12865,10 +12883,10 @@
         <v>2059002</v>
       </c>
       <c r="B233" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C233" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="D233" s="2">
         <v>1</v>
@@ -12877,7 +12895,7 @@
         <v>21</v>
       </c>
       <c r="F233" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G233" t="s">
         <v>23</v>
@@ -12892,10 +12910,10 @@
         <v>42</v>
       </c>
       <c r="K233" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="L233" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="M233" t="s">
         <v>27</v>
@@ -12912,10 +12930,10 @@
         <v>2059006</v>
       </c>
       <c r="B234" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C234" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="D234" s="2">
         <v>1</v>
@@ -12939,10 +12957,10 @@
         <v>42</v>
       </c>
       <c r="K234" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="L234" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="M234" t="s">
         <v>27</v>
@@ -12959,10 +12977,10 @@
         <v>2140011</v>
       </c>
       <c r="B235" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C235" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="D235" s="2">
         <v>2</v>
@@ -12971,7 +12989,7 @@
         <v>21</v>
       </c>
       <c r="F235" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G235" t="s">
         <v>40</v>
@@ -12986,10 +13004,10 @@
         <v>42</v>
       </c>
       <c r="K235" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L235" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="M235" t="s">
         <v>27</v>
@@ -13006,10 +13024,10 @@
         <v>2390004</v>
       </c>
       <c r="B236" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="C236" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="D236" s="2">
         <v>1</v>
@@ -13033,10 +13051,10 @@
         <v>25</v>
       </c>
       <c r="K236" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="L236" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="M236" t="s">
         <v>27</v>
@@ -13053,10 +13071,10 @@
         <v>2390004</v>
       </c>
       <c r="B237" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="C237" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="D237" s="2">
         <v>1</v>
@@ -13074,16 +13092,16 @@
         <v>12</v>
       </c>
       <c r="I237" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J237" t="s">
         <v>25</v>
       </c>
       <c r="K237" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="L237" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="M237" t="s">
         <v>27</v>
@@ -13100,10 +13118,10 @@
         <v>2390004</v>
       </c>
       <c r="B238" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="C238" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="D238" s="2">
         <v>1</v>
@@ -13121,16 +13139,16 @@
         <v>12</v>
       </c>
       <c r="I238" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J238" t="s">
         <v>25</v>
       </c>
       <c r="K238" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="L238" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="M238" t="s">
         <v>27</v>
@@ -13147,10 +13165,10 @@
         <v>2390009</v>
       </c>
       <c r="B239" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="C239" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="D239" s="2">
         <v>1</v>
@@ -13174,10 +13192,10 @@
         <v>25</v>
       </c>
       <c r="K239" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="L239" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="M239" t="s">
         <v>27</v>
@@ -13194,10 +13212,10 @@
         <v>2390009</v>
       </c>
       <c r="B240" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="C240" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="D240" s="2">
         <v>1</v>
@@ -13215,16 +13233,16 @@
         <v>12</v>
       </c>
       <c r="I240" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J240" t="s">
         <v>25</v>
       </c>
       <c r="K240" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="L240" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="M240" t="s">
         <v>27</v>
@@ -13241,10 +13259,10 @@
         <v>2390009</v>
       </c>
       <c r="B241" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="C241" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="D241" s="2">
         <v>1</v>
@@ -13262,16 +13280,16 @@
         <v>12</v>
       </c>
       <c r="I241" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J241" t="s">
         <v>25</v>
       </c>
       <c r="K241" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="L241" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="M241" t="s">
         <v>27</v>
@@ -13288,10 +13306,10 @@
         <v>2390013</v>
       </c>
       <c r="B242" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="C242" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="D242" s="2">
         <v>2</v>
@@ -13300,7 +13318,7 @@
         <v>21</v>
       </c>
       <c r="F242" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G242" t="s">
         <v>23</v>
@@ -13315,7 +13333,7 @@
         <v>42</v>
       </c>
       <c r="K242" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="M242" t="s">
         <v>27</v>
@@ -13332,10 +13350,10 @@
         <v>2390013</v>
       </c>
       <c r="B243" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="C243" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="D243" s="2">
         <v>2</v>
@@ -13344,7 +13362,7 @@
         <v>21</v>
       </c>
       <c r="F243" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G243" t="s">
         <v>23</v>
@@ -13359,7 +13377,7 @@
         <v>42</v>
       </c>
       <c r="K243" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="M243" t="s">
         <v>27</v>
@@ -13376,10 +13394,10 @@
         <v>2390013</v>
       </c>
       <c r="B244" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="C244" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="D244" s="2">
         <v>2</v>
@@ -13388,7 +13406,7 @@
         <v>21</v>
       </c>
       <c r="F244" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G244" t="s">
         <v>23</v>
@@ -13403,7 +13421,7 @@
         <v>42</v>
       </c>
       <c r="K244" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="M244" t="s">
         <v>27</v>

--- a/POD_2026-27_11-5-2026.xlsx
+++ b/POD_2026-27_11-5-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://urjc-my.sharepoint.com/personal/esther_garcia_urjc_es/Documents/Documentos/POD 2026-27/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="289" documentId="11_79C815625599F410B0C00D3910C611C600045ACD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0ADBD62D-A6C4-4157-B246-38BE71564E3F}"/>
+  <xr:revisionPtr revIDLastSave="291" documentId="11_79C815625599F410B0C00D3910C611C600045ACD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18242A85-2A2B-4816-BF50-AEC34F59E758}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2938" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2939" uniqueCount="500">
   <si>
     <t>POD_2026-27_11-5-2026</t>
   </si>
@@ -371,7 +371,7 @@
     <t>G_AEROBIL_EXT_1A(F) (2125006), G_AERO_EXT_I_1A(F) (2151006), G_AERO_EXT822_II_1A(F) (2339006), G_TELECO-AEROESP_EXT822_1A(F) (2332006), G_TELECO-AEROESP_1A(F) (2412008), G_TRANSP_EXT822_1A(F) (2341006), G_VEHI_EXT_I_1A(F) (2284007), G_VEHI_EXT822_1A(F) (2356007)</t>
   </si>
   <si>
-    <t>MISAEL MARRIAGA (76)</t>
+    <t>MISAEL MARRIAGA (60)</t>
   </si>
   <si>
     <t>(2384) GRADO EN INGENIERÍA BIOMÉDICA (INGLÉS)(FUENLABRADA)</t>
@@ -594,9 +594,6 @@
   </si>
   <si>
     <t>G_INF-ADE_1A(M) (2097010)</t>
-  </si>
-  <si>
-    <t>MISAEL MARRIAGA (60)</t>
   </si>
   <si>
     <t>(2034) GRADO EN INGENIERIA DEL SOFTWARE (MOSTOLES)</t>
@@ -3860,7 +3857,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="43" spans="1:17" ht="43.15">
+    <row r="43" spans="1:17" ht="45.75">
       <c r="A43" s="2">
         <v>2383007</v>
       </c>
@@ -5617,7 +5614,7 @@
         <v>27</v>
       </c>
       <c r="N80" t="s">
-        <v>186</v>
+        <v>111</v>
       </c>
       <c r="P80" t="s">
         <v>28</v>
@@ -5631,7 +5628,7 @@
         <v>2034001</v>
       </c>
       <c r="B81" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C81" t="s">
         <v>158</v>
@@ -5661,7 +5658,7 @@
         <v>178</v>
       </c>
       <c r="L81" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M81" t="s">
         <v>27</v>
@@ -5678,7 +5675,7 @@
         <v>2034002</v>
       </c>
       <c r="B82" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C82" t="s">
         <v>158</v>
@@ -5705,10 +5702,10 @@
         <v>42</v>
       </c>
       <c r="K82" t="s">
+        <v>188</v>
+      </c>
+      <c r="L82" t="s">
         <v>189</v>
-      </c>
-      <c r="L82" t="s">
-        <v>190</v>
       </c>
       <c r="M82" t="s">
         <v>27</v>
@@ -5728,7 +5725,7 @@
         <v>2034006</v>
       </c>
       <c r="B83" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C83" t="s">
         <v>158</v>
@@ -5755,10 +5752,10 @@
         <v>42</v>
       </c>
       <c r="K83" t="s">
+        <v>190</v>
+      </c>
+      <c r="L83" t="s">
         <v>191</v>
-      </c>
-      <c r="L83" t="s">
-        <v>192</v>
       </c>
       <c r="M83" t="s">
         <v>27</v>
@@ -5775,7 +5772,7 @@
         <v>2061001</v>
       </c>
       <c r="B84" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C84" t="s">
         <v>158</v>
@@ -5819,7 +5816,7 @@
         <v>2061002</v>
       </c>
       <c r="B85" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C85" t="s">
         <v>158</v>
@@ -5852,7 +5849,7 @@
         <v>27</v>
       </c>
       <c r="N85" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P85" t="s">
         <v>28</v>
@@ -5866,7 +5863,7 @@
         <v>2061006</v>
       </c>
       <c r="B86" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C86" t="s">
         <v>158</v>
@@ -5910,7 +5907,7 @@
         <v>2107013</v>
       </c>
       <c r="B87" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C87" t="s">
         <v>158</v>
@@ -5922,7 +5919,7 @@
         <v>21</v>
       </c>
       <c r="F87" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G87" t="s">
         <v>40</v>
@@ -5940,7 +5937,7 @@
         <v>160</v>
       </c>
       <c r="L87" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M87" t="s">
         <v>27</v>
@@ -5957,7 +5954,7 @@
         <v>2143016</v>
       </c>
       <c r="B88" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C88" t="s">
         <v>158</v>
@@ -5969,7 +5966,7 @@
         <v>21</v>
       </c>
       <c r="F88" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G88" t="s">
         <v>40</v>
@@ -5987,7 +5984,7 @@
         <v>160</v>
       </c>
       <c r="L88" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M88" t="s">
         <v>27</v>
@@ -6004,7 +6001,7 @@
         <v>2148011</v>
       </c>
       <c r="B89" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C89" t="s">
         <v>158</v>
@@ -6016,7 +6013,7 @@
         <v>21</v>
       </c>
       <c r="F89" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G89" t="s">
         <v>40</v>
@@ -6048,7 +6045,7 @@
         <v>2175020</v>
       </c>
       <c r="B90" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C90" t="s">
         <v>158</v>
@@ -6075,10 +6072,10 @@
         <v>25</v>
       </c>
       <c r="K90" t="s">
+        <v>203</v>
+      </c>
+      <c r="L90" t="s">
         <v>204</v>
-      </c>
-      <c r="L90" t="s">
-        <v>205</v>
       </c>
       <c r="M90" t="s">
         <v>27</v>
@@ -6095,7 +6092,7 @@
         <v>2285005</v>
       </c>
       <c r="B91" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C91" t="s">
         <v>158</v>
@@ -6128,7 +6125,7 @@
         <v>27</v>
       </c>
       <c r="N91" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P91" t="s">
         <v>28</v>
@@ -6142,7 +6139,7 @@
         <v>2285006</v>
       </c>
       <c r="B92" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C92" t="s">
         <v>158</v>
@@ -6169,13 +6166,13 @@
         <v>42</v>
       </c>
       <c r="K92" t="s">
+        <v>207</v>
+      </c>
+      <c r="M92" t="s">
+        <v>27</v>
+      </c>
+      <c r="N92" t="s">
         <v>208</v>
-      </c>
-      <c r="M92" t="s">
-        <v>27</v>
-      </c>
-      <c r="N92" t="s">
-        <v>209</v>
       </c>
       <c r="P92" t="s">
         <v>28</v>
@@ -6189,7 +6186,7 @@
         <v>2285007</v>
       </c>
       <c r="B93" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C93" t="s">
         <v>158</v>
@@ -6201,7 +6198,7 @@
         <v>35</v>
       </c>
       <c r="F93" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G93" t="s">
         <v>40</v>
@@ -6216,10 +6213,13 @@
         <v>42</v>
       </c>
       <c r="K93" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M93" t="s">
         <v>27</v>
+      </c>
+      <c r="N93" t="s">
+        <v>111</v>
       </c>
       <c r="P93" t="s">
         <v>28</v>
@@ -6233,7 +6233,7 @@
         <v>2286015</v>
       </c>
       <c r="B94" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C94" t="s">
         <v>158</v>
@@ -6245,7 +6245,7 @@
         <v>21</v>
       </c>
       <c r="F94" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G94" t="s">
         <v>40</v>
@@ -6277,7 +6277,7 @@
         <v>2338044</v>
       </c>
       <c r="B95" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C95" t="s">
         <v>158</v>
@@ -6321,7 +6321,7 @@
         <v>2342014</v>
       </c>
       <c r="B96" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C96" t="s">
         <v>158</v>
@@ -6333,7 +6333,7 @@
         <v>21</v>
       </c>
       <c r="F96" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G96" t="s">
         <v>40</v>
@@ -6354,7 +6354,7 @@
         <v>27</v>
       </c>
       <c r="N96" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P96" t="s">
         <v>28</v>
@@ -6368,7 +6368,7 @@
         <v>5</v>
       </c>
       <c r="B97" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C97" t="s">
         <v>158</v>
@@ -6380,7 +6380,7 @@
         <v>21</v>
       </c>
       <c r="F97" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G97" t="s">
         <v>40</v>
@@ -6395,13 +6395,13 @@
         <v>42</v>
       </c>
       <c r="K97" t="s">
+        <v>216</v>
+      </c>
+      <c r="M97" t="s">
+        <v>27</v>
+      </c>
+      <c r="N97" s="3" t="s">
         <v>217</v>
-      </c>
-      <c r="M97" t="s">
-        <v>27</v>
-      </c>
-      <c r="N97" s="3" t="s">
-        <v>218</v>
       </c>
       <c r="P97" t="s">
         <v>28</v>
@@ -6415,7 +6415,7 @@
         <v>2343027</v>
       </c>
       <c r="B98" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C98" t="s">
         <v>158</v>
@@ -6427,7 +6427,7 @@
         <v>35</v>
       </c>
       <c r="F98" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G98" t="s">
         <v>40</v>
@@ -6442,13 +6442,13 @@
         <v>25</v>
       </c>
       <c r="K98" t="s">
+        <v>220</v>
+      </c>
+      <c r="M98" t="s">
         <v>221</v>
       </c>
-      <c r="M98" t="s">
+      <c r="N98" s="3" t="s">
         <v>222</v>
-      </c>
-      <c r="N98" s="3" t="s">
-        <v>223</v>
       </c>
       <c r="P98" t="s">
         <v>28</v>
@@ -6462,7 +6462,7 @@
         <v>2343027</v>
       </c>
       <c r="B99" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C99" t="s">
         <v>158</v>
@@ -6474,7 +6474,7 @@
         <v>35</v>
       </c>
       <c r="F99" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G99" t="s">
         <v>40</v>
@@ -6489,13 +6489,13 @@
         <v>25</v>
       </c>
       <c r="K99" t="s">
+        <v>223</v>
+      </c>
+      <c r="M99" t="s">
+        <v>221</v>
+      </c>
+      <c r="N99" t="s">
         <v>224</v>
-      </c>
-      <c r="M99" t="s">
-        <v>222</v>
-      </c>
-      <c r="N99" t="s">
-        <v>225</v>
       </c>
       <c r="P99" t="s">
         <v>28</v>
@@ -6509,7 +6509,7 @@
         <v>2343027</v>
       </c>
       <c r="B100" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C100" t="s">
         <v>158</v>
@@ -6521,7 +6521,7 @@
         <v>35</v>
       </c>
       <c r="F100" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G100" t="s">
         <v>40</v>
@@ -6536,10 +6536,10 @@
         <v>25</v>
       </c>
       <c r="K100" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="M100" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="N100" s="3"/>
       <c r="P100" t="s">
@@ -6554,7 +6554,7 @@
         <v>2347001</v>
       </c>
       <c r="B101" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C101" t="s">
         <v>158</v>
@@ -6581,16 +6581,16 @@
         <v>42</v>
       </c>
       <c r="K101" t="s">
+        <v>226</v>
+      </c>
+      <c r="L101" t="s">
         <v>227</v>
       </c>
-      <c r="L101" t="s">
+      <c r="M101" t="s">
+        <v>27</v>
+      </c>
+      <c r="N101" t="s">
         <v>228</v>
-      </c>
-      <c r="M101" t="s">
-        <v>27</v>
-      </c>
-      <c r="N101" t="s">
-        <v>229</v>
       </c>
       <c r="P101" t="s">
         <v>28</v>
@@ -6604,7 +6604,7 @@
         <v>2347003</v>
       </c>
       <c r="B102" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C102" t="s">
         <v>158</v>
@@ -6634,13 +6634,13 @@
         <v>178</v>
       </c>
       <c r="L102" t="s">
+        <v>229</v>
+      </c>
+      <c r="M102" t="s">
+        <v>27</v>
+      </c>
+      <c r="N102" t="s">
         <v>230</v>
-      </c>
-      <c r="M102" t="s">
-        <v>27</v>
-      </c>
-      <c r="N102" t="s">
-        <v>231</v>
       </c>
       <c r="P102" t="s">
         <v>28</v>
@@ -6654,7 +6654,7 @@
         <v>2347005</v>
       </c>
       <c r="B103" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C103" t="s">
         <v>158</v>
@@ -6666,7 +6666,7 @@
         <v>21</v>
       </c>
       <c r="F103" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G103" t="s">
         <v>40</v>
@@ -6681,16 +6681,16 @@
         <v>42</v>
       </c>
       <c r="K103" t="s">
+        <v>232</v>
+      </c>
+      <c r="L103" t="s">
         <v>233</v>
       </c>
-      <c r="L103" t="s">
+      <c r="M103" t="s">
+        <v>27</v>
+      </c>
+      <c r="N103" s="3" t="s">
         <v>234</v>
-      </c>
-      <c r="M103" t="s">
-        <v>27</v>
-      </c>
-      <c r="N103" s="3" t="s">
-        <v>235</v>
       </c>
       <c r="P103" t="s">
         <v>28</v>
@@ -6704,7 +6704,7 @@
         <v>2347006</v>
       </c>
       <c r="B104" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C104" t="s">
         <v>158</v>
@@ -6716,7 +6716,7 @@
         <v>35</v>
       </c>
       <c r="F104" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G104" t="s">
         <v>40</v>
@@ -6731,16 +6731,16 @@
         <v>42</v>
       </c>
       <c r="K104" t="s">
+        <v>236</v>
+      </c>
+      <c r="L104" t="s">
         <v>237</v>
       </c>
-      <c r="L104" t="s">
-        <v>238</v>
-      </c>
       <c r="M104" t="s">
         <v>27</v>
       </c>
       <c r="N104" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="P104" t="s">
         <v>28</v>
@@ -6754,7 +6754,7 @@
         <v>2347007</v>
       </c>
       <c r="B105" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C105" t="s">
         <v>158</v>
@@ -6781,16 +6781,16 @@
         <v>42</v>
       </c>
       <c r="K105" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L105" t="s">
+        <v>238</v>
+      </c>
+      <c r="M105" t="s">
+        <v>27</v>
+      </c>
+      <c r="N105" s="3" t="s">
         <v>239</v>
-      </c>
-      <c r="M105" t="s">
-        <v>27</v>
-      </c>
-      <c r="N105" s="3" t="s">
-        <v>240</v>
       </c>
       <c r="P105" t="s">
         <v>28</v>
@@ -6804,7 +6804,7 @@
         <v>2347013</v>
       </c>
       <c r="B106" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C106" t="s">
         <v>158</v>
@@ -6816,7 +6816,7 @@
         <v>21</v>
       </c>
       <c r="F106" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G106" t="s">
         <v>40</v>
@@ -6831,16 +6831,16 @@
         <v>42</v>
       </c>
       <c r="K106" t="s">
+        <v>241</v>
+      </c>
+      <c r="L106" t="s">
         <v>242</v>
       </c>
-      <c r="L106" t="s">
-        <v>243</v>
-      </c>
       <c r="M106" t="s">
         <v>27</v>
       </c>
       <c r="N106" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="P106" t="s">
         <v>28</v>
@@ -6854,7 +6854,7 @@
         <v>2347014</v>
       </c>
       <c r="B107" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C107" t="s">
         <v>158</v>
@@ -6866,7 +6866,7 @@
         <v>35</v>
       </c>
       <c r="F107" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G107" t="s">
         <v>40</v>
@@ -6881,10 +6881,10 @@
         <v>42</v>
       </c>
       <c r="K107" t="s">
+        <v>244</v>
+      </c>
+      <c r="L107" t="s">
         <v>245</v>
-      </c>
-      <c r="L107" t="s">
-        <v>246</v>
       </c>
       <c r="M107" t="s">
         <v>27</v>
@@ -6901,7 +6901,7 @@
         <v>2347017</v>
       </c>
       <c r="B108" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C108" t="s">
         <v>158</v>
@@ -6913,7 +6913,7 @@
         <v>35</v>
       </c>
       <c r="F108" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G108" t="s">
         <v>23</v>
@@ -6928,16 +6928,16 @@
         <v>42</v>
       </c>
       <c r="K108" t="s">
+        <v>247</v>
+      </c>
+      <c r="L108" t="s">
         <v>248</v>
       </c>
-      <c r="L108" t="s">
+      <c r="M108" t="s">
+        <v>27</v>
+      </c>
+      <c r="N108" t="s">
         <v>249</v>
-      </c>
-      <c r="M108" t="s">
-        <v>27</v>
-      </c>
-      <c r="N108" t="s">
-        <v>250</v>
       </c>
       <c r="P108" t="s">
         <v>28</v>
@@ -6951,7 +6951,7 @@
         <v>2347030</v>
       </c>
       <c r="B109" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C109" t="s">
         <v>158</v>
@@ -6963,7 +6963,7 @@
         <v>35</v>
       </c>
       <c r="F109" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G109" t="s">
         <v>40</v>
@@ -6978,16 +6978,16 @@
         <v>42</v>
       </c>
       <c r="K109" t="s">
+        <v>251</v>
+      </c>
+      <c r="L109" t="s">
         <v>252</v>
       </c>
-      <c r="L109" t="s">
-        <v>253</v>
-      </c>
       <c r="M109" t="s">
         <v>27</v>
       </c>
       <c r="N109" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P109" t="s">
         <v>28</v>
@@ -7001,7 +7001,7 @@
         <v>2347021</v>
       </c>
       <c r="B110" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C110" t="s">
         <v>158</v>
@@ -7013,7 +7013,7 @@
         <v>21</v>
       </c>
       <c r="F110" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G110" t="s">
         <v>40</v>
@@ -7028,16 +7028,16 @@
         <v>42</v>
       </c>
       <c r="K110" t="s">
+        <v>254</v>
+      </c>
+      <c r="L110" t="s">
         <v>255</v>
       </c>
-      <c r="L110" t="s">
-        <v>256</v>
-      </c>
       <c r="M110" t="s">
         <v>27</v>
       </c>
       <c r="N110" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P110" t="s">
         <v>28</v>
@@ -7051,7 +7051,7 @@
         <v>2347022</v>
       </c>
       <c r="B111" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C111" t="s">
         <v>158</v>
@@ -7063,7 +7063,7 @@
         <v>21</v>
       </c>
       <c r="F111" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G111" t="s">
         <v>40</v>
@@ -7078,16 +7078,16 @@
         <v>42</v>
       </c>
       <c r="K111" t="s">
+        <v>257</v>
+      </c>
+      <c r="L111" t="s">
         <v>258</v>
       </c>
-      <c r="L111" t="s">
+      <c r="M111" t="s">
+        <v>27</v>
+      </c>
+      <c r="N111" s="3" t="s">
         <v>259</v>
-      </c>
-      <c r="M111" t="s">
-        <v>27</v>
-      </c>
-      <c r="N111" s="3" t="s">
-        <v>260</v>
       </c>
       <c r="O111" s="1"/>
       <c r="P111" t="s">
@@ -7102,7 +7102,7 @@
         <v>2347024</v>
       </c>
       <c r="B112" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C112" t="s">
         <v>158</v>
@@ -7114,7 +7114,7 @@
         <v>21</v>
       </c>
       <c r="F112" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G112" t="s">
         <v>40</v>
@@ -7129,16 +7129,16 @@
         <v>42</v>
       </c>
       <c r="K112" t="s">
+        <v>261</v>
+      </c>
+      <c r="L112" t="s">
         <v>262</v>
       </c>
-      <c r="L112" t="s">
-        <v>263</v>
-      </c>
       <c r="M112" t="s">
         <v>27</v>
       </c>
       <c r="N112" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P112" t="s">
         <v>28</v>
@@ -7152,7 +7152,7 @@
         <v>2347026</v>
       </c>
       <c r="B113" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C113" t="s">
         <v>158</v>
@@ -7164,7 +7164,7 @@
         <v>35</v>
       </c>
       <c r="F113" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G113" t="s">
         <v>40</v>
@@ -7179,16 +7179,16 @@
         <v>42</v>
       </c>
       <c r="K113" t="s">
+        <v>264</v>
+      </c>
+      <c r="L113" t="s">
         <v>265</v>
       </c>
-      <c r="L113" t="s">
-        <v>266</v>
-      </c>
       <c r="M113" t="s">
         <v>27</v>
       </c>
       <c r="N113" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P113" t="s">
         <v>28</v>
@@ -7202,7 +7202,7 @@
         <v>2347027</v>
       </c>
       <c r="B114" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C114" t="s">
         <v>158</v>
@@ -7214,7 +7214,7 @@
         <v>35</v>
       </c>
       <c r="F114" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G114" t="s">
         <v>40</v>
@@ -7229,16 +7229,16 @@
         <v>42</v>
       </c>
       <c r="K114" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L114" t="s">
+        <v>267</v>
+      </c>
+      <c r="M114" t="s">
+        <v>27</v>
+      </c>
+      <c r="N114" s="3" t="s">
         <v>268</v>
-      </c>
-      <c r="M114" t="s">
-        <v>27</v>
-      </c>
-      <c r="N114" s="3" t="s">
-        <v>269</v>
       </c>
       <c r="P114" t="s">
         <v>28</v>
@@ -7252,7 +7252,7 @@
         <v>2347029</v>
       </c>
       <c r="B115" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C115" t="s">
         <v>158</v>
@@ -7264,7 +7264,7 @@
         <v>35</v>
       </c>
       <c r="F115" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G115" t="s">
         <v>40</v>
@@ -7279,16 +7279,16 @@
         <v>42</v>
       </c>
       <c r="K115" t="s">
+        <v>270</v>
+      </c>
+      <c r="L115" t="s">
         <v>271</v>
       </c>
-      <c r="L115" t="s">
+      <c r="M115" t="s">
+        <v>221</v>
+      </c>
+      <c r="N115" t="s">
         <v>272</v>
-      </c>
-      <c r="M115" t="s">
-        <v>222</v>
-      </c>
-      <c r="N115" t="s">
-        <v>273</v>
       </c>
       <c r="P115" t="s">
         <v>28</v>
@@ -7302,7 +7302,7 @@
         <v>2347031</v>
       </c>
       <c r="B116" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C116" t="s">
         <v>158</v>
@@ -7314,7 +7314,7 @@
         <v>21</v>
       </c>
       <c r="F116" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G116" t="s">
         <v>40</v>
@@ -7329,16 +7329,16 @@
         <v>42</v>
       </c>
       <c r="K116" t="s">
+        <v>274</v>
+      </c>
+      <c r="L116" t="s">
         <v>275</v>
       </c>
-      <c r="L116" t="s">
-        <v>276</v>
-      </c>
       <c r="M116" t="s">
         <v>27</v>
       </c>
       <c r="N116" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="P116" t="s">
         <v>28</v>
@@ -7352,7 +7352,7 @@
         <v>2347038</v>
       </c>
       <c r="B117" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C117" t="s">
         <v>158</v>
@@ -7364,10 +7364,10 @@
         <v>21</v>
       </c>
       <c r="F117" t="s">
+        <v>276</v>
+      </c>
+      <c r="G117" t="s">
         <v>277</v>
-      </c>
-      <c r="G117" t="s">
-        <v>278</v>
       </c>
       <c r="H117" s="2">
         <v>60</v>
@@ -7379,16 +7379,16 @@
         <v>42</v>
       </c>
       <c r="K117" t="s">
+        <v>278</v>
+      </c>
+      <c r="L117" t="s">
         <v>279</v>
       </c>
-      <c r="L117" t="s">
-        <v>280</v>
-      </c>
       <c r="M117" t="s">
         <v>27</v>
       </c>
       <c r="N117" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P117" t="s">
         <v>28</v>
@@ -7402,7 +7402,7 @@
         <v>2361002</v>
       </c>
       <c r="B118" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C118" t="s">
         <v>158</v>
@@ -7429,7 +7429,7 @@
         <v>42</v>
       </c>
       <c r="K118" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="M118" t="s">
         <v>27</v>
@@ -7446,7 +7446,7 @@
         <v>2361002</v>
       </c>
       <c r="B119" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C119" t="s">
         <v>158</v>
@@ -7473,7 +7473,7 @@
         <v>42</v>
       </c>
       <c r="K119" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="M119" t="s">
         <v>27</v>
@@ -7490,7 +7490,7 @@
         <v>2361002</v>
       </c>
       <c r="B120" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C120" t="s">
         <v>158</v>
@@ -7517,7 +7517,7 @@
         <v>42</v>
       </c>
       <c r="K120" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="M120" t="s">
         <v>27</v>
@@ -7534,7 +7534,7 @@
         <v>2361004</v>
       </c>
       <c r="B121" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C121" t="s">
         <v>158</v>
@@ -7561,7 +7561,7 @@
         <v>42</v>
       </c>
       <c r="K121" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="M121" t="s">
         <v>27</v>
@@ -7578,7 +7578,7 @@
         <v>2393002</v>
       </c>
       <c r="B122" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C122" t="s">
         <v>158</v>
@@ -7605,10 +7605,10 @@
         <v>42</v>
       </c>
       <c r="K122" t="s">
+        <v>285</v>
+      </c>
+      <c r="L122" t="s">
         <v>286</v>
-      </c>
-      <c r="L122" t="s">
-        <v>287</v>
       </c>
       <c r="M122" t="s">
         <v>27</v>
@@ -7625,7 +7625,7 @@
         <v>2393002</v>
       </c>
       <c r="B123" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C123" t="s">
         <v>158</v>
@@ -7646,16 +7646,16 @@
         <v>20</v>
       </c>
       <c r="I123" t="s">
+        <v>287</v>
+      </c>
+      <c r="J123" t="s">
+        <v>42</v>
+      </c>
+      <c r="K123" t="s">
         <v>288</v>
       </c>
-      <c r="J123" t="s">
-        <v>42</v>
-      </c>
-      <c r="K123" t="s">
+      <c r="L123" t="s">
         <v>289</v>
-      </c>
-      <c r="L123" t="s">
-        <v>290</v>
       </c>
       <c r="M123" t="s">
         <v>27</v>
@@ -7672,7 +7672,7 @@
         <v>2393002</v>
       </c>
       <c r="B124" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C124" t="s">
         <v>158</v>
@@ -7693,16 +7693,16 @@
         <v>20</v>
       </c>
       <c r="I124" t="s">
+        <v>290</v>
+      </c>
+      <c r="J124" t="s">
+        <v>42</v>
+      </c>
+      <c r="K124" t="s">
         <v>291</v>
       </c>
-      <c r="J124" t="s">
-        <v>42</v>
-      </c>
-      <c r="K124" t="s">
-        <v>292</v>
-      </c>
       <c r="L124" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="M124" t="s">
         <v>27</v>
@@ -7719,7 +7719,7 @@
         <v>2394004</v>
       </c>
       <c r="B125" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C125" t="s">
         <v>158</v>
@@ -7746,10 +7746,10 @@
         <v>25</v>
       </c>
       <c r="K125" t="s">
+        <v>293</v>
+      </c>
+      <c r="L125" t="s">
         <v>294</v>
-      </c>
-      <c r="L125" t="s">
-        <v>295</v>
       </c>
       <c r="M125" t="s">
         <v>27</v>
@@ -7766,7 +7766,7 @@
         <v>2394004</v>
       </c>
       <c r="B126" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C126" t="s">
         <v>158</v>
@@ -7793,10 +7793,10 @@
         <v>25</v>
       </c>
       <c r="K126" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="L126" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="M126" t="s">
         <v>27</v>
@@ -7813,7 +7813,7 @@
         <v>2394004</v>
       </c>
       <c r="B127" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C127" t="s">
         <v>158</v>
@@ -7840,10 +7840,10 @@
         <v>25</v>
       </c>
       <c r="K127" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="L127" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="M127" t="s">
         <v>27</v>
@@ -7860,7 +7860,7 @@
         <v>2395003</v>
       </c>
       <c r="B128" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C128" t="s">
         <v>158</v>
@@ -7887,10 +7887,10 @@
         <v>42</v>
       </c>
       <c r="K128" t="s">
+        <v>298</v>
+      </c>
+      <c r="L128" t="s">
         <v>299</v>
-      </c>
-      <c r="L128" t="s">
-        <v>300</v>
       </c>
       <c r="M128" t="s">
         <v>27</v>
@@ -7907,7 +7907,7 @@
         <v>2395003</v>
       </c>
       <c r="B129" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C129" t="s">
         <v>158</v>
@@ -7934,10 +7934,10 @@
         <v>42</v>
       </c>
       <c r="K129" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L129" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="M129" t="s">
         <v>27</v>
@@ -7954,7 +7954,7 @@
         <v>2395003</v>
       </c>
       <c r="B130" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C130" t="s">
         <v>158</v>
@@ -7981,10 +7981,10 @@
         <v>42</v>
       </c>
       <c r="K130" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L130" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="M130" t="s">
         <v>27</v>
@@ -8001,7 +8001,7 @@
         <v>2396001</v>
       </c>
       <c r="B131" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C131" t="s">
         <v>158</v>
@@ -8028,10 +8028,10 @@
         <v>25</v>
       </c>
       <c r="K131" t="s">
+        <v>303</v>
+      </c>
+      <c r="L131" t="s">
         <v>304</v>
-      </c>
-      <c r="L131" t="s">
-        <v>305</v>
       </c>
       <c r="M131" t="s">
         <v>27</v>
@@ -8048,7 +8048,7 @@
         <v>2396001</v>
       </c>
       <c r="B132" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C132" t="s">
         <v>158</v>
@@ -8075,10 +8075,10 @@
         <v>25</v>
       </c>
       <c r="K132" t="s">
+        <v>305</v>
+      </c>
+      <c r="L132" t="s">
         <v>306</v>
-      </c>
-      <c r="L132" t="s">
-        <v>307</v>
       </c>
       <c r="M132" t="s">
         <v>27</v>
@@ -8095,7 +8095,7 @@
         <v>2396001</v>
       </c>
       <c r="B133" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C133" t="s">
         <v>158</v>
@@ -8122,10 +8122,10 @@
         <v>25</v>
       </c>
       <c r="K133" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L133" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="M133" t="s">
         <v>27</v>
@@ -8142,7 +8142,7 @@
         <v>2397003</v>
       </c>
       <c r="B134" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C134" t="s">
         <v>158</v>
@@ -8169,16 +8169,16 @@
         <v>25</v>
       </c>
       <c r="K134" t="s">
+        <v>309</v>
+      </c>
+      <c r="L134" t="s">
         <v>310</v>
       </c>
-      <c r="L134" t="s">
+      <c r="M134" t="s">
+        <v>27</v>
+      </c>
+      <c r="N134" t="s">
         <v>311</v>
-      </c>
-      <c r="M134" t="s">
-        <v>27</v>
-      </c>
-      <c r="N134" t="s">
-        <v>312</v>
       </c>
       <c r="P134" t="s">
         <v>28</v>
@@ -8192,7 +8192,7 @@
         <v>2397003</v>
       </c>
       <c r="B135" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C135" t="s">
         <v>158</v>
@@ -8219,16 +8219,16 @@
         <v>25</v>
       </c>
       <c r="K135" t="s">
+        <v>312</v>
+      </c>
+      <c r="L135" t="s">
         <v>313</v>
       </c>
-      <c r="L135" t="s">
+      <c r="M135" t="s">
+        <v>27</v>
+      </c>
+      <c r="N135" t="s">
         <v>314</v>
-      </c>
-      <c r="M135" t="s">
-        <v>27</v>
-      </c>
-      <c r="N135" t="s">
-        <v>315</v>
       </c>
       <c r="P135" t="s">
         <v>28</v>
@@ -8242,7 +8242,7 @@
         <v>2397003</v>
       </c>
       <c r="B136" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C136" t="s">
         <v>158</v>
@@ -8269,16 +8269,16 @@
         <v>25</v>
       </c>
       <c r="K136" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="L136" t="s">
+        <v>313</v>
+      </c>
+      <c r="M136" t="s">
+        <v>27</v>
+      </c>
+      <c r="N136" t="s">
         <v>314</v>
-      </c>
-      <c r="M136" t="s">
-        <v>27</v>
-      </c>
-      <c r="N136" t="s">
-        <v>315</v>
       </c>
       <c r="P136" t="s">
         <v>28</v>
@@ -8292,7 +8292,7 @@
         <v>2397008</v>
       </c>
       <c r="B137" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C137" t="s">
         <v>158</v>
@@ -8319,10 +8319,10 @@
         <v>25</v>
       </c>
       <c r="K137" t="s">
+        <v>316</v>
+      </c>
+      <c r="L137" t="s">
         <v>317</v>
-      </c>
-      <c r="L137" t="s">
-        <v>318</v>
       </c>
       <c r="M137" t="s">
         <v>27</v>
@@ -8339,7 +8339,7 @@
         <v>2397008</v>
       </c>
       <c r="B138" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C138" t="s">
         <v>158</v>
@@ -8366,10 +8366,10 @@
         <v>25</v>
       </c>
       <c r="K138" t="s">
+        <v>318</v>
+      </c>
+      <c r="L138" t="s">
         <v>319</v>
-      </c>
-      <c r="L138" t="s">
-        <v>320</v>
       </c>
       <c r="M138" t="s">
         <v>27</v>
@@ -8386,7 +8386,7 @@
         <v>2397008</v>
       </c>
       <c r="B139" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C139" t="s">
         <v>158</v>
@@ -8413,10 +8413,10 @@
         <v>25</v>
       </c>
       <c r="K139" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="L139" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="M139" t="s">
         <v>27</v>
@@ -8433,7 +8433,7 @@
         <v>2398001</v>
       </c>
       <c r="B140" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C140" t="s">
         <v>158</v>
@@ -8460,16 +8460,16 @@
         <v>42</v>
       </c>
       <c r="K140" t="s">
+        <v>322</v>
+      </c>
+      <c r="L140" t="s">
         <v>323</v>
       </c>
-      <c r="L140" t="s">
+      <c r="M140" t="s">
+        <v>27</v>
+      </c>
+      <c r="N140" t="s">
         <v>324</v>
-      </c>
-      <c r="M140" t="s">
-        <v>27</v>
-      </c>
-      <c r="N140" t="s">
-        <v>325</v>
       </c>
       <c r="P140" t="s">
         <v>28</v>
@@ -8483,7 +8483,7 @@
         <v>2398001</v>
       </c>
       <c r="B141" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C141" t="s">
         <v>158</v>
@@ -8510,16 +8510,16 @@
         <v>42</v>
       </c>
       <c r="K141" t="s">
+        <v>325</v>
+      </c>
+      <c r="L141" t="s">
+        <v>323</v>
+      </c>
+      <c r="M141" t="s">
+        <v>27</v>
+      </c>
+      <c r="N141" s="4" t="s">
         <v>326</v>
-      </c>
-      <c r="L141" t="s">
-        <v>324</v>
-      </c>
-      <c r="M141" t="s">
-        <v>27</v>
-      </c>
-      <c r="N141" s="4" t="s">
-        <v>327</v>
       </c>
       <c r="P141" t="s">
         <v>28</v>
@@ -8533,7 +8533,7 @@
         <v>2398001</v>
       </c>
       <c r="B142" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C142" t="s">
         <v>158</v>
@@ -8560,16 +8560,16 @@
         <v>42</v>
       </c>
       <c r="K142" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="L142" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="M142" t="s">
         <v>27</v>
       </c>
       <c r="N142" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="P142" t="s">
         <v>28</v>
@@ -8583,7 +8583,7 @@
         <v>2398006</v>
       </c>
       <c r="B143" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C143" t="s">
         <v>158</v>
@@ -8610,10 +8610,10 @@
         <v>42</v>
       </c>
       <c r="K143" t="s">
+        <v>328</v>
+      </c>
+      <c r="L143" t="s">
         <v>329</v>
-      </c>
-      <c r="L143" t="s">
-        <v>330</v>
       </c>
       <c r="M143" t="s">
         <v>27</v>
@@ -8630,7 +8630,7 @@
         <v>2398006</v>
       </c>
       <c r="B144" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C144" t="s">
         <v>158</v>
@@ -8657,10 +8657,10 @@
         <v>42</v>
       </c>
       <c r="K144" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="L144" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="M144" t="s">
         <v>27</v>
@@ -8677,7 +8677,7 @@
         <v>2398006</v>
       </c>
       <c r="B145" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C145" t="s">
         <v>158</v>
@@ -8704,10 +8704,10 @@
         <v>42</v>
       </c>
       <c r="K145" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="L145" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="M145" t="s">
         <v>27</v>
@@ -8724,7 +8724,7 @@
         <v>2398013</v>
       </c>
       <c r="B146" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C146" t="s">
         <v>158</v>
@@ -8736,7 +8736,7 @@
         <v>21</v>
       </c>
       <c r="F146" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G146" t="s">
         <v>23</v>
@@ -8751,10 +8751,10 @@
         <v>25</v>
       </c>
       <c r="K146" t="s">
+        <v>332</v>
+      </c>
+      <c r="L146" t="s">
         <v>333</v>
-      </c>
-      <c r="L146" t="s">
-        <v>334</v>
       </c>
       <c r="M146" t="s">
         <v>27</v>
@@ -8771,7 +8771,7 @@
         <v>2398013</v>
       </c>
       <c r="B147" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C147" t="s">
         <v>158</v>
@@ -8783,7 +8783,7 @@
         <v>21</v>
       </c>
       <c r="F147" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G147" t="s">
         <v>23</v>
@@ -8798,10 +8798,10 @@
         <v>25</v>
       </c>
       <c r="K147" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="L147" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="M147" t="s">
         <v>27</v>
@@ -8818,7 +8818,7 @@
         <v>2398013</v>
       </c>
       <c r="B148" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C148" t="s">
         <v>158</v>
@@ -8830,7 +8830,7 @@
         <v>21</v>
       </c>
       <c r="F148" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G148" t="s">
         <v>23</v>
@@ -8845,7 +8845,7 @@
         <v>25</v>
       </c>
       <c r="K148" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="M148" t="s">
         <v>27</v>
@@ -8862,7 +8862,7 @@
         <v>2399003</v>
       </c>
       <c r="B149" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C149" t="s">
         <v>158</v>
@@ -8889,10 +8889,10 @@
         <v>42</v>
       </c>
       <c r="K149" t="s">
+        <v>337</v>
+      </c>
+      <c r="L149" t="s">
         <v>338</v>
-      </c>
-      <c r="L149" t="s">
-        <v>339</v>
       </c>
       <c r="M149" t="s">
         <v>27</v>
@@ -8909,7 +8909,7 @@
         <v>2399003</v>
       </c>
       <c r="B150" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C150" t="s">
         <v>158</v>
@@ -8936,10 +8936,10 @@
         <v>42</v>
       </c>
       <c r="K150" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="L150" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="M150" t="s">
         <v>27</v>
@@ -8956,7 +8956,7 @@
         <v>2399003</v>
       </c>
       <c r="B151" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C151" t="s">
         <v>158</v>
@@ -8983,10 +8983,10 @@
         <v>42</v>
       </c>
       <c r="K151" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="L151" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="M151" t="s">
         <v>27</v>
@@ -9003,7 +9003,7 @@
         <v>2399010</v>
       </c>
       <c r="B152" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C152" t="s">
         <v>158</v>
@@ -9030,10 +9030,10 @@
         <v>42</v>
       </c>
       <c r="K152" t="s">
+        <v>341</v>
+      </c>
+      <c r="L152" t="s">
         <v>342</v>
-      </c>
-      <c r="L152" t="s">
-        <v>343</v>
       </c>
       <c r="M152" t="s">
         <v>27</v>
@@ -9050,7 +9050,7 @@
         <v>2399010</v>
       </c>
       <c r="B153" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C153" t="s">
         <v>158</v>
@@ -9077,10 +9077,10 @@
         <v>42</v>
       </c>
       <c r="K153" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="L153" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M153" t="s">
         <v>27</v>
@@ -9097,7 +9097,7 @@
         <v>2399010</v>
       </c>
       <c r="B154" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C154" t="s">
         <v>158</v>
@@ -9124,10 +9124,10 @@
         <v>42</v>
       </c>
       <c r="K154" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="L154" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="M154" t="s">
         <v>27</v>
@@ -9144,7 +9144,7 @@
         <v>2399014</v>
       </c>
       <c r="B155" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C155" t="s">
         <v>158</v>
@@ -9171,10 +9171,10 @@
         <v>25</v>
       </c>
       <c r="K155" t="s">
+        <v>345</v>
+      </c>
+      <c r="L155" t="s">
         <v>346</v>
-      </c>
-      <c r="L155" t="s">
-        <v>347</v>
       </c>
       <c r="M155" t="s">
         <v>27</v>
@@ -9191,7 +9191,7 @@
         <v>2399014</v>
       </c>
       <c r="B156" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C156" t="s">
         <v>158</v>
@@ -9218,10 +9218,10 @@
         <v>25</v>
       </c>
       <c r="K156" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L156" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="M156" t="s">
         <v>27</v>
@@ -9238,7 +9238,7 @@
         <v>2399014</v>
       </c>
       <c r="B157" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C157" t="s">
         <v>158</v>
@@ -9265,7 +9265,7 @@
         <v>25</v>
       </c>
       <c r="K157" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="M157" t="s">
         <v>27</v>
@@ -9282,7 +9282,7 @@
         <v>2400003</v>
       </c>
       <c r="B158" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C158" t="s">
         <v>158</v>
@@ -9309,16 +9309,16 @@
         <v>42</v>
       </c>
       <c r="K158" t="s">
+        <v>350</v>
+      </c>
+      <c r="L158" t="s">
         <v>351</v>
       </c>
-      <c r="L158" t="s">
+      <c r="M158" t="s">
+        <v>27</v>
+      </c>
+      <c r="N158" t="s">
         <v>352</v>
-      </c>
-      <c r="M158" t="s">
-        <v>27</v>
-      </c>
-      <c r="N158" t="s">
-        <v>353</v>
       </c>
       <c r="P158" t="s">
         <v>28</v>
@@ -9332,7 +9332,7 @@
         <v>2400003</v>
       </c>
       <c r="B159" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C159" t="s">
         <v>158</v>
@@ -9359,16 +9359,16 @@
         <v>42</v>
       </c>
       <c r="K159" t="s">
+        <v>353</v>
+      </c>
+      <c r="L159" t="s">
+        <v>351</v>
+      </c>
+      <c r="M159" t="s">
+        <v>27</v>
+      </c>
+      <c r="N159" t="s">
         <v>354</v>
-      </c>
-      <c r="L159" t="s">
-        <v>352</v>
-      </c>
-      <c r="M159" t="s">
-        <v>27</v>
-      </c>
-      <c r="N159" t="s">
-        <v>355</v>
       </c>
       <c r="P159" t="s">
         <v>28</v>
@@ -9382,7 +9382,7 @@
         <v>2400003</v>
       </c>
       <c r="B160" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C160" t="s">
         <v>158</v>
@@ -9409,16 +9409,16 @@
         <v>42</v>
       </c>
       <c r="K160" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="L160" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="M160" t="s">
         <v>27</v>
       </c>
       <c r="N160" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="P160" t="s">
         <v>28</v>
@@ -9432,7 +9432,7 @@
         <v>2400008</v>
       </c>
       <c r="B161" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C161" t="s">
         <v>158</v>
@@ -9459,10 +9459,10 @@
         <v>42</v>
       </c>
       <c r="K161" t="s">
+        <v>356</v>
+      </c>
+      <c r="L161" t="s">
         <v>357</v>
-      </c>
-      <c r="L161" t="s">
-        <v>358</v>
       </c>
       <c r="M161" t="s">
         <v>27</v>
@@ -9479,7 +9479,7 @@
         <v>2400008</v>
       </c>
       <c r="B162" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C162" t="s">
         <v>158</v>
@@ -9506,10 +9506,10 @@
         <v>42</v>
       </c>
       <c r="K162" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="L162" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="M162" t="s">
         <v>27</v>
@@ -9526,7 +9526,7 @@
         <v>2400008</v>
       </c>
       <c r="B163" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C163" t="s">
         <v>158</v>
@@ -9553,10 +9553,10 @@
         <v>42</v>
       </c>
       <c r="K163" t="s">
+        <v>359</v>
+      </c>
+      <c r="L163" t="s">
         <v>360</v>
-      </c>
-      <c r="L163" t="s">
-        <v>361</v>
       </c>
       <c r="M163" t="s">
         <v>27</v>
@@ -9573,7 +9573,7 @@
         <v>2400012</v>
       </c>
       <c r="B164" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C164" t="s">
         <v>158</v>
@@ -9585,7 +9585,7 @@
         <v>21</v>
       </c>
       <c r="F164" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G164" t="s">
         <v>23</v>
@@ -9600,16 +9600,16 @@
         <v>25</v>
       </c>
       <c r="K164" t="s">
+        <v>361</v>
+      </c>
+      <c r="L164" t="s">
         <v>362</v>
       </c>
-      <c r="L164" t="s">
+      <c r="M164" t="s">
+        <v>27</v>
+      </c>
+      <c r="N164" t="s">
         <v>363</v>
-      </c>
-      <c r="M164" t="s">
-        <v>27</v>
-      </c>
-      <c r="N164" t="s">
-        <v>364</v>
       </c>
       <c r="P164" t="s">
         <v>28</v>
@@ -9623,7 +9623,7 @@
         <v>2400012</v>
       </c>
       <c r="B165" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C165" t="s">
         <v>158</v>
@@ -9635,7 +9635,7 @@
         <v>21</v>
       </c>
       <c r="F165" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G165" t="s">
         <v>23</v>
@@ -9650,16 +9650,16 @@
         <v>25</v>
       </c>
       <c r="K165" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="L165" t="s">
+        <v>362</v>
+      </c>
+      <c r="M165" t="s">
+        <v>27</v>
+      </c>
+      <c r="N165" t="s">
         <v>365</v>
-      </c>
-      <c r="L165" t="s">
-        <v>363</v>
-      </c>
-      <c r="M165" t="s">
-        <v>27</v>
-      </c>
-      <c r="N165" t="s">
-        <v>366</v>
       </c>
       <c r="P165" t="s">
         <v>28</v>
@@ -9673,7 +9673,7 @@
         <v>2400012</v>
       </c>
       <c r="B166" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C166" t="s">
         <v>158</v>
@@ -9685,7 +9685,7 @@
         <v>21</v>
       </c>
       <c r="F166" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G166" t="s">
         <v>23</v>
@@ -9700,13 +9700,13 @@
         <v>25</v>
       </c>
       <c r="K166" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="M166" t="s">
         <v>27</v>
       </c>
       <c r="N166" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="P166" t="s">
         <v>28</v>
@@ -9720,7 +9720,7 @@
         <v>2401001</v>
       </c>
       <c r="B167" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C167" t="s">
         <v>158</v>
@@ -9747,10 +9747,10 @@
         <v>25</v>
       </c>
       <c r="K167" t="s">
+        <v>368</v>
+      </c>
+      <c r="L167" t="s">
         <v>369</v>
-      </c>
-      <c r="L167" t="s">
-        <v>370</v>
       </c>
       <c r="M167" t="s">
         <v>27</v>
@@ -9767,7 +9767,7 @@
         <v>2401001</v>
       </c>
       <c r="B168" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C168" t="s">
         <v>158</v>
@@ -9794,10 +9794,10 @@
         <v>25</v>
       </c>
       <c r="K168" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="L168" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M168" t="s">
         <v>27</v>
@@ -9814,7 +9814,7 @@
         <v>2401001</v>
       </c>
       <c r="B169" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C169" t="s">
         <v>158</v>
@@ -9841,10 +9841,10 @@
         <v>25</v>
       </c>
       <c r="K169" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="L169" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M169" t="s">
         <v>27</v>
@@ -9861,7 +9861,7 @@
         <v>2401007</v>
       </c>
       <c r="B170" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C170" t="s">
         <v>158</v>
@@ -9888,10 +9888,10 @@
         <v>25</v>
       </c>
       <c r="K170" t="s">
+        <v>372</v>
+      </c>
+      <c r="L170" t="s">
         <v>373</v>
-      </c>
-      <c r="L170" t="s">
-        <v>374</v>
       </c>
       <c r="M170" t="s">
         <v>27</v>
@@ -9908,7 +9908,7 @@
         <v>2401007</v>
       </c>
       <c r="B171" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C171" t="s">
         <v>158</v>
@@ -9935,10 +9935,10 @@
         <v>25</v>
       </c>
       <c r="K171" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="L171" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="M171" t="s">
         <v>27</v>
@@ -9955,7 +9955,7 @@
         <v>2401007</v>
       </c>
       <c r="B172" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C172" t="s">
         <v>158</v>
@@ -9982,10 +9982,10 @@
         <v>25</v>
       </c>
       <c r="K172" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L172" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="M172" t="s">
         <v>27</v>
@@ -10002,7 +10002,7 @@
         <v>2401013</v>
       </c>
       <c r="B173" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C173" t="s">
         <v>158</v>
@@ -10014,7 +10014,7 @@
         <v>21</v>
       </c>
       <c r="F173" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G173" t="s">
         <v>40</v>
@@ -10029,16 +10029,16 @@
         <v>42</v>
       </c>
       <c r="K173" t="s">
+        <v>377</v>
+      </c>
+      <c r="L173" t="s">
         <v>378</v>
       </c>
-      <c r="L173" t="s">
+      <c r="M173" t="s">
+        <v>27</v>
+      </c>
+      <c r="N173" t="s">
         <v>379</v>
-      </c>
-      <c r="M173" t="s">
-        <v>27</v>
-      </c>
-      <c r="N173" t="s">
-        <v>380</v>
       </c>
       <c r="P173" t="s">
         <v>28</v>
@@ -10052,7 +10052,7 @@
         <v>2401013</v>
       </c>
       <c r="B174" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C174" t="s">
         <v>158</v>
@@ -10064,7 +10064,7 @@
         <v>21</v>
       </c>
       <c r="F174" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G174" t="s">
         <v>40</v>
@@ -10079,16 +10079,16 @@
         <v>42</v>
       </c>
       <c r="K174" t="s">
+        <v>380</v>
+      </c>
+      <c r="L174" t="s">
+        <v>378</v>
+      </c>
+      <c r="M174" t="s">
+        <v>27</v>
+      </c>
+      <c r="N174" t="s">
         <v>381</v>
-      </c>
-      <c r="L174" t="s">
-        <v>379</v>
-      </c>
-      <c r="M174" t="s">
-        <v>27</v>
-      </c>
-      <c r="N174" t="s">
-        <v>382</v>
       </c>
       <c r="P174" t="s">
         <v>28</v>
@@ -10102,7 +10102,7 @@
         <v>2401013</v>
       </c>
       <c r="B175" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C175" t="s">
         <v>158</v>
@@ -10114,7 +10114,7 @@
         <v>21</v>
       </c>
       <c r="F175" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G175" t="s">
         <v>40</v>
@@ -10129,16 +10129,16 @@
         <v>42</v>
       </c>
       <c r="K175" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="L175" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="M175" t="s">
         <v>27</v>
       </c>
       <c r="N175" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P175" t="s">
         <v>28</v>
@@ -10152,7 +10152,7 @@
         <v>2401018</v>
       </c>
       <c r="B176" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C176" t="s">
         <v>158</v>
@@ -10164,7 +10164,7 @@
         <v>35</v>
       </c>
       <c r="F176" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="G176" t="s">
         <v>40</v>
@@ -10179,10 +10179,10 @@
         <v>42</v>
       </c>
       <c r="K176" t="s">
+        <v>384</v>
+      </c>
+      <c r="L176" t="s">
         <v>385</v>
-      </c>
-      <c r="L176" t="s">
-        <v>386</v>
       </c>
       <c r="M176" t="s">
         <v>27</v>
@@ -10199,7 +10199,7 @@
         <v>2401018</v>
       </c>
       <c r="B177" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C177" t="s">
         <v>158</v>
@@ -10211,7 +10211,7 @@
         <v>35</v>
       </c>
       <c r="F177" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="G177" t="s">
         <v>40</v>
@@ -10226,10 +10226,10 @@
         <v>42</v>
       </c>
       <c r="K177" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="L177" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="M177" t="s">
         <v>27</v>
@@ -10246,7 +10246,7 @@
         <v>2401018</v>
       </c>
       <c r="B178" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C178" t="s">
         <v>158</v>
@@ -10258,7 +10258,7 @@
         <v>35</v>
       </c>
       <c r="F178" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="G178" t="s">
         <v>40</v>
@@ -10267,16 +10267,16 @@
         <v>4</v>
       </c>
       <c r="I178" t="s">
+        <v>387</v>
+      </c>
+      <c r="J178" t="s">
+        <v>42</v>
+      </c>
+      <c r="K178" t="s">
         <v>388</v>
       </c>
-      <c r="J178" t="s">
-        <v>42</v>
-      </c>
-      <c r="K178" t="s">
-        <v>389</v>
-      </c>
       <c r="L178" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="M178" t="s">
         <v>27</v>
@@ -10293,7 +10293,7 @@
         <v>2401018</v>
       </c>
       <c r="B179" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C179" t="s">
         <v>158</v>
@@ -10305,7 +10305,7 @@
         <v>35</v>
       </c>
       <c r="F179" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="G179" t="s">
         <v>40</v>
@@ -10320,10 +10320,10 @@
         <v>42</v>
       </c>
       <c r="K179" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="L179" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="M179" t="s">
         <v>27</v>
@@ -10340,7 +10340,7 @@
         <v>2401018</v>
       </c>
       <c r="B180" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C180" t="s">
         <v>158</v>
@@ -10352,7 +10352,7 @@
         <v>35</v>
       </c>
       <c r="F180" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="G180" t="s">
         <v>40</v>
@@ -10361,16 +10361,16 @@
         <v>4</v>
       </c>
       <c r="I180" t="s">
+        <v>390</v>
+      </c>
+      <c r="J180" t="s">
+        <v>42</v>
+      </c>
+      <c r="K180" t="s">
         <v>391</v>
       </c>
-      <c r="J180" t="s">
-        <v>42</v>
-      </c>
-      <c r="K180" t="s">
-        <v>392</v>
-      </c>
       <c r="L180" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="M180" t="s">
         <v>27</v>
@@ -10387,7 +10387,7 @@
         <v>2401018</v>
       </c>
       <c r="B181" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C181" t="s">
         <v>158</v>
@@ -10399,7 +10399,7 @@
         <v>35</v>
       </c>
       <c r="F181" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="G181" t="s">
         <v>40</v>
@@ -10408,16 +10408,16 @@
         <v>4</v>
       </c>
       <c r="I181" t="s">
+        <v>392</v>
+      </c>
+      <c r="J181" t="s">
+        <v>42</v>
+      </c>
+      <c r="K181" t="s">
         <v>393</v>
       </c>
-      <c r="J181" t="s">
-        <v>42</v>
-      </c>
-      <c r="K181" t="s">
-        <v>394</v>
-      </c>
       <c r="L181" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="M181" t="s">
         <v>27</v>
@@ -10434,7 +10434,7 @@
         <v>2401018</v>
       </c>
       <c r="B182" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C182" t="s">
         <v>158</v>
@@ -10446,7 +10446,7 @@
         <v>35</v>
       </c>
       <c r="F182" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="G182" t="s">
         <v>40</v>
@@ -10455,16 +10455,16 @@
         <v>4</v>
       </c>
       <c r="I182" t="s">
+        <v>394</v>
+      </c>
+      <c r="J182" t="s">
+        <v>42</v>
+      </c>
+      <c r="K182" t="s">
         <v>395</v>
       </c>
-      <c r="J182" t="s">
-        <v>42</v>
-      </c>
-      <c r="K182" t="s">
-        <v>396</v>
-      </c>
       <c r="L182" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="M182" t="s">
         <v>27</v>
@@ -10481,7 +10481,7 @@
         <v>2402003</v>
       </c>
       <c r="B183" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C183" t="s">
         <v>158</v>
@@ -10508,16 +10508,16 @@
         <v>25</v>
       </c>
       <c r="K183" t="s">
+        <v>397</v>
+      </c>
+      <c r="L183" t="s">
         <v>398</v>
       </c>
-      <c r="L183" t="s">
-        <v>399</v>
-      </c>
       <c r="M183" t="s">
         <v>27</v>
       </c>
       <c r="N183" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="P183" t="s">
         <v>28</v>
@@ -10531,7 +10531,7 @@
         <v>2402003</v>
       </c>
       <c r="B184" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C184" t="s">
         <v>158</v>
@@ -10558,16 +10558,16 @@
         <v>25</v>
       </c>
       <c r="K184" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="L184" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="M184" t="s">
         <v>27</v>
       </c>
       <c r="N184" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="P184" t="s">
         <v>28</v>
@@ -10581,7 +10581,7 @@
         <v>2402003</v>
       </c>
       <c r="B185" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C185" t="s">
         <v>158</v>
@@ -10608,16 +10608,16 @@
         <v>25</v>
       </c>
       <c r="K185" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="L185" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="M185" t="s">
         <v>27</v>
       </c>
       <c r="N185" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="P185" t="s">
         <v>28</v>
@@ -10631,7 +10631,7 @@
         <v>2402008</v>
       </c>
       <c r="B186" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C186" t="s">
         <v>158</v>
@@ -10658,16 +10658,16 @@
         <v>25</v>
       </c>
       <c r="K186" t="s">
+        <v>401</v>
+      </c>
+      <c r="L186" t="s">
         <v>402</v>
       </c>
-      <c r="L186" t="s">
+      <c r="M186" t="s">
+        <v>27</v>
+      </c>
+      <c r="N186" t="s">
         <v>403</v>
-      </c>
-      <c r="M186" t="s">
-        <v>27</v>
-      </c>
-      <c r="N186" t="s">
-        <v>404</v>
       </c>
       <c r="P186" t="s">
         <v>28</v>
@@ -10681,7 +10681,7 @@
         <v>2402008</v>
       </c>
       <c r="B187" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C187" t="s">
         <v>158</v>
@@ -10708,16 +10708,16 @@
         <v>25</v>
       </c>
       <c r="K187" t="s">
+        <v>404</v>
+      </c>
+      <c r="L187" t="s">
+        <v>402</v>
+      </c>
+      <c r="M187" t="s">
+        <v>27</v>
+      </c>
+      <c r="N187" t="s">
         <v>405</v>
-      </c>
-      <c r="L187" t="s">
-        <v>403</v>
-      </c>
-      <c r="M187" t="s">
-        <v>27</v>
-      </c>
-      <c r="N187" t="s">
-        <v>406</v>
       </c>
       <c r="P187" t="s">
         <v>28</v>
@@ -10731,7 +10731,7 @@
         <v>2402008</v>
       </c>
       <c r="B188" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C188" t="s">
         <v>158</v>
@@ -10758,16 +10758,16 @@
         <v>25</v>
       </c>
       <c r="K188" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="L188" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="M188" t="s">
         <v>27</v>
       </c>
       <c r="N188" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="P188" t="s">
         <v>28</v>
@@ -10781,7 +10781,7 @@
         <v>2402015</v>
       </c>
       <c r="B189" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C189" t="s">
         <v>158</v>
@@ -10793,7 +10793,7 @@
         <v>21</v>
       </c>
       <c r="F189" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G189" t="s">
         <v>23</v>
@@ -10808,13 +10808,13 @@
         <v>42</v>
       </c>
       <c r="K189" t="s">
+        <v>407</v>
+      </c>
+      <c r="M189" t="s">
+        <v>27</v>
+      </c>
+      <c r="N189" t="s">
         <v>408</v>
-      </c>
-      <c r="M189" t="s">
-        <v>27</v>
-      </c>
-      <c r="N189" t="s">
-        <v>409</v>
       </c>
       <c r="P189" t="s">
         <v>28</v>
@@ -10828,7 +10828,7 @@
         <v>2402015</v>
       </c>
       <c r="B190" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C190" t="s">
         <v>158</v>
@@ -10840,7 +10840,7 @@
         <v>21</v>
       </c>
       <c r="F190" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G190" t="s">
         <v>23</v>
@@ -10855,13 +10855,13 @@
         <v>42</v>
       </c>
       <c r="K190" t="s">
+        <v>409</v>
+      </c>
+      <c r="M190" t="s">
+        <v>27</v>
+      </c>
+      <c r="N190" t="s">
         <v>410</v>
-      </c>
-      <c r="M190" t="s">
-        <v>27</v>
-      </c>
-      <c r="N190" t="s">
-        <v>411</v>
       </c>
       <c r="P190" t="s">
         <v>28</v>
@@ -10875,7 +10875,7 @@
         <v>2402015</v>
       </c>
       <c r="B191" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C191" t="s">
         <v>158</v>
@@ -10887,7 +10887,7 @@
         <v>21</v>
       </c>
       <c r="F191" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G191" t="s">
         <v>23</v>
@@ -10902,7 +10902,7 @@
         <v>42</v>
       </c>
       <c r="K191" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="M191" t="s">
         <v>27</v>
@@ -10920,7 +10920,7 @@
         <v>2403004</v>
       </c>
       <c r="B192" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C192" t="s">
         <v>158</v>
@@ -10947,16 +10947,16 @@
         <v>42</v>
       </c>
       <c r="K192" t="s">
+        <v>413</v>
+      </c>
+      <c r="L192" t="s">
         <v>414</v>
       </c>
-      <c r="L192" t="s">
-        <v>415</v>
-      </c>
       <c r="M192" t="s">
         <v>27</v>
       </c>
       <c r="N192" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="P192" t="s">
         <v>28</v>
@@ -10970,7 +10970,7 @@
         <v>2403004</v>
       </c>
       <c r="B193" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C193" t="s">
         <v>158</v>
@@ -10997,16 +10997,16 @@
         <v>42</v>
       </c>
       <c r="K193" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="L193" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="M193" t="s">
         <v>27</v>
       </c>
       <c r="N193" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="P193" t="s">
         <v>28</v>
@@ -11020,7 +11020,7 @@
         <v>2403004</v>
       </c>
       <c r="B194" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C194" t="s">
         <v>158</v>
@@ -11047,16 +11047,16 @@
         <v>42</v>
       </c>
       <c r="K194" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="L194" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="M194" t="s">
         <v>27</v>
       </c>
       <c r="N194" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="P194" t="s">
         <v>28</v>
@@ -11070,7 +11070,7 @@
         <v>2403009</v>
       </c>
       <c r="B195" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C195" t="s">
         <v>158</v>
@@ -11097,10 +11097,10 @@
         <v>42</v>
       </c>
       <c r="K195" t="s">
+        <v>417</v>
+      </c>
+      <c r="L195" t="s">
         <v>418</v>
-      </c>
-      <c r="L195" t="s">
-        <v>419</v>
       </c>
       <c r="M195" t="s">
         <v>27</v>
@@ -11117,7 +11117,7 @@
         <v>2403009</v>
       </c>
       <c r="B196" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C196" t="s">
         <v>158</v>
@@ -11144,10 +11144,10 @@
         <v>42</v>
       </c>
       <c r="K196" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="L196" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="M196" t="s">
         <v>27</v>
@@ -11164,7 +11164,7 @@
         <v>2403009</v>
       </c>
       <c r="B197" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C197" t="s">
         <v>158</v>
@@ -11191,10 +11191,10 @@
         <v>42</v>
       </c>
       <c r="K197" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="L197" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="M197" t="s">
         <v>27</v>
@@ -11211,7 +11211,7 @@
         <v>2403013</v>
       </c>
       <c r="B198" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C198" t="s">
         <v>158</v>
@@ -11223,7 +11223,7 @@
         <v>21</v>
       </c>
       <c r="F198" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G198" t="s">
         <v>23</v>
@@ -11238,7 +11238,7 @@
         <v>25</v>
       </c>
       <c r="K198" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="M198" t="s">
         <v>27</v>
@@ -11255,7 +11255,7 @@
         <v>2403013</v>
       </c>
       <c r="B199" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C199" t="s">
         <v>158</v>
@@ -11267,7 +11267,7 @@
         <v>21</v>
       </c>
       <c r="F199" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G199" t="s">
         <v>23</v>
@@ -11282,7 +11282,7 @@
         <v>25</v>
       </c>
       <c r="K199" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="M199" t="s">
         <v>27</v>
@@ -11299,7 +11299,7 @@
         <v>2403013</v>
       </c>
       <c r="B200" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C200" t="s">
         <v>158</v>
@@ -11311,7 +11311,7 @@
         <v>21</v>
       </c>
       <c r="F200" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G200" t="s">
         <v>23</v>
@@ -11326,7 +11326,7 @@
         <v>25</v>
       </c>
       <c r="K200" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="M200" t="s">
         <v>27</v>
@@ -11343,7 +11343,7 @@
         <v>2404001</v>
       </c>
       <c r="B201" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C201" t="s">
         <v>158</v>
@@ -11370,16 +11370,16 @@
         <v>42</v>
       </c>
       <c r="K201" t="s">
+        <v>425</v>
+      </c>
+      <c r="L201" t="s">
         <v>426</v>
       </c>
-      <c r="L201" t="s">
+      <c r="M201" t="s">
+        <v>27</v>
+      </c>
+      <c r="N201" t="s">
         <v>427</v>
-      </c>
-      <c r="M201" t="s">
-        <v>27</v>
-      </c>
-      <c r="N201" t="s">
-        <v>428</v>
       </c>
       <c r="P201" t="s">
         <v>28</v>
@@ -11393,7 +11393,7 @@
         <v>2404001</v>
       </c>
       <c r="B202" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C202" t="s">
         <v>158</v>
@@ -11420,16 +11420,16 @@
         <v>42</v>
       </c>
       <c r="K202" t="s">
+        <v>428</v>
+      </c>
+      <c r="L202" t="s">
+        <v>426</v>
+      </c>
+      <c r="M202" t="s">
+        <v>27</v>
+      </c>
+      <c r="N202" t="s">
         <v>429</v>
-      </c>
-      <c r="L202" t="s">
-        <v>427</v>
-      </c>
-      <c r="M202" t="s">
-        <v>27</v>
-      </c>
-      <c r="N202" t="s">
-        <v>430</v>
       </c>
       <c r="P202" t="s">
         <v>28</v>
@@ -11443,7 +11443,7 @@
         <v>2404001</v>
       </c>
       <c r="B203" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C203" t="s">
         <v>158</v>
@@ -11470,16 +11470,16 @@
         <v>42</v>
       </c>
       <c r="K203" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="L203" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="M203" t="s">
         <v>27</v>
       </c>
       <c r="N203" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="P203" t="s">
         <v>28</v>
@@ -11493,7 +11493,7 @@
         <v>2404006</v>
       </c>
       <c r="B204" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C204" t="s">
         <v>158</v>
@@ -11520,16 +11520,16 @@
         <v>42</v>
       </c>
       <c r="K204" t="s">
+        <v>431</v>
+      </c>
+      <c r="L204" t="s">
         <v>432</v>
       </c>
-      <c r="L204" t="s">
+      <c r="M204" t="s">
+        <v>27</v>
+      </c>
+      <c r="N204" t="s">
         <v>433</v>
-      </c>
-      <c r="M204" t="s">
-        <v>27</v>
-      </c>
-      <c r="N204" t="s">
-        <v>434</v>
       </c>
       <c r="P204" t="s">
         <v>28</v>
@@ -11543,7 +11543,7 @@
         <v>2404006</v>
       </c>
       <c r="B205" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C205" t="s">
         <v>158</v>
@@ -11570,16 +11570,16 @@
         <v>42</v>
       </c>
       <c r="K205" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="L205" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="M205" t="s">
         <v>27</v>
       </c>
       <c r="N205" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="P205" t="s">
         <v>28</v>
@@ -11593,7 +11593,7 @@
         <v>2404006</v>
       </c>
       <c r="B206" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C206" t="s">
         <v>158</v>
@@ -11620,16 +11620,16 @@
         <v>42</v>
       </c>
       <c r="K206" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="L206" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="M206" t="s">
         <v>27</v>
       </c>
       <c r="N206" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="P206" t="s">
         <v>28</v>
@@ -11643,7 +11643,7 @@
         <v>2404015</v>
       </c>
       <c r="B207" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C207" t="s">
         <v>158</v>
@@ -11655,7 +11655,7 @@
         <v>21</v>
       </c>
       <c r="F207" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G207" t="s">
         <v>40</v>
@@ -11670,13 +11670,13 @@
         <v>25</v>
       </c>
       <c r="K207" t="s">
+        <v>437</v>
+      </c>
+      <c r="M207" t="s">
+        <v>27</v>
+      </c>
+      <c r="N207" t="s">
         <v>438</v>
-      </c>
-      <c r="M207" t="s">
-        <v>27</v>
-      </c>
-      <c r="N207" t="s">
-        <v>439</v>
       </c>
       <c r="P207" t="s">
         <v>28</v>
@@ -11690,7 +11690,7 @@
         <v>2404015</v>
       </c>
       <c r="B208" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C208" t="s">
         <v>158</v>
@@ -11702,7 +11702,7 @@
         <v>21</v>
       </c>
       <c r="F208" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G208" t="s">
         <v>40</v>
@@ -11711,19 +11711,19 @@
         <v>32</v>
       </c>
       <c r="I208" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J208" t="s">
         <v>25</v>
       </c>
       <c r="K208" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="M208" t="s">
         <v>27</v>
       </c>
       <c r="N208" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P208" t="s">
         <v>28</v>
@@ -11737,7 +11737,7 @@
         <v>2404015</v>
       </c>
       <c r="B209" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C209" t="s">
         <v>158</v>
@@ -11749,7 +11749,7 @@
         <v>21</v>
       </c>
       <c r="F209" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G209" t="s">
         <v>40</v>
@@ -11758,19 +11758,19 @@
         <v>32</v>
       </c>
       <c r="I209" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="J209" t="s">
         <v>25</v>
       </c>
       <c r="K209" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="M209" t="s">
         <v>27</v>
       </c>
       <c r="N209" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="P209" t="s">
         <v>28</v>
@@ -11784,7 +11784,7 @@
         <v>2405001</v>
       </c>
       <c r="B210" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C210" t="s">
         <v>158</v>
@@ -11811,16 +11811,16 @@
         <v>42</v>
       </c>
       <c r="K210" t="s">
+        <v>444</v>
+      </c>
+      <c r="L210" t="s">
         <v>445</v>
       </c>
-      <c r="L210" t="s">
-        <v>446</v>
-      </c>
       <c r="M210" t="s">
         <v>27</v>
       </c>
       <c r="N210" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="P210" t="s">
         <v>28</v>
@@ -11834,7 +11834,7 @@
         <v>2405001</v>
       </c>
       <c r="B211" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C211" t="s">
         <v>158</v>
@@ -11861,16 +11861,16 @@
         <v>42</v>
       </c>
       <c r="K211" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="L211" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="M211" t="s">
         <v>27</v>
       </c>
       <c r="N211" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="P211" t="s">
         <v>28</v>
@@ -11884,7 +11884,7 @@
         <v>2405001</v>
       </c>
       <c r="B212" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C212" t="s">
         <v>158</v>
@@ -11911,16 +11911,16 @@
         <v>42</v>
       </c>
       <c r="K212" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="L212" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="M212" t="s">
         <v>27</v>
       </c>
       <c r="N212" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="P212" t="s">
         <v>28</v>
@@ -11934,7 +11934,7 @@
         <v>2405006</v>
       </c>
       <c r="B213" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C213" t="s">
         <v>158</v>
@@ -11961,16 +11961,16 @@
         <v>42</v>
       </c>
       <c r="K213" t="s">
+        <v>448</v>
+      </c>
+      <c r="L213" t="s">
         <v>449</v>
       </c>
-      <c r="L213" t="s">
+      <c r="M213" t="s">
+        <v>27</v>
+      </c>
+      <c r="N213" t="s">
         <v>450</v>
-      </c>
-      <c r="M213" t="s">
-        <v>27</v>
-      </c>
-      <c r="N213" t="s">
-        <v>451</v>
       </c>
       <c r="P213" t="s">
         <v>28</v>
@@ -11984,7 +11984,7 @@
         <v>2405006</v>
       </c>
       <c r="B214" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C214" t="s">
         <v>158</v>
@@ -12011,16 +12011,16 @@
         <v>42</v>
       </c>
       <c r="K214" t="s">
+        <v>451</v>
+      </c>
+      <c r="L214" t="s">
+        <v>449</v>
+      </c>
+      <c r="M214" t="s">
+        <v>27</v>
+      </c>
+      <c r="N214" t="s">
         <v>452</v>
-      </c>
-      <c r="L214" t="s">
-        <v>450</v>
-      </c>
-      <c r="M214" t="s">
-        <v>27</v>
-      </c>
-      <c r="N214" t="s">
-        <v>453</v>
       </c>
       <c r="P214" t="s">
         <v>28</v>
@@ -12034,7 +12034,7 @@
         <v>2405006</v>
       </c>
       <c r="B215" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C215" t="s">
         <v>158</v>
@@ -12061,16 +12061,16 @@
         <v>42</v>
       </c>
       <c r="K215" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="L215" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="M215" t="s">
         <v>27</v>
       </c>
       <c r="N215" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="P215" t="s">
         <v>28</v>
@@ -12084,7 +12084,7 @@
         <v>2405015</v>
       </c>
       <c r="B216" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C216" t="s">
         <v>158</v>
@@ -12096,7 +12096,7 @@
         <v>21</v>
       </c>
       <c r="F216" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G216" t="s">
         <v>23</v>
@@ -12111,16 +12111,16 @@
         <v>25</v>
       </c>
       <c r="K216" t="s">
+        <v>454</v>
+      </c>
+      <c r="L216" t="s">
         <v>455</v>
       </c>
-      <c r="L216" t="s">
+      <c r="M216" t="s">
+        <v>27</v>
+      </c>
+      <c r="N216" t="s">
         <v>456</v>
-      </c>
-      <c r="M216" t="s">
-        <v>27</v>
-      </c>
-      <c r="N216" t="s">
-        <v>457</v>
       </c>
       <c r="P216" t="s">
         <v>28</v>
@@ -12134,7 +12134,7 @@
         <v>2405015</v>
       </c>
       <c r="B217" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C217" t="s">
         <v>158</v>
@@ -12146,7 +12146,7 @@
         <v>21</v>
       </c>
       <c r="F217" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G217" t="s">
         <v>23</v>
@@ -12161,16 +12161,16 @@
         <v>25</v>
       </c>
       <c r="K217" t="s">
+        <v>457</v>
+      </c>
+      <c r="L217" t="s">
+        <v>455</v>
+      </c>
+      <c r="M217" t="s">
+        <v>27</v>
+      </c>
+      <c r="N217" t="s">
         <v>458</v>
-      </c>
-      <c r="L217" t="s">
-        <v>456</v>
-      </c>
-      <c r="M217" t="s">
-        <v>27</v>
-      </c>
-      <c r="N217" t="s">
-        <v>459</v>
       </c>
       <c r="P217" t="s">
         <v>28</v>
@@ -12184,7 +12184,7 @@
         <v>2405015</v>
       </c>
       <c r="B218" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C218" t="s">
         <v>158</v>
@@ -12196,7 +12196,7 @@
         <v>21</v>
       </c>
       <c r="F218" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G218" t="s">
         <v>23</v>
@@ -12211,13 +12211,13 @@
         <v>25</v>
       </c>
       <c r="K218" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="M218" t="s">
         <v>27</v>
       </c>
       <c r="N218" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="P218" t="s">
         <v>28</v>
@@ -12231,7 +12231,7 @@
         <v>2406004</v>
       </c>
       <c r="B219" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C219" t="s">
         <v>158</v>
@@ -12258,10 +12258,10 @@
         <v>25</v>
       </c>
       <c r="K219" t="s">
+        <v>461</v>
+      </c>
+      <c r="L219" t="s">
         <v>462</v>
-      </c>
-      <c r="L219" t="s">
-        <v>463</v>
       </c>
       <c r="M219" t="s">
         <v>27</v>
@@ -12278,7 +12278,7 @@
         <v>2406004</v>
       </c>
       <c r="B220" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C220" t="s">
         <v>158</v>
@@ -12305,10 +12305,10 @@
         <v>25</v>
       </c>
       <c r="K220" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L220" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="M220" t="s">
         <v>27</v>
@@ -12325,7 +12325,7 @@
         <v>2406004</v>
       </c>
       <c r="B221" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C221" t="s">
         <v>158</v>
@@ -12346,13 +12346,13 @@
         <v>8</v>
       </c>
       <c r="I221" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J221" t="s">
         <v>25</v>
       </c>
       <c r="L221" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="M221" t="s">
         <v>27</v>
@@ -12369,7 +12369,7 @@
         <v>2406004</v>
       </c>
       <c r="B222" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C222" t="s">
         <v>158</v>
@@ -12396,10 +12396,10 @@
         <v>25</v>
       </c>
       <c r="K222" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="L222" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="M222" t="s">
         <v>27</v>
@@ -12416,7 +12416,7 @@
         <v>2406004</v>
       </c>
       <c r="B223" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C223" t="s">
         <v>158</v>
@@ -12437,13 +12437,13 @@
         <v>8</v>
       </c>
       <c r="I223" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="J223" t="s">
         <v>25</v>
       </c>
       <c r="L223" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="M223" t="s">
         <v>27</v>
@@ -12460,7 +12460,7 @@
         <v>2406009</v>
       </c>
       <c r="B224" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C224" t="s">
         <v>158</v>
@@ -12487,10 +12487,10 @@
         <v>25</v>
       </c>
       <c r="K224" t="s">
+        <v>465</v>
+      </c>
+      <c r="L224" t="s">
         <v>466</v>
-      </c>
-      <c r="L224" t="s">
-        <v>467</v>
       </c>
       <c r="M224" t="s">
         <v>27</v>
@@ -12507,7 +12507,7 @@
         <v>2406009</v>
       </c>
       <c r="B225" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C225" t="s">
         <v>158</v>
@@ -12534,10 +12534,10 @@
         <v>25</v>
       </c>
       <c r="K225" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="L225" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="M225" t="s">
         <v>27</v>
@@ -12554,7 +12554,7 @@
         <v>2406009</v>
       </c>
       <c r="B226" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C226" t="s">
         <v>158</v>
@@ -12575,16 +12575,16 @@
         <v>8</v>
       </c>
       <c r="I226" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J226" t="s">
         <v>25</v>
       </c>
       <c r="K226" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="L226" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="M226" t="s">
         <v>27</v>
@@ -12601,7 +12601,7 @@
         <v>2406009</v>
       </c>
       <c r="B227" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C227" t="s">
         <v>158</v>
@@ -12628,10 +12628,10 @@
         <v>25</v>
       </c>
       <c r="K227" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="L227" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="M227" t="s">
         <v>27</v>
@@ -12648,7 +12648,7 @@
         <v>2406009</v>
       </c>
       <c r="B228" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C228" t="s">
         <v>158</v>
@@ -12669,16 +12669,16 @@
         <v>8</v>
       </c>
       <c r="I228" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="J228" t="s">
         <v>25</v>
       </c>
       <c r="K228" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="L228" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="M228" t="s">
         <v>27</v>
@@ -12695,7 +12695,7 @@
         <v>2406012</v>
       </c>
       <c r="B229" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C229" t="s">
         <v>158</v>
@@ -12707,7 +12707,7 @@
         <v>21</v>
       </c>
       <c r="F229" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="G229" t="s">
         <v>40</v>
@@ -12722,10 +12722,10 @@
         <v>42</v>
       </c>
       <c r="K229" t="s">
+        <v>472</v>
+      </c>
+      <c r="L229" t="s">
         <v>473</v>
-      </c>
-      <c r="L229" t="s">
-        <v>474</v>
       </c>
       <c r="M229" t="s">
         <v>27</v>
@@ -12742,7 +12742,7 @@
         <v>2406012</v>
       </c>
       <c r="B230" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C230" t="s">
         <v>158</v>
@@ -12754,7 +12754,7 @@
         <v>21</v>
       </c>
       <c r="F230" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="G230" t="s">
         <v>40</v>
@@ -12763,16 +12763,16 @@
         <v>8</v>
       </c>
       <c r="I230" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="J230" t="s">
         <v>42</v>
       </c>
       <c r="K230" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="L230" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="M230" t="s">
         <v>27</v>
@@ -12789,7 +12789,7 @@
         <v>2406012</v>
       </c>
       <c r="B231" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C231" t="s">
         <v>158</v>
@@ -12801,7 +12801,7 @@
         <v>21</v>
       </c>
       <c r="F231" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="G231" t="s">
         <v>40</v>
@@ -12810,16 +12810,16 @@
         <v>8</v>
       </c>
       <c r="I231" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="J231" t="s">
         <v>42</v>
       </c>
       <c r="K231" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="L231" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="M231" t="s">
         <v>27</v>
@@ -12836,10 +12836,10 @@
         <v>2059001</v>
       </c>
       <c r="B232" t="s">
+        <v>476</v>
+      </c>
+      <c r="C232" t="s">
         <v>477</v>
-      </c>
-      <c r="C232" t="s">
-        <v>478</v>
       </c>
       <c r="D232" s="2">
         <v>1</v>
@@ -12863,10 +12863,10 @@
         <v>42</v>
       </c>
       <c r="K232" t="s">
+        <v>478</v>
+      </c>
+      <c r="L232" t="s">
         <v>479</v>
-      </c>
-      <c r="L232" t="s">
-        <v>480</v>
       </c>
       <c r="M232" t="s">
         <v>27</v>
@@ -12883,10 +12883,10 @@
         <v>2059002</v>
       </c>
       <c r="B233" t="s">
+        <v>476</v>
+      </c>
+      <c r="C233" t="s">
         <v>477</v>
-      </c>
-      <c r="C233" t="s">
-        <v>478</v>
       </c>
       <c r="D233" s="2">
         <v>1</v>
@@ -12910,10 +12910,10 @@
         <v>42</v>
       </c>
       <c r="K233" t="s">
+        <v>480</v>
+      </c>
+      <c r="L233" t="s">
         <v>481</v>
-      </c>
-      <c r="L233" t="s">
-        <v>482</v>
       </c>
       <c r="M233" t="s">
         <v>27</v>
@@ -12930,10 +12930,10 @@
         <v>2059006</v>
       </c>
       <c r="B234" t="s">
+        <v>476</v>
+      </c>
+      <c r="C234" t="s">
         <v>477</v>
-      </c>
-      <c r="C234" t="s">
-        <v>478</v>
       </c>
       <c r="D234" s="2">
         <v>1</v>
@@ -12957,10 +12957,10 @@
         <v>42</v>
       </c>
       <c r="K234" t="s">
+        <v>482</v>
+      </c>
+      <c r="L234" t="s">
         <v>483</v>
-      </c>
-      <c r="L234" t="s">
-        <v>484</v>
       </c>
       <c r="M234" t="s">
         <v>27</v>
@@ -12977,10 +12977,10 @@
         <v>2140011</v>
       </c>
       <c r="B235" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C235" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D235" s="2">
         <v>2</v>
@@ -12989,7 +12989,7 @@
         <v>21</v>
       </c>
       <c r="F235" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G235" t="s">
         <v>40</v>
@@ -13007,7 +13007,7 @@
         <v>160</v>
       </c>
       <c r="L235" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="M235" t="s">
         <v>27</v>
@@ -13024,10 +13024,10 @@
         <v>2390004</v>
       </c>
       <c r="B236" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C236" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D236" s="2">
         <v>1</v>
@@ -13051,10 +13051,10 @@
         <v>25</v>
       </c>
       <c r="K236" t="s">
+        <v>487</v>
+      </c>
+      <c r="L236" t="s">
         <v>488</v>
-      </c>
-      <c r="L236" t="s">
-        <v>489</v>
       </c>
       <c r="M236" t="s">
         <v>27</v>
@@ -13071,10 +13071,10 @@
         <v>2390004</v>
       </c>
       <c r="B237" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C237" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D237" s="2">
         <v>1</v>
@@ -13098,10 +13098,10 @@
         <v>25</v>
       </c>
       <c r="K237" t="s">
+        <v>489</v>
+      </c>
+      <c r="L237" t="s">
         <v>490</v>
-      </c>
-      <c r="L237" t="s">
-        <v>491</v>
       </c>
       <c r="M237" t="s">
         <v>27</v>
@@ -13118,10 +13118,10 @@
         <v>2390004</v>
       </c>
       <c r="B238" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C238" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D238" s="2">
         <v>1</v>
@@ -13145,10 +13145,10 @@
         <v>25</v>
       </c>
       <c r="K238" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="L238" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="M238" t="s">
         <v>27</v>
@@ -13165,10 +13165,10 @@
         <v>2390009</v>
       </c>
       <c r="B239" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C239" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D239" s="2">
         <v>1</v>
@@ -13192,10 +13192,10 @@
         <v>25</v>
       </c>
       <c r="K239" t="s">
+        <v>492</v>
+      </c>
+      <c r="L239" t="s">
         <v>493</v>
-      </c>
-      <c r="L239" t="s">
-        <v>494</v>
       </c>
       <c r="M239" t="s">
         <v>27</v>
@@ -13212,10 +13212,10 @@
         <v>2390009</v>
       </c>
       <c r="B240" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C240" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D240" s="2">
         <v>1</v>
@@ -13239,10 +13239,10 @@
         <v>25</v>
       </c>
       <c r="K240" t="s">
+        <v>494</v>
+      </c>
+      <c r="L240" t="s">
         <v>495</v>
-      </c>
-      <c r="L240" t="s">
-        <v>496</v>
       </c>
       <c r="M240" t="s">
         <v>27</v>
@@ -13259,10 +13259,10 @@
         <v>2390009</v>
       </c>
       <c r="B241" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C241" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D241" s="2">
         <v>1</v>
@@ -13286,10 +13286,10 @@
         <v>25</v>
       </c>
       <c r="K241" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="L241" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="M241" t="s">
         <v>27</v>
@@ -13306,10 +13306,10 @@
         <v>2390013</v>
       </c>
       <c r="B242" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C242" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D242" s="2">
         <v>2</v>
@@ -13318,7 +13318,7 @@
         <v>21</v>
       </c>
       <c r="F242" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G242" t="s">
         <v>23</v>
@@ -13333,7 +13333,7 @@
         <v>42</v>
       </c>
       <c r="K242" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="M242" t="s">
         <v>27</v>
@@ -13350,10 +13350,10 @@
         <v>2390013</v>
       </c>
       <c r="B243" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C243" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D243" s="2">
         <v>2</v>
@@ -13362,7 +13362,7 @@
         <v>21</v>
       </c>
       <c r="F243" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G243" t="s">
         <v>23</v>
@@ -13377,7 +13377,7 @@
         <v>42</v>
       </c>
       <c r="K243" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="M243" t="s">
         <v>27</v>
@@ -13394,10 +13394,10 @@
         <v>2390013</v>
       </c>
       <c r="B244" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C244" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D244" s="2">
         <v>2</v>
@@ -13406,7 +13406,7 @@
         <v>21</v>
       </c>
       <c r="F244" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G244" t="s">
         <v>23</v>
@@ -13421,7 +13421,7 @@
         <v>42</v>
       </c>
       <c r="K244" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="M244" t="s">
         <v>27</v>

--- a/POD_2026-27_11-5-2026.xlsx
+++ b/POD_2026-27_11-5-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://urjc-my.sharepoint.com/personal/esther_garcia_urjc_es/Documents/Documentos/POD 2026-27/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="291" documentId="11_79C815625599F410B0C00D3910C611C600045ACD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18242A85-2A2B-4816-BF50-AEC34F59E758}"/>
+  <xr:revisionPtr revIDLastSave="292" documentId="11_79C815625599F410B0C00D3910C611C600045ACD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9A12C8E-E5EC-4D0A-8FA3-35E32CB589F9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2939" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2939" uniqueCount="501">
   <si>
     <t>POD_2026-27_11-5-2026</t>
   </si>
@@ -371,229 +371,232 @@
     <t>G_AEROBIL_EXT_1A(F) (2125006), G_AERO_EXT_I_1A(F) (2151006), G_AERO_EXT822_II_1A(F) (2339006), G_TELECO-AEROESP_EXT822_1A(F) (2332006), G_TELECO-AEROESP_1A(F) (2412008), G_TRANSP_EXT822_1A(F) (2341006), G_VEHI_EXT_I_1A(F) (2284007), G_VEHI_EXT822_1A(F) (2356007)</t>
   </si>
   <si>
+    <t>MISAEL MARRIAGA (76)</t>
+  </si>
+  <si>
+    <t>(2384) GRADO EN INGENIERÍA BIOMÉDICA (INGLÉS)(FUENLABRADA)</t>
+  </si>
+  <si>
+    <t>MATHEMATICS I</t>
+  </si>
+  <si>
+    <t>L=&gt;(17:00-19:00)[21/09/26, 28/09/26, 05/10/26, 19/10/26, 26/10/26, 09/11/26, 16/11/26, 23/11/26, 30/11/26, 14/12/26], J=&gt;(15:00-17:00)[10/09/26, 17/09/26, 01/10/26, 15/10/26, 29/10/26, 12/11/26, 26/11/26, 10/12/26], X=&gt;(11:00-13:00)[30/09/26]</t>
+  </si>
+  <si>
+    <t>G_BIOMEDBIL_EXT822_1A(F) (2374009)</t>
+  </si>
+  <si>
+    <t>ATG1P2</t>
+  </si>
+  <si>
+    <t>X=&gt;(11:00-13:00)[23/09/26, 21/10/26, 28/10/26, 16/12/26], J=&gt;(15:00-17:00)[05/11/26, 19/11/26, 03/12/26]</t>
+  </si>
+  <si>
+    <t>ATG2P2</t>
+  </si>
+  <si>
+    <t>J=&gt;(15:00-17:00)[24/09/26, 08/10/26, 22/10/26, 17/12/26], X=&gt;(11:00-13:00)[04/11/26, 18/11/26, 02/12/26]</t>
+  </si>
+  <si>
+    <t>MATHEMATICS II</t>
+  </si>
+  <si>
+    <t>J=&gt;(17:00-19:00)[10/09/26, 17/09/26, 24/09/26, 01/10/26, 08/10/26, 15/10/26, 22/10/26, 29/10/26, 05/11/26, 12/11/26, 19/11/26, 26/11/26, 03/12/26, 10/12/26, 17/12/26], V=&gt;(11:00-13:00)[11/09/26], M=&gt;(17:00-19:00)[15/09/26, 29/09/26, 13/10/26, 27/10/26, 10/11/26, 24/11/26]</t>
+  </si>
+  <si>
+    <t>G_BIOMEDBIL_EXT822_1A(F) (2374005)</t>
+  </si>
+  <si>
+    <t>M=&gt;(11:00-13:00)[22/09/26, 06/10/26, 20/10/26, 03/11/26, 17/11/26, 01/12/26, 15/12/26]</t>
+  </si>
+  <si>
+    <t>M=&gt;(17:00-19:00)[22/09/26, 06/10/26, 20/10/26, 03/11/26, 17/11/26, 01/12/26, 15/12/26]</t>
+  </si>
+  <si>
+    <t>(2385) GRADO EN INGENIERÍA BIOMÉDICA (FUENLABRADA)</t>
+  </si>
+  <si>
+    <t>V=&gt;(17:00-19:00)[11/09/26, 18/09/26, 02/10/26, 16/10/26, 30/10/26, 13/11/26, 27/11/26, 11/12/26], X=&gt;(17:00-19:00)[16/09/26, 23/09/26, 30/09/26, 07/10/26, 14/10/26, 21/10/26, 28/10/26, 04/11/26, 11/11/26, 18/11/26, 25/11/26, 09/12/26, 16/12/26], J=&gt;(11:00-13:00)[15/10/26, 26/11/26]</t>
+  </si>
+  <si>
+    <t>G_BIOMED_EXT822_1A(F) (2229007)</t>
+  </si>
+  <si>
+    <t>J=&gt;(11:00-13:00)[24/09/26, 22/10/26, 19/11/26, 17/12/26], V=&gt;(17:00-19:00)[09/10/26, 06/11/26], X=&gt;(17:00-19:00)[02/12/26]</t>
+  </si>
+  <si>
+    <t>V=&gt;(17:00-19:00)[25/09/26, 23/10/26, 20/11/26, 18/12/26], J=&gt;(11:00-13:00)[08/10/26, 05/11/26, 03/12/26]</t>
+  </si>
+  <si>
+    <t>M=&gt;(11:00-13:00)[15/09/26], X=&gt;(15:00-17:00)[16/09/26, 23/09/26, 30/09/26, 07/10/26, 14/10/26, 21/10/26, 28/10/26, 04/11/26, 11/11/26, 18/11/26, 25/11/26, 02/12/26, 09/12/26, 16/12/26], J=&gt;(11:00-13:00)[17/09/26], L=&gt;(17:00-19:00)[28/09/26, 26/10/26, 09/11/26, 23/11/26]</t>
+  </si>
+  <si>
+    <t>G_BIOMED_EXT822_1A(F) (2229002)</t>
+  </si>
+  <si>
+    <t>L=&gt;(13:00-15:00)[21/09/26, 19/10/26, 16/11/26, 14/12/26] | (17:00-19:00)[05/10/26, 30/11/26]</t>
+  </si>
+  <si>
+    <t>L=&gt;(17:00-19:00)[21/09/26, 19/10/26, 16/11/26, 14/12/26] | (13:00-15:00)[05/10/26, 30/11/26]</t>
+  </si>
+  <si>
+    <t>(2386) GRADO EN INGENIERÍA EN TECNOLOGÍAS DE TELECOMUNICACIÓN (FUENLABRADA)</t>
+  </si>
+  <si>
+    <t>L=&gt;(09:00-11:00)[21/09/26, 28/09/26, 05/10/26, 19/10/26, 26/10/26, 09/11/26, 16/11/26, 23/11/26, 30/11/26, 14/12/26, 21/12/26], J=&gt;(09:00-11:00)[10/09/26, 17/09/26, 24/09/26, 01/10/26, 08/10/26, 15/10/26, 22/10/26, 29/10/26, 05/11/26, 12/11/26, 19/11/26, 26/11/26, 03/12/26, 10/12/26, 17/12/26]</t>
+  </si>
+  <si>
+    <t>G_ISTC_EXT822_1A(F) (2040001), G_ITELEMA_EXT822_1A(F) (2041001), G_ITT_EXT822_I_1A(F) (2042001), G_TELECO-ADE_EXT_1A(F) (2377003), G_TELECO-ADE_SUSP_1A(F) (2077003)</t>
+  </si>
+  <si>
+    <t>G_ISTC_EXT822_1A(F) (2040001), G_ITELEMA_EXT822_1A(F) (2041001), G_ITT_EXT822_I_1A(F) (2042001), G_TELECO-ADE_EXT_1A(F) (2377003)</t>
+  </si>
+  <si>
+    <t>BM</t>
+  </si>
+  <si>
+    <t>M(11:00 - 13:00), J(11:00 - 13:00)</t>
+  </si>
+  <si>
+    <t>G_SAM_EXT822_1A(F) (2039001)</t>
+  </si>
+  <si>
+    <t>BMG1P2</t>
+  </si>
+  <si>
+    <t>BMG2P2</t>
+  </si>
+  <si>
+    <t>X=&gt;(09:00-11:00)[16/09/26, 23/09/26, 30/09/26, 07/10/26, 14/10/26, 21/10/26, 28/10/26, 04/11/26, 11/11/26, 18/11/26, 25/11/26, 02/12/26, 09/12/26, 16/12/26], V=&gt;(09:00-11:00)[11/09/26, 18/09/26, 25/09/26, 02/10/26, 09/10/26, 16/10/26, 23/10/26, 30/10/26, 06/11/26, 13/11/26, 20/11/26, 27/11/26, 11/12/26, 18/12/26]</t>
+  </si>
+  <si>
+    <t>G_ISTC_EXT822_1A(F) (2040002), G_ITELEMA_EXT822_1A(F) (2041002), G_ITT_EXT822_I_1A(F) (2042002), G_TELECO-ADE_EXT_1A(F) (2377004), G_TELECO-ADE_SUSP_1A(F) (2077004)</t>
+  </si>
+  <si>
+    <t>L=&gt;(11:00-13:00)[21/09/26, 28/09/26, 05/10/26, 19/10/26, 26/10/26, 09/11/26, 16/11/26, 23/11/26, 30/11/26, 14/12/26, 21/12/26], X=&gt;(11:00-13:00)[16/09/26, 23/09/26, 30/09/26, 07/10/26, 14/10/26, 21/10/26, 28/10/26, 04/11/26, 11/11/26, 18/11/26, 25/11/26, 02/12/26, 09/12/26, 16/12/26]</t>
+  </si>
+  <si>
+    <t>G_SAM_EXT822_1A(F) (2039002)</t>
+  </si>
+  <si>
+    <t>Mofdi El Anjoumi (38)</t>
+  </si>
+  <si>
+    <t>(2387) GRADO EN PAISAJISMO (FUENLABRADA)</t>
+  </si>
+  <si>
+    <t>L(11:00 - 13:00), M(11:00 - 13:00)</t>
+  </si>
+  <si>
+    <t>G_PAISAJ_EXT822_1A(F) (2376011)</t>
+  </si>
+  <si>
+    <t>M(17:00 - 19:00), J(19:00 - 21:00)</t>
+  </si>
+  <si>
+    <t>(2265) GRADO EN DISEÑO Y DESARROLLO DE VIDEOJUEGOS (MADRID-QUINTANA)</t>
+  </si>
+  <si>
+    <t>MADRID-QUINTANA</t>
+  </si>
+  <si>
+    <t>INTRODUCCION A LOS METODOS MATEMATICOS Y NUMERICOS</t>
+  </si>
+  <si>
+    <t>L(17:00 - 19:00), J(17:00 - 19:00)</t>
+  </si>
+  <si>
+    <t>CHRISTIAN VANHILLE (35)</t>
+  </si>
+  <si>
+    <t>(2029) GRADO EN INGENIERIA DE LA ENERGIA (MOSTOLES)</t>
+  </si>
+  <si>
+    <t>MOSTOLES</t>
+  </si>
+  <si>
+    <t>METODOS MATEMATICOS APLICADOS A LA INGENIERIA DE LA ENERGIA</t>
+  </si>
+  <si>
+    <t>Examen y Tutorías</t>
+  </si>
+  <si>
+    <t>G_IENERG-IORG_EXT822_I_2A(M) (2124015)</t>
+  </si>
+  <si>
+    <t>(2030) GRADO EN INGENIERIA DE MATERIALES (MOSTOLES)</t>
+  </si>
+  <si>
+    <t>METODOS MATEMATICOS APLICADOS A LA INGENIERIA DE MATERIALES</t>
+  </si>
+  <si>
+    <t>G_IMAT-IENERG_EXT822_I_2A(M) (2163018), G_IMAT-IORG_EXT822_I_2A(M) (2122012)</t>
+  </si>
+  <si>
+    <t>(2031) GRADO EN CIENCIA Y TECNOLOGIA DE LOS ALIMENTOS (MOSTOLES)</t>
+  </si>
+  <si>
+    <t>ANUAL</t>
+  </si>
+  <si>
+    <t>MATEMATICAS</t>
+  </si>
+  <si>
+    <t>(2032) GRADO EN INGENIERIA DE COMPUTADORES (MOSTOLES)</t>
+  </si>
+  <si>
+    <t>LOGICA Y MATEMATICA DISCRETA</t>
+  </si>
+  <si>
+    <t>X(11:00 - 13:00), V(11:00 - 13:00)</t>
+  </si>
+  <si>
+    <t>G_VIDEO-COMP_1A(M) (2321002)</t>
+  </si>
+  <si>
+    <t>X(13:00 - 15:00), V(11:00 - 13:00)</t>
+  </si>
+  <si>
+    <t>G_INF-COMP_1A(M) (2113006)</t>
+  </si>
+  <si>
+    <t>ANDREW PICKERING (60)</t>
+  </si>
+  <si>
+    <t>L(11:00 - 13:00), X(11:00 - 13:00)</t>
+  </si>
+  <si>
+    <t>(2033) GRADO EN INGENIERIA INFORMATICA (MOSTOLES)</t>
+  </si>
+  <si>
+    <t>LOGICA</t>
+  </si>
+  <si>
+    <t>M(11:00 - 13:00), X(13:00 - 15:00)</t>
+  </si>
+  <si>
+    <t>G_INF-ADE_1A(M) (2097002), G_INF-COMP_1A(M) (2113002)</t>
+  </si>
+  <si>
+    <t>MATEMATICA DISCRETA Y ALGEBRA</t>
+  </si>
+  <si>
+    <t>M(09:00 - 11:00), V(11:00 - 13:00)</t>
+  </si>
+  <si>
+    <t>G_INF-ADE_1A(M) (2097015), G_INF-COMP_1A(M) (2113005), G_INF-MAT_EXT_1A(M) (2117003)</t>
+  </si>
+  <si>
+    <t>ÁNGEL PÉREZ (35/70) (*hablar con quien coja la otra media sobre reparto temporal)</t>
+  </si>
+  <si>
+    <t>J(13:00 - 15:00), V(09:00 - 11:00)</t>
+  </si>
+  <si>
+    <t>G_INF-ADE_1A(M) (2097010)</t>
+  </si>
+  <si>
     <t>MISAEL MARRIAGA (60)</t>
-  </si>
-  <si>
-    <t>(2384) GRADO EN INGENIERÍA BIOMÉDICA (INGLÉS)(FUENLABRADA)</t>
-  </si>
-  <si>
-    <t>MATHEMATICS I</t>
-  </si>
-  <si>
-    <t>L=&gt;(17:00-19:00)[21/09/26, 28/09/26, 05/10/26, 19/10/26, 26/10/26, 09/11/26, 16/11/26, 23/11/26, 30/11/26, 14/12/26], J=&gt;(15:00-17:00)[10/09/26, 17/09/26, 01/10/26, 15/10/26, 29/10/26, 12/11/26, 26/11/26, 10/12/26], X=&gt;(11:00-13:00)[30/09/26]</t>
-  </si>
-  <si>
-    <t>G_BIOMEDBIL_EXT822_1A(F) (2374009)</t>
-  </si>
-  <si>
-    <t>ATG1P2</t>
-  </si>
-  <si>
-    <t>X=&gt;(11:00-13:00)[23/09/26, 21/10/26, 28/10/26, 16/12/26], J=&gt;(15:00-17:00)[05/11/26, 19/11/26, 03/12/26]</t>
-  </si>
-  <si>
-    <t>ATG2P2</t>
-  </si>
-  <si>
-    <t>J=&gt;(15:00-17:00)[24/09/26, 08/10/26, 22/10/26, 17/12/26], X=&gt;(11:00-13:00)[04/11/26, 18/11/26, 02/12/26]</t>
-  </si>
-  <si>
-    <t>MATHEMATICS II</t>
-  </si>
-  <si>
-    <t>J=&gt;(17:00-19:00)[10/09/26, 17/09/26, 24/09/26, 01/10/26, 08/10/26, 15/10/26, 22/10/26, 29/10/26, 05/11/26, 12/11/26, 19/11/26, 26/11/26, 03/12/26, 10/12/26, 17/12/26], V=&gt;(11:00-13:00)[11/09/26], M=&gt;(17:00-19:00)[15/09/26, 29/09/26, 13/10/26, 27/10/26, 10/11/26, 24/11/26]</t>
-  </si>
-  <si>
-    <t>G_BIOMEDBIL_EXT822_1A(F) (2374005)</t>
-  </si>
-  <si>
-    <t>M=&gt;(11:00-13:00)[22/09/26, 06/10/26, 20/10/26, 03/11/26, 17/11/26, 01/12/26, 15/12/26]</t>
-  </si>
-  <si>
-    <t>M=&gt;(17:00-19:00)[22/09/26, 06/10/26, 20/10/26, 03/11/26, 17/11/26, 01/12/26, 15/12/26]</t>
-  </si>
-  <si>
-    <t>(2385) GRADO EN INGENIERÍA BIOMÉDICA (FUENLABRADA)</t>
-  </si>
-  <si>
-    <t>V=&gt;(17:00-19:00)[11/09/26, 18/09/26, 02/10/26, 16/10/26, 30/10/26, 13/11/26, 27/11/26, 11/12/26], X=&gt;(17:00-19:00)[16/09/26, 23/09/26, 30/09/26, 07/10/26, 14/10/26, 21/10/26, 28/10/26, 04/11/26, 11/11/26, 18/11/26, 25/11/26, 09/12/26, 16/12/26], J=&gt;(11:00-13:00)[15/10/26, 26/11/26]</t>
-  </si>
-  <si>
-    <t>G_BIOMED_EXT822_1A(F) (2229007)</t>
-  </si>
-  <si>
-    <t>J=&gt;(11:00-13:00)[24/09/26, 22/10/26, 19/11/26, 17/12/26], V=&gt;(17:00-19:00)[09/10/26, 06/11/26], X=&gt;(17:00-19:00)[02/12/26]</t>
-  </si>
-  <si>
-    <t>V=&gt;(17:00-19:00)[25/09/26, 23/10/26, 20/11/26, 18/12/26], J=&gt;(11:00-13:00)[08/10/26, 05/11/26, 03/12/26]</t>
-  </si>
-  <si>
-    <t>M=&gt;(11:00-13:00)[15/09/26], X=&gt;(15:00-17:00)[16/09/26, 23/09/26, 30/09/26, 07/10/26, 14/10/26, 21/10/26, 28/10/26, 04/11/26, 11/11/26, 18/11/26, 25/11/26, 02/12/26, 09/12/26, 16/12/26], J=&gt;(11:00-13:00)[17/09/26], L=&gt;(17:00-19:00)[28/09/26, 26/10/26, 09/11/26, 23/11/26]</t>
-  </si>
-  <si>
-    <t>G_BIOMED_EXT822_1A(F) (2229002)</t>
-  </si>
-  <si>
-    <t>L=&gt;(13:00-15:00)[21/09/26, 19/10/26, 16/11/26, 14/12/26] | (17:00-19:00)[05/10/26, 30/11/26]</t>
-  </si>
-  <si>
-    <t>L=&gt;(17:00-19:00)[21/09/26, 19/10/26, 16/11/26, 14/12/26] | (13:00-15:00)[05/10/26, 30/11/26]</t>
-  </si>
-  <si>
-    <t>(2386) GRADO EN INGENIERÍA EN TECNOLOGÍAS DE TELECOMUNICACIÓN (FUENLABRADA)</t>
-  </si>
-  <si>
-    <t>L=&gt;(09:00-11:00)[21/09/26, 28/09/26, 05/10/26, 19/10/26, 26/10/26, 09/11/26, 16/11/26, 23/11/26, 30/11/26, 14/12/26, 21/12/26], J=&gt;(09:00-11:00)[10/09/26, 17/09/26, 24/09/26, 01/10/26, 08/10/26, 15/10/26, 22/10/26, 29/10/26, 05/11/26, 12/11/26, 19/11/26, 26/11/26, 03/12/26, 10/12/26, 17/12/26]</t>
-  </si>
-  <si>
-    <t>G_ISTC_EXT822_1A(F) (2040001), G_ITELEMA_EXT822_1A(F) (2041001), G_ITT_EXT822_I_1A(F) (2042001), G_TELECO-ADE_EXT_1A(F) (2377003), G_TELECO-ADE_SUSP_1A(F) (2077003)</t>
-  </si>
-  <si>
-    <t>G_ISTC_EXT822_1A(F) (2040001), G_ITELEMA_EXT822_1A(F) (2041001), G_ITT_EXT822_I_1A(F) (2042001), G_TELECO-ADE_EXT_1A(F) (2377003)</t>
-  </si>
-  <si>
-    <t>BM</t>
-  </si>
-  <si>
-    <t>M(11:00 - 13:00), J(11:00 - 13:00)</t>
-  </si>
-  <si>
-    <t>G_SAM_EXT822_1A(F) (2039001)</t>
-  </si>
-  <si>
-    <t>BMG1P2</t>
-  </si>
-  <si>
-    <t>BMG2P2</t>
-  </si>
-  <si>
-    <t>X=&gt;(09:00-11:00)[16/09/26, 23/09/26, 30/09/26, 07/10/26, 14/10/26, 21/10/26, 28/10/26, 04/11/26, 11/11/26, 18/11/26, 25/11/26, 02/12/26, 09/12/26, 16/12/26], V=&gt;(09:00-11:00)[11/09/26, 18/09/26, 25/09/26, 02/10/26, 09/10/26, 16/10/26, 23/10/26, 30/10/26, 06/11/26, 13/11/26, 20/11/26, 27/11/26, 11/12/26, 18/12/26]</t>
-  </si>
-  <si>
-    <t>G_ISTC_EXT822_1A(F) (2040002), G_ITELEMA_EXT822_1A(F) (2041002), G_ITT_EXT822_I_1A(F) (2042002), G_TELECO-ADE_EXT_1A(F) (2377004), G_TELECO-ADE_SUSP_1A(F) (2077004)</t>
-  </si>
-  <si>
-    <t>L=&gt;(11:00-13:00)[21/09/26, 28/09/26, 05/10/26, 19/10/26, 26/10/26, 09/11/26, 16/11/26, 23/11/26, 30/11/26, 14/12/26, 21/12/26], X=&gt;(11:00-13:00)[16/09/26, 23/09/26, 30/09/26, 07/10/26, 14/10/26, 21/10/26, 28/10/26, 04/11/26, 11/11/26, 18/11/26, 25/11/26, 02/12/26, 09/12/26, 16/12/26]</t>
-  </si>
-  <si>
-    <t>G_SAM_EXT822_1A(F) (2039002)</t>
-  </si>
-  <si>
-    <t>Mofdi El Anjoumi (38)</t>
-  </si>
-  <si>
-    <t>(2387) GRADO EN PAISAJISMO (FUENLABRADA)</t>
-  </si>
-  <si>
-    <t>L(11:00 - 13:00), M(11:00 - 13:00)</t>
-  </si>
-  <si>
-    <t>G_PAISAJ_EXT822_1A(F) (2376011)</t>
-  </si>
-  <si>
-    <t>M(17:00 - 19:00), J(19:00 - 21:00)</t>
-  </si>
-  <si>
-    <t>(2265) GRADO EN DISEÑO Y DESARROLLO DE VIDEOJUEGOS (MADRID-QUINTANA)</t>
-  </si>
-  <si>
-    <t>MADRID-QUINTANA</t>
-  </si>
-  <si>
-    <t>INTRODUCCION A LOS METODOS MATEMATICOS Y NUMERICOS</t>
-  </si>
-  <si>
-    <t>L(17:00 - 19:00), J(17:00 - 19:00)</t>
-  </si>
-  <si>
-    <t>CHRISTIAN VANHILLE (35)</t>
-  </si>
-  <si>
-    <t>(2029) GRADO EN INGENIERIA DE LA ENERGIA (MOSTOLES)</t>
-  </si>
-  <si>
-    <t>MOSTOLES</t>
-  </si>
-  <si>
-    <t>METODOS MATEMATICOS APLICADOS A LA INGENIERIA DE LA ENERGIA</t>
-  </si>
-  <si>
-    <t>Examen y Tutorías</t>
-  </si>
-  <si>
-    <t>G_IENERG-IORG_EXT822_I_2A(M) (2124015)</t>
-  </si>
-  <si>
-    <t>(2030) GRADO EN INGENIERIA DE MATERIALES (MOSTOLES)</t>
-  </si>
-  <si>
-    <t>METODOS MATEMATICOS APLICADOS A LA INGENIERIA DE MATERIALES</t>
-  </si>
-  <si>
-    <t>G_IMAT-IENERG_EXT822_I_2A(M) (2163018), G_IMAT-IORG_EXT822_I_2A(M) (2122012)</t>
-  </si>
-  <si>
-    <t>(2031) GRADO EN CIENCIA Y TECNOLOGIA DE LOS ALIMENTOS (MOSTOLES)</t>
-  </si>
-  <si>
-    <t>ANUAL</t>
-  </si>
-  <si>
-    <t>MATEMATICAS</t>
-  </si>
-  <si>
-    <t>(2032) GRADO EN INGENIERIA DE COMPUTADORES (MOSTOLES)</t>
-  </si>
-  <si>
-    <t>LOGICA Y MATEMATICA DISCRETA</t>
-  </si>
-  <si>
-    <t>X(11:00 - 13:00), V(11:00 - 13:00)</t>
-  </si>
-  <si>
-    <t>G_VIDEO-COMP_1A(M) (2321002)</t>
-  </si>
-  <si>
-    <t>X(13:00 - 15:00), V(11:00 - 13:00)</t>
-  </si>
-  <si>
-    <t>G_INF-COMP_1A(M) (2113006)</t>
-  </si>
-  <si>
-    <t>ANDREW PICKERING (60)</t>
-  </si>
-  <si>
-    <t>L(11:00 - 13:00), X(11:00 - 13:00)</t>
-  </si>
-  <si>
-    <t>(2033) GRADO EN INGENIERIA INFORMATICA (MOSTOLES)</t>
-  </si>
-  <si>
-    <t>LOGICA</t>
-  </si>
-  <si>
-    <t>M(11:00 - 13:00), X(13:00 - 15:00)</t>
-  </si>
-  <si>
-    <t>G_INF-ADE_1A(M) (2097002), G_INF-COMP_1A(M) (2113002)</t>
-  </si>
-  <si>
-    <t>MATEMATICA DISCRETA Y ALGEBRA</t>
-  </si>
-  <si>
-    <t>M(09:00 - 11:00), V(11:00 - 13:00)</t>
-  </si>
-  <si>
-    <t>G_INF-ADE_1A(M) (2097015), G_INF-COMP_1A(M) (2113005), G_INF-MAT_EXT_1A(M) (2117003)</t>
-  </si>
-  <si>
-    <t>ÁNGEL PÉREZ (35/70) (*hablar con quien coja la otra media sobre reparto temporal)</t>
-  </si>
-  <si>
-    <t>J(13:00 - 15:00), V(09:00 - 11:00)</t>
-  </si>
-  <si>
-    <t>G_INF-ADE_1A(M) (2097010)</t>
   </si>
   <si>
     <t>(2034) GRADO EN INGENIERIA DEL SOFTWARE (MOSTOLES)</t>
@@ -5614,7 +5617,7 @@
         <v>27</v>
       </c>
       <c r="N80" t="s">
-        <v>111</v>
+        <v>186</v>
       </c>
       <c r="P80" t="s">
         <v>28</v>
@@ -5628,7 +5631,7 @@
         <v>2034001</v>
       </c>
       <c r="B81" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C81" t="s">
         <v>158</v>
@@ -5658,7 +5661,7 @@
         <v>178</v>
       </c>
       <c r="L81" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M81" t="s">
         <v>27</v>
@@ -5675,7 +5678,7 @@
         <v>2034002</v>
       </c>
       <c r="B82" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C82" t="s">
         <v>158</v>
@@ -5702,10 +5705,10 @@
         <v>42</v>
       </c>
       <c r="K82" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L82" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M82" t="s">
         <v>27</v>
@@ -5725,7 +5728,7 @@
         <v>2034006</v>
       </c>
       <c r="B83" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C83" t="s">
         <v>158</v>
@@ -5752,10 +5755,10 @@
         <v>42</v>
       </c>
       <c r="K83" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L83" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M83" t="s">
         <v>27</v>
@@ -5772,7 +5775,7 @@
         <v>2061001</v>
       </c>
       <c r="B84" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C84" t="s">
         <v>158</v>
@@ -5816,7 +5819,7 @@
         <v>2061002</v>
       </c>
       <c r="B85" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C85" t="s">
         <v>158</v>
@@ -5849,7 +5852,7 @@
         <v>27</v>
       </c>
       <c r="N85" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P85" t="s">
         <v>28</v>
@@ -5863,7 +5866,7 @@
         <v>2061006</v>
       </c>
       <c r="B86" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C86" t="s">
         <v>158</v>
@@ -5907,7 +5910,7 @@
         <v>2107013</v>
       </c>
       <c r="B87" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C87" t="s">
         <v>158</v>
@@ -5919,7 +5922,7 @@
         <v>21</v>
       </c>
       <c r="F87" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G87" t="s">
         <v>40</v>
@@ -5937,7 +5940,7 @@
         <v>160</v>
       </c>
       <c r="L87" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M87" t="s">
         <v>27</v>
@@ -5954,7 +5957,7 @@
         <v>2143016</v>
       </c>
       <c r="B88" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C88" t="s">
         <v>158</v>
@@ -5966,7 +5969,7 @@
         <v>21</v>
       </c>
       <c r="F88" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G88" t="s">
         <v>40</v>
@@ -5984,7 +5987,7 @@
         <v>160</v>
       </c>
       <c r="L88" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M88" t="s">
         <v>27</v>
@@ -6001,7 +6004,7 @@
         <v>2148011</v>
       </c>
       <c r="B89" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C89" t="s">
         <v>158</v>
@@ -6013,7 +6016,7 @@
         <v>21</v>
       </c>
       <c r="F89" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G89" t="s">
         <v>40</v>
@@ -6045,7 +6048,7 @@
         <v>2175020</v>
       </c>
       <c r="B90" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C90" t="s">
         <v>158</v>
@@ -6072,10 +6075,10 @@
         <v>25</v>
       </c>
       <c r="K90" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L90" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M90" t="s">
         <v>27</v>
@@ -6092,7 +6095,7 @@
         <v>2285005</v>
       </c>
       <c r="B91" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C91" t="s">
         <v>158</v>
@@ -6125,7 +6128,7 @@
         <v>27</v>
       </c>
       <c r="N91" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P91" t="s">
         <v>28</v>
@@ -6139,7 +6142,7 @@
         <v>2285006</v>
       </c>
       <c r="B92" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C92" t="s">
         <v>158</v>
@@ -6166,13 +6169,13 @@
         <v>42</v>
       </c>
       <c r="K92" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M92" t="s">
         <v>27</v>
       </c>
       <c r="N92" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P92" t="s">
         <v>28</v>
@@ -6186,7 +6189,7 @@
         <v>2285007</v>
       </c>
       <c r="B93" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C93" t="s">
         <v>158</v>
@@ -6198,7 +6201,7 @@
         <v>35</v>
       </c>
       <c r="F93" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G93" t="s">
         <v>40</v>
@@ -6213,13 +6216,13 @@
         <v>42</v>
       </c>
       <c r="K93" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M93" t="s">
         <v>27</v>
       </c>
       <c r="N93" t="s">
-        <v>111</v>
+        <v>186</v>
       </c>
       <c r="P93" t="s">
         <v>28</v>
@@ -6233,7 +6236,7 @@
         <v>2286015</v>
       </c>
       <c r="B94" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C94" t="s">
         <v>158</v>
@@ -6245,7 +6248,7 @@
         <v>21</v>
       </c>
       <c r="F94" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G94" t="s">
         <v>40</v>
@@ -6277,7 +6280,7 @@
         <v>2338044</v>
       </c>
       <c r="B95" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C95" t="s">
         <v>158</v>
@@ -6321,7 +6324,7 @@
         <v>2342014</v>
       </c>
       <c r="B96" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C96" t="s">
         <v>158</v>
@@ -6333,7 +6336,7 @@
         <v>21</v>
       </c>
       <c r="F96" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G96" t="s">
         <v>40</v>
@@ -6354,7 +6357,7 @@
         <v>27</v>
       </c>
       <c r="N96" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P96" t="s">
         <v>28</v>
@@ -6368,7 +6371,7 @@
         <v>5</v>
       </c>
       <c r="B97" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C97" t="s">
         <v>158</v>
@@ -6380,7 +6383,7 @@
         <v>21</v>
       </c>
       <c r="F97" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G97" t="s">
         <v>40</v>
@@ -6395,13 +6398,13 @@
         <v>42</v>
       </c>
       <c r="K97" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M97" t="s">
         <v>27</v>
       </c>
       <c r="N97" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P97" t="s">
         <v>28</v>
@@ -6415,7 +6418,7 @@
         <v>2343027</v>
       </c>
       <c r="B98" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C98" t="s">
         <v>158</v>
@@ -6427,7 +6430,7 @@
         <v>35</v>
       </c>
       <c r="F98" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G98" t="s">
         <v>40</v>
@@ -6442,13 +6445,13 @@
         <v>25</v>
       </c>
       <c r="K98" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M98" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N98" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P98" t="s">
         <v>28</v>
@@ -6462,7 +6465,7 @@
         <v>2343027</v>
       </c>
       <c r="B99" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C99" t="s">
         <v>158</v>
@@ -6474,7 +6477,7 @@
         <v>35</v>
       </c>
       <c r="F99" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G99" t="s">
         <v>40</v>
@@ -6489,13 +6492,13 @@
         <v>25</v>
       </c>
       <c r="K99" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M99" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N99" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P99" t="s">
         <v>28</v>
@@ -6509,7 +6512,7 @@
         <v>2343027</v>
       </c>
       <c r="B100" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C100" t="s">
         <v>158</v>
@@ -6521,7 +6524,7 @@
         <v>35</v>
       </c>
       <c r="F100" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G100" t="s">
         <v>40</v>
@@ -6536,10 +6539,10 @@
         <v>25</v>
       </c>
       <c r="K100" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M100" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N100" s="3"/>
       <c r="P100" t="s">
@@ -6554,7 +6557,7 @@
         <v>2347001</v>
       </c>
       <c r="B101" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C101" t="s">
         <v>158</v>
@@ -6581,16 +6584,16 @@
         <v>42</v>
       </c>
       <c r="K101" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L101" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M101" t="s">
         <v>27</v>
       </c>
       <c r="N101" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P101" t="s">
         <v>28</v>
@@ -6604,7 +6607,7 @@
         <v>2347003</v>
       </c>
       <c r="B102" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C102" t="s">
         <v>158</v>
@@ -6634,13 +6637,13 @@
         <v>178</v>
       </c>
       <c r="L102" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M102" t="s">
         <v>27</v>
       </c>
       <c r="N102" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P102" t="s">
         <v>28</v>
@@ -6654,7 +6657,7 @@
         <v>2347005</v>
       </c>
       <c r="B103" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C103" t="s">
         <v>158</v>
@@ -6666,7 +6669,7 @@
         <v>21</v>
       </c>
       <c r="F103" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G103" t="s">
         <v>40</v>
@@ -6681,16 +6684,16 @@
         <v>42</v>
       </c>
       <c r="K103" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L103" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="M103" t="s">
         <v>27</v>
       </c>
       <c r="N103" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P103" t="s">
         <v>28</v>
@@ -6704,7 +6707,7 @@
         <v>2347006</v>
       </c>
       <c r="B104" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C104" t="s">
         <v>158</v>
@@ -6716,7 +6719,7 @@
         <v>35</v>
       </c>
       <c r="F104" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G104" t="s">
         <v>40</v>
@@ -6731,16 +6734,16 @@
         <v>42</v>
       </c>
       <c r="K104" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L104" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M104" t="s">
         <v>27</v>
       </c>
       <c r="N104" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P104" t="s">
         <v>28</v>
@@ -6754,7 +6757,7 @@
         <v>2347007</v>
       </c>
       <c r="B105" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C105" t="s">
         <v>158</v>
@@ -6781,16 +6784,16 @@
         <v>42</v>
       </c>
       <c r="K105" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L105" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M105" t="s">
         <v>27</v>
       </c>
       <c r="N105" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P105" t="s">
         <v>28</v>
@@ -6804,7 +6807,7 @@
         <v>2347013</v>
       </c>
       <c r="B106" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C106" t="s">
         <v>158</v>
@@ -6816,7 +6819,7 @@
         <v>21</v>
       </c>
       <c r="F106" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G106" t="s">
         <v>40</v>
@@ -6831,16 +6834,16 @@
         <v>42</v>
       </c>
       <c r="K106" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L106" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M106" t="s">
         <v>27</v>
       </c>
       <c r="N106" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P106" t="s">
         <v>28</v>
@@ -6854,7 +6857,7 @@
         <v>2347014</v>
       </c>
       <c r="B107" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C107" t="s">
         <v>158</v>
@@ -6866,7 +6869,7 @@
         <v>35</v>
       </c>
       <c r="F107" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G107" t="s">
         <v>40</v>
@@ -6881,10 +6884,10 @@
         <v>42</v>
       </c>
       <c r="K107" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L107" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M107" t="s">
         <v>27</v>
@@ -6901,7 +6904,7 @@
         <v>2347017</v>
       </c>
       <c r="B108" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C108" t="s">
         <v>158</v>
@@ -6913,7 +6916,7 @@
         <v>35</v>
       </c>
       <c r="F108" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G108" t="s">
         <v>23</v>
@@ -6928,16 +6931,16 @@
         <v>42</v>
       </c>
       <c r="K108" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L108" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M108" t="s">
         <v>27</v>
       </c>
       <c r="N108" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P108" t="s">
         <v>28</v>
@@ -6951,7 +6954,7 @@
         <v>2347030</v>
       </c>
       <c r="B109" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C109" t="s">
         <v>158</v>
@@ -6963,7 +6966,7 @@
         <v>35</v>
       </c>
       <c r="F109" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G109" t="s">
         <v>40</v>
@@ -6978,16 +6981,16 @@
         <v>42</v>
       </c>
       <c r="K109" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L109" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M109" t="s">
         <v>27</v>
       </c>
       <c r="N109" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P109" t="s">
         <v>28</v>
@@ -7001,7 +7004,7 @@
         <v>2347021</v>
       </c>
       <c r="B110" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C110" t="s">
         <v>158</v>
@@ -7013,7 +7016,7 @@
         <v>21</v>
       </c>
       <c r="F110" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G110" t="s">
         <v>40</v>
@@ -7028,16 +7031,16 @@
         <v>42</v>
       </c>
       <c r="K110" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L110" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M110" t="s">
         <v>27</v>
       </c>
       <c r="N110" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P110" t="s">
         <v>28</v>
@@ -7051,7 +7054,7 @@
         <v>2347022</v>
       </c>
       <c r="B111" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C111" t="s">
         <v>158</v>
@@ -7063,7 +7066,7 @@
         <v>21</v>
       </c>
       <c r="F111" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G111" t="s">
         <v>40</v>
@@ -7078,16 +7081,16 @@
         <v>42</v>
       </c>
       <c r="K111" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L111" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M111" t="s">
         <v>27</v>
       </c>
       <c r="N111" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O111" s="1"/>
       <c r="P111" t="s">
@@ -7102,7 +7105,7 @@
         <v>2347024</v>
       </c>
       <c r="B112" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C112" t="s">
         <v>158</v>
@@ -7114,7 +7117,7 @@
         <v>21</v>
       </c>
       <c r="F112" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G112" t="s">
         <v>40</v>
@@ -7129,16 +7132,16 @@
         <v>42</v>
       </c>
       <c r="K112" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L112" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M112" t="s">
         <v>27</v>
       </c>
       <c r="N112" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P112" t="s">
         <v>28</v>
@@ -7152,7 +7155,7 @@
         <v>2347026</v>
       </c>
       <c r="B113" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C113" t="s">
         <v>158</v>
@@ -7164,7 +7167,7 @@
         <v>35</v>
       </c>
       <c r="F113" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G113" t="s">
         <v>40</v>
@@ -7179,16 +7182,16 @@
         <v>42</v>
       </c>
       <c r="K113" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L113" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M113" t="s">
         <v>27</v>
       </c>
       <c r="N113" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P113" t="s">
         <v>28</v>
@@ -7202,7 +7205,7 @@
         <v>2347027</v>
       </c>
       <c r="B114" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C114" t="s">
         <v>158</v>
@@ -7214,7 +7217,7 @@
         <v>35</v>
       </c>
       <c r="F114" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G114" t="s">
         <v>40</v>
@@ -7229,16 +7232,16 @@
         <v>42</v>
       </c>
       <c r="K114" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L114" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M114" t="s">
         <v>27</v>
       </c>
       <c r="N114" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P114" t="s">
         <v>28</v>
@@ -7252,7 +7255,7 @@
         <v>2347029</v>
       </c>
       <c r="B115" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C115" t="s">
         <v>158</v>
@@ -7264,7 +7267,7 @@
         <v>35</v>
       </c>
       <c r="F115" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G115" t="s">
         <v>40</v>
@@ -7279,16 +7282,16 @@
         <v>42</v>
       </c>
       <c r="K115" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L115" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M115" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N115" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="P115" t="s">
         <v>28</v>
@@ -7302,7 +7305,7 @@
         <v>2347031</v>
       </c>
       <c r="B116" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C116" t="s">
         <v>158</v>
@@ -7314,7 +7317,7 @@
         <v>21</v>
       </c>
       <c r="F116" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G116" t="s">
         <v>40</v>
@@ -7329,16 +7332,16 @@
         <v>42</v>
       </c>
       <c r="K116" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L116" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M116" t="s">
         <v>27</v>
       </c>
       <c r="N116" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P116" t="s">
         <v>28</v>
@@ -7352,7 +7355,7 @@
         <v>2347038</v>
       </c>
       <c r="B117" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C117" t="s">
         <v>158</v>
@@ -7364,10 +7367,10 @@
         <v>21</v>
       </c>
       <c r="F117" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G117" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H117" s="2">
         <v>60</v>
@@ -7379,16 +7382,16 @@
         <v>42</v>
       </c>
       <c r="K117" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L117" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M117" t="s">
         <v>27</v>
       </c>
       <c r="N117" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P117" t="s">
         <v>28</v>
@@ -7402,7 +7405,7 @@
         <v>2361002</v>
       </c>
       <c r="B118" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C118" t="s">
         <v>158</v>
@@ -7429,7 +7432,7 @@
         <v>42</v>
       </c>
       <c r="K118" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M118" t="s">
         <v>27</v>
@@ -7446,7 +7449,7 @@
         <v>2361002</v>
       </c>
       <c r="B119" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C119" t="s">
         <v>158</v>
@@ -7473,7 +7476,7 @@
         <v>42</v>
       </c>
       <c r="K119" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M119" t="s">
         <v>27</v>
@@ -7490,7 +7493,7 @@
         <v>2361002</v>
       </c>
       <c r="B120" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C120" t="s">
         <v>158</v>
@@ -7517,7 +7520,7 @@
         <v>42</v>
       </c>
       <c r="K120" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M120" t="s">
         <v>27</v>
@@ -7534,7 +7537,7 @@
         <v>2361004</v>
       </c>
       <c r="B121" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C121" t="s">
         <v>158</v>
@@ -7561,7 +7564,7 @@
         <v>42</v>
       </c>
       <c r="K121" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M121" t="s">
         <v>27</v>
@@ -7578,7 +7581,7 @@
         <v>2393002</v>
       </c>
       <c r="B122" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C122" t="s">
         <v>158</v>
@@ -7605,10 +7608,10 @@
         <v>42</v>
       </c>
       <c r="K122" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L122" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M122" t="s">
         <v>27</v>
@@ -7625,7 +7628,7 @@
         <v>2393002</v>
       </c>
       <c r="B123" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C123" t="s">
         <v>158</v>
@@ -7646,16 +7649,16 @@
         <v>20</v>
       </c>
       <c r="I123" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="J123" t="s">
         <v>42</v>
       </c>
       <c r="K123" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L123" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M123" t="s">
         <v>27</v>
@@ -7672,7 +7675,7 @@
         <v>2393002</v>
       </c>
       <c r="B124" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C124" t="s">
         <v>158</v>
@@ -7693,16 +7696,16 @@
         <v>20</v>
       </c>
       <c r="I124" t="s">
+        <v>291</v>
+      </c>
+      <c r="J124" t="s">
+        <v>42</v>
+      </c>
+      <c r="K124" t="s">
+        <v>292</v>
+      </c>
+      <c r="L124" t="s">
         <v>290</v>
-      </c>
-      <c r="J124" t="s">
-        <v>42</v>
-      </c>
-      <c r="K124" t="s">
-        <v>291</v>
-      </c>
-      <c r="L124" t="s">
-        <v>289</v>
       </c>
       <c r="M124" t="s">
         <v>27</v>
@@ -7719,7 +7722,7 @@
         <v>2394004</v>
       </c>
       <c r="B125" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C125" t="s">
         <v>158</v>
@@ -7746,10 +7749,10 @@
         <v>25</v>
       </c>
       <c r="K125" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L125" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M125" t="s">
         <v>27</v>
@@ -7766,7 +7769,7 @@
         <v>2394004</v>
       </c>
       <c r="B126" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C126" t="s">
         <v>158</v>
@@ -7793,10 +7796,10 @@
         <v>25</v>
       </c>
       <c r="K126" t="s">
+        <v>296</v>
+      </c>
+      <c r="L126" t="s">
         <v>295</v>
-      </c>
-      <c r="L126" t="s">
-        <v>294</v>
       </c>
       <c r="M126" t="s">
         <v>27</v>
@@ -7813,7 +7816,7 @@
         <v>2394004</v>
       </c>
       <c r="B127" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C127" t="s">
         <v>158</v>
@@ -7840,10 +7843,10 @@
         <v>25</v>
       </c>
       <c r="K127" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L127" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M127" t="s">
         <v>27</v>
@@ -7860,7 +7863,7 @@
         <v>2395003</v>
       </c>
       <c r="B128" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C128" t="s">
         <v>158</v>
@@ -7887,10 +7890,10 @@
         <v>42</v>
       </c>
       <c r="K128" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L128" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M128" t="s">
         <v>27</v>
@@ -7907,7 +7910,7 @@
         <v>2395003</v>
       </c>
       <c r="B129" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C129" t="s">
         <v>158</v>
@@ -7934,10 +7937,10 @@
         <v>42</v>
       </c>
       <c r="K129" t="s">
+        <v>301</v>
+      </c>
+      <c r="L129" t="s">
         <v>300</v>
-      </c>
-      <c r="L129" t="s">
-        <v>299</v>
       </c>
       <c r="M129" t="s">
         <v>27</v>
@@ -7954,7 +7957,7 @@
         <v>2395003</v>
       </c>
       <c r="B130" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C130" t="s">
         <v>158</v>
@@ -7981,10 +7984,10 @@
         <v>42</v>
       </c>
       <c r="K130" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L130" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M130" t="s">
         <v>27</v>
@@ -8001,7 +8004,7 @@
         <v>2396001</v>
       </c>
       <c r="B131" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C131" t="s">
         <v>158</v>
@@ -8028,10 +8031,10 @@
         <v>25</v>
       </c>
       <c r="K131" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L131" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M131" t="s">
         <v>27</v>
@@ -8048,7 +8051,7 @@
         <v>2396001</v>
       </c>
       <c r="B132" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C132" t="s">
         <v>158</v>
@@ -8075,10 +8078,10 @@
         <v>25</v>
       </c>
       <c r="K132" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L132" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M132" t="s">
         <v>27</v>
@@ -8095,7 +8098,7 @@
         <v>2396001</v>
       </c>
       <c r="B133" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C133" t="s">
         <v>158</v>
@@ -8122,10 +8125,10 @@
         <v>25</v>
       </c>
       <c r="K133" t="s">
+        <v>308</v>
+      </c>
+      <c r="L133" t="s">
         <v>307</v>
-      </c>
-      <c r="L133" t="s">
-        <v>306</v>
       </c>
       <c r="M133" t="s">
         <v>27</v>
@@ -8142,7 +8145,7 @@
         <v>2397003</v>
       </c>
       <c r="B134" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C134" t="s">
         <v>158</v>
@@ -8169,16 +8172,16 @@
         <v>25</v>
       </c>
       <c r="K134" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L134" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M134" t="s">
         <v>27</v>
       </c>
       <c r="N134" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="P134" t="s">
         <v>28</v>
@@ -8192,7 +8195,7 @@
         <v>2397003</v>
       </c>
       <c r="B135" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C135" t="s">
         <v>158</v>
@@ -8219,16 +8222,16 @@
         <v>25</v>
       </c>
       <c r="K135" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L135" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M135" t="s">
         <v>27</v>
       </c>
       <c r="N135" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P135" t="s">
         <v>28</v>
@@ -8242,7 +8245,7 @@
         <v>2397003</v>
       </c>
       <c r="B136" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C136" t="s">
         <v>158</v>
@@ -8269,16 +8272,16 @@
         <v>25</v>
       </c>
       <c r="K136" t="s">
+        <v>316</v>
+      </c>
+      <c r="L136" t="s">
+        <v>314</v>
+      </c>
+      <c r="M136" t="s">
+        <v>27</v>
+      </c>
+      <c r="N136" t="s">
         <v>315</v>
-      </c>
-      <c r="L136" t="s">
-        <v>313</v>
-      </c>
-      <c r="M136" t="s">
-        <v>27</v>
-      </c>
-      <c r="N136" t="s">
-        <v>314</v>
       </c>
       <c r="P136" t="s">
         <v>28</v>
@@ -8292,7 +8295,7 @@
         <v>2397008</v>
       </c>
       <c r="B137" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C137" t="s">
         <v>158</v>
@@ -8319,10 +8322,10 @@
         <v>25</v>
       </c>
       <c r="K137" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L137" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M137" t="s">
         <v>27</v>
@@ -8339,7 +8342,7 @@
         <v>2397008</v>
       </c>
       <c r="B138" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C138" t="s">
         <v>158</v>
@@ -8366,10 +8369,10 @@
         <v>25</v>
       </c>
       <c r="K138" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L138" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M138" t="s">
         <v>27</v>
@@ -8386,7 +8389,7 @@
         <v>2397008</v>
       </c>
       <c r="B139" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C139" t="s">
         <v>158</v>
@@ -8413,10 +8416,10 @@
         <v>25</v>
       </c>
       <c r="K139" t="s">
+        <v>321</v>
+      </c>
+      <c r="L139" t="s">
         <v>320</v>
-      </c>
-      <c r="L139" t="s">
-        <v>319</v>
       </c>
       <c r="M139" t="s">
         <v>27</v>
@@ -8433,7 +8436,7 @@
         <v>2398001</v>
       </c>
       <c r="B140" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C140" t="s">
         <v>158</v>
@@ -8460,16 +8463,16 @@
         <v>42</v>
       </c>
       <c r="K140" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L140" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M140" t="s">
         <v>27</v>
       </c>
       <c r="N140" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P140" t="s">
         <v>28</v>
@@ -8483,7 +8486,7 @@
         <v>2398001</v>
       </c>
       <c r="B141" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C141" t="s">
         <v>158</v>
@@ -8510,16 +8513,16 @@
         <v>42</v>
       </c>
       <c r="K141" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L141" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M141" t="s">
         <v>27</v>
       </c>
       <c r="N141" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P141" t="s">
         <v>28</v>
@@ -8533,7 +8536,7 @@
         <v>2398001</v>
       </c>
       <c r="B142" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C142" t="s">
         <v>158</v>
@@ -8560,16 +8563,16 @@
         <v>42</v>
       </c>
       <c r="K142" t="s">
+        <v>328</v>
+      </c>
+      <c r="L142" t="s">
+        <v>324</v>
+      </c>
+      <c r="M142" t="s">
+        <v>27</v>
+      </c>
+      <c r="N142" s="4" t="s">
         <v>327</v>
-      </c>
-      <c r="L142" t="s">
-        <v>323</v>
-      </c>
-      <c r="M142" t="s">
-        <v>27</v>
-      </c>
-      <c r="N142" s="4" t="s">
-        <v>326</v>
       </c>
       <c r="P142" t="s">
         <v>28</v>
@@ -8583,7 +8586,7 @@
         <v>2398006</v>
       </c>
       <c r="B143" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C143" t="s">
         <v>158</v>
@@ -8610,10 +8613,10 @@
         <v>42</v>
       </c>
       <c r="K143" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L143" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M143" t="s">
         <v>27</v>
@@ -8630,7 +8633,7 @@
         <v>2398006</v>
       </c>
       <c r="B144" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C144" t="s">
         <v>158</v>
@@ -8657,10 +8660,10 @@
         <v>42</v>
       </c>
       <c r="K144" t="s">
+        <v>331</v>
+      </c>
+      <c r="L144" t="s">
         <v>330</v>
-      </c>
-      <c r="L144" t="s">
-        <v>329</v>
       </c>
       <c r="M144" t="s">
         <v>27</v>
@@ -8677,7 +8680,7 @@
         <v>2398006</v>
       </c>
       <c r="B145" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C145" t="s">
         <v>158</v>
@@ -8704,10 +8707,10 @@
         <v>42</v>
       </c>
       <c r="K145" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L145" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M145" t="s">
         <v>27</v>
@@ -8724,7 +8727,7 @@
         <v>2398013</v>
       </c>
       <c r="B146" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C146" t="s">
         <v>158</v>
@@ -8736,7 +8739,7 @@
         <v>21</v>
       </c>
       <c r="F146" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G146" t="s">
         <v>23</v>
@@ -8751,10 +8754,10 @@
         <v>25</v>
       </c>
       <c r="K146" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L146" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M146" t="s">
         <v>27</v>
@@ -8771,7 +8774,7 @@
         <v>2398013</v>
       </c>
       <c r="B147" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C147" t="s">
         <v>158</v>
@@ -8783,7 +8786,7 @@
         <v>21</v>
       </c>
       <c r="F147" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G147" t="s">
         <v>23</v>
@@ -8798,10 +8801,10 @@
         <v>25</v>
       </c>
       <c r="K147" t="s">
+        <v>335</v>
+      </c>
+      <c r="L147" t="s">
         <v>334</v>
-      </c>
-      <c r="L147" t="s">
-        <v>333</v>
       </c>
       <c r="M147" t="s">
         <v>27</v>
@@ -8818,7 +8821,7 @@
         <v>2398013</v>
       </c>
       <c r="B148" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C148" t="s">
         <v>158</v>
@@ -8830,7 +8833,7 @@
         <v>21</v>
       </c>
       <c r="F148" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G148" t="s">
         <v>23</v>
@@ -8845,7 +8848,7 @@
         <v>25</v>
       </c>
       <c r="K148" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M148" t="s">
         <v>27</v>
@@ -8862,7 +8865,7 @@
         <v>2399003</v>
       </c>
       <c r="B149" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C149" t="s">
         <v>158</v>
@@ -8889,10 +8892,10 @@
         <v>42</v>
       </c>
       <c r="K149" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L149" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M149" t="s">
         <v>27</v>
@@ -8909,7 +8912,7 @@
         <v>2399003</v>
       </c>
       <c r="B150" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C150" t="s">
         <v>158</v>
@@ -8936,10 +8939,10 @@
         <v>42</v>
       </c>
       <c r="K150" t="s">
+        <v>340</v>
+      </c>
+      <c r="L150" t="s">
         <v>339</v>
-      </c>
-      <c r="L150" t="s">
-        <v>338</v>
       </c>
       <c r="M150" t="s">
         <v>27</v>
@@ -8956,7 +8959,7 @@
         <v>2399003</v>
       </c>
       <c r="B151" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C151" t="s">
         <v>158</v>
@@ -8983,10 +8986,10 @@
         <v>42</v>
       </c>
       <c r="K151" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L151" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M151" t="s">
         <v>27</v>
@@ -9003,7 +9006,7 @@
         <v>2399010</v>
       </c>
       <c r="B152" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C152" t="s">
         <v>158</v>
@@ -9030,10 +9033,10 @@
         <v>42</v>
       </c>
       <c r="K152" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L152" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M152" t="s">
         <v>27</v>
@@ -9050,7 +9053,7 @@
         <v>2399010</v>
       </c>
       <c r="B153" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C153" t="s">
         <v>158</v>
@@ -9077,10 +9080,10 @@
         <v>42</v>
       </c>
       <c r="K153" t="s">
+        <v>344</v>
+      </c>
+      <c r="L153" t="s">
         <v>343</v>
-      </c>
-      <c r="L153" t="s">
-        <v>342</v>
       </c>
       <c r="M153" t="s">
         <v>27</v>
@@ -9097,7 +9100,7 @@
         <v>2399010</v>
       </c>
       <c r="B154" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C154" t="s">
         <v>158</v>
@@ -9124,10 +9127,10 @@
         <v>42</v>
       </c>
       <c r="K154" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L154" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M154" t="s">
         <v>27</v>
@@ -9144,7 +9147,7 @@
         <v>2399014</v>
       </c>
       <c r="B155" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C155" t="s">
         <v>158</v>
@@ -9171,10 +9174,10 @@
         <v>25</v>
       </c>
       <c r="K155" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L155" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M155" t="s">
         <v>27</v>
@@ -9191,7 +9194,7 @@
         <v>2399014</v>
       </c>
       <c r="B156" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C156" t="s">
         <v>158</v>
@@ -9218,10 +9221,10 @@
         <v>25</v>
       </c>
       <c r="K156" t="s">
+        <v>348</v>
+      </c>
+      <c r="L156" t="s">
         <v>347</v>
-      </c>
-      <c r="L156" t="s">
-        <v>346</v>
       </c>
       <c r="M156" t="s">
         <v>27</v>
@@ -9238,7 +9241,7 @@
         <v>2399014</v>
       </c>
       <c r="B157" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C157" t="s">
         <v>158</v>
@@ -9265,7 +9268,7 @@
         <v>25</v>
       </c>
       <c r="K157" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M157" t="s">
         <v>27</v>
@@ -9282,7 +9285,7 @@
         <v>2400003</v>
       </c>
       <c r="B158" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C158" t="s">
         <v>158</v>
@@ -9309,16 +9312,16 @@
         <v>42</v>
       </c>
       <c r="K158" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L158" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M158" t="s">
         <v>27</v>
       </c>
       <c r="N158" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P158" t="s">
         <v>28</v>
@@ -9332,7 +9335,7 @@
         <v>2400003</v>
       </c>
       <c r="B159" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C159" t="s">
         <v>158</v>
@@ -9359,16 +9362,16 @@
         <v>42</v>
       </c>
       <c r="K159" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L159" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M159" t="s">
         <v>27</v>
       </c>
       <c r="N159" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P159" t="s">
         <v>28</v>
@@ -9382,7 +9385,7 @@
         <v>2400003</v>
       </c>
       <c r="B160" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C160" t="s">
         <v>158</v>
@@ -9409,16 +9412,16 @@
         <v>42</v>
       </c>
       <c r="K160" t="s">
+        <v>356</v>
+      </c>
+      <c r="L160" t="s">
+        <v>352</v>
+      </c>
+      <c r="M160" t="s">
+        <v>27</v>
+      </c>
+      <c r="N160" t="s">
         <v>355</v>
-      </c>
-      <c r="L160" t="s">
-        <v>351</v>
-      </c>
-      <c r="M160" t="s">
-        <v>27</v>
-      </c>
-      <c r="N160" t="s">
-        <v>354</v>
       </c>
       <c r="P160" t="s">
         <v>28</v>
@@ -9432,7 +9435,7 @@
         <v>2400008</v>
       </c>
       <c r="B161" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C161" t="s">
         <v>158</v>
@@ -9459,10 +9462,10 @@
         <v>42</v>
       </c>
       <c r="K161" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L161" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M161" t="s">
         <v>27</v>
@@ -9479,7 +9482,7 @@
         <v>2400008</v>
       </c>
       <c r="B162" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C162" t="s">
         <v>158</v>
@@ -9506,10 +9509,10 @@
         <v>42</v>
       </c>
       <c r="K162" t="s">
+        <v>359</v>
+      </c>
+      <c r="L162" t="s">
         <v>358</v>
-      </c>
-      <c r="L162" t="s">
-        <v>357</v>
       </c>
       <c r="M162" t="s">
         <v>27</v>
@@ -9526,7 +9529,7 @@
         <v>2400008</v>
       </c>
       <c r="B163" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C163" t="s">
         <v>158</v>
@@ -9553,10 +9556,10 @@
         <v>42</v>
       </c>
       <c r="K163" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L163" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M163" t="s">
         <v>27</v>
@@ -9573,7 +9576,7 @@
         <v>2400012</v>
       </c>
       <c r="B164" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C164" t="s">
         <v>158</v>
@@ -9585,7 +9588,7 @@
         <v>21</v>
       </c>
       <c r="F164" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G164" t="s">
         <v>23</v>
@@ -9600,16 +9603,16 @@
         <v>25</v>
       </c>
       <c r="K164" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L164" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M164" t="s">
         <v>27</v>
       </c>
       <c r="N164" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="P164" t="s">
         <v>28</v>
@@ -9623,7 +9626,7 @@
         <v>2400012</v>
       </c>
       <c r="B165" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C165" t="s">
         <v>158</v>
@@ -9635,7 +9638,7 @@
         <v>21</v>
       </c>
       <c r="F165" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G165" t="s">
         <v>23</v>
@@ -9650,16 +9653,16 @@
         <v>25</v>
       </c>
       <c r="K165" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="L165" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M165" t="s">
         <v>27</v>
       </c>
       <c r="N165" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P165" t="s">
         <v>28</v>
@@ -9673,7 +9676,7 @@
         <v>2400012</v>
       </c>
       <c r="B166" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C166" t="s">
         <v>158</v>
@@ -9685,7 +9688,7 @@
         <v>21</v>
       </c>
       <c r="F166" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G166" t="s">
         <v>23</v>
@@ -9700,13 +9703,13 @@
         <v>25</v>
       </c>
       <c r="K166" t="s">
+        <v>367</v>
+      </c>
+      <c r="M166" t="s">
+        <v>27</v>
+      </c>
+      <c r="N166" t="s">
         <v>366</v>
-      </c>
-      <c r="M166" t="s">
-        <v>27</v>
-      </c>
-      <c r="N166" t="s">
-        <v>365</v>
       </c>
       <c r="P166" t="s">
         <v>28</v>
@@ -9720,7 +9723,7 @@
         <v>2401001</v>
       </c>
       <c r="B167" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C167" t="s">
         <v>158</v>
@@ -9747,10 +9750,10 @@
         <v>25</v>
       </c>
       <c r="K167" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L167" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M167" t="s">
         <v>27</v>
@@ -9767,7 +9770,7 @@
         <v>2401001</v>
       </c>
       <c r="B168" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C168" t="s">
         <v>158</v>
@@ -9794,10 +9797,10 @@
         <v>25</v>
       </c>
       <c r="K168" t="s">
+        <v>371</v>
+      </c>
+      <c r="L168" t="s">
         <v>370</v>
-      </c>
-      <c r="L168" t="s">
-        <v>369</v>
       </c>
       <c r="M168" t="s">
         <v>27</v>
@@ -9814,7 +9817,7 @@
         <v>2401001</v>
       </c>
       <c r="B169" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C169" t="s">
         <v>158</v>
@@ -9841,10 +9844,10 @@
         <v>25</v>
       </c>
       <c r="K169" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L169" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M169" t="s">
         <v>27</v>
@@ -9861,7 +9864,7 @@
         <v>2401007</v>
       </c>
       <c r="B170" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C170" t="s">
         <v>158</v>
@@ -9888,10 +9891,10 @@
         <v>25</v>
       </c>
       <c r="K170" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L170" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M170" t="s">
         <v>27</v>
@@ -9908,7 +9911,7 @@
         <v>2401007</v>
       </c>
       <c r="B171" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C171" t="s">
         <v>158</v>
@@ -9935,10 +9938,10 @@
         <v>25</v>
       </c>
       <c r="K171" t="s">
+        <v>375</v>
+      </c>
+      <c r="L171" t="s">
         <v>374</v>
-      </c>
-      <c r="L171" t="s">
-        <v>373</v>
       </c>
       <c r="M171" t="s">
         <v>27</v>
@@ -9955,7 +9958,7 @@
         <v>2401007</v>
       </c>
       <c r="B172" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C172" t="s">
         <v>158</v>
@@ -9982,10 +9985,10 @@
         <v>25</v>
       </c>
       <c r="K172" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L172" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M172" t="s">
         <v>27</v>
@@ -10002,7 +10005,7 @@
         <v>2401013</v>
       </c>
       <c r="B173" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C173" t="s">
         <v>158</v>
@@ -10014,7 +10017,7 @@
         <v>21</v>
       </c>
       <c r="F173" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="G173" t="s">
         <v>40</v>
@@ -10029,16 +10032,16 @@
         <v>42</v>
       </c>
       <c r="K173" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L173" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M173" t="s">
         <v>27</v>
       </c>
       <c r="N173" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P173" t="s">
         <v>28</v>
@@ -10052,7 +10055,7 @@
         <v>2401013</v>
       </c>
       <c r="B174" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C174" t="s">
         <v>158</v>
@@ -10064,7 +10067,7 @@
         <v>21</v>
       </c>
       <c r="F174" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="G174" t="s">
         <v>40</v>
@@ -10079,16 +10082,16 @@
         <v>42</v>
       </c>
       <c r="K174" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L174" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M174" t="s">
         <v>27</v>
       </c>
       <c r="N174" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P174" t="s">
         <v>28</v>
@@ -10102,7 +10105,7 @@
         <v>2401013</v>
       </c>
       <c r="B175" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C175" t="s">
         <v>158</v>
@@ -10114,7 +10117,7 @@
         <v>21</v>
       </c>
       <c r="F175" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="G175" t="s">
         <v>40</v>
@@ -10129,16 +10132,16 @@
         <v>42</v>
       </c>
       <c r="K175" t="s">
+        <v>383</v>
+      </c>
+      <c r="L175" t="s">
+        <v>379</v>
+      </c>
+      <c r="M175" t="s">
+        <v>27</v>
+      </c>
+      <c r="N175" t="s">
         <v>382</v>
-      </c>
-      <c r="L175" t="s">
-        <v>378</v>
-      </c>
-      <c r="M175" t="s">
-        <v>27</v>
-      </c>
-      <c r="N175" t="s">
-        <v>381</v>
       </c>
       <c r="P175" t="s">
         <v>28</v>
@@ -10152,7 +10155,7 @@
         <v>2401018</v>
       </c>
       <c r="B176" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C176" t="s">
         <v>158</v>
@@ -10164,7 +10167,7 @@
         <v>35</v>
       </c>
       <c r="F176" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="G176" t="s">
         <v>40</v>
@@ -10179,10 +10182,10 @@
         <v>42</v>
       </c>
       <c r="K176" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L176" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M176" t="s">
         <v>27</v>
@@ -10199,7 +10202,7 @@
         <v>2401018</v>
       </c>
       <c r="B177" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C177" t="s">
         <v>158</v>
@@ -10211,7 +10214,7 @@
         <v>35</v>
       </c>
       <c r="F177" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="G177" t="s">
         <v>40</v>
@@ -10226,10 +10229,10 @@
         <v>42</v>
       </c>
       <c r="K177" t="s">
+        <v>387</v>
+      </c>
+      <c r="L177" t="s">
         <v>386</v>
-      </c>
-      <c r="L177" t="s">
-        <v>385</v>
       </c>
       <c r="M177" t="s">
         <v>27</v>
@@ -10246,7 +10249,7 @@
         <v>2401018</v>
       </c>
       <c r="B178" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C178" t="s">
         <v>158</v>
@@ -10258,7 +10261,7 @@
         <v>35</v>
       </c>
       <c r="F178" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="G178" t="s">
         <v>40</v>
@@ -10267,16 +10270,16 @@
         <v>4</v>
       </c>
       <c r="I178" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J178" t="s">
         <v>42</v>
       </c>
       <c r="K178" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L178" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M178" t="s">
         <v>27</v>
@@ -10293,7 +10296,7 @@
         <v>2401018</v>
       </c>
       <c r="B179" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C179" t="s">
         <v>158</v>
@@ -10305,7 +10308,7 @@
         <v>35</v>
       </c>
       <c r="F179" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="G179" t="s">
         <v>40</v>
@@ -10320,10 +10323,10 @@
         <v>42</v>
       </c>
       <c r="K179" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L179" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M179" t="s">
         <v>27</v>
@@ -10340,7 +10343,7 @@
         <v>2401018</v>
       </c>
       <c r="B180" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C180" t="s">
         <v>158</v>
@@ -10352,7 +10355,7 @@
         <v>35</v>
       </c>
       <c r="F180" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="G180" t="s">
         <v>40</v>
@@ -10361,16 +10364,16 @@
         <v>4</v>
       </c>
       <c r="I180" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J180" t="s">
         <v>42</v>
       </c>
       <c r="K180" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L180" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M180" t="s">
         <v>27</v>
@@ -10387,7 +10390,7 @@
         <v>2401018</v>
       </c>
       <c r="B181" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C181" t="s">
         <v>158</v>
@@ -10399,7 +10402,7 @@
         <v>35</v>
       </c>
       <c r="F181" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="G181" t="s">
         <v>40</v>
@@ -10408,16 +10411,16 @@
         <v>4</v>
       </c>
       <c r="I181" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="J181" t="s">
         <v>42</v>
       </c>
       <c r="K181" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L181" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M181" t="s">
         <v>27</v>
@@ -10434,7 +10437,7 @@
         <v>2401018</v>
       </c>
       <c r="B182" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C182" t="s">
         <v>158</v>
@@ -10446,7 +10449,7 @@
         <v>35</v>
       </c>
       <c r="F182" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="G182" t="s">
         <v>40</v>
@@ -10455,16 +10458,16 @@
         <v>4</v>
       </c>
       <c r="I182" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="J182" t="s">
         <v>42</v>
       </c>
       <c r="K182" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L182" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M182" t="s">
         <v>27</v>
@@ -10481,7 +10484,7 @@
         <v>2402003</v>
       </c>
       <c r="B183" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C183" t="s">
         <v>158</v>
@@ -10508,16 +10511,16 @@
         <v>25</v>
       </c>
       <c r="K183" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L183" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M183" t="s">
         <v>27</v>
       </c>
       <c r="N183" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P183" t="s">
         <v>28</v>
@@ -10531,7 +10534,7 @@
         <v>2402003</v>
       </c>
       <c r="B184" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C184" t="s">
         <v>158</v>
@@ -10558,16 +10561,16 @@
         <v>25</v>
       </c>
       <c r="K184" t="s">
+        <v>400</v>
+      </c>
+      <c r="L184" t="s">
         <v>399</v>
       </c>
-      <c r="L184" t="s">
-        <v>398</v>
-      </c>
       <c r="M184" t="s">
         <v>27</v>
       </c>
       <c r="N184" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P184" t="s">
         <v>28</v>
@@ -10581,7 +10584,7 @@
         <v>2402003</v>
       </c>
       <c r="B185" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C185" t="s">
         <v>158</v>
@@ -10608,16 +10611,16 @@
         <v>25</v>
       </c>
       <c r="K185" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="L185" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M185" t="s">
         <v>27</v>
       </c>
       <c r="N185" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P185" t="s">
         <v>28</v>
@@ -10631,7 +10634,7 @@
         <v>2402008</v>
       </c>
       <c r="B186" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C186" t="s">
         <v>158</v>
@@ -10658,16 +10661,16 @@
         <v>25</v>
       </c>
       <c r="K186" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L186" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M186" t="s">
         <v>27</v>
       </c>
       <c r="N186" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="P186" t="s">
         <v>28</v>
@@ -10681,7 +10684,7 @@
         <v>2402008</v>
       </c>
       <c r="B187" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C187" t="s">
         <v>158</v>
@@ -10708,16 +10711,16 @@
         <v>25</v>
       </c>
       <c r="K187" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L187" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M187" t="s">
         <v>27</v>
       </c>
       <c r="N187" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="P187" t="s">
         <v>28</v>
@@ -10731,7 +10734,7 @@
         <v>2402008</v>
       </c>
       <c r="B188" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C188" t="s">
         <v>158</v>
@@ -10758,16 +10761,16 @@
         <v>25</v>
       </c>
       <c r="K188" t="s">
+        <v>407</v>
+      </c>
+      <c r="L188" t="s">
+        <v>403</v>
+      </c>
+      <c r="M188" t="s">
+        <v>27</v>
+      </c>
+      <c r="N188" t="s">
         <v>406</v>
-      </c>
-      <c r="L188" t="s">
-        <v>402</v>
-      </c>
-      <c r="M188" t="s">
-        <v>27</v>
-      </c>
-      <c r="N188" t="s">
-        <v>405</v>
       </c>
       <c r="P188" t="s">
         <v>28</v>
@@ -10781,7 +10784,7 @@
         <v>2402015</v>
       </c>
       <c r="B189" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C189" t="s">
         <v>158</v>
@@ -10793,7 +10796,7 @@
         <v>21</v>
       </c>
       <c r="F189" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G189" t="s">
         <v>23</v>
@@ -10808,13 +10811,13 @@
         <v>42</v>
       </c>
       <c r="K189" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M189" t="s">
         <v>27</v>
       </c>
       <c r="N189" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="P189" t="s">
         <v>28</v>
@@ -10828,7 +10831,7 @@
         <v>2402015</v>
       </c>
       <c r="B190" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C190" t="s">
         <v>158</v>
@@ -10840,7 +10843,7 @@
         <v>21</v>
       </c>
       <c r="F190" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G190" t="s">
         <v>23</v>
@@ -10855,13 +10858,13 @@
         <v>42</v>
       </c>
       <c r="K190" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M190" t="s">
         <v>27</v>
       </c>
       <c r="N190" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="P190" t="s">
         <v>28</v>
@@ -10875,7 +10878,7 @@
         <v>2402015</v>
       </c>
       <c r="B191" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C191" t="s">
         <v>158</v>
@@ -10887,7 +10890,7 @@
         <v>21</v>
       </c>
       <c r="F191" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G191" t="s">
         <v>23</v>
@@ -10902,7 +10905,7 @@
         <v>42</v>
       </c>
       <c r="K191" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M191" t="s">
         <v>27</v>
@@ -10920,7 +10923,7 @@
         <v>2403004</v>
       </c>
       <c r="B192" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C192" t="s">
         <v>158</v>
@@ -10947,16 +10950,16 @@
         <v>42</v>
       </c>
       <c r="K192" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L192" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M192" t="s">
         <v>27</v>
       </c>
       <c r="N192" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P192" t="s">
         <v>28</v>
@@ -10970,7 +10973,7 @@
         <v>2403004</v>
       </c>
       <c r="B193" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C193" t="s">
         <v>158</v>
@@ -10997,16 +11000,16 @@
         <v>42</v>
       </c>
       <c r="K193" t="s">
+        <v>416</v>
+      </c>
+      <c r="L193" t="s">
         <v>415</v>
       </c>
-      <c r="L193" t="s">
-        <v>414</v>
-      </c>
       <c r="M193" t="s">
         <v>27</v>
       </c>
       <c r="N193" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P193" t="s">
         <v>28</v>
@@ -11020,7 +11023,7 @@
         <v>2403004</v>
       </c>
       <c r="B194" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C194" t="s">
         <v>158</v>
@@ -11047,16 +11050,16 @@
         <v>42</v>
       </c>
       <c r="K194" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L194" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M194" t="s">
         <v>27</v>
       </c>
       <c r="N194" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P194" t="s">
         <v>28</v>
@@ -11070,7 +11073,7 @@
         <v>2403009</v>
       </c>
       <c r="B195" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C195" t="s">
         <v>158</v>
@@ -11097,10 +11100,10 @@
         <v>42</v>
       </c>
       <c r="K195" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L195" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M195" t="s">
         <v>27</v>
@@ -11117,7 +11120,7 @@
         <v>2403009</v>
       </c>
       <c r="B196" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C196" t="s">
         <v>158</v>
@@ -11144,10 +11147,10 @@
         <v>42</v>
       </c>
       <c r="K196" t="s">
+        <v>420</v>
+      </c>
+      <c r="L196" t="s">
         <v>419</v>
-      </c>
-      <c r="L196" t="s">
-        <v>418</v>
       </c>
       <c r="M196" t="s">
         <v>27</v>
@@ -11164,7 +11167,7 @@
         <v>2403009</v>
       </c>
       <c r="B197" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C197" t="s">
         <v>158</v>
@@ -11191,10 +11194,10 @@
         <v>42</v>
       </c>
       <c r="K197" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L197" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M197" t="s">
         <v>27</v>
@@ -11211,7 +11214,7 @@
         <v>2403013</v>
       </c>
       <c r="B198" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C198" t="s">
         <v>158</v>
@@ -11223,7 +11226,7 @@
         <v>21</v>
       </c>
       <c r="F198" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G198" t="s">
         <v>23</v>
@@ -11238,7 +11241,7 @@
         <v>25</v>
       </c>
       <c r="K198" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M198" t="s">
         <v>27</v>
@@ -11255,7 +11258,7 @@
         <v>2403013</v>
       </c>
       <c r="B199" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C199" t="s">
         <v>158</v>
@@ -11267,7 +11270,7 @@
         <v>21</v>
       </c>
       <c r="F199" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G199" t="s">
         <v>23</v>
@@ -11282,7 +11285,7 @@
         <v>25</v>
       </c>
       <c r="K199" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M199" t="s">
         <v>27</v>
@@ -11299,7 +11302,7 @@
         <v>2403013</v>
       </c>
       <c r="B200" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C200" t="s">
         <v>158</v>
@@ -11311,7 +11314,7 @@
         <v>21</v>
       </c>
       <c r="F200" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G200" t="s">
         <v>23</v>
@@ -11326,7 +11329,7 @@
         <v>25</v>
       </c>
       <c r="K200" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M200" t="s">
         <v>27</v>
@@ -11343,7 +11346,7 @@
         <v>2404001</v>
       </c>
       <c r="B201" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C201" t="s">
         <v>158</v>
@@ -11370,16 +11373,16 @@
         <v>42</v>
       </c>
       <c r="K201" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L201" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M201" t="s">
         <v>27</v>
       </c>
       <c r="N201" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P201" t="s">
         <v>28</v>
@@ -11393,7 +11396,7 @@
         <v>2404001</v>
       </c>
       <c r="B202" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C202" t="s">
         <v>158</v>
@@ -11420,16 +11423,16 @@
         <v>42</v>
       </c>
       <c r="K202" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L202" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M202" t="s">
         <v>27</v>
       </c>
       <c r="N202" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P202" t="s">
         <v>28</v>
@@ -11443,7 +11446,7 @@
         <v>2404001</v>
       </c>
       <c r="B203" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C203" t="s">
         <v>158</v>
@@ -11470,16 +11473,16 @@
         <v>42</v>
       </c>
       <c r="K203" t="s">
+        <v>431</v>
+      </c>
+      <c r="L203" t="s">
+        <v>427</v>
+      </c>
+      <c r="M203" t="s">
+        <v>27</v>
+      </c>
+      <c r="N203" t="s">
         <v>430</v>
-      </c>
-      <c r="L203" t="s">
-        <v>426</v>
-      </c>
-      <c r="M203" t="s">
-        <v>27</v>
-      </c>
-      <c r="N203" t="s">
-        <v>429</v>
       </c>
       <c r="P203" t="s">
         <v>28</v>
@@ -11493,7 +11496,7 @@
         <v>2404006</v>
       </c>
       <c r="B204" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C204" t="s">
         <v>158</v>
@@ -11520,16 +11523,16 @@
         <v>42</v>
       </c>
       <c r="K204" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L204" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M204" t="s">
         <v>27</v>
       </c>
       <c r="N204" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="P204" t="s">
         <v>28</v>
@@ -11543,7 +11546,7 @@
         <v>2404006</v>
       </c>
       <c r="B205" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C205" t="s">
         <v>158</v>
@@ -11570,16 +11573,16 @@
         <v>42</v>
       </c>
       <c r="K205" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L205" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M205" t="s">
         <v>27</v>
       </c>
       <c r="N205" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="P205" t="s">
         <v>28</v>
@@ -11593,7 +11596,7 @@
         <v>2404006</v>
       </c>
       <c r="B206" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C206" t="s">
         <v>158</v>
@@ -11620,16 +11623,16 @@
         <v>42</v>
       </c>
       <c r="K206" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L206" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M206" t="s">
         <v>27</v>
       </c>
       <c r="N206" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="P206" t="s">
         <v>28</v>
@@ -11643,7 +11646,7 @@
         <v>2404015</v>
       </c>
       <c r="B207" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C207" t="s">
         <v>158</v>
@@ -11655,7 +11658,7 @@
         <v>21</v>
       </c>
       <c r="F207" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G207" t="s">
         <v>40</v>
@@ -11670,13 +11673,13 @@
         <v>25</v>
       </c>
       <c r="K207" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M207" t="s">
         <v>27</v>
       </c>
       <c r="N207" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P207" t="s">
         <v>28</v>
@@ -11690,7 +11693,7 @@
         <v>2404015</v>
       </c>
       <c r="B208" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C208" t="s">
         <v>158</v>
@@ -11702,7 +11705,7 @@
         <v>21</v>
       </c>
       <c r="F208" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G208" t="s">
         <v>40</v>
@@ -11711,19 +11714,19 @@
         <v>32</v>
       </c>
       <c r="I208" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="J208" t="s">
         <v>25</v>
       </c>
       <c r="K208" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M208" t="s">
         <v>27</v>
       </c>
       <c r="N208" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P208" t="s">
         <v>28</v>
@@ -11737,7 +11740,7 @@
         <v>2404015</v>
       </c>
       <c r="B209" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C209" t="s">
         <v>158</v>
@@ -11749,7 +11752,7 @@
         <v>21</v>
       </c>
       <c r="F209" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G209" t="s">
         <v>40</v>
@@ -11758,19 +11761,19 @@
         <v>32</v>
       </c>
       <c r="I209" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="J209" t="s">
         <v>25</v>
       </c>
       <c r="K209" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M209" t="s">
         <v>27</v>
       </c>
       <c r="N209" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P209" t="s">
         <v>28</v>
@@ -11784,7 +11787,7 @@
         <v>2405001</v>
       </c>
       <c r="B210" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C210" t="s">
         <v>158</v>
@@ -11811,16 +11814,16 @@
         <v>42</v>
       </c>
       <c r="K210" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L210" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M210" t="s">
         <v>27</v>
       </c>
       <c r="N210" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P210" t="s">
         <v>28</v>
@@ -11834,7 +11837,7 @@
         <v>2405001</v>
       </c>
       <c r="B211" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C211" t="s">
         <v>158</v>
@@ -11861,16 +11864,16 @@
         <v>42</v>
       </c>
       <c r="K211" t="s">
+        <v>447</v>
+      </c>
+      <c r="L211" t="s">
         <v>446</v>
       </c>
-      <c r="L211" t="s">
-        <v>445</v>
-      </c>
       <c r="M211" t="s">
         <v>27</v>
       </c>
       <c r="N211" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P211" t="s">
         <v>28</v>
@@ -11884,7 +11887,7 @@
         <v>2405001</v>
       </c>
       <c r="B212" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C212" t="s">
         <v>158</v>
@@ -11911,16 +11914,16 @@
         <v>42</v>
       </c>
       <c r="K212" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L212" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M212" t="s">
         <v>27</v>
       </c>
       <c r="N212" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P212" t="s">
         <v>28</v>
@@ -11934,7 +11937,7 @@
         <v>2405006</v>
       </c>
       <c r="B213" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C213" t="s">
         <v>158</v>
@@ -11961,16 +11964,16 @@
         <v>42</v>
       </c>
       <c r="K213" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L213" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M213" t="s">
         <v>27</v>
       </c>
       <c r="N213" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="P213" t="s">
         <v>28</v>
@@ -11984,7 +11987,7 @@
         <v>2405006</v>
       </c>
       <c r="B214" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C214" t="s">
         <v>158</v>
@@ -12011,16 +12014,16 @@
         <v>42</v>
       </c>
       <c r="K214" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="L214" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M214" t="s">
         <v>27</v>
       </c>
       <c r="N214" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="P214" t="s">
         <v>28</v>
@@ -12034,7 +12037,7 @@
         <v>2405006</v>
       </c>
       <c r="B215" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C215" t="s">
         <v>158</v>
@@ -12061,16 +12064,16 @@
         <v>42</v>
       </c>
       <c r="K215" t="s">
+        <v>454</v>
+      </c>
+      <c r="L215" t="s">
+        <v>450</v>
+      </c>
+      <c r="M215" t="s">
+        <v>27</v>
+      </c>
+      <c r="N215" t="s">
         <v>453</v>
-      </c>
-      <c r="L215" t="s">
-        <v>449</v>
-      </c>
-      <c r="M215" t="s">
-        <v>27</v>
-      </c>
-      <c r="N215" t="s">
-        <v>452</v>
       </c>
       <c r="P215" t="s">
         <v>28</v>
@@ -12084,7 +12087,7 @@
         <v>2405015</v>
       </c>
       <c r="B216" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C216" t="s">
         <v>158</v>
@@ -12096,7 +12099,7 @@
         <v>21</v>
       </c>
       <c r="F216" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G216" t="s">
         <v>23</v>
@@ -12111,16 +12114,16 @@
         <v>25</v>
       </c>
       <c r="K216" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L216" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M216" t="s">
         <v>27</v>
       </c>
       <c r="N216" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="P216" t="s">
         <v>28</v>
@@ -12134,7 +12137,7 @@
         <v>2405015</v>
       </c>
       <c r="B217" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C217" t="s">
         <v>158</v>
@@ -12146,7 +12149,7 @@
         <v>21</v>
       </c>
       <c r="F217" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G217" t="s">
         <v>23</v>
@@ -12161,16 +12164,16 @@
         <v>25</v>
       </c>
       <c r="K217" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L217" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M217" t="s">
         <v>27</v>
       </c>
       <c r="N217" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="P217" t="s">
         <v>28</v>
@@ -12184,7 +12187,7 @@
         <v>2405015</v>
       </c>
       <c r="B218" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C218" t="s">
         <v>158</v>
@@ -12196,7 +12199,7 @@
         <v>21</v>
       </c>
       <c r="F218" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G218" t="s">
         <v>23</v>
@@ -12211,13 +12214,13 @@
         <v>25</v>
       </c>
       <c r="K218" t="s">
+        <v>460</v>
+      </c>
+      <c r="M218" t="s">
+        <v>27</v>
+      </c>
+      <c r="N218" t="s">
         <v>459</v>
-      </c>
-      <c r="M218" t="s">
-        <v>27</v>
-      </c>
-      <c r="N218" t="s">
-        <v>458</v>
       </c>
       <c r="P218" t="s">
         <v>28</v>
@@ -12231,7 +12234,7 @@
         <v>2406004</v>
       </c>
       <c r="B219" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C219" t="s">
         <v>158</v>
@@ -12258,10 +12261,10 @@
         <v>25</v>
       </c>
       <c r="K219" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="L219" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M219" t="s">
         <v>27</v>
@@ -12278,7 +12281,7 @@
         <v>2406004</v>
       </c>
       <c r="B220" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C220" t="s">
         <v>158</v>
@@ -12305,10 +12308,10 @@
         <v>25</v>
       </c>
       <c r="K220" t="s">
+        <v>464</v>
+      </c>
+      <c r="L220" t="s">
         <v>463</v>
-      </c>
-      <c r="L220" t="s">
-        <v>462</v>
       </c>
       <c r="M220" t="s">
         <v>27</v>
@@ -12325,7 +12328,7 @@
         <v>2406004</v>
       </c>
       <c r="B221" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C221" t="s">
         <v>158</v>
@@ -12346,13 +12349,13 @@
         <v>8</v>
       </c>
       <c r="I221" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="J221" t="s">
         <v>25</v>
       </c>
       <c r="L221" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M221" t="s">
         <v>27</v>
@@ -12369,7 +12372,7 @@
         <v>2406004</v>
       </c>
       <c r="B222" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C222" t="s">
         <v>158</v>
@@ -12396,10 +12399,10 @@
         <v>25</v>
       </c>
       <c r="K222" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L222" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M222" t="s">
         <v>27</v>
@@ -12416,7 +12419,7 @@
         <v>2406004</v>
       </c>
       <c r="B223" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C223" t="s">
         <v>158</v>
@@ -12437,13 +12440,13 @@
         <v>8</v>
       </c>
       <c r="I223" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="J223" t="s">
         <v>25</v>
       </c>
       <c r="L223" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M223" t="s">
         <v>27</v>
@@ -12460,7 +12463,7 @@
         <v>2406009</v>
       </c>
       <c r="B224" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C224" t="s">
         <v>158</v>
@@ -12487,10 +12490,10 @@
         <v>25</v>
       </c>
       <c r="K224" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L224" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M224" t="s">
         <v>27</v>
@@ -12507,7 +12510,7 @@
         <v>2406009</v>
       </c>
       <c r="B225" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C225" t="s">
         <v>158</v>
@@ -12534,10 +12537,10 @@
         <v>25</v>
       </c>
       <c r="K225" t="s">
+        <v>468</v>
+      </c>
+      <c r="L225" t="s">
         <v>467</v>
-      </c>
-      <c r="L225" t="s">
-        <v>466</v>
       </c>
       <c r="M225" t="s">
         <v>27</v>
@@ -12554,7 +12557,7 @@
         <v>2406009</v>
       </c>
       <c r="B226" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C226" t="s">
         <v>158</v>
@@ -12575,16 +12578,16 @@
         <v>8</v>
       </c>
       <c r="I226" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="J226" t="s">
         <v>25</v>
       </c>
       <c r="K226" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L226" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M226" t="s">
         <v>27</v>
@@ -12601,7 +12604,7 @@
         <v>2406009</v>
       </c>
       <c r="B227" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C227" t="s">
         <v>158</v>
@@ -12628,10 +12631,10 @@
         <v>25</v>
       </c>
       <c r="K227" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L227" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M227" t="s">
         <v>27</v>
@@ -12648,7 +12651,7 @@
         <v>2406009</v>
       </c>
       <c r="B228" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C228" t="s">
         <v>158</v>
@@ -12669,16 +12672,16 @@
         <v>8</v>
       </c>
       <c r="I228" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="J228" t="s">
         <v>25</v>
       </c>
       <c r="K228" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L228" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M228" t="s">
         <v>27</v>
@@ -12695,7 +12698,7 @@
         <v>2406012</v>
       </c>
       <c r="B229" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C229" t="s">
         <v>158</v>
@@ -12707,7 +12710,7 @@
         <v>21</v>
       </c>
       <c r="F229" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G229" t="s">
         <v>40</v>
@@ -12722,10 +12725,10 @@
         <v>42</v>
       </c>
       <c r="K229" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L229" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="M229" t="s">
         <v>27</v>
@@ -12742,7 +12745,7 @@
         <v>2406012</v>
       </c>
       <c r="B230" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C230" t="s">
         <v>158</v>
@@ -12754,7 +12757,7 @@
         <v>21</v>
       </c>
       <c r="F230" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G230" t="s">
         <v>40</v>
@@ -12763,16 +12766,16 @@
         <v>8</v>
       </c>
       <c r="I230" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J230" t="s">
         <v>42</v>
       </c>
       <c r="K230" t="s">
+        <v>475</v>
+      </c>
+      <c r="L230" t="s">
         <v>474</v>
-      </c>
-      <c r="L230" t="s">
-        <v>473</v>
       </c>
       <c r="M230" t="s">
         <v>27</v>
@@ -12789,7 +12792,7 @@
         <v>2406012</v>
       </c>
       <c r="B231" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C231" t="s">
         <v>158</v>
@@ -12801,7 +12804,7 @@
         <v>21</v>
       </c>
       <c r="F231" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G231" t="s">
         <v>40</v>
@@ -12810,16 +12813,16 @@
         <v>8</v>
       </c>
       <c r="I231" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J231" t="s">
         <v>42</v>
       </c>
       <c r="K231" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="L231" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="M231" t="s">
         <v>27</v>
@@ -12836,10 +12839,10 @@
         <v>2059001</v>
       </c>
       <c r="B232" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C232" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D232" s="2">
         <v>1</v>
@@ -12863,10 +12866,10 @@
         <v>42</v>
       </c>
       <c r="K232" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="L232" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M232" t="s">
         <v>27</v>
@@ -12883,10 +12886,10 @@
         <v>2059002</v>
       </c>
       <c r="B233" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C233" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D233" s="2">
         <v>1</v>
@@ -12910,10 +12913,10 @@
         <v>42</v>
       </c>
       <c r="K233" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L233" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M233" t="s">
         <v>27</v>
@@ -12930,10 +12933,10 @@
         <v>2059006</v>
       </c>
       <c r="B234" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C234" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D234" s="2">
         <v>1</v>
@@ -12957,10 +12960,10 @@
         <v>42</v>
       </c>
       <c r="K234" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L234" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M234" t="s">
         <v>27</v>
@@ -12977,10 +12980,10 @@
         <v>2140011</v>
       </c>
       <c r="B235" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C235" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D235" s="2">
         <v>2</v>
@@ -12989,7 +12992,7 @@
         <v>21</v>
       </c>
       <c r="F235" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G235" t="s">
         <v>40</v>
@@ -13007,7 +13010,7 @@
         <v>160</v>
       </c>
       <c r="L235" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M235" t="s">
         <v>27</v>
@@ -13024,10 +13027,10 @@
         <v>2390004</v>
       </c>
       <c r="B236" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C236" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D236" s="2">
         <v>1</v>
@@ -13051,10 +13054,10 @@
         <v>25</v>
       </c>
       <c r="K236" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L236" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M236" t="s">
         <v>27</v>
@@ -13071,10 +13074,10 @@
         <v>2390004</v>
       </c>
       <c r="B237" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C237" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D237" s="2">
         <v>1</v>
@@ -13098,10 +13101,10 @@
         <v>25</v>
       </c>
       <c r="K237" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L237" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M237" t="s">
         <v>27</v>
@@ -13118,10 +13121,10 @@
         <v>2390004</v>
       </c>
       <c r="B238" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C238" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D238" s="2">
         <v>1</v>
@@ -13145,10 +13148,10 @@
         <v>25</v>
       </c>
       <c r="K238" t="s">
+        <v>492</v>
+      </c>
+      <c r="L238" t="s">
         <v>491</v>
-      </c>
-      <c r="L238" t="s">
-        <v>490</v>
       </c>
       <c r="M238" t="s">
         <v>27</v>
@@ -13165,10 +13168,10 @@
         <v>2390009</v>
       </c>
       <c r="B239" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C239" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D239" s="2">
         <v>1</v>
@@ -13192,10 +13195,10 @@
         <v>25</v>
       </c>
       <c r="K239" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L239" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M239" t="s">
         <v>27</v>
@@ -13212,10 +13215,10 @@
         <v>2390009</v>
       </c>
       <c r="B240" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C240" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D240" s="2">
         <v>1</v>
@@ -13239,10 +13242,10 @@
         <v>25</v>
       </c>
       <c r="K240" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="L240" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M240" t="s">
         <v>27</v>
@@ -13259,10 +13262,10 @@
         <v>2390009</v>
       </c>
       <c r="B241" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C241" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D241" s="2">
         <v>1</v>
@@ -13286,10 +13289,10 @@
         <v>25</v>
       </c>
       <c r="K241" t="s">
+        <v>497</v>
+      </c>
+      <c r="L241" t="s">
         <v>496</v>
-      </c>
-      <c r="L241" t="s">
-        <v>495</v>
       </c>
       <c r="M241" t="s">
         <v>27</v>
@@ -13306,10 +13309,10 @@
         <v>2390013</v>
       </c>
       <c r="B242" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C242" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D242" s="2">
         <v>2</v>
@@ -13318,7 +13321,7 @@
         <v>21</v>
       </c>
       <c r="F242" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G242" t="s">
         <v>23</v>
@@ -13333,7 +13336,7 @@
         <v>42</v>
       </c>
       <c r="K242" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M242" t="s">
         <v>27</v>
@@ -13350,10 +13353,10 @@
         <v>2390013</v>
       </c>
       <c r="B243" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C243" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D243" s="2">
         <v>2</v>
@@ -13362,7 +13365,7 @@
         <v>21</v>
       </c>
       <c r="F243" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G243" t="s">
         <v>23</v>
@@ -13377,7 +13380,7 @@
         <v>42</v>
       </c>
       <c r="K243" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M243" t="s">
         <v>27</v>
@@ -13394,10 +13397,10 @@
         <v>2390013</v>
       </c>
       <c r="B244" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C244" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D244" s="2">
         <v>2</v>
@@ -13406,7 +13409,7 @@
         <v>21</v>
       </c>
       <c r="F244" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G244" t="s">
         <v>23</v>
@@ -13421,7 +13424,7 @@
         <v>42</v>
       </c>
       <c r="K244" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M244" t="s">
         <v>27</v>

--- a/POD_2026-27_11-5-2026.xlsx
+++ b/POD_2026-27_11-5-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guillermo.vera/Desktop/POD2627/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC1E04D4-4127-CB4D-8C98-06667343A95E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{364BD2D1-76E2-CA46-9B01-A9F7734E2F60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2942" uniqueCount="504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2949" uniqueCount="506">
   <si>
     <t>POD_2026-27_11-5-2026</t>
   </si>
@@ -464,9 +464,6 @@
     <t>G_SAM_EXT822_1A(F) (2039002)</t>
   </si>
   <si>
-    <t>Mofdi El Anjoumi (38)</t>
-  </si>
-  <si>
     <t>(2387) GRADO EN PAISAJISMO (FUENLABRADA)</t>
   </si>
   <si>
@@ -1548,6 +1545,15 @@
   </si>
   <si>
     <t>JAVIER PELLO (6)</t>
+  </si>
+  <si>
+    <t>MOFDI EL ANJOUMI (38)</t>
+  </si>
+  <si>
+    <t>MICHAEL STICH (46)</t>
+  </si>
+  <si>
+    <t>MICHAEL STICH (14)</t>
   </si>
 </sst>
 </file>
@@ -2017,10 +2023,10 @@
         <v>14</v>
       </c>
       <c r="O2" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>487</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>488</v>
       </c>
       <c r="Q2" s="1" t="s">
         <v>15</v>
@@ -2428,10 +2434,10 @@
         <v>26</v>
       </c>
       <c r="N11" s="8" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="O11" s="8" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="Q11" t="s">
         <v>27</v>
@@ -2478,10 +2484,10 @@
         <v>26</v>
       </c>
       <c r="N12" s="8" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="O12" s="8" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="Q12" t="s">
         <v>27</v>
@@ -2528,10 +2534,10 @@
         <v>26</v>
       </c>
       <c r="N13" s="8" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="O13" s="8" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="Q13" t="s">
         <v>27</v>
@@ -3362,7 +3368,7 @@
         <v>26</v>
       </c>
       <c r="N31" s="8" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="Q31" t="s">
         <v>27</v>
@@ -3409,7 +3415,7 @@
         <v>26</v>
       </c>
       <c r="N32" s="8" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="Q32" t="s">
         <v>27</v>
@@ -3456,7 +3462,7 @@
         <v>26</v>
       </c>
       <c r="N33" s="8" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="Q33" t="s">
         <v>27</v>
@@ -3506,7 +3512,7 @@
         <v>26</v>
       </c>
       <c r="N34" s="8" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="Q34" t="s">
         <v>27</v>
@@ -3556,7 +3562,7 @@
         <v>26</v>
       </c>
       <c r="N35" s="8" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="Q35" t="s">
         <v>27</v>
@@ -3606,7 +3612,7 @@
         <v>26</v>
       </c>
       <c r="N36" s="8" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="Q36" t="s">
         <v>27</v>
@@ -4031,6 +4037,9 @@
       <c r="M45" t="s">
         <v>26</v>
       </c>
+      <c r="N45" s="8" t="s">
+        <v>504</v>
+      </c>
       <c r="Q45" t="s">
         <v>27</v>
       </c>
@@ -4078,6 +4087,9 @@
       <c r="M46" t="s">
         <v>26</v>
       </c>
+      <c r="N46" s="8" t="s">
+        <v>505</v>
+      </c>
       <c r="Q46" t="s">
         <v>27</v>
       </c>
@@ -4125,6 +4137,9 @@
       <c r="M47" t="s">
         <v>26</v>
       </c>
+      <c r="N47" s="8" t="s">
+        <v>505</v>
+      </c>
       <c r="Q47" t="s">
         <v>27</v>
       </c>
@@ -4313,6 +4328,9 @@
       <c r="M51" t="s">
         <v>26</v>
       </c>
+      <c r="N51" s="8" t="s">
+        <v>504</v>
+      </c>
       <c r="Q51" t="s">
         <v>27</v>
       </c>
@@ -4360,6 +4378,9 @@
       <c r="M52" t="s">
         <v>26</v>
       </c>
+      <c r="N52" s="8" t="s">
+        <v>505</v>
+      </c>
       <c r="Q52" t="s">
         <v>27</v>
       </c>
@@ -4407,6 +4428,9 @@
       <c r="M53" t="s">
         <v>26</v>
       </c>
+      <c r="N53" s="8" t="s">
+        <v>505</v>
+      </c>
       <c r="Q53" t="s">
         <v>27</v>
       </c>
@@ -4913,8 +4937,8 @@
       <c r="M64" t="s">
         <v>26</v>
       </c>
-      <c r="N64" t="s">
-        <v>142</v>
+      <c r="N64" s="8" t="s">
+        <v>503</v>
       </c>
       <c r="Q64" t="s">
         <v>27</v>
@@ -4928,7 +4952,7 @@
         <v>2387009</v>
       </c>
       <c r="B65" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C65" t="s">
         <v>43</v>
@@ -4955,10 +4979,10 @@
         <v>41</v>
       </c>
       <c r="K65" t="s">
+        <v>143</v>
+      </c>
+      <c r="L65" t="s">
         <v>144</v>
-      </c>
-      <c r="L65" t="s">
-        <v>145</v>
       </c>
       <c r="M65" t="s">
         <v>26</v>
@@ -4975,7 +4999,7 @@
         <v>2387009</v>
       </c>
       <c r="B66" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C66" t="s">
         <v>43</v>
@@ -5002,7 +5026,7 @@
         <v>41</v>
       </c>
       <c r="L66" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="M66" t="s">
         <v>26</v>
@@ -5019,7 +5043,7 @@
         <v>2387009</v>
       </c>
       <c r="B67" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C67" t="s">
         <v>43</v>
@@ -5046,7 +5070,7 @@
         <v>41</v>
       </c>
       <c r="L67" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="M67" t="s">
         <v>26</v>
@@ -5063,7 +5087,7 @@
         <v>2387016</v>
       </c>
       <c r="B68" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C68" t="s">
         <v>43</v>
@@ -5090,7 +5114,7 @@
         <v>24</v>
       </c>
       <c r="K68" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="M68" t="s">
         <v>26</v>
@@ -5107,7 +5131,7 @@
         <v>2387016</v>
       </c>
       <c r="B69" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C69" t="s">
         <v>43</v>
@@ -5148,7 +5172,7 @@
         <v>2387016</v>
       </c>
       <c r="B70" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C70" t="s">
         <v>43</v>
@@ -5189,10 +5213,10 @@
         <v>2265020</v>
       </c>
       <c r="B71" t="s">
+        <v>146</v>
+      </c>
+      <c r="C71" t="s">
         <v>147</v>
-      </c>
-      <c r="C71" t="s">
-        <v>148</v>
       </c>
       <c r="D71" s="2">
         <v>2</v>
@@ -5201,7 +5225,7 @@
         <v>34</v>
       </c>
       <c r="F71" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G71" t="s">
         <v>22</v>
@@ -5216,13 +5240,13 @@
         <v>24</v>
       </c>
       <c r="K71" t="s">
+        <v>149</v>
+      </c>
+      <c r="M71" t="s">
+        <v>26</v>
+      </c>
+      <c r="N71" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="M71" t="s">
-        <v>26</v>
-      </c>
-      <c r="N71" s="3" t="s">
-        <v>151</v>
       </c>
       <c r="O71" s="3"/>
       <c r="Q71" t="s">
@@ -5237,10 +5261,10 @@
         <v>2029018</v>
       </c>
       <c r="B72" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C72" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D72" s="2">
         <v>2</v>
@@ -5249,7 +5273,7 @@
         <v>20</v>
       </c>
       <c r="F72" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G72" t="s">
         <v>39</v>
@@ -5264,10 +5288,10 @@
         <v>24</v>
       </c>
       <c r="K72" t="s">
+        <v>154</v>
+      </c>
+      <c r="L72" t="s">
         <v>155</v>
-      </c>
-      <c r="L72" t="s">
-        <v>156</v>
       </c>
       <c r="M72" t="s">
         <v>26</v>
@@ -5284,10 +5308,10 @@
         <v>2030013</v>
       </c>
       <c r="B73" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C73" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D73" s="2">
         <v>2</v>
@@ -5296,7 +5320,7 @@
         <v>34</v>
       </c>
       <c r="F73" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G73" t="s">
         <v>22</v>
@@ -5311,10 +5335,10 @@
         <v>24</v>
       </c>
       <c r="K73" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L73" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M73" t="s">
         <v>26</v>
@@ -5331,19 +5355,19 @@
         <v>2031001</v>
       </c>
       <c r="B74" t="s">
+        <v>159</v>
+      </c>
+      <c r="C74" t="s">
+        <v>152</v>
+      </c>
+      <c r="D74" s="2">
+        <v>1</v>
+      </c>
+      <c r="E74" t="s">
         <v>160</v>
       </c>
-      <c r="C74" t="s">
-        <v>153</v>
-      </c>
-      <c r="D74" s="2">
-        <v>1</v>
-      </c>
-      <c r="E74" t="s">
+      <c r="F74" t="s">
         <v>161</v>
-      </c>
-      <c r="F74" t="s">
-        <v>162</v>
       </c>
       <c r="G74" t="s">
         <v>22</v>
@@ -5375,19 +5399,19 @@
         <v>2032001</v>
       </c>
       <c r="B75" t="s">
+        <v>162</v>
+      </c>
+      <c r="C75" t="s">
+        <v>152</v>
+      </c>
+      <c r="D75" s="2">
+        <v>1</v>
+      </c>
+      <c r="E75" t="s">
+        <v>20</v>
+      </c>
+      <c r="F75" t="s">
         <v>163</v>
-      </c>
-      <c r="C75" t="s">
-        <v>153</v>
-      </c>
-      <c r="D75" s="2">
-        <v>1</v>
-      </c>
-      <c r="E75" t="s">
-        <v>20</v>
-      </c>
-      <c r="F75" t="s">
-        <v>164</v>
       </c>
       <c r="G75" t="s">
         <v>22</v>
@@ -5402,10 +5426,10 @@
         <v>41</v>
       </c>
       <c r="K75" t="s">
+        <v>164</v>
+      </c>
+      <c r="L75" t="s">
         <v>165</v>
-      </c>
-      <c r="L75" t="s">
-        <v>166</v>
       </c>
       <c r="M75" t="s">
         <v>26</v>
@@ -5422,10 +5446,10 @@
         <v>2032007</v>
       </c>
       <c r="B76" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C76" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D76" s="2">
         <v>1</v>
@@ -5449,16 +5473,16 @@
         <v>41</v>
       </c>
       <c r="K76" t="s">
+        <v>166</v>
+      </c>
+      <c r="L76" t="s">
         <v>167</v>
       </c>
-      <c r="L76" t="s">
+      <c r="M76" t="s">
+        <v>26</v>
+      </c>
+      <c r="N76" t="s">
         <v>168</v>
-      </c>
-      <c r="M76" t="s">
-        <v>26</v>
-      </c>
-      <c r="N76" t="s">
-        <v>169</v>
       </c>
       <c r="Q76" t="s">
         <v>27</v>
@@ -5472,10 +5496,10 @@
         <v>2032009</v>
       </c>
       <c r="B77" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C77" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D77" s="2">
         <v>1</v>
@@ -5499,7 +5523,7 @@
         <v>41</v>
       </c>
       <c r="K77" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="M77" t="s">
         <v>26</v>
@@ -5516,19 +5540,19 @@
         <v>2033001</v>
       </c>
       <c r="B78" t="s">
+        <v>170</v>
+      </c>
+      <c r="C78" t="s">
+        <v>152</v>
+      </c>
+      <c r="D78" s="2">
+        <v>1</v>
+      </c>
+      <c r="E78" t="s">
+        <v>20</v>
+      </c>
+      <c r="F78" t="s">
         <v>171</v>
-      </c>
-      <c r="C78" t="s">
-        <v>153</v>
-      </c>
-      <c r="D78" s="2">
-        <v>1</v>
-      </c>
-      <c r="E78" t="s">
-        <v>20</v>
-      </c>
-      <c r="F78" t="s">
-        <v>172</v>
       </c>
       <c r="G78" t="s">
         <v>22</v>
@@ -5543,10 +5567,10 @@
         <v>41</v>
       </c>
       <c r="K78" t="s">
+        <v>172</v>
+      </c>
+      <c r="L78" t="s">
         <v>173</v>
-      </c>
-      <c r="L78" t="s">
-        <v>174</v>
       </c>
       <c r="M78" t="s">
         <v>26</v>
@@ -5563,10 +5587,10 @@
         <v>2033002</v>
       </c>
       <c r="B79" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C79" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D79" s="2">
         <v>1</v>
@@ -5575,7 +5599,7 @@
         <v>20</v>
       </c>
       <c r="F79" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G79" t="s">
         <v>22</v>
@@ -5590,16 +5614,16 @@
         <v>41</v>
       </c>
       <c r="K79" t="s">
+        <v>175</v>
+      </c>
+      <c r="L79" t="s">
         <v>176</v>
       </c>
-      <c r="L79" t="s">
-        <v>177</v>
-      </c>
       <c r="M79" t="s">
         <v>26</v>
       </c>
       <c r="N79" s="7" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O79" s="3"/>
       <c r="Q79" t="s">
@@ -5614,10 +5638,10 @@
         <v>2033006</v>
       </c>
       <c r="B80" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C80" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D80" s="2">
         <v>1</v>
@@ -5641,16 +5665,16 @@
         <v>41</v>
       </c>
       <c r="K80" t="s">
+        <v>177</v>
+      </c>
+      <c r="L80" t="s">
         <v>178</v>
       </c>
-      <c r="L80" t="s">
+      <c r="M80" t="s">
+        <v>26</v>
+      </c>
+      <c r="N80" t="s">
         <v>179</v>
-      </c>
-      <c r="M80" t="s">
-        <v>26</v>
-      </c>
-      <c r="N80" t="s">
-        <v>180</v>
       </c>
       <c r="Q80" t="s">
         <v>27</v>
@@ -5664,10 +5688,10 @@
         <v>2034001</v>
       </c>
       <c r="B81" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C81" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D81" s="2">
         <v>1</v>
@@ -5676,7 +5700,7 @@
         <v>20</v>
       </c>
       <c r="F81" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G81" t="s">
         <v>22</v>
@@ -5691,10 +5715,10 @@
         <v>41</v>
       </c>
       <c r="K81" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L81" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="M81" t="s">
         <v>26</v>
@@ -5711,10 +5735,10 @@
         <v>2034002</v>
       </c>
       <c r="B82" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C82" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D82" s="2">
         <v>1</v>
@@ -5723,7 +5747,7 @@
         <v>20</v>
       </c>
       <c r="F82" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G82" t="s">
         <v>22</v>
@@ -5738,16 +5762,16 @@
         <v>41</v>
       </c>
       <c r="K82" t="s">
+        <v>182</v>
+      </c>
+      <c r="L82" t="s">
         <v>183</v>
       </c>
-      <c r="L82" t="s">
-        <v>184</v>
-      </c>
       <c r="M82" t="s">
         <v>26</v>
       </c>
       <c r="N82" s="7" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O82" s="3"/>
       <c r="Q82" t="s">
@@ -5762,10 +5786,10 @@
         <v>2034006</v>
       </c>
       <c r="B83" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C83" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D83" s="2">
         <v>1</v>
@@ -5789,10 +5813,10 @@
         <v>41</v>
       </c>
       <c r="K83" t="s">
+        <v>184</v>
+      </c>
+      <c r="L83" t="s">
         <v>185</v>
-      </c>
-      <c r="L83" t="s">
-        <v>186</v>
       </c>
       <c r="M83" t="s">
         <v>26</v>
@@ -5809,10 +5833,10 @@
         <v>2061001</v>
       </c>
       <c r="B84" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C84" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D84" s="2">
         <v>1</v>
@@ -5821,7 +5845,7 @@
         <v>20</v>
       </c>
       <c r="F84" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G84" t="s">
         <v>22</v>
@@ -5853,10 +5877,10 @@
         <v>2061002</v>
       </c>
       <c r="B85" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C85" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D85" s="2">
         <v>1</v>
@@ -5865,7 +5889,7 @@
         <v>20</v>
       </c>
       <c r="F85" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G85" t="s">
         <v>22</v>
@@ -5886,7 +5910,7 @@
         <v>26</v>
       </c>
       <c r="N85" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q85" t="s">
         <v>27</v>
@@ -5900,10 +5924,10 @@
         <v>2061006</v>
       </c>
       <c r="B86" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C86" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D86" s="2">
         <v>1</v>
@@ -5944,10 +5968,10 @@
         <v>2107013</v>
       </c>
       <c r="B87" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C87" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D87" s="2">
         <v>2</v>
@@ -5956,7 +5980,7 @@
         <v>20</v>
       </c>
       <c r="F87" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G87" t="s">
         <v>39</v>
@@ -5971,10 +5995,10 @@
         <v>24</v>
       </c>
       <c r="K87" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L87" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="M87" t="s">
         <v>26</v>
@@ -5991,10 +6015,10 @@
         <v>2143016</v>
       </c>
       <c r="B88" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C88" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D88" s="2">
         <v>2</v>
@@ -6003,7 +6027,7 @@
         <v>20</v>
       </c>
       <c r="F88" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G88" t="s">
         <v>39</v>
@@ -6018,10 +6042,10 @@
         <v>24</v>
       </c>
       <c r="K88" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L88" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="M88" t="s">
         <v>26</v>
@@ -6038,10 +6062,10 @@
         <v>2148011</v>
       </c>
       <c r="B89" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C89" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D89" s="2">
         <v>2</v>
@@ -6050,7 +6074,7 @@
         <v>20</v>
       </c>
       <c r="F89" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G89" t="s">
         <v>39</v>
@@ -6065,7 +6089,7 @@
         <v>24</v>
       </c>
       <c r="K89" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M89" t="s">
         <v>26</v>
@@ -6082,10 +6106,10 @@
         <v>2175020</v>
       </c>
       <c r="B90" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C90" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D90" s="2">
         <v>2</v>
@@ -6094,7 +6118,7 @@
         <v>34</v>
       </c>
       <c r="F90" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G90" t="s">
         <v>22</v>
@@ -6109,10 +6133,10 @@
         <v>24</v>
       </c>
       <c r="K90" t="s">
+        <v>197</v>
+      </c>
+      <c r="L90" t="s">
         <v>198</v>
-      </c>
-      <c r="L90" t="s">
-        <v>199</v>
       </c>
       <c r="M90" t="s">
         <v>26</v>
@@ -6129,10 +6153,10 @@
         <v>2285005</v>
       </c>
       <c r="B91" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C91" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D91" s="2">
         <v>1</v>
@@ -6141,7 +6165,7 @@
         <v>20</v>
       </c>
       <c r="F91" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G91" t="s">
         <v>22</v>
@@ -6156,13 +6180,13 @@
         <v>41</v>
       </c>
       <c r="K91" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M91" t="s">
         <v>26</v>
       </c>
       <c r="N91" s="7" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="O91" s="3"/>
       <c r="Q91" t="s">
@@ -6177,10 +6201,10 @@
         <v>2285006</v>
       </c>
       <c r="B92" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C92" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D92" s="2">
         <v>1</v>
@@ -6204,13 +6228,13 @@
         <v>41</v>
       </c>
       <c r="K92" t="s">
+        <v>200</v>
+      </c>
+      <c r="M92" t="s">
+        <v>26</v>
+      </c>
+      <c r="N92" t="s">
         <v>201</v>
-      </c>
-      <c r="M92" t="s">
-        <v>26</v>
-      </c>
-      <c r="N92" t="s">
-        <v>202</v>
       </c>
       <c r="Q92" t="s">
         <v>27</v>
@@ -6224,10 +6248,10 @@
         <v>2285007</v>
       </c>
       <c r="B93" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C93" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D93" s="2">
         <v>1</v>
@@ -6236,7 +6260,7 @@
         <v>34</v>
       </c>
       <c r="F93" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G93" t="s">
         <v>39</v>
@@ -6251,10 +6275,13 @@
         <v>41</v>
       </c>
       <c r="K93" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="M93" t="s">
         <v>26</v>
+      </c>
+      <c r="N93" s="8" t="s">
+        <v>179</v>
       </c>
       <c r="Q93" t="s">
         <v>27</v>
@@ -6268,10 +6295,10 @@
         <v>2286015</v>
       </c>
       <c r="B94" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C94" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D94" s="2">
         <v>2</v>
@@ -6280,7 +6307,7 @@
         <v>20</v>
       </c>
       <c r="F94" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G94" t="s">
         <v>39</v>
@@ -6295,7 +6322,7 @@
         <v>24</v>
       </c>
       <c r="K94" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M94" t="s">
         <v>26</v>
@@ -6312,10 +6339,10 @@
         <v>2338044</v>
       </c>
       <c r="B95" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C95" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D95" s="2">
         <v>1</v>
@@ -6356,10 +6383,10 @@
         <v>2342014</v>
       </c>
       <c r="B96" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C96" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D96" s="2">
         <v>2</v>
@@ -6368,7 +6395,7 @@
         <v>20</v>
       </c>
       <c r="F96" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G96" t="s">
         <v>39</v>
@@ -6383,13 +6410,13 @@
         <v>41</v>
       </c>
       <c r="K96" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M96" t="s">
         <v>26</v>
       </c>
       <c r="N96" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Q96" t="s">
         <v>27</v>
@@ -6403,10 +6430,10 @@
         <v>5</v>
       </c>
       <c r="B97" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C97" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D97" s="2">
         <v>4</v>
@@ -6415,7 +6442,7 @@
         <v>20</v>
       </c>
       <c r="F97" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G97" t="s">
         <v>39</v>
@@ -6430,13 +6457,13 @@
         <v>41</v>
       </c>
       <c r="K97" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="M97" t="s">
         <v>26</v>
       </c>
       <c r="N97" s="7" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="O97" s="3"/>
       <c r="Q97" t="s">
@@ -6451,10 +6478,10 @@
         <v>2343027</v>
       </c>
       <c r="B98" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C98" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D98" s="2">
         <v>3</v>
@@ -6463,7 +6490,7 @@
         <v>34</v>
       </c>
       <c r="F98" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G98" t="s">
         <v>39</v>
@@ -6478,13 +6505,13 @@
         <v>24</v>
       </c>
       <c r="K98" t="s">
+        <v>212</v>
+      </c>
+      <c r="M98" t="s">
         <v>213</v>
       </c>
-      <c r="M98" t="s">
-        <v>214</v>
-      </c>
       <c r="N98" s="7" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="O98" s="3"/>
       <c r="Q98" t="s">
@@ -6499,10 +6526,10 @@
         <v>2343027</v>
       </c>
       <c r="B99" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C99" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D99" s="2">
         <v>3</v>
@@ -6511,7 +6538,7 @@
         <v>34</v>
       </c>
       <c r="F99" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G99" t="s">
         <v>39</v>
@@ -6526,13 +6553,13 @@
         <v>24</v>
       </c>
       <c r="K99" t="s">
+        <v>214</v>
+      </c>
+      <c r="M99" t="s">
+        <v>213</v>
+      </c>
+      <c r="N99" t="s">
         <v>215</v>
-      </c>
-      <c r="M99" t="s">
-        <v>214</v>
-      </c>
-      <c r="N99" t="s">
-        <v>216</v>
       </c>
       <c r="Q99" t="s">
         <v>27</v>
@@ -6546,10 +6573,10 @@
         <v>2343027</v>
       </c>
       <c r="B100" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C100" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D100" s="2">
         <v>3</v>
@@ -6558,7 +6585,7 @@
         <v>34</v>
       </c>
       <c r="F100" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G100" t="s">
         <v>39</v>
@@ -6573,10 +6600,10 @@
         <v>24</v>
       </c>
       <c r="K100" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="M100" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="N100" s="3"/>
       <c r="O100" s="3"/>
@@ -6592,10 +6619,10 @@
         <v>2347001</v>
       </c>
       <c r="B101" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C101" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D101" s="2">
         <v>1</v>
@@ -6619,16 +6646,16 @@
         <v>41</v>
       </c>
       <c r="K101" t="s">
+        <v>217</v>
+      </c>
+      <c r="L101" t="s">
         <v>218</v>
       </c>
-      <c r="L101" t="s">
+      <c r="M101" t="s">
+        <v>26</v>
+      </c>
+      <c r="N101" t="s">
         <v>219</v>
-      </c>
-      <c r="M101" t="s">
-        <v>26</v>
-      </c>
-      <c r="N101" t="s">
-        <v>220</v>
       </c>
       <c r="Q101" t="s">
         <v>27</v>
@@ -6642,10 +6669,10 @@
         <v>2347003</v>
       </c>
       <c r="B102" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C102" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D102" s="2">
         <v>1</v>
@@ -6654,7 +6681,7 @@
         <v>20</v>
       </c>
       <c r="F102" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G102" t="s">
         <v>39</v>
@@ -6669,16 +6696,16 @@
         <v>41</v>
       </c>
       <c r="K102" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L102" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="M102" t="s">
         <v>26</v>
       </c>
       <c r="N102" s="8" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="Q102" t="s">
         <v>27</v>
@@ -6692,10 +6719,10 @@
         <v>2347005</v>
       </c>
       <c r="B103" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C103" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D103" s="2">
         <v>1</v>
@@ -6704,7 +6731,7 @@
         <v>20</v>
       </c>
       <c r="F103" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G103" t="s">
         <v>39</v>
@@ -6719,16 +6746,16 @@
         <v>41</v>
       </c>
       <c r="K103" t="s">
+        <v>222</v>
+      </c>
+      <c r="L103" t="s">
         <v>223</v>
       </c>
-      <c r="L103" t="s">
+      <c r="M103" t="s">
+        <v>26</v>
+      </c>
+      <c r="N103" s="3" t="s">
         <v>224</v>
-      </c>
-      <c r="M103" t="s">
-        <v>26</v>
-      </c>
-      <c r="N103" s="3" t="s">
-        <v>225</v>
       </c>
       <c r="O103" s="3"/>
       <c r="Q103" t="s">
@@ -6743,10 +6770,10 @@
         <v>2347006</v>
       </c>
       <c r="B104" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C104" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D104" s="2">
         <v>1</v>
@@ -6755,7 +6782,7 @@
         <v>34</v>
       </c>
       <c r="F104" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G104" t="s">
         <v>39</v>
@@ -6770,16 +6797,16 @@
         <v>41</v>
       </c>
       <c r="K104" t="s">
+        <v>226</v>
+      </c>
+      <c r="L104" t="s">
         <v>227</v>
       </c>
-      <c r="L104" t="s">
-        <v>228</v>
-      </c>
       <c r="M104" t="s">
         <v>26</v>
       </c>
       <c r="N104" s="8" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="Q104" t="s">
         <v>27</v>
@@ -6793,10 +6820,10 @@
         <v>2347007</v>
       </c>
       <c r="B105" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C105" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D105" s="2">
         <v>1</v>
@@ -6820,16 +6847,16 @@
         <v>41</v>
       </c>
       <c r="K105" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L105" t="s">
+        <v>228</v>
+      </c>
+      <c r="M105" t="s">
+        <v>26</v>
+      </c>
+      <c r="N105" s="3" t="s">
         <v>229</v>
-      </c>
-      <c r="M105" t="s">
-        <v>26</v>
-      </c>
-      <c r="N105" s="3" t="s">
-        <v>230</v>
       </c>
       <c r="O105" s="3"/>
       <c r="Q105" t="s">
@@ -6844,10 +6871,10 @@
         <v>2347013</v>
       </c>
       <c r="B106" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C106" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D106" s="2">
         <v>2</v>
@@ -6856,7 +6883,7 @@
         <v>20</v>
       </c>
       <c r="F106" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G106" t="s">
         <v>39</v>
@@ -6871,16 +6898,16 @@
         <v>41</v>
       </c>
       <c r="K106" t="s">
+        <v>231</v>
+      </c>
+      <c r="L106" t="s">
         <v>232</v>
       </c>
-      <c r="L106" t="s">
-        <v>233</v>
-      </c>
       <c r="M106" t="s">
         <v>26</v>
       </c>
       <c r="N106" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q106" t="s">
         <v>27</v>
@@ -6894,10 +6921,10 @@
         <v>2347014</v>
       </c>
       <c r="B107" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C107" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D107" s="2">
         <v>2</v>
@@ -6906,7 +6933,7 @@
         <v>34</v>
       </c>
       <c r="F107" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G107" t="s">
         <v>39</v>
@@ -6921,10 +6948,10 @@
         <v>41</v>
       </c>
       <c r="K107" t="s">
+        <v>234</v>
+      </c>
+      <c r="L107" t="s">
         <v>235</v>
-      </c>
-      <c r="L107" t="s">
-        <v>236</v>
       </c>
       <c r="M107" t="s">
         <v>26</v>
@@ -6941,10 +6968,10 @@
         <v>2347017</v>
       </c>
       <c r="B108" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C108" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D108" s="2">
         <v>2</v>
@@ -6953,7 +6980,7 @@
         <v>34</v>
       </c>
       <c r="F108" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G108" t="s">
         <v>22</v>
@@ -6968,16 +6995,16 @@
         <v>41</v>
       </c>
       <c r="K108" t="s">
+        <v>237</v>
+      </c>
+      <c r="L108" t="s">
         <v>238</v>
       </c>
-      <c r="L108" t="s">
+      <c r="M108" t="s">
+        <v>26</v>
+      </c>
+      <c r="N108" t="s">
         <v>239</v>
-      </c>
-      <c r="M108" t="s">
-        <v>26</v>
-      </c>
-      <c r="N108" t="s">
-        <v>240</v>
       </c>
       <c r="Q108" t="s">
         <v>27</v>
@@ -6991,10 +7018,10 @@
         <v>2347030</v>
       </c>
       <c r="B109" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C109" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D109" s="2">
         <v>2</v>
@@ -7003,7 +7030,7 @@
         <v>34</v>
       </c>
       <c r="F109" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G109" t="s">
         <v>39</v>
@@ -7018,16 +7045,16 @@
         <v>41</v>
       </c>
       <c r="K109" t="s">
+        <v>241</v>
+      </c>
+      <c r="L109" t="s">
         <v>242</v>
       </c>
-      <c r="L109" t="s">
-        <v>243</v>
-      </c>
       <c r="M109" t="s">
         <v>26</v>
       </c>
       <c r="N109" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="O109" s="3"/>
       <c r="Q109" t="s">
@@ -7042,10 +7069,10 @@
         <v>2347021</v>
       </c>
       <c r="B110" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C110" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D110" s="2">
         <v>3</v>
@@ -7054,7 +7081,7 @@
         <v>20</v>
       </c>
       <c r="F110" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G110" t="s">
         <v>39</v>
@@ -7069,16 +7096,16 @@
         <v>41</v>
       </c>
       <c r="K110" t="s">
+        <v>244</v>
+      </c>
+      <c r="L110" t="s">
         <v>245</v>
       </c>
-      <c r="L110" t="s">
-        <v>246</v>
-      </c>
       <c r="M110" t="s">
         <v>26</v>
       </c>
       <c r="N110" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Q110" t="s">
         <v>27</v>
@@ -7092,10 +7119,10 @@
         <v>2347022</v>
       </c>
       <c r="B111" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C111" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D111" s="2">
         <v>3</v>
@@ -7104,7 +7131,7 @@
         <v>20</v>
       </c>
       <c r="F111" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G111" t="s">
         <v>39</v>
@@ -7119,16 +7146,16 @@
         <v>41</v>
       </c>
       <c r="K111" t="s">
+        <v>247</v>
+      </c>
+      <c r="L111" t="s">
         <v>248</v>
       </c>
-      <c r="L111" t="s">
+      <c r="M111" t="s">
+        <v>26</v>
+      </c>
+      <c r="N111" s="3" t="s">
         <v>249</v>
-      </c>
-      <c r="M111" t="s">
-        <v>26</v>
-      </c>
-      <c r="N111" s="3" t="s">
-        <v>250</v>
       </c>
       <c r="O111" s="3"/>
       <c r="P111" s="1"/>
@@ -7144,10 +7171,10 @@
         <v>2347024</v>
       </c>
       <c r="B112" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C112" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D112" s="2">
         <v>3</v>
@@ -7156,7 +7183,7 @@
         <v>20</v>
       </c>
       <c r="F112" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G112" t="s">
         <v>39</v>
@@ -7171,16 +7198,16 @@
         <v>41</v>
       </c>
       <c r="K112" t="s">
+        <v>251</v>
+      </c>
+      <c r="L112" t="s">
         <v>252</v>
       </c>
-      <c r="L112" t="s">
-        <v>253</v>
-      </c>
       <c r="M112" t="s">
         <v>26</v>
       </c>
       <c r="N112" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Q112" t="s">
         <v>27</v>
@@ -7194,10 +7221,10 @@
         <v>2347026</v>
       </c>
       <c r="B113" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C113" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D113" s="2">
         <v>3</v>
@@ -7206,7 +7233,7 @@
         <v>34</v>
       </c>
       <c r="F113" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G113" t="s">
         <v>39</v>
@@ -7221,16 +7248,16 @@
         <v>41</v>
       </c>
       <c r="K113" t="s">
+        <v>254</v>
+      </c>
+      <c r="L113" t="s">
         <v>255</v>
       </c>
-      <c r="L113" t="s">
-        <v>256</v>
-      </c>
       <c r="M113" t="s">
         <v>26</v>
       </c>
       <c r="N113" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O113" s="3"/>
       <c r="Q113" t="s">
@@ -7245,10 +7272,10 @@
         <v>2347027</v>
       </c>
       <c r="B114" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C114" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D114" s="2">
         <v>3</v>
@@ -7257,7 +7284,7 @@
         <v>34</v>
       </c>
       <c r="F114" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G114" t="s">
         <v>39</v>
@@ -7272,16 +7299,16 @@
         <v>41</v>
       </c>
       <c r="K114" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="L114" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="M114" t="s">
         <v>26</v>
       </c>
       <c r="N114" s="7" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="O114" s="7"/>
       <c r="Q114" t="s">
@@ -7296,10 +7323,10 @@
         <v>2347029</v>
       </c>
       <c r="B115" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C115" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D115" s="2">
         <v>3</v>
@@ -7308,7 +7335,7 @@
         <v>34</v>
       </c>
       <c r="F115" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G115" t="s">
         <v>39</v>
@@ -7323,16 +7350,16 @@
         <v>41</v>
       </c>
       <c r="K115" t="s">
+        <v>259</v>
+      </c>
+      <c r="L115" t="s">
         <v>260</v>
       </c>
-      <c r="L115" t="s">
+      <c r="M115" t="s">
+        <v>213</v>
+      </c>
+      <c r="N115" t="s">
         <v>261</v>
-      </c>
-      <c r="M115" t="s">
-        <v>214</v>
-      </c>
-      <c r="N115" t="s">
-        <v>262</v>
       </c>
       <c r="Q115" t="s">
         <v>27</v>
@@ -7346,10 +7373,10 @@
         <v>2347031</v>
       </c>
       <c r="B116" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C116" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D116" s="2">
         <v>4</v>
@@ -7358,7 +7385,7 @@
         <v>20</v>
       </c>
       <c r="F116" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G116" t="s">
         <v>39</v>
@@ -7373,16 +7400,16 @@
         <v>41</v>
       </c>
       <c r="K116" t="s">
+        <v>263</v>
+      </c>
+      <c r="L116" t="s">
         <v>264</v>
       </c>
-      <c r="L116" t="s">
-        <v>265</v>
-      </c>
       <c r="M116" t="s">
         <v>26</v>
       </c>
       <c r="N116" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Q116" t="s">
         <v>27</v>
@@ -7396,10 +7423,10 @@
         <v>2347038</v>
       </c>
       <c r="B117" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C117" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D117" s="2">
         <v>4</v>
@@ -7408,10 +7435,10 @@
         <v>20</v>
       </c>
       <c r="F117" t="s">
+        <v>265</v>
+      </c>
+      <c r="G117" t="s">
         <v>266</v>
-      </c>
-      <c r="G117" t="s">
-        <v>267</v>
       </c>
       <c r="H117" s="2">
         <v>60</v>
@@ -7423,16 +7450,16 @@
         <v>41</v>
       </c>
       <c r="K117" t="s">
+        <v>267</v>
+      </c>
+      <c r="L117" t="s">
         <v>268</v>
       </c>
-      <c r="L117" t="s">
-        <v>269</v>
-      </c>
       <c r="M117" t="s">
         <v>26</v>
       </c>
       <c r="N117" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O117" s="3"/>
       <c r="Q117" t="s">
@@ -7447,10 +7474,10 @@
         <v>2361002</v>
       </c>
       <c r="B118" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C118" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D118" s="2">
         <v>1</v>
@@ -7474,7 +7501,7 @@
         <v>41</v>
       </c>
       <c r="K118" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="M118" t="s">
         <v>26</v>
@@ -7491,10 +7518,10 @@
         <v>2361002</v>
       </c>
       <c r="B119" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C119" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D119" s="2">
         <v>1</v>
@@ -7518,7 +7545,7 @@
         <v>41</v>
       </c>
       <c r="K119" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="M119" t="s">
         <v>26</v>
@@ -7535,10 +7562,10 @@
         <v>2361002</v>
       </c>
       <c r="B120" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C120" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D120" s="2">
         <v>1</v>
@@ -7562,7 +7589,7 @@
         <v>41</v>
       </c>
       <c r="K120" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="M120" t="s">
         <v>26</v>
@@ -7579,10 +7606,10 @@
         <v>2361004</v>
       </c>
       <c r="B121" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C121" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D121" s="2">
         <v>1</v>
@@ -7591,7 +7618,7 @@
         <v>20</v>
       </c>
       <c r="F121" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G121" t="s">
         <v>22</v>
@@ -7606,7 +7633,7 @@
         <v>41</v>
       </c>
       <c r="K121" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="M121" t="s">
         <v>26</v>
@@ -7623,10 +7650,10 @@
         <v>2393002</v>
       </c>
       <c r="B122" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C122" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D122" s="2">
         <v>1</v>
@@ -7635,7 +7662,7 @@
         <v>20</v>
       </c>
       <c r="F122" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G122" t="s">
         <v>22</v>
@@ -7650,10 +7677,10 @@
         <v>41</v>
       </c>
       <c r="K122" t="s">
+        <v>274</v>
+      </c>
+      <c r="L122" t="s">
         <v>275</v>
-      </c>
-      <c r="L122" t="s">
-        <v>276</v>
       </c>
       <c r="M122" t="s">
         <v>26</v>
@@ -7670,10 +7697,10 @@
         <v>2393002</v>
       </c>
       <c r="B123" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C123" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D123" s="2">
         <v>1</v>
@@ -7682,7 +7709,7 @@
         <v>20</v>
       </c>
       <c r="F123" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G123" t="s">
         <v>22</v>
@@ -7691,16 +7718,16 @@
         <v>20</v>
       </c>
       <c r="I123" t="s">
+        <v>276</v>
+      </c>
+      <c r="J123" t="s">
+        <v>41</v>
+      </c>
+      <c r="K123" t="s">
         <v>277</v>
       </c>
-      <c r="J123" t="s">
-        <v>41</v>
-      </c>
-      <c r="K123" t="s">
+      <c r="L123" t="s">
         <v>278</v>
-      </c>
-      <c r="L123" t="s">
-        <v>279</v>
       </c>
       <c r="M123" t="s">
         <v>26</v>
@@ -7717,10 +7744,10 @@
         <v>2393002</v>
       </c>
       <c r="B124" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C124" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D124" s="2">
         <v>1</v>
@@ -7729,7 +7756,7 @@
         <v>20</v>
       </c>
       <c r="F124" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G124" t="s">
         <v>22</v>
@@ -7738,16 +7765,16 @@
         <v>20</v>
       </c>
       <c r="I124" t="s">
+        <v>279</v>
+      </c>
+      <c r="J124" t="s">
+        <v>41</v>
+      </c>
+      <c r="K124" t="s">
         <v>280</v>
       </c>
-      <c r="J124" t="s">
-        <v>41</v>
-      </c>
-      <c r="K124" t="s">
-        <v>281</v>
-      </c>
       <c r="L124" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="M124" t="s">
         <v>26</v>
@@ -7764,10 +7791,10 @@
         <v>2394004</v>
       </c>
       <c r="B125" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C125" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D125" s="2">
         <v>1</v>
@@ -7776,7 +7803,7 @@
         <v>20</v>
       </c>
       <c r="F125" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G125" t="s">
         <v>22</v>
@@ -7791,10 +7818,10 @@
         <v>24</v>
       </c>
       <c r="K125" t="s">
+        <v>282</v>
+      </c>
+      <c r="L125" t="s">
         <v>283</v>
-      </c>
-      <c r="L125" t="s">
-        <v>284</v>
       </c>
       <c r="M125" t="s">
         <v>26</v>
@@ -7811,10 +7838,10 @@
         <v>2394004</v>
       </c>
       <c r="B126" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C126" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D126" s="2">
         <v>1</v>
@@ -7823,7 +7850,7 @@
         <v>20</v>
       </c>
       <c r="F126" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G126" t="s">
         <v>22</v>
@@ -7838,10 +7865,10 @@
         <v>24</v>
       </c>
       <c r="K126" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="L126" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="M126" t="s">
         <v>26</v>
@@ -7858,10 +7885,10 @@
         <v>2394004</v>
       </c>
       <c r="B127" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C127" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D127" s="2">
         <v>1</v>
@@ -7870,7 +7897,7 @@
         <v>20</v>
       </c>
       <c r="F127" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G127" t="s">
         <v>22</v>
@@ -7885,10 +7912,10 @@
         <v>24</v>
       </c>
       <c r="K127" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="L127" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="M127" t="s">
         <v>26</v>
@@ -7905,10 +7932,10 @@
         <v>2395003</v>
       </c>
       <c r="B128" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C128" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D128" s="2">
         <v>1</v>
@@ -7917,7 +7944,7 @@
         <v>20</v>
       </c>
       <c r="F128" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G128" t="s">
         <v>22</v>
@@ -7932,10 +7959,10 @@
         <v>41</v>
       </c>
       <c r="K128" t="s">
+        <v>287</v>
+      </c>
+      <c r="L128" t="s">
         <v>288</v>
-      </c>
-      <c r="L128" t="s">
-        <v>289</v>
       </c>
       <c r="M128" t="s">
         <v>26</v>
@@ -7952,10 +7979,10 @@
         <v>2395003</v>
       </c>
       <c r="B129" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C129" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D129" s="2">
         <v>1</v>
@@ -7964,7 +7991,7 @@
         <v>20</v>
       </c>
       <c r="F129" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G129" t="s">
         <v>22</v>
@@ -7979,10 +8006,10 @@
         <v>41</v>
       </c>
       <c r="K129" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="L129" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="M129" t="s">
         <v>26</v>
@@ -7999,10 +8026,10 @@
         <v>2395003</v>
       </c>
       <c r="B130" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C130" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D130" s="2">
         <v>1</v>
@@ -8011,7 +8038,7 @@
         <v>20</v>
       </c>
       <c r="F130" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G130" t="s">
         <v>22</v>
@@ -8026,10 +8053,10 @@
         <v>41</v>
       </c>
       <c r="K130" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L130" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="M130" t="s">
         <v>26</v>
@@ -8046,10 +8073,10 @@
         <v>2396001</v>
       </c>
       <c r="B131" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C131" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D131" s="2">
         <v>1</v>
@@ -8058,7 +8085,7 @@
         <v>20</v>
       </c>
       <c r="F131" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G131" t="s">
         <v>22</v>
@@ -8073,10 +8100,10 @@
         <v>24</v>
       </c>
       <c r="K131" t="s">
+        <v>292</v>
+      </c>
+      <c r="L131" t="s">
         <v>293</v>
-      </c>
-      <c r="L131" t="s">
-        <v>294</v>
       </c>
       <c r="M131" t="s">
         <v>26</v>
@@ -8093,10 +8120,10 @@
         <v>2396001</v>
       </c>
       <c r="B132" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C132" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D132" s="2">
         <v>1</v>
@@ -8105,7 +8132,7 @@
         <v>20</v>
       </c>
       <c r="F132" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G132" t="s">
         <v>22</v>
@@ -8120,10 +8147,10 @@
         <v>24</v>
       </c>
       <c r="K132" t="s">
+        <v>294</v>
+      </c>
+      <c r="L132" t="s">
         <v>295</v>
-      </c>
-      <c r="L132" t="s">
-        <v>296</v>
       </c>
       <c r="M132" t="s">
         <v>26</v>
@@ -8140,10 +8167,10 @@
         <v>2396001</v>
       </c>
       <c r="B133" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C133" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D133" s="2">
         <v>1</v>
@@ -8152,7 +8179,7 @@
         <v>20</v>
       </c>
       <c r="F133" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G133" t="s">
         <v>22</v>
@@ -8167,10 +8194,10 @@
         <v>24</v>
       </c>
       <c r="K133" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="L133" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="M133" t="s">
         <v>26</v>
@@ -8187,10 +8214,10 @@
         <v>2397003</v>
       </c>
       <c r="B134" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C134" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D134" s="2">
         <v>1</v>
@@ -8214,16 +8241,16 @@
         <v>24</v>
       </c>
       <c r="K134" t="s">
+        <v>298</v>
+      </c>
+      <c r="L134" t="s">
         <v>299</v>
       </c>
-      <c r="L134" t="s">
+      <c r="M134" t="s">
+        <v>26</v>
+      </c>
+      <c r="N134" t="s">
         <v>300</v>
-      </c>
-      <c r="M134" t="s">
-        <v>26</v>
-      </c>
-      <c r="N134" t="s">
-        <v>301</v>
       </c>
       <c r="Q134" t="s">
         <v>27</v>
@@ -8237,10 +8264,10 @@
         <v>2397003</v>
       </c>
       <c r="B135" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C135" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D135" s="2">
         <v>1</v>
@@ -8264,16 +8291,16 @@
         <v>24</v>
       </c>
       <c r="K135" t="s">
+        <v>301</v>
+      </c>
+      <c r="L135" t="s">
         <v>302</v>
       </c>
-      <c r="L135" t="s">
+      <c r="M135" t="s">
+        <v>26</v>
+      </c>
+      <c r="N135" t="s">
         <v>303</v>
-      </c>
-      <c r="M135" t="s">
-        <v>26</v>
-      </c>
-      <c r="N135" t="s">
-        <v>304</v>
       </c>
       <c r="Q135" t="s">
         <v>27</v>
@@ -8287,10 +8314,10 @@
         <v>2397003</v>
       </c>
       <c r="B136" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C136" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D136" s="2">
         <v>1</v>
@@ -8314,16 +8341,16 @@
         <v>24</v>
       </c>
       <c r="K136" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L136" t="s">
+        <v>302</v>
+      </c>
+      <c r="M136" t="s">
+        <v>26</v>
+      </c>
+      <c r="N136" t="s">
         <v>303</v>
-      </c>
-      <c r="M136" t="s">
-        <v>26</v>
-      </c>
-      <c r="N136" t="s">
-        <v>304</v>
       </c>
       <c r="Q136" t="s">
         <v>27</v>
@@ -8337,10 +8364,10 @@
         <v>2397008</v>
       </c>
       <c r="B137" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C137" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D137" s="2">
         <v>1</v>
@@ -8364,10 +8391,10 @@
         <v>24</v>
       </c>
       <c r="K137" t="s">
+        <v>305</v>
+      </c>
+      <c r="L137" t="s">
         <v>306</v>
-      </c>
-      <c r="L137" t="s">
-        <v>307</v>
       </c>
       <c r="M137" t="s">
         <v>26</v>
@@ -8384,10 +8411,10 @@
         <v>2397008</v>
       </c>
       <c r="B138" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C138" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D138" s="2">
         <v>1</v>
@@ -8411,10 +8438,10 @@
         <v>24</v>
       </c>
       <c r="K138" t="s">
+        <v>307</v>
+      </c>
+      <c r="L138" t="s">
         <v>308</v>
-      </c>
-      <c r="L138" t="s">
-        <v>309</v>
       </c>
       <c r="M138" t="s">
         <v>26</v>
@@ -8431,10 +8458,10 @@
         <v>2397008</v>
       </c>
       <c r="B139" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C139" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D139" s="2">
         <v>1</v>
@@ -8458,10 +8485,10 @@
         <v>24</v>
       </c>
       <c r="K139" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="L139" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="M139" t="s">
         <v>26</v>
@@ -8478,10 +8505,10 @@
         <v>2398001</v>
       </c>
       <c r="B140" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C140" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D140" s="2">
         <v>1</v>
@@ -8505,16 +8532,16 @@
         <v>41</v>
       </c>
       <c r="K140" t="s">
+        <v>311</v>
+      </c>
+      <c r="L140" t="s">
         <v>312</v>
       </c>
-      <c r="L140" t="s">
+      <c r="M140" t="s">
+        <v>26</v>
+      </c>
+      <c r="N140" t="s">
         <v>313</v>
-      </c>
-      <c r="M140" t="s">
-        <v>26</v>
-      </c>
-      <c r="N140" t="s">
-        <v>314</v>
       </c>
       <c r="Q140" t="s">
         <v>27</v>
@@ -8528,10 +8555,10 @@
         <v>2398001</v>
       </c>
       <c r="B141" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C141" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D141" s="2">
         <v>1</v>
@@ -8555,16 +8582,16 @@
         <v>41</v>
       </c>
       <c r="K141" t="s">
+        <v>314</v>
+      </c>
+      <c r="L141" t="s">
+        <v>312</v>
+      </c>
+      <c r="M141" t="s">
+        <v>26</v>
+      </c>
+      <c r="N141" s="4" t="s">
         <v>315</v>
-      </c>
-      <c r="L141" t="s">
-        <v>313</v>
-      </c>
-      <c r="M141" t="s">
-        <v>26</v>
-      </c>
-      <c r="N141" s="4" t="s">
-        <v>316</v>
       </c>
       <c r="O141" s="4"/>
       <c r="Q141" t="s">
@@ -8579,10 +8606,10 @@
         <v>2398001</v>
       </c>
       <c r="B142" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C142" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D142" s="2">
         <v>1</v>
@@ -8606,16 +8633,16 @@
         <v>41</v>
       </c>
       <c r="K142" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="L142" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="M142" t="s">
         <v>26</v>
       </c>
       <c r="N142" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O142" s="4"/>
       <c r="Q142" t="s">
@@ -8630,10 +8657,10 @@
         <v>2398006</v>
       </c>
       <c r="B143" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C143" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D143" s="2">
         <v>1</v>
@@ -8657,10 +8684,10 @@
         <v>41</v>
       </c>
       <c r="K143" t="s">
+        <v>317</v>
+      </c>
+      <c r="L143" t="s">
         <v>318</v>
-      </c>
-      <c r="L143" t="s">
-        <v>319</v>
       </c>
       <c r="M143" t="s">
         <v>26</v>
@@ -8677,10 +8704,10 @@
         <v>2398006</v>
       </c>
       <c r="B144" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C144" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D144" s="2">
         <v>1</v>
@@ -8704,10 +8731,10 @@
         <v>41</v>
       </c>
       <c r="K144" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="L144" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="M144" t="s">
         <v>26</v>
@@ -8724,10 +8751,10 @@
         <v>2398006</v>
       </c>
       <c r="B145" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C145" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D145" s="2">
         <v>1</v>
@@ -8751,10 +8778,10 @@
         <v>41</v>
       </c>
       <c r="K145" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="L145" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="M145" t="s">
         <v>26</v>
@@ -8771,10 +8798,10 @@
         <v>2398013</v>
       </c>
       <c r="B146" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C146" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D146" s="2">
         <v>2</v>
@@ -8783,7 +8810,7 @@
         <v>20</v>
       </c>
       <c r="F146" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G146" t="s">
         <v>22</v>
@@ -8798,10 +8825,10 @@
         <v>24</v>
       </c>
       <c r="K146" t="s">
+        <v>321</v>
+      </c>
+      <c r="L146" t="s">
         <v>322</v>
-      </c>
-      <c r="L146" t="s">
-        <v>323</v>
       </c>
       <c r="M146" t="s">
         <v>26</v>
@@ -8818,10 +8845,10 @@
         <v>2398013</v>
       </c>
       <c r="B147" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C147" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D147" s="2">
         <v>2</v>
@@ -8830,7 +8857,7 @@
         <v>20</v>
       </c>
       <c r="F147" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G147" t="s">
         <v>22</v>
@@ -8845,10 +8872,10 @@
         <v>24</v>
       </c>
       <c r="K147" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="L147" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="M147" t="s">
         <v>26</v>
@@ -8865,10 +8892,10 @@
         <v>2398013</v>
       </c>
       <c r="B148" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C148" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D148" s="2">
         <v>2</v>
@@ -8877,7 +8904,7 @@
         <v>20</v>
       </c>
       <c r="F148" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G148" t="s">
         <v>22</v>
@@ -8892,7 +8919,7 @@
         <v>24</v>
       </c>
       <c r="K148" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="M148" t="s">
         <v>26</v>
@@ -8909,10 +8936,10 @@
         <v>2399003</v>
       </c>
       <c r="B149" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C149" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D149" s="2">
         <v>1</v>
@@ -8936,10 +8963,10 @@
         <v>41</v>
       </c>
       <c r="K149" t="s">
+        <v>326</v>
+      </c>
+      <c r="L149" t="s">
         <v>327</v>
-      </c>
-      <c r="L149" t="s">
-        <v>328</v>
       </c>
       <c r="M149" t="s">
         <v>26</v>
@@ -8956,10 +8983,10 @@
         <v>2399003</v>
       </c>
       <c r="B150" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C150" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D150" s="2">
         <v>1</v>
@@ -8983,10 +9010,10 @@
         <v>41</v>
       </c>
       <c r="K150" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="L150" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="M150" t="s">
         <v>26</v>
@@ -9003,10 +9030,10 @@
         <v>2399003</v>
       </c>
       <c r="B151" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C151" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D151" s="2">
         <v>1</v>
@@ -9030,10 +9057,10 @@
         <v>41</v>
       </c>
       <c r="K151" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="L151" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="M151" t="s">
         <v>26</v>
@@ -9050,10 +9077,10 @@
         <v>2399010</v>
       </c>
       <c r="B152" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C152" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D152" s="2">
         <v>1</v>
@@ -9077,10 +9104,10 @@
         <v>41</v>
       </c>
       <c r="K152" t="s">
+        <v>330</v>
+      </c>
+      <c r="L152" t="s">
         <v>331</v>
-      </c>
-      <c r="L152" t="s">
-        <v>332</v>
       </c>
       <c r="M152" t="s">
         <v>26</v>
@@ -9097,10 +9124,10 @@
         <v>2399010</v>
       </c>
       <c r="B153" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C153" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D153" s="2">
         <v>1</v>
@@ -9124,10 +9151,10 @@
         <v>41</v>
       </c>
       <c r="K153" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="L153" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="M153" t="s">
         <v>26</v>
@@ -9144,10 +9171,10 @@
         <v>2399010</v>
       </c>
       <c r="B154" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C154" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D154" s="2">
         <v>1</v>
@@ -9171,10 +9198,10 @@
         <v>41</v>
       </c>
       <c r="K154" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="L154" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="M154" t="s">
         <v>26</v>
@@ -9191,10 +9218,10 @@
         <v>2399014</v>
       </c>
       <c r="B155" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C155" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D155" s="2">
         <v>2</v>
@@ -9203,7 +9230,7 @@
         <v>20</v>
       </c>
       <c r="F155" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G155" t="s">
         <v>22</v>
@@ -9218,10 +9245,10 @@
         <v>24</v>
       </c>
       <c r="K155" t="s">
+        <v>334</v>
+      </c>
+      <c r="L155" t="s">
         <v>335</v>
-      </c>
-      <c r="L155" t="s">
-        <v>336</v>
       </c>
       <c r="M155" t="s">
         <v>26</v>
@@ -9238,10 +9265,10 @@
         <v>2399014</v>
       </c>
       <c r="B156" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C156" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D156" s="2">
         <v>2</v>
@@ -9250,7 +9277,7 @@
         <v>20</v>
       </c>
       <c r="F156" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G156" t="s">
         <v>22</v>
@@ -9265,10 +9292,10 @@
         <v>24</v>
       </c>
       <c r="K156" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="L156" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="M156" t="s">
         <v>26</v>
@@ -9285,10 +9312,10 @@
         <v>2399014</v>
       </c>
       <c r="B157" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C157" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D157" s="2">
         <v>2</v>
@@ -9297,7 +9324,7 @@
         <v>20</v>
       </c>
       <c r="F157" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G157" t="s">
         <v>22</v>
@@ -9312,7 +9339,7 @@
         <v>24</v>
       </c>
       <c r="K157" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="M157" t="s">
         <v>26</v>
@@ -9329,10 +9356,10 @@
         <v>2400003</v>
       </c>
       <c r="B158" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C158" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D158" s="2">
         <v>1</v>
@@ -9356,16 +9383,16 @@
         <v>41</v>
       </c>
       <c r="K158" t="s">
+        <v>339</v>
+      </c>
+      <c r="L158" t="s">
         <v>340</v>
       </c>
-      <c r="L158" t="s">
-        <v>341</v>
-      </c>
       <c r="M158" t="s">
         <v>26</v>
       </c>
       <c r="N158" s="8" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="Q158" t="s">
         <v>27</v>
@@ -9379,10 +9406,10 @@
         <v>2400003</v>
       </c>
       <c r="B159" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C159" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D159" s="2">
         <v>1</v>
@@ -9406,16 +9433,16 @@
         <v>41</v>
       </c>
       <c r="K159" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="L159" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="M159" t="s">
         <v>26</v>
       </c>
       <c r="N159" s="8" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="Q159" t="s">
         <v>27</v>
@@ -9429,10 +9456,10 @@
         <v>2400003</v>
       </c>
       <c r="B160" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C160" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D160" s="2">
         <v>1</v>
@@ -9456,16 +9483,16 @@
         <v>41</v>
       </c>
       <c r="K160" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="L160" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="M160" t="s">
         <v>26</v>
       </c>
       <c r="N160" s="8" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="Q160" t="s">
         <v>27</v>
@@ -9479,10 +9506,10 @@
         <v>2400008</v>
       </c>
       <c r="B161" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C161" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D161" s="2">
         <v>1</v>
@@ -9506,10 +9533,10 @@
         <v>41</v>
       </c>
       <c r="K161" t="s">
+        <v>343</v>
+      </c>
+      <c r="L161" t="s">
         <v>344</v>
-      </c>
-      <c r="L161" t="s">
-        <v>345</v>
       </c>
       <c r="M161" t="s">
         <v>26</v>
@@ -9526,10 +9553,10 @@
         <v>2400008</v>
       </c>
       <c r="B162" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C162" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D162" s="2">
         <v>1</v>
@@ -9553,10 +9580,10 @@
         <v>41</v>
       </c>
       <c r="K162" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="L162" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="M162" t="s">
         <v>26</v>
@@ -9573,10 +9600,10 @@
         <v>2400008</v>
       </c>
       <c r="B163" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C163" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D163" s="2">
         <v>1</v>
@@ -9600,10 +9627,10 @@
         <v>41</v>
       </c>
       <c r="K163" t="s">
+        <v>346</v>
+      </c>
+      <c r="L163" t="s">
         <v>347</v>
-      </c>
-      <c r="L163" t="s">
-        <v>348</v>
       </c>
       <c r="M163" t="s">
         <v>26</v>
@@ -9620,10 +9647,10 @@
         <v>2400012</v>
       </c>
       <c r="B164" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C164" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D164" s="2">
         <v>2</v>
@@ -9632,7 +9659,7 @@
         <v>20</v>
       </c>
       <c r="F164" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G164" t="s">
         <v>22</v>
@@ -9647,16 +9674,16 @@
         <v>24</v>
       </c>
       <c r="K164" t="s">
+        <v>348</v>
+      </c>
+      <c r="L164" t="s">
         <v>349</v>
       </c>
-      <c r="L164" t="s">
+      <c r="M164" t="s">
+        <v>26</v>
+      </c>
+      <c r="N164" t="s">
         <v>350</v>
-      </c>
-      <c r="M164" t="s">
-        <v>26</v>
-      </c>
-      <c r="N164" t="s">
-        <v>351</v>
       </c>
       <c r="Q164" t="s">
         <v>27</v>
@@ -9670,10 +9697,10 @@
         <v>2400012</v>
       </c>
       <c r="B165" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C165" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D165" s="2">
         <v>2</v>
@@ -9682,7 +9709,7 @@
         <v>20</v>
       </c>
       <c r="F165" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G165" t="s">
         <v>22</v>
@@ -9697,16 +9724,16 @@
         <v>24</v>
       </c>
       <c r="K165" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="L165" t="s">
+        <v>349</v>
+      </c>
+      <c r="M165" t="s">
+        <v>26</v>
+      </c>
+      <c r="N165" t="s">
         <v>352</v>
-      </c>
-      <c r="L165" t="s">
-        <v>350</v>
-      </c>
-      <c r="M165" t="s">
-        <v>26</v>
-      </c>
-      <c r="N165" t="s">
-        <v>353</v>
       </c>
       <c r="Q165" t="s">
         <v>27</v>
@@ -9720,10 +9747,10 @@
         <v>2400012</v>
       </c>
       <c r="B166" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C166" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D166" s="2">
         <v>2</v>
@@ -9732,7 +9759,7 @@
         <v>20</v>
       </c>
       <c r="F166" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G166" t="s">
         <v>22</v>
@@ -9747,13 +9774,13 @@
         <v>24</v>
       </c>
       <c r="K166" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="M166" t="s">
         <v>26</v>
       </c>
       <c r="N166" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="Q166" t="s">
         <v>27</v>
@@ -9767,10 +9794,10 @@
         <v>2401001</v>
       </c>
       <c r="B167" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C167" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D167" s="2">
         <v>1</v>
@@ -9794,10 +9821,10 @@
         <v>24</v>
       </c>
       <c r="K167" t="s">
+        <v>355</v>
+      </c>
+      <c r="L167" t="s">
         <v>356</v>
-      </c>
-      <c r="L167" t="s">
-        <v>357</v>
       </c>
       <c r="M167" t="s">
         <v>26</v>
@@ -9814,10 +9841,10 @@
         <v>2401001</v>
       </c>
       <c r="B168" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C168" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D168" s="2">
         <v>1</v>
@@ -9841,10 +9868,10 @@
         <v>24</v>
       </c>
       <c r="K168" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="L168" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="M168" t="s">
         <v>26</v>
@@ -9861,10 +9888,10 @@
         <v>2401001</v>
       </c>
       <c r="B169" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C169" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D169" s="2">
         <v>1</v>
@@ -9888,10 +9915,10 @@
         <v>24</v>
       </c>
       <c r="K169" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="L169" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="M169" t="s">
         <v>26</v>
@@ -9908,10 +9935,10 @@
         <v>2401007</v>
       </c>
       <c r="B170" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C170" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D170" s="2">
         <v>1</v>
@@ -9935,10 +9962,10 @@
         <v>24</v>
       </c>
       <c r="K170" t="s">
+        <v>359</v>
+      </c>
+      <c r="L170" t="s">
         <v>360</v>
-      </c>
-      <c r="L170" t="s">
-        <v>361</v>
       </c>
       <c r="M170" t="s">
         <v>26</v>
@@ -9955,10 +9982,10 @@
         <v>2401007</v>
       </c>
       <c r="B171" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C171" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D171" s="2">
         <v>1</v>
@@ -9982,10 +10009,10 @@
         <v>24</v>
       </c>
       <c r="K171" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="L171" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="M171" t="s">
         <v>26</v>
@@ -10002,10 +10029,10 @@
         <v>2401007</v>
       </c>
       <c r="B172" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C172" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D172" s="2">
         <v>1</v>
@@ -10029,10 +10056,10 @@
         <v>24</v>
       </c>
       <c r="K172" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="L172" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="M172" t="s">
         <v>26</v>
@@ -10049,10 +10076,10 @@
         <v>2401013</v>
       </c>
       <c r="B173" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C173" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D173" s="2">
         <v>2</v>
@@ -10061,7 +10088,7 @@
         <v>20</v>
       </c>
       <c r="F173" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G173" t="s">
         <v>39</v>
@@ -10076,16 +10103,16 @@
         <v>41</v>
       </c>
       <c r="K173" t="s">
+        <v>364</v>
+      </c>
+      <c r="L173" t="s">
         <v>365</v>
       </c>
-      <c r="L173" t="s">
+      <c r="M173" t="s">
+        <v>26</v>
+      </c>
+      <c r="N173" t="s">
         <v>366</v>
-      </c>
-      <c r="M173" t="s">
-        <v>26</v>
-      </c>
-      <c r="N173" t="s">
-        <v>367</v>
       </c>
       <c r="Q173" t="s">
         <v>27</v>
@@ -10099,10 +10126,10 @@
         <v>2401013</v>
       </c>
       <c r="B174" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C174" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D174" s="2">
         <v>2</v>
@@ -10111,7 +10138,7 @@
         <v>20</v>
       </c>
       <c r="F174" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G174" t="s">
         <v>39</v>
@@ -10126,16 +10153,16 @@
         <v>41</v>
       </c>
       <c r="K174" t="s">
+        <v>367</v>
+      </c>
+      <c r="L174" t="s">
+        <v>365</v>
+      </c>
+      <c r="M174" t="s">
+        <v>26</v>
+      </c>
+      <c r="N174" t="s">
         <v>368</v>
-      </c>
-      <c r="L174" t="s">
-        <v>366</v>
-      </c>
-      <c r="M174" t="s">
-        <v>26</v>
-      </c>
-      <c r="N174" t="s">
-        <v>369</v>
       </c>
       <c r="Q174" t="s">
         <v>27</v>
@@ -10149,10 +10176,10 @@
         <v>2401013</v>
       </c>
       <c r="B175" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C175" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D175" s="2">
         <v>2</v>
@@ -10161,7 +10188,7 @@
         <v>20</v>
       </c>
       <c r="F175" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G175" t="s">
         <v>39</v>
@@ -10176,16 +10203,16 @@
         <v>41</v>
       </c>
       <c r="K175" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="L175" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="M175" t="s">
         <v>26</v>
       </c>
       <c r="N175" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="Q175" t="s">
         <v>27</v>
@@ -10199,10 +10226,10 @@
         <v>2401018</v>
       </c>
       <c r="B176" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C176" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D176" s="2">
         <v>2</v>
@@ -10211,7 +10238,7 @@
         <v>34</v>
       </c>
       <c r="F176" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G176" t="s">
         <v>39</v>
@@ -10226,10 +10253,10 @@
         <v>41</v>
       </c>
       <c r="K176" t="s">
+        <v>371</v>
+      </c>
+      <c r="L176" t="s">
         <v>372</v>
-      </c>
-      <c r="L176" t="s">
-        <v>373</v>
       </c>
       <c r="M176" t="s">
         <v>26</v>
@@ -10246,10 +10273,10 @@
         <v>2401018</v>
       </c>
       <c r="B177" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C177" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D177" s="2">
         <v>2</v>
@@ -10258,7 +10285,7 @@
         <v>34</v>
       </c>
       <c r="F177" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G177" t="s">
         <v>39</v>
@@ -10273,10 +10300,10 @@
         <v>41</v>
       </c>
       <c r="K177" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="L177" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="M177" t="s">
         <v>26</v>
@@ -10293,10 +10320,10 @@
         <v>2401018</v>
       </c>
       <c r="B178" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C178" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D178" s="2">
         <v>2</v>
@@ -10305,7 +10332,7 @@
         <v>34</v>
       </c>
       <c r="F178" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G178" t="s">
         <v>39</v>
@@ -10314,16 +10341,16 @@
         <v>4</v>
       </c>
       <c r="I178" t="s">
+        <v>374</v>
+      </c>
+      <c r="J178" t="s">
+        <v>41</v>
+      </c>
+      <c r="K178" t="s">
         <v>375</v>
       </c>
-      <c r="J178" t="s">
-        <v>41</v>
-      </c>
-      <c r="K178" t="s">
-        <v>376</v>
-      </c>
       <c r="L178" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="M178" t="s">
         <v>26</v>
@@ -10340,10 +10367,10 @@
         <v>2401018</v>
       </c>
       <c r="B179" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C179" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D179" s="2">
         <v>2</v>
@@ -10352,7 +10379,7 @@
         <v>34</v>
       </c>
       <c r="F179" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G179" t="s">
         <v>39</v>
@@ -10367,10 +10394,10 @@
         <v>41</v>
       </c>
       <c r="K179" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="L179" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="M179" t="s">
         <v>26</v>
@@ -10387,10 +10414,10 @@
         <v>2401018</v>
       </c>
       <c r="B180" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C180" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D180" s="2">
         <v>2</v>
@@ -10399,7 +10426,7 @@
         <v>34</v>
       </c>
       <c r="F180" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G180" t="s">
         <v>39</v>
@@ -10408,16 +10435,16 @@
         <v>4</v>
       </c>
       <c r="I180" t="s">
+        <v>377</v>
+      </c>
+      <c r="J180" t="s">
+        <v>41</v>
+      </c>
+      <c r="K180" t="s">
         <v>378</v>
       </c>
-      <c r="J180" t="s">
-        <v>41</v>
-      </c>
-      <c r="K180" t="s">
-        <v>379</v>
-      </c>
       <c r="L180" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="M180" t="s">
         <v>26</v>
@@ -10434,10 +10461,10 @@
         <v>2401018</v>
       </c>
       <c r="B181" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C181" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D181" s="2">
         <v>2</v>
@@ -10446,7 +10473,7 @@
         <v>34</v>
       </c>
       <c r="F181" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G181" t="s">
         <v>39</v>
@@ -10455,16 +10482,16 @@
         <v>4</v>
       </c>
       <c r="I181" t="s">
+        <v>379</v>
+      </c>
+      <c r="J181" t="s">
+        <v>41</v>
+      </c>
+      <c r="K181" t="s">
         <v>380</v>
       </c>
-      <c r="J181" t="s">
-        <v>41</v>
-      </c>
-      <c r="K181" t="s">
-        <v>381</v>
-      </c>
       <c r="L181" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="M181" t="s">
         <v>26</v>
@@ -10481,10 +10508,10 @@
         <v>2401018</v>
       </c>
       <c r="B182" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C182" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D182" s="2">
         <v>2</v>
@@ -10493,7 +10520,7 @@
         <v>34</v>
       </c>
       <c r="F182" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G182" t="s">
         <v>39</v>
@@ -10502,16 +10529,16 @@
         <v>4</v>
       </c>
       <c r="I182" t="s">
+        <v>381</v>
+      </c>
+      <c r="J182" t="s">
+        <v>41</v>
+      </c>
+      <c r="K182" t="s">
         <v>382</v>
       </c>
-      <c r="J182" t="s">
-        <v>41</v>
-      </c>
-      <c r="K182" t="s">
-        <v>383</v>
-      </c>
       <c r="L182" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="M182" t="s">
         <v>26</v>
@@ -10528,10 +10555,10 @@
         <v>2402003</v>
       </c>
       <c r="B183" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C183" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D183" s="2">
         <v>1</v>
@@ -10555,16 +10582,16 @@
         <v>24</v>
       </c>
       <c r="K183" t="s">
+        <v>384</v>
+      </c>
+      <c r="L183" t="s">
         <v>385</v>
       </c>
-      <c r="L183" t="s">
-        <v>386</v>
-      </c>
       <c r="M183" t="s">
         <v>26</v>
       </c>
       <c r="N183" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="O183" s="4"/>
       <c r="Q183" t="s">
@@ -10579,10 +10606,10 @@
         <v>2402003</v>
       </c>
       <c r="B184" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C184" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D184" s="2">
         <v>1</v>
@@ -10606,16 +10633,16 @@
         <v>24</v>
       </c>
       <c r="K184" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="L184" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="M184" t="s">
         <v>26</v>
       </c>
       <c r="N184" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O184" s="4"/>
       <c r="Q184" t="s">
@@ -10630,10 +10657,10 @@
         <v>2402003</v>
       </c>
       <c r="B185" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C185" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D185" s="2">
         <v>1</v>
@@ -10657,16 +10684,16 @@
         <v>24</v>
       </c>
       <c r="K185" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="L185" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="M185" t="s">
         <v>26</v>
       </c>
       <c r="N185" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O185" s="4"/>
       <c r="Q185" t="s">
@@ -10681,10 +10708,10 @@
         <v>2402008</v>
       </c>
       <c r="B186" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C186" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D186" s="2">
         <v>1</v>
@@ -10708,16 +10735,16 @@
         <v>24</v>
       </c>
       <c r="K186" t="s">
+        <v>388</v>
+      </c>
+      <c r="L186" t="s">
         <v>389</v>
       </c>
-      <c r="L186" t="s">
+      <c r="M186" t="s">
+        <v>26</v>
+      </c>
+      <c r="N186" t="s">
         <v>390</v>
-      </c>
-      <c r="M186" t="s">
-        <v>26</v>
-      </c>
-      <c r="N186" t="s">
-        <v>391</v>
       </c>
       <c r="Q186" t="s">
         <v>27</v>
@@ -10731,10 +10758,10 @@
         <v>2402008</v>
       </c>
       <c r="B187" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C187" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D187" s="2">
         <v>1</v>
@@ -10758,16 +10785,16 @@
         <v>24</v>
       </c>
       <c r="K187" t="s">
+        <v>391</v>
+      </c>
+      <c r="L187" t="s">
+        <v>389</v>
+      </c>
+      <c r="M187" t="s">
+        <v>26</v>
+      </c>
+      <c r="N187" t="s">
         <v>392</v>
-      </c>
-      <c r="L187" t="s">
-        <v>390</v>
-      </c>
-      <c r="M187" t="s">
-        <v>26</v>
-      </c>
-      <c r="N187" t="s">
-        <v>393</v>
       </c>
       <c r="Q187" t="s">
         <v>27</v>
@@ -10781,10 +10808,10 @@
         <v>2402008</v>
       </c>
       <c r="B188" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C188" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D188" s="2">
         <v>1</v>
@@ -10808,16 +10835,16 @@
         <v>24</v>
       </c>
       <c r="K188" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="L188" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="M188" t="s">
         <v>26</v>
       </c>
       <c r="N188" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="Q188" t="s">
         <v>27</v>
@@ -10831,10 +10858,10 @@
         <v>2402015</v>
       </c>
       <c r="B189" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C189" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D189" s="2">
         <v>2</v>
@@ -10843,7 +10870,7 @@
         <v>20</v>
       </c>
       <c r="F189" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G189" t="s">
         <v>22</v>
@@ -10858,13 +10885,13 @@
         <v>41</v>
       </c>
       <c r="K189" t="s">
+        <v>394</v>
+      </c>
+      <c r="M189" t="s">
+        <v>26</v>
+      </c>
+      <c r="N189" t="s">
         <v>395</v>
-      </c>
-      <c r="M189" t="s">
-        <v>26</v>
-      </c>
-      <c r="N189" t="s">
-        <v>396</v>
       </c>
       <c r="Q189" t="s">
         <v>27</v>
@@ -10878,10 +10905,10 @@
         <v>2402015</v>
       </c>
       <c r="B190" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C190" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D190" s="2">
         <v>2</v>
@@ -10890,7 +10917,7 @@
         <v>20</v>
       </c>
       <c r="F190" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G190" t="s">
         <v>22</v>
@@ -10905,13 +10932,13 @@
         <v>41</v>
       </c>
       <c r="K190" t="s">
+        <v>396</v>
+      </c>
+      <c r="M190" t="s">
+        <v>26</v>
+      </c>
+      <c r="N190" t="s">
         <v>397</v>
-      </c>
-      <c r="M190" t="s">
-        <v>26</v>
-      </c>
-      <c r="N190" t="s">
-        <v>398</v>
       </c>
       <c r="Q190" t="s">
         <v>27</v>
@@ -10925,10 +10952,10 @@
         <v>2402015</v>
       </c>
       <c r="B191" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C191" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D191" s="2">
         <v>2</v>
@@ -10937,7 +10964,7 @@
         <v>20</v>
       </c>
       <c r="F191" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G191" t="s">
         <v>22</v>
@@ -10952,7 +10979,7 @@
         <v>41</v>
       </c>
       <c r="K191" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="M191" t="s">
         <v>26</v>
@@ -10971,10 +10998,10 @@
         <v>2403004</v>
       </c>
       <c r="B192" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C192" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D192" s="2">
         <v>1</v>
@@ -10998,16 +11025,16 @@
         <v>41</v>
       </c>
       <c r="K192" t="s">
+        <v>400</v>
+      </c>
+      <c r="L192" t="s">
         <v>401</v>
       </c>
-      <c r="L192" t="s">
-        <v>402</v>
-      </c>
       <c r="M192" t="s">
         <v>26</v>
       </c>
       <c r="N192" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="O192" s="4"/>
       <c r="Q192" t="s">
@@ -11022,10 +11049,10 @@
         <v>2403004</v>
       </c>
       <c r="B193" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C193" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D193" s="2">
         <v>1</v>
@@ -11049,16 +11076,16 @@
         <v>41</v>
       </c>
       <c r="K193" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="L193" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="M193" t="s">
         <v>26</v>
       </c>
       <c r="N193" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O193" s="4"/>
       <c r="Q193" t="s">
@@ -11073,10 +11100,10 @@
         <v>2403004</v>
       </c>
       <c r="B194" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C194" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D194" s="2">
         <v>1</v>
@@ -11100,16 +11127,16 @@
         <v>41</v>
       </c>
       <c r="K194" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="L194" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="M194" t="s">
         <v>26</v>
       </c>
       <c r="N194" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O194" s="4"/>
       <c r="Q194" t="s">
@@ -11124,10 +11151,10 @@
         <v>2403009</v>
       </c>
       <c r="B195" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C195" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D195" s="2">
         <v>1</v>
@@ -11151,10 +11178,10 @@
         <v>41</v>
       </c>
       <c r="K195" t="s">
+        <v>404</v>
+      </c>
+      <c r="L195" t="s">
         <v>405</v>
-      </c>
-      <c r="L195" t="s">
-        <v>406</v>
       </c>
       <c r="M195" t="s">
         <v>26</v>
@@ -11171,10 +11198,10 @@
         <v>2403009</v>
       </c>
       <c r="B196" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C196" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D196" s="2">
         <v>1</v>
@@ -11198,10 +11225,10 @@
         <v>41</v>
       </c>
       <c r="K196" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="L196" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="M196" t="s">
         <v>26</v>
@@ -11218,10 +11245,10 @@
         <v>2403009</v>
       </c>
       <c r="B197" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C197" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D197" s="2">
         <v>1</v>
@@ -11245,10 +11272,10 @@
         <v>41</v>
       </c>
       <c r="K197" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="L197" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="M197" t="s">
         <v>26</v>
@@ -11265,10 +11292,10 @@
         <v>2403013</v>
       </c>
       <c r="B198" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C198" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D198" s="2">
         <v>2</v>
@@ -11277,7 +11304,7 @@
         <v>20</v>
       </c>
       <c r="F198" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G198" t="s">
         <v>22</v>
@@ -11292,7 +11319,7 @@
         <v>24</v>
       </c>
       <c r="K198" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="M198" t="s">
         <v>26</v>
@@ -11309,10 +11336,10 @@
         <v>2403013</v>
       </c>
       <c r="B199" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C199" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D199" s="2">
         <v>2</v>
@@ -11321,7 +11348,7 @@
         <v>20</v>
       </c>
       <c r="F199" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G199" t="s">
         <v>22</v>
@@ -11336,7 +11363,7 @@
         <v>24</v>
       </c>
       <c r="K199" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="M199" t="s">
         <v>26</v>
@@ -11353,10 +11380,10 @@
         <v>2403013</v>
       </c>
       <c r="B200" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C200" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D200" s="2">
         <v>2</v>
@@ -11365,7 +11392,7 @@
         <v>20</v>
       </c>
       <c r="F200" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G200" t="s">
         <v>22</v>
@@ -11380,7 +11407,7 @@
         <v>24</v>
       </c>
       <c r="K200" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M200" t="s">
         <v>26</v>
@@ -11397,10 +11424,10 @@
         <v>2404001</v>
       </c>
       <c r="B201" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C201" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D201" s="2">
         <v>1</v>
@@ -11424,16 +11451,16 @@
         <v>41</v>
       </c>
       <c r="K201" t="s">
+        <v>412</v>
+      </c>
+      <c r="L201" t="s">
         <v>413</v>
       </c>
-      <c r="L201" t="s">
+      <c r="M201" t="s">
+        <v>26</v>
+      </c>
+      <c r="N201" t="s">
         <v>414</v>
-      </c>
-      <c r="M201" t="s">
-        <v>26</v>
-      </c>
-      <c r="N201" t="s">
-        <v>415</v>
       </c>
       <c r="Q201" t="s">
         <v>27</v>
@@ -11447,10 +11474,10 @@
         <v>2404001</v>
       </c>
       <c r="B202" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C202" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D202" s="2">
         <v>1</v>
@@ -11474,16 +11501,16 @@
         <v>41</v>
       </c>
       <c r="K202" t="s">
+        <v>415</v>
+      </c>
+      <c r="L202" t="s">
+        <v>413</v>
+      </c>
+      <c r="M202" t="s">
+        <v>26</v>
+      </c>
+      <c r="N202" t="s">
         <v>416</v>
-      </c>
-      <c r="L202" t="s">
-        <v>414</v>
-      </c>
-      <c r="M202" t="s">
-        <v>26</v>
-      </c>
-      <c r="N202" t="s">
-        <v>417</v>
       </c>
       <c r="Q202" t="s">
         <v>27</v>
@@ -11497,10 +11524,10 @@
         <v>2404001</v>
       </c>
       <c r="B203" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C203" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D203" s="2">
         <v>1</v>
@@ -11524,16 +11551,16 @@
         <v>41</v>
       </c>
       <c r="K203" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="L203" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M203" t="s">
         <v>26</v>
       </c>
       <c r="N203" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="Q203" t="s">
         <v>27</v>
@@ -11547,10 +11574,10 @@
         <v>2404006</v>
       </c>
       <c r="B204" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C204" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D204" s="2">
         <v>1</v>
@@ -11574,16 +11601,16 @@
         <v>41</v>
       </c>
       <c r="K204" t="s">
+        <v>418</v>
+      </c>
+      <c r="L204" t="s">
         <v>419</v>
       </c>
-      <c r="L204" t="s">
+      <c r="M204" t="s">
+        <v>26</v>
+      </c>
+      <c r="N204" t="s">
         <v>420</v>
-      </c>
-      <c r="M204" t="s">
-        <v>26</v>
-      </c>
-      <c r="N204" t="s">
-        <v>421</v>
       </c>
       <c r="Q204" t="s">
         <v>27</v>
@@ -11597,10 +11624,10 @@
         <v>2404006</v>
       </c>
       <c r="B205" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C205" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D205" s="2">
         <v>1</v>
@@ -11624,16 +11651,16 @@
         <v>41</v>
       </c>
       <c r="K205" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="L205" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="M205" t="s">
         <v>26</v>
       </c>
       <c r="N205" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="Q205" t="s">
         <v>27</v>
@@ -11647,10 +11674,10 @@
         <v>2404006</v>
       </c>
       <c r="B206" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C206" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D206" s="2">
         <v>1</v>
@@ -11674,16 +11701,16 @@
         <v>41</v>
       </c>
       <c r="K206" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L206" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="M206" t="s">
         <v>26</v>
       </c>
       <c r="N206" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="Q206" t="s">
         <v>27</v>
@@ -11697,10 +11724,10 @@
         <v>2404015</v>
       </c>
       <c r="B207" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C207" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D207" s="2">
         <v>2</v>
@@ -11709,7 +11736,7 @@
         <v>20</v>
       </c>
       <c r="F207" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="G207" t="s">
         <v>39</v>
@@ -11724,13 +11751,13 @@
         <v>24</v>
       </c>
       <c r="K207" t="s">
+        <v>424</v>
+      </c>
+      <c r="M207" t="s">
+        <v>26</v>
+      </c>
+      <c r="N207" t="s">
         <v>425</v>
-      </c>
-      <c r="M207" t="s">
-        <v>26</v>
-      </c>
-      <c r="N207" t="s">
-        <v>426</v>
       </c>
       <c r="Q207" t="s">
         <v>27</v>
@@ -11744,10 +11771,10 @@
         <v>2404015</v>
       </c>
       <c r="B208" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C208" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D208" s="2">
         <v>2</v>
@@ -11756,7 +11783,7 @@
         <v>20</v>
       </c>
       <c r="F208" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="G208" t="s">
         <v>39</v>
@@ -11765,19 +11792,19 @@
         <v>32</v>
       </c>
       <c r="I208" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="J208" t="s">
         <v>24</v>
       </c>
       <c r="K208" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="M208" t="s">
         <v>26</v>
       </c>
       <c r="N208" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="Q208" t="s">
         <v>27</v>
@@ -11791,10 +11818,10 @@
         <v>2404015</v>
       </c>
       <c r="B209" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C209" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D209" s="2">
         <v>2</v>
@@ -11803,7 +11830,7 @@
         <v>20</v>
       </c>
       <c r="F209" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="G209" t="s">
         <v>39</v>
@@ -11812,19 +11839,19 @@
         <v>32</v>
       </c>
       <c r="I209" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="J209" t="s">
         <v>24</v>
       </c>
       <c r="K209" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="M209" t="s">
         <v>26</v>
       </c>
       <c r="N209" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="Q209" t="s">
         <v>27</v>
@@ -11838,10 +11865,10 @@
         <v>2405001</v>
       </c>
       <c r="B210" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C210" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D210" s="2">
         <v>1</v>
@@ -11865,16 +11892,16 @@
         <v>41</v>
       </c>
       <c r="K210" t="s">
+        <v>431</v>
+      </c>
+      <c r="L210" t="s">
         <v>432</v>
       </c>
-      <c r="L210" t="s">
-        <v>433</v>
-      </c>
       <c r="M210" t="s">
         <v>26</v>
       </c>
       <c r="N210" s="8" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="Q210" t="s">
         <v>27</v>
@@ -11888,10 +11915,10 @@
         <v>2405001</v>
       </c>
       <c r="B211" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C211" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D211" s="2">
         <v>1</v>
@@ -11915,16 +11942,16 @@
         <v>41</v>
       </c>
       <c r="K211" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="L211" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="M211" t="s">
         <v>26</v>
       </c>
       <c r="N211" s="8" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="Q211" t="s">
         <v>27</v>
@@ -11938,10 +11965,10 @@
         <v>2405001</v>
       </c>
       <c r="B212" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C212" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D212" s="2">
         <v>1</v>
@@ -11965,16 +11992,16 @@
         <v>41</v>
       </c>
       <c r="K212" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="L212" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="M212" t="s">
         <v>26</v>
       </c>
       <c r="N212" s="8" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="Q212" t="s">
         <v>27</v>
@@ -11988,10 +12015,10 @@
         <v>2405006</v>
       </c>
       <c r="B213" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C213" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D213" s="2">
         <v>1</v>
@@ -12015,16 +12042,16 @@
         <v>41</v>
       </c>
       <c r="K213" t="s">
+        <v>435</v>
+      </c>
+      <c r="L213" t="s">
         <v>436</v>
       </c>
-      <c r="L213" t="s">
-        <v>437</v>
-      </c>
       <c r="M213" t="s">
         <v>26</v>
       </c>
       <c r="N213" s="8" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q213" t="s">
         <v>27</v>
@@ -12038,10 +12065,10 @@
         <v>2405006</v>
       </c>
       <c r="B214" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C214" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D214" s="2">
         <v>1</v>
@@ -12065,16 +12092,16 @@
         <v>41</v>
       </c>
       <c r="K214" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="L214" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="M214" t="s">
         <v>26</v>
       </c>
       <c r="N214" s="8" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="Q214" t="s">
         <v>27</v>
@@ -12088,10 +12115,10 @@
         <v>2405006</v>
       </c>
       <c r="B215" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C215" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D215" s="2">
         <v>1</v>
@@ -12115,16 +12142,16 @@
         <v>41</v>
       </c>
       <c r="K215" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="L215" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="M215" t="s">
         <v>26</v>
       </c>
       <c r="N215" s="8" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="Q215" t="s">
         <v>27</v>
@@ -12138,10 +12165,10 @@
         <v>2405015</v>
       </c>
       <c r="B216" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C216" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D216" s="2">
         <v>2</v>
@@ -12150,7 +12177,7 @@
         <v>20</v>
       </c>
       <c r="F216" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G216" t="s">
         <v>22</v>
@@ -12165,16 +12192,16 @@
         <v>24</v>
       </c>
       <c r="K216" t="s">
+        <v>439</v>
+      </c>
+      <c r="L216" t="s">
         <v>440</v>
       </c>
-      <c r="L216" t="s">
+      <c r="M216" t="s">
+        <v>26</v>
+      </c>
+      <c r="N216" t="s">
         <v>441</v>
-      </c>
-      <c r="M216" t="s">
-        <v>26</v>
-      </c>
-      <c r="N216" t="s">
-        <v>442</v>
       </c>
       <c r="Q216" t="s">
         <v>27</v>
@@ -12188,10 +12215,10 @@
         <v>2405015</v>
       </c>
       <c r="B217" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C217" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D217" s="2">
         <v>2</v>
@@ -12200,7 +12227,7 @@
         <v>20</v>
       </c>
       <c r="F217" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G217" t="s">
         <v>22</v>
@@ -12215,16 +12242,16 @@
         <v>24</v>
       </c>
       <c r="K217" t="s">
+        <v>442</v>
+      </c>
+      <c r="L217" t="s">
+        <v>440</v>
+      </c>
+      <c r="M217" t="s">
+        <v>26</v>
+      </c>
+      <c r="N217" t="s">
         <v>443</v>
-      </c>
-      <c r="L217" t="s">
-        <v>441</v>
-      </c>
-      <c r="M217" t="s">
-        <v>26</v>
-      </c>
-      <c r="N217" t="s">
-        <v>444</v>
       </c>
       <c r="Q217" t="s">
         <v>27</v>
@@ -12238,10 +12265,10 @@
         <v>2405015</v>
       </c>
       <c r="B218" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C218" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D218" s="2">
         <v>2</v>
@@ -12250,7 +12277,7 @@
         <v>20</v>
       </c>
       <c r="F218" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G218" t="s">
         <v>22</v>
@@ -12265,13 +12292,13 @@
         <v>24</v>
       </c>
       <c r="K218" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="M218" t="s">
         <v>26</v>
       </c>
       <c r="N218" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="Q218" t="s">
         <v>27</v>
@@ -12285,10 +12312,10 @@
         <v>2406004</v>
       </c>
       <c r="B219" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C219" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D219" s="2">
         <v>1</v>
@@ -12312,10 +12339,10 @@
         <v>24</v>
       </c>
       <c r="K219" t="s">
+        <v>446</v>
+      </c>
+      <c r="L219" t="s">
         <v>447</v>
-      </c>
-      <c r="L219" t="s">
-        <v>448</v>
       </c>
       <c r="M219" t="s">
         <v>26</v>
@@ -12332,10 +12359,10 @@
         <v>2406004</v>
       </c>
       <c r="B220" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C220" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D220" s="2">
         <v>1</v>
@@ -12359,10 +12386,10 @@
         <v>24</v>
       </c>
       <c r="K220" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="L220" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="M220" t="s">
         <v>26</v>
@@ -12379,10 +12406,10 @@
         <v>2406004</v>
       </c>
       <c r="B221" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C221" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D221" s="2">
         <v>1</v>
@@ -12400,13 +12427,13 @@
         <v>8</v>
       </c>
       <c r="I221" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="J221" t="s">
         <v>24</v>
       </c>
       <c r="L221" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="M221" t="s">
         <v>26</v>
@@ -12423,10 +12450,10 @@
         <v>2406004</v>
       </c>
       <c r="B222" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C222" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D222" s="2">
         <v>1</v>
@@ -12450,10 +12477,10 @@
         <v>24</v>
       </c>
       <c r="K222" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="L222" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="M222" t="s">
         <v>26</v>
@@ -12470,10 +12497,10 @@
         <v>2406004</v>
       </c>
       <c r="B223" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C223" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D223" s="2">
         <v>1</v>
@@ -12491,13 +12518,13 @@
         <v>8</v>
       </c>
       <c r="I223" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="J223" t="s">
         <v>24</v>
       </c>
       <c r="L223" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="M223" t="s">
         <v>26</v>
@@ -12514,10 +12541,10 @@
         <v>2406009</v>
       </c>
       <c r="B224" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C224" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D224" s="2">
         <v>1</v>
@@ -12541,10 +12568,10 @@
         <v>24</v>
       </c>
       <c r="K224" t="s">
+        <v>450</v>
+      </c>
+      <c r="L224" t="s">
         <v>451</v>
-      </c>
-      <c r="L224" t="s">
-        <v>452</v>
       </c>
       <c r="M224" t="s">
         <v>26</v>
@@ -12561,10 +12588,10 @@
         <v>2406009</v>
       </c>
       <c r="B225" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C225" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D225" s="2">
         <v>1</v>
@@ -12588,10 +12615,10 @@
         <v>24</v>
       </c>
       <c r="K225" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="L225" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="M225" t="s">
         <v>26</v>
@@ -12608,10 +12635,10 @@
         <v>2406009</v>
       </c>
       <c r="B226" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C226" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D226" s="2">
         <v>1</v>
@@ -12629,16 +12656,16 @@
         <v>8</v>
       </c>
       <c r="I226" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="J226" t="s">
         <v>24</v>
       </c>
       <c r="K226" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="L226" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="M226" t="s">
         <v>26</v>
@@ -12655,10 +12682,10 @@
         <v>2406009</v>
       </c>
       <c r="B227" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C227" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D227" s="2">
         <v>1</v>
@@ -12682,10 +12709,10 @@
         <v>24</v>
       </c>
       <c r="K227" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="L227" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="M227" t="s">
         <v>26</v>
@@ -12702,10 +12729,10 @@
         <v>2406009</v>
       </c>
       <c r="B228" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C228" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D228" s="2">
         <v>1</v>
@@ -12723,16 +12750,16 @@
         <v>8</v>
       </c>
       <c r="I228" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="J228" t="s">
         <v>24</v>
       </c>
       <c r="K228" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L228" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="M228" t="s">
         <v>26</v>
@@ -12749,10 +12776,10 @@
         <v>2406012</v>
       </c>
       <c r="B229" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C229" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D229" s="2">
         <v>2</v>
@@ -12761,7 +12788,7 @@
         <v>20</v>
       </c>
       <c r="F229" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G229" t="s">
         <v>39</v>
@@ -12776,10 +12803,10 @@
         <v>41</v>
       </c>
       <c r="K229" t="s">
+        <v>457</v>
+      </c>
+      <c r="L229" t="s">
         <v>458</v>
-      </c>
-      <c r="L229" t="s">
-        <v>459</v>
       </c>
       <c r="M229" t="s">
         <v>26</v>
@@ -12796,10 +12823,10 @@
         <v>2406012</v>
       </c>
       <c r="B230" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C230" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D230" s="2">
         <v>2</v>
@@ -12808,7 +12835,7 @@
         <v>20</v>
       </c>
       <c r="F230" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G230" t="s">
         <v>39</v>
@@ -12817,16 +12844,16 @@
         <v>8</v>
       </c>
       <c r="I230" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="J230" t="s">
         <v>41</v>
       </c>
       <c r="K230" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="L230" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="M230" t="s">
         <v>26</v>
@@ -12843,10 +12870,10 @@
         <v>2406012</v>
       </c>
       <c r="B231" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C231" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D231" s="2">
         <v>2</v>
@@ -12855,7 +12882,7 @@
         <v>20</v>
       </c>
       <c r="F231" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G231" t="s">
         <v>39</v>
@@ -12864,16 +12891,16 @@
         <v>8</v>
       </c>
       <c r="I231" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J231" t="s">
         <v>41</v>
       </c>
       <c r="K231" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="L231" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="M231" t="s">
         <v>26</v>
@@ -12890,11 +12917,11 @@
         <v>2059001</v>
       </c>
       <c r="B232" t="s">
+        <v>461</v>
+      </c>
+      <c r="C232" t="s">
         <v>462</v>
       </c>
-      <c r="C232" t="s">
-        <v>463</v>
-      </c>
       <c r="D232" s="2">
         <v>1</v>
       </c>
@@ -12902,7 +12929,7 @@
         <v>20</v>
       </c>
       <c r="F232" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G232" t="s">
         <v>22</v>
@@ -12917,10 +12944,10 @@
         <v>41</v>
       </c>
       <c r="K232" t="s">
+        <v>463</v>
+      </c>
+      <c r="L232" t="s">
         <v>464</v>
-      </c>
-      <c r="L232" t="s">
-        <v>465</v>
       </c>
       <c r="M232" t="s">
         <v>26</v>
@@ -12937,11 +12964,11 @@
         <v>2059002</v>
       </c>
       <c r="B233" t="s">
+        <v>461</v>
+      </c>
+      <c r="C233" t="s">
         <v>462</v>
       </c>
-      <c r="C233" t="s">
-        <v>463</v>
-      </c>
       <c r="D233" s="2">
         <v>1</v>
       </c>
@@ -12949,7 +12976,7 @@
         <v>20</v>
       </c>
       <c r="F233" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G233" t="s">
         <v>22</v>
@@ -12964,10 +12991,10 @@
         <v>41</v>
       </c>
       <c r="K233" t="s">
+        <v>465</v>
+      </c>
+      <c r="L233" t="s">
         <v>466</v>
-      </c>
-      <c r="L233" t="s">
-        <v>467</v>
       </c>
       <c r="M233" t="s">
         <v>26</v>
@@ -12984,10 +13011,10 @@
         <v>2059006</v>
       </c>
       <c r="B234" t="s">
+        <v>461</v>
+      </c>
+      <c r="C234" t="s">
         <v>462</v>
-      </c>
-      <c r="C234" t="s">
-        <v>463</v>
       </c>
       <c r="D234" s="2">
         <v>1</v>
@@ -13011,10 +13038,10 @@
         <v>41</v>
       </c>
       <c r="K234" t="s">
+        <v>467</v>
+      </c>
+      <c r="L234" t="s">
         <v>468</v>
-      </c>
-      <c r="L234" t="s">
-        <v>469</v>
       </c>
       <c r="M234" t="s">
         <v>26</v>
@@ -13031,10 +13058,10 @@
         <v>2140011</v>
       </c>
       <c r="B235" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C235" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D235" s="2">
         <v>2</v>
@@ -13043,7 +13070,7 @@
         <v>20</v>
       </c>
       <c r="F235" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G235" t="s">
         <v>39</v>
@@ -13058,10 +13085,10 @@
         <v>41</v>
       </c>
       <c r="K235" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L235" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="M235" t="s">
         <v>26</v>
@@ -13078,10 +13105,10 @@
         <v>2390004</v>
       </c>
       <c r="B236" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C236" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D236" s="2">
         <v>1</v>
@@ -13105,10 +13132,10 @@
         <v>24</v>
       </c>
       <c r="K236" t="s">
+        <v>472</v>
+      </c>
+      <c r="L236" t="s">
         <v>473</v>
-      </c>
-      <c r="L236" t="s">
-        <v>474</v>
       </c>
       <c r="M236" t="s">
         <v>26</v>
@@ -13125,10 +13152,10 @@
         <v>2390004</v>
       </c>
       <c r="B237" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C237" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D237" s="2">
         <v>1</v>
@@ -13152,10 +13179,10 @@
         <v>24</v>
       </c>
       <c r="K237" t="s">
+        <v>474</v>
+      </c>
+      <c r="L237" t="s">
         <v>475</v>
-      </c>
-      <c r="L237" t="s">
-        <v>476</v>
       </c>
       <c r="M237" t="s">
         <v>26</v>
@@ -13172,10 +13199,10 @@
         <v>2390004</v>
       </c>
       <c r="B238" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C238" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D238" s="2">
         <v>1</v>
@@ -13199,10 +13226,10 @@
         <v>24</v>
       </c>
       <c r="K238" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="L238" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="M238" t="s">
         <v>26</v>
@@ -13219,10 +13246,10 @@
         <v>2390009</v>
       </c>
       <c r="B239" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C239" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D239" s="2">
         <v>1</v>
@@ -13246,10 +13273,10 @@
         <v>24</v>
       </c>
       <c r="K239" t="s">
+        <v>477</v>
+      </c>
+      <c r="L239" t="s">
         <v>478</v>
-      </c>
-      <c r="L239" t="s">
-        <v>479</v>
       </c>
       <c r="M239" t="s">
         <v>26</v>
@@ -13266,10 +13293,10 @@
         <v>2390009</v>
       </c>
       <c r="B240" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C240" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D240" s="2">
         <v>1</v>
@@ -13293,10 +13320,10 @@
         <v>24</v>
       </c>
       <c r="K240" t="s">
+        <v>479</v>
+      </c>
+      <c r="L240" t="s">
         <v>480</v>
-      </c>
-      <c r="L240" t="s">
-        <v>481</v>
       </c>
       <c r="M240" t="s">
         <v>26</v>
@@ -13313,10 +13340,10 @@
         <v>2390009</v>
       </c>
       <c r="B241" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C241" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D241" s="2">
         <v>1</v>
@@ -13340,10 +13367,10 @@
         <v>24</v>
       </c>
       <c r="K241" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="L241" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="M241" t="s">
         <v>26</v>
@@ -13360,10 +13387,10 @@
         <v>2390013</v>
       </c>
       <c r="B242" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C242" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D242" s="2">
         <v>2</v>
@@ -13372,7 +13399,7 @@
         <v>20</v>
       </c>
       <c r="F242" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G242" t="s">
         <v>22</v>
@@ -13387,7 +13414,7 @@
         <v>41</v>
       </c>
       <c r="K242" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="M242" t="s">
         <v>26</v>
@@ -13404,10 +13431,10 @@
         <v>2390013</v>
       </c>
       <c r="B243" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C243" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D243" s="2">
         <v>2</v>
@@ -13416,7 +13443,7 @@
         <v>20</v>
       </c>
       <c r="F243" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G243" t="s">
         <v>22</v>
@@ -13431,7 +13458,7 @@
         <v>41</v>
       </c>
       <c r="K243" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="M243" t="s">
         <v>26</v>
@@ -13448,10 +13475,10 @@
         <v>2390013</v>
       </c>
       <c r="B244" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C244" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D244" s="2">
         <v>2</v>
@@ -13460,7 +13487,7 @@
         <v>20</v>
       </c>
       <c r="F244" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G244" t="s">
         <v>22</v>
@@ -13475,7 +13502,7 @@
         <v>41</v>
       </c>
       <c r="K244" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="M244" t="s">
         <v>26</v>

--- a/POD_2026-27_11-5-2026.xlsx
+++ b/POD_2026-27_11-5-2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guillermo.vera/Desktop/POD2627/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\misael.marriaga\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{364BD2D1-76E2-CA46-9B01-A9F7734E2F60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2154AF3F-8C8B-486B-BBEA-DF6EC509CE37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="POD" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2949" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2957" uniqueCount="511">
   <si>
     <t>POD_2026-27_11-5-2026</t>
   </si>
@@ -1554,6 +1554,21 @@
   </si>
   <si>
     <t>MICHAEL STICH (14)</t>
+  </si>
+  <si>
+    <t>ELENA CASTILLA (60)</t>
+  </si>
+  <si>
+    <t>ELENA CASTILLA (35)</t>
+  </si>
+  <si>
+    <t>ELENA CASTILLA (52)</t>
+  </si>
+  <si>
+    <t>ELENA CASTILLA (4)</t>
+  </si>
+  <si>
+    <t>ELENA CASTILLA (8)</t>
   </si>
 </sst>
 </file>
@@ -1610,14 +1625,14 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1636,9 +1651,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1676,7 +1691,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1782,7 +1797,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1924,7 +1939,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1933,53 +1948,53 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S252"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="71.33203125" customWidth="1"/>
+    <col min="2" max="2" width="71.36328125" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" customWidth="1"/>
-    <col min="5" max="5" width="20.1640625" customWidth="1"/>
-    <col min="6" max="6" width="64.1640625" customWidth="1"/>
-    <col min="7" max="7" width="20.83203125" customWidth="1"/>
-    <col min="8" max="8" width="6.5" customWidth="1"/>
-    <col min="9" max="9" width="7.83203125" customWidth="1"/>
-    <col min="10" max="10" width="6.5" customWidth="1"/>
-    <col min="11" max="11" width="107.1640625" customWidth="1"/>
-    <col min="12" max="12" width="53.6640625" customWidth="1"/>
-    <col min="13" max="13" width="12.6640625" customWidth="1"/>
-    <col min="14" max="14" width="36.5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="36.5" customWidth="1"/>
-    <col min="16" max="16" width="20.83203125" customWidth="1"/>
+    <col min="4" max="4" width="9.1796875" customWidth="1"/>
+    <col min="5" max="5" width="20.1796875" customWidth="1"/>
+    <col min="6" max="6" width="64.1796875" customWidth="1"/>
+    <col min="7" max="7" width="20.81640625" customWidth="1"/>
+    <col min="8" max="8" width="6.453125" customWidth="1"/>
+    <col min="9" max="9" width="7.81640625" customWidth="1"/>
+    <col min="10" max="10" width="6.453125" customWidth="1"/>
+    <col min="11" max="11" width="107.1796875" customWidth="1"/>
+    <col min="12" max="12" width="53.6328125" customWidth="1"/>
+    <col min="13" max="13" width="12.6328125" customWidth="1"/>
+    <col min="14" max="14" width="36.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="36.453125" customWidth="1"/>
+    <col min="16" max="16" width="20.81640625" customWidth="1"/>
     <col min="17" max="17" width="52" customWidth="1"/>
-    <col min="18" max="18" width="32.5" customWidth="1"/>
-    <col min="19" max="19" width="16.83203125" customWidth="1"/>
+    <col min="18" max="18" width="32.453125" customWidth="1"/>
+    <col min="19" max="19" width="16.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8"/>
+      <c r="R1" s="8"/>
+      <c r="S1" s="8"/>
+    </row>
+    <row r="2" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2038,7 +2053,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>2291005</v>
       </c>
@@ -2082,7 +2097,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>2291009</v>
       </c>
@@ -2126,7 +2141,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>2240005</v>
       </c>
@@ -2173,7 +2188,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>2240009</v>
       </c>
@@ -2220,7 +2235,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>2251011</v>
       </c>
@@ -2264,7 +2279,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>2327002</v>
       </c>
@@ -2308,7 +2323,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>2327002</v>
       </c>
@@ -2352,7 +2367,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>2327002</v>
       </c>
@@ -2396,7 +2411,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>2327007</v>
       </c>
@@ -2433,10 +2448,10 @@
       <c r="M11" t="s">
         <v>26</v>
       </c>
-      <c r="N11" s="8" t="s">
+      <c r="N11" s="6" t="s">
         <v>490</v>
       </c>
-      <c r="O11" s="8" t="s">
+      <c r="O11" s="6" t="s">
         <v>488</v>
       </c>
       <c r="Q11" t="s">
@@ -2446,7 +2461,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>2327007</v>
       </c>
@@ -2483,10 +2498,10 @@
       <c r="M12" t="s">
         <v>26</v>
       </c>
-      <c r="N12" s="8" t="s">
+      <c r="N12" s="6" t="s">
         <v>491</v>
       </c>
-      <c r="O12" s="8" t="s">
+      <c r="O12" s="6" t="s">
         <v>489</v>
       </c>
       <c r="Q12" t="s">
@@ -2496,7 +2511,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>2327007</v>
       </c>
@@ -2533,10 +2548,10 @@
       <c r="M13" t="s">
         <v>26</v>
       </c>
-      <c r="N13" s="8" t="s">
+      <c r="N13" s="6" t="s">
         <v>491</v>
       </c>
-      <c r="O13" s="8" t="s">
+      <c r="O13" s="6" t="s">
         <v>489</v>
       </c>
       <c r="Q13" t="s">
@@ -2546,7 +2561,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>2327015</v>
       </c>
@@ -2590,7 +2605,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>2327015</v>
       </c>
@@ -2634,7 +2649,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>2327015</v>
       </c>
@@ -2678,7 +2693,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>2360001</v>
       </c>
@@ -2722,7 +2737,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>2360002</v>
       </c>
@@ -2766,7 +2781,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>2382005</v>
       </c>
@@ -2813,7 +2828,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>2382005</v>
       </c>
@@ -2860,7 +2875,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>2382005</v>
       </c>
@@ -2907,7 +2922,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>2382005</v>
       </c>
@@ -2954,7 +2969,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>2382005</v>
       </c>
@@ -3001,7 +3016,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>2382005</v>
       </c>
@@ -3048,7 +3063,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>2382010</v>
       </c>
@@ -3095,7 +3110,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>2382010</v>
       </c>
@@ -3142,7 +3157,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>2382010</v>
       </c>
@@ -3189,7 +3204,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>2382010</v>
       </c>
@@ -3236,7 +3251,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>2382010</v>
       </c>
@@ -3280,7 +3295,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>2382010</v>
       </c>
@@ -3327,7 +3342,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>2383001</v>
       </c>
@@ -3367,7 +3382,7 @@
       <c r="M31" t="s">
         <v>26</v>
       </c>
-      <c r="N31" s="8" t="s">
+      <c r="N31" s="6" t="s">
         <v>492</v>
       </c>
       <c r="Q31" t="s">
@@ -3377,7 +3392,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>2383001</v>
       </c>
@@ -3414,7 +3429,7 @@
       <c r="M32" t="s">
         <v>26</v>
       </c>
-      <c r="N32" s="8" t="s">
+      <c r="N32" s="6" t="s">
         <v>493</v>
       </c>
       <c r="Q32" t="s">
@@ -3424,7 +3439,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>2383001</v>
       </c>
@@ -3461,7 +3476,7 @@
       <c r="M33" t="s">
         <v>26</v>
       </c>
-      <c r="N33" s="8" t="s">
+      <c r="N33" s="6" t="s">
         <v>493</v>
       </c>
       <c r="Q33" t="s">
@@ -3471,7 +3486,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>2383001</v>
       </c>
@@ -3511,7 +3526,7 @@
       <c r="M34" t="s">
         <v>26</v>
       </c>
-      <c r="N34" s="8" t="s">
+      <c r="N34" s="6" t="s">
         <v>492</v>
       </c>
       <c r="Q34" t="s">
@@ -3521,7 +3536,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>2383001</v>
       </c>
@@ -3561,7 +3576,7 @@
       <c r="M35" t="s">
         <v>26</v>
       </c>
-      <c r="N35" s="8" t="s">
+      <c r="N35" s="6" t="s">
         <v>493</v>
       </c>
       <c r="Q35" t="s">
@@ -3571,7 +3586,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>2383001</v>
       </c>
@@ -3611,7 +3626,7 @@
       <c r="M36" t="s">
         <v>26</v>
       </c>
-      <c r="N36" s="8" t="s">
+      <c r="N36" s="6" t="s">
         <v>493</v>
       </c>
       <c r="Q36" t="s">
@@ -3621,7 +3636,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <v>2383002</v>
       </c>
@@ -3668,7 +3683,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <v>2383002</v>
       </c>
@@ -3712,7 +3727,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <v>2383002</v>
       </c>
@@ -3756,7 +3771,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>2383002</v>
       </c>
@@ -3803,7 +3818,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>2383002</v>
       </c>
@@ -3850,7 +3865,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>2383002</v>
       </c>
@@ -3897,7 +3912,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="48" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <v>2383007</v>
       </c>
@@ -3947,7 +3962,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:18" ht="48" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>2383007</v>
       </c>
@@ -3997,7 +4012,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <v>2384001</v>
       </c>
@@ -4037,7 +4052,7 @@
       <c r="M45" t="s">
         <v>26</v>
       </c>
-      <c r="N45" s="8" t="s">
+      <c r="N45" s="6" t="s">
         <v>504</v>
       </c>
       <c r="Q45" t="s">
@@ -4047,7 +4062,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>2384001</v>
       </c>
@@ -4087,7 +4102,7 @@
       <c r="M46" t="s">
         <v>26</v>
       </c>
-      <c r="N46" s="8" t="s">
+      <c r="N46" s="6" t="s">
         <v>505</v>
       </c>
       <c r="Q46" t="s">
@@ -4097,7 +4112,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <v>2384001</v>
       </c>
@@ -4137,7 +4152,7 @@
       <c r="M47" t="s">
         <v>26</v>
       </c>
-      <c r="N47" s="8" t="s">
+      <c r="N47" s="6" t="s">
         <v>505</v>
       </c>
       <c r="Q47" t="s">
@@ -4147,7 +4162,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>2384005</v>
       </c>
@@ -4194,7 +4209,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <v>2384005</v>
       </c>
@@ -4241,7 +4256,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <v>2384005</v>
       </c>
@@ -4288,7 +4303,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <v>2385001</v>
       </c>
@@ -4328,7 +4343,7 @@
       <c r="M51" t="s">
         <v>26</v>
       </c>
-      <c r="N51" s="8" t="s">
+      <c r="N51" s="6" t="s">
         <v>504</v>
       </c>
       <c r="Q51" t="s">
@@ -4338,7 +4353,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <v>2385001</v>
       </c>
@@ -4378,7 +4393,7 @@
       <c r="M52" t="s">
         <v>26</v>
       </c>
-      <c r="N52" s="8" t="s">
+      <c r="N52" s="6" t="s">
         <v>505</v>
       </c>
       <c r="Q52" t="s">
@@ -4388,7 +4403,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
         <v>2385001</v>
       </c>
@@ -4428,7 +4443,7 @@
       <c r="M53" t="s">
         <v>26</v>
       </c>
-      <c r="N53" s="8" t="s">
+      <c r="N53" s="6" t="s">
         <v>505</v>
       </c>
       <c r="Q53" t="s">
@@ -4438,7 +4453,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <v>2385005</v>
       </c>
@@ -4485,7 +4500,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
         <v>2385005</v>
       </c>
@@ -4532,7 +4547,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <v>2385005</v>
       </c>
@@ -4579,7 +4594,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
         <v>2386001</v>
       </c>
@@ -4626,7 +4641,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <v>2386001</v>
       </c>
@@ -4670,7 +4685,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
         <v>2386001</v>
       </c>
@@ -4714,7 +4729,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>2386001</v>
       </c>
@@ -4761,7 +4776,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <v>2386001</v>
       </c>
@@ -4805,7 +4820,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <v>2386001</v>
       </c>
@@ -4850,7 +4865,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
         <v>2386002</v>
       </c>
@@ -4897,7 +4912,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
         <v>2386002</v>
       </c>
@@ -4937,7 +4952,7 @@
       <c r="M64" t="s">
         <v>26</v>
       </c>
-      <c r="N64" s="8" t="s">
+      <c r="N64" s="6" t="s">
         <v>503</v>
       </c>
       <c r="Q64" t="s">
@@ -4947,7 +4962,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A65" s="2">
         <v>2387009</v>
       </c>
@@ -4994,7 +5009,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A66" s="2">
         <v>2387009</v>
       </c>
@@ -5038,7 +5053,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A67" s="2">
         <v>2387009</v>
       </c>
@@ -5082,7 +5097,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A68" s="2">
         <v>2387016</v>
       </c>
@@ -5126,7 +5141,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A69" s="2">
         <v>2387016</v>
       </c>
@@ -5167,7 +5182,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A70" s="2">
         <v>2387016</v>
       </c>
@@ -5208,7 +5223,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="71" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A71" s="2">
         <v>2265020</v>
       </c>
@@ -5256,7 +5271,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A72" s="2">
         <v>2029018</v>
       </c>
@@ -5303,7 +5318,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A73" s="2">
         <v>2030013</v>
       </c>
@@ -5350,7 +5365,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A74" s="2">
         <v>2031001</v>
       </c>
@@ -5394,7 +5409,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A75" s="2">
         <v>2032001</v>
       </c>
@@ -5434,6 +5449,9 @@
       <c r="M75" t="s">
         <v>26</v>
       </c>
+      <c r="N75" s="6" t="s">
+        <v>506</v>
+      </c>
       <c r="Q75" t="s">
         <v>27</v>
       </c>
@@ -5441,7 +5459,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A76" s="2">
         <v>2032007</v>
       </c>
@@ -5491,7 +5509,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A77" s="2">
         <v>2032009</v>
       </c>
@@ -5535,7 +5553,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A78" s="2">
         <v>2033001</v>
       </c>
@@ -5582,7 +5600,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="79" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A79" s="2">
         <v>2033002</v>
       </c>
@@ -5622,7 +5640,7 @@
       <c r="M79" t="s">
         <v>26</v>
       </c>
-      <c r="N79" s="7" t="s">
+      <c r="N79" s="5" t="s">
         <v>494</v>
       </c>
       <c r="O79" s="3"/>
@@ -5633,7 +5651,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A80" s="2">
         <v>2033006</v>
       </c>
@@ -5683,7 +5701,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A81" s="2">
         <v>2034001</v>
       </c>
@@ -5730,7 +5748,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="82" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A82" s="2">
         <v>2034002</v>
       </c>
@@ -5770,10 +5788,12 @@
       <c r="M82" t="s">
         <v>26</v>
       </c>
-      <c r="N82" s="7" t="s">
+      <c r="N82" s="5" t="s">
         <v>494</v>
       </c>
-      <c r="O82" s="3"/>
+      <c r="O82" s="5" t="s">
+        <v>507</v>
+      </c>
       <c r="Q82" t="s">
         <v>27</v>
       </c>
@@ -5781,7 +5801,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A83" s="2">
         <v>2034006</v>
       </c>
@@ -5828,7 +5848,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A84" s="2">
         <v>2061001</v>
       </c>
@@ -5872,7 +5892,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A85" s="2">
         <v>2061002</v>
       </c>
@@ -5919,7 +5939,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A86" s="2">
         <v>2061006</v>
       </c>
@@ -5963,7 +5983,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A87" s="2">
         <v>2107013</v>
       </c>
@@ -6010,7 +6030,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A88" s="2">
         <v>2143016</v>
       </c>
@@ -6057,7 +6077,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A89" s="2">
         <v>2148011</v>
       </c>
@@ -6101,7 +6121,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A90" s="2">
         <v>2175020</v>
       </c>
@@ -6148,7 +6168,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="91" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A91" s="2">
         <v>2285005</v>
       </c>
@@ -6185,7 +6205,7 @@
       <c r="M91" t="s">
         <v>26</v>
       </c>
-      <c r="N91" s="7" t="s">
+      <c r="N91" s="5" t="s">
         <v>495</v>
       </c>
       <c r="O91" s="3"/>
@@ -6196,7 +6216,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A92" s="2">
         <v>2285006</v>
       </c>
@@ -6243,7 +6263,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A93" s="2">
         <v>2285007</v>
       </c>
@@ -6280,7 +6300,7 @@
       <c r="M93" t="s">
         <v>26</v>
       </c>
-      <c r="N93" s="8" t="s">
+      <c r="N93" s="6" t="s">
         <v>179</v>
       </c>
       <c r="Q93" t="s">
@@ -6290,7 +6310,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A94" s="2">
         <v>2286015</v>
       </c>
@@ -6334,7 +6354,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A95" s="2">
         <v>2338044</v>
       </c>
@@ -6378,7 +6398,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A96" s="2">
         <v>2342014</v>
       </c>
@@ -6425,7 +6445,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="97" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A97" s="2">
         <v>5</v>
       </c>
@@ -6462,7 +6482,7 @@
       <c r="M97" t="s">
         <v>26</v>
       </c>
-      <c r="N97" s="7" t="s">
+      <c r="N97" s="5" t="s">
         <v>496</v>
       </c>
       <c r="O97" s="3"/>
@@ -6473,7 +6493,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="98" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A98" s="2">
         <v>2343027</v>
       </c>
@@ -6510,7 +6530,7 @@
       <c r="M98" t="s">
         <v>213</v>
       </c>
-      <c r="N98" s="7" t="s">
+      <c r="N98" s="5" t="s">
         <v>497</v>
       </c>
       <c r="O98" s="3"/>
@@ -6521,7 +6541,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A99" s="2">
         <v>2343027</v>
       </c>
@@ -6568,7 +6588,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A100" s="2">
         <v>2343027</v>
       </c>
@@ -6614,7 +6634,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A101" s="2">
         <v>2347001</v>
       </c>
@@ -6664,7 +6684,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A102" s="2">
         <v>2347003</v>
       </c>
@@ -6704,7 +6724,7 @@
       <c r="M102" t="s">
         <v>26</v>
       </c>
-      <c r="N102" s="8" t="s">
+      <c r="N102" s="6" t="s">
         <v>498</v>
       </c>
       <c r="Q102" t="s">
@@ -6714,7 +6734,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="103" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A103" s="2">
         <v>2347005</v>
       </c>
@@ -6765,7 +6785,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A104" s="2">
         <v>2347006</v>
       </c>
@@ -6805,7 +6825,7 @@
       <c r="M104" t="s">
         <v>26</v>
       </c>
-      <c r="N104" s="8" t="s">
+      <c r="N104" s="6" t="s">
         <v>498</v>
       </c>
       <c r="Q104" t="s">
@@ -6815,7 +6835,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="105" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A105" s="2">
         <v>2347007</v>
       </c>
@@ -6866,7 +6886,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A106" s="2">
         <v>2347013</v>
       </c>
@@ -6916,7 +6936,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A107" s="2">
         <v>2347014</v>
       </c>
@@ -6963,7 +6983,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A108" s="2">
         <v>2347017</v>
       </c>
@@ -7013,7 +7033,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="109" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A109" s="2">
         <v>2347030</v>
       </c>
@@ -7064,7 +7084,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A110" s="2">
         <v>2347021</v>
       </c>
@@ -7114,7 +7134,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="111" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A111" s="2">
         <v>2347022</v>
       </c>
@@ -7166,7 +7186,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A112" s="2">
         <v>2347024</v>
       </c>
@@ -7216,7 +7236,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="113" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A113" s="2">
         <v>2347026</v>
       </c>
@@ -7267,7 +7287,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="114" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A114" s="2">
         <v>2347027</v>
       </c>
@@ -7307,10 +7327,10 @@
       <c r="M114" t="s">
         <v>26</v>
       </c>
-      <c r="N114" s="7" t="s">
+      <c r="N114" s="5" t="s">
         <v>485</v>
       </c>
-      <c r="O114" s="7"/>
+      <c r="O114" s="5"/>
       <c r="Q114" t="s">
         <v>27</v>
       </c>
@@ -7318,7 +7338,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A115" s="2">
         <v>2347029</v>
       </c>
@@ -7368,7 +7388,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="116" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A116" s="2">
         <v>2347031</v>
       </c>
@@ -7418,7 +7438,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="117" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A117" s="2">
         <v>2347038</v>
       </c>
@@ -7469,7 +7489,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="118" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A118" s="2">
         <v>2361002</v>
       </c>
@@ -7513,7 +7533,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="119" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A119" s="2">
         <v>2361002</v>
       </c>
@@ -7557,7 +7577,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="120" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A120" s="2">
         <v>2361002</v>
       </c>
@@ -7601,7 +7621,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="121" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A121" s="2">
         <v>2361004</v>
       </c>
@@ -7638,6 +7658,9 @@
       <c r="M121" t="s">
         <v>26</v>
       </c>
+      <c r="N121" s="6" t="s">
+        <v>506</v>
+      </c>
       <c r="Q121" t="s">
         <v>27</v>
       </c>
@@ -7645,7 +7668,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="122" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A122" s="2">
         <v>2393002</v>
       </c>
@@ -7692,7 +7715,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="123" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A123" s="2">
         <v>2393002</v>
       </c>
@@ -7739,7 +7762,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="124" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A124" s="2">
         <v>2393002</v>
       </c>
@@ -7786,7 +7809,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="125" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A125" s="2">
         <v>2394004</v>
       </c>
@@ -7833,7 +7856,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="126" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A126" s="2">
         <v>2394004</v>
       </c>
@@ -7880,7 +7903,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="127" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A127" s="2">
         <v>2394004</v>
       </c>
@@ -7927,7 +7950,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="128" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A128" s="2">
         <v>2395003</v>
       </c>
@@ -7974,7 +7997,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="129" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A129" s="2">
         <v>2395003</v>
       </c>
@@ -8021,7 +8044,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="130" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A130" s="2">
         <v>2395003</v>
       </c>
@@ -8068,7 +8091,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="131" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A131" s="2">
         <v>2396001</v>
       </c>
@@ -8115,7 +8138,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="132" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A132" s="2">
         <v>2396001</v>
       </c>
@@ -8162,7 +8185,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="133" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A133" s="2">
         <v>2396001</v>
       </c>
@@ -8209,7 +8232,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="134" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A134" s="2">
         <v>2397003</v>
       </c>
@@ -8259,7 +8282,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="135" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A135" s="2">
         <v>2397003</v>
       </c>
@@ -8309,7 +8332,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="136" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A136" s="2">
         <v>2397003</v>
       </c>
@@ -8359,7 +8382,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="137" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A137" s="2">
         <v>2397008</v>
       </c>
@@ -8406,7 +8429,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="138" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A138" s="2">
         <v>2397008</v>
       </c>
@@ -8453,7 +8476,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="139" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A139" s="2">
         <v>2397008</v>
       </c>
@@ -8500,7 +8523,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="140" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A140" s="2">
         <v>2398001</v>
       </c>
@@ -8550,7 +8573,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="141" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A141" s="2">
         <v>2398001</v>
       </c>
@@ -8601,7 +8624,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="142" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A142" s="2">
         <v>2398001</v>
       </c>
@@ -8652,7 +8675,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="143" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A143" s="2">
         <v>2398006</v>
       </c>
@@ -8699,7 +8722,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="144" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A144" s="2">
         <v>2398006</v>
       </c>
@@ -8746,7 +8769,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="145" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A145" s="2">
         <v>2398006</v>
       </c>
@@ -8793,7 +8816,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="146" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A146" s="2">
         <v>2398013</v>
       </c>
@@ -8840,7 +8863,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="147" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A147" s="2">
         <v>2398013</v>
       </c>
@@ -8887,7 +8910,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A148" s="2">
         <v>2398013</v>
       </c>
@@ -8931,7 +8954,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="149" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A149" s="2">
         <v>2399003</v>
       </c>
@@ -8978,7 +9001,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="150" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A150" s="2">
         <v>2399003</v>
       </c>
@@ -9025,7 +9048,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="151" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A151" s="2">
         <v>2399003</v>
       </c>
@@ -9072,7 +9095,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="152" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A152" s="2">
         <v>2399010</v>
       </c>
@@ -9119,7 +9142,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="153" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A153" s="2">
         <v>2399010</v>
       </c>
@@ -9166,7 +9189,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="154" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A154" s="2">
         <v>2399010</v>
       </c>
@@ -9213,7 +9236,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="155" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A155" s="2">
         <v>2399014</v>
       </c>
@@ -9260,7 +9283,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A156" s="2">
         <v>2399014</v>
       </c>
@@ -9307,7 +9330,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A157" s="2">
         <v>2399014</v>
       </c>
@@ -9351,7 +9374,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="158" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A158" s="2">
         <v>2400003</v>
       </c>
@@ -9391,7 +9414,7 @@
       <c r="M158" t="s">
         <v>26</v>
       </c>
-      <c r="N158" s="8" t="s">
+      <c r="N158" s="6" t="s">
         <v>499</v>
       </c>
       <c r="Q158" t="s">
@@ -9401,7 +9424,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="159" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A159" s="2">
         <v>2400003</v>
       </c>
@@ -9441,7 +9464,7 @@
       <c r="M159" t="s">
         <v>26</v>
       </c>
-      <c r="N159" s="8" t="s">
+      <c r="N159" s="6" t="s">
         <v>500</v>
       </c>
       <c r="Q159" t="s">
@@ -9451,7 +9474,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="160" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A160" s="2">
         <v>2400003</v>
       </c>
@@ -9491,7 +9514,7 @@
       <c r="M160" t="s">
         <v>26</v>
       </c>
-      <c r="N160" s="8" t="s">
+      <c r="N160" s="6" t="s">
         <v>500</v>
       </c>
       <c r="Q160" t="s">
@@ -9501,7 +9524,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="161" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A161" s="2">
         <v>2400008</v>
       </c>
@@ -9548,7 +9571,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="162" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A162" s="2">
         <v>2400008</v>
       </c>
@@ -9595,7 +9618,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="163" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A163" s="2">
         <v>2400008</v>
       </c>
@@ -9642,7 +9665,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="164" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A164" s="2">
         <v>2400012</v>
       </c>
@@ -9692,7 +9715,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="165" spans="1:18" ht="32" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A165" s="2">
         <v>2400012</v>
       </c>
@@ -9742,7 +9765,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="166" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A166" s="2">
         <v>2400012</v>
       </c>
@@ -9789,7 +9812,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="167" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A167" s="2">
         <v>2401001</v>
       </c>
@@ -9836,7 +9859,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="168" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A168" s="2">
         <v>2401001</v>
       </c>
@@ -9883,7 +9906,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="169" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A169" s="2">
         <v>2401001</v>
       </c>
@@ -9930,7 +9953,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="170" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A170" s="2">
         <v>2401007</v>
       </c>
@@ -9977,7 +10000,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="171" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A171" s="2">
         <v>2401007</v>
       </c>
@@ -10024,7 +10047,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="172" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A172" s="2">
         <v>2401007</v>
       </c>
@@ -10071,7 +10094,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="173" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A173" s="2">
         <v>2401013</v>
       </c>
@@ -10121,7 +10144,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="174" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A174" s="2">
         <v>2401013</v>
       </c>
@@ -10171,7 +10194,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="175" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A175" s="2">
         <v>2401013</v>
       </c>
@@ -10221,7 +10244,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="176" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A176" s="2">
         <v>2401018</v>
       </c>
@@ -10268,7 +10291,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="177" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A177" s="2">
         <v>2401018</v>
       </c>
@@ -10315,7 +10338,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="178" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A178" s="2">
         <v>2401018</v>
       </c>
@@ -10362,7 +10385,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="179" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A179" s="2">
         <v>2401018</v>
       </c>
@@ -10409,7 +10432,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="180" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A180" s="2">
         <v>2401018</v>
       </c>
@@ -10456,7 +10479,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="181" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A181" s="2">
         <v>2401018</v>
       </c>
@@ -10503,7 +10526,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="182" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A182" s="2">
         <v>2401018</v>
       </c>
@@ -10550,7 +10573,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="183" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A183" s="2">
         <v>2402003</v>
       </c>
@@ -10601,7 +10624,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="184" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A184" s="2">
         <v>2402003</v>
       </c>
@@ -10652,7 +10675,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="185" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A185" s="2">
         <v>2402003</v>
       </c>
@@ -10703,7 +10726,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="186" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A186" s="2">
         <v>2402008</v>
       </c>
@@ -10753,7 +10776,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="187" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A187" s="2">
         <v>2402008</v>
       </c>
@@ -10803,7 +10826,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="188" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A188" s="2">
         <v>2402008</v>
       </c>
@@ -10853,7 +10876,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="189" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A189" s="2">
         <v>2402015</v>
       </c>
@@ -10900,7 +10923,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="190" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A190" s="2">
         <v>2402015</v>
       </c>
@@ -10947,7 +10970,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="191" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A191" s="2">
         <v>2402015</v>
       </c>
@@ -10993,7 +11016,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="192" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A192" s="2">
         <v>2403004</v>
       </c>
@@ -11044,7 +11067,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="193" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A193" s="2">
         <v>2403004</v>
       </c>
@@ -11095,7 +11118,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="194" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A194" s="2">
         <v>2403004</v>
       </c>
@@ -11146,7 +11169,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="195" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A195" s="2">
         <v>2403009</v>
       </c>
@@ -11193,7 +11216,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="196" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A196" s="2">
         <v>2403009</v>
       </c>
@@ -11240,7 +11263,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="197" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A197" s="2">
         <v>2403009</v>
       </c>
@@ -11287,7 +11310,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="198" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A198" s="2">
         <v>2403013</v>
       </c>
@@ -11331,7 +11354,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="199" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A199" s="2">
         <v>2403013</v>
       </c>
@@ -11375,7 +11398,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="200" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A200" s="2">
         <v>2403013</v>
       </c>
@@ -11419,7 +11442,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="201" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A201" s="2">
         <v>2404001</v>
       </c>
@@ -11469,7 +11492,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="202" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A202" s="2">
         <v>2404001</v>
       </c>
@@ -11519,7 +11542,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="203" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A203" s="2">
         <v>2404001</v>
       </c>
@@ -11569,7 +11592,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="204" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A204" s="2">
         <v>2404006</v>
       </c>
@@ -11619,7 +11642,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="205" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A205" s="2">
         <v>2404006</v>
       </c>
@@ -11669,7 +11692,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="206" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A206" s="2">
         <v>2404006</v>
       </c>
@@ -11719,7 +11742,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="207" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A207" s="2">
         <v>2404015</v>
       </c>
@@ -11766,7 +11789,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="208" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A208" s="2">
         <v>2404015</v>
       </c>
@@ -11813,7 +11836,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="209" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A209" s="2">
         <v>2404015</v>
       </c>
@@ -11860,7 +11883,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="210" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A210" s="2">
         <v>2405001</v>
       </c>
@@ -11900,7 +11923,7 @@
       <c r="M210" t="s">
         <v>26</v>
       </c>
-      <c r="N210" s="8" t="s">
+      <c r="N210" s="6" t="s">
         <v>499</v>
       </c>
       <c r="Q210" t="s">
@@ -11910,7 +11933,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="211" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A211" s="2">
         <v>2405001</v>
       </c>
@@ -11950,7 +11973,7 @@
       <c r="M211" t="s">
         <v>26</v>
       </c>
-      <c r="N211" s="8" t="s">
+      <c r="N211" s="6" t="s">
         <v>500</v>
       </c>
       <c r="Q211" t="s">
@@ -11960,7 +11983,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="212" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A212" s="2">
         <v>2405001</v>
       </c>
@@ -12000,7 +12023,7 @@
       <c r="M212" t="s">
         <v>26</v>
       </c>
-      <c r="N212" s="8" t="s">
+      <c r="N212" s="6" t="s">
         <v>500</v>
       </c>
       <c r="Q212" t="s">
@@ -12010,7 +12033,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="213" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A213" s="2">
         <v>2405006</v>
       </c>
@@ -12050,7 +12073,7 @@
       <c r="M213" t="s">
         <v>26</v>
       </c>
-      <c r="N213" s="8" t="s">
+      <c r="N213" s="6" t="s">
         <v>501</v>
       </c>
       <c r="Q213" t="s">
@@ -12060,7 +12083,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="214" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A214" s="2">
         <v>2405006</v>
       </c>
@@ -12100,7 +12123,7 @@
       <c r="M214" t="s">
         <v>26</v>
       </c>
-      <c r="N214" s="8" t="s">
+      <c r="N214" s="6" t="s">
         <v>502</v>
       </c>
       <c r="Q214" t="s">
@@ -12110,7 +12133,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="215" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A215" s="2">
         <v>2405006</v>
       </c>
@@ -12150,7 +12173,7 @@
       <c r="M215" t="s">
         <v>26</v>
       </c>
-      <c r="N215" s="8" t="s">
+      <c r="N215" s="6" t="s">
         <v>502</v>
       </c>
       <c r="Q215" t="s">
@@ -12160,7 +12183,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="216" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A216" s="2">
         <v>2405015</v>
       </c>
@@ -12210,7 +12233,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="217" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A217" s="2">
         <v>2405015</v>
       </c>
@@ -12260,7 +12283,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="218" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A218" s="2">
         <v>2405015</v>
       </c>
@@ -12307,7 +12330,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="219" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A219" s="2">
         <v>2406004</v>
       </c>
@@ -12347,6 +12370,9 @@
       <c r="M219" t="s">
         <v>26</v>
       </c>
+      <c r="N219" s="6" t="s">
+        <v>508</v>
+      </c>
       <c r="Q219" t="s">
         <v>27</v>
       </c>
@@ -12354,7 +12380,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="220" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A220" s="2">
         <v>2406004</v>
       </c>
@@ -12394,6 +12420,9 @@
       <c r="M220" t="s">
         <v>26</v>
       </c>
+      <c r="N220" s="6" t="s">
+        <v>509</v>
+      </c>
       <c r="Q220" t="s">
         <v>27</v>
       </c>
@@ -12401,7 +12430,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="221" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A221" s="2">
         <v>2406004</v>
       </c>
@@ -12438,6 +12467,9 @@
       <c r="M221" t="s">
         <v>26</v>
       </c>
+      <c r="N221" s="6" t="s">
+        <v>510</v>
+      </c>
       <c r="Q221" t="s">
         <v>27</v>
       </c>
@@ -12445,7 +12477,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="222" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A222" s="2">
         <v>2406004</v>
       </c>
@@ -12485,6 +12517,9 @@
       <c r="M222" t="s">
         <v>26</v>
       </c>
+      <c r="N222" s="6" t="s">
+        <v>509</v>
+      </c>
       <c r="Q222" t="s">
         <v>27</v>
       </c>
@@ -12492,7 +12527,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="223" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A223" s="2">
         <v>2406004</v>
       </c>
@@ -12529,6 +12564,9 @@
       <c r="M223" t="s">
         <v>26</v>
       </c>
+      <c r="N223" s="6" t="s">
+        <v>510</v>
+      </c>
       <c r="Q223" t="s">
         <v>27</v>
       </c>
@@ -12536,7 +12574,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="224" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A224" s="2">
         <v>2406009</v>
       </c>
@@ -12583,7 +12621,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="225" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A225" s="2">
         <v>2406009</v>
       </c>
@@ -12630,7 +12668,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="226" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A226" s="2">
         <v>2406009</v>
       </c>
@@ -12677,7 +12715,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="227" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A227" s="2">
         <v>2406009</v>
       </c>
@@ -12724,7 +12762,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="228" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A228" s="2">
         <v>2406009</v>
       </c>
@@ -12771,7 +12809,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="229" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A229" s="2">
         <v>2406012</v>
       </c>
@@ -12818,7 +12856,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="230" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A230" s="2">
         <v>2406012</v>
       </c>
@@ -12865,7 +12903,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="231" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A231" s="2">
         <v>2406012</v>
       </c>
@@ -12912,7 +12950,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="232" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A232" s="2">
         <v>2059001</v>
       </c>
@@ -12959,7 +12997,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="233" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A233" s="2">
         <v>2059002</v>
       </c>
@@ -13006,7 +13044,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="234" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A234" s="2">
         <v>2059006</v>
       </c>
@@ -13053,7 +13091,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="235" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A235" s="2">
         <v>2140011</v>
       </c>
@@ -13100,7 +13138,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="236" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A236" s="2">
         <v>2390004</v>
       </c>
@@ -13147,7 +13185,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="237" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A237" s="2">
         <v>2390004</v>
       </c>
@@ -13194,7 +13232,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="238" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A238" s="2">
         <v>2390004</v>
       </c>
@@ -13241,7 +13279,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="239" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A239" s="2">
         <v>2390009</v>
       </c>
@@ -13288,7 +13326,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="240" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A240" s="2">
         <v>2390009</v>
       </c>
@@ -13335,7 +13373,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="241" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A241" s="2">
         <v>2390009</v>
       </c>
@@ -13382,7 +13420,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="242" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A242" s="2">
         <v>2390013</v>
       </c>
@@ -13426,7 +13464,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="243" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A243" s="2">
         <v>2390013</v>
       </c>
@@ -13470,7 +13508,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="244" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A244" s="2">
         <v>2390013</v>
       </c>
@@ -13514,7 +13552,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="252" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="L252" s="1"/>
     </row>
   </sheetData>

--- a/POD_2026-27_11-5-2026.xlsx
+++ b/POD_2026-27_11-5-2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10811"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\misael.marriaga\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guillermo.vera/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2154AF3F-8C8B-486B-BBEA-DF6EC509CE37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19609D64-F2BC-D446-ADE4-AD54680CBE62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="POD" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2957" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2959" uniqueCount="513">
   <si>
     <t>POD_2026-27_11-5-2026</t>
   </si>
@@ -1569,6 +1569,12 @@
   </si>
   <si>
     <t>ELENA CASTILLA (8)</t>
+  </si>
+  <si>
+    <t>X=&gt;(21:00-22:00)[16/09/26, 23/09/26, 07/10/26, 14/10/26, 28/10/26, 04/11/26, 11/11/26, 18/11/26]</t>
+  </si>
+  <si>
+    <t>J=&gt;(21:00-22:00)[10/09/26, 17/09/26, 24/09/26, 01/10/26, 08/10/26, 15/10/26, 22/10/26, 29/10/26]</t>
   </si>
 </sst>
 </file>
@@ -1651,9 +1657,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1691,7 +1697,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1797,7 +1803,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1939,7 +1945,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1948,30 +1954,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S252"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="71.36328125" customWidth="1"/>
+    <col min="2" max="2" width="71.33203125" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="9.1796875" customWidth="1"/>
-    <col min="5" max="5" width="20.1796875" customWidth="1"/>
-    <col min="6" max="6" width="64.1796875" customWidth="1"/>
-    <col min="7" max="7" width="20.81640625" customWidth="1"/>
-    <col min="8" max="8" width="6.453125" customWidth="1"/>
-    <col min="9" max="9" width="7.81640625" customWidth="1"/>
-    <col min="10" max="10" width="6.453125" customWidth="1"/>
-    <col min="11" max="11" width="107.1796875" customWidth="1"/>
-    <col min="12" max="12" width="53.6328125" customWidth="1"/>
-    <col min="13" max="13" width="12.6328125" customWidth="1"/>
-    <col min="14" max="14" width="36.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="36.453125" customWidth="1"/>
-    <col min="16" max="16" width="20.81640625" customWidth="1"/>
+    <col min="4" max="4" width="9.1640625" customWidth="1"/>
+    <col min="5" max="5" width="20.1640625" customWidth="1"/>
+    <col min="6" max="6" width="64.1640625" customWidth="1"/>
+    <col min="7" max="7" width="20.83203125" customWidth="1"/>
+    <col min="8" max="8" width="6.5" customWidth="1"/>
+    <col min="9" max="9" width="7.83203125" customWidth="1"/>
+    <col min="10" max="10" width="6.5" customWidth="1"/>
+    <col min="11" max="11" width="107.1640625" customWidth="1"/>
+    <col min="12" max="12" width="53.6640625" customWidth="1"/>
+    <col min="13" max="13" width="12.6640625" customWidth="1"/>
+    <col min="14" max="14" width="36.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="36.5" customWidth="1"/>
+    <col min="16" max="16" width="20.83203125" customWidth="1"/>
     <col min="17" max="17" width="52" customWidth="1"/>
-    <col min="18" max="18" width="32.453125" customWidth="1"/>
-    <col min="19" max="19" width="16.81640625" customWidth="1"/>
+    <col min="18" max="18" width="32.5" customWidth="1"/>
+    <col min="19" max="19" width="16.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1994,7 +2000,7 @@
       <c r="R1" s="8"/>
       <c r="S1" s="8"/>
     </row>
-    <row r="2" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2053,7 +2059,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>2291005</v>
       </c>
@@ -2097,7 +2103,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>2291009</v>
       </c>
@@ -2141,7 +2147,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>2240005</v>
       </c>
@@ -2188,7 +2194,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>2240009</v>
       </c>
@@ -2235,7 +2241,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>2251011</v>
       </c>
@@ -2279,7 +2285,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>2327002</v>
       </c>
@@ -2323,7 +2329,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>2327002</v>
       </c>
@@ -2367,7 +2373,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>2327002</v>
       </c>
@@ -2411,7 +2417,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>2327007</v>
       </c>
@@ -2461,7 +2467,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>2327007</v>
       </c>
@@ -2511,7 +2517,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>2327007</v>
       </c>
@@ -2561,7 +2567,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>2327015</v>
       </c>
@@ -2605,7 +2611,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>2327015</v>
       </c>
@@ -2649,7 +2655,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>2327015</v>
       </c>
@@ -2693,7 +2699,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>2360001</v>
       </c>
@@ -2737,7 +2743,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>2360002</v>
       </c>
@@ -2781,7 +2787,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>2382005</v>
       </c>
@@ -2828,7 +2834,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>2382005</v>
       </c>
@@ -2875,7 +2881,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>2382005</v>
       </c>
@@ -2922,7 +2928,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>2382005</v>
       </c>
@@ -2969,7 +2975,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>2382005</v>
       </c>
@@ -3016,7 +3022,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>2382005</v>
       </c>
@@ -3063,7 +3069,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>2382010</v>
       </c>
@@ -3110,7 +3116,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>2382010</v>
       </c>
@@ -3157,7 +3163,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>2382010</v>
       </c>
@@ -3204,7 +3210,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>2382010</v>
       </c>
@@ -3251,7 +3257,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>2382010</v>
       </c>
@@ -3295,7 +3301,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>2382010</v>
       </c>
@@ -3342,7 +3348,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>2383001</v>
       </c>
@@ -3392,7 +3398,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>2383001</v>
       </c>
@@ -3439,7 +3445,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>2383001</v>
       </c>
@@ -3486,7 +3492,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>2383001</v>
       </c>
@@ -3536,7 +3542,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>2383001</v>
       </c>
@@ -3586,7 +3592,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>2383001</v>
       </c>
@@ -3636,7 +3642,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>2383002</v>
       </c>
@@ -3683,7 +3689,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>2383002</v>
       </c>
@@ -3727,7 +3733,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>2383002</v>
       </c>
@@ -3771,7 +3777,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>2383002</v>
       </c>
@@ -3818,7 +3824,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>2383002</v>
       </c>
@@ -3865,7 +3871,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>2383002</v>
       </c>
@@ -3912,7 +3918,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:18" ht="48" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>2383007</v>
       </c>
@@ -3962,7 +3968,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:18" ht="48" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>2383007</v>
       </c>
@@ -4012,7 +4018,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>2384001</v>
       </c>
@@ -4062,7 +4068,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>2384001</v>
       </c>
@@ -4112,7 +4118,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>2384001</v>
       </c>
@@ -4162,7 +4168,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
         <v>2384005</v>
       </c>
@@ -4209,7 +4215,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
         <v>2384005</v>
       </c>
@@ -4256,7 +4262,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
         <v>2384005</v>
       </c>
@@ -4303,7 +4309,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="51" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
         <v>2385001</v>
       </c>
@@ -4353,7 +4359,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="52" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
         <v>2385001</v>
       </c>
@@ -4403,7 +4409,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="53" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
         <v>2385001</v>
       </c>
@@ -4453,7 +4459,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
         <v>2385005</v>
       </c>
@@ -4500,7 +4506,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
         <v>2385005</v>
       </c>
@@ -4547,7 +4553,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="56" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
         <v>2385005</v>
       </c>
@@ -4594,7 +4600,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="57" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
         <v>2386001</v>
       </c>
@@ -4641,7 +4647,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="58" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
         <v>2386001</v>
       </c>
@@ -4685,7 +4691,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="59" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
         <v>2386001</v>
       </c>
@@ -4729,7 +4735,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="60" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
         <v>2386001</v>
       </c>
@@ -4776,7 +4782,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="61" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
         <v>2386001</v>
       </c>
@@ -4820,7 +4826,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="62" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
         <v>2386001</v>
       </c>
@@ -4865,7 +4871,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="63" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
         <v>2386002</v>
       </c>
@@ -4912,7 +4918,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="64" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
         <v>2386002</v>
       </c>
@@ -4962,7 +4968,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="65" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
         <v>2387009</v>
       </c>
@@ -5009,7 +5015,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="66" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
         <v>2387009</v>
       </c>
@@ -5053,7 +5059,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="67" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
         <v>2387009</v>
       </c>
@@ -5097,7 +5103,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="68" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
         <v>2387016</v>
       </c>
@@ -5141,7 +5147,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="69" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
         <v>2387016</v>
       </c>
@@ -5182,7 +5188,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="70" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
         <v>2387016</v>
       </c>
@@ -5223,7 +5229,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="71" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
         <v>2265020</v>
       </c>
@@ -5271,7 +5277,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="72" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
         <v>2029018</v>
       </c>
@@ -5318,7 +5324,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="73" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
         <v>2030013</v>
       </c>
@@ -5365,7 +5371,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="74" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
         <v>2031001</v>
       </c>
@@ -5409,7 +5415,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="75" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
         <v>2032001</v>
       </c>
@@ -5459,7 +5465,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="76" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
         <v>2032007</v>
       </c>
@@ -5509,7 +5515,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="77" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
         <v>2032009</v>
       </c>
@@ -5553,7 +5559,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="78" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
         <v>2033001</v>
       </c>
@@ -5600,7 +5606,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="79" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
         <v>2033002</v>
       </c>
@@ -5651,7 +5657,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="80" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
         <v>2033006</v>
       </c>
@@ -5701,7 +5707,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="81" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
         <v>2034001</v>
       </c>
@@ -5748,7 +5754,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="82" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
         <v>2034002</v>
       </c>
@@ -5801,7 +5807,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="83" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
         <v>2034006</v>
       </c>
@@ -5848,7 +5854,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="84" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
         <v>2061001</v>
       </c>
@@ -5892,7 +5898,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="85" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
         <v>2061002</v>
       </c>
@@ -5939,7 +5945,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="86" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
         <v>2061006</v>
       </c>
@@ -5983,7 +5989,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="87" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
         <v>2107013</v>
       </c>
@@ -6030,7 +6036,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="88" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
         <v>2143016</v>
       </c>
@@ -6077,7 +6083,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="89" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
         <v>2148011</v>
       </c>
@@ -6121,7 +6127,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="90" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
         <v>2175020</v>
       </c>
@@ -6168,7 +6174,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="91" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
         <v>2285005</v>
       </c>
@@ -6216,7 +6222,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="92" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
         <v>2285006</v>
       </c>
@@ -6263,7 +6269,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="93" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
         <v>2285007</v>
       </c>
@@ -6310,7 +6316,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="94" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
         <v>2286015</v>
       </c>
@@ -6354,7 +6360,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="95" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
         <v>2338044</v>
       </c>
@@ -6398,7 +6404,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="96" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
         <v>2342014</v>
       </c>
@@ -6445,7 +6451,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="97" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
         <v>5</v>
       </c>
@@ -6493,7 +6499,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="98" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
         <v>2343027</v>
       </c>
@@ -6541,7 +6547,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="99" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
         <v>2343027</v>
       </c>
@@ -6588,7 +6594,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="100" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
         <v>2343027</v>
       </c>
@@ -6634,7 +6640,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="101" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
         <v>2347001</v>
       </c>
@@ -6684,7 +6690,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="102" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
         <v>2347003</v>
       </c>
@@ -6734,7 +6740,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="103" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
         <v>2347005</v>
       </c>
@@ -6785,7 +6791,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="104" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A104" s="2">
         <v>2347006</v>
       </c>
@@ -6835,7 +6841,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="105" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A105" s="2">
         <v>2347007</v>
       </c>
@@ -6886,7 +6892,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="106" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A106" s="2">
         <v>2347013</v>
       </c>
@@ -6936,7 +6942,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="107" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A107" s="2">
         <v>2347014</v>
       </c>
@@ -6983,7 +6989,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="108" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A108" s="2">
         <v>2347017</v>
       </c>
@@ -7033,7 +7039,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="109" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A109" s="2">
         <v>2347030</v>
       </c>
@@ -7084,7 +7090,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="110" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A110" s="2">
         <v>2347021</v>
       </c>
@@ -7134,7 +7140,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="111" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A111" s="2">
         <v>2347022</v>
       </c>
@@ -7186,7 +7192,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="112" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A112" s="2">
         <v>2347024</v>
       </c>
@@ -7236,7 +7242,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="113" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A113" s="2">
         <v>2347026</v>
       </c>
@@ -7287,7 +7293,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="114" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A114" s="2">
         <v>2347027</v>
       </c>
@@ -7338,7 +7344,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="115" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A115" s="2">
         <v>2347029</v>
       </c>
@@ -7388,7 +7394,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="116" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A116" s="2">
         <v>2347031</v>
       </c>
@@ -7438,7 +7444,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="117" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A117" s="2">
         <v>2347038</v>
       </c>
@@ -7489,7 +7495,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="118" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A118" s="2">
         <v>2361002</v>
       </c>
@@ -7533,7 +7539,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="119" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A119" s="2">
         <v>2361002</v>
       </c>
@@ -7577,7 +7583,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="120" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A120" s="2">
         <v>2361002</v>
       </c>
@@ -7621,7 +7627,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="121" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A121" s="2">
         <v>2361004</v>
       </c>
@@ -7668,7 +7674,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="122" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A122" s="2">
         <v>2393002</v>
       </c>
@@ -7715,7 +7721,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="123" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A123" s="2">
         <v>2393002</v>
       </c>
@@ -7762,7 +7768,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="124" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A124" s="2">
         <v>2393002</v>
       </c>
@@ -7809,7 +7815,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="125" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A125" s="2">
         <v>2394004</v>
       </c>
@@ -7856,7 +7862,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="126" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A126" s="2">
         <v>2394004</v>
       </c>
@@ -7903,7 +7909,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="127" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A127" s="2">
         <v>2394004</v>
       </c>
@@ -7950,7 +7956,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="128" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A128" s="2">
         <v>2395003</v>
       </c>
@@ -7997,7 +8003,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="129" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A129" s="2">
         <v>2395003</v>
       </c>
@@ -8044,7 +8050,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="130" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A130" s="2">
         <v>2395003</v>
       </c>
@@ -8091,7 +8097,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="131" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A131" s="2">
         <v>2396001</v>
       </c>
@@ -8138,7 +8144,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="132" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A132" s="2">
         <v>2396001</v>
       </c>
@@ -8185,7 +8191,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="133" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A133" s="2">
         <v>2396001</v>
       </c>
@@ -8232,7 +8238,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="134" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A134" s="2">
         <v>2397003</v>
       </c>
@@ -8282,7 +8288,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="135" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A135" s="2">
         <v>2397003</v>
       </c>
@@ -8332,7 +8338,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="136" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A136" s="2">
         <v>2397003</v>
       </c>
@@ -8382,7 +8388,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="137" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A137" s="2">
         <v>2397008</v>
       </c>
@@ -8429,7 +8435,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="138" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A138" s="2">
         <v>2397008</v>
       </c>
@@ -8476,7 +8482,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="139" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A139" s="2">
         <v>2397008</v>
       </c>
@@ -8523,7 +8529,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="140" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A140" s="2">
         <v>2398001</v>
       </c>
@@ -8573,7 +8579,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="141" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A141" s="2">
         <v>2398001</v>
       </c>
@@ -8624,7 +8630,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="142" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A142" s="2">
         <v>2398001</v>
       </c>
@@ -8675,7 +8681,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="143" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A143" s="2">
         <v>2398006</v>
       </c>
@@ -8722,7 +8728,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="144" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A144" s="2">
         <v>2398006</v>
       </c>
@@ -8769,7 +8775,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="145" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A145" s="2">
         <v>2398006</v>
       </c>
@@ -8816,7 +8822,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="146" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A146" s="2">
         <v>2398013</v>
       </c>
@@ -8863,7 +8869,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="147" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A147" s="2">
         <v>2398013</v>
       </c>
@@ -8910,7 +8916,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="148" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A148" s="2">
         <v>2398013</v>
       </c>
@@ -8954,7 +8960,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="149" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A149" s="2">
         <v>2399003</v>
       </c>
@@ -9001,7 +9007,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="150" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A150" s="2">
         <v>2399003</v>
       </c>
@@ -9048,7 +9054,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="151" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A151" s="2">
         <v>2399003</v>
       </c>
@@ -9095,7 +9101,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="152" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A152" s="2">
         <v>2399010</v>
       </c>
@@ -9142,7 +9148,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="153" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A153" s="2">
         <v>2399010</v>
       </c>
@@ -9189,7 +9195,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="154" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A154" s="2">
         <v>2399010</v>
       </c>
@@ -9236,7 +9242,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="155" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A155" s="2">
         <v>2399014</v>
       </c>
@@ -9283,7 +9289,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="156" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A156" s="2">
         <v>2399014</v>
       </c>
@@ -9330,7 +9336,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="157" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A157" s="2">
         <v>2399014</v>
       </c>
@@ -9374,7 +9380,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="158" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A158" s="2">
         <v>2400003</v>
       </c>
@@ -9424,7 +9430,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="159" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A159" s="2">
         <v>2400003</v>
       </c>
@@ -9474,7 +9480,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="160" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A160" s="2">
         <v>2400003</v>
       </c>
@@ -9524,7 +9530,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="161" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A161" s="2">
         <v>2400008</v>
       </c>
@@ -9571,7 +9577,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="162" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A162" s="2">
         <v>2400008</v>
       </c>
@@ -9618,7 +9624,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="163" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A163" s="2">
         <v>2400008</v>
       </c>
@@ -9665,7 +9671,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="164" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A164" s="2">
         <v>2400012</v>
       </c>
@@ -9715,7 +9721,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="165" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:18" ht="32" x14ac:dyDescent="0.2">
       <c r="A165" s="2">
         <v>2400012</v>
       </c>
@@ -9765,7 +9771,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="166" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A166" s="2">
         <v>2400012</v>
       </c>
@@ -9812,7 +9818,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="167" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A167" s="2">
         <v>2401001</v>
       </c>
@@ -9859,7 +9865,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="168" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A168" s="2">
         <v>2401001</v>
       </c>
@@ -9906,7 +9912,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="169" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A169" s="2">
         <v>2401001</v>
       </c>
@@ -9953,7 +9959,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="170" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A170" s="2">
         <v>2401007</v>
       </c>
@@ -10000,7 +10006,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="171" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A171" s="2">
         <v>2401007</v>
       </c>
@@ -10047,7 +10053,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="172" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A172" s="2">
         <v>2401007</v>
       </c>
@@ -10094,7 +10100,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="173" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A173" s="2">
         <v>2401013</v>
       </c>
@@ -10144,7 +10150,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="174" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A174" s="2">
         <v>2401013</v>
       </c>
@@ -10194,7 +10200,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="175" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A175" s="2">
         <v>2401013</v>
       </c>
@@ -10244,7 +10250,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="176" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A176" s="2">
         <v>2401018</v>
       </c>
@@ -10291,7 +10297,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="177" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A177" s="2">
         <v>2401018</v>
       </c>
@@ -10338,7 +10344,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="178" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A178" s="2">
         <v>2401018</v>
       </c>
@@ -10385,7 +10391,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="179" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A179" s="2">
         <v>2401018</v>
       </c>
@@ -10432,7 +10438,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="180" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A180" s="2">
         <v>2401018</v>
       </c>
@@ -10479,7 +10485,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="181" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A181" s="2">
         <v>2401018</v>
       </c>
@@ -10526,7 +10532,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="182" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A182" s="2">
         <v>2401018</v>
       </c>
@@ -10573,7 +10579,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="183" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A183" s="2">
         <v>2402003</v>
       </c>
@@ -10624,7 +10630,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="184" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A184" s="2">
         <v>2402003</v>
       </c>
@@ -10675,7 +10681,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="185" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A185" s="2">
         <v>2402003</v>
       </c>
@@ -10726,7 +10732,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="186" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A186" s="2">
         <v>2402008</v>
       </c>
@@ -10776,7 +10782,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="187" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A187" s="2">
         <v>2402008</v>
       </c>
@@ -10826,7 +10832,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="188" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A188" s="2">
         <v>2402008</v>
       </c>
@@ -10876,7 +10882,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="189" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A189" s="2">
         <v>2402015</v>
       </c>
@@ -10923,7 +10929,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="190" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A190" s="2">
         <v>2402015</v>
       </c>
@@ -10970,7 +10976,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="191" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A191" s="2">
         <v>2402015</v>
       </c>
@@ -11016,7 +11022,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="192" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A192" s="2">
         <v>2403004</v>
       </c>
@@ -11067,7 +11073,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="193" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A193" s="2">
         <v>2403004</v>
       </c>
@@ -11118,7 +11124,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="194" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A194" s="2">
         <v>2403004</v>
       </c>
@@ -11169,7 +11175,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="195" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A195" s="2">
         <v>2403009</v>
       </c>
@@ -11216,7 +11222,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="196" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A196" s="2">
         <v>2403009</v>
       </c>
@@ -11263,7 +11269,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="197" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A197" s="2">
         <v>2403009</v>
       </c>
@@ -11310,7 +11316,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="198" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A198" s="2">
         <v>2403013</v>
       </c>
@@ -11354,7 +11360,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="199" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A199" s="2">
         <v>2403013</v>
       </c>
@@ -11398,7 +11404,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="200" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A200" s="2">
         <v>2403013</v>
       </c>
@@ -11442,7 +11448,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="201" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A201" s="2">
         <v>2404001</v>
       </c>
@@ -11492,7 +11498,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="202" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A202" s="2">
         <v>2404001</v>
       </c>
@@ -11542,7 +11548,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="203" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A203" s="2">
         <v>2404001</v>
       </c>
@@ -11592,7 +11598,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="204" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A204" s="2">
         <v>2404006</v>
       </c>
@@ -11642,7 +11648,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="205" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A205" s="2">
         <v>2404006</v>
       </c>
@@ -11692,7 +11698,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="206" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A206" s="2">
         <v>2404006</v>
       </c>
@@ -11742,7 +11748,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="207" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A207" s="2">
         <v>2404015</v>
       </c>
@@ -11789,7 +11795,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="208" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A208" s="2">
         <v>2404015</v>
       </c>
@@ -11836,7 +11842,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="209" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A209" s="2">
         <v>2404015</v>
       </c>
@@ -11883,7 +11889,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="210" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A210" s="2">
         <v>2405001</v>
       </c>
@@ -11933,7 +11939,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="211" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A211" s="2">
         <v>2405001</v>
       </c>
@@ -11983,7 +11989,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="212" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A212" s="2">
         <v>2405001</v>
       </c>
@@ -12033,7 +12039,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="213" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A213" s="2">
         <v>2405006</v>
       </c>
@@ -12083,7 +12089,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="214" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A214" s="2">
         <v>2405006</v>
       </c>
@@ -12133,7 +12139,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="215" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A215" s="2">
         <v>2405006</v>
       </c>
@@ -12183,7 +12189,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="216" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A216" s="2">
         <v>2405015</v>
       </c>
@@ -12233,7 +12239,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="217" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A217" s="2">
         <v>2405015</v>
       </c>
@@ -12283,7 +12289,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="218" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A218" s="2">
         <v>2405015</v>
       </c>
@@ -12330,7 +12336,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="219" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A219" s="2">
         <v>2406004</v>
       </c>
@@ -12361,7 +12367,7 @@
       <c r="J219" t="s">
         <v>24</v>
       </c>
-      <c r="K219" t="s">
+      <c r="K219" s="6" t="s">
         <v>446</v>
       </c>
       <c r="L219" t="s">
@@ -12380,7 +12386,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="220" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A220" s="2">
         <v>2406004</v>
       </c>
@@ -12430,7 +12436,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="221" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A221" s="2">
         <v>2406004</v>
       </c>
@@ -12461,6 +12467,9 @@
       <c r="J221" t="s">
         <v>24</v>
       </c>
+      <c r="K221" s="6" t="s">
+        <v>511</v>
+      </c>
       <c r="L221" t="s">
         <v>447</v>
       </c>
@@ -12477,7 +12486,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="222" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A222" s="2">
         <v>2406004</v>
       </c>
@@ -12527,7 +12536,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="223" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A223" s="2">
         <v>2406004</v>
       </c>
@@ -12558,6 +12567,9 @@
       <c r="J223" t="s">
         <v>24</v>
       </c>
+      <c r="K223" s="6" t="s">
+        <v>512</v>
+      </c>
       <c r="L223" t="s">
         <v>447</v>
       </c>
@@ -12574,7 +12586,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="224" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A224" s="2">
         <v>2406009</v>
       </c>
@@ -12621,7 +12633,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="225" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A225" s="2">
         <v>2406009</v>
       </c>
@@ -12668,7 +12680,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="226" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A226" s="2">
         <v>2406009</v>
       </c>
@@ -12715,7 +12727,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="227" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A227" s="2">
         <v>2406009</v>
       </c>
@@ -12762,7 +12774,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="228" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A228" s="2">
         <v>2406009</v>
       </c>
@@ -12809,7 +12821,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="229" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A229" s="2">
         <v>2406012</v>
       </c>
@@ -12856,7 +12868,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="230" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A230" s="2">
         <v>2406012</v>
       </c>
@@ -12903,7 +12915,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="231" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A231" s="2">
         <v>2406012</v>
       </c>
@@ -12950,7 +12962,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="232" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A232" s="2">
         <v>2059001</v>
       </c>
@@ -12997,7 +13009,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="233" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A233" s="2">
         <v>2059002</v>
       </c>
@@ -13044,7 +13056,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="234" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A234" s="2">
         <v>2059006</v>
       </c>
@@ -13091,7 +13103,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="235" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A235" s="2">
         <v>2140011</v>
       </c>
@@ -13138,7 +13150,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="236" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A236" s="2">
         <v>2390004</v>
       </c>
@@ -13185,7 +13197,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="237" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A237" s="2">
         <v>2390004</v>
       </c>
@@ -13232,7 +13244,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="238" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A238" s="2">
         <v>2390004</v>
       </c>
@@ -13279,7 +13291,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="239" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A239" s="2">
         <v>2390009</v>
       </c>
@@ -13326,7 +13338,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="240" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A240" s="2">
         <v>2390009</v>
       </c>
@@ -13373,7 +13385,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="241" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A241" s="2">
         <v>2390009</v>
       </c>
@@ -13420,7 +13432,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="242" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A242" s="2">
         <v>2390013</v>
       </c>
@@ -13464,7 +13476,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="243" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A243" s="2">
         <v>2390013</v>
       </c>
@@ -13508,7 +13520,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="244" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A244" s="2">
         <v>2390013</v>
       </c>
@@ -13552,7 +13564,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="252" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L252" s="1"/>
     </row>
   </sheetData>

--- a/POD_2026-27_11-5-2026.xlsx
+++ b/POD_2026-27_11-5-2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guillermo.vera/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\misael.marriaga\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19609D64-F2BC-D446-ADE4-AD54680CBE62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{645D15A8-518B-4DEF-9D73-600E718810F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="POD" sheetId="1" r:id="rId1"/>
@@ -1571,10 +1571,10 @@
     <t>ELENA CASTILLA (8)</t>
   </si>
   <si>
-    <t>X=&gt;(21:00-22:00)[16/09/26, 23/09/26, 07/10/26, 14/10/26, 28/10/26, 04/11/26, 11/11/26, 18/11/26]</t>
-  </si>
-  <si>
-    <t>J=&gt;(21:00-22:00)[10/09/26, 17/09/26, 24/09/26, 01/10/26, 08/10/26, 15/10/26, 22/10/26, 29/10/26]</t>
+    <t>V=&gt;(17:00-18:00)[11/09/26, 18/09/26]</t>
+  </si>
+  <si>
+    <t>V=&gt;(17:00-18:00)[25/09/26, 02/10/26]</t>
   </si>
 </sst>
 </file>
@@ -1657,9 +1657,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1697,7 +1697,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1803,7 +1803,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1945,7 +1945,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1954,30 +1954,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S252"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="71.33203125" customWidth="1"/>
+    <col min="2" max="2" width="71.36328125" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" customWidth="1"/>
-    <col min="5" max="5" width="20.1640625" customWidth="1"/>
-    <col min="6" max="6" width="64.1640625" customWidth="1"/>
-    <col min="7" max="7" width="20.83203125" customWidth="1"/>
-    <col min="8" max="8" width="6.5" customWidth="1"/>
-    <col min="9" max="9" width="7.83203125" customWidth="1"/>
-    <col min="10" max="10" width="6.5" customWidth="1"/>
-    <col min="11" max="11" width="107.1640625" customWidth="1"/>
-    <col min="12" max="12" width="53.6640625" customWidth="1"/>
-    <col min="13" max="13" width="12.6640625" customWidth="1"/>
-    <col min="14" max="14" width="36.5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="36.5" customWidth="1"/>
-    <col min="16" max="16" width="20.83203125" customWidth="1"/>
+    <col min="4" max="4" width="9.1796875" customWidth="1"/>
+    <col min="5" max="5" width="20.1796875" customWidth="1"/>
+    <col min="6" max="6" width="64.1796875" customWidth="1"/>
+    <col min="7" max="7" width="20.81640625" customWidth="1"/>
+    <col min="8" max="8" width="6.453125" customWidth="1"/>
+    <col min="9" max="9" width="7.81640625" customWidth="1"/>
+    <col min="10" max="10" width="6.453125" customWidth="1"/>
+    <col min="11" max="11" width="107.1796875" customWidth="1"/>
+    <col min="12" max="12" width="53.6328125" customWidth="1"/>
+    <col min="13" max="13" width="12.6328125" customWidth="1"/>
+    <col min="14" max="14" width="36.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="36.453125" customWidth="1"/>
+    <col min="16" max="16" width="20.81640625" customWidth="1"/>
     <col min="17" max="17" width="52" customWidth="1"/>
-    <col min="18" max="18" width="32.5" customWidth="1"/>
-    <col min="19" max="19" width="16.83203125" customWidth="1"/>
+    <col min="18" max="18" width="32.453125" customWidth="1"/>
+    <col min="19" max="19" width="16.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -2000,7 +2000,7 @@
       <c r="R1" s="8"/>
       <c r="S1" s="8"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2059,7 +2059,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>2291005</v>
       </c>
@@ -2103,7 +2103,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>2291009</v>
       </c>
@@ -2147,7 +2147,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>2240005</v>
       </c>
@@ -2194,7 +2194,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>2240009</v>
       </c>
@@ -2241,7 +2241,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>2251011</v>
       </c>
@@ -2285,7 +2285,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>2327002</v>
       </c>
@@ -2329,7 +2329,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>2327002</v>
       </c>
@@ -2373,7 +2373,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>2327002</v>
       </c>
@@ -2417,7 +2417,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>2327007</v>
       </c>
@@ -2467,7 +2467,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>2327007</v>
       </c>
@@ -2517,7 +2517,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>2327007</v>
       </c>
@@ -2567,7 +2567,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>2327015</v>
       </c>
@@ -2611,7 +2611,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>2327015</v>
       </c>
@@ -2655,7 +2655,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>2327015</v>
       </c>
@@ -2699,7 +2699,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>2360001</v>
       </c>
@@ -2743,7 +2743,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>2360002</v>
       </c>
@@ -2787,7 +2787,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>2382005</v>
       </c>
@@ -2834,7 +2834,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>2382005</v>
       </c>
@@ -2881,7 +2881,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>2382005</v>
       </c>
@@ -2928,7 +2928,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>2382005</v>
       </c>
@@ -2975,7 +2975,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>2382005</v>
       </c>
@@ -3022,7 +3022,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>2382005</v>
       </c>
@@ -3069,7 +3069,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>2382010</v>
       </c>
@@ -3116,7 +3116,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>2382010</v>
       </c>
@@ -3163,7 +3163,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>2382010</v>
       </c>
@@ -3210,7 +3210,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>2382010</v>
       </c>
@@ -3257,7 +3257,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>2382010</v>
       </c>
@@ -3301,7 +3301,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>2382010</v>
       </c>
@@ -3348,7 +3348,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>2383001</v>
       </c>
@@ -3398,7 +3398,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>2383001</v>
       </c>
@@ -3445,7 +3445,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>2383001</v>
       </c>
@@ -3492,7 +3492,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>2383001</v>
       </c>
@@ -3542,7 +3542,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>2383001</v>
       </c>
@@ -3592,7 +3592,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>2383001</v>
       </c>
@@ -3642,7 +3642,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <v>2383002</v>
       </c>
@@ -3689,7 +3689,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <v>2383002</v>
       </c>
@@ -3733,7 +3733,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <v>2383002</v>
       </c>
@@ -3777,7 +3777,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>2383002</v>
       </c>
@@ -3824,7 +3824,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>2383002</v>
       </c>
@@ -3871,7 +3871,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>2383002</v>
       </c>
@@ -3918,7 +3918,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="48" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <v>2383007</v>
       </c>
@@ -3968,7 +3968,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:18" ht="48" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>2383007</v>
       </c>
@@ -4018,7 +4018,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <v>2384001</v>
       </c>
@@ -4068,7 +4068,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>2384001</v>
       </c>
@@ -4118,7 +4118,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <v>2384001</v>
       </c>
@@ -4168,7 +4168,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>2384005</v>
       </c>
@@ -4215,7 +4215,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <v>2384005</v>
       </c>
@@ -4262,7 +4262,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <v>2384005</v>
       </c>
@@ -4309,7 +4309,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <v>2385001</v>
       </c>
@@ -4359,7 +4359,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <v>2385001</v>
       </c>
@@ -4409,7 +4409,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
         <v>2385001</v>
       </c>
@@ -4459,7 +4459,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <v>2385005</v>
       </c>
@@ -4506,7 +4506,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
         <v>2385005</v>
       </c>
@@ -4553,7 +4553,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <v>2385005</v>
       </c>
@@ -4600,7 +4600,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
         <v>2386001</v>
       </c>
@@ -4647,7 +4647,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <v>2386001</v>
       </c>
@@ -4691,7 +4691,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
         <v>2386001</v>
       </c>
@@ -4735,7 +4735,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>2386001</v>
       </c>
@@ -4782,7 +4782,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <v>2386001</v>
       </c>
@@ -4826,7 +4826,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <v>2386001</v>
       </c>
@@ -4871,7 +4871,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
         <v>2386002</v>
       </c>
@@ -4918,7 +4918,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
         <v>2386002</v>
       </c>
@@ -4968,7 +4968,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A65" s="2">
         <v>2387009</v>
       </c>
@@ -5015,7 +5015,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A66" s="2">
         <v>2387009</v>
       </c>
@@ -5059,7 +5059,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A67" s="2">
         <v>2387009</v>
       </c>
@@ -5103,7 +5103,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A68" s="2">
         <v>2387016</v>
       </c>
@@ -5147,7 +5147,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A69" s="2">
         <v>2387016</v>
       </c>
@@ -5188,7 +5188,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A70" s="2">
         <v>2387016</v>
       </c>
@@ -5229,7 +5229,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="71" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A71" s="2">
         <v>2265020</v>
       </c>
@@ -5277,7 +5277,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A72" s="2">
         <v>2029018</v>
       </c>
@@ -5324,7 +5324,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A73" s="2">
         <v>2030013</v>
       </c>
@@ -5371,7 +5371,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A74" s="2">
         <v>2031001</v>
       </c>
@@ -5415,7 +5415,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A75" s="2">
         <v>2032001</v>
       </c>
@@ -5465,7 +5465,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A76" s="2">
         <v>2032007</v>
       </c>
@@ -5515,7 +5515,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A77" s="2">
         <v>2032009</v>
       </c>
@@ -5559,7 +5559,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A78" s="2">
         <v>2033001</v>
       </c>
@@ -5606,7 +5606,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="79" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A79" s="2">
         <v>2033002</v>
       </c>
@@ -5657,7 +5657,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A80" s="2">
         <v>2033006</v>
       </c>
@@ -5707,7 +5707,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A81" s="2">
         <v>2034001</v>
       </c>
@@ -5754,7 +5754,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="82" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A82" s="2">
         <v>2034002</v>
       </c>
@@ -5807,7 +5807,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A83" s="2">
         <v>2034006</v>
       </c>
@@ -5854,7 +5854,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A84" s="2">
         <v>2061001</v>
       </c>
@@ -5898,7 +5898,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A85" s="2">
         <v>2061002</v>
       </c>
@@ -5945,7 +5945,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A86" s="2">
         <v>2061006</v>
       </c>
@@ -5989,7 +5989,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A87" s="2">
         <v>2107013</v>
       </c>
@@ -6036,7 +6036,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A88" s="2">
         <v>2143016</v>
       </c>
@@ -6083,7 +6083,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A89" s="2">
         <v>2148011</v>
       </c>
@@ -6127,7 +6127,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A90" s="2">
         <v>2175020</v>
       </c>
@@ -6174,7 +6174,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="91" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A91" s="2">
         <v>2285005</v>
       </c>
@@ -6222,7 +6222,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A92" s="2">
         <v>2285006</v>
       </c>
@@ -6269,7 +6269,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A93" s="2">
         <v>2285007</v>
       </c>
@@ -6316,7 +6316,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A94" s="2">
         <v>2286015</v>
       </c>
@@ -6360,7 +6360,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A95" s="2">
         <v>2338044</v>
       </c>
@@ -6404,7 +6404,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A96" s="2">
         <v>2342014</v>
       </c>
@@ -6451,7 +6451,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="97" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A97" s="2">
         <v>5</v>
       </c>
@@ -6499,7 +6499,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="98" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A98" s="2">
         <v>2343027</v>
       </c>
@@ -6547,7 +6547,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A99" s="2">
         <v>2343027</v>
       </c>
@@ -6594,7 +6594,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A100" s="2">
         <v>2343027</v>
       </c>
@@ -6640,7 +6640,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A101" s="2">
         <v>2347001</v>
       </c>
@@ -6690,7 +6690,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A102" s="2">
         <v>2347003</v>
       </c>
@@ -6740,7 +6740,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="103" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A103" s="2">
         <v>2347005</v>
       </c>
@@ -6791,7 +6791,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A104" s="2">
         <v>2347006</v>
       </c>
@@ -6841,7 +6841,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="105" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A105" s="2">
         <v>2347007</v>
       </c>
@@ -6892,7 +6892,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A106" s="2">
         <v>2347013</v>
       </c>
@@ -6942,7 +6942,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A107" s="2">
         <v>2347014</v>
       </c>
@@ -6989,7 +6989,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A108" s="2">
         <v>2347017</v>
       </c>
@@ -7039,7 +7039,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="109" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A109" s="2">
         <v>2347030</v>
       </c>
@@ -7090,7 +7090,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A110" s="2">
         <v>2347021</v>
       </c>
@@ -7140,7 +7140,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="111" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A111" s="2">
         <v>2347022</v>
       </c>
@@ -7192,7 +7192,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A112" s="2">
         <v>2347024</v>
       </c>
@@ -7242,7 +7242,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="113" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A113" s="2">
         <v>2347026</v>
       </c>
@@ -7293,7 +7293,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="114" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A114" s="2">
         <v>2347027</v>
       </c>
@@ -7344,7 +7344,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A115" s="2">
         <v>2347029</v>
       </c>
@@ -7394,7 +7394,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="116" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A116" s="2">
         <v>2347031</v>
       </c>
@@ -7444,7 +7444,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="117" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A117" s="2">
         <v>2347038</v>
       </c>
@@ -7495,7 +7495,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="118" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A118" s="2">
         <v>2361002</v>
       </c>
@@ -7539,7 +7539,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="119" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A119" s="2">
         <v>2361002</v>
       </c>
@@ -7583,7 +7583,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="120" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A120" s="2">
         <v>2361002</v>
       </c>
@@ -7627,7 +7627,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="121" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A121" s="2">
         <v>2361004</v>
       </c>
@@ -7674,7 +7674,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="122" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A122" s="2">
         <v>2393002</v>
       </c>
@@ -7721,7 +7721,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="123" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A123" s="2">
         <v>2393002</v>
       </c>
@@ -7768,7 +7768,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="124" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A124" s="2">
         <v>2393002</v>
       </c>
@@ -7815,7 +7815,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="125" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A125" s="2">
         <v>2394004</v>
       </c>
@@ -7862,7 +7862,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="126" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A126" s="2">
         <v>2394004</v>
       </c>
@@ -7909,7 +7909,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="127" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A127" s="2">
         <v>2394004</v>
       </c>
@@ -7956,7 +7956,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="128" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A128" s="2">
         <v>2395003</v>
       </c>
@@ -8003,7 +8003,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="129" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A129" s="2">
         <v>2395003</v>
       </c>
@@ -8050,7 +8050,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="130" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A130" s="2">
         <v>2395003</v>
       </c>
@@ -8097,7 +8097,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="131" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A131" s="2">
         <v>2396001</v>
       </c>
@@ -8144,7 +8144,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="132" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A132" s="2">
         <v>2396001</v>
       </c>
@@ -8191,7 +8191,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="133" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A133" s="2">
         <v>2396001</v>
       </c>
@@ -8238,7 +8238,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="134" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A134" s="2">
         <v>2397003</v>
       </c>
@@ -8288,7 +8288,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="135" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A135" s="2">
         <v>2397003</v>
       </c>
@@ -8338,7 +8338,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="136" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A136" s="2">
         <v>2397003</v>
       </c>
@@ -8388,7 +8388,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="137" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A137" s="2">
         <v>2397008</v>
       </c>
@@ -8435,7 +8435,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="138" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A138" s="2">
         <v>2397008</v>
       </c>
@@ -8482,7 +8482,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="139" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A139" s="2">
         <v>2397008</v>
       </c>
@@ -8529,7 +8529,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="140" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A140" s="2">
         <v>2398001</v>
       </c>
@@ -8579,7 +8579,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="141" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A141" s="2">
         <v>2398001</v>
       </c>
@@ -8630,7 +8630,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="142" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A142" s="2">
         <v>2398001</v>
       </c>
@@ -8681,7 +8681,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="143" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A143" s="2">
         <v>2398006</v>
       </c>
@@ -8728,7 +8728,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="144" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A144" s="2">
         <v>2398006</v>
       </c>
@@ -8775,7 +8775,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="145" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A145" s="2">
         <v>2398006</v>
       </c>
@@ -8822,7 +8822,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="146" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A146" s="2">
         <v>2398013</v>
       </c>
@@ -8869,7 +8869,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="147" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A147" s="2">
         <v>2398013</v>
       </c>
@@ -8916,7 +8916,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A148" s="2">
         <v>2398013</v>
       </c>
@@ -8960,7 +8960,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="149" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A149" s="2">
         <v>2399003</v>
       </c>
@@ -9007,7 +9007,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="150" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A150" s="2">
         <v>2399003</v>
       </c>
@@ -9054,7 +9054,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="151" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A151" s="2">
         <v>2399003</v>
       </c>
@@ -9101,7 +9101,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="152" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A152" s="2">
         <v>2399010</v>
       </c>
@@ -9148,7 +9148,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="153" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A153" s="2">
         <v>2399010</v>
       </c>
@@ -9195,7 +9195,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="154" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A154" s="2">
         <v>2399010</v>
       </c>
@@ -9242,7 +9242,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="155" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A155" s="2">
         <v>2399014</v>
       </c>
@@ -9289,7 +9289,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A156" s="2">
         <v>2399014</v>
       </c>
@@ -9336,7 +9336,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A157" s="2">
         <v>2399014</v>
       </c>
@@ -9380,7 +9380,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="158" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A158" s="2">
         <v>2400003</v>
       </c>
@@ -9430,7 +9430,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="159" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A159" s="2">
         <v>2400003</v>
       </c>
@@ -9480,7 +9480,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="160" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A160" s="2">
         <v>2400003</v>
       </c>
@@ -9530,7 +9530,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="161" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A161" s="2">
         <v>2400008</v>
       </c>
@@ -9577,7 +9577,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="162" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A162" s="2">
         <v>2400008</v>
       </c>
@@ -9624,7 +9624,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="163" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A163" s="2">
         <v>2400008</v>
       </c>
@@ -9671,7 +9671,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="164" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A164" s="2">
         <v>2400012</v>
       </c>
@@ -9721,7 +9721,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="165" spans="1:18" ht="32" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A165" s="2">
         <v>2400012</v>
       </c>
@@ -9771,7 +9771,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="166" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A166" s="2">
         <v>2400012</v>
       </c>
@@ -9818,7 +9818,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="167" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A167" s="2">
         <v>2401001</v>
       </c>
@@ -9865,7 +9865,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="168" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A168" s="2">
         <v>2401001</v>
       </c>
@@ -9912,7 +9912,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="169" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A169" s="2">
         <v>2401001</v>
       </c>
@@ -9959,7 +9959,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="170" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A170" s="2">
         <v>2401007</v>
       </c>
@@ -10006,7 +10006,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="171" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A171" s="2">
         <v>2401007</v>
       </c>
@@ -10053,7 +10053,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="172" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A172" s="2">
         <v>2401007</v>
       </c>
@@ -10100,7 +10100,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="173" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A173" s="2">
         <v>2401013</v>
       </c>
@@ -10150,7 +10150,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="174" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A174" s="2">
         <v>2401013</v>
       </c>
@@ -10200,7 +10200,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="175" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A175" s="2">
         <v>2401013</v>
       </c>
@@ -10250,7 +10250,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="176" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A176" s="2">
         <v>2401018</v>
       </c>
@@ -10297,7 +10297,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="177" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A177" s="2">
         <v>2401018</v>
       </c>
@@ -10344,7 +10344,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="178" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A178" s="2">
         <v>2401018</v>
       </c>
@@ -10391,7 +10391,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="179" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A179" s="2">
         <v>2401018</v>
       </c>
@@ -10438,7 +10438,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="180" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A180" s="2">
         <v>2401018</v>
       </c>
@@ -10485,7 +10485,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="181" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A181" s="2">
         <v>2401018</v>
       </c>
@@ -10532,7 +10532,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="182" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A182" s="2">
         <v>2401018</v>
       </c>
@@ -10579,7 +10579,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="183" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A183" s="2">
         <v>2402003</v>
       </c>
@@ -10630,7 +10630,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="184" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A184" s="2">
         <v>2402003</v>
       </c>
@@ -10681,7 +10681,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="185" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A185" s="2">
         <v>2402003</v>
       </c>
@@ -10732,7 +10732,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="186" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A186" s="2">
         <v>2402008</v>
       </c>
@@ -10782,7 +10782,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="187" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A187" s="2">
         <v>2402008</v>
       </c>
@@ -10832,7 +10832,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="188" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A188" s="2">
         <v>2402008</v>
       </c>
@@ -10882,7 +10882,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="189" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A189" s="2">
         <v>2402015</v>
       </c>
@@ -10929,7 +10929,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="190" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A190" s="2">
         <v>2402015</v>
       </c>
@@ -10976,7 +10976,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="191" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A191" s="2">
         <v>2402015</v>
       </c>
@@ -11022,7 +11022,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="192" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A192" s="2">
         <v>2403004</v>
       </c>
@@ -11073,7 +11073,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="193" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A193" s="2">
         <v>2403004</v>
       </c>
@@ -11124,7 +11124,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="194" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A194" s="2">
         <v>2403004</v>
       </c>
@@ -11175,7 +11175,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="195" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A195" s="2">
         <v>2403009</v>
       </c>
@@ -11222,7 +11222,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="196" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A196" s="2">
         <v>2403009</v>
       </c>
@@ -11269,7 +11269,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="197" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A197" s="2">
         <v>2403009</v>
       </c>
@@ -11316,7 +11316,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="198" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A198" s="2">
         <v>2403013</v>
       </c>
@@ -11360,7 +11360,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="199" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A199" s="2">
         <v>2403013</v>
       </c>
@@ -11404,7 +11404,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="200" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A200" s="2">
         <v>2403013</v>
       </c>
@@ -11448,7 +11448,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="201" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A201" s="2">
         <v>2404001</v>
       </c>
@@ -11498,7 +11498,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="202" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A202" s="2">
         <v>2404001</v>
       </c>
@@ -11548,7 +11548,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="203" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A203" s="2">
         <v>2404001</v>
       </c>
@@ -11598,7 +11598,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="204" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A204" s="2">
         <v>2404006</v>
       </c>
@@ -11648,7 +11648,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="205" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A205" s="2">
         <v>2404006</v>
       </c>
@@ -11698,7 +11698,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="206" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A206" s="2">
         <v>2404006</v>
       </c>
@@ -11748,7 +11748,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="207" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A207" s="2">
         <v>2404015</v>
       </c>
@@ -11795,7 +11795,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="208" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A208" s="2">
         <v>2404015</v>
       </c>
@@ -11842,7 +11842,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="209" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A209" s="2">
         <v>2404015</v>
       </c>
@@ -11889,7 +11889,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="210" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A210" s="2">
         <v>2405001</v>
       </c>
@@ -11939,7 +11939,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="211" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A211" s="2">
         <v>2405001</v>
       </c>
@@ -11989,7 +11989,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="212" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A212" s="2">
         <v>2405001</v>
       </c>
@@ -12039,7 +12039,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="213" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A213" s="2">
         <v>2405006</v>
       </c>
@@ -12089,7 +12089,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="214" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A214" s="2">
         <v>2405006</v>
       </c>
@@ -12139,7 +12139,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="215" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A215" s="2">
         <v>2405006</v>
       </c>
@@ -12189,7 +12189,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="216" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A216" s="2">
         <v>2405015</v>
       </c>
@@ -12239,7 +12239,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="217" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A217" s="2">
         <v>2405015</v>
       </c>
@@ -12289,7 +12289,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="218" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A218" s="2">
         <v>2405015</v>
       </c>
@@ -12336,7 +12336,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="219" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A219" s="2">
         <v>2406004</v>
       </c>
@@ -12367,7 +12367,7 @@
       <c r="J219" t="s">
         <v>24</v>
       </c>
-      <c r="K219" s="6" t="s">
+      <c r="K219" t="s">
         <v>446</v>
       </c>
       <c r="L219" t="s">
@@ -12386,7 +12386,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="220" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A220" s="2">
         <v>2406004</v>
       </c>
@@ -12436,7 +12436,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="221" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A221" s="2">
         <v>2406004</v>
       </c>
@@ -12467,7 +12467,7 @@
       <c r="J221" t="s">
         <v>24</v>
       </c>
-      <c r="K221" s="6" t="s">
+      <c r="K221" t="s">
         <v>511</v>
       </c>
       <c r="L221" t="s">
@@ -12486,7 +12486,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="222" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A222" s="2">
         <v>2406004</v>
       </c>
@@ -12536,7 +12536,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="223" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A223" s="2">
         <v>2406004</v>
       </c>
@@ -12567,7 +12567,7 @@
       <c r="J223" t="s">
         <v>24</v>
       </c>
-      <c r="K223" s="6" t="s">
+      <c r="K223" t="s">
         <v>512</v>
       </c>
       <c r="L223" t="s">
@@ -12586,7 +12586,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="224" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A224" s="2">
         <v>2406009</v>
       </c>
@@ -12633,7 +12633,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="225" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A225" s="2">
         <v>2406009</v>
       </c>
@@ -12680,7 +12680,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="226" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A226" s="2">
         <v>2406009</v>
       </c>
@@ -12727,7 +12727,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="227" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A227" s="2">
         <v>2406009</v>
       </c>
@@ -12774,7 +12774,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="228" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A228" s="2">
         <v>2406009</v>
       </c>
@@ -12821,7 +12821,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="229" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A229" s="2">
         <v>2406012</v>
       </c>
@@ -12868,7 +12868,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="230" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A230" s="2">
         <v>2406012</v>
       </c>
@@ -12915,7 +12915,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="231" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A231" s="2">
         <v>2406012</v>
       </c>
@@ -12962,7 +12962,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="232" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A232" s="2">
         <v>2059001</v>
       </c>
@@ -13009,7 +13009,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="233" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A233" s="2">
         <v>2059002</v>
       </c>
@@ -13056,7 +13056,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="234" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A234" s="2">
         <v>2059006</v>
       </c>
@@ -13103,7 +13103,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="235" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A235" s="2">
         <v>2140011</v>
       </c>
@@ -13150,7 +13150,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="236" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A236" s="2">
         <v>2390004</v>
       </c>
@@ -13197,7 +13197,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="237" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A237" s="2">
         <v>2390004</v>
       </c>
@@ -13244,7 +13244,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="238" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A238" s="2">
         <v>2390004</v>
       </c>
@@ -13291,7 +13291,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="239" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A239" s="2">
         <v>2390009</v>
       </c>
@@ -13338,7 +13338,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="240" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A240" s="2">
         <v>2390009</v>
       </c>
@@ -13385,7 +13385,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="241" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A241" s="2">
         <v>2390009</v>
       </c>
@@ -13432,7 +13432,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="242" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A242" s="2">
         <v>2390013</v>
       </c>
@@ -13476,7 +13476,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="243" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A243" s="2">
         <v>2390013</v>
       </c>
@@ -13520,7 +13520,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="244" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A244" s="2">
         <v>2390013</v>
       </c>
@@ -13564,7 +13564,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="252" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="L252" s="1"/>
     </row>
   </sheetData>

--- a/POD_2026-27_11-5-2026.xlsx
+++ b/POD_2026-27_11-5-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\misael.marriaga\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{645D15A8-518B-4DEF-9D73-600E718810F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CCDDB71-85DC-4A1D-A0FB-BB17922331C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2959" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2959" uniqueCount="512">
   <si>
     <t>POD_2026-27_11-5-2026</t>
   </si>
@@ -1566,9 +1566,6 @@
   </si>
   <si>
     <t>ELENA CASTILLA (4)</t>
-  </si>
-  <si>
-    <t>ELENA CASTILLA (8)</t>
   </si>
   <si>
     <t>V=&gt;(17:00-18:00)[11/09/26, 18/09/26]</t>
@@ -12468,7 +12465,7 @@
         <v>24</v>
       </c>
       <c r="K221" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="L221" t="s">
         <v>447</v>
@@ -12477,7 +12474,7 @@
         <v>26</v>
       </c>
       <c r="N221" s="6" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="Q221" t="s">
         <v>27</v>
@@ -12568,7 +12565,7 @@
         <v>24</v>
       </c>
       <c r="K223" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="L223" t="s">
         <v>447</v>
@@ -12577,7 +12574,7 @@
         <v>26</v>
       </c>
       <c r="N223" s="6" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="Q223" t="s">
         <v>27</v>

--- a/POD_2026-27_11-5-2026.xlsx
+++ b/POD_2026-27_11-5-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\misael.marriaga\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CCDDB71-85DC-4A1D-A0FB-BB17922331C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73D0278A-89E8-48BE-AA38-DC91383860C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1568,10 +1568,10 @@
     <t>ELENA CASTILLA (4)</t>
   </si>
   <si>
-    <t>V=&gt;(17:00-18:00)[11/09/26, 18/09/26]</t>
-  </si>
-  <si>
-    <t>V=&gt;(17:00-18:00)[25/09/26, 02/10/26]</t>
+    <t>X=&gt;(21:00-22:00)[16/09/26, 23/09/26, 07/10/26, 14/10/26, 28/10/26, 04/11/26, 11/11/26, 18/11/26]</t>
+  </si>
+  <si>
+    <t>J=&gt;(21:00-22:00)[10/09/26, 17/09/26, 24/09/26, 01/10/26, 08/10/26, 15/10/26, 22/10/26, 29/10/26]</t>
   </si>
 </sst>
 </file>

--- a/POD_2026-27_11-5-2026.xlsx
+++ b/POD_2026-27_11-5-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\misael.marriaga\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73D0278A-89E8-48BE-AA38-DC91383860C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E54E290D-C997-4D3E-8734-FB5F36DBCDEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2959" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2959" uniqueCount="513">
   <si>
     <t>POD_2026-27_11-5-2026</t>
   </si>
@@ -1572,6 +1572,9 @@
   </si>
   <si>
     <t>J=&gt;(21:00-22:00)[10/09/26, 17/09/26, 24/09/26, 01/10/26, 08/10/26, 15/10/26, 22/10/26, 29/10/26]</t>
+  </si>
+  <si>
+    <t>PILAR RUIZ (8)</t>
   </si>
 </sst>
 </file>
@@ -11830,7 +11833,7 @@
         <v>26</v>
       </c>
       <c r="N208" t="s">
-        <v>368</v>
+        <v>512</v>
       </c>
       <c r="Q208" t="s">
         <v>27</v>
@@ -11877,7 +11880,7 @@
         <v>26</v>
       </c>
       <c r="N209" t="s">
-        <v>368</v>
+        <v>512</v>
       </c>
       <c r="Q209" t="s">
         <v>27</v>

--- a/POD_2026-27_11-5-2026.xlsx
+++ b/POD_2026-27_11-5-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\misael.marriaga\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E54E290D-C997-4D3E-8734-FB5F36DBCDEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D94E1803-C4B9-4196-818D-35E6C05F3FF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2959" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2968" uniqueCount="515">
   <si>
     <t>POD_2026-27_11-5-2026</t>
   </si>
@@ -1575,6 +1575,12 @@
   </si>
   <si>
     <t>PILAR RUIZ (8)</t>
+  </si>
+  <si>
+    <t>DAVID ALEJA (44)</t>
+  </si>
+  <si>
+    <t>DAVID ALEJA (16)</t>
   </si>
 </sst>
 </file>
@@ -2322,6 +2328,9 @@
       <c r="M8" t="s">
         <v>26</v>
       </c>
+      <c r="N8" t="s">
+        <v>513</v>
+      </c>
       <c r="Q8" t="s">
         <v>27</v>
       </c>
@@ -2366,6 +2375,9 @@
       <c r="M9" t="s">
         <v>26</v>
       </c>
+      <c r="N9" t="s">
+        <v>514</v>
+      </c>
       <c r="Q9" t="s">
         <v>27</v>
       </c>
@@ -2410,6 +2422,9 @@
       <c r="M10" t="s">
         <v>26</v>
       </c>
+      <c r="N10" t="s">
+        <v>514</v>
+      </c>
       <c r="Q10" t="s">
         <v>27</v>
       </c>
@@ -3682,6 +3697,9 @@
       <c r="M37" t="s">
         <v>26</v>
       </c>
+      <c r="N37" t="s">
+        <v>513</v>
+      </c>
       <c r="Q37" t="s">
         <v>27</v>
       </c>
@@ -3726,6 +3744,9 @@
       <c r="M38" t="s">
         <v>26</v>
       </c>
+      <c r="N38" t="s">
+        <v>514</v>
+      </c>
       <c r="Q38" t="s">
         <v>27</v>
       </c>
@@ -3770,6 +3791,9 @@
       <c r="M39" t="s">
         <v>26</v>
       </c>
+      <c r="N39" t="s">
+        <v>514</v>
+      </c>
       <c r="Q39" t="s">
         <v>27</v>
       </c>
@@ -3817,6 +3841,9 @@
       <c r="M40" t="s">
         <v>26</v>
       </c>
+      <c r="N40" t="s">
+        <v>513</v>
+      </c>
       <c r="Q40" t="s">
         <v>27</v>
       </c>
@@ -3864,6 +3891,9 @@
       <c r="M41" t="s">
         <v>26</v>
       </c>
+      <c r="N41" t="s">
+        <v>514</v>
+      </c>
       <c r="Q41" t="s">
         <v>27</v>
       </c>
@@ -3910,6 +3940,9 @@
       </c>
       <c r="M42" t="s">
         <v>26</v>
+      </c>
+      <c r="N42" t="s">
+        <v>514</v>
       </c>
       <c r="Q42" t="s">
         <v>27</v>

--- a/POD_2026-27_11-5-2026.xlsx
+++ b/POD_2026-27_11-5-2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10811"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\misael.marriaga\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guillermo.vera/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D94E1803-C4B9-4196-818D-35E6C05F3FF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4AC1A18-C88D-7641-8EEE-7E1D0486837C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="POD" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2968" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2982" uniqueCount="525">
   <si>
     <t>POD_2026-27_11-5-2026</t>
   </si>
@@ -1581,6 +1581,36 @@
   </si>
   <si>
     <t>DAVID ALEJA (16)</t>
+  </si>
+  <si>
+    <t>KARIN ALFARO (60)</t>
+  </si>
+  <si>
+    <t>KARIN ALFARO (35)</t>
+  </si>
+  <si>
+    <t>KARIN ALFARO (30)</t>
+  </si>
+  <si>
+    <t>KARIN ALFARO (48)</t>
+  </si>
+  <si>
+    <t>KARIN ALFARO (12)</t>
+  </si>
+  <si>
+    <t>EVA PRIMO (35)</t>
+  </si>
+  <si>
+    <t>EVA PRIMO (55)</t>
+  </si>
+  <si>
+    <t>EVA PRIMO (20)</t>
+  </si>
+  <si>
+    <t>EVA PRIMO (48)</t>
+  </si>
+  <si>
+    <t>EVA PRIMO (12)</t>
   </si>
 </sst>
 </file>
@@ -1629,7 +1659,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1645,6 +1675,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1663,9 +1696,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1703,7 +1736,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1809,7 +1842,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1951,7 +1984,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1960,30 +1993,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S252"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="71.36328125" customWidth="1"/>
+    <col min="2" max="2" width="71.33203125" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="9.1796875" customWidth="1"/>
-    <col min="5" max="5" width="20.1796875" customWidth="1"/>
-    <col min="6" max="6" width="64.1796875" customWidth="1"/>
-    <col min="7" max="7" width="20.81640625" customWidth="1"/>
-    <col min="8" max="8" width="6.453125" customWidth="1"/>
-    <col min="9" max="9" width="7.81640625" customWidth="1"/>
-    <col min="10" max="10" width="6.453125" customWidth="1"/>
-    <col min="11" max="11" width="107.1796875" customWidth="1"/>
-    <col min="12" max="12" width="53.6328125" customWidth="1"/>
-    <col min="13" max="13" width="12.6328125" customWidth="1"/>
-    <col min="14" max="14" width="36.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="36.453125" customWidth="1"/>
-    <col min="16" max="16" width="20.81640625" customWidth="1"/>
+    <col min="4" max="4" width="9.1640625" customWidth="1"/>
+    <col min="5" max="5" width="20.1640625" customWidth="1"/>
+    <col min="6" max="6" width="64.1640625" customWidth="1"/>
+    <col min="7" max="7" width="20.83203125" customWidth="1"/>
+    <col min="8" max="8" width="6.5" customWidth="1"/>
+    <col min="9" max="9" width="7.83203125" customWidth="1"/>
+    <col min="10" max="10" width="6.5" customWidth="1"/>
+    <col min="11" max="11" width="107.1640625" customWidth="1"/>
+    <col min="12" max="12" width="53.6640625" customWidth="1"/>
+    <col min="13" max="13" width="12.6640625" customWidth="1"/>
+    <col min="14" max="14" width="36.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="36.5" customWidth="1"/>
+    <col min="16" max="16" width="20.83203125" customWidth="1"/>
     <col min="17" max="17" width="52" customWidth="1"/>
-    <col min="18" max="18" width="32.453125" customWidth="1"/>
-    <col min="19" max="19" width="16.81640625" customWidth="1"/>
+    <col min="18" max="18" width="32.5" customWidth="1"/>
+    <col min="19" max="19" width="16.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -2006,7 +2039,7 @@
       <c r="R1" s="8"/>
       <c r="S1" s="8"/>
     </row>
-    <row r="2" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2065,7 +2098,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>2291005</v>
       </c>
@@ -2109,7 +2142,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>2291009</v>
       </c>
@@ -2153,7 +2186,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>2240005</v>
       </c>
@@ -2200,7 +2233,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>2240009</v>
       </c>
@@ -2247,7 +2280,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>2251011</v>
       </c>
@@ -2291,7 +2324,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>2327002</v>
       </c>
@@ -2338,7 +2371,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>2327002</v>
       </c>
@@ -2385,7 +2418,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>2327002</v>
       </c>
@@ -2432,7 +2465,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>2327007</v>
       </c>
@@ -2482,7 +2515,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>2327007</v>
       </c>
@@ -2532,7 +2565,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>2327007</v>
       </c>
@@ -2582,7 +2615,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>2327015</v>
       </c>
@@ -2626,7 +2659,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>2327015</v>
       </c>
@@ -2670,7 +2703,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>2327015</v>
       </c>
@@ -2714,7 +2747,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>2360001</v>
       </c>
@@ -2758,7 +2791,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>2360002</v>
       </c>
@@ -2802,7 +2835,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>2382005</v>
       </c>
@@ -2849,7 +2882,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>2382005</v>
       </c>
@@ -2896,7 +2929,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>2382005</v>
       </c>
@@ -2943,7 +2976,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>2382005</v>
       </c>
@@ -2990,7 +3023,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>2382005</v>
       </c>
@@ -3037,7 +3070,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>2382005</v>
       </c>
@@ -3084,7 +3117,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>2382010</v>
       </c>
@@ -3131,7 +3164,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>2382010</v>
       </c>
@@ -3178,7 +3211,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>2382010</v>
       </c>
@@ -3225,7 +3258,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>2382010</v>
       </c>
@@ -3272,7 +3305,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>2382010</v>
       </c>
@@ -3316,7 +3349,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>2382010</v>
       </c>
@@ -3363,7 +3396,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>2383001</v>
       </c>
@@ -3413,7 +3446,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>2383001</v>
       </c>
@@ -3460,7 +3493,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>2383001</v>
       </c>
@@ -3507,7 +3540,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>2383001</v>
       </c>
@@ -3557,7 +3590,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>2383001</v>
       </c>
@@ -3607,7 +3640,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>2383001</v>
       </c>
@@ -3657,7 +3690,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>2383002</v>
       </c>
@@ -3707,7 +3740,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>2383002</v>
       </c>
@@ -3754,7 +3787,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>2383002</v>
       </c>
@@ -3801,7 +3834,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>2383002</v>
       </c>
@@ -3851,7 +3884,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>2383002</v>
       </c>
@@ -3901,7 +3934,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>2383002</v>
       </c>
@@ -3951,7 +3984,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:18" ht="48" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>2383007</v>
       </c>
@@ -4001,7 +4034,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:18" ht="48" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>2383007</v>
       </c>
@@ -4051,7 +4084,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>2384001</v>
       </c>
@@ -4101,7 +4134,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>2384001</v>
       </c>
@@ -4151,7 +4184,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>2384001</v>
       </c>
@@ -4201,7 +4234,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
         <v>2384005</v>
       </c>
@@ -4248,7 +4281,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
         <v>2384005</v>
       </c>
@@ -4295,7 +4328,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
         <v>2384005</v>
       </c>
@@ -4342,7 +4375,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="51" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
         <v>2385001</v>
       </c>
@@ -4392,7 +4425,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="52" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
         <v>2385001</v>
       </c>
@@ -4442,7 +4475,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="53" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
         <v>2385001</v>
       </c>
@@ -4492,7 +4525,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
         <v>2385005</v>
       </c>
@@ -4539,7 +4572,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
         <v>2385005</v>
       </c>
@@ -4586,7 +4619,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="56" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
         <v>2385005</v>
       </c>
@@ -4633,7 +4666,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="57" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
         <v>2386001</v>
       </c>
@@ -4680,7 +4713,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="58" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
         <v>2386001</v>
       </c>
@@ -4724,7 +4757,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="59" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
         <v>2386001</v>
       </c>
@@ -4768,7 +4801,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="60" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
         <v>2386001</v>
       </c>
@@ -4815,7 +4848,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="61" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
         <v>2386001</v>
       </c>
@@ -4859,7 +4892,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="62" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
         <v>2386001</v>
       </c>
@@ -4904,7 +4937,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="63" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
         <v>2386002</v>
       </c>
@@ -4951,7 +4984,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="64" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
         <v>2386002</v>
       </c>
@@ -5001,7 +5034,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="65" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
         <v>2387009</v>
       </c>
@@ -5048,7 +5081,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="66" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
         <v>2387009</v>
       </c>
@@ -5092,7 +5125,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="67" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
         <v>2387009</v>
       </c>
@@ -5136,7 +5169,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="68" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
         <v>2387016</v>
       </c>
@@ -5180,7 +5213,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="69" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
         <v>2387016</v>
       </c>
@@ -5221,7 +5254,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="70" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
         <v>2387016</v>
       </c>
@@ -5262,7 +5295,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="71" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
         <v>2265020</v>
       </c>
@@ -5310,7 +5343,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="72" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
         <v>2029018</v>
       </c>
@@ -5357,7 +5390,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="73" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
         <v>2030013</v>
       </c>
@@ -5404,7 +5437,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="74" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
         <v>2031001</v>
       </c>
@@ -5448,7 +5481,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="75" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
         <v>2032001</v>
       </c>
@@ -5498,7 +5531,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="76" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
         <v>2032007</v>
       </c>
@@ -5548,7 +5581,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="77" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
         <v>2032009</v>
       </c>
@@ -5585,6 +5618,9 @@
       <c r="M77" t="s">
         <v>26</v>
       </c>
+      <c r="N77" s="6" t="s">
+        <v>515</v>
+      </c>
       <c r="Q77" t="s">
         <v>27</v>
       </c>
@@ -5592,7 +5628,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="78" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
         <v>2033001</v>
       </c>
@@ -5639,7 +5675,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="79" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
         <v>2033002</v>
       </c>
@@ -5682,7 +5718,9 @@
       <c r="N79" s="5" t="s">
         <v>494</v>
       </c>
-      <c r="O79" s="3"/>
+      <c r="O79" s="5" t="s">
+        <v>516</v>
+      </c>
       <c r="Q79" t="s">
         <v>27</v>
       </c>
@@ -5690,7 +5728,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="80" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
         <v>2033006</v>
       </c>
@@ -5740,7 +5778,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="81" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
         <v>2034001</v>
       </c>
@@ -5787,7 +5825,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="82" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
         <v>2034002</v>
       </c>
@@ -5840,7 +5878,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="83" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
         <v>2034006</v>
       </c>
@@ -5887,7 +5925,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="84" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
         <v>2061001</v>
       </c>
@@ -5931,7 +5969,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="85" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
         <v>2061002</v>
       </c>
@@ -5978,7 +6016,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="86" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
         <v>2061006</v>
       </c>
@@ -6022,7 +6060,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="87" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
         <v>2107013</v>
       </c>
@@ -6069,7 +6107,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="88" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
         <v>2143016</v>
       </c>
@@ -6116,7 +6154,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="89" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
         <v>2148011</v>
       </c>
@@ -6160,7 +6198,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="90" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
         <v>2175020</v>
       </c>
@@ -6207,7 +6245,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="91" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
         <v>2285005</v>
       </c>
@@ -6247,7 +6285,9 @@
       <c r="N91" s="5" t="s">
         <v>495</v>
       </c>
-      <c r="O91" s="3"/>
+      <c r="O91" s="5" t="s">
+        <v>520</v>
+      </c>
       <c r="Q91" t="s">
         <v>27</v>
       </c>
@@ -6255,7 +6295,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="92" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
         <v>2285006</v>
       </c>
@@ -6302,7 +6342,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="93" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
         <v>2285007</v>
       </c>
@@ -6349,7 +6389,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="94" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
         <v>2286015</v>
       </c>
@@ -6393,7 +6433,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="95" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
         <v>2338044</v>
       </c>
@@ -6437,7 +6477,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="96" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
         <v>2342014</v>
       </c>
@@ -6484,7 +6524,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="97" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
         <v>5</v>
       </c>
@@ -6532,7 +6572,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="98" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
         <v>2343027</v>
       </c>
@@ -6580,7 +6620,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="99" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
         <v>2343027</v>
       </c>
@@ -6627,7 +6667,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="100" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
         <v>2343027</v>
       </c>
@@ -6673,7 +6713,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="101" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
         <v>2347001</v>
       </c>
@@ -6723,7 +6763,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="102" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
         <v>2347003</v>
       </c>
@@ -6773,7 +6813,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="103" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
         <v>2347005</v>
       </c>
@@ -6824,7 +6864,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="104" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A104" s="2">
         <v>2347006</v>
       </c>
@@ -6874,7 +6914,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="105" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A105" s="2">
         <v>2347007</v>
       </c>
@@ -6925,7 +6965,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="106" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A106" s="2">
         <v>2347013</v>
       </c>
@@ -6975,7 +7015,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="107" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A107" s="2">
         <v>2347014</v>
       </c>
@@ -7022,7 +7062,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="108" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A108" s="2">
         <v>2347017</v>
       </c>
@@ -7072,7 +7112,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="109" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A109" s="2">
         <v>2347030</v>
       </c>
@@ -7123,7 +7163,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="110" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A110" s="2">
         <v>2347021</v>
       </c>
@@ -7173,7 +7213,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="111" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A111" s="2">
         <v>2347022</v>
       </c>
@@ -7225,7 +7265,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="112" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A112" s="2">
         <v>2347024</v>
       </c>
@@ -7275,7 +7315,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="113" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A113" s="2">
         <v>2347026</v>
       </c>
@@ -7326,7 +7366,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="114" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A114" s="2">
         <v>2347027</v>
       </c>
@@ -7377,7 +7417,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="115" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A115" s="2">
         <v>2347029</v>
       </c>
@@ -7427,7 +7467,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="116" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A116" s="2">
         <v>2347031</v>
       </c>
@@ -7477,7 +7517,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="117" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A117" s="2">
         <v>2347038</v>
       </c>
@@ -7528,7 +7568,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="118" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A118" s="2">
         <v>2361002</v>
       </c>
@@ -7565,6 +7605,9 @@
       <c r="M118" t="s">
         <v>26</v>
       </c>
+      <c r="N118" s="9" t="s">
+        <v>517</v>
+      </c>
       <c r="Q118" t="s">
         <v>27</v>
       </c>
@@ -7572,7 +7615,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="119" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A119" s="2">
         <v>2361002</v>
       </c>
@@ -7609,6 +7652,9 @@
       <c r="M119" t="s">
         <v>26</v>
       </c>
+      <c r="N119" s="9" t="s">
+        <v>517</v>
+      </c>
       <c r="Q119" t="s">
         <v>27</v>
       </c>
@@ -7616,7 +7662,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="120" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A120" s="2">
         <v>2361002</v>
       </c>
@@ -7660,7 +7706,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="121" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A121" s="2">
         <v>2361004</v>
       </c>
@@ -7707,7 +7753,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="122" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A122" s="2">
         <v>2393002</v>
       </c>
@@ -7754,7 +7800,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="123" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A123" s="2">
         <v>2393002</v>
       </c>
@@ -7801,7 +7847,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="124" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A124" s="2">
         <v>2393002</v>
       </c>
@@ -7848,7 +7894,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="125" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A125" s="2">
         <v>2394004</v>
       </c>
@@ -7895,7 +7941,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="126" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A126" s="2">
         <v>2394004</v>
       </c>
@@ -7942,7 +7988,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="127" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A127" s="2">
         <v>2394004</v>
       </c>
@@ -7989,7 +8035,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="128" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A128" s="2">
         <v>2395003</v>
       </c>
@@ -8036,7 +8082,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="129" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A129" s="2">
         <v>2395003</v>
       </c>
@@ -8083,7 +8129,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="130" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A130" s="2">
         <v>2395003</v>
       </c>
@@ -8130,7 +8176,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="131" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A131" s="2">
         <v>2396001</v>
       </c>
@@ -8170,6 +8216,9 @@
       <c r="M131" t="s">
         <v>26</v>
       </c>
+      <c r="N131" s="6" t="s">
+        <v>521</v>
+      </c>
       <c r="Q131" t="s">
         <v>27</v>
       </c>
@@ -8177,7 +8226,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="132" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A132" s="2">
         <v>2396001</v>
       </c>
@@ -8217,6 +8266,9 @@
       <c r="M132" t="s">
         <v>26</v>
       </c>
+      <c r="N132" s="6" t="s">
+        <v>522</v>
+      </c>
       <c r="Q132" t="s">
         <v>27</v>
       </c>
@@ -8224,7 +8276,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="133" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A133" s="2">
         <v>2396001</v>
       </c>
@@ -8264,6 +8316,9 @@
       <c r="M133" t="s">
         <v>26</v>
       </c>
+      <c r="N133" s="6" t="s">
+        <v>522</v>
+      </c>
       <c r="Q133" t="s">
         <v>27</v>
       </c>
@@ -8271,7 +8326,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="134" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A134" s="2">
         <v>2397003</v>
       </c>
@@ -8321,7 +8376,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="135" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A135" s="2">
         <v>2397003</v>
       </c>
@@ -8371,7 +8426,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="136" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A136" s="2">
         <v>2397003</v>
       </c>
@@ -8421,7 +8476,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="137" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A137" s="2">
         <v>2397008</v>
       </c>
@@ -8468,7 +8523,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="138" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A138" s="2">
         <v>2397008</v>
       </c>
@@ -8515,7 +8570,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="139" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A139" s="2">
         <v>2397008</v>
       </c>
@@ -8562,7 +8617,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="140" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A140" s="2">
         <v>2398001</v>
       </c>
@@ -8612,7 +8667,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="141" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A141" s="2">
         <v>2398001</v>
       </c>
@@ -8663,7 +8718,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="142" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A142" s="2">
         <v>2398001</v>
       </c>
@@ -8714,7 +8769,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="143" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A143" s="2">
         <v>2398006</v>
       </c>
@@ -8761,7 +8816,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="144" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A144" s="2">
         <v>2398006</v>
       </c>
@@ -8808,7 +8863,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="145" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A145" s="2">
         <v>2398006</v>
       </c>
@@ -8855,7 +8910,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="146" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A146" s="2">
         <v>2398013</v>
       </c>
@@ -8902,7 +8957,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="147" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A147" s="2">
         <v>2398013</v>
       </c>
@@ -8949,7 +9004,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="148" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A148" s="2">
         <v>2398013</v>
       </c>
@@ -8993,7 +9048,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="149" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A149" s="2">
         <v>2399003</v>
       </c>
@@ -9040,7 +9095,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="150" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A150" s="2">
         <v>2399003</v>
       </c>
@@ -9087,7 +9142,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="151" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A151" s="2">
         <v>2399003</v>
       </c>
@@ -9134,7 +9189,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="152" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A152" s="2">
         <v>2399010</v>
       </c>
@@ -9181,7 +9236,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="153" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A153" s="2">
         <v>2399010</v>
       </c>
@@ -9228,7 +9283,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="154" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A154" s="2">
         <v>2399010</v>
       </c>
@@ -9275,7 +9330,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="155" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A155" s="2">
         <v>2399014</v>
       </c>
@@ -9322,7 +9377,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="156" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A156" s="2">
         <v>2399014</v>
       </c>
@@ -9369,7 +9424,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="157" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A157" s="2">
         <v>2399014</v>
       </c>
@@ -9413,7 +9468,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="158" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A158" s="2">
         <v>2400003</v>
       </c>
@@ -9463,7 +9518,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="159" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A159" s="2">
         <v>2400003</v>
       </c>
@@ -9513,7 +9568,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="160" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A160" s="2">
         <v>2400003</v>
       </c>
@@ -9563,7 +9618,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="161" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A161" s="2">
         <v>2400008</v>
       </c>
@@ -9603,6 +9658,9 @@
       <c r="M161" t="s">
         <v>26</v>
       </c>
+      <c r="N161" s="6" t="s">
+        <v>518</v>
+      </c>
       <c r="Q161" t="s">
         <v>27</v>
       </c>
@@ -9610,7 +9668,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="162" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A162" s="2">
         <v>2400008</v>
       </c>
@@ -9650,6 +9708,9 @@
       <c r="M162" t="s">
         <v>26</v>
       </c>
+      <c r="N162" s="6" t="s">
+        <v>519</v>
+      </c>
       <c r="Q162" t="s">
         <v>27</v>
       </c>
@@ -9657,7 +9718,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="163" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A163" s="2">
         <v>2400008</v>
       </c>
@@ -9697,6 +9758,9 @@
       <c r="M163" t="s">
         <v>26</v>
       </c>
+      <c r="N163" s="6" t="s">
+        <v>519</v>
+      </c>
       <c r="Q163" t="s">
         <v>27</v>
       </c>
@@ -9704,7 +9768,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="164" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A164" s="2">
         <v>2400012</v>
       </c>
@@ -9754,7 +9818,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="165" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:18" ht="32" x14ac:dyDescent="0.2">
       <c r="A165" s="2">
         <v>2400012</v>
       </c>
@@ -9804,7 +9868,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="166" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A166" s="2">
         <v>2400012</v>
       </c>
@@ -9851,7 +9915,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="167" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A167" s="2">
         <v>2401001</v>
       </c>
@@ -9891,6 +9955,9 @@
       <c r="M167" t="s">
         <v>26</v>
       </c>
+      <c r="N167" s="6" t="s">
+        <v>523</v>
+      </c>
       <c r="Q167" t="s">
         <v>27</v>
       </c>
@@ -9898,7 +9965,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="168" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A168" s="2">
         <v>2401001</v>
       </c>
@@ -9938,6 +10005,9 @@
       <c r="M168" t="s">
         <v>26</v>
       </c>
+      <c r="N168" s="6" t="s">
+        <v>524</v>
+      </c>
       <c r="Q168" t="s">
         <v>27</v>
       </c>
@@ -9945,7 +10015,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="169" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A169" s="2">
         <v>2401001</v>
       </c>
@@ -9985,6 +10055,9 @@
       <c r="M169" t="s">
         <v>26</v>
       </c>
+      <c r="N169" s="6" t="s">
+        <v>524</v>
+      </c>
       <c r="Q169" t="s">
         <v>27</v>
       </c>
@@ -9992,7 +10065,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="170" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A170" s="2">
         <v>2401007</v>
       </c>
@@ -10039,7 +10112,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="171" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A171" s="2">
         <v>2401007</v>
       </c>
@@ -10086,7 +10159,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="172" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A172" s="2">
         <v>2401007</v>
       </c>
@@ -10133,7 +10206,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="173" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A173" s="2">
         <v>2401013</v>
       </c>
@@ -10183,7 +10256,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="174" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A174" s="2">
         <v>2401013</v>
       </c>
@@ -10233,7 +10306,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="175" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A175" s="2">
         <v>2401013</v>
       </c>
@@ -10283,7 +10356,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="176" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A176" s="2">
         <v>2401018</v>
       </c>
@@ -10330,7 +10403,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="177" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A177" s="2">
         <v>2401018</v>
       </c>
@@ -10377,7 +10450,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="178" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A178" s="2">
         <v>2401018</v>
       </c>
@@ -10424,7 +10497,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="179" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A179" s="2">
         <v>2401018</v>
       </c>
@@ -10471,7 +10544,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="180" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A180" s="2">
         <v>2401018</v>
       </c>
@@ -10518,7 +10591,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="181" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A181" s="2">
         <v>2401018</v>
       </c>
@@ -10565,7 +10638,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="182" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A182" s="2">
         <v>2401018</v>
       </c>
@@ -10612,7 +10685,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="183" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A183" s="2">
         <v>2402003</v>
       </c>
@@ -10663,7 +10736,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="184" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A184" s="2">
         <v>2402003</v>
       </c>
@@ -10714,7 +10787,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="185" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A185" s="2">
         <v>2402003</v>
       </c>
@@ -10765,7 +10838,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="186" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A186" s="2">
         <v>2402008</v>
       </c>
@@ -10815,7 +10888,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="187" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A187" s="2">
         <v>2402008</v>
       </c>
@@ -10865,7 +10938,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="188" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A188" s="2">
         <v>2402008</v>
       </c>
@@ -10915,7 +10988,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="189" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A189" s="2">
         <v>2402015</v>
       </c>
@@ -10962,7 +11035,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="190" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A190" s="2">
         <v>2402015</v>
       </c>
@@ -11009,7 +11082,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="191" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A191" s="2">
         <v>2402015</v>
       </c>
@@ -11055,7 +11128,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="192" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A192" s="2">
         <v>2403004</v>
       </c>
@@ -11106,7 +11179,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="193" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A193" s="2">
         <v>2403004</v>
       </c>
@@ -11157,7 +11230,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="194" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A194" s="2">
         <v>2403004</v>
       </c>
@@ -11208,7 +11281,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="195" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A195" s="2">
         <v>2403009</v>
       </c>
@@ -11255,7 +11328,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="196" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A196" s="2">
         <v>2403009</v>
       </c>
@@ -11302,7 +11375,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="197" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A197" s="2">
         <v>2403009</v>
       </c>
@@ -11349,7 +11422,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="198" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A198" s="2">
         <v>2403013</v>
       </c>
@@ -11393,7 +11466,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="199" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A199" s="2">
         <v>2403013</v>
       </c>
@@ -11437,7 +11510,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="200" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A200" s="2">
         <v>2403013</v>
       </c>
@@ -11481,7 +11554,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="201" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A201" s="2">
         <v>2404001</v>
       </c>
@@ -11531,7 +11604,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="202" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A202" s="2">
         <v>2404001</v>
       </c>
@@ -11581,7 +11654,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="203" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A203" s="2">
         <v>2404001</v>
       </c>
@@ -11631,7 +11704,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="204" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A204" s="2">
         <v>2404006</v>
       </c>
@@ -11681,7 +11754,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="205" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A205" s="2">
         <v>2404006</v>
       </c>
@@ -11731,7 +11804,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="206" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A206" s="2">
         <v>2404006</v>
       </c>
@@ -11781,7 +11854,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="207" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A207" s="2">
         <v>2404015</v>
       </c>
@@ -11828,7 +11901,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="208" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A208" s="2">
         <v>2404015</v>
       </c>
@@ -11875,7 +11948,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="209" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A209" s="2">
         <v>2404015</v>
       </c>
@@ -11922,7 +11995,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="210" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A210" s="2">
         <v>2405001</v>
       </c>
@@ -11972,7 +12045,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="211" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A211" s="2">
         <v>2405001</v>
       </c>
@@ -12022,7 +12095,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="212" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A212" s="2">
         <v>2405001</v>
       </c>
@@ -12072,7 +12145,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="213" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A213" s="2">
         <v>2405006</v>
       </c>
@@ -12122,7 +12195,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="214" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A214" s="2">
         <v>2405006</v>
       </c>
@@ -12172,7 +12245,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="215" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A215" s="2">
         <v>2405006</v>
       </c>
@@ -12222,7 +12295,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="216" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A216" s="2">
         <v>2405015</v>
       </c>
@@ -12272,7 +12345,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="217" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A217" s="2">
         <v>2405015</v>
       </c>
@@ -12322,7 +12395,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="218" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A218" s="2">
         <v>2405015</v>
       </c>
@@ -12369,7 +12442,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="219" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A219" s="2">
         <v>2406004</v>
       </c>
@@ -12419,7 +12492,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="220" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A220" s="2">
         <v>2406004</v>
       </c>
@@ -12469,7 +12542,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="221" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A221" s="2">
         <v>2406004</v>
       </c>
@@ -12519,7 +12592,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="222" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A222" s="2">
         <v>2406004</v>
       </c>
@@ -12569,7 +12642,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="223" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A223" s="2">
         <v>2406004</v>
       </c>
@@ -12619,7 +12692,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="224" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A224" s="2">
         <v>2406009</v>
       </c>
@@ -12666,7 +12739,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="225" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A225" s="2">
         <v>2406009</v>
       </c>
@@ -12713,7 +12786,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="226" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A226" s="2">
         <v>2406009</v>
       </c>
@@ -12760,7 +12833,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="227" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A227" s="2">
         <v>2406009</v>
       </c>
@@ -12807,7 +12880,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="228" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A228" s="2">
         <v>2406009</v>
       </c>
@@ -12854,7 +12927,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="229" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A229" s="2">
         <v>2406012</v>
       </c>
@@ -12901,7 +12974,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="230" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A230" s="2">
         <v>2406012</v>
       </c>
@@ -12948,7 +13021,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="231" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A231" s="2">
         <v>2406012</v>
       </c>
@@ -12995,7 +13068,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="232" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A232" s="2">
         <v>2059001</v>
       </c>
@@ -13042,7 +13115,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="233" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A233" s="2">
         <v>2059002</v>
       </c>
@@ -13089,7 +13162,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="234" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A234" s="2">
         <v>2059006</v>
       </c>
@@ -13136,7 +13209,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="235" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A235" s="2">
         <v>2140011</v>
       </c>
@@ -13183,7 +13256,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="236" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A236" s="2">
         <v>2390004</v>
       </c>
@@ -13230,7 +13303,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="237" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A237" s="2">
         <v>2390004</v>
       </c>
@@ -13277,7 +13350,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="238" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A238" s="2">
         <v>2390004</v>
       </c>
@@ -13324,7 +13397,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="239" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A239" s="2">
         <v>2390009</v>
       </c>
@@ -13371,7 +13444,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="240" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A240" s="2">
         <v>2390009</v>
       </c>
@@ -13418,7 +13491,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="241" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A241" s="2">
         <v>2390009</v>
       </c>
@@ -13465,7 +13538,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="242" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A242" s="2">
         <v>2390013</v>
       </c>
@@ -13509,7 +13582,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="243" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A243" s="2">
         <v>2390013</v>
       </c>
@@ -13553,7 +13626,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="244" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A244" s="2">
         <v>2390013</v>
       </c>
@@ -13597,7 +13670,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="252" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L252" s="1"/>
     </row>
   </sheetData>

--- a/POD_2026-27_11-5-2026.xlsx
+++ b/POD_2026-27_11-5-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guillermo.vera/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4AC1A18-C88D-7641-8EEE-7E1D0486837C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E7464F1-4647-7541-8E37-4FEEC6A212DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="POD" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2982" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2987" uniqueCount="528">
   <si>
     <t>POD_2026-27_11-5-2026</t>
   </si>
@@ -1611,6 +1611,15 @@
   </si>
   <si>
     <t>EVA PRIMO (12)</t>
+  </si>
+  <si>
+    <t>MARTA LATORRE (60)</t>
+  </si>
+  <si>
+    <t>MARTA LATORRE (44)</t>
+  </si>
+  <si>
+    <t>MARTA LATORRE (16)</t>
   </si>
 </sst>
 </file>
@@ -1659,7 +1668,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1675,9 +1684,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2828,6 +2834,9 @@
       <c r="M18" t="s">
         <v>26</v>
       </c>
+      <c r="N18" s="6" t="s">
+        <v>525</v>
+      </c>
       <c r="Q18" t="s">
         <v>27</v>
       </c>
@@ -2875,6 +2884,9 @@
       <c r="M19" t="s">
         <v>26</v>
       </c>
+      <c r="N19" s="6" t="s">
+        <v>526</v>
+      </c>
       <c r="Q19" t="s">
         <v>27</v>
       </c>
@@ -2922,6 +2934,9 @@
       <c r="M20" t="s">
         <v>26</v>
       </c>
+      <c r="N20" s="6" t="s">
+        <v>527</v>
+      </c>
       <c r="Q20" t="s">
         <v>27</v>
       </c>
@@ -2969,6 +2984,9 @@
       <c r="M21" t="s">
         <v>26</v>
       </c>
+      <c r="N21" s="6" t="s">
+        <v>527</v>
+      </c>
       <c r="Q21" t="s">
         <v>27</v>
       </c>
@@ -5918,6 +5936,9 @@
       <c r="M83" t="s">
         <v>26</v>
       </c>
+      <c r="N83" s="6" t="s">
+        <v>525</v>
+      </c>
       <c r="Q83" t="s">
         <v>27</v>
       </c>
@@ -7605,7 +7626,7 @@
       <c r="M118" t="s">
         <v>26</v>
       </c>
-      <c r="N118" s="9" t="s">
+      <c r="N118" s="3" t="s">
         <v>517</v>
       </c>
       <c r="Q118" t="s">
@@ -7652,7 +7673,7 @@
       <c r="M119" t="s">
         <v>26</v>
       </c>
-      <c r="N119" s="9" t="s">
+      <c r="N119" s="3" t="s">
         <v>517</v>
       </c>
       <c r="Q119" t="s">

--- a/POD_2026-27_11-5-2026.xlsx
+++ b/POD_2026-27_11-5-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guillermo.vera/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E7464F1-4647-7541-8E37-4FEEC6A212DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D5BA426-1976-AC46-95B3-FCD1D8114471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2987" uniqueCount="528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2995" uniqueCount="533">
   <si>
     <t>POD_2026-27_11-5-2026</t>
   </si>
@@ -1620,6 +1620,21 @@
   </si>
   <si>
     <t>MARTA LATORRE (16)</t>
+  </si>
+  <si>
+    <t>L=&gt;(20:00-22:00)[21/09/26, 28/09/26, 05/10/26, 19/10/26, 26/10/26, 09/11/26, 16/11/26, 23/11/26]</t>
+  </si>
+  <si>
+    <t>M=&gt;(20:00-22:00)[21/09/26, 28/09/26, 05/10/26, 19/10/26, 26/10/26, 09/11/26, 16/11/26, 23/11/26]</t>
+  </si>
+  <si>
+    <t>X=&gt;(20:00-22:00)[21/09/26, 28/09/26, 05/10/26, 19/10/26, 26/10/26, 09/11/26, 16/11/26, 23/11/26]</t>
+  </si>
+  <si>
+    <t>J=&gt;(20:00-22:00)[21/09/26, 28/09/26, 05/10/26, 19/10/26, 26/10/26, 09/11/26, 16/11/26, 23/11/26]</t>
+  </si>
+  <si>
+    <t>V=&gt;(20:00-22:00)[21/09/26, 28/09/26, 05/10/26, 19/10/26, 26/10/26, 09/11/26, 16/11/26, 23/11/26]</t>
   </si>
 </sst>
 </file>
@@ -4715,7 +4730,7 @@
       <c r="J57" t="s">
         <v>41</v>
       </c>
-      <c r="K57" t="s">
+      <c r="K57" s="6" t="s">
         <v>130</v>
       </c>
       <c r="L57" t="s">
@@ -4762,6 +4777,9 @@
       <c r="J58" t="s">
         <v>41</v>
       </c>
+      <c r="K58" s="6" t="s">
+        <v>528</v>
+      </c>
       <c r="L58" t="s">
         <v>132</v>
       </c>
@@ -4806,6 +4824,9 @@
       <c r="J59" t="s">
         <v>41</v>
       </c>
+      <c r="K59" s="6" t="s">
+        <v>529</v>
+      </c>
       <c r="L59" t="s">
         <v>132</v>
       </c>
@@ -4897,6 +4918,9 @@
       <c r="J61" t="s">
         <v>41</v>
       </c>
+      <c r="K61" t="s">
+        <v>528</v>
+      </c>
       <c r="L61" t="s">
         <v>135</v>
       </c>
@@ -4941,7 +4965,9 @@
       <c r="J62" t="s">
         <v>41</v>
       </c>
-      <c r="K62" s="1"/>
+      <c r="K62" s="6" t="s">
+        <v>529</v>
+      </c>
       <c r="L62" t="s">
         <v>135</v>
       </c>
@@ -5130,6 +5156,9 @@
       <c r="J66" t="s">
         <v>41</v>
       </c>
+      <c r="K66" s="6" t="s">
+        <v>528</v>
+      </c>
       <c r="L66" t="s">
         <v>144</v>
       </c>
@@ -5174,6 +5203,9 @@
       <c r="J67" t="s">
         <v>41</v>
       </c>
+      <c r="K67" s="6" t="s">
+        <v>530</v>
+      </c>
       <c r="L67" t="s">
         <v>144</v>
       </c>
@@ -5262,6 +5294,9 @@
       <c r="J69" t="s">
         <v>24</v>
       </c>
+      <c r="K69" s="6" t="s">
+        <v>531</v>
+      </c>
       <c r="M69" t="s">
         <v>26</v>
       </c>
@@ -5302,6 +5337,9 @@
       </c>
       <c r="J70" t="s">
         <v>24</v>
+      </c>
+      <c r="K70" s="6" t="s">
+        <v>532</v>
       </c>
       <c r="M70" t="s">
         <v>26</v>

--- a/POD_2026-27_11-5-2026.xlsx
+++ b/POD_2026-27_11-5-2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr showInkAnnotation="0" autoCompressPictures="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guillermo.vera/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guillermo.vera/Desktop/POD2627/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D5BA426-1976-AC46-95B3-FCD1D8114471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A62830C5-C08A-E345-9A6E-41BCD6196DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2995" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3005" uniqueCount="540">
   <si>
     <t>POD_2026-27_11-5-2026</t>
   </si>
@@ -1635,6 +1635,27 @@
   </si>
   <si>
     <t>V=&gt;(20:00-22:00)[21/09/26, 28/09/26, 05/10/26, 19/10/26, 26/10/26, 09/11/26, 16/11/26, 23/11/26]</t>
+  </si>
+  <si>
+    <t>ELIO VALERO (48)</t>
+  </si>
+  <si>
+    <t>ELIO VALERO (12)</t>
+  </si>
+  <si>
+    <t>ELIO VALERO (22)</t>
+  </si>
+  <si>
+    <t>ELIO VALERO (4)</t>
+  </si>
+  <si>
+    <t>ELIO VALERO (39)</t>
+  </si>
+  <si>
+    <t>ELIO VALERO (21)</t>
+  </si>
+  <si>
+    <t>ELIO VALERO (60)</t>
   </si>
 </sst>
 </file>
@@ -5874,6 +5895,9 @@
       <c r="M81" t="s">
         <v>26</v>
       </c>
+      <c r="N81" s="6" t="s">
+        <v>539</v>
+      </c>
       <c r="Q81" t="s">
         <v>27</v>
       </c>
@@ -10164,6 +10188,9 @@
       <c r="M170" t="s">
         <v>26</v>
       </c>
+      <c r="N170" s="6" t="s">
+        <v>533</v>
+      </c>
       <c r="Q170" t="s">
         <v>27</v>
       </c>
@@ -10211,6 +10238,9 @@
       <c r="M171" t="s">
         <v>26</v>
       </c>
+      <c r="N171" s="6" t="s">
+        <v>534</v>
+      </c>
       <c r="Q171" t="s">
         <v>27</v>
       </c>
@@ -10258,6 +10288,9 @@
       <c r="M172" t="s">
         <v>26</v>
       </c>
+      <c r="N172" s="6" t="s">
+        <v>534</v>
+      </c>
       <c r="Q172" t="s">
         <v>27</v>
       </c>
@@ -10455,6 +10488,9 @@
       <c r="M176" t="s">
         <v>26</v>
       </c>
+      <c r="N176" s="6" t="s">
+        <v>535</v>
+      </c>
       <c r="Q176" t="s">
         <v>27</v>
       </c>
@@ -10502,6 +10538,9 @@
       <c r="M177" t="s">
         <v>26</v>
       </c>
+      <c r="N177" s="6" t="s">
+        <v>536</v>
+      </c>
       <c r="Q177" t="s">
         <v>27</v>
       </c>
@@ -10596,6 +10635,9 @@
       <c r="M179" t="s">
         <v>26</v>
       </c>
+      <c r="N179" s="6" t="s">
+        <v>536</v>
+      </c>
       <c r="Q179" t="s">
         <v>27</v>
       </c>
@@ -11518,6 +11560,9 @@
       <c r="M198" t="s">
         <v>26</v>
       </c>
+      <c r="N198" s="6" t="s">
+        <v>537</v>
+      </c>
       <c r="Q198" t="s">
         <v>27</v>
       </c>
@@ -11562,6 +11607,9 @@
       <c r="M199" t="s">
         <v>26</v>
       </c>
+      <c r="N199" s="6" t="s">
+        <v>538</v>
+      </c>
       <c r="Q199" t="s">
         <v>27</v>
       </c>
@@ -11605,6 +11653,9 @@
       </c>
       <c r="M200" t="s">
         <v>26</v>
+      </c>
+      <c r="N200" s="6" t="s">
+        <v>538</v>
       </c>
       <c r="Q200" t="s">
         <v>27</v>

--- a/POD_2026-27_11-5-2026.xlsx
+++ b/POD_2026-27_11-5-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guillermo.vera/Desktop/POD2627/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A62830C5-C08A-E345-9A6E-41BCD6196DD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EEA20F1-FBC5-6C47-8E70-0E65FB72B0E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3005" uniqueCount="540">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3016" uniqueCount="546">
   <si>
     <t>POD_2026-27_11-5-2026</t>
   </si>
@@ -1656,6 +1656,24 @@
   </si>
   <si>
     <t>ELIO VALERO (60)</t>
+  </si>
+  <si>
+    <t>DAVID PUERTAS (40)</t>
+  </si>
+  <si>
+    <t>DAVID PUERTAS (20)</t>
+  </si>
+  <si>
+    <t>DAVID PUERTAS (48)</t>
+  </si>
+  <si>
+    <t>DAVID PUERTAS (12)</t>
+  </si>
+  <si>
+    <t>DAVID PUERTAS (52)</t>
+  </si>
+  <si>
+    <t>DAVID PUERTAS (4)</t>
   </si>
 </sst>
 </file>
@@ -8158,6 +8176,9 @@
       <c r="M128" t="s">
         <v>26</v>
       </c>
+      <c r="N128" s="6" t="s">
+        <v>540</v>
+      </c>
       <c r="Q128" t="s">
         <v>27</v>
       </c>
@@ -8205,6 +8226,9 @@
       <c r="M129" t="s">
         <v>26</v>
       </c>
+      <c r="N129" s="6" t="s">
+        <v>541</v>
+      </c>
       <c r="Q129" t="s">
         <v>27</v>
       </c>
@@ -8252,6 +8276,9 @@
       <c r="M130" t="s">
         <v>26</v>
       </c>
+      <c r="N130" s="6" t="s">
+        <v>541</v>
+      </c>
       <c r="Q130" t="s">
         <v>27</v>
       </c>
@@ -8892,6 +8919,9 @@
       <c r="M143" t="s">
         <v>26</v>
       </c>
+      <c r="N143" s="6" t="s">
+        <v>542</v>
+      </c>
       <c r="Q143" t="s">
         <v>27</v>
       </c>
@@ -8939,6 +8969,9 @@
       <c r="M144" t="s">
         <v>26</v>
       </c>
+      <c r="N144" s="6" t="s">
+        <v>543</v>
+      </c>
       <c r="Q144" t="s">
         <v>27</v>
       </c>
@@ -8986,6 +9019,9 @@
       <c r="M145" t="s">
         <v>26</v>
       </c>
+      <c r="N145" s="6" t="s">
+        <v>543</v>
+      </c>
       <c r="Q145" t="s">
         <v>27</v>
       </c>
@@ -12842,6 +12878,9 @@
       <c r="M224" t="s">
         <v>26</v>
       </c>
+      <c r="N224" s="6" t="s">
+        <v>544</v>
+      </c>
       <c r="Q224" t="s">
         <v>27</v>
       </c>
@@ -12889,6 +12928,9 @@
       <c r="M225" t="s">
         <v>26</v>
       </c>
+      <c r="N225" s="6" t="s">
+        <v>545</v>
+      </c>
       <c r="Q225" t="s">
         <v>27</v>
       </c>
@@ -12936,6 +12978,9 @@
       <c r="M226" t="s">
         <v>26</v>
       </c>
+      <c r="N226" s="6" t="s">
+        <v>545</v>
+      </c>
       <c r="Q226" t="s">
         <v>27</v>
       </c>
@@ -12983,6 +13028,9 @@
       <c r="M227" t="s">
         <v>26</v>
       </c>
+      <c r="N227" s="6" t="s">
+        <v>545</v>
+      </c>
       <c r="Q227" t="s">
         <v>27</v>
       </c>
@@ -13029,6 +13077,9 @@
       </c>
       <c r="M228" t="s">
         <v>26</v>
+      </c>
+      <c r="N228" s="6" t="s">
+        <v>545</v>
       </c>
       <c r="Q228" t="s">
         <v>27</v>

--- a/POD_2026-27_11-5-2026.xlsx
+++ b/POD_2026-27_11-5-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guillermo.vera/Desktop/POD2627/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EEA20F1-FBC5-6C47-8E70-0E65FB72B0E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E892D8FA-841F-BF48-A74C-07D5ED9D1E64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3016" uniqueCount="546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3024" uniqueCount="548">
   <si>
     <t>POD_2026-27_11-5-2026</t>
   </si>
@@ -1674,6 +1674,12 @@
   </si>
   <si>
     <t>DAVID PUERTAS (4)</t>
+  </si>
+  <si>
+    <t>MARIA TERESA TEJEDOR (44)</t>
+  </si>
+  <si>
+    <t>MARIA TERESA TEJEDOR (16)</t>
   </si>
 </sst>
 </file>
@@ -2712,6 +2718,9 @@
       <c r="M14" t="s">
         <v>26</v>
       </c>
+      <c r="N14" s="6" t="s">
+        <v>546</v>
+      </c>
       <c r="Q14" t="s">
         <v>27</v>
       </c>
@@ -2756,6 +2765,9 @@
       <c r="M15" t="s">
         <v>26</v>
       </c>
+      <c r="N15" s="6" t="s">
+        <v>547</v>
+      </c>
       <c r="Q15" t="s">
         <v>27</v>
       </c>
@@ -2800,6 +2812,9 @@
       <c r="M16" t="s">
         <v>26</v>
       </c>
+      <c r="N16" s="6" t="s">
+        <v>547</v>
+      </c>
       <c r="Q16" t="s">
         <v>27</v>
       </c>
@@ -3229,6 +3244,9 @@
       <c r="M25" t="s">
         <v>26</v>
       </c>
+      <c r="N25" s="6" t="s">
+        <v>546</v>
+      </c>
       <c r="Q25" t="s">
         <v>27</v>
       </c>
@@ -3276,6 +3294,9 @@
       <c r="M26" t="s">
         <v>26</v>
       </c>
+      <c r="N26" s="6" t="s">
+        <v>547</v>
+      </c>
       <c r="Q26" t="s">
         <v>27</v>
       </c>
@@ -3323,6 +3344,9 @@
       <c r="M27" t="s">
         <v>26</v>
       </c>
+      <c r="N27" s="6" t="s">
+        <v>547</v>
+      </c>
       <c r="Q27" t="s">
         <v>27</v>
       </c>
@@ -3370,6 +3394,9 @@
       <c r="M28" t="s">
         <v>26</v>
       </c>
+      <c r="N28" s="6" t="s">
+        <v>546</v>
+      </c>
       <c r="Q28" t="s">
         <v>27</v>
       </c>
@@ -3413,6 +3440,9 @@
       </c>
       <c r="M29" t="s">
         <v>26</v>
+      </c>
+      <c r="N29" s="6" t="s">
+        <v>547</v>
       </c>
       <c r="Q29" t="s">
         <v>27</v>

--- a/POD_2026-27_11-5-2026.xlsx
+++ b/POD_2026-27_11-5-2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guillermo.vera/Desktop/POD2627/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guillermo.vera\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E892D8FA-841F-BF48-A74C-07D5ED9D1E64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D26D43E2-2BD9-4520-98CB-B41B073D61E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="POD" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3024" uniqueCount="548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3025" uniqueCount="548">
   <si>
     <t>POD_2026-27_11-5-2026</t>
   </si>
@@ -1762,9 +1762,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1802,7 +1802,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1908,7 +1908,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2050,7 +2050,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2059,30 +2059,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S252"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="71.33203125" customWidth="1"/>
+    <col min="2" max="2" width="71.28515625" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" customWidth="1"/>
-    <col min="5" max="5" width="20.1640625" customWidth="1"/>
-    <col min="6" max="6" width="64.1640625" customWidth="1"/>
-    <col min="7" max="7" width="20.83203125" customWidth="1"/>
-    <col min="8" max="8" width="6.5" customWidth="1"/>
-    <col min="9" max="9" width="7.83203125" customWidth="1"/>
-    <col min="10" max="10" width="6.5" customWidth="1"/>
-    <col min="11" max="11" width="107.1640625" customWidth="1"/>
-    <col min="12" max="12" width="53.6640625" customWidth="1"/>
-    <col min="13" max="13" width="12.6640625" customWidth="1"/>
-    <col min="14" max="14" width="36.5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="36.5" customWidth="1"/>
-    <col min="16" max="16" width="20.83203125" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" customWidth="1"/>
+    <col min="5" max="5" width="20.140625" customWidth="1"/>
+    <col min="6" max="6" width="64.140625" customWidth="1"/>
+    <col min="7" max="7" width="20.85546875" customWidth="1"/>
+    <col min="8" max="8" width="6.42578125" customWidth="1"/>
+    <col min="9" max="9" width="7.85546875" customWidth="1"/>
+    <col min="10" max="10" width="6.42578125" customWidth="1"/>
+    <col min="11" max="11" width="107.140625" customWidth="1"/>
+    <col min="12" max="12" width="53.7109375" customWidth="1"/>
+    <col min="13" max="13" width="12.7109375" customWidth="1"/>
+    <col min="14" max="14" width="36.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="36.42578125" customWidth="1"/>
+    <col min="16" max="16" width="20.85546875" customWidth="1"/>
     <col min="17" max="17" width="52" customWidth="1"/>
-    <col min="18" max="18" width="32.5" customWidth="1"/>
-    <col min="19" max="19" width="16.83203125" customWidth="1"/>
+    <col min="18" max="18" width="32.42578125" customWidth="1"/>
+    <col min="19" max="19" width="16.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -2105,7 +2105,7 @@
       <c r="R1" s="8"/>
       <c r="S1" s="8"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2164,7 +2164,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2291005</v>
       </c>
@@ -2208,7 +2208,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>2291009</v>
       </c>
@@ -2252,7 +2252,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>2240005</v>
       </c>
@@ -2299,7 +2299,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>2240009</v>
       </c>
@@ -2346,7 +2346,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>2251011</v>
       </c>
@@ -2390,7 +2390,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>2327002</v>
       </c>
@@ -2437,7 +2437,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>2327002</v>
       </c>
@@ -2484,7 +2484,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>2327002</v>
       </c>
@@ -2531,7 +2531,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>2327007</v>
       </c>
@@ -2581,7 +2581,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>2327007</v>
       </c>
@@ -2631,7 +2631,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>2327007</v>
       </c>
@@ -2681,7 +2681,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>2327015</v>
       </c>
@@ -2728,7 +2728,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>2327015</v>
       </c>
@@ -2775,7 +2775,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>2327015</v>
       </c>
@@ -2822,7 +2822,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>2360001</v>
       </c>
@@ -2866,7 +2866,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>2360002</v>
       </c>
@@ -2913,7 +2913,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>2382005</v>
       </c>
@@ -2963,7 +2963,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>2382005</v>
       </c>
@@ -3013,7 +3013,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>2382005</v>
       </c>
@@ -3063,7 +3063,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>2382005</v>
       </c>
@@ -3110,7 +3110,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>2382005</v>
       </c>
@@ -3157,7 +3157,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>2382005</v>
       </c>
@@ -3204,7 +3204,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>2382010</v>
       </c>
@@ -3254,7 +3254,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>2382010</v>
       </c>
@@ -3304,7 +3304,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>2382010</v>
       </c>
@@ -3354,7 +3354,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>2382010</v>
       </c>
@@ -3394,9 +3394,7 @@
       <c r="M28" t="s">
         <v>26</v>
       </c>
-      <c r="N28" s="6" t="s">
-        <v>546</v>
-      </c>
+      <c r="N28" s="6"/>
       <c r="Q28" t="s">
         <v>27</v>
       </c>
@@ -3404,7 +3402,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>2382010</v>
       </c>
@@ -3441,9 +3439,7 @@
       <c r="M29" t="s">
         <v>26</v>
       </c>
-      <c r="N29" s="6" t="s">
-        <v>547</v>
-      </c>
+      <c r="N29" s="6"/>
       <c r="Q29" t="s">
         <v>27</v>
       </c>
@@ -3451,7 +3447,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>2382010</v>
       </c>
@@ -3498,7 +3494,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>2383001</v>
       </c>
@@ -3548,7 +3544,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>2383001</v>
       </c>
@@ -3595,7 +3591,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>2383001</v>
       </c>
@@ -3642,7 +3638,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>2383001</v>
       </c>
@@ -3692,7 +3688,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>2383001</v>
       </c>
@@ -3742,7 +3738,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>2383001</v>
       </c>
@@ -3792,7 +3788,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>2383002</v>
       </c>
@@ -3842,7 +3838,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>2383002</v>
       </c>
@@ -3889,7 +3885,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>2383002</v>
       </c>
@@ -3936,7 +3932,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>2383002</v>
       </c>
@@ -3986,7 +3982,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>2383002</v>
       </c>
@@ -4036,7 +4032,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>2383002</v>
       </c>
@@ -4086,7 +4082,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="48" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>2383007</v>
       </c>
@@ -4136,7 +4132,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:18" ht="48" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>2383007</v>
       </c>
@@ -4186,7 +4182,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>2384001</v>
       </c>
@@ -4236,7 +4232,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>2384001</v>
       </c>
@@ -4286,7 +4282,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>2384001</v>
       </c>
@@ -4336,7 +4332,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>2384005</v>
       </c>
@@ -4383,7 +4379,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>2384005</v>
       </c>
@@ -4430,7 +4426,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>2384005</v>
       </c>
@@ -4477,7 +4473,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>2385001</v>
       </c>
@@ -4527,7 +4523,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>2385001</v>
       </c>
@@ -4577,7 +4573,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>2385001</v>
       </c>
@@ -4627,7 +4623,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>2385005</v>
       </c>
@@ -4674,7 +4670,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>2385005</v>
       </c>
@@ -4721,7 +4717,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>2385005</v>
       </c>
@@ -4768,7 +4764,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>2386001</v>
       </c>
@@ -4815,7 +4811,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>2386001</v>
       </c>
@@ -4862,7 +4858,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>2386001</v>
       </c>
@@ -4909,7 +4905,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>2386001</v>
       </c>
@@ -4956,7 +4952,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>2386001</v>
       </c>
@@ -5003,7 +4999,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>2386001</v>
       </c>
@@ -5050,7 +5046,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>2386002</v>
       </c>
@@ -5097,7 +5093,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>2386002</v>
       </c>
@@ -5147,7 +5143,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>2387009</v>
       </c>
@@ -5194,7 +5190,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>2387009</v>
       </c>
@@ -5241,7 +5237,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>2387009</v>
       </c>
@@ -5288,7 +5284,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>2387016</v>
       </c>
@@ -5325,6 +5321,9 @@
       <c r="M68" t="s">
         <v>26</v>
       </c>
+      <c r="N68" t="s">
+        <v>546</v>
+      </c>
       <c r="Q68" t="s">
         <v>27</v>
       </c>
@@ -5332,7 +5331,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>2387016</v>
       </c>
@@ -5369,6 +5368,9 @@
       <c r="M69" t="s">
         <v>26</v>
       </c>
+      <c r="N69" t="s">
+        <v>547</v>
+      </c>
       <c r="Q69" t="s">
         <v>27</v>
       </c>
@@ -5376,7 +5378,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>2387016</v>
       </c>
@@ -5413,6 +5415,9 @@
       <c r="M70" t="s">
         <v>26</v>
       </c>
+      <c r="N70" t="s">
+        <v>547</v>
+      </c>
       <c r="Q70" t="s">
         <v>27</v>
       </c>
@@ -5420,7 +5425,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="71" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>2265020</v>
       </c>
@@ -5468,7 +5473,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>2029018</v>
       </c>
@@ -5515,7 +5520,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>2030013</v>
       </c>
@@ -5562,7 +5567,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>2031001</v>
       </c>
@@ -5606,7 +5611,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>2032001</v>
       </c>
@@ -5656,7 +5661,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>2032007</v>
       </c>
@@ -5706,7 +5711,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>2032009</v>
       </c>
@@ -5753,7 +5758,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>2033001</v>
       </c>
@@ -5800,7 +5805,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="79" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>2033002</v>
       </c>
@@ -5853,7 +5858,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>2033006</v>
       </c>
@@ -5903,7 +5908,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>2034001</v>
       </c>
@@ -5953,7 +5958,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="82" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>2034002</v>
       </c>
@@ -6006,7 +6011,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>2034006</v>
       </c>
@@ -6056,7 +6061,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>2061001</v>
       </c>
@@ -6100,7 +6105,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>2061002</v>
       </c>
@@ -6147,7 +6152,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>2061006</v>
       </c>
@@ -6191,7 +6196,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>2107013</v>
       </c>
@@ -6238,7 +6243,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>2143016</v>
       </c>
@@ -6285,7 +6290,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>2148011</v>
       </c>
@@ -6329,7 +6334,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>2175020</v>
       </c>
@@ -6376,7 +6381,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="91" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>2285005</v>
       </c>
@@ -6426,7 +6431,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>2285006</v>
       </c>
@@ -6473,7 +6478,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>2285007</v>
       </c>
@@ -6520,7 +6525,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>2286015</v>
       </c>
@@ -6564,7 +6569,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>2338044</v>
       </c>
@@ -6608,7 +6613,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>2342014</v>
       </c>
@@ -6655,7 +6660,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="97" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>5</v>
       </c>
@@ -6703,7 +6708,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="98" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>2343027</v>
       </c>
@@ -6751,7 +6756,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>2343027</v>
       </c>
@@ -6798,7 +6803,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>2343027</v>
       </c>
@@ -6844,7 +6849,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>2347001</v>
       </c>
@@ -6894,7 +6899,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>2347003</v>
       </c>
@@ -6944,7 +6949,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="103" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
         <v>2347005</v>
       </c>
@@ -6995,7 +7000,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
         <v>2347006</v>
       </c>
@@ -7045,7 +7050,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="105" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
         <v>2347007</v>
       </c>
@@ -7096,7 +7101,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
         <v>2347013</v>
       </c>
@@ -7146,7 +7151,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
         <v>2347014</v>
       </c>
@@ -7193,7 +7198,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
         <v>2347017</v>
       </c>
@@ -7243,7 +7248,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="109" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>2347030</v>
       </c>
@@ -7294,7 +7299,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>2347021</v>
       </c>
@@ -7344,7 +7349,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="111" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <v>2347022</v>
       </c>
@@ -7396,7 +7401,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
         <v>2347024</v>
       </c>
@@ -7446,7 +7451,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="113" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
         <v>2347026</v>
       </c>
@@ -7497,7 +7502,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="114" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
         <v>2347027</v>
       </c>
@@ -7548,7 +7553,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
         <v>2347029</v>
       </c>
@@ -7598,7 +7603,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="116" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
         <v>2347031</v>
       </c>
@@ -7648,7 +7653,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="117" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
         <v>2347038</v>
       </c>
@@ -7699,7 +7704,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="118" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
         <v>2361002</v>
       </c>
@@ -7746,7 +7751,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="119" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
         <v>2361002</v>
       </c>
@@ -7793,7 +7798,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="120" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
         <v>2361002</v>
       </c>
@@ -7837,7 +7842,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="121" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
         <v>2361004</v>
       </c>
@@ -7884,7 +7889,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="122" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
         <v>2393002</v>
       </c>
@@ -7931,7 +7936,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="123" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
         <v>2393002</v>
       </c>
@@ -7978,7 +7983,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="124" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
         <v>2393002</v>
       </c>
@@ -8025,7 +8030,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="125" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
         <v>2394004</v>
       </c>
@@ -8072,7 +8077,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="126" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
         <v>2394004</v>
       </c>
@@ -8119,7 +8124,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="127" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
         <v>2394004</v>
       </c>
@@ -8166,7 +8171,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="128" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
         <v>2395003</v>
       </c>
@@ -8216,7 +8221,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="129" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
         <v>2395003</v>
       </c>
@@ -8266,7 +8271,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="130" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
         <v>2395003</v>
       </c>
@@ -8316,7 +8321,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="131" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A131" s="2">
         <v>2396001</v>
       </c>
@@ -8366,7 +8371,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="132" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
         <v>2396001</v>
       </c>
@@ -8416,7 +8421,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="133" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
         <v>2396001</v>
       </c>
@@ -8466,7 +8471,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="134" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
         <v>2397003</v>
       </c>
@@ -8516,7 +8521,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="135" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
         <v>2397003</v>
       </c>
@@ -8566,7 +8571,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="136" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
         <v>2397003</v>
       </c>
@@ -8616,7 +8621,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="137" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
         <v>2397008</v>
       </c>
@@ -8663,7 +8668,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="138" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A138" s="2">
         <v>2397008</v>
       </c>
@@ -8710,7 +8715,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="139" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A139" s="2">
         <v>2397008</v>
       </c>
@@ -8757,7 +8762,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="140" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A140" s="2">
         <v>2398001</v>
       </c>
@@ -8807,7 +8812,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="141" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
         <v>2398001</v>
       </c>
@@ -8858,7 +8863,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="142" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A142" s="2">
         <v>2398001</v>
       </c>
@@ -8909,7 +8914,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="143" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A143" s="2">
         <v>2398006</v>
       </c>
@@ -8959,7 +8964,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="144" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A144" s="2">
         <v>2398006</v>
       </c>
@@ -9009,7 +9014,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="145" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A145" s="2">
         <v>2398006</v>
       </c>
@@ -9059,7 +9064,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="146" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
         <v>2398013</v>
       </c>
@@ -9106,7 +9111,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="147" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A147" s="2">
         <v>2398013</v>
       </c>
@@ -9153,7 +9158,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A148" s="2">
         <v>2398013</v>
       </c>
@@ -9197,7 +9202,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="149" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A149" s="2">
         <v>2399003</v>
       </c>
@@ -9244,7 +9249,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="150" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
         <v>2399003</v>
       </c>
@@ -9291,7 +9296,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="151" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A151" s="2">
         <v>2399003</v>
       </c>
@@ -9338,7 +9343,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="152" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A152" s="2">
         <v>2399010</v>
       </c>
@@ -9385,7 +9390,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="153" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A153" s="2">
         <v>2399010</v>
       </c>
@@ -9432,7 +9437,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="154" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A154" s="2">
         <v>2399010</v>
       </c>
@@ -9479,7 +9484,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="155" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A155" s="2">
         <v>2399014</v>
       </c>
@@ -9526,7 +9531,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A156" s="2">
         <v>2399014</v>
       </c>
@@ -9573,7 +9578,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
         <v>2399014</v>
       </c>
@@ -9617,7 +9622,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="158" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A158" s="2">
         <v>2400003</v>
       </c>
@@ -9667,7 +9672,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="159" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A159" s="2">
         <v>2400003</v>
       </c>
@@ -9717,7 +9722,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="160" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A160" s="2">
         <v>2400003</v>
       </c>
@@ -9767,7 +9772,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="161" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A161" s="2">
         <v>2400008</v>
       </c>
@@ -9817,7 +9822,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="162" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A162" s="2">
         <v>2400008</v>
       </c>
@@ -9867,7 +9872,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="163" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A163" s="2">
         <v>2400008</v>
       </c>
@@ -9917,7 +9922,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="164" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A164" s="2">
         <v>2400012</v>
       </c>
@@ -9967,7 +9972,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="165" spans="1:18" ht="32" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A165" s="2">
         <v>2400012</v>
       </c>
@@ -10017,7 +10022,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="166" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A166" s="2">
         <v>2400012</v>
       </c>
@@ -10064,7 +10069,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="167" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A167" s="2">
         <v>2401001</v>
       </c>
@@ -10114,7 +10119,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="168" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A168" s="2">
         <v>2401001</v>
       </c>
@@ -10164,7 +10169,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="169" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A169" s="2">
         <v>2401001</v>
       </c>
@@ -10214,7 +10219,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="170" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A170" s="2">
         <v>2401007</v>
       </c>
@@ -10264,7 +10269,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="171" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A171" s="2">
         <v>2401007</v>
       </c>
@@ -10314,7 +10319,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="172" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A172" s="2">
         <v>2401007</v>
       </c>
@@ -10364,7 +10369,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="173" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A173" s="2">
         <v>2401013</v>
       </c>
@@ -10414,7 +10419,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="174" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A174" s="2">
         <v>2401013</v>
       </c>
@@ -10464,7 +10469,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="175" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A175" s="2">
         <v>2401013</v>
       </c>
@@ -10514,7 +10519,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="176" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A176" s="2">
         <v>2401018</v>
       </c>
@@ -10564,7 +10569,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="177" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A177" s="2">
         <v>2401018</v>
       </c>
@@ -10614,7 +10619,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="178" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A178" s="2">
         <v>2401018</v>
       </c>
@@ -10661,7 +10666,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="179" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A179" s="2">
         <v>2401018</v>
       </c>
@@ -10711,7 +10716,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="180" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A180" s="2">
         <v>2401018</v>
       </c>
@@ -10758,7 +10763,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="181" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A181" s="2">
         <v>2401018</v>
       </c>
@@ -10805,7 +10810,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="182" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A182" s="2">
         <v>2401018</v>
       </c>
@@ -10852,7 +10857,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="183" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A183" s="2">
         <v>2402003</v>
       </c>
@@ -10903,7 +10908,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="184" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A184" s="2">
         <v>2402003</v>
       </c>
@@ -10954,7 +10959,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="185" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A185" s="2">
         <v>2402003</v>
       </c>
@@ -11005,7 +11010,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="186" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A186" s="2">
         <v>2402008</v>
       </c>
@@ -11055,7 +11060,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="187" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A187" s="2">
         <v>2402008</v>
       </c>
@@ -11105,7 +11110,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="188" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A188" s="2">
         <v>2402008</v>
       </c>
@@ -11155,7 +11160,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="189" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A189" s="2">
         <v>2402015</v>
       </c>
@@ -11202,7 +11207,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="190" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A190" s="2">
         <v>2402015</v>
       </c>
@@ -11249,7 +11254,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="191" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A191" s="2">
         <v>2402015</v>
       </c>
@@ -11295,7 +11300,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="192" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A192" s="2">
         <v>2403004</v>
       </c>
@@ -11346,7 +11351,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="193" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A193" s="2">
         <v>2403004</v>
       </c>
@@ -11397,7 +11402,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="194" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A194" s="2">
         <v>2403004</v>
       </c>
@@ -11448,7 +11453,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="195" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A195" s="2">
         <v>2403009</v>
       </c>
@@ -11495,7 +11500,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="196" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A196" s="2">
         <v>2403009</v>
       </c>
@@ -11542,7 +11547,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="197" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A197" s="2">
         <v>2403009</v>
       </c>
@@ -11589,7 +11594,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="198" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A198" s="2">
         <v>2403013</v>
       </c>
@@ -11636,7 +11641,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="199" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A199" s="2">
         <v>2403013</v>
       </c>
@@ -11683,7 +11688,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="200" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A200" s="2">
         <v>2403013</v>
       </c>
@@ -11730,7 +11735,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="201" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A201" s="2">
         <v>2404001</v>
       </c>
@@ -11780,7 +11785,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="202" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A202" s="2">
         <v>2404001</v>
       </c>
@@ -11830,7 +11835,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="203" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A203" s="2">
         <v>2404001</v>
       </c>
@@ -11880,7 +11885,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="204" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A204" s="2">
         <v>2404006</v>
       </c>
@@ -11930,7 +11935,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="205" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A205" s="2">
         <v>2404006</v>
       </c>
@@ -11980,7 +11985,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="206" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A206" s="2">
         <v>2404006</v>
       </c>
@@ -12030,7 +12035,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="207" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A207" s="2">
         <v>2404015</v>
       </c>
@@ -12077,7 +12082,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="208" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A208" s="2">
         <v>2404015</v>
       </c>
@@ -12124,7 +12129,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="209" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A209" s="2">
         <v>2404015</v>
       </c>
@@ -12171,7 +12176,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="210" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A210" s="2">
         <v>2405001</v>
       </c>
@@ -12221,7 +12226,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="211" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A211" s="2">
         <v>2405001</v>
       </c>
@@ -12271,7 +12276,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="212" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A212" s="2">
         <v>2405001</v>
       </c>
@@ -12321,7 +12326,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="213" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A213" s="2">
         <v>2405006</v>
       </c>
@@ -12371,7 +12376,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="214" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A214" s="2">
         <v>2405006</v>
       </c>
@@ -12421,7 +12426,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="215" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A215" s="2">
         <v>2405006</v>
       </c>
@@ -12471,7 +12476,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="216" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A216" s="2">
         <v>2405015</v>
       </c>
@@ -12521,7 +12526,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="217" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A217" s="2">
         <v>2405015</v>
       </c>
@@ -12571,7 +12576,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="218" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A218" s="2">
         <v>2405015</v>
       </c>
@@ -12618,7 +12623,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="219" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A219" s="2">
         <v>2406004</v>
       </c>
@@ -12668,7 +12673,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="220" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A220" s="2">
         <v>2406004</v>
       </c>
@@ -12718,7 +12723,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="221" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A221" s="2">
         <v>2406004</v>
       </c>
@@ -12768,7 +12773,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="222" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A222" s="2">
         <v>2406004</v>
       </c>
@@ -12818,7 +12823,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="223" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A223" s="2">
         <v>2406004</v>
       </c>
@@ -12868,7 +12873,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="224" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A224" s="2">
         <v>2406009</v>
       </c>
@@ -12918,7 +12923,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="225" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A225" s="2">
         <v>2406009</v>
       </c>
@@ -12968,7 +12973,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="226" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A226" s="2">
         <v>2406009</v>
       </c>
@@ -13018,7 +13023,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="227" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A227" s="2">
         <v>2406009</v>
       </c>
@@ -13068,7 +13073,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="228" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A228" s="2">
         <v>2406009</v>
       </c>
@@ -13118,7 +13123,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="229" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A229" s="2">
         <v>2406012</v>
       </c>
@@ -13165,7 +13170,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="230" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A230" s="2">
         <v>2406012</v>
       </c>
@@ -13212,7 +13217,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="231" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A231" s="2">
         <v>2406012</v>
       </c>
@@ -13259,7 +13264,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="232" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A232" s="2">
         <v>2059001</v>
       </c>
@@ -13306,7 +13311,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="233" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A233" s="2">
         <v>2059002</v>
       </c>
@@ -13353,7 +13358,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="234" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A234" s="2">
         <v>2059006</v>
       </c>
@@ -13400,7 +13405,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="235" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A235" s="2">
         <v>2140011</v>
       </c>
@@ -13447,7 +13452,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="236" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A236" s="2">
         <v>2390004</v>
       </c>
@@ -13494,7 +13499,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="237" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A237" s="2">
         <v>2390004</v>
       </c>
@@ -13541,7 +13546,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="238" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A238" s="2">
         <v>2390004</v>
       </c>
@@ -13588,7 +13593,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="239" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A239" s="2">
         <v>2390009</v>
       </c>
@@ -13635,7 +13640,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="240" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A240" s="2">
         <v>2390009</v>
       </c>
@@ -13682,7 +13687,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="241" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A241" s="2">
         <v>2390009</v>
       </c>
@@ -13729,7 +13734,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="242" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A242" s="2">
         <v>2390013</v>
       </c>
@@ -13773,7 +13778,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="243" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A243" s="2">
         <v>2390013</v>
       </c>
@@ -13817,7 +13822,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="244" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A244" s="2">
         <v>2390013</v>
       </c>
@@ -13861,7 +13866,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="252" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L252" s="1"/>
     </row>
   </sheetData>

--- a/POD_2026-27_11-5-2026.xlsx
+++ b/POD_2026-27_11-5-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guillermo.vera\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D26D43E2-2BD9-4520-98CB-B41B073D61E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8029A388-7BDD-4AF9-A975-70143EE7D363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3025" uniqueCount="548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3032" uniqueCount="551">
   <si>
     <t>POD_2026-27_11-5-2026</t>
   </si>
@@ -1680,6 +1680,15 @@
   </si>
   <si>
     <t>MARIA TERESA TEJEDOR (16)</t>
+  </si>
+  <si>
+    <t>GUILLERMO VERA (46)</t>
+  </si>
+  <si>
+    <t>GUILLERMO VERA (14)</t>
+  </si>
+  <si>
+    <t>GUILLERMO VERA (38)</t>
   </si>
 </sst>
 </file>
@@ -4372,6 +4381,9 @@
       <c r="M48" t="s">
         <v>26</v>
       </c>
+      <c r="N48" s="6" t="s">
+        <v>548</v>
+      </c>
       <c r="Q48" t="s">
         <v>27</v>
       </c>
@@ -4419,6 +4431,9 @@
       <c r="M49" t="s">
         <v>26</v>
       </c>
+      <c r="N49" s="6" t="s">
+        <v>549</v>
+      </c>
       <c r="Q49" t="s">
         <v>27</v>
       </c>
@@ -4466,6 +4481,9 @@
       <c r="M50" t="s">
         <v>26</v>
       </c>
+      <c r="N50" s="6" t="s">
+        <v>549</v>
+      </c>
       <c r="Q50" t="s">
         <v>27</v>
       </c>
@@ -4663,6 +4681,9 @@
       <c r="M54" t="s">
         <v>26</v>
       </c>
+      <c r="N54" s="6" t="s">
+        <v>548</v>
+      </c>
       <c r="Q54" t="s">
         <v>27</v>
       </c>
@@ -4710,6 +4731,9 @@
       <c r="M55" t="s">
         <v>26</v>
       </c>
+      <c r="N55" s="6" t="s">
+        <v>549</v>
+      </c>
       <c r="Q55" t="s">
         <v>27</v>
       </c>
@@ -4757,6 +4781,9 @@
       <c r="M56" t="s">
         <v>26</v>
       </c>
+      <c r="N56" s="6" t="s">
+        <v>549</v>
+      </c>
       <c r="Q56" t="s">
         <v>27</v>
       </c>
@@ -5135,6 +5162,9 @@
       </c>
       <c r="N64" s="6" t="s">
         <v>503</v>
+      </c>
+      <c r="O64" s="6" t="s">
+        <v>550</v>
       </c>
       <c r="Q64" t="s">
         <v>27</v>

--- a/POD_2026-27_11-5-2026.xlsx
+++ b/POD_2026-27_11-5-2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guillermo.vera\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\misael.marriaga\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8029A388-7BDD-4AF9-A975-70143EE7D363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA325700-3223-4D20-AD90-9DA0C4D4001D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="POD" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3032" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3041" uniqueCount="555">
   <si>
     <t>POD_2026-27_11-5-2026</t>
   </si>
@@ -1689,13 +1689,25 @@
   </si>
   <si>
     <t>GUILLERMO VERA (38)</t>
+  </si>
+  <si>
+    <t>Enrique Benito Matías (44)</t>
+  </si>
+  <si>
+    <t>Enrique Benito Matías (16)</t>
+  </si>
+  <si>
+    <t>Enrique Benito Matías (24)</t>
+  </si>
+  <si>
+    <t>Enrique Benito Matías (6)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1714,6 +1726,18 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -1737,7 +1761,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1753,6 +1777,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2068,30 +2094,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S252"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="71.28515625" customWidth="1"/>
+    <col min="2" max="2" width="71.26953125" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" customWidth="1"/>
-    <col min="5" max="5" width="20.140625" customWidth="1"/>
-    <col min="6" max="6" width="64.140625" customWidth="1"/>
-    <col min="7" max="7" width="20.85546875" customWidth="1"/>
-    <col min="8" max="8" width="6.42578125" customWidth="1"/>
-    <col min="9" max="9" width="7.85546875" customWidth="1"/>
-    <col min="10" max="10" width="6.42578125" customWidth="1"/>
-    <col min="11" max="11" width="107.140625" customWidth="1"/>
-    <col min="12" max="12" width="53.7109375" customWidth="1"/>
-    <col min="13" max="13" width="12.7109375" customWidth="1"/>
-    <col min="14" max="14" width="36.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="36.42578125" customWidth="1"/>
-    <col min="16" max="16" width="20.85546875" customWidth="1"/>
+    <col min="4" max="4" width="9.1796875" customWidth="1"/>
+    <col min="5" max="5" width="20.1796875" customWidth="1"/>
+    <col min="6" max="6" width="64.1796875" customWidth="1"/>
+    <col min="7" max="7" width="20.81640625" customWidth="1"/>
+    <col min="8" max="8" width="6.453125" customWidth="1"/>
+    <col min="9" max="9" width="7.81640625" customWidth="1"/>
+    <col min="10" max="10" width="6.453125" customWidth="1"/>
+    <col min="11" max="11" width="107.1796875" customWidth="1"/>
+    <col min="12" max="12" width="53.7265625" customWidth="1"/>
+    <col min="13" max="13" width="12.7265625" customWidth="1"/>
+    <col min="14" max="14" width="36.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="36.453125" customWidth="1"/>
+    <col min="16" max="16" width="20.81640625" customWidth="1"/>
     <col min="17" max="17" width="52" customWidth="1"/>
-    <col min="18" max="18" width="32.42578125" customWidth="1"/>
-    <col min="19" max="19" width="16.85546875" customWidth="1"/>
+    <col min="18" max="18" width="32.453125" customWidth="1"/>
+    <col min="19" max="19" width="16.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -2114,7 +2140,7 @@
       <c r="R1" s="8"/>
       <c r="S1" s="8"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2173,7 +2199,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>2291005</v>
       </c>
@@ -2217,7 +2243,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>2291009</v>
       </c>
@@ -2261,7 +2287,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>2240005</v>
       </c>
@@ -2308,7 +2334,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>2240009</v>
       </c>
@@ -2355,7 +2381,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>2251011</v>
       </c>
@@ -2399,7 +2425,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>2327002</v>
       </c>
@@ -2446,7 +2472,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>2327002</v>
       </c>
@@ -2493,7 +2519,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>2327002</v>
       </c>
@@ -2540,7 +2566,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>2327007</v>
       </c>
@@ -2590,7 +2616,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>2327007</v>
       </c>
@@ -2640,7 +2666,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>2327007</v>
       </c>
@@ -2690,7 +2716,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>2327015</v>
       </c>
@@ -2737,7 +2763,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>2327015</v>
       </c>
@@ -2784,7 +2810,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>2327015</v>
       </c>
@@ -2831,7 +2857,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>2360001</v>
       </c>
@@ -2875,7 +2901,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>2360002</v>
       </c>
@@ -2922,7 +2948,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>2382005</v>
       </c>
@@ -2972,7 +2998,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>2382005</v>
       </c>
@@ -3022,7 +3048,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>2382005</v>
       </c>
@@ -3072,7 +3098,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>2382005</v>
       </c>
@@ -3112,6 +3138,9 @@
       <c r="M22" t="s">
         <v>26</v>
       </c>
+      <c r="N22" s="6" t="s">
+        <v>551</v>
+      </c>
       <c r="Q22" t="s">
         <v>27</v>
       </c>
@@ -3119,7 +3148,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>2382005</v>
       </c>
@@ -3159,6 +3188,9 @@
       <c r="M23" t="s">
         <v>26</v>
       </c>
+      <c r="N23" s="6" t="s">
+        <v>552</v>
+      </c>
       <c r="Q23" t="s">
         <v>27</v>
       </c>
@@ -3166,7 +3198,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>2382005</v>
       </c>
@@ -3206,6 +3238,9 @@
       <c r="M24" t="s">
         <v>26</v>
       </c>
+      <c r="N24" s="6" t="s">
+        <v>552</v>
+      </c>
       <c r="Q24" t="s">
         <v>27</v>
       </c>
@@ -3213,7 +3248,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>2382010</v>
       </c>
@@ -3263,7 +3298,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>2382010</v>
       </c>
@@ -3313,7 +3348,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>2382010</v>
       </c>
@@ -3363,7 +3398,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>2382010</v>
       </c>
@@ -3403,7 +3438,9 @@
       <c r="M28" t="s">
         <v>26</v>
       </c>
-      <c r="N28" s="6"/>
+      <c r="N28" s="6" t="s">
+        <v>551</v>
+      </c>
       <c r="Q28" t="s">
         <v>27</v>
       </c>
@@ -3411,7 +3448,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>2382010</v>
       </c>
@@ -3448,7 +3485,9 @@
       <c r="M29" t="s">
         <v>26</v>
       </c>
-      <c r="N29" s="6"/>
+      <c r="N29" s="9" t="s">
+        <v>552</v>
+      </c>
       <c r="Q29" t="s">
         <v>27</v>
       </c>
@@ -3456,7 +3495,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>2382010</v>
       </c>
@@ -3496,6 +3535,9 @@
       <c r="M30" t="s">
         <v>26</v>
       </c>
+      <c r="N30" s="6" t="s">
+        <v>552</v>
+      </c>
       <c r="Q30" t="s">
         <v>27</v>
       </c>
@@ -3503,7 +3545,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>2383001</v>
       </c>
@@ -3553,7 +3595,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>2383001</v>
       </c>
@@ -3600,7 +3642,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>2383001</v>
       </c>
@@ -3647,7 +3689,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>2383001</v>
       </c>
@@ -3697,7 +3739,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>2383001</v>
       </c>
@@ -3747,7 +3789,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>2383001</v>
       </c>
@@ -3797,7 +3839,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <v>2383002</v>
       </c>
@@ -3847,7 +3889,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <v>2383002</v>
       </c>
@@ -3894,7 +3936,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <v>2383002</v>
       </c>
@@ -3941,7 +3983,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>2383002</v>
       </c>
@@ -3991,7 +4033,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>2383002</v>
       </c>
@@ -4041,7 +4083,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>2383002</v>
       </c>
@@ -4091,7 +4133,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <v>2383007</v>
       </c>
@@ -4141,7 +4183,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>2383007</v>
       </c>
@@ -4191,7 +4233,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <v>2384001</v>
       </c>
@@ -4241,7 +4283,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>2384001</v>
       </c>
@@ -4291,7 +4333,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <v>2384001</v>
       </c>
@@ -4341,7 +4383,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>2384005</v>
       </c>
@@ -4391,7 +4433,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <v>2384005</v>
       </c>
@@ -4441,7 +4483,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <v>2384005</v>
       </c>
@@ -4491,7 +4533,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <v>2385001</v>
       </c>
@@ -4541,7 +4583,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <v>2385001</v>
       </c>
@@ -4591,7 +4633,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
         <v>2385001</v>
       </c>
@@ -4641,7 +4683,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <v>2385005</v>
       </c>
@@ -4691,7 +4733,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
         <v>2385005</v>
       </c>
@@ -4741,7 +4783,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <v>2385005</v>
       </c>
@@ -4791,7 +4833,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
         <v>2386001</v>
       </c>
@@ -4838,7 +4880,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <v>2386001</v>
       </c>
@@ -4885,7 +4927,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
         <v>2386001</v>
       </c>
@@ -4932,7 +4974,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>2386001</v>
       </c>
@@ -4979,7 +5021,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <v>2386001</v>
       </c>
@@ -5026,7 +5068,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <v>2386001</v>
       </c>
@@ -5073,7 +5115,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
         <v>2386002</v>
       </c>
@@ -5120,7 +5162,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
         <v>2386002</v>
       </c>
@@ -5173,7 +5215,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A65" s="2">
         <v>2387009</v>
       </c>
@@ -5220,7 +5262,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A66" s="2">
         <v>2387009</v>
       </c>
@@ -5267,7 +5309,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A67" s="2">
         <v>2387009</v>
       </c>
@@ -5314,7 +5356,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A68" s="2">
         <v>2387016</v>
       </c>
@@ -5361,7 +5403,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A69" s="2">
         <v>2387016</v>
       </c>
@@ -5408,7 +5450,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A70" s="2">
         <v>2387016</v>
       </c>
@@ -5455,7 +5497,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A71" s="2">
         <v>2265020</v>
       </c>
@@ -5503,7 +5545,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A72" s="2">
         <v>2029018</v>
       </c>
@@ -5550,7 +5592,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A73" s="2">
         <v>2030013</v>
       </c>
@@ -5597,7 +5639,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A74" s="2">
         <v>2031001</v>
       </c>
@@ -5641,7 +5683,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A75" s="2">
         <v>2032001</v>
       </c>
@@ -5691,7 +5733,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A76" s="2">
         <v>2032007</v>
       </c>
@@ -5741,7 +5783,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A77" s="2">
         <v>2032009</v>
       </c>
@@ -5788,7 +5830,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A78" s="2">
         <v>2033001</v>
       </c>
@@ -5835,7 +5877,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A79" s="2">
         <v>2033002</v>
       </c>
@@ -5888,7 +5930,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A80" s="2">
         <v>2033006</v>
       </c>
@@ -5938,7 +5980,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A81" s="2">
         <v>2034001</v>
       </c>
@@ -5988,7 +6030,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A82" s="2">
         <v>2034002</v>
       </c>
@@ -6041,7 +6083,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A83" s="2">
         <v>2034006</v>
       </c>
@@ -6091,7 +6133,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A84" s="2">
         <v>2061001</v>
       </c>
@@ -6135,7 +6177,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A85" s="2">
         <v>2061002</v>
       </c>
@@ -6182,7 +6224,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A86" s="2">
         <v>2061006</v>
       </c>
@@ -6226,7 +6268,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A87" s="2">
         <v>2107013</v>
       </c>
@@ -6273,7 +6315,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A88" s="2">
         <v>2143016</v>
       </c>
@@ -6320,7 +6362,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A89" s="2">
         <v>2148011</v>
       </c>
@@ -6364,7 +6406,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A90" s="2">
         <v>2175020</v>
       </c>
@@ -6411,7 +6453,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A91" s="2">
         <v>2285005</v>
       </c>
@@ -6461,7 +6503,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A92" s="2">
         <v>2285006</v>
       </c>
@@ -6508,7 +6550,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A93" s="2">
         <v>2285007</v>
       </c>
@@ -6555,7 +6597,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A94" s="2">
         <v>2286015</v>
       </c>
@@ -6599,7 +6641,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A95" s="2">
         <v>2338044</v>
       </c>
@@ -6643,7 +6685,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A96" s="2">
         <v>2342014</v>
       </c>
@@ -6690,7 +6732,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A97" s="2">
         <v>5</v>
       </c>
@@ -6738,7 +6780,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A98" s="2">
         <v>2343027</v>
       </c>
@@ -6786,7 +6828,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A99" s="2">
         <v>2343027</v>
       </c>
@@ -6833,7 +6875,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A100" s="2">
         <v>2343027</v>
       </c>
@@ -6879,7 +6921,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A101" s="2">
         <v>2347001</v>
       </c>
@@ -6929,7 +6971,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A102" s="2">
         <v>2347003</v>
       </c>
@@ -6979,7 +7021,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A103" s="2">
         <v>2347005</v>
       </c>
@@ -7030,7 +7072,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A104" s="2">
         <v>2347006</v>
       </c>
@@ -7080,7 +7122,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A105" s="2">
         <v>2347007</v>
       </c>
@@ -7131,7 +7173,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A106" s="2">
         <v>2347013</v>
       </c>
@@ -7181,7 +7223,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A107" s="2">
         <v>2347014</v>
       </c>
@@ -7228,7 +7270,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A108" s="2">
         <v>2347017</v>
       </c>
@@ -7278,7 +7320,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A109" s="2">
         <v>2347030</v>
       </c>
@@ -7329,7 +7371,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A110" s="2">
         <v>2347021</v>
       </c>
@@ -7379,7 +7421,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A111" s="2">
         <v>2347022</v>
       </c>
@@ -7431,7 +7473,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A112" s="2">
         <v>2347024</v>
       </c>
@@ -7481,7 +7523,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="113" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A113" s="2">
         <v>2347026</v>
       </c>
@@ -7532,7 +7574,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A114" s="2">
         <v>2347027</v>
       </c>
@@ -7583,7 +7625,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A115" s="2">
         <v>2347029</v>
       </c>
@@ -7633,7 +7675,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="116" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A116" s="2">
         <v>2347031</v>
       </c>
@@ -7683,7 +7725,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="117" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A117" s="2">
         <v>2347038</v>
       </c>
@@ -7734,7 +7776,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="118" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A118" s="2">
         <v>2361002</v>
       </c>
@@ -7781,7 +7823,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="119" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A119" s="2">
         <v>2361002</v>
       </c>
@@ -7828,7 +7870,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="120" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A120" s="2">
         <v>2361002</v>
       </c>
@@ -7872,7 +7914,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="121" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A121" s="2">
         <v>2361004</v>
       </c>
@@ -7919,7 +7961,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="122" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A122" s="2">
         <v>2393002</v>
       </c>
@@ -7966,7 +8008,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="123" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A123" s="2">
         <v>2393002</v>
       </c>
@@ -8013,7 +8055,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="124" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A124" s="2">
         <v>2393002</v>
       </c>
@@ -8060,7 +8102,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="125" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A125" s="2">
         <v>2394004</v>
       </c>
@@ -8107,7 +8149,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="126" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A126" s="2">
         <v>2394004</v>
       </c>
@@ -8154,7 +8196,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="127" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A127" s="2">
         <v>2394004</v>
       </c>
@@ -8201,7 +8243,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="128" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A128" s="2">
         <v>2395003</v>
       </c>
@@ -8251,7 +8293,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="129" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A129" s="2">
         <v>2395003</v>
       </c>
@@ -8301,7 +8343,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="130" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A130" s="2">
         <v>2395003</v>
       </c>
@@ -8351,7 +8393,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="131" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A131" s="2">
         <v>2396001</v>
       </c>
@@ -8401,7 +8443,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="132" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A132" s="2">
         <v>2396001</v>
       </c>
@@ -8451,7 +8493,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="133" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A133" s="2">
         <v>2396001</v>
       </c>
@@ -8501,7 +8543,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="134" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A134" s="2">
         <v>2397003</v>
       </c>
@@ -8551,7 +8593,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="135" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A135" s="2">
         <v>2397003</v>
       </c>
@@ -8601,7 +8643,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="136" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A136" s="2">
         <v>2397003</v>
       </c>
@@ -8651,7 +8693,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="137" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A137" s="2">
         <v>2397008</v>
       </c>
@@ -8698,7 +8740,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="138" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A138" s="2">
         <v>2397008</v>
       </c>
@@ -8745,7 +8787,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="139" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A139" s="2">
         <v>2397008</v>
       </c>
@@ -8792,7 +8834,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="140" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A140" s="2">
         <v>2398001</v>
       </c>
@@ -8842,7 +8884,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="141" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A141" s="2">
         <v>2398001</v>
       </c>
@@ -8893,7 +8935,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="142" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A142" s="2">
         <v>2398001</v>
       </c>
@@ -8944,7 +8986,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="143" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A143" s="2">
         <v>2398006</v>
       </c>
@@ -8994,7 +9036,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="144" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A144" s="2">
         <v>2398006</v>
       </c>
@@ -9044,7 +9086,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="145" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A145" s="2">
         <v>2398006</v>
       </c>
@@ -9094,7 +9136,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="146" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A146" s="2">
         <v>2398013</v>
       </c>
@@ -9141,7 +9183,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="147" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A147" s="2">
         <v>2398013</v>
       </c>
@@ -9188,7 +9230,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A148" s="2">
         <v>2398013</v>
       </c>
@@ -9232,7 +9274,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="149" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A149" s="2">
         <v>2399003</v>
       </c>
@@ -9279,7 +9321,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="150" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A150" s="2">
         <v>2399003</v>
       </c>
@@ -9326,7 +9368,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="151" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A151" s="2">
         <v>2399003</v>
       </c>
@@ -9373,7 +9415,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="152" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A152" s="2">
         <v>2399010</v>
       </c>
@@ -9420,7 +9462,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="153" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A153" s="2">
         <v>2399010</v>
       </c>
@@ -9467,7 +9509,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="154" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A154" s="2">
         <v>2399010</v>
       </c>
@@ -9514,7 +9556,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="155" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A155" s="2">
         <v>2399014</v>
       </c>
@@ -9561,7 +9603,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A156" s="2">
         <v>2399014</v>
       </c>
@@ -9608,7 +9650,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A157" s="2">
         <v>2399014</v>
       </c>
@@ -9652,7 +9694,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="158" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A158" s="2">
         <v>2400003</v>
       </c>
@@ -9702,7 +9744,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="159" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A159" s="2">
         <v>2400003</v>
       </c>
@@ -9752,7 +9794,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="160" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A160" s="2">
         <v>2400003</v>
       </c>
@@ -9802,7 +9844,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="161" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A161" s="2">
         <v>2400008</v>
       </c>
@@ -9852,7 +9894,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="162" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A162" s="2">
         <v>2400008</v>
       </c>
@@ -9902,7 +9944,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="163" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A163" s="2">
         <v>2400008</v>
       </c>
@@ -9952,7 +9994,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="164" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A164" s="2">
         <v>2400012</v>
       </c>
@@ -10002,7 +10044,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="165" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A165" s="2">
         <v>2400012</v>
       </c>
@@ -10052,7 +10094,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="166" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A166" s="2">
         <v>2400012</v>
       </c>
@@ -10099,7 +10141,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="167" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A167" s="2">
         <v>2401001</v>
       </c>
@@ -10149,7 +10191,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="168" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A168" s="2">
         <v>2401001</v>
       </c>
@@ -10199,7 +10241,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="169" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A169" s="2">
         <v>2401001</v>
       </c>
@@ -10249,7 +10291,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="170" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A170" s="2">
         <v>2401007</v>
       </c>
@@ -10299,7 +10341,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="171" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A171" s="2">
         <v>2401007</v>
       </c>
@@ -10349,7 +10391,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="172" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A172" s="2">
         <v>2401007</v>
       </c>
@@ -10399,7 +10441,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="173" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A173" s="2">
         <v>2401013</v>
       </c>
@@ -10449,7 +10491,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="174" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A174" s="2">
         <v>2401013</v>
       </c>
@@ -10499,7 +10541,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="175" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A175" s="2">
         <v>2401013</v>
       </c>
@@ -10549,7 +10591,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="176" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A176" s="2">
         <v>2401018</v>
       </c>
@@ -10599,7 +10641,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="177" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A177" s="2">
         <v>2401018</v>
       </c>
@@ -10649,7 +10691,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="178" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A178" s="2">
         <v>2401018</v>
       </c>
@@ -10696,7 +10738,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="179" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A179" s="2">
         <v>2401018</v>
       </c>
@@ -10746,7 +10788,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="180" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A180" s="2">
         <v>2401018</v>
       </c>
@@ -10793,7 +10835,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="181" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A181" s="2">
         <v>2401018</v>
       </c>
@@ -10840,7 +10882,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="182" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A182" s="2">
         <v>2401018</v>
       </c>
@@ -10887,7 +10929,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="183" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A183" s="2">
         <v>2402003</v>
       </c>
@@ -10938,7 +10980,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="184" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A184" s="2">
         <v>2402003</v>
       </c>
@@ -10989,7 +11031,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="185" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A185" s="2">
         <v>2402003</v>
       </c>
@@ -11040,7 +11082,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="186" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A186" s="2">
         <v>2402008</v>
       </c>
@@ -11090,7 +11132,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="187" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A187" s="2">
         <v>2402008</v>
       </c>
@@ -11140,7 +11182,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="188" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A188" s="2">
         <v>2402008</v>
       </c>
@@ -11190,7 +11232,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="189" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A189" s="2">
         <v>2402015</v>
       </c>
@@ -11237,7 +11279,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="190" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A190" s="2">
         <v>2402015</v>
       </c>
@@ -11284,7 +11326,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="191" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A191" s="2">
         <v>2402015</v>
       </c>
@@ -11330,7 +11372,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="192" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A192" s="2">
         <v>2403004</v>
       </c>
@@ -11381,7 +11423,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="193" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A193" s="2">
         <v>2403004</v>
       </c>
@@ -11432,7 +11474,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="194" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A194" s="2">
         <v>2403004</v>
       </c>
@@ -11483,7 +11525,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="195" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A195" s="2">
         <v>2403009</v>
       </c>
@@ -11523,6 +11565,9 @@
       <c r="M195" t="s">
         <v>26</v>
       </c>
+      <c r="N195" s="10" t="s">
+        <v>553</v>
+      </c>
       <c r="Q195" t="s">
         <v>27</v>
       </c>
@@ -11530,7 +11575,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="196" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A196" s="2">
         <v>2403009</v>
       </c>
@@ -11570,6 +11615,9 @@
       <c r="M196" t="s">
         <v>26</v>
       </c>
+      <c r="N196" s="10" t="s">
+        <v>554</v>
+      </c>
       <c r="Q196" t="s">
         <v>27</v>
       </c>
@@ -11577,7 +11625,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="197" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A197" s="2">
         <v>2403009</v>
       </c>
@@ -11617,6 +11665,9 @@
       <c r="M197" t="s">
         <v>26</v>
       </c>
+      <c r="N197" s="10" t="s">
+        <v>554</v>
+      </c>
       <c r="Q197" t="s">
         <v>27</v>
       </c>
@@ -11624,7 +11675,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="198" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A198" s="2">
         <v>2403013</v>
       </c>
@@ -11671,7 +11722,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="199" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A199" s="2">
         <v>2403013</v>
       </c>
@@ -11718,7 +11769,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="200" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A200" s="2">
         <v>2403013</v>
       </c>
@@ -11765,7 +11816,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="201" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A201" s="2">
         <v>2404001</v>
       </c>
@@ -11815,7 +11866,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="202" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A202" s="2">
         <v>2404001</v>
       </c>
@@ -11865,7 +11916,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="203" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A203" s="2">
         <v>2404001</v>
       </c>
@@ -11915,7 +11966,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="204" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A204" s="2">
         <v>2404006</v>
       </c>
@@ -11965,7 +12016,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="205" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A205" s="2">
         <v>2404006</v>
       </c>
@@ -12015,7 +12066,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="206" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A206" s="2">
         <v>2404006</v>
       </c>
@@ -12065,7 +12116,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="207" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A207" s="2">
         <v>2404015</v>
       </c>
@@ -12112,7 +12163,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="208" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A208" s="2">
         <v>2404015</v>
       </c>
@@ -12159,7 +12210,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="209" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A209" s="2">
         <v>2404015</v>
       </c>
@@ -12206,7 +12257,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="210" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A210" s="2">
         <v>2405001</v>
       </c>
@@ -12256,7 +12307,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="211" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A211" s="2">
         <v>2405001</v>
       </c>
@@ -12306,7 +12357,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="212" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A212" s="2">
         <v>2405001</v>
       </c>
@@ -12356,7 +12407,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="213" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A213" s="2">
         <v>2405006</v>
       </c>
@@ -12406,7 +12457,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="214" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A214" s="2">
         <v>2405006</v>
       </c>
@@ -12456,7 +12507,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="215" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A215" s="2">
         <v>2405006</v>
       </c>
@@ -12506,7 +12557,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="216" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A216" s="2">
         <v>2405015</v>
       </c>
@@ -12556,7 +12607,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="217" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A217" s="2">
         <v>2405015</v>
       </c>
@@ -12606,7 +12657,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="218" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A218" s="2">
         <v>2405015</v>
       </c>
@@ -12653,7 +12704,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="219" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A219" s="2">
         <v>2406004</v>
       </c>
@@ -12703,7 +12754,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="220" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A220" s="2">
         <v>2406004</v>
       </c>
@@ -12753,7 +12804,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="221" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A221" s="2">
         <v>2406004</v>
       </c>
@@ -12803,7 +12854,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="222" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A222" s="2">
         <v>2406004</v>
       </c>
@@ -12853,7 +12904,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="223" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A223" s="2">
         <v>2406004</v>
       </c>
@@ -12903,7 +12954,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="224" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A224" s="2">
         <v>2406009</v>
       </c>
@@ -12953,7 +13004,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="225" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A225" s="2">
         <v>2406009</v>
       </c>
@@ -13003,7 +13054,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="226" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A226" s="2">
         <v>2406009</v>
       </c>
@@ -13053,7 +13104,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="227" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A227" s="2">
         <v>2406009</v>
       </c>
@@ -13103,7 +13154,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="228" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A228" s="2">
         <v>2406009</v>
       </c>
@@ -13153,7 +13204,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="229" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A229" s="2">
         <v>2406012</v>
       </c>
@@ -13200,7 +13251,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="230" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A230" s="2">
         <v>2406012</v>
       </c>
@@ -13247,7 +13298,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="231" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A231" s="2">
         <v>2406012</v>
       </c>
@@ -13294,7 +13345,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="232" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A232" s="2">
         <v>2059001</v>
       </c>
@@ -13341,7 +13392,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="233" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A233" s="2">
         <v>2059002</v>
       </c>
@@ -13388,7 +13439,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="234" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A234" s="2">
         <v>2059006</v>
       </c>
@@ -13435,7 +13486,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="235" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A235" s="2">
         <v>2140011</v>
       </c>
@@ -13482,7 +13533,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="236" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A236" s="2">
         <v>2390004</v>
       </c>
@@ -13529,7 +13580,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="237" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A237" s="2">
         <v>2390004</v>
       </c>
@@ -13576,7 +13627,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="238" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A238" s="2">
         <v>2390004</v>
       </c>
@@ -13623,7 +13674,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="239" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A239" s="2">
         <v>2390009</v>
       </c>
@@ -13670,7 +13721,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="240" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A240" s="2">
         <v>2390009</v>
       </c>
@@ -13717,7 +13768,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="241" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A241" s="2">
         <v>2390009</v>
       </c>
@@ -13764,7 +13815,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="242" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A242" s="2">
         <v>2390013</v>
       </c>
@@ -13808,7 +13859,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="243" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A243" s="2">
         <v>2390013</v>
       </c>
@@ -13852,7 +13903,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="244" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A244" s="2">
         <v>2390013</v>
       </c>
@@ -13896,7 +13947,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="252" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="L252" s="1"/>
     </row>
   </sheetData>

--- a/POD_2026-27_11-5-2026.xlsx
+++ b/POD_2026-27_11-5-2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10811"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\misael.marriaga\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guillermo.vera/Desktop/POD2627/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA325700-3223-4D20-AD90-9DA0C4D4001D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAD379A7-2F72-2147-AF37-A7BE160BC0B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="POD" sheetId="1" r:id="rId1"/>
@@ -419,12 +419,6 @@
     <t>G_BIOMED_EXT822_1A(F) (2229002)</t>
   </si>
   <si>
-    <t>L=&gt;(13:00-15:00)[21/09/26, 19/10/26, 16/11/26, 14/12/26] | (17:00-19:00)[05/10/26, 30/11/26]</t>
-  </si>
-  <si>
-    <t>L=&gt;(17:00-19:00)[21/09/26, 19/10/26, 16/11/26, 14/12/26] | (13:00-15:00)[05/10/26, 30/11/26]</t>
-  </si>
-  <si>
     <t>(2386) GRADO EN INGENIERÍA EN TECNOLOGÍAS DE TELECOMUNICACIÓN (FUENLABRADA)</t>
   </si>
   <si>
@@ -1701,6 +1695,12 @@
   </si>
   <si>
     <t>Enrique Benito Matías (6)</t>
+  </si>
+  <si>
+    <t>L=&gt;(13:00-15:00)[21/09/26, 19/10/26, 16/11/26, 14/12/26, 05/10/26, 30/11/26]</t>
+  </si>
+  <si>
+    <t>L=&gt;(17:00-19:00)[21/09/26, 19/10/26, 16/11/26, 14/12/26, 05/10/26, 30/11/26]</t>
   </si>
 </sst>
 </file>
@@ -1773,12 +1773,12 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1797,9 +1797,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1837,7 +1837,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1943,7 +1943,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2085,7 +2085,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2094,53 +2094,53 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S252"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="71.26953125" customWidth="1"/>
+    <col min="2" max="2" width="71.33203125" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="9.1796875" customWidth="1"/>
-    <col min="5" max="5" width="20.1796875" customWidth="1"/>
-    <col min="6" max="6" width="64.1796875" customWidth="1"/>
-    <col min="7" max="7" width="20.81640625" customWidth="1"/>
-    <col min="8" max="8" width="6.453125" customWidth="1"/>
-    <col min="9" max="9" width="7.81640625" customWidth="1"/>
-    <col min="10" max="10" width="6.453125" customWidth="1"/>
-    <col min="11" max="11" width="107.1796875" customWidth="1"/>
-    <col min="12" max="12" width="53.7265625" customWidth="1"/>
-    <col min="13" max="13" width="12.7265625" customWidth="1"/>
-    <col min="14" max="14" width="36.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="36.453125" customWidth="1"/>
-    <col min="16" max="16" width="20.81640625" customWidth="1"/>
+    <col min="4" max="4" width="9.1640625" customWidth="1"/>
+    <col min="5" max="5" width="20.1640625" customWidth="1"/>
+    <col min="6" max="6" width="64.1640625" customWidth="1"/>
+    <col min="7" max="7" width="20.83203125" customWidth="1"/>
+    <col min="8" max="8" width="6.5" customWidth="1"/>
+    <col min="9" max="9" width="7.83203125" customWidth="1"/>
+    <col min="10" max="10" width="6.5" customWidth="1"/>
+    <col min="11" max="11" width="107.1640625" customWidth="1"/>
+    <col min="12" max="12" width="53.6640625" customWidth="1"/>
+    <col min="13" max="13" width="12.6640625" customWidth="1"/>
+    <col min="14" max="14" width="36.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="36.5" customWidth="1"/>
+    <col min="16" max="16" width="20.83203125" customWidth="1"/>
     <col min="17" max="17" width="52" customWidth="1"/>
-    <col min="18" max="18" width="32.453125" customWidth="1"/>
-    <col min="19" max="19" width="16.81640625" customWidth="1"/>
+    <col min="18" max="18" width="32.5" customWidth="1"/>
+    <col min="19" max="19" width="16.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
-      <c r="O1" s="8"/>
-      <c r="P1" s="8"/>
-      <c r="Q1" s="8"/>
-      <c r="R1" s="8"/>
-      <c r="S1" s="8"/>
-    </row>
-    <row r="2" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+      <c r="S1" s="10"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2184,10 +2184,10 @@
         <v>14</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="Q2" s="1" t="s">
         <v>15</v>
@@ -2199,7 +2199,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>2291005</v>
       </c>
@@ -2243,7 +2243,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>2291009</v>
       </c>
@@ -2287,7 +2287,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>2240005</v>
       </c>
@@ -2334,7 +2334,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>2240009</v>
       </c>
@@ -2381,7 +2381,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>2251011</v>
       </c>
@@ -2425,7 +2425,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>2327002</v>
       </c>
@@ -2463,7 +2463,7 @@
         <v>26</v>
       </c>
       <c r="N8" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="Q8" t="s">
         <v>27</v>
@@ -2472,7 +2472,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>2327002</v>
       </c>
@@ -2510,7 +2510,7 @@
         <v>26</v>
       </c>
       <c r="N9" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="Q9" t="s">
         <v>27</v>
@@ -2519,7 +2519,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>2327002</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>26</v>
       </c>
       <c r="N10" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="Q10" t="s">
         <v>27</v>
@@ -2566,7 +2566,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>2327007</v>
       </c>
@@ -2604,10 +2604,10 @@
         <v>26</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="Q11" t="s">
         <v>27</v>
@@ -2616,7 +2616,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>2327007</v>
       </c>
@@ -2654,10 +2654,10 @@
         <v>26</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="Q12" t="s">
         <v>27</v>
@@ -2666,7 +2666,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>2327007</v>
       </c>
@@ -2704,10 +2704,10 @@
         <v>26</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="O13" s="6" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="Q13" t="s">
         <v>27</v>
@@ -2716,7 +2716,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>2327015</v>
       </c>
@@ -2754,7 +2754,7 @@
         <v>26</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="Q14" t="s">
         <v>27</v>
@@ -2763,7 +2763,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>2327015</v>
       </c>
@@ -2801,7 +2801,7 @@
         <v>26</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="Q15" t="s">
         <v>27</v>
@@ -2810,7 +2810,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>2327015</v>
       </c>
@@ -2848,7 +2848,7 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="Q16" t="s">
         <v>27</v>
@@ -2857,7 +2857,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>2360001</v>
       </c>
@@ -2901,7 +2901,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>2360002</v>
       </c>
@@ -2939,7 +2939,7 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="Q18" t="s">
         <v>27</v>
@@ -2948,7 +2948,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>2382005</v>
       </c>
@@ -2989,7 +2989,7 @@
         <v>26</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="Q19" t="s">
         <v>27</v>
@@ -2998,7 +2998,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>2382005</v>
       </c>
@@ -3039,7 +3039,7 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="Q20" t="s">
         <v>27</v>
@@ -3048,7 +3048,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>2382005</v>
       </c>
@@ -3089,7 +3089,7 @@
         <v>26</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="Q21" t="s">
         <v>27</v>
@@ -3098,7 +3098,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>2382005</v>
       </c>
@@ -3139,7 +3139,7 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="Q22" t="s">
         <v>27</v>
@@ -3148,7 +3148,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>2382005</v>
       </c>
@@ -3189,7 +3189,7 @@
         <v>26</v>
       </c>
       <c r="N23" s="6" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="Q23" t="s">
         <v>27</v>
@@ -3198,7 +3198,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>2382005</v>
       </c>
@@ -3239,7 +3239,7 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="Q24" t="s">
         <v>27</v>
@@ -3248,7 +3248,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>2382010</v>
       </c>
@@ -3289,7 +3289,7 @@
         <v>26</v>
       </c>
       <c r="N25" s="6" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="Q25" t="s">
         <v>27</v>
@@ -3298,7 +3298,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>2382010</v>
       </c>
@@ -3339,7 +3339,7 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="Q26" t="s">
         <v>27</v>
@@ -3348,7 +3348,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>2382010</v>
       </c>
@@ -3389,7 +3389,7 @@
         <v>26</v>
       </c>
       <c r="N27" s="6" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="Q27" t="s">
         <v>27</v>
@@ -3398,7 +3398,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>2382010</v>
       </c>
@@ -3439,7 +3439,7 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="Q28" t="s">
         <v>27</v>
@@ -3448,7 +3448,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>2382010</v>
       </c>
@@ -3485,8 +3485,8 @@
       <c r="M29" t="s">
         <v>26</v>
       </c>
-      <c r="N29" s="9" t="s">
-        <v>552</v>
+      <c r="N29" s="7" t="s">
+        <v>550</v>
       </c>
       <c r="Q29" t="s">
         <v>27</v>
@@ -3495,7 +3495,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>2382010</v>
       </c>
@@ -3536,7 +3536,7 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="Q30" t="s">
         <v>27</v>
@@ -3545,7 +3545,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>2383001</v>
       </c>
@@ -3586,7 +3586,7 @@
         <v>26</v>
       </c>
       <c r="N31" s="6" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="Q31" t="s">
         <v>27</v>
@@ -3595,7 +3595,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>2383001</v>
       </c>
@@ -3633,7 +3633,7 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="Q32" t="s">
         <v>27</v>
@@ -3642,7 +3642,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>2383001</v>
       </c>
@@ -3680,7 +3680,7 @@
         <v>26</v>
       </c>
       <c r="N33" s="6" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="Q33" t="s">
         <v>27</v>
@@ -3689,7 +3689,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>2383001</v>
       </c>
@@ -3730,7 +3730,7 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="Q34" t="s">
         <v>27</v>
@@ -3739,7 +3739,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>2383001</v>
       </c>
@@ -3780,7 +3780,7 @@
         <v>26</v>
       </c>
       <c r="N35" s="6" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="Q35" t="s">
         <v>27</v>
@@ -3789,7 +3789,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>2383001</v>
       </c>
@@ -3830,7 +3830,7 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="Q36" t="s">
         <v>27</v>
@@ -3839,7 +3839,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>2383002</v>
       </c>
@@ -3880,7 +3880,7 @@
         <v>26</v>
       </c>
       <c r="N37" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="Q37" t="s">
         <v>27</v>
@@ -3889,7 +3889,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>2383002</v>
       </c>
@@ -3927,7 +3927,7 @@
         <v>26</v>
       </c>
       <c r="N38" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="Q38" t="s">
         <v>27</v>
@@ -3936,7 +3936,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>2383002</v>
       </c>
@@ -3974,7 +3974,7 @@
         <v>26</v>
       </c>
       <c r="N39" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="Q39" t="s">
         <v>27</v>
@@ -3983,7 +3983,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>2383002</v>
       </c>
@@ -4024,7 +4024,7 @@
         <v>26</v>
       </c>
       <c r="N40" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="Q40" t="s">
         <v>27</v>
@@ -4033,7 +4033,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>2383002</v>
       </c>
@@ -4074,7 +4074,7 @@
         <v>26</v>
       </c>
       <c r="N41" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="Q41" t="s">
         <v>27</v>
@@ -4083,7 +4083,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>2383002</v>
       </c>
@@ -4124,7 +4124,7 @@
         <v>26</v>
       </c>
       <c r="N42" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="Q42" t="s">
         <v>27</v>
@@ -4133,7 +4133,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:18" ht="48" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>2383007</v>
       </c>
@@ -4183,7 +4183,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:18" ht="48" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>2383007</v>
       </c>
@@ -4233,7 +4233,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>2384001</v>
       </c>
@@ -4274,7 +4274,7 @@
         <v>26</v>
       </c>
       <c r="N45" s="6" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="Q45" t="s">
         <v>27</v>
@@ -4283,7 +4283,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>2384001</v>
       </c>
@@ -4324,7 +4324,7 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="Q46" t="s">
         <v>27</v>
@@ -4333,7 +4333,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>2384001</v>
       </c>
@@ -4374,7 +4374,7 @@
         <v>26</v>
       </c>
       <c r="N47" s="6" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="Q47" t="s">
         <v>27</v>
@@ -4383,7 +4383,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
         <v>2384005</v>
       </c>
@@ -4424,7 +4424,7 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="Q48" t="s">
         <v>27</v>
@@ -4433,7 +4433,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
         <v>2384005</v>
       </c>
@@ -4474,7 +4474,7 @@
         <v>26</v>
       </c>
       <c r="N49" s="6" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="Q49" t="s">
         <v>27</v>
@@ -4483,7 +4483,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
         <v>2384005</v>
       </c>
@@ -4524,7 +4524,7 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="Q50" t="s">
         <v>27</v>
@@ -4533,7 +4533,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="51" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
         <v>2385001</v>
       </c>
@@ -4574,7 +4574,7 @@
         <v>26</v>
       </c>
       <c r="N51" s="6" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="Q51" t="s">
         <v>27</v>
@@ -4583,7 +4583,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="52" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
         <v>2385001</v>
       </c>
@@ -4624,7 +4624,7 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="Q52" t="s">
         <v>27</v>
@@ -4633,7 +4633,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="53" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
         <v>2385001</v>
       </c>
@@ -4674,7 +4674,7 @@
         <v>26</v>
       </c>
       <c r="N53" s="6" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="Q53" t="s">
         <v>27</v>
@@ -4683,7 +4683,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
         <v>2385005</v>
       </c>
@@ -4724,7 +4724,7 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="Q54" t="s">
         <v>27</v>
@@ -4733,7 +4733,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
         <v>2385005</v>
       </c>
@@ -4764,8 +4764,8 @@
       <c r="J55" t="s">
         <v>24</v>
       </c>
-      <c r="K55" t="s">
-        <v>127</v>
+      <c r="K55" s="6" t="s">
+        <v>553</v>
       </c>
       <c r="L55" t="s">
         <v>126</v>
@@ -4774,7 +4774,7 @@
         <v>26</v>
       </c>
       <c r="N55" s="6" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="Q55" t="s">
         <v>27</v>
@@ -4783,7 +4783,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="56" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
         <v>2385005</v>
       </c>
@@ -4814,8 +4814,8 @@
       <c r="J56" t="s">
         <v>24</v>
       </c>
-      <c r="K56" t="s">
-        <v>128</v>
+      <c r="K56" s="6" t="s">
+        <v>554</v>
       </c>
       <c r="L56" t="s">
         <v>126</v>
@@ -4824,7 +4824,7 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="Q56" t="s">
         <v>27</v>
@@ -4833,12 +4833,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="57" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
         <v>2386001</v>
       </c>
       <c r="B57" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C57" t="s">
         <v>43</v>
@@ -4865,10 +4865,10 @@
         <v>41</v>
       </c>
       <c r="K57" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="L57" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="M57" t="s">
         <v>26</v>
@@ -4880,12 +4880,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="58" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
         <v>2386001</v>
       </c>
       <c r="B58" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C58" t="s">
         <v>43</v>
@@ -4912,10 +4912,10 @@
         <v>41</v>
       </c>
       <c r="K58" s="6" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="L58" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="M58" t="s">
         <v>26</v>
@@ -4927,12 +4927,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="59" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
         <v>2386001</v>
       </c>
       <c r="B59" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C59" t="s">
         <v>43</v>
@@ -4959,10 +4959,10 @@
         <v>41</v>
       </c>
       <c r="K59" s="6" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="L59" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="M59" t="s">
         <v>26</v>
@@ -4974,12 +4974,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="60" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
         <v>2386001</v>
       </c>
       <c r="B60" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C60" t="s">
         <v>43</v>
@@ -5000,17 +5000,17 @@
         <v>44</v>
       </c>
       <c r="I60" t="s">
+        <v>131</v>
+      </c>
+      <c r="J60" t="s">
+        <v>41</v>
+      </c>
+      <c r="K60" t="s">
+        <v>132</v>
+      </c>
+      <c r="L60" t="s">
         <v>133</v>
       </c>
-      <c r="J60" t="s">
-        <v>41</v>
-      </c>
-      <c r="K60" t="s">
-        <v>134</v>
-      </c>
-      <c r="L60" t="s">
-        <v>135</v>
-      </c>
       <c r="M60" t="s">
         <v>26</v>
       </c>
@@ -5021,12 +5021,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="61" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
         <v>2386001</v>
       </c>
       <c r="B61" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C61" t="s">
         <v>43</v>
@@ -5047,16 +5047,16 @@
         <v>16</v>
       </c>
       <c r="I61" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J61" t="s">
         <v>41</v>
       </c>
       <c r="K61" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="L61" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="M61" t="s">
         <v>26</v>
@@ -5068,12 +5068,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="62" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
         <v>2386001</v>
       </c>
       <c r="B62" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C62" t="s">
         <v>43</v>
@@ -5094,16 +5094,16 @@
         <v>16</v>
       </c>
       <c r="I62" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="J62" t="s">
         <v>41</v>
       </c>
       <c r="K62" s="6" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="L62" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="M62" t="s">
         <v>26</v>
@@ -5115,12 +5115,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="63" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
         <v>2386002</v>
       </c>
       <c r="B63" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C63" t="s">
         <v>43</v>
@@ -5147,10 +5147,10 @@
         <v>41</v>
       </c>
       <c r="K63" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="L63" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="M63" t="s">
         <v>26</v>
@@ -5162,12 +5162,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="64" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
         <v>2386002</v>
       </c>
       <c r="B64" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C64" t="s">
         <v>43</v>
@@ -5188,25 +5188,25 @@
         <v>76</v>
       </c>
       <c r="I64" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="J64" t="s">
         <v>41</v>
       </c>
       <c r="K64" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L64" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="M64" t="s">
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="Q64" t="s">
         <v>27</v>
@@ -5215,12 +5215,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="65" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
         <v>2387009</v>
       </c>
       <c r="B65" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C65" t="s">
         <v>43</v>
@@ -5247,10 +5247,10 @@
         <v>41</v>
       </c>
       <c r="K65" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="L65" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="M65" t="s">
         <v>26</v>
@@ -5262,12 +5262,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="66" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
         <v>2387009</v>
       </c>
       <c r="B66" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C66" t="s">
         <v>43</v>
@@ -5294,10 +5294,10 @@
         <v>41</v>
       </c>
       <c r="K66" s="6" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="L66" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="M66" t="s">
         <v>26</v>
@@ -5309,12 +5309,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="67" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
         <v>2387009</v>
       </c>
       <c r="B67" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C67" t="s">
         <v>43</v>
@@ -5341,10 +5341,10 @@
         <v>41</v>
       </c>
       <c r="K67" s="6" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="L67" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="M67" t="s">
         <v>26</v>
@@ -5356,12 +5356,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="68" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
         <v>2387016</v>
       </c>
       <c r="B68" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C68" t="s">
         <v>43</v>
@@ -5388,13 +5388,13 @@
         <v>24</v>
       </c>
       <c r="K68" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="M68" t="s">
         <v>26</v>
       </c>
       <c r="N68" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="Q68" t="s">
         <v>27</v>
@@ -5403,12 +5403,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="69" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
         <v>2387016</v>
       </c>
       <c r="B69" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C69" t="s">
         <v>43</v>
@@ -5435,13 +5435,13 @@
         <v>24</v>
       </c>
       <c r="K69" s="6" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="M69" t="s">
         <v>26</v>
       </c>
       <c r="N69" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="Q69" t="s">
         <v>27</v>
@@ -5450,12 +5450,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="70" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
         <v>2387016</v>
       </c>
       <c r="B70" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C70" t="s">
         <v>43</v>
@@ -5482,13 +5482,13 @@
         <v>24</v>
       </c>
       <c r="K70" s="6" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="M70" t="s">
         <v>26</v>
       </c>
       <c r="N70" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="Q70" t="s">
         <v>27</v>
@@ -5497,15 +5497,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="71" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
         <v>2265020</v>
       </c>
       <c r="B71" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C71" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D71" s="2">
         <v>2</v>
@@ -5514,7 +5514,7 @@
         <v>34</v>
       </c>
       <c r="F71" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G71" t="s">
         <v>22</v>
@@ -5529,13 +5529,13 @@
         <v>24</v>
       </c>
       <c r="K71" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="M71" t="s">
         <v>26</v>
       </c>
       <c r="N71" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="O71" s="3"/>
       <c r="Q71" t="s">
@@ -5545,15 +5545,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="72" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
         <v>2029018</v>
       </c>
       <c r="B72" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C72" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D72" s="2">
         <v>2</v>
@@ -5562,7 +5562,7 @@
         <v>20</v>
       </c>
       <c r="F72" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G72" t="s">
         <v>39</v>
@@ -5577,10 +5577,10 @@
         <v>24</v>
       </c>
       <c r="K72" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="L72" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="M72" t="s">
         <v>26</v>
@@ -5592,15 +5592,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="73" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
         <v>2030013</v>
       </c>
       <c r="B73" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C73" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D73" s="2">
         <v>2</v>
@@ -5609,7 +5609,7 @@
         <v>34</v>
       </c>
       <c r="F73" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G73" t="s">
         <v>22</v>
@@ -5624,10 +5624,10 @@
         <v>24</v>
       </c>
       <c r="K73" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="L73" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="M73" t="s">
         <v>26</v>
@@ -5639,24 +5639,24 @@
         <v>28</v>
       </c>
     </row>
-    <row r="74" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
         <v>2031001</v>
       </c>
       <c r="B74" t="s">
+        <v>157</v>
+      </c>
+      <c r="C74" t="s">
+        <v>150</v>
+      </c>
+      <c r="D74" s="2">
+        <v>1</v>
+      </c>
+      <c r="E74" t="s">
+        <v>158</v>
+      </c>
+      <c r="F74" t="s">
         <v>159</v>
-      </c>
-      <c r="C74" t="s">
-        <v>152</v>
-      </c>
-      <c r="D74" s="2">
-        <v>1</v>
-      </c>
-      <c r="E74" t="s">
-        <v>160</v>
-      </c>
-      <c r="F74" t="s">
-        <v>161</v>
       </c>
       <c r="G74" t="s">
         <v>22</v>
@@ -5683,15 +5683,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="75" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
         <v>2032001</v>
       </c>
       <c r="B75" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C75" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D75" s="2">
         <v>1</v>
@@ -5700,7 +5700,7 @@
         <v>20</v>
       </c>
       <c r="F75" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G75" t="s">
         <v>22</v>
@@ -5715,16 +5715,16 @@
         <v>41</v>
       </c>
       <c r="K75" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="L75" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="M75" t="s">
         <v>26</v>
       </c>
       <c r="N75" s="6" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="Q75" t="s">
         <v>27</v>
@@ -5733,15 +5733,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="76" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
         <v>2032007</v>
       </c>
       <c r="B76" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C76" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D76" s="2">
         <v>1</v>
@@ -5765,17 +5765,17 @@
         <v>41</v>
       </c>
       <c r="K76" t="s">
+        <v>164</v>
+      </c>
+      <c r="L76" t="s">
+        <v>165</v>
+      </c>
+      <c r="M76" t="s">
+        <v>26</v>
+      </c>
+      <c r="N76" t="s">
         <v>166</v>
       </c>
-      <c r="L76" t="s">
-        <v>167</v>
-      </c>
-      <c r="M76" t="s">
-        <v>26</v>
-      </c>
-      <c r="N76" t="s">
-        <v>168</v>
-      </c>
       <c r="Q76" t="s">
         <v>27</v>
       </c>
@@ -5783,15 +5783,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="77" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
         <v>2032009</v>
       </c>
       <c r="B77" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C77" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D77" s="2">
         <v>1</v>
@@ -5815,13 +5815,13 @@
         <v>41</v>
       </c>
       <c r="K77" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="M77" t="s">
         <v>26</v>
       </c>
       <c r="N77" s="6" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="Q77" t="s">
         <v>27</v>
@@ -5830,15 +5830,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="78" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
         <v>2033001</v>
       </c>
       <c r="B78" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C78" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D78" s="2">
         <v>1</v>
@@ -5847,7 +5847,7 @@
         <v>20</v>
       </c>
       <c r="F78" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G78" t="s">
         <v>22</v>
@@ -5862,10 +5862,10 @@
         <v>41</v>
       </c>
       <c r="K78" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L78" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="M78" t="s">
         <v>26</v>
@@ -5877,15 +5877,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="79" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
         <v>2033002</v>
       </c>
       <c r="B79" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C79" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D79" s="2">
         <v>1</v>
@@ -5894,7 +5894,7 @@
         <v>20</v>
       </c>
       <c r="F79" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G79" t="s">
         <v>22</v>
@@ -5909,19 +5909,19 @@
         <v>41</v>
       </c>
       <c r="K79" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="L79" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="M79" t="s">
         <v>26</v>
       </c>
       <c r="N79" s="5" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="O79" s="5" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="Q79" t="s">
         <v>27</v>
@@ -5930,15 +5930,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="80" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
         <v>2033006</v>
       </c>
       <c r="B80" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C80" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D80" s="2">
         <v>1</v>
@@ -5962,17 +5962,17 @@
         <v>41</v>
       </c>
       <c r="K80" t="s">
+        <v>175</v>
+      </c>
+      <c r="L80" t="s">
+        <v>176</v>
+      </c>
+      <c r="M80" t="s">
+        <v>26</v>
+      </c>
+      <c r="N80" t="s">
         <v>177</v>
       </c>
-      <c r="L80" t="s">
-        <v>178</v>
-      </c>
-      <c r="M80" t="s">
-        <v>26</v>
-      </c>
-      <c r="N80" t="s">
-        <v>179</v>
-      </c>
       <c r="Q80" t="s">
         <v>27</v>
       </c>
@@ -5980,15 +5980,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="81" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
         <v>2034001</v>
       </c>
       <c r="B81" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C81" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D81" s="2">
         <v>1</v>
@@ -5997,7 +5997,7 @@
         <v>20</v>
       </c>
       <c r="F81" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G81" t="s">
         <v>22</v>
@@ -6012,16 +6012,16 @@
         <v>41</v>
       </c>
       <c r="K81" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L81" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="M81" t="s">
         <v>26</v>
       </c>
       <c r="N81" s="6" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="Q81" t="s">
         <v>27</v>
@@ -6030,15 +6030,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="82" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
         <v>2034002</v>
       </c>
       <c r="B82" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C82" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D82" s="2">
         <v>1</v>
@@ -6047,7 +6047,7 @@
         <v>20</v>
       </c>
       <c r="F82" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G82" t="s">
         <v>22</v>
@@ -6062,19 +6062,19 @@
         <v>41</v>
       </c>
       <c r="K82" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="L82" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="M82" t="s">
         <v>26</v>
       </c>
       <c r="N82" s="5" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="O82" s="5" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="Q82" t="s">
         <v>27</v>
@@ -6083,15 +6083,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="83" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
         <v>2034006</v>
       </c>
       <c r="B83" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C83" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D83" s="2">
         <v>1</v>
@@ -6115,16 +6115,16 @@
         <v>41</v>
       </c>
       <c r="K83" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="L83" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="M83" t="s">
         <v>26</v>
       </c>
       <c r="N83" s="6" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="Q83" t="s">
         <v>27</v>
@@ -6133,15 +6133,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="84" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
         <v>2061001</v>
       </c>
       <c r="B84" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C84" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D84" s="2">
         <v>1</v>
@@ -6150,7 +6150,7 @@
         <v>20</v>
       </c>
       <c r="F84" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G84" t="s">
         <v>22</v>
@@ -6177,15 +6177,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="85" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
         <v>2061002</v>
       </c>
       <c r="B85" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C85" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D85" s="2">
         <v>1</v>
@@ -6194,7 +6194,7 @@
         <v>20</v>
       </c>
       <c r="F85" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G85" t="s">
         <v>22</v>
@@ -6215,7 +6215,7 @@
         <v>26</v>
       </c>
       <c r="N85" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="Q85" t="s">
         <v>27</v>
@@ -6224,15 +6224,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="86" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
         <v>2061006</v>
       </c>
       <c r="B86" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C86" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D86" s="2">
         <v>1</v>
@@ -6268,15 +6268,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="87" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
         <v>2107013</v>
       </c>
       <c r="B87" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C87" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D87" s="2">
         <v>2</v>
@@ -6285,7 +6285,7 @@
         <v>20</v>
       </c>
       <c r="F87" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G87" t="s">
         <v>39</v>
@@ -6300,10 +6300,10 @@
         <v>24</v>
       </c>
       <c r="K87" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="L87" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="M87" t="s">
         <v>26</v>
@@ -6315,15 +6315,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="88" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
         <v>2143016</v>
       </c>
       <c r="B88" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C88" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D88" s="2">
         <v>2</v>
@@ -6332,7 +6332,7 @@
         <v>20</v>
       </c>
       <c r="F88" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G88" t="s">
         <v>39</v>
@@ -6347,10 +6347,10 @@
         <v>24</v>
       </c>
       <c r="K88" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="L88" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M88" t="s">
         <v>26</v>
@@ -6362,15 +6362,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="89" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
         <v>2148011</v>
       </c>
       <c r="B89" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C89" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D89" s="2">
         <v>2</v>
@@ -6379,7 +6379,7 @@
         <v>20</v>
       </c>
       <c r="F89" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G89" t="s">
         <v>39</v>
@@ -6394,7 +6394,7 @@
         <v>24</v>
       </c>
       <c r="K89" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="M89" t="s">
         <v>26</v>
@@ -6406,15 +6406,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="90" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
         <v>2175020</v>
       </c>
       <c r="B90" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C90" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D90" s="2">
         <v>2</v>
@@ -6423,7 +6423,7 @@
         <v>34</v>
       </c>
       <c r="F90" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G90" t="s">
         <v>22</v>
@@ -6438,10 +6438,10 @@
         <v>24</v>
       </c>
       <c r="K90" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="L90" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="M90" t="s">
         <v>26</v>
@@ -6453,15 +6453,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="91" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
         <v>2285005</v>
       </c>
       <c r="B91" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C91" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D91" s="2">
         <v>1</v>
@@ -6470,7 +6470,7 @@
         <v>20</v>
       </c>
       <c r="F91" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G91" t="s">
         <v>22</v>
@@ -6485,16 +6485,16 @@
         <v>41</v>
       </c>
       <c r="K91" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="M91" t="s">
         <v>26</v>
       </c>
       <c r="N91" s="5" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="O91" s="5" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="Q91" t="s">
         <v>27</v>
@@ -6503,15 +6503,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="92" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
         <v>2285006</v>
       </c>
       <c r="B92" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C92" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D92" s="2">
         <v>1</v>
@@ -6535,13 +6535,13 @@
         <v>41</v>
       </c>
       <c r="K92" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="M92" t="s">
         <v>26</v>
       </c>
       <c r="N92" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="Q92" t="s">
         <v>27</v>
@@ -6550,15 +6550,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="93" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
         <v>2285007</v>
       </c>
       <c r="B93" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C93" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D93" s="2">
         <v>1</v>
@@ -6567,7 +6567,7 @@
         <v>34</v>
       </c>
       <c r="F93" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="G93" t="s">
         <v>39</v>
@@ -6582,13 +6582,13 @@
         <v>41</v>
       </c>
       <c r="K93" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="M93" t="s">
         <v>26</v>
       </c>
       <c r="N93" s="6" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="Q93" t="s">
         <v>27</v>
@@ -6597,15 +6597,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="94" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
         <v>2286015</v>
       </c>
       <c r="B94" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C94" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D94" s="2">
         <v>2</v>
@@ -6614,7 +6614,7 @@
         <v>20</v>
       </c>
       <c r="F94" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G94" t="s">
         <v>39</v>
@@ -6629,7 +6629,7 @@
         <v>24</v>
       </c>
       <c r="K94" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="M94" t="s">
         <v>26</v>
@@ -6641,15 +6641,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="95" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
         <v>2338044</v>
       </c>
       <c r="B95" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C95" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D95" s="2">
         <v>1</v>
@@ -6685,15 +6685,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="96" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
         <v>2342014</v>
       </c>
       <c r="B96" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C96" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D96" s="2">
         <v>2</v>
@@ -6702,7 +6702,7 @@
         <v>20</v>
       </c>
       <c r="F96" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G96" t="s">
         <v>39</v>
@@ -6717,13 +6717,13 @@
         <v>41</v>
       </c>
       <c r="K96" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="M96" t="s">
         <v>26</v>
       </c>
       <c r="N96" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="Q96" t="s">
         <v>27</v>
@@ -6732,15 +6732,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="97" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
         <v>5</v>
       </c>
       <c r="B97" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C97" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D97" s="2">
         <v>4</v>
@@ -6749,7 +6749,7 @@
         <v>20</v>
       </c>
       <c r="F97" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G97" t="s">
         <v>39</v>
@@ -6764,13 +6764,13 @@
         <v>41</v>
       </c>
       <c r="K97" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="M97" t="s">
         <v>26</v>
       </c>
       <c r="N97" s="5" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="O97" s="3"/>
       <c r="Q97" t="s">
@@ -6780,15 +6780,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="98" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
         <v>2343027</v>
       </c>
       <c r="B98" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C98" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D98" s="2">
         <v>3</v>
@@ -6797,7 +6797,7 @@
         <v>34</v>
       </c>
       <c r="F98" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G98" t="s">
         <v>39</v>
@@ -6812,13 +6812,13 @@
         <v>24</v>
       </c>
       <c r="K98" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="M98" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="N98" s="5" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="O98" s="3"/>
       <c r="Q98" t="s">
@@ -6828,15 +6828,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="99" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
         <v>2343027</v>
       </c>
       <c r="B99" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C99" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D99" s="2">
         <v>3</v>
@@ -6845,7 +6845,7 @@
         <v>34</v>
       </c>
       <c r="F99" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G99" t="s">
         <v>39</v>
@@ -6860,14 +6860,14 @@
         <v>24</v>
       </c>
       <c r="K99" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="M99" t="s">
+        <v>211</v>
+      </c>
+      <c r="N99" t="s">
         <v>213</v>
       </c>
-      <c r="N99" t="s">
-        <v>215</v>
-      </c>
       <c r="Q99" t="s">
         <v>27</v>
       </c>
@@ -6875,15 +6875,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="100" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
         <v>2343027</v>
       </c>
       <c r="B100" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C100" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D100" s="2">
         <v>3</v>
@@ -6892,7 +6892,7 @@
         <v>34</v>
       </c>
       <c r="F100" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G100" t="s">
         <v>39</v>
@@ -6907,10 +6907,10 @@
         <v>24</v>
       </c>
       <c r="K100" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="M100" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="N100" s="3"/>
       <c r="O100" s="3"/>
@@ -6921,15 +6921,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="101" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
         <v>2347001</v>
       </c>
       <c r="B101" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C101" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D101" s="2">
         <v>1</v>
@@ -6953,17 +6953,17 @@
         <v>41</v>
       </c>
       <c r="K101" t="s">
+        <v>215</v>
+      </c>
+      <c r="L101" t="s">
+        <v>216</v>
+      </c>
+      <c r="M101" t="s">
+        <v>26</v>
+      </c>
+      <c r="N101" t="s">
         <v>217</v>
       </c>
-      <c r="L101" t="s">
-        <v>218</v>
-      </c>
-      <c r="M101" t="s">
-        <v>26</v>
-      </c>
-      <c r="N101" t="s">
-        <v>219</v>
-      </c>
       <c r="Q101" t="s">
         <v>27</v>
       </c>
@@ -6971,15 +6971,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="102" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
         <v>2347003</v>
       </c>
       <c r="B102" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C102" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D102" s="2">
         <v>1</v>
@@ -6988,7 +6988,7 @@
         <v>20</v>
       </c>
       <c r="F102" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G102" t="s">
         <v>39</v>
@@ -7003,16 +7003,16 @@
         <v>41</v>
       </c>
       <c r="K102" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="L102" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="M102" t="s">
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="Q102" t="s">
         <v>27</v>
@@ -7021,15 +7021,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="103" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
         <v>2347005</v>
       </c>
       <c r="B103" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C103" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D103" s="2">
         <v>1</v>
@@ -7038,7 +7038,7 @@
         <v>20</v>
       </c>
       <c r="F103" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G103" t="s">
         <v>39</v>
@@ -7053,16 +7053,16 @@
         <v>41</v>
       </c>
       <c r="K103" t="s">
+        <v>220</v>
+      </c>
+      <c r="L103" t="s">
+        <v>221</v>
+      </c>
+      <c r="M103" t="s">
+        <v>26</v>
+      </c>
+      <c r="N103" s="3" t="s">
         <v>222</v>
-      </c>
-      <c r="L103" t="s">
-        <v>223</v>
-      </c>
-      <c r="M103" t="s">
-        <v>26</v>
-      </c>
-      <c r="N103" s="3" t="s">
-        <v>224</v>
       </c>
       <c r="O103" s="3"/>
       <c r="Q103" t="s">
@@ -7072,15 +7072,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="104" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A104" s="2">
         <v>2347006</v>
       </c>
       <c r="B104" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C104" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D104" s="2">
         <v>1</v>
@@ -7089,7 +7089,7 @@
         <v>34</v>
       </c>
       <c r="F104" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="G104" t="s">
         <v>39</v>
@@ -7104,16 +7104,16 @@
         <v>41</v>
       </c>
       <c r="K104" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L104" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="M104" t="s">
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="Q104" t="s">
         <v>27</v>
@@ -7122,15 +7122,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="105" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A105" s="2">
         <v>2347007</v>
       </c>
       <c r="B105" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C105" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D105" s="2">
         <v>1</v>
@@ -7154,16 +7154,16 @@
         <v>41</v>
       </c>
       <c r="K105" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="L105" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="M105" t="s">
         <v>26</v>
       </c>
       <c r="N105" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="O105" s="3"/>
       <c r="Q105" t="s">
@@ -7173,15 +7173,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="106" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A106" s="2">
         <v>2347013</v>
       </c>
       <c r="B106" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C106" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D106" s="2">
         <v>2</v>
@@ -7190,7 +7190,7 @@
         <v>20</v>
       </c>
       <c r="F106" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G106" t="s">
         <v>39</v>
@@ -7205,16 +7205,16 @@
         <v>41</v>
       </c>
       <c r="K106" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L106" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M106" t="s">
         <v>26</v>
       </c>
       <c r="N106" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="Q106" t="s">
         <v>27</v>
@@ -7223,15 +7223,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="107" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A107" s="2">
         <v>2347014</v>
       </c>
       <c r="B107" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C107" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D107" s="2">
         <v>2</v>
@@ -7240,7 +7240,7 @@
         <v>34</v>
       </c>
       <c r="F107" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G107" t="s">
         <v>39</v>
@@ -7255,10 +7255,10 @@
         <v>41</v>
       </c>
       <c r="K107" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L107" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="M107" t="s">
         <v>26</v>
@@ -7270,15 +7270,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="108" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A108" s="2">
         <v>2347017</v>
       </c>
       <c r="B108" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C108" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D108" s="2">
         <v>2</v>
@@ -7287,7 +7287,7 @@
         <v>34</v>
       </c>
       <c r="F108" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G108" t="s">
         <v>22</v>
@@ -7302,17 +7302,17 @@
         <v>41</v>
       </c>
       <c r="K108" t="s">
+        <v>235</v>
+      </c>
+      <c r="L108" t="s">
+        <v>236</v>
+      </c>
+      <c r="M108" t="s">
+        <v>26</v>
+      </c>
+      <c r="N108" t="s">
         <v>237</v>
       </c>
-      <c r="L108" t="s">
-        <v>238</v>
-      </c>
-      <c r="M108" t="s">
-        <v>26</v>
-      </c>
-      <c r="N108" t="s">
-        <v>239</v>
-      </c>
       <c r="Q108" t="s">
         <v>27</v>
       </c>
@@ -7320,15 +7320,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="109" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A109" s="2">
         <v>2347030</v>
       </c>
       <c r="B109" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C109" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D109" s="2">
         <v>2</v>
@@ -7337,7 +7337,7 @@
         <v>34</v>
       </c>
       <c r="F109" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G109" t="s">
         <v>39</v>
@@ -7352,16 +7352,16 @@
         <v>41</v>
       </c>
       <c r="K109" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="L109" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="M109" t="s">
         <v>26</v>
       </c>
       <c r="N109" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="O109" s="3"/>
       <c r="Q109" t="s">
@@ -7371,15 +7371,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="110" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A110" s="2">
         <v>2347021</v>
       </c>
       <c r="B110" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C110" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D110" s="2">
         <v>3</v>
@@ -7388,7 +7388,7 @@
         <v>20</v>
       </c>
       <c r="F110" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="G110" t="s">
         <v>39</v>
@@ -7403,16 +7403,16 @@
         <v>41</v>
       </c>
       <c r="K110" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="L110" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="M110" t="s">
         <v>26</v>
       </c>
       <c r="N110" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="Q110" t="s">
         <v>27</v>
@@ -7421,15 +7421,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="111" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A111" s="2">
         <v>2347022</v>
       </c>
       <c r="B111" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C111" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D111" s="2">
         <v>3</v>
@@ -7438,7 +7438,7 @@
         <v>20</v>
       </c>
       <c r="F111" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="G111" t="s">
         <v>39</v>
@@ -7453,16 +7453,16 @@
         <v>41</v>
       </c>
       <c r="K111" t="s">
+        <v>245</v>
+      </c>
+      <c r="L111" t="s">
+        <v>246</v>
+      </c>
+      <c r="M111" t="s">
+        <v>26</v>
+      </c>
+      <c r="N111" s="3" t="s">
         <v>247</v>
-      </c>
-      <c r="L111" t="s">
-        <v>248</v>
-      </c>
-      <c r="M111" t="s">
-        <v>26</v>
-      </c>
-      <c r="N111" s="3" t="s">
-        <v>249</v>
       </c>
       <c r="O111" s="3"/>
       <c r="P111" s="1"/>
@@ -7473,15 +7473,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="112" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A112" s="2">
         <v>2347024</v>
       </c>
       <c r="B112" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C112" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D112" s="2">
         <v>3</v>
@@ -7490,7 +7490,7 @@
         <v>20</v>
       </c>
       <c r="F112" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G112" t="s">
         <v>39</v>
@@ -7505,16 +7505,16 @@
         <v>41</v>
       </c>
       <c r="K112" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="L112" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="M112" t="s">
         <v>26</v>
       </c>
       <c r="N112" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="Q112" t="s">
         <v>27</v>
@@ -7523,15 +7523,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="113" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A113" s="2">
         <v>2347026</v>
       </c>
       <c r="B113" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C113" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D113" s="2">
         <v>3</v>
@@ -7540,7 +7540,7 @@
         <v>34</v>
       </c>
       <c r="F113" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="G113" t="s">
         <v>39</v>
@@ -7555,16 +7555,16 @@
         <v>41</v>
       </c>
       <c r="K113" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="L113" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="M113" t="s">
         <v>26</v>
       </c>
       <c r="N113" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="O113" s="3"/>
       <c r="Q113" t="s">
@@ -7574,15 +7574,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="114" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A114" s="2">
         <v>2347027</v>
       </c>
       <c r="B114" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C114" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D114" s="2">
         <v>3</v>
@@ -7591,7 +7591,7 @@
         <v>34</v>
       </c>
       <c r="F114" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G114" t="s">
         <v>39</v>
@@ -7606,16 +7606,16 @@
         <v>41</v>
       </c>
       <c r="K114" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="L114" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="M114" t="s">
         <v>26</v>
       </c>
       <c r="N114" s="5" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="O114" s="5"/>
       <c r="Q114" t="s">
@@ -7625,15 +7625,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="115" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A115" s="2">
         <v>2347029</v>
       </c>
       <c r="B115" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C115" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D115" s="2">
         <v>3</v>
@@ -7642,7 +7642,7 @@
         <v>34</v>
       </c>
       <c r="F115" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G115" t="s">
         <v>39</v>
@@ -7657,17 +7657,17 @@
         <v>41</v>
       </c>
       <c r="K115" t="s">
+        <v>257</v>
+      </c>
+      <c r="L115" t="s">
+        <v>258</v>
+      </c>
+      <c r="M115" t="s">
+        <v>211</v>
+      </c>
+      <c r="N115" t="s">
         <v>259</v>
       </c>
-      <c r="L115" t="s">
-        <v>260</v>
-      </c>
-      <c r="M115" t="s">
-        <v>213</v>
-      </c>
-      <c r="N115" t="s">
-        <v>261</v>
-      </c>
       <c r="Q115" t="s">
         <v>27</v>
       </c>
@@ -7675,15 +7675,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="116" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A116" s="2">
         <v>2347031</v>
       </c>
       <c r="B116" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C116" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D116" s="2">
         <v>4</v>
@@ -7692,7 +7692,7 @@
         <v>20</v>
       </c>
       <c r="F116" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G116" t="s">
         <v>39</v>
@@ -7707,16 +7707,16 @@
         <v>41</v>
       </c>
       <c r="K116" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="L116" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="M116" t="s">
         <v>26</v>
       </c>
       <c r="N116" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="Q116" t="s">
         <v>27</v>
@@ -7725,15 +7725,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="117" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A117" s="2">
         <v>2347038</v>
       </c>
       <c r="B117" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C117" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D117" s="2">
         <v>4</v>
@@ -7742,10 +7742,10 @@
         <v>20</v>
       </c>
       <c r="F117" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G117" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="H117" s="2">
         <v>60</v>
@@ -7757,16 +7757,16 @@
         <v>41</v>
       </c>
       <c r="K117" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="L117" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="M117" t="s">
         <v>26</v>
       </c>
       <c r="N117" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="O117" s="3"/>
       <c r="Q117" t="s">
@@ -7776,15 +7776,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="118" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A118" s="2">
         <v>2361002</v>
       </c>
       <c r="B118" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C118" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D118" s="2">
         <v>1</v>
@@ -7808,13 +7808,13 @@
         <v>41</v>
       </c>
       <c r="K118" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="M118" t="s">
         <v>26</v>
       </c>
       <c r="N118" s="3" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="Q118" t="s">
         <v>27</v>
@@ -7823,15 +7823,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="119" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A119" s="2">
         <v>2361002</v>
       </c>
       <c r="B119" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C119" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D119" s="2">
         <v>1</v>
@@ -7855,13 +7855,13 @@
         <v>41</v>
       </c>
       <c r="K119" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M119" t="s">
         <v>26</v>
       </c>
       <c r="N119" s="3" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="Q119" t="s">
         <v>27</v>
@@ -7870,15 +7870,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="120" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A120" s="2">
         <v>2361002</v>
       </c>
       <c r="B120" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C120" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D120" s="2">
         <v>1</v>
@@ -7902,7 +7902,7 @@
         <v>41</v>
       </c>
       <c r="K120" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="M120" t="s">
         <v>26</v>
@@ -7914,15 +7914,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="121" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A121" s="2">
         <v>2361004</v>
       </c>
       <c r="B121" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C121" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D121" s="2">
         <v>1</v>
@@ -7931,7 +7931,7 @@
         <v>20</v>
       </c>
       <c r="F121" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G121" t="s">
         <v>22</v>
@@ -7946,13 +7946,13 @@
         <v>41</v>
       </c>
       <c r="K121" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M121" t="s">
         <v>26</v>
       </c>
       <c r="N121" s="6" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="Q121" t="s">
         <v>27</v>
@@ -7961,15 +7961,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="122" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A122" s="2">
         <v>2393002</v>
       </c>
       <c r="B122" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C122" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D122" s="2">
         <v>1</v>
@@ -7978,7 +7978,7 @@
         <v>20</v>
       </c>
       <c r="F122" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G122" t="s">
         <v>22</v>
@@ -7993,10 +7993,10 @@
         <v>41</v>
       </c>
       <c r="K122" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="L122" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="M122" t="s">
         <v>26</v>
@@ -8008,15 +8008,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="123" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A123" s="2">
         <v>2393002</v>
       </c>
       <c r="B123" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C123" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D123" s="2">
         <v>1</v>
@@ -8025,7 +8025,7 @@
         <v>20</v>
       </c>
       <c r="F123" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G123" t="s">
         <v>22</v>
@@ -8034,17 +8034,17 @@
         <v>20</v>
       </c>
       <c r="I123" t="s">
+        <v>274</v>
+      </c>
+      <c r="J123" t="s">
+        <v>41</v>
+      </c>
+      <c r="K123" t="s">
+        <v>275</v>
+      </c>
+      <c r="L123" t="s">
         <v>276</v>
       </c>
-      <c r="J123" t="s">
-        <v>41</v>
-      </c>
-      <c r="K123" t="s">
-        <v>277</v>
-      </c>
-      <c r="L123" t="s">
-        <v>278</v>
-      </c>
       <c r="M123" t="s">
         <v>26</v>
       </c>
@@ -8055,15 +8055,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="124" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A124" s="2">
         <v>2393002</v>
       </c>
       <c r="B124" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C124" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D124" s="2">
         <v>1</v>
@@ -8072,7 +8072,7 @@
         <v>20</v>
       </c>
       <c r="F124" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G124" t="s">
         <v>22</v>
@@ -8081,16 +8081,16 @@
         <v>20</v>
       </c>
       <c r="I124" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="J124" t="s">
         <v>41</v>
       </c>
       <c r="K124" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="L124" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="M124" t="s">
         <v>26</v>
@@ -8102,15 +8102,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="125" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A125" s="2">
         <v>2394004</v>
       </c>
       <c r="B125" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C125" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D125" s="2">
         <v>1</v>
@@ -8119,7 +8119,7 @@
         <v>20</v>
       </c>
       <c r="F125" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G125" t="s">
         <v>22</v>
@@ -8134,10 +8134,10 @@
         <v>24</v>
       </c>
       <c r="K125" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="L125" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="M125" t="s">
         <v>26</v>
@@ -8149,15 +8149,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="126" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A126" s="2">
         <v>2394004</v>
       </c>
       <c r="B126" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C126" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D126" s="2">
         <v>1</v>
@@ -8166,7 +8166,7 @@
         <v>20</v>
       </c>
       <c r="F126" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G126" t="s">
         <v>22</v>
@@ -8181,10 +8181,10 @@
         <v>24</v>
       </c>
       <c r="K126" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="L126" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="M126" t="s">
         <v>26</v>
@@ -8196,15 +8196,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="127" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A127" s="2">
         <v>2394004</v>
       </c>
       <c r="B127" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C127" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D127" s="2">
         <v>1</v>
@@ -8213,7 +8213,7 @@
         <v>20</v>
       </c>
       <c r="F127" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G127" t="s">
         <v>22</v>
@@ -8228,10 +8228,10 @@
         <v>24</v>
       </c>
       <c r="K127" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="L127" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="M127" t="s">
         <v>26</v>
@@ -8243,15 +8243,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="128" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A128" s="2">
         <v>2395003</v>
       </c>
       <c r="B128" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C128" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D128" s="2">
         <v>1</v>
@@ -8260,7 +8260,7 @@
         <v>20</v>
       </c>
       <c r="F128" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G128" t="s">
         <v>22</v>
@@ -8275,16 +8275,16 @@
         <v>41</v>
       </c>
       <c r="K128" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="L128" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="M128" t="s">
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="Q128" t="s">
         <v>27</v>
@@ -8293,15 +8293,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="129" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A129" s="2">
         <v>2395003</v>
       </c>
       <c r="B129" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C129" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D129" s="2">
         <v>1</v>
@@ -8310,7 +8310,7 @@
         <v>20</v>
       </c>
       <c r="F129" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G129" t="s">
         <v>22</v>
@@ -8325,16 +8325,16 @@
         <v>41</v>
       </c>
       <c r="K129" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="L129" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="M129" t="s">
         <v>26</v>
       </c>
       <c r="N129" s="6" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="Q129" t="s">
         <v>27</v>
@@ -8343,15 +8343,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="130" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A130" s="2">
         <v>2395003</v>
       </c>
       <c r="B130" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C130" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D130" s="2">
         <v>1</v>
@@ -8360,7 +8360,7 @@
         <v>20</v>
       </c>
       <c r="F130" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G130" t="s">
         <v>22</v>
@@ -8375,16 +8375,16 @@
         <v>41</v>
       </c>
       <c r="K130" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="L130" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="M130" t="s">
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="Q130" t="s">
         <v>27</v>
@@ -8393,15 +8393,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="131" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A131" s="2">
         <v>2396001</v>
       </c>
       <c r="B131" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C131" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D131" s="2">
         <v>1</v>
@@ -8410,7 +8410,7 @@
         <v>20</v>
       </c>
       <c r="F131" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G131" t="s">
         <v>22</v>
@@ -8425,16 +8425,16 @@
         <v>24</v>
       </c>
       <c r="K131" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="L131" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="M131" t="s">
         <v>26</v>
       </c>
       <c r="N131" s="6" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="Q131" t="s">
         <v>27</v>
@@ -8443,15 +8443,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="132" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A132" s="2">
         <v>2396001</v>
       </c>
       <c r="B132" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C132" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D132" s="2">
         <v>1</v>
@@ -8460,7 +8460,7 @@
         <v>20</v>
       </c>
       <c r="F132" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G132" t="s">
         <v>22</v>
@@ -8475,16 +8475,16 @@
         <v>24</v>
       </c>
       <c r="K132" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="L132" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="M132" t="s">
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="Q132" t="s">
         <v>27</v>
@@ -8493,15 +8493,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="133" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A133" s="2">
         <v>2396001</v>
       </c>
       <c r="B133" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C133" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D133" s="2">
         <v>1</v>
@@ -8510,7 +8510,7 @@
         <v>20</v>
       </c>
       <c r="F133" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G133" t="s">
         <v>22</v>
@@ -8525,16 +8525,16 @@
         <v>24</v>
       </c>
       <c r="K133" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="L133" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="M133" t="s">
         <v>26</v>
       </c>
       <c r="N133" s="6" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="Q133" t="s">
         <v>27</v>
@@ -8543,15 +8543,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="134" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A134" s="2">
         <v>2397003</v>
       </c>
       <c r="B134" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C134" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D134" s="2">
         <v>1</v>
@@ -8575,17 +8575,17 @@
         <v>24</v>
       </c>
       <c r="K134" t="s">
+        <v>296</v>
+      </c>
+      <c r="L134" t="s">
+        <v>297</v>
+      </c>
+      <c r="M134" t="s">
+        <v>26</v>
+      </c>
+      <c r="N134" t="s">
         <v>298</v>
       </c>
-      <c r="L134" t="s">
-        <v>299</v>
-      </c>
-      <c r="M134" t="s">
-        <v>26</v>
-      </c>
-      <c r="N134" t="s">
-        <v>300</v>
-      </c>
       <c r="Q134" t="s">
         <v>27</v>
       </c>
@@ -8593,15 +8593,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="135" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A135" s="2">
         <v>2397003</v>
       </c>
       <c r="B135" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C135" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D135" s="2">
         <v>1</v>
@@ -8625,17 +8625,17 @@
         <v>24</v>
       </c>
       <c r="K135" t="s">
+        <v>299</v>
+      </c>
+      <c r="L135" t="s">
+        <v>300</v>
+      </c>
+      <c r="M135" t="s">
+        <v>26</v>
+      </c>
+      <c r="N135" t="s">
         <v>301</v>
       </c>
-      <c r="L135" t="s">
-        <v>302</v>
-      </c>
-      <c r="M135" t="s">
-        <v>26</v>
-      </c>
-      <c r="N135" t="s">
-        <v>303</v>
-      </c>
       <c r="Q135" t="s">
         <v>27</v>
       </c>
@@ -8643,15 +8643,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="136" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A136" s="2">
         <v>2397003</v>
       </c>
       <c r="B136" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C136" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D136" s="2">
         <v>1</v>
@@ -8675,16 +8675,16 @@
         <v>24</v>
       </c>
       <c r="K136" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="L136" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="M136" t="s">
         <v>26</v>
       </c>
       <c r="N136" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="Q136" t="s">
         <v>27</v>
@@ -8693,15 +8693,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="137" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A137" s="2">
         <v>2397008</v>
       </c>
       <c r="B137" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C137" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D137" s="2">
         <v>1</v>
@@ -8725,10 +8725,10 @@
         <v>24</v>
       </c>
       <c r="K137" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="L137" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="M137" t="s">
         <v>26</v>
@@ -8740,15 +8740,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="138" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A138" s="2">
         <v>2397008</v>
       </c>
       <c r="B138" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C138" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D138" s="2">
         <v>1</v>
@@ -8772,10 +8772,10 @@
         <v>24</v>
       </c>
       <c r="K138" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="L138" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="M138" t="s">
         <v>26</v>
@@ -8787,15 +8787,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="139" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A139" s="2">
         <v>2397008</v>
       </c>
       <c r="B139" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C139" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D139" s="2">
         <v>1</v>
@@ -8819,10 +8819,10 @@
         <v>24</v>
       </c>
       <c r="K139" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="L139" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="M139" t="s">
         <v>26</v>
@@ -8834,15 +8834,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="140" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A140" s="2">
         <v>2398001</v>
       </c>
       <c r="B140" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C140" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D140" s="2">
         <v>1</v>
@@ -8866,17 +8866,17 @@
         <v>41</v>
       </c>
       <c r="K140" t="s">
+        <v>309</v>
+      </c>
+      <c r="L140" t="s">
+        <v>310</v>
+      </c>
+      <c r="M140" t="s">
+        <v>26</v>
+      </c>
+      <c r="N140" t="s">
         <v>311</v>
       </c>
-      <c r="L140" t="s">
-        <v>312</v>
-      </c>
-      <c r="M140" t="s">
-        <v>26</v>
-      </c>
-      <c r="N140" t="s">
-        <v>313</v>
-      </c>
       <c r="Q140" t="s">
         <v>27</v>
       </c>
@@ -8884,15 +8884,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="141" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A141" s="2">
         <v>2398001</v>
       </c>
       <c r="B141" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C141" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D141" s="2">
         <v>1</v>
@@ -8916,16 +8916,16 @@
         <v>41</v>
       </c>
       <c r="K141" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="L141" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="M141" t="s">
         <v>26</v>
       </c>
       <c r="N141" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="O141" s="4"/>
       <c r="Q141" t="s">
@@ -8935,15 +8935,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="142" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A142" s="2">
         <v>2398001</v>
       </c>
       <c r="B142" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C142" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D142" s="2">
         <v>1</v>
@@ -8967,16 +8967,16 @@
         <v>41</v>
       </c>
       <c r="K142" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="L142" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="M142" t="s">
         <v>26</v>
       </c>
       <c r="N142" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="O142" s="4"/>
       <c r="Q142" t="s">
@@ -8986,15 +8986,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="143" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A143" s="2">
         <v>2398006</v>
       </c>
       <c r="B143" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C143" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D143" s="2">
         <v>1</v>
@@ -9018,16 +9018,16 @@
         <v>41</v>
       </c>
       <c r="K143" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="L143" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="M143" t="s">
         <v>26</v>
       </c>
       <c r="N143" s="6" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="Q143" t="s">
         <v>27</v>
@@ -9036,15 +9036,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="144" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A144" s="2">
         <v>2398006</v>
       </c>
       <c r="B144" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C144" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D144" s="2">
         <v>1</v>
@@ -9068,16 +9068,16 @@
         <v>41</v>
       </c>
       <c r="K144" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="L144" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="M144" t="s">
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="Q144" t="s">
         <v>27</v>
@@ -9086,15 +9086,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="145" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A145" s="2">
         <v>2398006</v>
       </c>
       <c r="B145" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C145" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D145" s="2">
         <v>1</v>
@@ -9118,16 +9118,16 @@
         <v>41</v>
       </c>
       <c r="K145" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="L145" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="M145" t="s">
         <v>26</v>
       </c>
       <c r="N145" s="6" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="Q145" t="s">
         <v>27</v>
@@ -9136,15 +9136,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="146" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A146" s="2">
         <v>2398013</v>
       </c>
       <c r="B146" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C146" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D146" s="2">
         <v>2</v>
@@ -9153,7 +9153,7 @@
         <v>20</v>
       </c>
       <c r="F146" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G146" t="s">
         <v>22</v>
@@ -9168,10 +9168,10 @@
         <v>24</v>
       </c>
       <c r="K146" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="L146" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="M146" t="s">
         <v>26</v>
@@ -9183,15 +9183,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="147" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A147" s="2">
         <v>2398013</v>
       </c>
       <c r="B147" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C147" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D147" s="2">
         <v>2</v>
@@ -9200,7 +9200,7 @@
         <v>20</v>
       </c>
       <c r="F147" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G147" t="s">
         <v>22</v>
@@ -9215,10 +9215,10 @@
         <v>24</v>
       </c>
       <c r="K147" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="L147" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="M147" t="s">
         <v>26</v>
@@ -9230,15 +9230,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="148" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A148" s="2">
         <v>2398013</v>
       </c>
       <c r="B148" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C148" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D148" s="2">
         <v>2</v>
@@ -9247,7 +9247,7 @@
         <v>20</v>
       </c>
       <c r="F148" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G148" t="s">
         <v>22</v>
@@ -9262,7 +9262,7 @@
         <v>24</v>
       </c>
       <c r="K148" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="M148" t="s">
         <v>26</v>
@@ -9274,15 +9274,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="149" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A149" s="2">
         <v>2399003</v>
       </c>
       <c r="B149" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C149" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D149" s="2">
         <v>1</v>
@@ -9306,10 +9306,10 @@
         <v>41</v>
       </c>
       <c r="K149" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="L149" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="M149" t="s">
         <v>26</v>
@@ -9321,15 +9321,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="150" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A150" s="2">
         <v>2399003</v>
       </c>
       <c r="B150" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C150" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D150" s="2">
         <v>1</v>
@@ -9353,10 +9353,10 @@
         <v>41</v>
       </c>
       <c r="K150" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="L150" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="M150" t="s">
         <v>26</v>
@@ -9368,15 +9368,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="151" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A151" s="2">
         <v>2399003</v>
       </c>
       <c r="B151" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C151" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D151" s="2">
         <v>1</v>
@@ -9400,10 +9400,10 @@
         <v>41</v>
       </c>
       <c r="K151" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="L151" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="M151" t="s">
         <v>26</v>
@@ -9415,15 +9415,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="152" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A152" s="2">
         <v>2399010</v>
       </c>
       <c r="B152" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C152" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D152" s="2">
         <v>1</v>
@@ -9447,10 +9447,10 @@
         <v>41</v>
       </c>
       <c r="K152" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="L152" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="M152" t="s">
         <v>26</v>
@@ -9462,15 +9462,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="153" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A153" s="2">
         <v>2399010</v>
       </c>
       <c r="B153" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C153" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D153" s="2">
         <v>1</v>
@@ -9494,10 +9494,10 @@
         <v>41</v>
       </c>
       <c r="K153" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="L153" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="M153" t="s">
         <v>26</v>
@@ -9509,15 +9509,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="154" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A154" s="2">
         <v>2399010</v>
       </c>
       <c r="B154" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C154" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D154" s="2">
         <v>1</v>
@@ -9541,10 +9541,10 @@
         <v>41</v>
       </c>
       <c r="K154" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="L154" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="M154" t="s">
         <v>26</v>
@@ -9556,15 +9556,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="155" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A155" s="2">
         <v>2399014</v>
       </c>
       <c r="B155" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C155" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D155" s="2">
         <v>2</v>
@@ -9573,7 +9573,7 @@
         <v>20</v>
       </c>
       <c r="F155" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G155" t="s">
         <v>22</v>
@@ -9588,10 +9588,10 @@
         <v>24</v>
       </c>
       <c r="K155" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="L155" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="M155" t="s">
         <v>26</v>
@@ -9603,15 +9603,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="156" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A156" s="2">
         <v>2399014</v>
       </c>
       <c r="B156" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C156" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D156" s="2">
         <v>2</v>
@@ -9620,7 +9620,7 @@
         <v>20</v>
       </c>
       <c r="F156" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G156" t="s">
         <v>22</v>
@@ -9635,10 +9635,10 @@
         <v>24</v>
       </c>
       <c r="K156" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="L156" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="M156" t="s">
         <v>26</v>
@@ -9650,15 +9650,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="157" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A157" s="2">
         <v>2399014</v>
       </c>
       <c r="B157" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C157" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D157" s="2">
         <v>2</v>
@@ -9667,7 +9667,7 @@
         <v>20</v>
       </c>
       <c r="F157" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G157" t="s">
         <v>22</v>
@@ -9682,7 +9682,7 @@
         <v>24</v>
       </c>
       <c r="K157" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="M157" t="s">
         <v>26</v>
@@ -9694,15 +9694,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="158" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A158" s="2">
         <v>2400003</v>
       </c>
       <c r="B158" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C158" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D158" s="2">
         <v>1</v>
@@ -9726,16 +9726,16 @@
         <v>41</v>
       </c>
       <c r="K158" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="L158" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="M158" t="s">
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="Q158" t="s">
         <v>27</v>
@@ -9744,15 +9744,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="159" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A159" s="2">
         <v>2400003</v>
       </c>
       <c r="B159" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C159" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D159" s="2">
         <v>1</v>
@@ -9776,16 +9776,16 @@
         <v>41</v>
       </c>
       <c r="K159" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="L159" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="M159" t="s">
         <v>26</v>
       </c>
       <c r="N159" s="6" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="Q159" t="s">
         <v>27</v>
@@ -9794,15 +9794,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="160" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A160" s="2">
         <v>2400003</v>
       </c>
       <c r="B160" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C160" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D160" s="2">
         <v>1</v>
@@ -9826,16 +9826,16 @@
         <v>41</v>
       </c>
       <c r="K160" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="L160" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="M160" t="s">
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="Q160" t="s">
         <v>27</v>
@@ -9844,15 +9844,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="161" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A161" s="2">
         <v>2400008</v>
       </c>
       <c r="B161" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C161" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D161" s="2">
         <v>1</v>
@@ -9876,16 +9876,16 @@
         <v>41</v>
       </c>
       <c r="K161" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="L161" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="M161" t="s">
         <v>26</v>
       </c>
       <c r="N161" s="6" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="Q161" t="s">
         <v>27</v>
@@ -9894,15 +9894,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="162" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A162" s="2">
         <v>2400008</v>
       </c>
       <c r="B162" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C162" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D162" s="2">
         <v>1</v>
@@ -9926,16 +9926,16 @@
         <v>41</v>
       </c>
       <c r="K162" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="L162" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="M162" t="s">
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="Q162" t="s">
         <v>27</v>
@@ -9944,15 +9944,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="163" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A163" s="2">
         <v>2400008</v>
       </c>
       <c r="B163" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C163" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D163" s="2">
         <v>1</v>
@@ -9976,16 +9976,16 @@
         <v>41</v>
       </c>
       <c r="K163" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="L163" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M163" t="s">
         <v>26</v>
       </c>
       <c r="N163" s="6" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="Q163" t="s">
         <v>27</v>
@@ -9994,15 +9994,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="164" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A164" s="2">
         <v>2400012</v>
       </c>
       <c r="B164" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C164" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D164" s="2">
         <v>2</v>
@@ -10011,7 +10011,7 @@
         <v>20</v>
       </c>
       <c r="F164" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G164" t="s">
         <v>22</v>
@@ -10026,17 +10026,17 @@
         <v>24</v>
       </c>
       <c r="K164" t="s">
+        <v>346</v>
+      </c>
+      <c r="L164" t="s">
+        <v>347</v>
+      </c>
+      <c r="M164" t="s">
+        <v>26</v>
+      </c>
+      <c r="N164" t="s">
         <v>348</v>
       </c>
-      <c r="L164" t="s">
-        <v>349</v>
-      </c>
-      <c r="M164" t="s">
-        <v>26</v>
-      </c>
-      <c r="N164" t="s">
-        <v>350</v>
-      </c>
       <c r="Q164" t="s">
         <v>27</v>
       </c>
@@ -10044,15 +10044,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="165" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:18" ht="32" x14ac:dyDescent="0.2">
       <c r="A165" s="2">
         <v>2400012</v>
       </c>
       <c r="B165" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C165" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D165" s="2">
         <v>2</v>
@@ -10061,7 +10061,7 @@
         <v>20</v>
       </c>
       <c r="F165" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G165" t="s">
         <v>22</v>
@@ -10076,16 +10076,16 @@
         <v>24</v>
       </c>
       <c r="K165" s="3" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="L165" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="M165" t="s">
         <v>26</v>
       </c>
       <c r="N165" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="Q165" t="s">
         <v>27</v>
@@ -10094,15 +10094,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="166" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A166" s="2">
         <v>2400012</v>
       </c>
       <c r="B166" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C166" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D166" s="2">
         <v>2</v>
@@ -10111,7 +10111,7 @@
         <v>20</v>
       </c>
       <c r="F166" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G166" t="s">
         <v>22</v>
@@ -10126,13 +10126,13 @@
         <v>24</v>
       </c>
       <c r="K166" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="M166" t="s">
         <v>26</v>
       </c>
       <c r="N166" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="Q166" t="s">
         <v>27</v>
@@ -10141,15 +10141,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="167" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A167" s="2">
         <v>2401001</v>
       </c>
       <c r="B167" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C167" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D167" s="2">
         <v>1</v>
@@ -10173,16 +10173,16 @@
         <v>24</v>
       </c>
       <c r="K167" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="L167" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="M167" t="s">
         <v>26</v>
       </c>
       <c r="N167" s="6" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="Q167" t="s">
         <v>27</v>
@@ -10191,15 +10191,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="168" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A168" s="2">
         <v>2401001</v>
       </c>
       <c r="B168" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C168" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D168" s="2">
         <v>1</v>
@@ -10223,16 +10223,16 @@
         <v>24</v>
       </c>
       <c r="K168" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="L168" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="M168" t="s">
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="Q168" t="s">
         <v>27</v>
@@ -10241,15 +10241,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="169" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A169" s="2">
         <v>2401001</v>
       </c>
       <c r="B169" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C169" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D169" s="2">
         <v>1</v>
@@ -10273,16 +10273,16 @@
         <v>24</v>
       </c>
       <c r="K169" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="L169" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="M169" t="s">
         <v>26</v>
       </c>
       <c r="N169" s="6" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="Q169" t="s">
         <v>27</v>
@@ -10291,15 +10291,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="170" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A170" s="2">
         <v>2401007</v>
       </c>
       <c r="B170" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C170" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D170" s="2">
         <v>1</v>
@@ -10323,16 +10323,16 @@
         <v>24</v>
       </c>
       <c r="K170" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="L170" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="M170" t="s">
         <v>26</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="Q170" t="s">
         <v>27</v>
@@ -10341,15 +10341,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="171" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A171" s="2">
         <v>2401007</v>
       </c>
       <c r="B171" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C171" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D171" s="2">
         <v>1</v>
@@ -10373,16 +10373,16 @@
         <v>24</v>
       </c>
       <c r="K171" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="L171" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="M171" t="s">
         <v>26</v>
       </c>
       <c r="N171" s="6" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="Q171" t="s">
         <v>27</v>
@@ -10391,15 +10391,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="172" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A172" s="2">
         <v>2401007</v>
       </c>
       <c r="B172" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C172" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D172" s="2">
         <v>1</v>
@@ -10423,16 +10423,16 @@
         <v>24</v>
       </c>
       <c r="K172" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="L172" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="M172" t="s">
         <v>26</v>
       </c>
       <c r="N172" s="6" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="Q172" t="s">
         <v>27</v>
@@ -10441,15 +10441,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="173" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A173" s="2">
         <v>2401013</v>
       </c>
       <c r="B173" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C173" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D173" s="2">
         <v>2</v>
@@ -10458,7 +10458,7 @@
         <v>20</v>
       </c>
       <c r="F173" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="G173" t="s">
         <v>39</v>
@@ -10473,17 +10473,17 @@
         <v>41</v>
       </c>
       <c r="K173" t="s">
+        <v>362</v>
+      </c>
+      <c r="L173" t="s">
+        <v>363</v>
+      </c>
+      <c r="M173" t="s">
+        <v>26</v>
+      </c>
+      <c r="N173" t="s">
         <v>364</v>
       </c>
-      <c r="L173" t="s">
-        <v>365</v>
-      </c>
-      <c r="M173" t="s">
-        <v>26</v>
-      </c>
-      <c r="N173" t="s">
-        <v>366</v>
-      </c>
       <c r="Q173" t="s">
         <v>27</v>
       </c>
@@ -10491,15 +10491,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="174" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A174" s="2">
         <v>2401013</v>
       </c>
       <c r="B174" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C174" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D174" s="2">
         <v>2</v>
@@ -10508,7 +10508,7 @@
         <v>20</v>
       </c>
       <c r="F174" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="G174" t="s">
         <v>39</v>
@@ -10523,16 +10523,16 @@
         <v>41</v>
       </c>
       <c r="K174" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="L174" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="M174" t="s">
         <v>26</v>
       </c>
       <c r="N174" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="Q174" t="s">
         <v>27</v>
@@ -10541,15 +10541,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="175" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A175" s="2">
         <v>2401013</v>
       </c>
       <c r="B175" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C175" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D175" s="2">
         <v>2</v>
@@ -10558,7 +10558,7 @@
         <v>20</v>
       </c>
       <c r="F175" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="G175" t="s">
         <v>39</v>
@@ -10573,16 +10573,16 @@
         <v>41</v>
       </c>
       <c r="K175" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="L175" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="M175" t="s">
         <v>26</v>
       </c>
       <c r="N175" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="Q175" t="s">
         <v>27</v>
@@ -10591,15 +10591,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="176" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A176" s="2">
         <v>2401018</v>
       </c>
       <c r="B176" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C176" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D176" s="2">
         <v>2</v>
@@ -10608,7 +10608,7 @@
         <v>34</v>
       </c>
       <c r="F176" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G176" t="s">
         <v>39</v>
@@ -10623,16 +10623,16 @@
         <v>41</v>
       </c>
       <c r="K176" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="L176" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="M176" t="s">
         <v>26</v>
       </c>
       <c r="N176" s="6" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="Q176" t="s">
         <v>27</v>
@@ -10641,15 +10641,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="177" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A177" s="2">
         <v>2401018</v>
       </c>
       <c r="B177" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C177" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D177" s="2">
         <v>2</v>
@@ -10658,7 +10658,7 @@
         <v>34</v>
       </c>
       <c r="F177" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G177" t="s">
         <v>39</v>
@@ -10673,16 +10673,16 @@
         <v>41</v>
       </c>
       <c r="K177" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="L177" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="M177" t="s">
         <v>26</v>
       </c>
       <c r="N177" s="6" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="Q177" t="s">
         <v>27</v>
@@ -10691,15 +10691,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="178" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A178" s="2">
         <v>2401018</v>
       </c>
       <c r="B178" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C178" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D178" s="2">
         <v>2</v>
@@ -10708,7 +10708,7 @@
         <v>34</v>
       </c>
       <c r="F178" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G178" t="s">
         <v>39</v>
@@ -10717,16 +10717,16 @@
         <v>4</v>
       </c>
       <c r="I178" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="J178" t="s">
         <v>41</v>
       </c>
       <c r="K178" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="L178" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="M178" t="s">
         <v>26</v>
@@ -10738,15 +10738,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="179" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A179" s="2">
         <v>2401018</v>
       </c>
       <c r="B179" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C179" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D179" s="2">
         <v>2</v>
@@ -10755,7 +10755,7 @@
         <v>34</v>
       </c>
       <c r="F179" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G179" t="s">
         <v>39</v>
@@ -10770,16 +10770,16 @@
         <v>41</v>
       </c>
       <c r="K179" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="L179" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="M179" t="s">
         <v>26</v>
       </c>
       <c r="N179" s="6" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="Q179" t="s">
         <v>27</v>
@@ -10788,15 +10788,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="180" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A180" s="2">
         <v>2401018</v>
       </c>
       <c r="B180" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C180" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D180" s="2">
         <v>2</v>
@@ -10805,7 +10805,7 @@
         <v>34</v>
       </c>
       <c r="F180" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G180" t="s">
         <v>39</v>
@@ -10814,16 +10814,16 @@
         <v>4</v>
       </c>
       <c r="I180" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="J180" t="s">
         <v>41</v>
       </c>
       <c r="K180" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="L180" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="M180" t="s">
         <v>26</v>
@@ -10835,15 +10835,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="181" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A181" s="2">
         <v>2401018</v>
       </c>
       <c r="B181" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C181" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D181" s="2">
         <v>2</v>
@@ -10852,7 +10852,7 @@
         <v>34</v>
       </c>
       <c r="F181" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G181" t="s">
         <v>39</v>
@@ -10861,16 +10861,16 @@
         <v>4</v>
       </c>
       <c r="I181" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="J181" t="s">
         <v>41</v>
       </c>
       <c r="K181" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="L181" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="M181" t="s">
         <v>26</v>
@@ -10882,15 +10882,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="182" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A182" s="2">
         <v>2401018</v>
       </c>
       <c r="B182" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C182" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D182" s="2">
         <v>2</v>
@@ -10899,7 +10899,7 @@
         <v>34</v>
       </c>
       <c r="F182" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G182" t="s">
         <v>39</v>
@@ -10908,16 +10908,16 @@
         <v>4</v>
       </c>
       <c r="I182" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="J182" t="s">
         <v>41</v>
       </c>
       <c r="K182" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="L182" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="M182" t="s">
         <v>26</v>
@@ -10929,15 +10929,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="183" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A183" s="2">
         <v>2402003</v>
       </c>
       <c r="B183" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C183" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D183" s="2">
         <v>1</v>
@@ -10961,16 +10961,16 @@
         <v>24</v>
       </c>
       <c r="K183" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="L183" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="M183" t="s">
         <v>26</v>
       </c>
       <c r="N183" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="O183" s="4"/>
       <c r="Q183" t="s">
@@ -10980,15 +10980,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="184" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A184" s="2">
         <v>2402003</v>
       </c>
       <c r="B184" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C184" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D184" s="2">
         <v>1</v>
@@ -11012,16 +11012,16 @@
         <v>24</v>
       </c>
       <c r="K184" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="L184" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="M184" t="s">
         <v>26</v>
       </c>
       <c r="N184" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="O184" s="4"/>
       <c r="Q184" t="s">
@@ -11031,15 +11031,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="185" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A185" s="2">
         <v>2402003</v>
       </c>
       <c r="B185" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C185" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D185" s="2">
         <v>1</v>
@@ -11063,16 +11063,16 @@
         <v>24</v>
       </c>
       <c r="K185" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="L185" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="M185" t="s">
         <v>26</v>
       </c>
       <c r="N185" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="O185" s="4"/>
       <c r="Q185" t="s">
@@ -11082,15 +11082,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="186" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A186" s="2">
         <v>2402008</v>
       </c>
       <c r="B186" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C186" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D186" s="2">
         <v>1</v>
@@ -11114,17 +11114,17 @@
         <v>24</v>
       </c>
       <c r="K186" t="s">
+        <v>386</v>
+      </c>
+      <c r="L186" t="s">
+        <v>387</v>
+      </c>
+      <c r="M186" t="s">
+        <v>26</v>
+      </c>
+      <c r="N186" t="s">
         <v>388</v>
       </c>
-      <c r="L186" t="s">
-        <v>389</v>
-      </c>
-      <c r="M186" t="s">
-        <v>26</v>
-      </c>
-      <c r="N186" t="s">
-        <v>390</v>
-      </c>
       <c r="Q186" t="s">
         <v>27</v>
       </c>
@@ -11132,15 +11132,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="187" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A187" s="2">
         <v>2402008</v>
       </c>
       <c r="B187" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C187" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D187" s="2">
         <v>1</v>
@@ -11164,16 +11164,16 @@
         <v>24</v>
       </c>
       <c r="K187" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="L187" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="M187" t="s">
         <v>26</v>
       </c>
       <c r="N187" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="Q187" t="s">
         <v>27</v>
@@ -11182,15 +11182,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="188" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A188" s="2">
         <v>2402008</v>
       </c>
       <c r="B188" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C188" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D188" s="2">
         <v>1</v>
@@ -11214,16 +11214,16 @@
         <v>24</v>
       </c>
       <c r="K188" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="L188" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="M188" t="s">
         <v>26</v>
       </c>
       <c r="N188" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="Q188" t="s">
         <v>27</v>
@@ -11232,15 +11232,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="189" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A189" s="2">
         <v>2402015</v>
       </c>
       <c r="B189" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C189" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D189" s="2">
         <v>2</v>
@@ -11249,7 +11249,7 @@
         <v>20</v>
       </c>
       <c r="F189" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G189" t="s">
         <v>22</v>
@@ -11264,13 +11264,13 @@
         <v>41</v>
       </c>
       <c r="K189" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="M189" t="s">
         <v>26</v>
       </c>
       <c r="N189" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="Q189" t="s">
         <v>27</v>
@@ -11279,15 +11279,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="190" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A190" s="2">
         <v>2402015</v>
       </c>
       <c r="B190" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C190" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D190" s="2">
         <v>2</v>
@@ -11296,7 +11296,7 @@
         <v>20</v>
       </c>
       <c r="F190" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G190" t="s">
         <v>22</v>
@@ -11311,13 +11311,13 @@
         <v>41</v>
       </c>
       <c r="K190" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="M190" t="s">
         <v>26</v>
       </c>
       <c r="N190" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="Q190" t="s">
         <v>27</v>
@@ -11326,15 +11326,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="191" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A191" s="2">
         <v>2402015</v>
       </c>
       <c r="B191" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C191" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D191" s="2">
         <v>2</v>
@@ -11343,7 +11343,7 @@
         <v>20</v>
       </c>
       <c r="F191" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G191" t="s">
         <v>22</v>
@@ -11358,7 +11358,7 @@
         <v>41</v>
       </c>
       <c r="K191" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="M191" t="s">
         <v>26</v>
@@ -11372,15 +11372,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="192" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A192" s="2">
         <v>2403004</v>
       </c>
       <c r="B192" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C192" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D192" s="2">
         <v>1</v>
@@ -11404,16 +11404,16 @@
         <v>41</v>
       </c>
       <c r="K192" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="L192" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="M192" t="s">
         <v>26</v>
       </c>
       <c r="N192" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="O192" s="4"/>
       <c r="Q192" t="s">
@@ -11423,15 +11423,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="193" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A193" s="2">
         <v>2403004</v>
       </c>
       <c r="B193" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C193" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D193" s="2">
         <v>1</v>
@@ -11455,16 +11455,16 @@
         <v>41</v>
       </c>
       <c r="K193" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="L193" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="M193" t="s">
         <v>26</v>
       </c>
       <c r="N193" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="O193" s="4"/>
       <c r="Q193" t="s">
@@ -11474,15 +11474,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="194" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A194" s="2">
         <v>2403004</v>
       </c>
       <c r="B194" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C194" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D194" s="2">
         <v>1</v>
@@ -11506,16 +11506,16 @@
         <v>41</v>
       </c>
       <c r="K194" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="L194" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="M194" t="s">
         <v>26</v>
       </c>
       <c r="N194" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="O194" s="4"/>
       <c r="Q194" t="s">
@@ -11525,15 +11525,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="195" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A195" s="2">
         <v>2403009</v>
       </c>
       <c r="B195" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C195" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D195" s="2">
         <v>1</v>
@@ -11557,16 +11557,16 @@
         <v>41</v>
       </c>
       <c r="K195" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="L195" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="M195" t="s">
         <v>26</v>
       </c>
-      <c r="N195" s="10" t="s">
-        <v>553</v>
+      <c r="N195" s="8" t="s">
+        <v>551</v>
       </c>
       <c r="Q195" t="s">
         <v>27</v>
@@ -11575,15 +11575,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="196" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A196" s="2">
         <v>2403009</v>
       </c>
       <c r="B196" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C196" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D196" s="2">
         <v>1</v>
@@ -11607,16 +11607,16 @@
         <v>41</v>
       </c>
       <c r="K196" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="L196" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="M196" t="s">
         <v>26</v>
       </c>
-      <c r="N196" s="10" t="s">
-        <v>554</v>
+      <c r="N196" s="8" t="s">
+        <v>552</v>
       </c>
       <c r="Q196" t="s">
         <v>27</v>
@@ -11625,15 +11625,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="197" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A197" s="2">
         <v>2403009</v>
       </c>
       <c r="B197" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C197" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D197" s="2">
         <v>1</v>
@@ -11657,16 +11657,16 @@
         <v>41</v>
       </c>
       <c r="K197" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="L197" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="M197" t="s">
         <v>26</v>
       </c>
-      <c r="N197" s="10" t="s">
-        <v>554</v>
+      <c r="N197" s="8" t="s">
+        <v>552</v>
       </c>
       <c r="Q197" t="s">
         <v>27</v>
@@ -11675,15 +11675,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="198" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A198" s="2">
         <v>2403013</v>
       </c>
       <c r="B198" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C198" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D198" s="2">
         <v>2</v>
@@ -11692,7 +11692,7 @@
         <v>20</v>
       </c>
       <c r="F198" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G198" t="s">
         <v>22</v>
@@ -11707,13 +11707,13 @@
         <v>24</v>
       </c>
       <c r="K198" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="M198" t="s">
         <v>26</v>
       </c>
       <c r="N198" s="6" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="Q198" t="s">
         <v>27</v>
@@ -11722,15 +11722,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="199" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A199" s="2">
         <v>2403013</v>
       </c>
       <c r="B199" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C199" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D199" s="2">
         <v>2</v>
@@ -11739,7 +11739,7 @@
         <v>20</v>
       </c>
       <c r="F199" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G199" t="s">
         <v>22</v>
@@ -11754,13 +11754,13 @@
         <v>24</v>
       </c>
       <c r="K199" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="M199" t="s">
         <v>26</v>
       </c>
       <c r="N199" s="6" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="Q199" t="s">
         <v>27</v>
@@ -11769,15 +11769,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="200" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A200" s="2">
         <v>2403013</v>
       </c>
       <c r="B200" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C200" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D200" s="2">
         <v>2</v>
@@ -11786,7 +11786,7 @@
         <v>20</v>
       </c>
       <c r="F200" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G200" t="s">
         <v>22</v>
@@ -11801,13 +11801,13 @@
         <v>24</v>
       </c>
       <c r="K200" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="M200" t="s">
         <v>26</v>
       </c>
       <c r="N200" s="6" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="Q200" t="s">
         <v>27</v>
@@ -11816,15 +11816,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="201" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A201" s="2">
         <v>2404001</v>
       </c>
       <c r="B201" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C201" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D201" s="2">
         <v>1</v>
@@ -11848,17 +11848,17 @@
         <v>41</v>
       </c>
       <c r="K201" t="s">
+        <v>410</v>
+      </c>
+      <c r="L201" t="s">
+        <v>411</v>
+      </c>
+      <c r="M201" t="s">
+        <v>26</v>
+      </c>
+      <c r="N201" t="s">
         <v>412</v>
       </c>
-      <c r="L201" t="s">
-        <v>413</v>
-      </c>
-      <c r="M201" t="s">
-        <v>26</v>
-      </c>
-      <c r="N201" t="s">
-        <v>414</v>
-      </c>
       <c r="Q201" t="s">
         <v>27</v>
       </c>
@@ -11866,15 +11866,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="202" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A202" s="2">
         <v>2404001</v>
       </c>
       <c r="B202" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C202" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D202" s="2">
         <v>1</v>
@@ -11898,16 +11898,16 @@
         <v>41</v>
       </c>
       <c r="K202" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="L202" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="M202" t="s">
         <v>26</v>
       </c>
       <c r="N202" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="Q202" t="s">
         <v>27</v>
@@ -11916,15 +11916,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="203" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A203" s="2">
         <v>2404001</v>
       </c>
       <c r="B203" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C203" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D203" s="2">
         <v>1</v>
@@ -11948,16 +11948,16 @@
         <v>41</v>
       </c>
       <c r="K203" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="L203" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="M203" t="s">
         <v>26</v>
       </c>
       <c r="N203" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="Q203" t="s">
         <v>27</v>
@@ -11966,15 +11966,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="204" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A204" s="2">
         <v>2404006</v>
       </c>
       <c r="B204" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C204" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D204" s="2">
         <v>1</v>
@@ -11998,17 +11998,17 @@
         <v>41</v>
       </c>
       <c r="K204" t="s">
+        <v>416</v>
+      </c>
+      <c r="L204" t="s">
+        <v>417</v>
+      </c>
+      <c r="M204" t="s">
+        <v>26</v>
+      </c>
+      <c r="N204" t="s">
         <v>418</v>
       </c>
-      <c r="L204" t="s">
-        <v>419</v>
-      </c>
-      <c r="M204" t="s">
-        <v>26</v>
-      </c>
-      <c r="N204" t="s">
-        <v>420</v>
-      </c>
       <c r="Q204" t="s">
         <v>27</v>
       </c>
@@ -12016,15 +12016,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="205" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A205" s="2">
         <v>2404006</v>
       </c>
       <c r="B205" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C205" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D205" s="2">
         <v>1</v>
@@ -12048,16 +12048,16 @@
         <v>41</v>
       </c>
       <c r="K205" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="L205" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="M205" t="s">
         <v>26</v>
       </c>
       <c r="N205" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="Q205" t="s">
         <v>27</v>
@@ -12066,15 +12066,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="206" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A206" s="2">
         <v>2404006</v>
       </c>
       <c r="B206" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C206" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D206" s="2">
         <v>1</v>
@@ -12098,16 +12098,16 @@
         <v>41</v>
       </c>
       <c r="K206" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="L206" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="M206" t="s">
         <v>26</v>
       </c>
       <c r="N206" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="Q206" t="s">
         <v>27</v>
@@ -12116,15 +12116,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="207" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A207" s="2">
         <v>2404015</v>
       </c>
       <c r="B207" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C207" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D207" s="2">
         <v>2</v>
@@ -12133,7 +12133,7 @@
         <v>20</v>
       </c>
       <c r="F207" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="G207" t="s">
         <v>39</v>
@@ -12148,13 +12148,13 @@
         <v>24</v>
       </c>
       <c r="K207" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="M207" t="s">
         <v>26</v>
       </c>
       <c r="N207" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="Q207" t="s">
         <v>27</v>
@@ -12163,15 +12163,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="208" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A208" s="2">
         <v>2404015</v>
       </c>
       <c r="B208" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C208" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D208" s="2">
         <v>2</v>
@@ -12180,7 +12180,7 @@
         <v>20</v>
       </c>
       <c r="F208" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="G208" t="s">
         <v>39</v>
@@ -12189,19 +12189,19 @@
         <v>32</v>
       </c>
       <c r="I208" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="J208" t="s">
         <v>24</v>
       </c>
       <c r="K208" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="M208" t="s">
         <v>26</v>
       </c>
       <c r="N208" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="Q208" t="s">
         <v>27</v>
@@ -12210,15 +12210,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="209" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A209" s="2">
         <v>2404015</v>
       </c>
       <c r="B209" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C209" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D209" s="2">
         <v>2</v>
@@ -12227,7 +12227,7 @@
         <v>20</v>
       </c>
       <c r="F209" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="G209" t="s">
         <v>39</v>
@@ -12236,19 +12236,19 @@
         <v>32</v>
       </c>
       <c r="I209" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="J209" t="s">
         <v>24</v>
       </c>
       <c r="K209" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="M209" t="s">
         <v>26</v>
       </c>
       <c r="N209" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="Q209" t="s">
         <v>27</v>
@@ -12257,15 +12257,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="210" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A210" s="2">
         <v>2405001</v>
       </c>
       <c r="B210" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C210" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D210" s="2">
         <v>1</v>
@@ -12289,16 +12289,16 @@
         <v>41</v>
       </c>
       <c r="K210" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="L210" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="M210" t="s">
         <v>26</v>
       </c>
       <c r="N210" s="6" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="Q210" t="s">
         <v>27</v>
@@ -12307,15 +12307,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="211" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A211" s="2">
         <v>2405001</v>
       </c>
       <c r="B211" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C211" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D211" s="2">
         <v>1</v>
@@ -12339,16 +12339,16 @@
         <v>41</v>
       </c>
       <c r="K211" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="L211" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="M211" t="s">
         <v>26</v>
       </c>
       <c r="N211" s="6" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="Q211" t="s">
         <v>27</v>
@@ -12357,15 +12357,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="212" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A212" s="2">
         <v>2405001</v>
       </c>
       <c r="B212" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C212" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D212" s="2">
         <v>1</v>
@@ -12389,16 +12389,16 @@
         <v>41</v>
       </c>
       <c r="K212" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="L212" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="M212" t="s">
         <v>26</v>
       </c>
       <c r="N212" s="6" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="Q212" t="s">
         <v>27</v>
@@ -12407,15 +12407,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="213" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A213" s="2">
         <v>2405006</v>
       </c>
       <c r="B213" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C213" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D213" s="2">
         <v>1</v>
@@ -12439,16 +12439,16 @@
         <v>41</v>
       </c>
       <c r="K213" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="L213" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="M213" t="s">
         <v>26</v>
       </c>
       <c r="N213" s="6" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="Q213" t="s">
         <v>27</v>
@@ -12457,15 +12457,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="214" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A214" s="2">
         <v>2405006</v>
       </c>
       <c r="B214" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C214" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D214" s="2">
         <v>1</v>
@@ -12489,16 +12489,16 @@
         <v>41</v>
       </c>
       <c r="K214" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="L214" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="M214" t="s">
         <v>26</v>
       </c>
       <c r="N214" s="6" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="Q214" t="s">
         <v>27</v>
@@ -12507,15 +12507,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="215" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A215" s="2">
         <v>2405006</v>
       </c>
       <c r="B215" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C215" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D215" s="2">
         <v>1</v>
@@ -12539,16 +12539,16 @@
         <v>41</v>
       </c>
       <c r="K215" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="L215" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="M215" t="s">
         <v>26</v>
       </c>
       <c r="N215" s="6" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="Q215" t="s">
         <v>27</v>
@@ -12557,15 +12557,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="216" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A216" s="2">
         <v>2405015</v>
       </c>
       <c r="B216" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C216" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D216" s="2">
         <v>2</v>
@@ -12574,7 +12574,7 @@
         <v>20</v>
       </c>
       <c r="F216" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G216" t="s">
         <v>22</v>
@@ -12589,17 +12589,17 @@
         <v>24</v>
       </c>
       <c r="K216" t="s">
+        <v>437</v>
+      </c>
+      <c r="L216" t="s">
+        <v>438</v>
+      </c>
+      <c r="M216" t="s">
+        <v>26</v>
+      </c>
+      <c r="N216" t="s">
         <v>439</v>
       </c>
-      <c r="L216" t="s">
-        <v>440</v>
-      </c>
-      <c r="M216" t="s">
-        <v>26</v>
-      </c>
-      <c r="N216" t="s">
-        <v>441</v>
-      </c>
       <c r="Q216" t="s">
         <v>27</v>
       </c>
@@ -12607,15 +12607,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="217" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A217" s="2">
         <v>2405015</v>
       </c>
       <c r="B217" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C217" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D217" s="2">
         <v>2</v>
@@ -12624,7 +12624,7 @@
         <v>20</v>
       </c>
       <c r="F217" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G217" t="s">
         <v>22</v>
@@ -12639,16 +12639,16 @@
         <v>24</v>
       </c>
       <c r="K217" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="L217" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="M217" t="s">
         <v>26</v>
       </c>
       <c r="N217" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="Q217" t="s">
         <v>27</v>
@@ -12657,15 +12657,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="218" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A218" s="2">
         <v>2405015</v>
       </c>
       <c r="B218" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C218" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D218" s="2">
         <v>2</v>
@@ -12674,7 +12674,7 @@
         <v>20</v>
       </c>
       <c r="F218" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G218" t="s">
         <v>22</v>
@@ -12689,13 +12689,13 @@
         <v>24</v>
       </c>
       <c r="K218" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="M218" t="s">
         <v>26</v>
       </c>
       <c r="N218" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="Q218" t="s">
         <v>27</v>
@@ -12704,15 +12704,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="219" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A219" s="2">
         <v>2406004</v>
       </c>
       <c r="B219" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C219" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D219" s="2">
         <v>1</v>
@@ -12736,16 +12736,16 @@
         <v>24</v>
       </c>
       <c r="K219" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="L219" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="M219" t="s">
         <v>26</v>
       </c>
       <c r="N219" s="6" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="Q219" t="s">
         <v>27</v>
@@ -12754,15 +12754,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="220" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A220" s="2">
         <v>2406004</v>
       </c>
       <c r="B220" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C220" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D220" s="2">
         <v>1</v>
@@ -12786,16 +12786,16 @@
         <v>24</v>
       </c>
       <c r="K220" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="L220" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="M220" t="s">
         <v>26</v>
       </c>
       <c r="N220" s="6" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="Q220" t="s">
         <v>27</v>
@@ -12804,15 +12804,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="221" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A221" s="2">
         <v>2406004</v>
       </c>
       <c r="B221" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C221" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D221" s="2">
         <v>1</v>
@@ -12830,22 +12830,22 @@
         <v>8</v>
       </c>
       <c r="I221" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="J221" t="s">
         <v>24</v>
       </c>
       <c r="K221" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="L221" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="M221" t="s">
         <v>26</v>
       </c>
       <c r="N221" s="6" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="Q221" t="s">
         <v>27</v>
@@ -12854,15 +12854,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="222" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A222" s="2">
         <v>2406004</v>
       </c>
       <c r="B222" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C222" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D222" s="2">
         <v>1</v>
@@ -12886,16 +12886,16 @@
         <v>24</v>
       </c>
       <c r="K222" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="L222" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="M222" t="s">
         <v>26</v>
       </c>
       <c r="N222" s="6" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="Q222" t="s">
         <v>27</v>
@@ -12904,15 +12904,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="223" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A223" s="2">
         <v>2406004</v>
       </c>
       <c r="B223" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C223" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D223" s="2">
         <v>1</v>
@@ -12930,22 +12930,22 @@
         <v>8</v>
       </c>
       <c r="I223" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="J223" t="s">
         <v>24</v>
       </c>
       <c r="K223" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="L223" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="M223" t="s">
         <v>26</v>
       </c>
       <c r="N223" s="6" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="Q223" t="s">
         <v>27</v>
@@ -12954,15 +12954,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="224" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A224" s="2">
         <v>2406009</v>
       </c>
       <c r="B224" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C224" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D224" s="2">
         <v>1</v>
@@ -12986,16 +12986,16 @@
         <v>24</v>
       </c>
       <c r="K224" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="L224" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="M224" t="s">
         <v>26</v>
       </c>
       <c r="N224" s="6" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="Q224" t="s">
         <v>27</v>
@@ -13004,15 +13004,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="225" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A225" s="2">
         <v>2406009</v>
       </c>
       <c r="B225" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C225" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D225" s="2">
         <v>1</v>
@@ -13036,16 +13036,16 @@
         <v>24</v>
       </c>
       <c r="K225" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="L225" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="M225" t="s">
         <v>26</v>
       </c>
       <c r="N225" s="6" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="Q225" t="s">
         <v>27</v>
@@ -13054,15 +13054,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="226" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A226" s="2">
         <v>2406009</v>
       </c>
       <c r="B226" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C226" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D226" s="2">
         <v>1</v>
@@ -13080,22 +13080,22 @@
         <v>8</v>
       </c>
       <c r="I226" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="J226" t="s">
         <v>24</v>
       </c>
       <c r="K226" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="L226" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="M226" t="s">
         <v>26</v>
       </c>
       <c r="N226" s="6" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="Q226" t="s">
         <v>27</v>
@@ -13104,15 +13104,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="227" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A227" s="2">
         <v>2406009</v>
       </c>
       <c r="B227" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C227" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D227" s="2">
         <v>1</v>
@@ -13136,16 +13136,16 @@
         <v>24</v>
       </c>
       <c r="K227" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="L227" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="M227" t="s">
         <v>26</v>
       </c>
       <c r="N227" s="6" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="Q227" t="s">
         <v>27</v>
@@ -13154,15 +13154,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="228" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A228" s="2">
         <v>2406009</v>
       </c>
       <c r="B228" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C228" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D228" s="2">
         <v>1</v>
@@ -13180,22 +13180,22 @@
         <v>8</v>
       </c>
       <c r="I228" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="J228" t="s">
         <v>24</v>
       </c>
       <c r="K228" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="L228" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="M228" t="s">
         <v>26</v>
       </c>
       <c r="N228" s="6" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="Q228" t="s">
         <v>27</v>
@@ -13204,15 +13204,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="229" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A229" s="2">
         <v>2406012</v>
       </c>
       <c r="B229" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C229" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D229" s="2">
         <v>2</v>
@@ -13221,7 +13221,7 @@
         <v>20</v>
       </c>
       <c r="F229" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="G229" t="s">
         <v>39</v>
@@ -13236,10 +13236,10 @@
         <v>41</v>
       </c>
       <c r="K229" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="L229" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="M229" t="s">
         <v>26</v>
@@ -13251,15 +13251,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="230" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A230" s="2">
         <v>2406012</v>
       </c>
       <c r="B230" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C230" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D230" s="2">
         <v>2</v>
@@ -13268,7 +13268,7 @@
         <v>20</v>
       </c>
       <c r="F230" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="G230" t="s">
         <v>39</v>
@@ -13277,16 +13277,16 @@
         <v>8</v>
       </c>
       <c r="I230" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="J230" t="s">
         <v>41</v>
       </c>
       <c r="K230" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="L230" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="M230" t="s">
         <v>26</v>
@@ -13298,15 +13298,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="231" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A231" s="2">
         <v>2406012</v>
       </c>
       <c r="B231" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C231" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D231" s="2">
         <v>2</v>
@@ -13315,7 +13315,7 @@
         <v>20</v>
       </c>
       <c r="F231" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="G231" t="s">
         <v>39</v>
@@ -13324,16 +13324,16 @@
         <v>8</v>
       </c>
       <c r="I231" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="J231" t="s">
         <v>41</v>
       </c>
       <c r="K231" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="L231" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="M231" t="s">
         <v>26</v>
@@ -13345,15 +13345,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="232" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A232" s="2">
         <v>2059001</v>
       </c>
       <c r="B232" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C232" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D232" s="2">
         <v>1</v>
@@ -13362,7 +13362,7 @@
         <v>20</v>
       </c>
       <c r="F232" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G232" t="s">
         <v>22</v>
@@ -13377,10 +13377,10 @@
         <v>41</v>
       </c>
       <c r="K232" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="L232" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="M232" t="s">
         <v>26</v>
@@ -13392,15 +13392,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="233" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A233" s="2">
         <v>2059002</v>
       </c>
       <c r="B233" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C233" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D233" s="2">
         <v>1</v>
@@ -13409,7 +13409,7 @@
         <v>20</v>
       </c>
       <c r="F233" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G233" t="s">
         <v>22</v>
@@ -13424,10 +13424,10 @@
         <v>41</v>
       </c>
       <c r="K233" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="L233" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="M233" t="s">
         <v>26</v>
@@ -13439,15 +13439,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="234" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A234" s="2">
         <v>2059006</v>
       </c>
       <c r="B234" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C234" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D234" s="2">
         <v>1</v>
@@ -13471,10 +13471,10 @@
         <v>41</v>
       </c>
       <c r="K234" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L234" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="M234" t="s">
         <v>26</v>
@@ -13486,15 +13486,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="235" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A235" s="2">
         <v>2140011</v>
       </c>
       <c r="B235" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C235" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D235" s="2">
         <v>2</v>
@@ -13503,7 +13503,7 @@
         <v>20</v>
       </c>
       <c r="F235" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G235" t="s">
         <v>39</v>
@@ -13518,10 +13518,10 @@
         <v>41</v>
       </c>
       <c r="K235" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="L235" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="M235" t="s">
         <v>26</v>
@@ -13533,15 +13533,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="236" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A236" s="2">
         <v>2390004</v>
       </c>
       <c r="B236" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C236" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D236" s="2">
         <v>1</v>
@@ -13565,10 +13565,10 @@
         <v>24</v>
       </c>
       <c r="K236" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="L236" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="M236" t="s">
         <v>26</v>
@@ -13580,15 +13580,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="237" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A237" s="2">
         <v>2390004</v>
       </c>
       <c r="B237" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C237" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D237" s="2">
         <v>1</v>
@@ -13612,10 +13612,10 @@
         <v>24</v>
       </c>
       <c r="K237" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="L237" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="M237" t="s">
         <v>26</v>
@@ -13627,15 +13627,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="238" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A238" s="2">
         <v>2390004</v>
       </c>
       <c r="B238" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C238" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D238" s="2">
         <v>1</v>
@@ -13659,10 +13659,10 @@
         <v>24</v>
       </c>
       <c r="K238" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="L238" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="M238" t="s">
         <v>26</v>
@@ -13674,15 +13674,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="239" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A239" s="2">
         <v>2390009</v>
       </c>
       <c r="B239" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C239" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D239" s="2">
         <v>1</v>
@@ -13706,10 +13706,10 @@
         <v>24</v>
       </c>
       <c r="K239" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="L239" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="M239" t="s">
         <v>26</v>
@@ -13721,15 +13721,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="240" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A240" s="2">
         <v>2390009</v>
       </c>
       <c r="B240" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C240" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D240" s="2">
         <v>1</v>
@@ -13753,10 +13753,10 @@
         <v>24</v>
       </c>
       <c r="K240" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="L240" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="M240" t="s">
         <v>26</v>
@@ -13768,15 +13768,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="241" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A241" s="2">
         <v>2390009</v>
       </c>
       <c r="B241" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C241" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D241" s="2">
         <v>1</v>
@@ -13800,10 +13800,10 @@
         <v>24</v>
       </c>
       <c r="K241" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="L241" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="M241" t="s">
         <v>26</v>
@@ -13815,15 +13815,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="242" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A242" s="2">
         <v>2390013</v>
       </c>
       <c r="B242" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C242" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D242" s="2">
         <v>2</v>
@@ -13832,7 +13832,7 @@
         <v>20</v>
       </c>
       <c r="F242" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G242" t="s">
         <v>22</v>
@@ -13847,7 +13847,7 @@
         <v>41</v>
       </c>
       <c r="K242" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="M242" t="s">
         <v>26</v>
@@ -13859,15 +13859,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="243" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A243" s="2">
         <v>2390013</v>
       </c>
       <c r="B243" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C243" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D243" s="2">
         <v>2</v>
@@ -13876,7 +13876,7 @@
         <v>20</v>
       </c>
       <c r="F243" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G243" t="s">
         <v>22</v>
@@ -13891,7 +13891,7 @@
         <v>41</v>
       </c>
       <c r="K243" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="M243" t="s">
         <v>26</v>
@@ -13903,15 +13903,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="244" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A244" s="2">
         <v>2390013</v>
       </c>
       <c r="B244" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C244" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D244" s="2">
         <v>2</v>
@@ -13920,7 +13920,7 @@
         <v>20</v>
       </c>
       <c r="F244" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G244" t="s">
         <v>22</v>
@@ -13935,7 +13935,7 @@
         <v>41</v>
       </c>
       <c r="K244" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="M244" t="s">
         <v>26</v>
@@ -13947,7 +13947,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="252" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L252" s="1"/>
     </row>
   </sheetData>

--- a/POD_2026-27_11-5-2026.xlsx
+++ b/POD_2026-27_11-5-2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guillermo.vera/Desktop/POD2627/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\misael.marriaga\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAD379A7-2F72-2147-AF37-A7BE160BC0B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D2F840D-652E-439C-A8E7-C66348B1142B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="POD" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3041" uniqueCount="555">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3046" uniqueCount="557">
   <si>
     <t>POD_2026-27_11-5-2026</t>
   </si>
@@ -347,18 +347,12 @@
     <t>G_TELECO-AEROESP_EXT_I_2A(F) (2174019)</t>
   </si>
   <si>
-    <t>ANA I. MUÑOZ (76)</t>
-  </si>
-  <si>
     <t>V=&gt;(15:00-17:00)[29/01/27, 05/02/27, 12/02/27, 19/02/27, 26/02/27, 05/03/27, 12/03/27, 19/03/27, 02/04/27, 09/04/27, 16/04/27, 23/04/27, 30/04/27, 07/05/27], X=&gt;(15:00-17:00)[27/01/27, 03/02/27, 10/02/27, 17/02/27, 24/02/27, 03/03/27, 10/03/27, 17/03/27, 31/03/27, 07/04/27, 14/04/27, 21/04/27, 28/04/27, 05/05/27]</t>
   </si>
   <si>
     <t>G_AEROBIL_EXT_1A(F) (2125006), G_AERO_EXT_I_1A(F) (2151006), G_AERO_EXT822_II_1A(F) (2339006), G_TELECO-AEROESP_EXT822_1A(F) (2332006), G_TELECO-AEROESP_1A(F) (2412008), G_TRANSP_EXT822_1A(F) (2341006), G_VEHI_EXT_I_1A(F) (2284007), G_VEHI_EXT822_1A(F) (2356007)</t>
   </si>
   <si>
-    <t>MISAEL MARRIAGA (76)</t>
-  </si>
-  <si>
     <t>(2384) GRADO EN INGENIERÍA BIOMÉDICA (INGLÉS)(FUENLABRADA)</t>
   </si>
   <si>
@@ -419,6 +413,12 @@
     <t>G_BIOMED_EXT822_1A(F) (2229002)</t>
   </si>
   <si>
+    <t>L=&gt;(13:00-15:00)[21/09/26, 19/10/26, 16/11/26, 14/12/26] | (17:00-19:00)[05/10/26, 30/11/26]</t>
+  </si>
+  <si>
+    <t>L=&gt;(17:00-19:00)[21/09/26, 19/10/26, 16/11/26, 14/12/26] | (13:00-15:00)[05/10/26, 30/11/26]</t>
+  </si>
+  <si>
     <t>(2386) GRADO EN INGENIERÍA EN TECNOLOGÍAS DE TELECOMUNICACIÓN (FUENLABRADA)</t>
   </si>
   <si>
@@ -1697,10 +1697,16 @@
     <t>Enrique Benito Matías (6)</t>
   </si>
   <si>
-    <t>L=&gt;(13:00-15:00)[21/09/26, 19/10/26, 16/11/26, 14/12/26, 05/10/26, 30/11/26]</t>
-  </si>
-  <si>
-    <t>L=&gt;(17:00-19:00)[21/09/26, 19/10/26, 16/11/26, 14/12/26, 05/10/26, 30/11/26]</t>
+    <t>ANA I. MUÑOZ (60)</t>
+  </si>
+  <si>
+    <t>MISAEL MARRIAGA (16)</t>
+  </si>
+  <si>
+    <t>ANA I. MUÑOZ (16)</t>
+  </si>
+  <si>
+    <t>Pedro J. Chocano (60)</t>
   </si>
 </sst>
 </file>
@@ -1773,12 +1779,12 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1797,9 +1803,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1837,7 +1843,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1943,7 +1949,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2085,7 +2091,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2094,53 +2100,53 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S252"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="71.33203125" customWidth="1"/>
+    <col min="2" max="2" width="71.26953125" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" customWidth="1"/>
-    <col min="5" max="5" width="20.1640625" customWidth="1"/>
-    <col min="6" max="6" width="64.1640625" customWidth="1"/>
-    <col min="7" max="7" width="20.83203125" customWidth="1"/>
-    <col min="8" max="8" width="6.5" customWidth="1"/>
-    <col min="9" max="9" width="7.83203125" customWidth="1"/>
-    <col min="10" max="10" width="6.5" customWidth="1"/>
-    <col min="11" max="11" width="107.1640625" customWidth="1"/>
-    <col min="12" max="12" width="53.6640625" customWidth="1"/>
-    <col min="13" max="13" width="12.6640625" customWidth="1"/>
-    <col min="14" max="14" width="36.5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="36.5" customWidth="1"/>
-    <col min="16" max="16" width="20.83203125" customWidth="1"/>
+    <col min="4" max="4" width="9.1796875" customWidth="1"/>
+    <col min="5" max="5" width="20.1796875" customWidth="1"/>
+    <col min="6" max="6" width="64.1796875" customWidth="1"/>
+    <col min="7" max="7" width="20.81640625" customWidth="1"/>
+    <col min="8" max="8" width="6.453125" customWidth="1"/>
+    <col min="9" max="9" width="7.81640625" customWidth="1"/>
+    <col min="10" max="10" width="6.453125" customWidth="1"/>
+    <col min="11" max="11" width="107.1796875" customWidth="1"/>
+    <col min="12" max="12" width="53.7265625" customWidth="1"/>
+    <col min="13" max="13" width="12.7265625" customWidth="1"/>
+    <col min="14" max="14" width="36.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="36.453125" customWidth="1"/>
+    <col min="16" max="16" width="20.81640625" customWidth="1"/>
     <col min="17" max="17" width="52" customWidth="1"/>
-    <col min="18" max="18" width="32.5" customWidth="1"/>
-    <col min="19" max="19" width="16.83203125" customWidth="1"/>
+    <col min="18" max="18" width="32.453125" customWidth="1"/>
+    <col min="19" max="19" width="16.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="10"/>
-      <c r="R1" s="10"/>
-      <c r="S1" s="10"/>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8"/>
+      <c r="R1" s="8"/>
+      <c r="S1" s="8"/>
+    </row>
+    <row r="2" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2199,7 +2205,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>2291005</v>
       </c>
@@ -2243,7 +2249,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>2291009</v>
       </c>
@@ -2287,7 +2293,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>2240005</v>
       </c>
@@ -2334,7 +2340,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>2240009</v>
       </c>
@@ -2381,7 +2387,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>2251011</v>
       </c>
@@ -2425,7 +2431,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>2327002</v>
       </c>
@@ -2472,7 +2478,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>2327002</v>
       </c>
@@ -2519,7 +2525,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>2327002</v>
       </c>
@@ -2566,7 +2572,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>2327007</v>
       </c>
@@ -2616,7 +2622,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>2327007</v>
       </c>
@@ -2666,7 +2672,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>2327007</v>
       </c>
@@ -2716,7 +2722,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>2327015</v>
       </c>
@@ -2763,7 +2769,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>2327015</v>
       </c>
@@ -2810,7 +2816,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>2327015</v>
       </c>
@@ -2857,7 +2863,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>2360001</v>
       </c>
@@ -2894,6 +2900,9 @@
       <c r="M17" t="s">
         <v>26</v>
       </c>
+      <c r="N17" s="6" t="s">
+        <v>556</v>
+      </c>
       <c r="Q17" t="s">
         <v>27</v>
       </c>
@@ -2901,7 +2910,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>2360002</v>
       </c>
@@ -2948,7 +2957,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>2382005</v>
       </c>
@@ -2998,7 +3007,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>2382005</v>
       </c>
@@ -3048,7 +3057,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>2382005</v>
       </c>
@@ -3098,7 +3107,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>2382005</v>
       </c>
@@ -3148,7 +3157,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>2382005</v>
       </c>
@@ -3198,7 +3207,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>2382005</v>
       </c>
@@ -3248,7 +3257,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>2382010</v>
       </c>
@@ -3298,7 +3307,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>2382010</v>
       </c>
@@ -3348,7 +3357,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>2382010</v>
       </c>
@@ -3398,7 +3407,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>2382010</v>
       </c>
@@ -3448,7 +3457,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>2382010</v>
       </c>
@@ -3485,7 +3494,7 @@
       <c r="M29" t="s">
         <v>26</v>
       </c>
-      <c r="N29" s="7" t="s">
+      <c r="N29" s="9" t="s">
         <v>550</v>
       </c>
       <c r="Q29" t="s">
@@ -3495,7 +3504,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>2382010</v>
       </c>
@@ -3545,7 +3554,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>2383001</v>
       </c>
@@ -3595,7 +3604,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>2383001</v>
       </c>
@@ -3642,7 +3651,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>2383001</v>
       </c>
@@ -3689,7 +3698,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>2383001</v>
       </c>
@@ -3739,7 +3748,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>2383001</v>
       </c>
@@ -3789,7 +3798,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>2383001</v>
       </c>
@@ -3839,7 +3848,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <v>2383002</v>
       </c>
@@ -3889,7 +3898,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <v>2383002</v>
       </c>
@@ -3936,7 +3945,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <v>2383002</v>
       </c>
@@ -3983,7 +3992,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>2383002</v>
       </c>
@@ -4033,7 +4042,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>2383002</v>
       </c>
@@ -4083,7 +4092,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>2383002</v>
       </c>
@@ -4133,7 +4142,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="48" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <v>2383007</v>
       </c>
@@ -4174,7 +4183,10 @@
         <v>26</v>
       </c>
       <c r="N43" t="s">
-        <v>103</v>
+        <v>553</v>
+      </c>
+      <c r="O43" t="s">
+        <v>554</v>
       </c>
       <c r="Q43" t="s">
         <v>27</v>
@@ -4183,7 +4195,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:18" ht="48" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>2383007</v>
       </c>
@@ -4215,16 +4227,19 @@
         <v>24</v>
       </c>
       <c r="K44" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="L44" t="s">
         <v>104</v>
       </c>
-      <c r="L44" t="s">
-        <v>105</v>
-      </c>
       <c r="M44" t="s">
         <v>26</v>
       </c>
       <c r="N44" t="s">
-        <v>106</v>
+        <v>177</v>
+      </c>
+      <c r="O44" t="s">
+        <v>555</v>
       </c>
       <c r="Q44" t="s">
         <v>27</v>
@@ -4233,12 +4248,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <v>2384001</v>
       </c>
       <c r="B45" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C45" t="s">
         <v>43</v>
@@ -4250,7 +4265,7 @@
         <v>20</v>
       </c>
       <c r="F45" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G45" t="s">
         <v>22</v>
@@ -4265,10 +4280,10 @@
         <v>24</v>
       </c>
       <c r="K45" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L45" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="M45" t="s">
         <v>26</v>
@@ -4283,12 +4298,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>2384001</v>
       </c>
       <c r="B46" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C46" t="s">
         <v>43</v>
@@ -4300,7 +4315,7 @@
         <v>20</v>
       </c>
       <c r="F46" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G46" t="s">
         <v>22</v>
@@ -4309,16 +4324,16 @@
         <v>14</v>
       </c>
       <c r="I46" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J46" t="s">
         <v>24</v>
       </c>
       <c r="K46" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="L46" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="M46" t="s">
         <v>26</v>
@@ -4333,12 +4348,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <v>2384001</v>
       </c>
       <c r="B47" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C47" t="s">
         <v>43</v>
@@ -4350,7 +4365,7 @@
         <v>20</v>
       </c>
       <c r="F47" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G47" t="s">
         <v>22</v>
@@ -4359,16 +4374,16 @@
         <v>14</v>
       </c>
       <c r="I47" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J47" t="s">
         <v>24</v>
       </c>
       <c r="K47" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="L47" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="M47" t="s">
         <v>26</v>
@@ -4383,12 +4398,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>2384005</v>
       </c>
       <c r="B48" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C48" t="s">
         <v>43</v>
@@ -4400,7 +4415,7 @@
         <v>20</v>
       </c>
       <c r="F48" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G48" t="s">
         <v>22</v>
@@ -4415,10 +4430,10 @@
         <v>24</v>
       </c>
       <c r="K48" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L48" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="M48" t="s">
         <v>26</v>
@@ -4433,12 +4448,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <v>2384005</v>
       </c>
       <c r="B49" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C49" t="s">
         <v>43</v>
@@ -4450,7 +4465,7 @@
         <v>20</v>
       </c>
       <c r="F49" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G49" t="s">
         <v>22</v>
@@ -4459,16 +4474,16 @@
         <v>14</v>
       </c>
       <c r="I49" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J49" t="s">
         <v>24</v>
       </c>
       <c r="K49" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="L49" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="M49" t="s">
         <v>26</v>
@@ -4483,12 +4498,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <v>2384005</v>
       </c>
       <c r="B50" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C50" t="s">
         <v>43</v>
@@ -4500,7 +4515,7 @@
         <v>20</v>
       </c>
       <c r="F50" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G50" t="s">
         <v>22</v>
@@ -4509,16 +4524,16 @@
         <v>14</v>
       </c>
       <c r="I50" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J50" t="s">
         <v>24</v>
       </c>
       <c r="K50" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="L50" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="M50" t="s">
         <v>26</v>
@@ -4533,12 +4548,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <v>2385001</v>
       </c>
       <c r="B51" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C51" t="s">
         <v>43</v>
@@ -4565,10 +4580,10 @@
         <v>24</v>
       </c>
       <c r="K51" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="L51" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="M51" t="s">
         <v>26</v>
@@ -4583,12 +4598,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <v>2385001</v>
       </c>
       <c r="B52" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C52" t="s">
         <v>43</v>
@@ -4609,16 +4624,16 @@
         <v>14</v>
       </c>
       <c r="I52" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J52" t="s">
         <v>24</v>
       </c>
       <c r="K52" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L52" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="M52" t="s">
         <v>26</v>
@@ -4633,12 +4648,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
         <v>2385001</v>
       </c>
       <c r="B53" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C53" t="s">
         <v>43</v>
@@ -4659,16 +4674,16 @@
         <v>14</v>
       </c>
       <c r="I53" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J53" t="s">
         <v>24</v>
       </c>
       <c r="K53" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="L53" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="M53" t="s">
         <v>26</v>
@@ -4683,12 +4698,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <v>2385005</v>
       </c>
       <c r="B54" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C54" t="s">
         <v>43</v>
@@ -4715,10 +4730,10 @@
         <v>24</v>
       </c>
       <c r="K54" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="L54" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M54" t="s">
         <v>26</v>
@@ -4733,12 +4748,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
         <v>2385005</v>
       </c>
       <c r="B55" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C55" t="s">
         <v>43</v>
@@ -4759,16 +4774,16 @@
         <v>14</v>
       </c>
       <c r="I55" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J55" t="s">
         <v>24</v>
       </c>
-      <c r="K55" s="6" t="s">
-        <v>553</v>
+      <c r="K55" t="s">
+        <v>125</v>
       </c>
       <c r="L55" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M55" t="s">
         <v>26</v>
@@ -4783,12 +4798,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <v>2385005</v>
       </c>
       <c r="B56" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C56" t="s">
         <v>43</v>
@@ -4809,16 +4824,16 @@
         <v>14</v>
       </c>
       <c r="I56" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J56" t="s">
         <v>24</v>
       </c>
-      <c r="K56" s="6" t="s">
-        <v>554</v>
+      <c r="K56" t="s">
+        <v>126</v>
       </c>
       <c r="L56" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M56" t="s">
         <v>26</v>
@@ -4833,7 +4848,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
         <v>2386001</v>
       </c>
@@ -4880,7 +4895,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <v>2386001</v>
       </c>
@@ -4927,7 +4942,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
         <v>2386001</v>
       </c>
@@ -4974,7 +4989,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>2386001</v>
       </c>
@@ -5021,7 +5036,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <v>2386001</v>
       </c>
@@ -5068,7 +5083,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <v>2386001</v>
       </c>
@@ -5115,7 +5130,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
         <v>2386002</v>
       </c>
@@ -5155,6 +5170,9 @@
       <c r="M63" t="s">
         <v>26</v>
       </c>
+      <c r="N63" t="s">
+        <v>556</v>
+      </c>
       <c r="Q63" t="s">
         <v>27</v>
       </c>
@@ -5162,7 +5180,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
         <v>2386002</v>
       </c>
@@ -5215,7 +5233,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A65" s="2">
         <v>2387009</v>
       </c>
@@ -5262,7 +5280,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A66" s="2">
         <v>2387009</v>
       </c>
@@ -5309,7 +5327,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A67" s="2">
         <v>2387009</v>
       </c>
@@ -5356,7 +5374,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A68" s="2">
         <v>2387016</v>
       </c>
@@ -5403,7 +5421,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A69" s="2">
         <v>2387016</v>
       </c>
@@ -5429,7 +5447,7 @@
         <v>16</v>
       </c>
       <c r="I69" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J69" t="s">
         <v>24</v>
@@ -5450,7 +5468,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A70" s="2">
         <v>2387016</v>
       </c>
@@ -5476,7 +5494,7 @@
         <v>16</v>
       </c>
       <c r="I70" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J70" t="s">
         <v>24</v>
@@ -5497,7 +5515,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="71" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A71" s="2">
         <v>2265020</v>
       </c>
@@ -5545,7 +5563,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A72" s="2">
         <v>2029018</v>
       </c>
@@ -5592,7 +5610,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A73" s="2">
         <v>2030013</v>
       </c>
@@ -5639,7 +5657,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A74" s="2">
         <v>2031001</v>
       </c>
@@ -5683,7 +5701,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A75" s="2">
         <v>2032001</v>
       </c>
@@ -5733,7 +5751,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A76" s="2">
         <v>2032007</v>
       </c>
@@ -5783,7 +5801,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A77" s="2">
         <v>2032009</v>
       </c>
@@ -5830,7 +5848,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A78" s="2">
         <v>2033001</v>
       </c>
@@ -5877,7 +5895,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="79" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A79" s="2">
         <v>2033002</v>
       </c>
@@ -5930,7 +5948,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A80" s="2">
         <v>2033006</v>
       </c>
@@ -5980,7 +5998,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A81" s="2">
         <v>2034001</v>
       </c>
@@ -6030,7 +6048,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="82" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A82" s="2">
         <v>2034002</v>
       </c>
@@ -6083,7 +6101,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A83" s="2">
         <v>2034006</v>
       </c>
@@ -6133,7 +6151,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A84" s="2">
         <v>2061001</v>
       </c>
@@ -6177,7 +6195,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A85" s="2">
         <v>2061002</v>
       </c>
@@ -6224,7 +6242,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A86" s="2">
         <v>2061006</v>
       </c>
@@ -6268,7 +6286,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A87" s="2">
         <v>2107013</v>
       </c>
@@ -6315,7 +6333,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A88" s="2">
         <v>2143016</v>
       </c>
@@ -6362,7 +6380,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A89" s="2">
         <v>2148011</v>
       </c>
@@ -6406,7 +6424,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A90" s="2">
         <v>2175020</v>
       </c>
@@ -6453,7 +6471,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="91" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A91" s="2">
         <v>2285005</v>
       </c>
@@ -6503,7 +6521,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A92" s="2">
         <v>2285006</v>
       </c>
@@ -6550,7 +6568,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A93" s="2">
         <v>2285007</v>
       </c>
@@ -6597,7 +6615,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A94" s="2">
         <v>2286015</v>
       </c>
@@ -6641,7 +6659,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A95" s="2">
         <v>2338044</v>
       </c>
@@ -6685,7 +6703,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A96" s="2">
         <v>2342014</v>
       </c>
@@ -6732,7 +6750,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="97" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A97" s="2">
         <v>5</v>
       </c>
@@ -6780,7 +6798,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="98" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A98" s="2">
         <v>2343027</v>
       </c>
@@ -6828,7 +6846,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A99" s="2">
         <v>2343027</v>
       </c>
@@ -6854,7 +6872,7 @@
         <v>6</v>
       </c>
       <c r="I99" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J99" t="s">
         <v>24</v>
@@ -6875,7 +6893,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A100" s="2">
         <v>2343027</v>
       </c>
@@ -6901,7 +6919,7 @@
         <v>6</v>
       </c>
       <c r="I100" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J100" t="s">
         <v>24</v>
@@ -6921,7 +6939,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A101" s="2">
         <v>2347001</v>
       </c>
@@ -6971,7 +6989,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A102" s="2">
         <v>2347003</v>
       </c>
@@ -7021,7 +7039,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="103" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A103" s="2">
         <v>2347005</v>
       </c>
@@ -7072,7 +7090,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A104" s="2">
         <v>2347006</v>
       </c>
@@ -7122,7 +7140,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="105" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A105" s="2">
         <v>2347007</v>
       </c>
@@ -7173,7 +7191,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A106" s="2">
         <v>2347013</v>
       </c>
@@ -7223,7 +7241,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A107" s="2">
         <v>2347014</v>
       </c>
@@ -7263,6 +7281,9 @@
       <c r="M107" t="s">
         <v>26</v>
       </c>
+      <c r="N107" s="3" t="s">
+        <v>556</v>
+      </c>
       <c r="Q107" t="s">
         <v>27</v>
       </c>
@@ -7270,7 +7291,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A108" s="2">
         <v>2347017</v>
       </c>
@@ -7320,7 +7341,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="109" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A109" s="2">
         <v>2347030</v>
       </c>
@@ -7371,7 +7392,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A110" s="2">
         <v>2347021</v>
       </c>
@@ -7421,7 +7442,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="111" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A111" s="2">
         <v>2347022</v>
       </c>
@@ -7473,7 +7494,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A112" s="2">
         <v>2347024</v>
       </c>
@@ -7523,7 +7544,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="113" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A113" s="2">
         <v>2347026</v>
       </c>
@@ -7574,7 +7595,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="114" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A114" s="2">
         <v>2347027</v>
       </c>
@@ -7625,7 +7646,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A115" s="2">
         <v>2347029</v>
       </c>
@@ -7675,7 +7696,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="116" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A116" s="2">
         <v>2347031</v>
       </c>
@@ -7725,7 +7746,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="117" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A117" s="2">
         <v>2347038</v>
       </c>
@@ -7776,7 +7797,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="118" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A118" s="2">
         <v>2361002</v>
       </c>
@@ -7823,7 +7844,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="119" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A119" s="2">
         <v>2361002</v>
       </c>
@@ -7870,7 +7891,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="120" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A120" s="2">
         <v>2361002</v>
       </c>
@@ -7914,7 +7935,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="121" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A121" s="2">
         <v>2361004</v>
       </c>
@@ -7961,7 +7982,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="122" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A122" s="2">
         <v>2393002</v>
       </c>
@@ -8008,7 +8029,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="123" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A123" s="2">
         <v>2393002</v>
       </c>
@@ -8055,7 +8076,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="124" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A124" s="2">
         <v>2393002</v>
       </c>
@@ -8102,7 +8123,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="125" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A125" s="2">
         <v>2394004</v>
       </c>
@@ -8149,7 +8170,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="126" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A126" s="2">
         <v>2394004</v>
       </c>
@@ -8175,7 +8196,7 @@
         <v>12</v>
       </c>
       <c r="I126" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J126" t="s">
         <v>24</v>
@@ -8196,7 +8217,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="127" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A127" s="2">
         <v>2394004</v>
       </c>
@@ -8222,7 +8243,7 @@
         <v>12</v>
       </c>
       <c r="I127" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J127" t="s">
         <v>24</v>
@@ -8243,7 +8264,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="128" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A128" s="2">
         <v>2395003</v>
       </c>
@@ -8293,7 +8314,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="129" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A129" s="2">
         <v>2395003</v>
       </c>
@@ -8343,7 +8364,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="130" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A130" s="2">
         <v>2395003</v>
       </c>
@@ -8393,7 +8414,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="131" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A131" s="2">
         <v>2396001</v>
       </c>
@@ -8443,7 +8464,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="132" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A132" s="2">
         <v>2396001</v>
       </c>
@@ -8469,7 +8490,7 @@
         <v>20</v>
       </c>
       <c r="I132" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J132" t="s">
         <v>24</v>
@@ -8493,7 +8514,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="133" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A133" s="2">
         <v>2396001</v>
       </c>
@@ -8519,7 +8540,7 @@
         <v>20</v>
       </c>
       <c r="I133" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J133" t="s">
         <v>24</v>
@@ -8543,7 +8564,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="134" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A134" s="2">
         <v>2397003</v>
       </c>
@@ -8593,7 +8614,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="135" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A135" s="2">
         <v>2397003</v>
       </c>
@@ -8619,7 +8640,7 @@
         <v>12</v>
       </c>
       <c r="I135" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J135" t="s">
         <v>24</v>
@@ -8643,7 +8664,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="136" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A136" s="2">
         <v>2397003</v>
       </c>
@@ -8669,7 +8690,7 @@
         <v>12</v>
       </c>
       <c r="I136" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J136" t="s">
         <v>24</v>
@@ -8693,7 +8714,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="137" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A137" s="2">
         <v>2397008</v>
       </c>
@@ -8740,7 +8761,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="138" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A138" s="2">
         <v>2397008</v>
       </c>
@@ -8766,7 +8787,7 @@
         <v>12</v>
       </c>
       <c r="I138" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J138" t="s">
         <v>24</v>
@@ -8787,7 +8808,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="139" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A139" s="2">
         <v>2397008</v>
       </c>
@@ -8813,7 +8834,7 @@
         <v>12</v>
       </c>
       <c r="I139" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J139" t="s">
         <v>24</v>
@@ -8834,7 +8855,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="140" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A140" s="2">
         <v>2398001</v>
       </c>
@@ -8884,7 +8905,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="141" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A141" s="2">
         <v>2398001</v>
       </c>
@@ -8935,7 +8956,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="142" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A142" s="2">
         <v>2398001</v>
       </c>
@@ -8986,7 +9007,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="143" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A143" s="2">
         <v>2398006</v>
       </c>
@@ -9036,7 +9057,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="144" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A144" s="2">
         <v>2398006</v>
       </c>
@@ -9086,7 +9107,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="145" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A145" s="2">
         <v>2398006</v>
       </c>
@@ -9136,7 +9157,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="146" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A146" s="2">
         <v>2398013</v>
       </c>
@@ -9183,7 +9204,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="147" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A147" s="2">
         <v>2398013</v>
       </c>
@@ -9209,7 +9230,7 @@
         <v>20</v>
       </c>
       <c r="I147" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J147" t="s">
         <v>24</v>
@@ -9230,7 +9251,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A148" s="2">
         <v>2398013</v>
       </c>
@@ -9256,7 +9277,7 @@
         <v>20</v>
       </c>
       <c r="I148" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J148" t="s">
         <v>24</v>
@@ -9274,7 +9295,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="149" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A149" s="2">
         <v>2399003</v>
       </c>
@@ -9321,7 +9342,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="150" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A150" s="2">
         <v>2399003</v>
       </c>
@@ -9368,7 +9389,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="151" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A151" s="2">
         <v>2399003</v>
       </c>
@@ -9415,7 +9436,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="152" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A152" s="2">
         <v>2399010</v>
       </c>
@@ -9462,7 +9483,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="153" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A153" s="2">
         <v>2399010</v>
       </c>
@@ -9509,7 +9530,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="154" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A154" s="2">
         <v>2399010</v>
       </c>
@@ -9556,7 +9577,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="155" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A155" s="2">
         <v>2399014</v>
       </c>
@@ -9603,7 +9624,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A156" s="2">
         <v>2399014</v>
       </c>
@@ -9629,7 +9650,7 @@
         <v>21</v>
       </c>
       <c r="I156" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J156" t="s">
         <v>24</v>
@@ -9650,7 +9671,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A157" s="2">
         <v>2399014</v>
       </c>
@@ -9676,7 +9697,7 @@
         <v>21</v>
       </c>
       <c r="I157" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J157" t="s">
         <v>24</v>
@@ -9694,7 +9715,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="158" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A158" s="2">
         <v>2400003</v>
       </c>
@@ -9744,7 +9765,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="159" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A159" s="2">
         <v>2400003</v>
       </c>
@@ -9794,7 +9815,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="160" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A160" s="2">
         <v>2400003</v>
       </c>
@@ -9844,7 +9865,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="161" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A161" s="2">
         <v>2400008</v>
       </c>
@@ -9894,7 +9915,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="162" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A162" s="2">
         <v>2400008</v>
       </c>
@@ -9944,7 +9965,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="163" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A163" s="2">
         <v>2400008</v>
       </c>
@@ -9994,7 +10015,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="164" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A164" s="2">
         <v>2400012</v>
       </c>
@@ -10044,7 +10065,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="165" spans="1:18" ht="32" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A165" s="2">
         <v>2400012</v>
       </c>
@@ -10070,7 +10091,7 @@
         <v>21</v>
       </c>
       <c r="I165" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J165" t="s">
         <v>24</v>
@@ -10094,7 +10115,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="166" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A166" s="2">
         <v>2400012</v>
       </c>
@@ -10120,7 +10141,7 @@
         <v>21</v>
       </c>
       <c r="I166" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J166" t="s">
         <v>24</v>
@@ -10141,7 +10162,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="167" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A167" s="2">
         <v>2401001</v>
       </c>
@@ -10191,7 +10212,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="168" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A168" s="2">
         <v>2401001</v>
       </c>
@@ -10217,7 +10238,7 @@
         <v>12</v>
       </c>
       <c r="I168" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J168" t="s">
         <v>24</v>
@@ -10241,7 +10262,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="169" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A169" s="2">
         <v>2401001</v>
       </c>
@@ -10267,7 +10288,7 @@
         <v>12</v>
       </c>
       <c r="I169" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J169" t="s">
         <v>24</v>
@@ -10291,7 +10312,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="170" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A170" s="2">
         <v>2401007</v>
       </c>
@@ -10341,7 +10362,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="171" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A171" s="2">
         <v>2401007</v>
       </c>
@@ -10367,7 +10388,7 @@
         <v>12</v>
       </c>
       <c r="I171" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J171" t="s">
         <v>24</v>
@@ -10391,7 +10412,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="172" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A172" s="2">
         <v>2401007</v>
       </c>
@@ -10417,7 +10438,7 @@
         <v>12</v>
       </c>
       <c r="I172" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J172" t="s">
         <v>24</v>
@@ -10441,7 +10462,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="173" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A173" s="2">
         <v>2401013</v>
       </c>
@@ -10491,7 +10512,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="174" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A174" s="2">
         <v>2401013</v>
       </c>
@@ -10541,7 +10562,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="175" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A175" s="2">
         <v>2401013</v>
       </c>
@@ -10591,7 +10612,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="176" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A176" s="2">
         <v>2401018</v>
       </c>
@@ -10641,7 +10662,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="177" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A177" s="2">
         <v>2401018</v>
       </c>
@@ -10691,7 +10712,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="178" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A178" s="2">
         <v>2401018</v>
       </c>
@@ -10738,7 +10759,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="179" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A179" s="2">
         <v>2401018</v>
       </c>
@@ -10788,7 +10809,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="180" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A180" s="2">
         <v>2401018</v>
       </c>
@@ -10835,7 +10856,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="181" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A181" s="2">
         <v>2401018</v>
       </c>
@@ -10882,7 +10903,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="182" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A182" s="2">
         <v>2401018</v>
       </c>
@@ -10929,7 +10950,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="183" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A183" s="2">
         <v>2402003</v>
       </c>
@@ -10980,7 +11001,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="184" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A184" s="2">
         <v>2402003</v>
       </c>
@@ -11006,7 +11027,7 @@
         <v>12</v>
       </c>
       <c r="I184" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J184" t="s">
         <v>24</v>
@@ -11031,7 +11052,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="185" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A185" s="2">
         <v>2402003</v>
       </c>
@@ -11057,7 +11078,7 @@
         <v>12</v>
       </c>
       <c r="I185" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J185" t="s">
         <v>24</v>
@@ -11082,7 +11103,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="186" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A186" s="2">
         <v>2402008</v>
       </c>
@@ -11132,7 +11153,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="187" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A187" s="2">
         <v>2402008</v>
       </c>
@@ -11158,7 +11179,7 @@
         <v>12</v>
       </c>
       <c r="I187" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J187" t="s">
         <v>24</v>
@@ -11182,7 +11203,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="188" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A188" s="2">
         <v>2402008</v>
       </c>
@@ -11208,7 +11229,7 @@
         <v>12</v>
       </c>
       <c r="I188" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J188" t="s">
         <v>24</v>
@@ -11232,7 +11253,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="189" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A189" s="2">
         <v>2402015</v>
       </c>
@@ -11279,7 +11300,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="190" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A190" s="2">
         <v>2402015</v>
       </c>
@@ -11326,7 +11347,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="191" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A191" s="2">
         <v>2402015</v>
       </c>
@@ -11372,7 +11393,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="192" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A192" s="2">
         <v>2403004</v>
       </c>
@@ -11423,7 +11444,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="193" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A193" s="2">
         <v>2403004</v>
       </c>
@@ -11474,7 +11495,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="194" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A194" s="2">
         <v>2403004</v>
       </c>
@@ -11525,7 +11546,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="195" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A195" s="2">
         <v>2403009</v>
       </c>
@@ -11565,7 +11586,7 @@
       <c r="M195" t="s">
         <v>26</v>
       </c>
-      <c r="N195" s="8" t="s">
+      <c r="N195" s="10" t="s">
         <v>551</v>
       </c>
       <c r="Q195" t="s">
@@ -11575,7 +11596,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="196" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A196" s="2">
         <v>2403009</v>
       </c>
@@ -11615,7 +11636,7 @@
       <c r="M196" t="s">
         <v>26</v>
       </c>
-      <c r="N196" s="8" t="s">
+      <c r="N196" s="10" t="s">
         <v>552</v>
       </c>
       <c r="Q196" t="s">
@@ -11625,7 +11646,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="197" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A197" s="2">
         <v>2403009</v>
       </c>
@@ -11665,7 +11686,7 @@
       <c r="M197" t="s">
         <v>26</v>
       </c>
-      <c r="N197" s="8" t="s">
+      <c r="N197" s="10" t="s">
         <v>552</v>
       </c>
       <c r="Q197" t="s">
@@ -11675,7 +11696,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="198" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A198" s="2">
         <v>2403013</v>
       </c>
@@ -11722,7 +11743,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="199" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A199" s="2">
         <v>2403013</v>
       </c>
@@ -11748,7 +11769,7 @@
         <v>21</v>
       </c>
       <c r="I199" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J199" t="s">
         <v>24</v>
@@ -11769,7 +11790,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="200" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A200" s="2">
         <v>2403013</v>
       </c>
@@ -11795,7 +11816,7 @@
         <v>21</v>
       </c>
       <c r="I200" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J200" t="s">
         <v>24</v>
@@ -11816,7 +11837,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="201" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A201" s="2">
         <v>2404001</v>
       </c>
@@ -11866,7 +11887,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="202" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A202" s="2">
         <v>2404001</v>
       </c>
@@ -11916,7 +11937,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="203" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A203" s="2">
         <v>2404001</v>
       </c>
@@ -11966,7 +11987,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="204" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A204" s="2">
         <v>2404006</v>
       </c>
@@ -12016,7 +12037,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="205" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A205" s="2">
         <v>2404006</v>
       </c>
@@ -12066,7 +12087,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="206" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A206" s="2">
         <v>2404006</v>
       </c>
@@ -12116,7 +12137,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="207" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A207" s="2">
         <v>2404015</v>
       </c>
@@ -12163,7 +12184,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="208" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A208" s="2">
         <v>2404015</v>
       </c>
@@ -12210,7 +12231,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="209" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A209" s="2">
         <v>2404015</v>
       </c>
@@ -12257,7 +12278,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="210" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A210" s="2">
         <v>2405001</v>
       </c>
@@ -12307,7 +12328,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="211" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A211" s="2">
         <v>2405001</v>
       </c>
@@ -12357,7 +12378,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="212" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A212" s="2">
         <v>2405001</v>
       </c>
@@ -12407,7 +12428,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="213" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A213" s="2">
         <v>2405006</v>
       </c>
@@ -12457,7 +12478,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="214" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A214" s="2">
         <v>2405006</v>
       </c>
@@ -12507,7 +12528,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="215" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A215" s="2">
         <v>2405006</v>
       </c>
@@ -12557,7 +12578,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="216" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A216" s="2">
         <v>2405015</v>
       </c>
@@ -12607,7 +12628,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="217" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A217" s="2">
         <v>2405015</v>
       </c>
@@ -12633,7 +12654,7 @@
         <v>20</v>
       </c>
       <c r="I217" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J217" t="s">
         <v>24</v>
@@ -12657,7 +12678,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="218" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A218" s="2">
         <v>2405015</v>
       </c>
@@ -12683,7 +12704,7 @@
         <v>20</v>
       </c>
       <c r="I218" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J218" t="s">
         <v>24</v>
@@ -12704,7 +12725,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="219" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A219" s="2">
         <v>2406004</v>
       </c>
@@ -12754,7 +12775,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="220" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A220" s="2">
         <v>2406004</v>
       </c>
@@ -12780,7 +12801,7 @@
         <v>4</v>
       </c>
       <c r="I220" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J220" t="s">
         <v>24</v>
@@ -12804,7 +12825,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="221" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A221" s="2">
         <v>2406004</v>
       </c>
@@ -12854,7 +12875,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="222" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A222" s="2">
         <v>2406004</v>
       </c>
@@ -12880,7 +12901,7 @@
         <v>4</v>
       </c>
       <c r="I222" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J222" t="s">
         <v>24</v>
@@ -12904,7 +12925,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="223" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A223" s="2">
         <v>2406004</v>
       </c>
@@ -12954,7 +12975,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="224" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A224" s="2">
         <v>2406009</v>
       </c>
@@ -13004,7 +13025,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="225" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A225" s="2">
         <v>2406009</v>
       </c>
@@ -13030,7 +13051,7 @@
         <v>4</v>
       </c>
       <c r="I225" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J225" t="s">
         <v>24</v>
@@ -13054,7 +13075,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="226" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A226" s="2">
         <v>2406009</v>
       </c>
@@ -13104,7 +13125,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="227" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A227" s="2">
         <v>2406009</v>
       </c>
@@ -13130,7 +13151,7 @@
         <v>4</v>
       </c>
       <c r="I227" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J227" t="s">
         <v>24</v>
@@ -13154,7 +13175,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="228" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A228" s="2">
         <v>2406009</v>
       </c>
@@ -13204,7 +13225,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="229" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A229" s="2">
         <v>2406012</v>
       </c>
@@ -13251,7 +13272,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="230" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A230" s="2">
         <v>2406012</v>
       </c>
@@ -13298,7 +13319,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="231" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A231" s="2">
         <v>2406012</v>
       </c>
@@ -13345,7 +13366,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="232" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A232" s="2">
         <v>2059001</v>
       </c>
@@ -13392,7 +13413,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="233" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A233" s="2">
         <v>2059002</v>
       </c>
@@ -13439,7 +13460,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="234" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A234" s="2">
         <v>2059006</v>
       </c>
@@ -13486,7 +13507,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="235" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A235" s="2">
         <v>2140011</v>
       </c>
@@ -13533,7 +13554,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="236" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A236" s="2">
         <v>2390004</v>
       </c>
@@ -13580,7 +13601,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="237" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A237" s="2">
         <v>2390004</v>
       </c>
@@ -13606,7 +13627,7 @@
         <v>12</v>
       </c>
       <c r="I237" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J237" t="s">
         <v>24</v>
@@ -13627,7 +13648,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="238" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A238" s="2">
         <v>2390004</v>
       </c>
@@ -13653,7 +13674,7 @@
         <v>12</v>
       </c>
       <c r="I238" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J238" t="s">
         <v>24</v>
@@ -13674,7 +13695,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="239" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A239" s="2">
         <v>2390009</v>
       </c>
@@ -13721,7 +13742,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="240" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A240" s="2">
         <v>2390009</v>
       </c>
@@ -13747,7 +13768,7 @@
         <v>12</v>
       </c>
       <c r="I240" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J240" t="s">
         <v>24</v>
@@ -13768,7 +13789,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="241" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A241" s="2">
         <v>2390009</v>
       </c>
@@ -13794,7 +13815,7 @@
         <v>12</v>
       </c>
       <c r="I241" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J241" t="s">
         <v>24</v>
@@ -13815,7 +13836,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="242" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A242" s="2">
         <v>2390013</v>
       </c>
@@ -13859,7 +13880,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="243" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A243" s="2">
         <v>2390013</v>
       </c>
@@ -13903,7 +13924,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="244" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A244" s="2">
         <v>2390013</v>
       </c>
@@ -13947,7 +13968,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="252" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="L252" s="1"/>
     </row>
   </sheetData>

--- a/POD_2026-27_11-5-2026.xlsx
+++ b/POD_2026-27_11-5-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\misael.marriaga\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D2F840D-652E-439C-A8E7-C66348B1142B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CA4322D-4B47-42F9-84AA-ECB7F51BEC7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3046" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3051" uniqueCount="562">
   <si>
     <t>POD_2026-27_11-5-2026</t>
   </si>
@@ -1649,9 +1649,6 @@
     <t>ELIO VALERO (21)</t>
   </si>
   <si>
-    <t>ELIO VALERO (60)</t>
-  </si>
-  <si>
     <t>DAVID PUERTAS (40)</t>
   </si>
   <si>
@@ -1707,6 +1704,24 @@
   </si>
   <si>
     <t>Pedro J. Chocano (60)</t>
+  </si>
+  <si>
+    <t>María Elena Martínez (44)</t>
+  </si>
+  <si>
+    <t>María Elena Martínez (16)</t>
+  </si>
+  <si>
+    <t>María Elena Martínez (60)</t>
+  </si>
+  <si>
+    <t>María Elena Martínez (48)</t>
+  </si>
+  <si>
+    <t>María Elena Martínez (12)</t>
+  </si>
+  <si>
+    <t>ELIO VALERO TORANZO (60)</t>
   </si>
 </sst>
 </file>
@@ -2760,7 +2775,7 @@
         <v>26</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="Q14" t="s">
         <v>27</v>
@@ -2807,7 +2822,7 @@
         <v>26</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="Q15" t="s">
         <v>27</v>
@@ -2854,7 +2869,7 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="Q16" t="s">
         <v>27</v>
@@ -2901,7 +2916,7 @@
         <v>26</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="Q17" t="s">
         <v>27</v>
@@ -3148,7 +3163,7 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="Q22" t="s">
         <v>27</v>
@@ -3198,7 +3213,7 @@
         <v>26</v>
       </c>
       <c r="N23" s="6" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="Q23" t="s">
         <v>27</v>
@@ -3248,7 +3263,7 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="Q24" t="s">
         <v>27</v>
@@ -3298,7 +3313,7 @@
         <v>26</v>
       </c>
       <c r="N25" s="6" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="Q25" t="s">
         <v>27</v>
@@ -3348,7 +3363,7 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="Q26" t="s">
         <v>27</v>
@@ -3398,7 +3413,7 @@
         <v>26</v>
       </c>
       <c r="N27" s="6" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="Q27" t="s">
         <v>27</v>
@@ -3448,7 +3463,7 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="Q28" t="s">
         <v>27</v>
@@ -3495,7 +3510,7 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="Q29" t="s">
         <v>27</v>
@@ -3545,7 +3560,7 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="Q30" t="s">
         <v>27</v>
@@ -4183,10 +4198,10 @@
         <v>26</v>
       </c>
       <c r="N43" t="s">
+        <v>552</v>
+      </c>
+      <c r="O43" t="s">
         <v>553</v>
-      </c>
-      <c r="O43" t="s">
-        <v>554</v>
       </c>
       <c r="Q43" t="s">
         <v>27</v>
@@ -4239,7 +4254,7 @@
         <v>177</v>
       </c>
       <c r="O44" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q44" t="s">
         <v>27</v>
@@ -4439,7 +4454,7 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="Q48" t="s">
         <v>27</v>
@@ -4489,7 +4504,7 @@
         <v>26</v>
       </c>
       <c r="N49" s="6" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="Q49" t="s">
         <v>27</v>
@@ -4539,7 +4554,7 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="Q50" t="s">
         <v>27</v>
@@ -4739,7 +4754,7 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="Q54" t="s">
         <v>27</v>
@@ -4789,7 +4804,7 @@
         <v>26</v>
       </c>
       <c r="N55" s="6" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="Q55" t="s">
         <v>27</v>
@@ -4839,7 +4854,7 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="Q56" t="s">
         <v>27</v>
@@ -4888,6 +4903,9 @@
       <c r="M57" t="s">
         <v>26</v>
       </c>
+      <c r="N57" s="6" t="s">
+        <v>556</v>
+      </c>
       <c r="Q57" t="s">
         <v>27</v>
       </c>
@@ -4935,6 +4953,9 @@
       <c r="M58" t="s">
         <v>26</v>
       </c>
+      <c r="N58" s="6" t="s">
+        <v>557</v>
+      </c>
       <c r="Q58" t="s">
         <v>27</v>
       </c>
@@ -5171,7 +5192,7 @@
         <v>26</v>
       </c>
       <c r="N63" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="Q63" t="s">
         <v>27</v>
@@ -5224,7 +5245,7 @@
         <v>501</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="Q64" t="s">
         <v>27</v>
@@ -5412,7 +5433,7 @@
         <v>26</v>
       </c>
       <c r="N68" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="Q68" t="s">
         <v>27</v>
@@ -5459,7 +5480,7 @@
         <v>26</v>
       </c>
       <c r="N69" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="Q69" t="s">
         <v>27</v>
@@ -5506,7 +5527,7 @@
         <v>26</v>
       </c>
       <c r="N70" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="Q70" t="s">
         <v>27</v>
@@ -5888,6 +5909,9 @@
       <c r="M78" t="s">
         <v>26</v>
       </c>
+      <c r="N78" s="6" t="s">
+        <v>561</v>
+      </c>
       <c r="Q78" t="s">
         <v>27</v>
       </c>
@@ -6039,7 +6063,7 @@
         <v>26</v>
       </c>
       <c r="N81" s="6" t="s">
-        <v>537</v>
+        <v>558</v>
       </c>
       <c r="Q81" t="s">
         <v>27</v>
@@ -7282,7 +7306,7 @@
         <v>26</v>
       </c>
       <c r="N107" s="3" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="Q107" t="s">
         <v>27</v>
@@ -8305,7 +8329,7 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="Q128" t="s">
         <v>27</v>
@@ -8355,7 +8379,7 @@
         <v>26</v>
       </c>
       <c r="N129" s="6" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="Q129" t="s">
         <v>27</v>
@@ -8405,7 +8429,7 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="Q130" t="s">
         <v>27</v>
@@ -9048,7 +9072,7 @@
         <v>26</v>
       </c>
       <c r="N143" s="6" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="Q143" t="s">
         <v>27</v>
@@ -9098,7 +9122,7 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="Q144" t="s">
         <v>27</v>
@@ -9148,7 +9172,7 @@
         <v>26</v>
       </c>
       <c r="N145" s="6" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="Q145" t="s">
         <v>27</v>
@@ -9335,6 +9359,9 @@
       <c r="M149" t="s">
         <v>26</v>
       </c>
+      <c r="N149" t="s">
+        <v>559</v>
+      </c>
       <c r="Q149" t="s">
         <v>27</v>
       </c>
@@ -9429,6 +9456,9 @@
       <c r="M151" t="s">
         <v>26</v>
       </c>
+      <c r="N151" t="s">
+        <v>560</v>
+      </c>
       <c r="Q151" t="s">
         <v>27</v>
       </c>
@@ -11587,7 +11617,7 @@
         <v>26</v>
       </c>
       <c r="N195" s="10" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="Q195" t="s">
         <v>27</v>
@@ -11637,7 +11667,7 @@
         <v>26</v>
       </c>
       <c r="N196" s="10" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="Q196" t="s">
         <v>27</v>
@@ -11687,7 +11717,7 @@
         <v>26</v>
       </c>
       <c r="N197" s="10" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="Q197" t="s">
         <v>27</v>
@@ -13016,7 +13046,7 @@
         <v>26</v>
       </c>
       <c r="N224" s="6" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="Q224" t="s">
         <v>27</v>
@@ -13066,7 +13096,7 @@
         <v>26</v>
       </c>
       <c r="N225" s="6" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="Q225" t="s">
         <v>27</v>
@@ -13116,7 +13146,7 @@
         <v>26</v>
       </c>
       <c r="N226" s="6" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="Q226" t="s">
         <v>27</v>
@@ -13166,7 +13196,7 @@
         <v>26</v>
       </c>
       <c r="N227" s="6" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="Q227" t="s">
         <v>27</v>
@@ -13216,7 +13246,7 @@
         <v>26</v>
       </c>
       <c r="N228" s="6" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="Q228" t="s">
         <v>27</v>

--- a/POD_2026-27_11-5-2026.xlsx
+++ b/POD_2026-27_11-5-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\misael.marriaga\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CA4322D-4B47-42F9-84AA-ECB7F51BEC7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BFEF0A3-E988-49E5-BDEC-9061709A1364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3051" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3052" uniqueCount="562">
   <si>
     <t>POD_2026-27_11-5-2026</t>
   </si>
@@ -1715,13 +1715,13 @@
     <t>María Elena Martínez (60)</t>
   </si>
   <si>
-    <t>María Elena Martínez (48)</t>
-  </si>
-  <si>
-    <t>María Elena Martínez (12)</t>
-  </si>
-  <si>
     <t>ELIO VALERO TORANZO (60)</t>
+  </si>
+  <si>
+    <t>María Elena Martínez (24)</t>
+  </si>
+  <si>
+    <t>María Elena Martínez (6)</t>
   </si>
 </sst>
 </file>
@@ -5910,7 +5910,7 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="Q78" t="s">
         <v>27</v>
@@ -9360,7 +9360,7 @@
         <v>26</v>
       </c>
       <c r="N149" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="Q149" t="s">
         <v>27</v>
@@ -9409,6 +9409,9 @@
       <c r="M150" t="s">
         <v>26</v>
       </c>
+      <c r="N150" t="s">
+        <v>561</v>
+      </c>
       <c r="Q150" t="s">
         <v>27</v>
       </c>
@@ -9457,7 +9460,7 @@
         <v>26</v>
       </c>
       <c r="N151" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="Q151" t="s">
         <v>27</v>

--- a/POD_2026-27_11-5-2026.xlsx
+++ b/POD_2026-27_11-5-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\misael.marriaga\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BFEF0A3-E988-49E5-BDEC-9061709A1364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE43F609-E4CB-404E-AAFA-662B8771FB2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1649,6 +1649,9 @@
     <t>ELIO VALERO (21)</t>
   </si>
   <si>
+    <t>ELIO VALERO (60)</t>
+  </si>
+  <si>
     <t>DAVID PUERTAS (40)</t>
   </si>
   <si>
@@ -1713,9 +1716,6 @@
   </si>
   <si>
     <t>María Elena Martínez (60)</t>
-  </si>
-  <si>
-    <t>ELIO VALERO TORANZO (60)</t>
   </si>
   <si>
     <t>María Elena Martínez (24)</t>
@@ -2775,7 +2775,7 @@
         <v>26</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="Q14" t="s">
         <v>27</v>
@@ -2822,7 +2822,7 @@
         <v>26</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="Q15" t="s">
         <v>27</v>
@@ -2869,7 +2869,7 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="Q16" t="s">
         <v>27</v>
@@ -2916,7 +2916,7 @@
         <v>26</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="Q17" t="s">
         <v>27</v>
@@ -3163,7 +3163,7 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="Q22" t="s">
         <v>27</v>
@@ -3213,7 +3213,7 @@
         <v>26</v>
       </c>
       <c r="N23" s="6" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="Q23" t="s">
         <v>27</v>
@@ -3263,7 +3263,7 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="Q24" t="s">
         <v>27</v>
@@ -3313,7 +3313,7 @@
         <v>26</v>
       </c>
       <c r="N25" s="6" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="Q25" t="s">
         <v>27</v>
@@ -3363,7 +3363,7 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="Q26" t="s">
         <v>27</v>
@@ -3413,7 +3413,7 @@
         <v>26</v>
       </c>
       <c r="N27" s="6" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="Q27" t="s">
         <v>27</v>
@@ -3463,7 +3463,7 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="Q28" t="s">
         <v>27</v>
@@ -3510,7 +3510,7 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="Q29" t="s">
         <v>27</v>
@@ -3560,7 +3560,7 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="Q30" t="s">
         <v>27</v>
@@ -4198,10 +4198,10 @@
         <v>26</v>
       </c>
       <c r="N43" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="O43" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="Q43" t="s">
         <v>27</v>
@@ -4254,7 +4254,7 @@
         <v>177</v>
       </c>
       <c r="O44" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="Q44" t="s">
         <v>27</v>
@@ -4454,7 +4454,7 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="Q48" t="s">
         <v>27</v>
@@ -4504,7 +4504,7 @@
         <v>26</v>
       </c>
       <c r="N49" s="6" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="Q49" t="s">
         <v>27</v>
@@ -4554,7 +4554,7 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="Q50" t="s">
         <v>27</v>
@@ -4754,7 +4754,7 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="Q54" t="s">
         <v>27</v>
@@ -4804,7 +4804,7 @@
         <v>26</v>
       </c>
       <c r="N55" s="6" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="Q55" t="s">
         <v>27</v>
@@ -4854,7 +4854,7 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="Q56" t="s">
         <v>27</v>
@@ -4904,7 +4904,7 @@
         <v>26</v>
       </c>
       <c r="N57" s="6" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="Q57" t="s">
         <v>27</v>
@@ -4954,7 +4954,7 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="Q58" t="s">
         <v>27</v>
@@ -5192,7 +5192,7 @@
         <v>26</v>
       </c>
       <c r="N63" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="Q63" t="s">
         <v>27</v>
@@ -5245,7 +5245,7 @@
         <v>501</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="Q64" t="s">
         <v>27</v>
@@ -5433,7 +5433,7 @@
         <v>26</v>
       </c>
       <c r="N68" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="Q68" t="s">
         <v>27</v>
@@ -5480,7 +5480,7 @@
         <v>26</v>
       </c>
       <c r="N69" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="Q69" t="s">
         <v>27</v>
@@ -5527,7 +5527,7 @@
         <v>26</v>
       </c>
       <c r="N70" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="Q70" t="s">
         <v>27</v>
@@ -5910,7 +5910,7 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>559</v>
+        <v>537</v>
       </c>
       <c r="Q78" t="s">
         <v>27</v>
@@ -6063,7 +6063,7 @@
         <v>26</v>
       </c>
       <c r="N81" s="6" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="Q81" t="s">
         <v>27</v>
@@ -7306,7 +7306,7 @@
         <v>26</v>
       </c>
       <c r="N107" s="3" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="Q107" t="s">
         <v>27</v>
@@ -8329,7 +8329,7 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="Q128" t="s">
         <v>27</v>
@@ -8379,7 +8379,7 @@
         <v>26</v>
       </c>
       <c r="N129" s="6" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="Q129" t="s">
         <v>27</v>
@@ -8429,7 +8429,7 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="Q130" t="s">
         <v>27</v>
@@ -9072,7 +9072,7 @@
         <v>26</v>
       </c>
       <c r="N143" s="6" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="Q143" t="s">
         <v>27</v>
@@ -9122,7 +9122,7 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="Q144" t="s">
         <v>27</v>
@@ -9172,7 +9172,7 @@
         <v>26</v>
       </c>
       <c r="N145" s="6" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="Q145" t="s">
         <v>27</v>
@@ -11620,7 +11620,7 @@
         <v>26</v>
       </c>
       <c r="N195" s="10" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="Q195" t="s">
         <v>27</v>
@@ -11670,7 +11670,7 @@
         <v>26</v>
       </c>
       <c r="N196" s="10" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="Q196" t="s">
         <v>27</v>
@@ -11720,7 +11720,7 @@
         <v>26</v>
       </c>
       <c r="N197" s="10" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="Q197" t="s">
         <v>27</v>
@@ -13049,7 +13049,7 @@
         <v>26</v>
       </c>
       <c r="N224" s="6" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="Q224" t="s">
         <v>27</v>
@@ -13099,7 +13099,7 @@
         <v>26</v>
       </c>
       <c r="N225" s="6" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="Q225" t="s">
         <v>27</v>
@@ -13149,7 +13149,7 @@
         <v>26</v>
       </c>
       <c r="N226" s="6" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="Q226" t="s">
         <v>27</v>
@@ -13199,7 +13199,7 @@
         <v>26</v>
       </c>
       <c r="N227" s="6" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="Q227" t="s">
         <v>27</v>
@@ -13249,7 +13249,7 @@
         <v>26</v>
       </c>
       <c r="N228" s="6" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="Q228" t="s">
         <v>27</v>

--- a/POD_2026-27_11-5-2026.xlsx
+++ b/POD_2026-27_11-5-2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10811"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\misael.marriaga\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guillermo.vera/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE43F609-E4CB-404E-AAFA-662B8771FB2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18346B4A-B481-9A43-899E-B98F11024DF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17260" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="POD" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3052" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3052" uniqueCount="563">
   <si>
     <t>POD_2026-27_11-5-2026</t>
   </si>
@@ -1722,6 +1722,9 @@
   </si>
   <si>
     <t>María Elena Martínez (6)</t>
+  </si>
+  <si>
+    <t>M=&gt;(20:00-22:00)[22/09/26, 29/09/26, 06/10/26, 20/10/26, 27/10/26, 10/11/26, 17/11/26, 24/11/26]</t>
   </si>
 </sst>
 </file>
@@ -1794,12 +1797,12 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1818,9 +1821,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1858,7 +1861,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1964,7 +1967,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2106,7 +2109,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2115,53 +2118,53 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S252"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="71.26953125" customWidth="1"/>
+    <col min="2" max="2" width="71.33203125" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="9.1796875" customWidth="1"/>
-    <col min="5" max="5" width="20.1796875" customWidth="1"/>
-    <col min="6" max="6" width="64.1796875" customWidth="1"/>
-    <col min="7" max="7" width="20.81640625" customWidth="1"/>
-    <col min="8" max="8" width="6.453125" customWidth="1"/>
-    <col min="9" max="9" width="7.81640625" customWidth="1"/>
-    <col min="10" max="10" width="6.453125" customWidth="1"/>
-    <col min="11" max="11" width="107.1796875" customWidth="1"/>
-    <col min="12" max="12" width="53.7265625" customWidth="1"/>
-    <col min="13" max="13" width="12.7265625" customWidth="1"/>
-    <col min="14" max="14" width="36.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="36.453125" customWidth="1"/>
-    <col min="16" max="16" width="20.81640625" customWidth="1"/>
+    <col min="4" max="4" width="9.1640625" customWidth="1"/>
+    <col min="5" max="5" width="20.1640625" customWidth="1"/>
+    <col min="6" max="6" width="64.1640625" customWidth="1"/>
+    <col min="7" max="7" width="20.83203125" customWidth="1"/>
+    <col min="8" max="8" width="6.5" customWidth="1"/>
+    <col min="9" max="9" width="7.83203125" customWidth="1"/>
+    <col min="10" max="10" width="6.5" customWidth="1"/>
+    <col min="11" max="11" width="107.1640625" customWidth="1"/>
+    <col min="12" max="12" width="53.6640625" customWidth="1"/>
+    <col min="13" max="13" width="12.6640625" customWidth="1"/>
+    <col min="14" max="14" width="36.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="36.5" customWidth="1"/>
+    <col min="16" max="16" width="20.83203125" customWidth="1"/>
     <col min="17" max="17" width="52" customWidth="1"/>
-    <col min="18" max="18" width="32.453125" customWidth="1"/>
-    <col min="19" max="19" width="16.81640625" customWidth="1"/>
+    <col min="18" max="18" width="32.5" customWidth="1"/>
+    <col min="19" max="19" width="16.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
-      <c r="O1" s="8"/>
-      <c r="P1" s="8"/>
-      <c r="Q1" s="8"/>
-      <c r="R1" s="8"/>
-      <c r="S1" s="8"/>
-    </row>
-    <row r="2" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+      <c r="S1" s="10"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2220,7 +2223,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>2291005</v>
       </c>
@@ -2264,7 +2267,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>2291009</v>
       </c>
@@ -2308,7 +2311,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>2240005</v>
       </c>
@@ -2355,7 +2358,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>2240009</v>
       </c>
@@ -2402,7 +2405,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>2251011</v>
       </c>
@@ -2446,7 +2449,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>2327002</v>
       </c>
@@ -2493,7 +2496,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>2327002</v>
       </c>
@@ -2540,7 +2543,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>2327002</v>
       </c>
@@ -2587,7 +2590,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>2327007</v>
       </c>
@@ -2637,7 +2640,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>2327007</v>
       </c>
@@ -2687,7 +2690,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>2327007</v>
       </c>
@@ -2737,7 +2740,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>2327015</v>
       </c>
@@ -2784,7 +2787,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>2327015</v>
       </c>
@@ -2831,7 +2834,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>2327015</v>
       </c>
@@ -2878,7 +2881,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>2360001</v>
       </c>
@@ -2925,7 +2928,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>2360002</v>
       </c>
@@ -2972,7 +2975,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>2382005</v>
       </c>
@@ -3022,7 +3025,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>2382005</v>
       </c>
@@ -3072,7 +3075,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>2382005</v>
       </c>
@@ -3122,7 +3125,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>2382005</v>
       </c>
@@ -3172,7 +3175,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>2382005</v>
       </c>
@@ -3222,7 +3225,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>2382005</v>
       </c>
@@ -3272,7 +3275,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>2382010</v>
       </c>
@@ -3322,7 +3325,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>2382010</v>
       </c>
@@ -3372,7 +3375,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>2382010</v>
       </c>
@@ -3422,7 +3425,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>2382010</v>
       </c>
@@ -3472,7 +3475,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>2382010</v>
       </c>
@@ -3509,7 +3512,7 @@
       <c r="M29" t="s">
         <v>26</v>
       </c>
-      <c r="N29" s="9" t="s">
+      <c r="N29" s="7" t="s">
         <v>550</v>
       </c>
       <c r="Q29" t="s">
@@ -3519,7 +3522,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>2382010</v>
       </c>
@@ -3569,7 +3572,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>2383001</v>
       </c>
@@ -3619,7 +3622,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>2383001</v>
       </c>
@@ -3666,7 +3669,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>2383001</v>
       </c>
@@ -3713,7 +3716,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>2383001</v>
       </c>
@@ -3763,7 +3766,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>2383001</v>
       </c>
@@ -3813,7 +3816,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>2383001</v>
       </c>
@@ -3863,7 +3866,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>2383002</v>
       </c>
@@ -3913,7 +3916,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>2383002</v>
       </c>
@@ -3960,7 +3963,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>2383002</v>
       </c>
@@ -4007,7 +4010,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>2383002</v>
       </c>
@@ -4057,7 +4060,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>2383002</v>
       </c>
@@ -4107,7 +4110,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>2383002</v>
       </c>
@@ -4157,7 +4160,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:18" ht="48" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>2383007</v>
       </c>
@@ -4210,7 +4213,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:18" ht="48" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>2383007</v>
       </c>
@@ -4263,7 +4266,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>2384001</v>
       </c>
@@ -4313,7 +4316,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>2384001</v>
       </c>
@@ -4363,7 +4366,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>2384001</v>
       </c>
@@ -4413,7 +4416,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
         <v>2384005</v>
       </c>
@@ -4463,7 +4466,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
         <v>2384005</v>
       </c>
@@ -4513,7 +4516,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
         <v>2384005</v>
       </c>
@@ -4563,7 +4566,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="51" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
         <v>2385001</v>
       </c>
@@ -4613,7 +4616,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="52" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
         <v>2385001</v>
       </c>
@@ -4663,7 +4666,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="53" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
         <v>2385001</v>
       </c>
@@ -4713,7 +4716,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
         <v>2385005</v>
       </c>
@@ -4763,7 +4766,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
         <v>2385005</v>
       </c>
@@ -4813,7 +4816,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="56" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
         <v>2385005</v>
       </c>
@@ -4863,7 +4866,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="57" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
         <v>2386001</v>
       </c>
@@ -4913,7 +4916,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="58" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
         <v>2386001</v>
       </c>
@@ -4963,7 +4966,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="59" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
         <v>2386001</v>
       </c>
@@ -5010,7 +5013,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="60" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
         <v>2386001</v>
       </c>
@@ -5057,7 +5060,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="61" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
         <v>2386001</v>
       </c>
@@ -5104,7 +5107,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="62" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
         <v>2386001</v>
       </c>
@@ -5136,7 +5139,7 @@
         <v>41</v>
       </c>
       <c r="K62" s="6" t="s">
-        <v>527</v>
+        <v>562</v>
       </c>
       <c r="L62" t="s">
         <v>133</v>
@@ -5151,7 +5154,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="63" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
         <v>2386002</v>
       </c>
@@ -5201,7 +5204,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="64" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
         <v>2386002</v>
       </c>
@@ -5254,7 +5257,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="65" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
         <v>2387009</v>
       </c>
@@ -5301,7 +5304,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="66" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
         <v>2387009</v>
       </c>
@@ -5348,7 +5351,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="67" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
         <v>2387009</v>
       </c>
@@ -5395,7 +5398,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="68" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
         <v>2387016</v>
       </c>
@@ -5442,7 +5445,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="69" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
         <v>2387016</v>
       </c>
@@ -5489,7 +5492,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="70" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
         <v>2387016</v>
       </c>
@@ -5536,7 +5539,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="71" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
         <v>2265020</v>
       </c>
@@ -5584,7 +5587,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="72" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
         <v>2029018</v>
       </c>
@@ -5631,7 +5634,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="73" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
         <v>2030013</v>
       </c>
@@ -5678,7 +5681,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="74" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
         <v>2031001</v>
       </c>
@@ -5722,7 +5725,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="75" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
         <v>2032001</v>
       </c>
@@ -5772,7 +5775,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="76" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
         <v>2032007</v>
       </c>
@@ -5822,7 +5825,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="77" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
         <v>2032009</v>
       </c>
@@ -5869,7 +5872,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="78" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
         <v>2033001</v>
       </c>
@@ -5919,7 +5922,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="79" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
         <v>2033002</v>
       </c>
@@ -5972,7 +5975,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="80" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
         <v>2033006</v>
       </c>
@@ -6022,7 +6025,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="81" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
         <v>2034001</v>
       </c>
@@ -6072,7 +6075,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="82" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
         <v>2034002</v>
       </c>
@@ -6125,7 +6128,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="83" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
         <v>2034006</v>
       </c>
@@ -6175,7 +6178,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="84" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
         <v>2061001</v>
       </c>
@@ -6219,7 +6222,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="85" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
         <v>2061002</v>
       </c>
@@ -6266,7 +6269,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="86" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
         <v>2061006</v>
       </c>
@@ -6310,7 +6313,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="87" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
         <v>2107013</v>
       </c>
@@ -6357,7 +6360,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="88" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
         <v>2143016</v>
       </c>
@@ -6404,7 +6407,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="89" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
         <v>2148011</v>
       </c>
@@ -6448,7 +6451,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="90" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
         <v>2175020</v>
       </c>
@@ -6495,7 +6498,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="91" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
         <v>2285005</v>
       </c>
@@ -6545,7 +6548,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="92" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
         <v>2285006</v>
       </c>
@@ -6592,7 +6595,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="93" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
         <v>2285007</v>
       </c>
@@ -6639,7 +6642,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="94" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
         <v>2286015</v>
       </c>
@@ -6683,7 +6686,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="95" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
         <v>2338044</v>
       </c>
@@ -6727,7 +6730,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="96" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
         <v>2342014</v>
       </c>
@@ -6774,7 +6777,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="97" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
         <v>5</v>
       </c>
@@ -6822,7 +6825,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="98" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
         <v>2343027</v>
       </c>
@@ -6870,7 +6873,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="99" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
         <v>2343027</v>
       </c>
@@ -6917,7 +6920,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="100" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
         <v>2343027</v>
       </c>
@@ -6963,7 +6966,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="101" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
         <v>2347001</v>
       </c>
@@ -7013,7 +7016,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="102" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
         <v>2347003</v>
       </c>
@@ -7063,7 +7066,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="103" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
         <v>2347005</v>
       </c>
@@ -7114,7 +7117,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="104" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A104" s="2">
         <v>2347006</v>
       </c>
@@ -7164,7 +7167,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="105" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A105" s="2">
         <v>2347007</v>
       </c>
@@ -7215,7 +7218,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="106" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A106" s="2">
         <v>2347013</v>
       </c>
@@ -7265,7 +7268,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="107" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A107" s="2">
         <v>2347014</v>
       </c>
@@ -7315,7 +7318,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="108" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A108" s="2">
         <v>2347017</v>
       </c>
@@ -7365,7 +7368,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="109" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A109" s="2">
         <v>2347030</v>
       </c>
@@ -7416,7 +7419,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="110" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A110" s="2">
         <v>2347021</v>
       </c>
@@ -7466,7 +7469,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="111" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A111" s="2">
         <v>2347022</v>
       </c>
@@ -7518,7 +7521,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="112" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A112" s="2">
         <v>2347024</v>
       </c>
@@ -7568,7 +7571,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="113" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A113" s="2">
         <v>2347026</v>
       </c>
@@ -7619,7 +7622,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="114" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A114" s="2">
         <v>2347027</v>
       </c>
@@ -7670,7 +7673,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="115" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A115" s="2">
         <v>2347029</v>
       </c>
@@ -7720,7 +7723,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="116" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A116" s="2">
         <v>2347031</v>
       </c>
@@ -7770,7 +7773,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="117" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A117" s="2">
         <v>2347038</v>
       </c>
@@ -7821,7 +7824,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="118" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A118" s="2">
         <v>2361002</v>
       </c>
@@ -7868,7 +7871,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="119" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A119" s="2">
         <v>2361002</v>
       </c>
@@ -7915,7 +7918,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="120" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A120" s="2">
         <v>2361002</v>
       </c>
@@ -7959,7 +7962,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="121" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A121" s="2">
         <v>2361004</v>
       </c>
@@ -8006,7 +8009,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="122" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A122" s="2">
         <v>2393002</v>
       </c>
@@ -8053,7 +8056,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="123" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A123" s="2">
         <v>2393002</v>
       </c>
@@ -8100,7 +8103,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="124" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A124" s="2">
         <v>2393002</v>
       </c>
@@ -8147,7 +8150,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="125" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A125" s="2">
         <v>2394004</v>
       </c>
@@ -8194,7 +8197,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="126" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A126" s="2">
         <v>2394004</v>
       </c>
@@ -8241,7 +8244,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="127" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A127" s="2">
         <v>2394004</v>
       </c>
@@ -8288,7 +8291,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="128" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A128" s="2">
         <v>2395003</v>
       </c>
@@ -8338,7 +8341,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="129" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A129" s="2">
         <v>2395003</v>
       </c>
@@ -8388,7 +8391,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="130" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A130" s="2">
         <v>2395003</v>
       </c>
@@ -8438,7 +8441,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="131" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A131" s="2">
         <v>2396001</v>
       </c>
@@ -8488,7 +8491,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="132" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A132" s="2">
         <v>2396001</v>
       </c>
@@ -8538,7 +8541,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="133" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A133" s="2">
         <v>2396001</v>
       </c>
@@ -8588,7 +8591,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="134" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A134" s="2">
         <v>2397003</v>
       </c>
@@ -8638,7 +8641,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="135" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A135" s="2">
         <v>2397003</v>
       </c>
@@ -8688,7 +8691,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="136" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A136" s="2">
         <v>2397003</v>
       </c>
@@ -8738,7 +8741,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="137" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A137" s="2">
         <v>2397008</v>
       </c>
@@ -8785,7 +8788,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="138" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A138" s="2">
         <v>2397008</v>
       </c>
@@ -8832,7 +8835,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="139" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A139" s="2">
         <v>2397008</v>
       </c>
@@ -8879,7 +8882,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="140" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A140" s="2">
         <v>2398001</v>
       </c>
@@ -8929,7 +8932,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="141" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A141" s="2">
         <v>2398001</v>
       </c>
@@ -8980,7 +8983,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="142" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A142" s="2">
         <v>2398001</v>
       </c>
@@ -9031,7 +9034,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="143" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A143" s="2">
         <v>2398006</v>
       </c>
@@ -9081,7 +9084,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="144" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A144" s="2">
         <v>2398006</v>
       </c>
@@ -9131,7 +9134,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="145" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A145" s="2">
         <v>2398006</v>
       </c>
@@ -9181,7 +9184,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="146" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A146" s="2">
         <v>2398013</v>
       </c>
@@ -9228,7 +9231,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="147" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A147" s="2">
         <v>2398013</v>
       </c>
@@ -9275,7 +9278,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="148" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A148" s="2">
         <v>2398013</v>
       </c>
@@ -9319,7 +9322,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="149" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A149" s="2">
         <v>2399003</v>
       </c>
@@ -9369,7 +9372,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="150" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A150" s="2">
         <v>2399003</v>
       </c>
@@ -9419,7 +9422,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="151" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A151" s="2">
         <v>2399003</v>
       </c>
@@ -9469,7 +9472,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="152" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A152" s="2">
         <v>2399010</v>
       </c>
@@ -9516,7 +9519,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="153" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A153" s="2">
         <v>2399010</v>
       </c>
@@ -9563,7 +9566,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="154" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A154" s="2">
         <v>2399010</v>
       </c>
@@ -9610,7 +9613,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="155" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A155" s="2">
         <v>2399014</v>
       </c>
@@ -9657,7 +9660,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="156" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A156" s="2">
         <v>2399014</v>
       </c>
@@ -9704,7 +9707,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="157" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A157" s="2">
         <v>2399014</v>
       </c>
@@ -9748,7 +9751,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="158" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A158" s="2">
         <v>2400003</v>
       </c>
@@ -9798,7 +9801,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="159" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A159" s="2">
         <v>2400003</v>
       </c>
@@ -9848,7 +9851,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="160" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A160" s="2">
         <v>2400003</v>
       </c>
@@ -9898,7 +9901,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="161" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A161" s="2">
         <v>2400008</v>
       </c>
@@ -9948,7 +9951,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="162" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A162" s="2">
         <v>2400008</v>
       </c>
@@ -9998,7 +10001,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="163" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A163" s="2">
         <v>2400008</v>
       </c>
@@ -10048,7 +10051,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="164" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A164" s="2">
         <v>2400012</v>
       </c>
@@ -10098,7 +10101,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="165" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:18" ht="32" x14ac:dyDescent="0.2">
       <c r="A165" s="2">
         <v>2400012</v>
       </c>
@@ -10148,7 +10151,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="166" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A166" s="2">
         <v>2400012</v>
       </c>
@@ -10195,7 +10198,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="167" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A167" s="2">
         <v>2401001</v>
       </c>
@@ -10245,7 +10248,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="168" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A168" s="2">
         <v>2401001</v>
       </c>
@@ -10295,7 +10298,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="169" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A169" s="2">
         <v>2401001</v>
       </c>
@@ -10345,7 +10348,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="170" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A170" s="2">
         <v>2401007</v>
       </c>
@@ -10395,7 +10398,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="171" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A171" s="2">
         <v>2401007</v>
       </c>
@@ -10445,7 +10448,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="172" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A172" s="2">
         <v>2401007</v>
       </c>
@@ -10495,7 +10498,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="173" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A173" s="2">
         <v>2401013</v>
       </c>
@@ -10545,7 +10548,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="174" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A174" s="2">
         <v>2401013</v>
       </c>
@@ -10595,7 +10598,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="175" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A175" s="2">
         <v>2401013</v>
       </c>
@@ -10645,7 +10648,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="176" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A176" s="2">
         <v>2401018</v>
       </c>
@@ -10695,7 +10698,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="177" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A177" s="2">
         <v>2401018</v>
       </c>
@@ -10745,7 +10748,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="178" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A178" s="2">
         <v>2401018</v>
       </c>
@@ -10792,7 +10795,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="179" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A179" s="2">
         <v>2401018</v>
       </c>
@@ -10842,7 +10845,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="180" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A180" s="2">
         <v>2401018</v>
       </c>
@@ -10889,7 +10892,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="181" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A181" s="2">
         <v>2401018</v>
       </c>
@@ -10936,7 +10939,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="182" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A182" s="2">
         <v>2401018</v>
       </c>
@@ -10983,7 +10986,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="183" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A183" s="2">
         <v>2402003</v>
       </c>
@@ -11034,7 +11037,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="184" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A184" s="2">
         <v>2402003</v>
       </c>
@@ -11085,7 +11088,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="185" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A185" s="2">
         <v>2402003</v>
       </c>
@@ -11136,7 +11139,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="186" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A186" s="2">
         <v>2402008</v>
       </c>
@@ -11186,7 +11189,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="187" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A187" s="2">
         <v>2402008</v>
       </c>
@@ -11236,7 +11239,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="188" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A188" s="2">
         <v>2402008</v>
       </c>
@@ -11286,7 +11289,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="189" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A189" s="2">
         <v>2402015</v>
       </c>
@@ -11333,7 +11336,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="190" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A190" s="2">
         <v>2402015</v>
       </c>
@@ -11380,7 +11383,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="191" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A191" s="2">
         <v>2402015</v>
       </c>
@@ -11426,7 +11429,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="192" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A192" s="2">
         <v>2403004</v>
       </c>
@@ -11477,7 +11480,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="193" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A193" s="2">
         <v>2403004</v>
       </c>
@@ -11528,7 +11531,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="194" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A194" s="2">
         <v>2403004</v>
       </c>
@@ -11579,7 +11582,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="195" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A195" s="2">
         <v>2403009</v>
       </c>
@@ -11619,7 +11622,7 @@
       <c r="M195" t="s">
         <v>26</v>
       </c>
-      <c r="N195" s="10" t="s">
+      <c r="N195" s="8" t="s">
         <v>551</v>
       </c>
       <c r="Q195" t="s">
@@ -11629,7 +11632,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="196" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A196" s="2">
         <v>2403009</v>
       </c>
@@ -11669,7 +11672,7 @@
       <c r="M196" t="s">
         <v>26</v>
       </c>
-      <c r="N196" s="10" t="s">
+      <c r="N196" s="8" t="s">
         <v>552</v>
       </c>
       <c r="Q196" t="s">
@@ -11679,7 +11682,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="197" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A197" s="2">
         <v>2403009</v>
       </c>
@@ -11719,7 +11722,7 @@
       <c r="M197" t="s">
         <v>26</v>
       </c>
-      <c r="N197" s="10" t="s">
+      <c r="N197" s="8" t="s">
         <v>552</v>
       </c>
       <c r="Q197" t="s">
@@ -11729,7 +11732,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="198" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A198" s="2">
         <v>2403013</v>
       </c>
@@ -11776,7 +11779,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="199" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A199" s="2">
         <v>2403013</v>
       </c>
@@ -11823,7 +11826,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="200" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A200" s="2">
         <v>2403013</v>
       </c>
@@ -11870,7 +11873,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="201" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A201" s="2">
         <v>2404001</v>
       </c>
@@ -11920,7 +11923,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="202" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A202" s="2">
         <v>2404001</v>
       </c>
@@ -11970,7 +11973,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="203" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A203" s="2">
         <v>2404001</v>
       </c>
@@ -12020,7 +12023,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="204" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A204" s="2">
         <v>2404006</v>
       </c>
@@ -12070,7 +12073,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="205" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A205" s="2">
         <v>2404006</v>
       </c>
@@ -12120,7 +12123,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="206" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A206" s="2">
         <v>2404006</v>
       </c>
@@ -12170,7 +12173,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="207" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A207" s="2">
         <v>2404015</v>
       </c>
@@ -12217,7 +12220,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="208" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A208" s="2">
         <v>2404015</v>
       </c>
@@ -12264,7 +12267,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="209" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A209" s="2">
         <v>2404015</v>
       </c>
@@ -12311,7 +12314,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="210" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A210" s="2">
         <v>2405001</v>
       </c>
@@ -12361,7 +12364,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="211" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A211" s="2">
         <v>2405001</v>
       </c>
@@ -12411,7 +12414,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="212" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A212" s="2">
         <v>2405001</v>
       </c>
@@ -12461,7 +12464,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="213" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A213" s="2">
         <v>2405006</v>
       </c>
@@ -12511,7 +12514,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="214" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A214" s="2">
         <v>2405006</v>
       </c>
@@ -12561,7 +12564,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="215" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A215" s="2">
         <v>2405006</v>
       </c>
@@ -12611,7 +12614,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="216" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A216" s="2">
         <v>2405015</v>
       </c>
@@ -12661,7 +12664,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="217" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A217" s="2">
         <v>2405015</v>
       </c>
@@ -12711,7 +12714,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="218" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A218" s="2">
         <v>2405015</v>
       </c>
@@ -12758,7 +12761,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="219" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A219" s="2">
         <v>2406004</v>
       </c>
@@ -12808,7 +12811,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="220" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A220" s="2">
         <v>2406004</v>
       </c>
@@ -12858,7 +12861,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="221" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A221" s="2">
         <v>2406004</v>
       </c>
@@ -12908,7 +12911,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="222" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A222" s="2">
         <v>2406004</v>
       </c>
@@ -12958,7 +12961,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="223" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A223" s="2">
         <v>2406004</v>
       </c>
@@ -13008,7 +13011,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="224" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A224" s="2">
         <v>2406009</v>
       </c>
@@ -13058,7 +13061,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="225" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A225" s="2">
         <v>2406009</v>
       </c>
@@ -13108,7 +13111,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="226" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A226" s="2">
         <v>2406009</v>
       </c>
@@ -13158,7 +13161,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="227" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A227" s="2">
         <v>2406009</v>
       </c>
@@ -13208,7 +13211,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="228" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A228" s="2">
         <v>2406009</v>
       </c>
@@ -13258,7 +13261,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="229" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A229" s="2">
         <v>2406012</v>
       </c>
@@ -13305,7 +13308,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="230" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A230" s="2">
         <v>2406012</v>
       </c>
@@ -13352,7 +13355,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="231" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A231" s="2">
         <v>2406012</v>
       </c>
@@ -13399,7 +13402,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="232" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A232" s="2">
         <v>2059001</v>
       </c>
@@ -13446,7 +13449,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="233" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A233" s="2">
         <v>2059002</v>
       </c>
@@ -13493,7 +13496,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="234" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A234" s="2">
         <v>2059006</v>
       </c>
@@ -13540,7 +13543,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="235" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A235" s="2">
         <v>2140011</v>
       </c>
@@ -13587,7 +13590,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="236" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A236" s="2">
         <v>2390004</v>
       </c>
@@ -13634,7 +13637,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="237" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A237" s="2">
         <v>2390004</v>
       </c>
@@ -13681,7 +13684,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="238" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A238" s="2">
         <v>2390004</v>
       </c>
@@ -13728,7 +13731,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="239" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A239" s="2">
         <v>2390009</v>
       </c>
@@ -13775,7 +13778,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="240" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A240" s="2">
         <v>2390009</v>
       </c>
@@ -13822,7 +13825,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="241" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A241" s="2">
         <v>2390009</v>
       </c>
@@ -13869,7 +13872,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="242" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A242" s="2">
         <v>2390013</v>
       </c>
@@ -13913,7 +13916,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="243" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A243" s="2">
         <v>2390013</v>
       </c>
@@ -13957,7 +13960,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="244" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A244" s="2">
         <v>2390013</v>
       </c>
@@ -14001,7 +14004,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="252" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L252" s="1"/>
     </row>
   </sheetData>

--- a/POD_2026-27_11-5-2026.xlsx
+++ b/POD_2026-27_11-5-2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guillermo.vera/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\misael.marriaga\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18346B4A-B481-9A43-899E-B98F11024DF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94AEE75B-CF8A-4758-BFE0-1B61F613C496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17260" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="POD" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3052" uniqueCount="563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3108" uniqueCount="603">
   <si>
     <t>POD_2026-27_11-5-2026</t>
   </si>
@@ -1725,6 +1725,126 @@
   </si>
   <si>
     <t>M=&gt;(20:00-22:00)[22/09/26, 29/09/26, 06/10/26, 20/10/26, 27/10/26, 10/11/26, 17/11/26, 24/11/26]</t>
+  </si>
+  <si>
+    <t>Erik Sarrión (44)</t>
+  </si>
+  <si>
+    <t>Erik Sarrión (16)</t>
+  </si>
+  <si>
+    <t>Guille Carrión (44)</t>
+  </si>
+  <si>
+    <t>Guille Carrión (16)</t>
+  </si>
+  <si>
+    <t>Lorenzo Martini (35)</t>
+  </si>
+  <si>
+    <t>Lorenzo Martini (60)</t>
+  </si>
+  <si>
+    <t>Francisco Oviaño (40)</t>
+  </si>
+  <si>
+    <t>Francisco Oviaño (20)</t>
+  </si>
+  <si>
+    <t>Francisco Oviaño (48)</t>
+  </si>
+  <si>
+    <t>Francisco Oviaño (12)</t>
+  </si>
+  <si>
+    <t>Guille Carrión (48)</t>
+  </si>
+  <si>
+    <t>Guille Carrión (12)</t>
+  </si>
+  <si>
+    <t>Daniel Rodríguez (12)</t>
+  </si>
+  <si>
+    <t>Daniel Rodríguez (48)</t>
+  </si>
+  <si>
+    <t>Erik Sarrión (40)</t>
+  </si>
+  <si>
+    <t>Erik Sarrión (20)</t>
+  </si>
+  <si>
+    <t>Daniel Rodríguez (24)</t>
+  </si>
+  <si>
+    <t>Daniel Rodríguez (6)</t>
+  </si>
+  <si>
+    <t>María Dolores Gómez (39)</t>
+  </si>
+  <si>
+    <t>María Dolores Gómez (21)</t>
+  </si>
+  <si>
+    <t>Daniel Rodríguez (32)</t>
+  </si>
+  <si>
+    <t>Daniel Rodríguez (4)</t>
+  </si>
+  <si>
+    <t>Rubén Carrillo (24)</t>
+  </si>
+  <si>
+    <t>Rubén Carrillo (6)</t>
+  </si>
+  <si>
+    <t>Rubén Carrillo (39)</t>
+  </si>
+  <si>
+    <t>Rubén Carrillo (21)</t>
+  </si>
+  <si>
+    <t>Lorenzo Martini (14)</t>
+  </si>
+  <si>
+    <t>Lorenzo Martini (16)</t>
+  </si>
+  <si>
+    <t>María Dolores Gómez (24)</t>
+  </si>
+  <si>
+    <t>María Dolores Gómez (6)</t>
+  </si>
+  <si>
+    <t>María Dolores Gómez (41)</t>
+  </si>
+  <si>
+    <t>María Dolores Gómez (4)</t>
+  </si>
+  <si>
+    <t>Alexandru Iosif (60)</t>
+  </si>
+  <si>
+    <t>Alexandru Iosif (35)</t>
+  </si>
+  <si>
+    <t>Rubén Carrillo (35)</t>
+  </si>
+  <si>
+    <t>Tayomara Borsich (60)</t>
+  </si>
+  <si>
+    <t>Alexandru Iosif (48)</t>
+  </si>
+  <si>
+    <t>Alexandru Iosif (12)</t>
+  </si>
+  <si>
+    <t>Tayomara Borsich (48)</t>
+  </si>
+  <si>
+    <t>Tayomara Borsich (12)</t>
   </si>
 </sst>
 </file>
@@ -1821,9 +1941,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1861,7 +1981,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1967,7 +2087,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2109,7 +2229,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2118,30 +2238,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S252"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="71.33203125" customWidth="1"/>
+    <col min="2" max="2" width="71.36328125" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" customWidth="1"/>
-    <col min="5" max="5" width="20.1640625" customWidth="1"/>
-    <col min="6" max="6" width="64.1640625" customWidth="1"/>
-    <col min="7" max="7" width="20.83203125" customWidth="1"/>
-    <col min="8" max="8" width="6.5" customWidth="1"/>
-    <col min="9" max="9" width="7.83203125" customWidth="1"/>
-    <col min="10" max="10" width="6.5" customWidth="1"/>
-    <col min="11" max="11" width="107.1640625" customWidth="1"/>
-    <col min="12" max="12" width="53.6640625" customWidth="1"/>
-    <col min="13" max="13" width="12.6640625" customWidth="1"/>
-    <col min="14" max="14" width="36.5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="36.5" customWidth="1"/>
-    <col min="16" max="16" width="20.83203125" customWidth="1"/>
+    <col min="4" max="4" width="9.1796875" customWidth="1"/>
+    <col min="5" max="5" width="20.1796875" customWidth="1"/>
+    <col min="6" max="6" width="64.1796875" customWidth="1"/>
+    <col min="7" max="7" width="20.81640625" customWidth="1"/>
+    <col min="8" max="8" width="6.453125" customWidth="1"/>
+    <col min="9" max="9" width="7.81640625" customWidth="1"/>
+    <col min="10" max="10" width="6.453125" customWidth="1"/>
+    <col min="11" max="11" width="107.1796875" customWidth="1"/>
+    <col min="12" max="12" width="53.6328125" customWidth="1"/>
+    <col min="13" max="13" width="12.6328125" customWidth="1"/>
+    <col min="14" max="14" width="36.453125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="36.453125" customWidth="1"/>
+    <col min="16" max="16" width="20.81640625" customWidth="1"/>
     <col min="17" max="17" width="52" customWidth="1"/>
-    <col min="18" max="18" width="32.5" customWidth="1"/>
-    <col min="19" max="19" width="16.83203125" customWidth="1"/>
+    <col min="18" max="18" width="32.453125" customWidth="1"/>
+    <col min="19" max="19" width="16.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -2164,7 +2284,7 @@
       <c r="R1" s="10"/>
       <c r="S1" s="10"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2223,7 +2343,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>2291005</v>
       </c>
@@ -2267,7 +2387,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>2291009</v>
       </c>
@@ -2311,7 +2431,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>2240005</v>
       </c>
@@ -2358,7 +2478,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>2240009</v>
       </c>
@@ -2405,7 +2525,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>2251011</v>
       </c>
@@ -2449,7 +2569,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>2327002</v>
       </c>
@@ -2496,7 +2616,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>2327002</v>
       </c>
@@ -2543,7 +2663,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>2327002</v>
       </c>
@@ -2590,7 +2710,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>2327007</v>
       </c>
@@ -2640,7 +2760,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>2327007</v>
       </c>
@@ -2690,7 +2810,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>2327007</v>
       </c>
@@ -2740,7 +2860,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>2327015</v>
       </c>
@@ -2787,7 +2907,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>2327015</v>
       </c>
@@ -2834,7 +2954,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>2327015</v>
       </c>
@@ -2881,7 +3001,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>2360001</v>
       </c>
@@ -2928,7 +3048,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>2360002</v>
       </c>
@@ -2975,7 +3095,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>2382005</v>
       </c>
@@ -3025,7 +3145,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>2382005</v>
       </c>
@@ -3075,7 +3195,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>2382005</v>
       </c>
@@ -3125,7 +3245,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>2382005</v>
       </c>
@@ -3175,7 +3295,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>2382005</v>
       </c>
@@ -3225,7 +3345,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>2382005</v>
       </c>
@@ -3275,7 +3395,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>2382010</v>
       </c>
@@ -3325,7 +3445,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>2382010</v>
       </c>
@@ -3375,7 +3495,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>2382010</v>
       </c>
@@ -3425,7 +3545,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>2382010</v>
       </c>
@@ -3475,7 +3595,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>2382010</v>
       </c>
@@ -3522,7 +3642,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>2382010</v>
       </c>
@@ -3572,7 +3692,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>2383001</v>
       </c>
@@ -3622,7 +3742,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>2383001</v>
       </c>
@@ -3669,7 +3789,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>2383001</v>
       </c>
@@ -3716,7 +3836,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>2383001</v>
       </c>
@@ -3766,7 +3886,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>2383001</v>
       </c>
@@ -3816,7 +3936,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>2383001</v>
       </c>
@@ -3866,7 +3986,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <v>2383002</v>
       </c>
@@ -3916,7 +4036,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <v>2383002</v>
       </c>
@@ -3963,7 +4083,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <v>2383002</v>
       </c>
@@ -4010,7 +4130,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>2383002</v>
       </c>
@@ -4060,7 +4180,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>2383002</v>
       </c>
@@ -4110,7 +4230,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>2383002</v>
       </c>
@@ -4160,7 +4280,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="48" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <v>2383007</v>
       </c>
@@ -4213,7 +4333,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:18" ht="48" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>2383007</v>
       </c>
@@ -4266,7 +4386,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <v>2384001</v>
       </c>
@@ -4316,7 +4436,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>2384001</v>
       </c>
@@ -4366,7 +4486,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <v>2384001</v>
       </c>
@@ -4416,7 +4536,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>2384005</v>
       </c>
@@ -4466,7 +4586,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <v>2384005</v>
       </c>
@@ -4516,7 +4636,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <v>2384005</v>
       </c>
@@ -4566,7 +4686,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <v>2385001</v>
       </c>
@@ -4616,7 +4736,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <v>2385001</v>
       </c>
@@ -4666,7 +4786,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
         <v>2385001</v>
       </c>
@@ -4716,7 +4836,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <v>2385005</v>
       </c>
@@ -4766,7 +4886,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
         <v>2385005</v>
       </c>
@@ -4816,7 +4936,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <v>2385005</v>
       </c>
@@ -4866,7 +4986,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
         <v>2386001</v>
       </c>
@@ -4916,7 +5036,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <v>2386001</v>
       </c>
@@ -4966,7 +5086,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
         <v>2386001</v>
       </c>
@@ -5013,7 +5133,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>2386001</v>
       </c>
@@ -5053,6 +5173,9 @@
       <c r="M60" t="s">
         <v>26</v>
       </c>
+      <c r="N60" t="s">
+        <v>563</v>
+      </c>
       <c r="Q60" t="s">
         <v>27</v>
       </c>
@@ -5060,7 +5183,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <v>2386001</v>
       </c>
@@ -5100,6 +5223,9 @@
       <c r="M61" t="s">
         <v>26</v>
       </c>
+      <c r="N61" t="s">
+        <v>564</v>
+      </c>
       <c r="Q61" t="s">
         <v>27</v>
       </c>
@@ -5107,7 +5233,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <v>2386001</v>
       </c>
@@ -5154,7 +5280,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
         <v>2386002</v>
       </c>
@@ -5204,7 +5330,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
         <v>2386002</v>
       </c>
@@ -5257,7 +5383,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A65" s="2">
         <v>2387009</v>
       </c>
@@ -5297,6 +5423,9 @@
       <c r="M65" t="s">
         <v>26</v>
       </c>
+      <c r="N65" s="6" t="s">
+        <v>565</v>
+      </c>
       <c r="Q65" t="s">
         <v>27</v>
       </c>
@@ -5304,7 +5433,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A66" s="2">
         <v>2387009</v>
       </c>
@@ -5344,6 +5473,9 @@
       <c r="M66" t="s">
         <v>26</v>
       </c>
+      <c r="N66" s="6" t="s">
+        <v>566</v>
+      </c>
       <c r="Q66" t="s">
         <v>27</v>
       </c>
@@ -5351,7 +5483,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A67" s="2">
         <v>2387009</v>
       </c>
@@ -5391,6 +5523,9 @@
       <c r="M67" t="s">
         <v>26</v>
       </c>
+      <c r="N67" s="6" t="s">
+        <v>566</v>
+      </c>
       <c r="Q67" t="s">
         <v>27</v>
       </c>
@@ -5398,7 +5533,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A68" s="2">
         <v>2387016</v>
       </c>
@@ -5445,7 +5580,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A69" s="2">
         <v>2387016</v>
       </c>
@@ -5492,7 +5627,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A70" s="2">
         <v>2387016</v>
       </c>
@@ -5539,7 +5674,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="71" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A71" s="2">
         <v>2265020</v>
       </c>
@@ -5579,7 +5714,9 @@
       <c r="N71" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="O71" s="3"/>
+      <c r="O71" s="3" t="s">
+        <v>567</v>
+      </c>
       <c r="Q71" t="s">
         <v>27</v>
       </c>
@@ -5587,7 +5724,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A72" s="2">
         <v>2029018</v>
       </c>
@@ -5634,7 +5771,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A73" s="2">
         <v>2030013</v>
       </c>
@@ -5681,7 +5818,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A74" s="2">
         <v>2031001</v>
       </c>
@@ -5725,7 +5862,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A75" s="2">
         <v>2032001</v>
       </c>
@@ -5775,7 +5912,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A76" s="2">
         <v>2032007</v>
       </c>
@@ -5825,7 +5962,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A77" s="2">
         <v>2032009</v>
       </c>
@@ -5872,7 +6009,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A78" s="2">
         <v>2033001</v>
       </c>
@@ -5922,7 +6059,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="79" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A79" s="2">
         <v>2033002</v>
       </c>
@@ -5975,7 +6112,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A80" s="2">
         <v>2033006</v>
       </c>
@@ -6025,7 +6162,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A81" s="2">
         <v>2034001</v>
       </c>
@@ -6075,7 +6212,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="82" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A82" s="2">
         <v>2034002</v>
       </c>
@@ -6128,7 +6265,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A83" s="2">
         <v>2034006</v>
       </c>
@@ -6178,7 +6315,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A84" s="2">
         <v>2061001</v>
       </c>
@@ -6222,7 +6359,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A85" s="2">
         <v>2061002</v>
       </c>
@@ -6269,7 +6406,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A86" s="2">
         <v>2061006</v>
       </c>
@@ -6313,7 +6450,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A87" s="2">
         <v>2107013</v>
       </c>
@@ -6360,7 +6497,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A88" s="2">
         <v>2143016</v>
       </c>
@@ -6407,7 +6544,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A89" s="2">
         <v>2148011</v>
       </c>
@@ -6451,7 +6588,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A90" s="2">
         <v>2175020</v>
       </c>
@@ -6491,6 +6628,9 @@
       <c r="M90" t="s">
         <v>26</v>
       </c>
+      <c r="N90" t="s">
+        <v>568</v>
+      </c>
       <c r="Q90" t="s">
         <v>27</v>
       </c>
@@ -6498,7 +6638,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="91" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A91" s="2">
         <v>2285005</v>
       </c>
@@ -6548,7 +6688,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A92" s="2">
         <v>2285006</v>
       </c>
@@ -6595,7 +6735,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A93" s="2">
         <v>2285007</v>
       </c>
@@ -6642,7 +6782,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A94" s="2">
         <v>2286015</v>
       </c>
@@ -6686,7 +6826,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A95" s="2">
         <v>2338044</v>
       </c>
@@ -6730,7 +6870,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A96" s="2">
         <v>2342014</v>
       </c>
@@ -6777,7 +6917,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="97" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A97" s="2">
         <v>5</v>
       </c>
@@ -6825,7 +6965,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="98" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A98" s="2">
         <v>2343027</v>
       </c>
@@ -6873,7 +7013,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A99" s="2">
         <v>2343027</v>
       </c>
@@ -6920,7 +7060,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A100" s="2">
         <v>2343027</v>
       </c>
@@ -6966,7 +7106,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A101" s="2">
         <v>2347001</v>
       </c>
@@ -7016,7 +7156,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A102" s="2">
         <v>2347003</v>
       </c>
@@ -7066,7 +7206,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="103" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A103" s="2">
         <v>2347005</v>
       </c>
@@ -7117,7 +7257,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A104" s="2">
         <v>2347006</v>
       </c>
@@ -7167,7 +7307,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="105" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A105" s="2">
         <v>2347007</v>
       </c>
@@ -7218,7 +7358,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A106" s="2">
         <v>2347013</v>
       </c>
@@ -7268,7 +7408,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="107" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A107" s="2">
         <v>2347014</v>
       </c>
@@ -7318,7 +7458,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A108" s="2">
         <v>2347017</v>
       </c>
@@ -7368,7 +7508,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="109" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A109" s="2">
         <v>2347030</v>
       </c>
@@ -7419,7 +7559,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A110" s="2">
         <v>2347021</v>
       </c>
@@ -7469,7 +7609,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="111" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A111" s="2">
         <v>2347022</v>
       </c>
@@ -7521,7 +7661,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A112" s="2">
         <v>2347024</v>
       </c>
@@ -7571,7 +7711,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="113" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A113" s="2">
         <v>2347026</v>
       </c>
@@ -7622,7 +7762,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="114" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A114" s="2">
         <v>2347027</v>
       </c>
@@ -7673,7 +7813,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A115" s="2">
         <v>2347029</v>
       </c>
@@ -7723,7 +7863,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="116" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A116" s="2">
         <v>2347031</v>
       </c>
@@ -7773,7 +7913,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="117" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A117" s="2">
         <v>2347038</v>
       </c>
@@ -7824,7 +7964,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="118" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A118" s="2">
         <v>2361002</v>
       </c>
@@ -7871,7 +8011,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="119" spans="1:18" ht="16" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A119" s="2">
         <v>2361002</v>
       </c>
@@ -7918,7 +8058,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="120" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A120" s="2">
         <v>2361002</v>
       </c>
@@ -7962,7 +8102,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="121" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A121" s="2">
         <v>2361004</v>
       </c>
@@ -8009,7 +8149,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="122" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A122" s="2">
         <v>2393002</v>
       </c>
@@ -8049,6 +8189,9 @@
       <c r="M122" t="s">
         <v>26</v>
       </c>
+      <c r="N122" s="3" t="s">
+        <v>569</v>
+      </c>
       <c r="Q122" t="s">
         <v>27</v>
       </c>
@@ -8056,7 +8199,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="123" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A123" s="2">
         <v>2393002</v>
       </c>
@@ -8096,6 +8239,9 @@
       <c r="M123" t="s">
         <v>26</v>
       </c>
+      <c r="N123" s="3" t="s">
+        <v>570</v>
+      </c>
       <c r="Q123" t="s">
         <v>27</v>
       </c>
@@ -8103,7 +8249,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="124" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A124" s="2">
         <v>2393002</v>
       </c>
@@ -8143,6 +8289,9 @@
       <c r="M124" t="s">
         <v>26</v>
       </c>
+      <c r="N124" s="3" t="s">
+        <v>570</v>
+      </c>
       <c r="Q124" t="s">
         <v>27</v>
       </c>
@@ -8150,7 +8299,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="125" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A125" s="2">
         <v>2394004</v>
       </c>
@@ -8190,6 +8339,9 @@
       <c r="M125" t="s">
         <v>26</v>
       </c>
+      <c r="N125" s="3" t="s">
+        <v>573</v>
+      </c>
       <c r="Q125" t="s">
         <v>27</v>
       </c>
@@ -8197,7 +8349,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="126" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A126" s="2">
         <v>2394004</v>
       </c>
@@ -8237,6 +8389,9 @@
       <c r="M126" t="s">
         <v>26</v>
       </c>
+      <c r="N126" s="3" t="s">
+        <v>574</v>
+      </c>
       <c r="Q126" t="s">
         <v>27</v>
       </c>
@@ -8244,7 +8399,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="127" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A127" s="2">
         <v>2394004</v>
       </c>
@@ -8284,6 +8439,9 @@
       <c r="M127" t="s">
         <v>26</v>
       </c>
+      <c r="N127" s="3" t="s">
+        <v>574</v>
+      </c>
       <c r="Q127" t="s">
         <v>27</v>
       </c>
@@ -8291,7 +8449,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="128" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A128" s="2">
         <v>2395003</v>
       </c>
@@ -8341,7 +8499,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="129" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A129" s="2">
         <v>2395003</v>
       </c>
@@ -8391,7 +8549,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="130" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A130" s="2">
         <v>2395003</v>
       </c>
@@ -8441,7 +8599,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="131" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A131" s="2">
         <v>2396001</v>
       </c>
@@ -8491,7 +8649,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="132" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A132" s="2">
         <v>2396001</v>
       </c>
@@ -8541,7 +8699,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="133" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A133" s="2">
         <v>2396001</v>
       </c>
@@ -8591,7 +8749,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="134" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A134" s="2">
         <v>2397003</v>
       </c>
@@ -8641,7 +8799,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="135" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A135" s="2">
         <v>2397003</v>
       </c>
@@ -8691,7 +8849,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="136" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A136" s="2">
         <v>2397003</v>
       </c>
@@ -8741,7 +8899,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="137" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A137" s="2">
         <v>2397008</v>
       </c>
@@ -8781,6 +8939,9 @@
       <c r="M137" t="s">
         <v>26</v>
       </c>
+      <c r="N137" t="s">
+        <v>576</v>
+      </c>
       <c r="Q137" t="s">
         <v>27</v>
       </c>
@@ -8788,7 +8949,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="138" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A138" s="2">
         <v>2397008</v>
       </c>
@@ -8828,6 +8989,9 @@
       <c r="M138" t="s">
         <v>26</v>
       </c>
+      <c r="N138" t="s">
+        <v>575</v>
+      </c>
       <c r="Q138" t="s">
         <v>27</v>
       </c>
@@ -8835,7 +8999,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="139" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A139" s="2">
         <v>2397008</v>
       </c>
@@ -8875,6 +9039,9 @@
       <c r="M139" t="s">
         <v>26</v>
       </c>
+      <c r="N139" t="s">
+        <v>575</v>
+      </c>
       <c r="Q139" t="s">
         <v>27</v>
       </c>
@@ -8882,7 +9049,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="140" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A140" s="2">
         <v>2398001</v>
       </c>
@@ -8932,7 +9099,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="141" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A141" s="2">
         <v>2398001</v>
       </c>
@@ -8983,7 +9150,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="142" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A142" s="2">
         <v>2398001</v>
       </c>
@@ -9034,7 +9201,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="143" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A143" s="2">
         <v>2398006</v>
       </c>
@@ -9084,7 +9251,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="144" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A144" s="2">
         <v>2398006</v>
       </c>
@@ -9134,7 +9301,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="145" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A145" s="2">
         <v>2398006</v>
       </c>
@@ -9184,7 +9351,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="146" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A146" s="2">
         <v>2398013</v>
       </c>
@@ -9224,6 +9391,9 @@
       <c r="M146" t="s">
         <v>26</v>
       </c>
+      <c r="N146" s="6" t="s">
+        <v>577</v>
+      </c>
       <c r="Q146" t="s">
         <v>27</v>
       </c>
@@ -9231,7 +9401,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="147" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A147" s="2">
         <v>2398013</v>
       </c>
@@ -9271,6 +9441,9 @@
       <c r="M147" t="s">
         <v>26</v>
       </c>
+      <c r="N147" s="6" t="s">
+        <v>578</v>
+      </c>
       <c r="Q147" t="s">
         <v>27</v>
       </c>
@@ -9278,7 +9451,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A148" s="2">
         <v>2398013</v>
       </c>
@@ -9315,6 +9488,9 @@
       <c r="M148" t="s">
         <v>26</v>
       </c>
+      <c r="N148" s="6" t="s">
+        <v>578</v>
+      </c>
       <c r="Q148" t="s">
         <v>27</v>
       </c>
@@ -9322,7 +9498,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="149" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A149" s="2">
         <v>2399003</v>
       </c>
@@ -9365,6 +9541,9 @@
       <c r="N149" t="s">
         <v>560</v>
       </c>
+      <c r="O149" t="s">
+        <v>579</v>
+      </c>
       <c r="Q149" t="s">
         <v>27</v>
       </c>
@@ -9372,7 +9551,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="150" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A150" s="2">
         <v>2399003</v>
       </c>
@@ -9415,6 +9594,9 @@
       <c r="N150" t="s">
         <v>561</v>
       </c>
+      <c r="O150" t="s">
+        <v>580</v>
+      </c>
       <c r="Q150" t="s">
         <v>27</v>
       </c>
@@ -9422,7 +9604,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="151" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A151" s="2">
         <v>2399003</v>
       </c>
@@ -9465,6 +9647,9 @@
       <c r="N151" t="s">
         <v>561</v>
       </c>
+      <c r="O151" t="s">
+        <v>580</v>
+      </c>
       <c r="Q151" t="s">
         <v>27</v>
       </c>
@@ -9472,7 +9657,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="152" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A152" s="2">
         <v>2399010</v>
       </c>
@@ -9512,6 +9697,9 @@
       <c r="M152" t="s">
         <v>26</v>
       </c>
+      <c r="N152" t="s">
+        <v>571</v>
+      </c>
       <c r="Q152" t="s">
         <v>27</v>
       </c>
@@ -9519,7 +9707,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="153" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A153" s="2">
         <v>2399010</v>
       </c>
@@ -9559,6 +9747,9 @@
       <c r="M153" t="s">
         <v>26</v>
       </c>
+      <c r="N153" t="s">
+        <v>572</v>
+      </c>
       <c r="Q153" t="s">
         <v>27</v>
       </c>
@@ -9566,7 +9757,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="154" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A154" s="2">
         <v>2399010</v>
       </c>
@@ -9606,6 +9797,9 @@
       <c r="M154" t="s">
         <v>26</v>
       </c>
+      <c r="N154" t="s">
+        <v>572</v>
+      </c>
       <c r="Q154" t="s">
         <v>27</v>
       </c>
@@ -9613,7 +9807,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="155" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A155" s="2">
         <v>2399014</v>
       </c>
@@ -9653,6 +9847,9 @@
       <c r="M155" t="s">
         <v>26</v>
       </c>
+      <c r="N155" t="s">
+        <v>581</v>
+      </c>
       <c r="Q155" t="s">
         <v>27</v>
       </c>
@@ -9660,7 +9857,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A156" s="2">
         <v>2399014</v>
       </c>
@@ -9700,6 +9897,9 @@
       <c r="M156" t="s">
         <v>26</v>
       </c>
+      <c r="N156" t="s">
+        <v>582</v>
+      </c>
       <c r="Q156" t="s">
         <v>27</v>
       </c>
@@ -9707,7 +9907,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A157" s="2">
         <v>2399014</v>
       </c>
@@ -9744,6 +9944,9 @@
       <c r="M157" t="s">
         <v>26</v>
       </c>
+      <c r="N157" t="s">
+        <v>582</v>
+      </c>
       <c r="Q157" t="s">
         <v>27</v>
       </c>
@@ -9751,7 +9954,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="158" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A158" s="2">
         <v>2400003</v>
       </c>
@@ -9801,7 +10004,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="159" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A159" s="2">
         <v>2400003</v>
       </c>
@@ -9851,7 +10054,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="160" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A160" s="2">
         <v>2400003</v>
       </c>
@@ -9901,7 +10104,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="161" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A161" s="2">
         <v>2400008</v>
       </c>
@@ -9951,7 +10154,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="162" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A162" s="2">
         <v>2400008</v>
       </c>
@@ -10001,7 +10204,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="163" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A163" s="2">
         <v>2400008</v>
       </c>
@@ -10051,7 +10254,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="164" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A164" s="2">
         <v>2400012</v>
       </c>
@@ -10101,7 +10304,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="165" spans="1:18" ht="32" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:18" ht="29" x14ac:dyDescent="0.35">
       <c r="A165" s="2">
         <v>2400012</v>
       </c>
@@ -10151,7 +10354,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="166" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A166" s="2">
         <v>2400012</v>
       </c>
@@ -10198,7 +10401,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="167" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A167" s="2">
         <v>2401001</v>
       </c>
@@ -10248,7 +10451,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="168" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A168" s="2">
         <v>2401001</v>
       </c>
@@ -10298,7 +10501,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="169" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A169" s="2">
         <v>2401001</v>
       </c>
@@ -10348,7 +10551,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="170" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A170" s="2">
         <v>2401007</v>
       </c>
@@ -10398,7 +10601,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="171" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A171" s="2">
         <v>2401007</v>
       </c>
@@ -10448,7 +10651,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="172" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A172" s="2">
         <v>2401007</v>
       </c>
@@ -10498,7 +10701,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="173" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A173" s="2">
         <v>2401013</v>
       </c>
@@ -10548,7 +10751,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="174" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A174" s="2">
         <v>2401013</v>
       </c>
@@ -10598,7 +10801,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="175" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A175" s="2">
         <v>2401013</v>
       </c>
@@ -10648,7 +10851,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="176" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A176" s="2">
         <v>2401018</v>
       </c>
@@ -10698,7 +10901,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="177" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A177" s="2">
         <v>2401018</v>
       </c>
@@ -10748,7 +10951,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="178" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A178" s="2">
         <v>2401018</v>
       </c>
@@ -10795,7 +10998,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="179" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A179" s="2">
         <v>2401018</v>
       </c>
@@ -10845,7 +11048,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="180" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A180" s="2">
         <v>2401018</v>
       </c>
@@ -10892,7 +11095,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="181" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A181" s="2">
         <v>2401018</v>
       </c>
@@ -10939,7 +11142,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="182" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A182" s="2">
         <v>2401018</v>
       </c>
@@ -10986,7 +11189,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="183" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A183" s="2">
         <v>2402003</v>
       </c>
@@ -11037,7 +11240,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="184" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A184" s="2">
         <v>2402003</v>
       </c>
@@ -11088,7 +11291,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="185" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A185" s="2">
         <v>2402003</v>
       </c>
@@ -11139,7 +11342,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="186" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A186" s="2">
         <v>2402008</v>
       </c>
@@ -11182,6 +11385,9 @@
       <c r="N186" t="s">
         <v>388</v>
       </c>
+      <c r="O186" t="s">
+        <v>583</v>
+      </c>
       <c r="Q186" t="s">
         <v>27</v>
       </c>
@@ -11189,7 +11395,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="187" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A187" s="2">
         <v>2402008</v>
       </c>
@@ -11232,6 +11438,9 @@
       <c r="N187" t="s">
         <v>390</v>
       </c>
+      <c r="O187" t="s">
+        <v>584</v>
+      </c>
       <c r="Q187" t="s">
         <v>27</v>
       </c>
@@ -11239,7 +11448,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="188" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A188" s="2">
         <v>2402008</v>
       </c>
@@ -11282,6 +11491,9 @@
       <c r="N188" t="s">
         <v>390</v>
       </c>
+      <c r="O188" t="s">
+        <v>584</v>
+      </c>
       <c r="Q188" t="s">
         <v>27</v>
       </c>
@@ -11289,7 +11501,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="189" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A189" s="2">
         <v>2402015</v>
       </c>
@@ -11336,7 +11548,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="190" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A190" s="2">
         <v>2402015</v>
       </c>
@@ -11383,7 +11595,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="191" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A191" s="2">
         <v>2402015</v>
       </c>
@@ -11429,7 +11641,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="192" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A192" s="2">
         <v>2403004</v>
       </c>
@@ -11480,7 +11692,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="193" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A193" s="2">
         <v>2403004</v>
       </c>
@@ -11531,7 +11743,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="194" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A194" s="2">
         <v>2403004</v>
       </c>
@@ -11582,7 +11794,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="195" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A195" s="2">
         <v>2403009</v>
       </c>
@@ -11625,6 +11837,9 @@
       <c r="N195" s="8" t="s">
         <v>551</v>
       </c>
+      <c r="O195" t="s">
+        <v>585</v>
+      </c>
       <c r="Q195" t="s">
         <v>27</v>
       </c>
@@ -11632,7 +11847,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="196" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A196" s="2">
         <v>2403009</v>
       </c>
@@ -11675,6 +11890,9 @@
       <c r="N196" s="8" t="s">
         <v>552</v>
       </c>
+      <c r="O196" t="s">
+        <v>586</v>
+      </c>
       <c r="Q196" t="s">
         <v>27</v>
       </c>
@@ -11682,7 +11900,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="197" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A197" s="2">
         <v>2403009</v>
       </c>
@@ -11725,6 +11943,9 @@
       <c r="N197" s="8" t="s">
         <v>552</v>
       </c>
+      <c r="O197" t="s">
+        <v>586</v>
+      </c>
       <c r="Q197" t="s">
         <v>27</v>
       </c>
@@ -11732,7 +11953,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="198" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A198" s="2">
         <v>2403013</v>
       </c>
@@ -11779,7 +12000,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="199" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A199" s="2">
         <v>2403013</v>
       </c>
@@ -11826,7 +12047,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="200" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A200" s="2">
         <v>2403013</v>
       </c>
@@ -11873,7 +12094,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="201" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A201" s="2">
         <v>2404001</v>
       </c>
@@ -11923,7 +12144,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="202" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A202" s="2">
         <v>2404001</v>
       </c>
@@ -11973,7 +12194,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="203" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A203" s="2">
         <v>2404001</v>
       </c>
@@ -12023,7 +12244,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="204" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A204" s="2">
         <v>2404006</v>
       </c>
@@ -12073,7 +12294,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="205" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A205" s="2">
         <v>2404006</v>
       </c>
@@ -12123,7 +12344,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="206" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A206" s="2">
         <v>2404006</v>
       </c>
@@ -12173,7 +12394,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="207" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A207" s="2">
         <v>2404015</v>
       </c>
@@ -12213,6 +12434,9 @@
       <c r="N207" t="s">
         <v>423</v>
       </c>
+      <c r="O207" t="s">
+        <v>589</v>
+      </c>
       <c r="Q207" t="s">
         <v>27</v>
       </c>
@@ -12220,7 +12444,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="208" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A208" s="2">
         <v>2404015</v>
       </c>
@@ -12260,6 +12484,9 @@
       <c r="N208" t="s">
         <v>510</v>
       </c>
+      <c r="O208" t="s">
+        <v>590</v>
+      </c>
       <c r="Q208" t="s">
         <v>27</v>
       </c>
@@ -12267,7 +12494,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="209" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A209" s="2">
         <v>2404015</v>
       </c>
@@ -12307,6 +12534,9 @@
       <c r="N209" t="s">
         <v>510</v>
       </c>
+      <c r="O209" t="s">
+        <v>590</v>
+      </c>
       <c r="Q209" t="s">
         <v>27</v>
       </c>
@@ -12314,7 +12544,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="210" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A210" s="2">
         <v>2405001</v>
       </c>
@@ -12364,7 +12594,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="211" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A211" s="2">
         <v>2405001</v>
       </c>
@@ -12414,7 +12644,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="212" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A212" s="2">
         <v>2405001</v>
       </c>
@@ -12464,7 +12694,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="213" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A213" s="2">
         <v>2405006</v>
       </c>
@@ -12507,6 +12737,9 @@
       <c r="N213" s="6" t="s">
         <v>499</v>
       </c>
+      <c r="O213" s="6" t="s">
+        <v>591</v>
+      </c>
       <c r="Q213" t="s">
         <v>27</v>
       </c>
@@ -12514,7 +12747,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="214" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A214" s="2">
         <v>2405006</v>
       </c>
@@ -12557,6 +12790,9 @@
       <c r="N214" s="6" t="s">
         <v>500</v>
       </c>
+      <c r="O214" s="6" t="s">
+        <v>592</v>
+      </c>
       <c r="Q214" t="s">
         <v>27</v>
       </c>
@@ -12564,7 +12800,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="215" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A215" s="2">
         <v>2405006</v>
       </c>
@@ -12607,6 +12843,9 @@
       <c r="N215" s="6" t="s">
         <v>500</v>
       </c>
+      <c r="O215" s="6" t="s">
+        <v>592</v>
+      </c>
       <c r="Q215" t="s">
         <v>27</v>
       </c>
@@ -12614,7 +12853,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="216" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A216" s="2">
         <v>2405015</v>
       </c>
@@ -12664,7 +12903,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="217" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A217" s="2">
         <v>2405015</v>
       </c>
@@ -12714,7 +12953,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="218" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A218" s="2">
         <v>2405015</v>
       </c>
@@ -12761,7 +13000,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="219" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A219" s="2">
         <v>2406004</v>
       </c>
@@ -12811,7 +13050,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="220" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A220" s="2">
         <v>2406004</v>
       </c>
@@ -12861,7 +13100,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="221" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A221" s="2">
         <v>2406004</v>
       </c>
@@ -12911,7 +13150,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="222" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A222" s="2">
         <v>2406004</v>
       </c>
@@ -12961,7 +13200,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="223" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A223" s="2">
         <v>2406004</v>
       </c>
@@ -13011,7 +13250,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="224" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A224" s="2">
         <v>2406009</v>
       </c>
@@ -13061,7 +13300,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="225" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A225" s="2">
         <v>2406009</v>
       </c>
@@ -13111,7 +13350,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="226" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A226" s="2">
         <v>2406009</v>
       </c>
@@ -13161,7 +13400,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="227" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A227" s="2">
         <v>2406009</v>
       </c>
@@ -13211,7 +13450,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="228" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A228" s="2">
         <v>2406009</v>
       </c>
@@ -13261,7 +13500,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="229" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A229" s="2">
         <v>2406012</v>
       </c>
@@ -13301,6 +13540,9 @@
       <c r="M229" t="s">
         <v>26</v>
       </c>
+      <c r="N229" s="6" t="s">
+        <v>593</v>
+      </c>
       <c r="Q229" t="s">
         <v>27</v>
       </c>
@@ -13308,7 +13550,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="230" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A230" s="2">
         <v>2406012</v>
       </c>
@@ -13348,6 +13590,9 @@
       <c r="M230" t="s">
         <v>26</v>
       </c>
+      <c r="N230" s="6" t="s">
+        <v>594</v>
+      </c>
       <c r="Q230" t="s">
         <v>27</v>
       </c>
@@ -13355,7 +13600,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="231" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A231" s="2">
         <v>2406012</v>
       </c>
@@ -13395,6 +13640,9 @@
       <c r="M231" t="s">
         <v>26</v>
       </c>
+      <c r="N231" s="6" t="s">
+        <v>594</v>
+      </c>
       <c r="Q231" t="s">
         <v>27</v>
       </c>
@@ -13402,7 +13650,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="232" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A232" s="2">
         <v>2059001</v>
       </c>
@@ -13442,6 +13690,9 @@
       <c r="M232" t="s">
         <v>26</v>
       </c>
+      <c r="N232" s="6" t="s">
+        <v>595</v>
+      </c>
       <c r="Q232" t="s">
         <v>27</v>
       </c>
@@ -13449,7 +13700,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="233" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A233" s="2">
         <v>2059002</v>
       </c>
@@ -13489,6 +13740,12 @@
       <c r="M233" t="s">
         <v>26</v>
       </c>
+      <c r="N233" s="6" t="s">
+        <v>596</v>
+      </c>
+      <c r="O233" s="6" t="s">
+        <v>597</v>
+      </c>
       <c r="Q233" t="s">
         <v>27</v>
       </c>
@@ -13496,7 +13753,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="234" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A234" s="2">
         <v>2059006</v>
       </c>
@@ -13536,6 +13793,9 @@
       <c r="M234" t="s">
         <v>26</v>
       </c>
+      <c r="N234" s="6" t="s">
+        <v>598</v>
+      </c>
       <c r="Q234" t="s">
         <v>27</v>
       </c>
@@ -13543,7 +13803,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="235" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A235" s="2">
         <v>2140011</v>
       </c>
@@ -13590,7 +13850,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="236" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A236" s="2">
         <v>2390004</v>
       </c>
@@ -13630,6 +13890,9 @@
       <c r="M236" t="s">
         <v>26</v>
       </c>
+      <c r="N236" t="s">
+        <v>599</v>
+      </c>
       <c r="Q236" t="s">
         <v>27</v>
       </c>
@@ -13637,7 +13900,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="237" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A237" s="2">
         <v>2390004</v>
       </c>
@@ -13677,6 +13940,9 @@
       <c r="M237" t="s">
         <v>26</v>
       </c>
+      <c r="N237" t="s">
+        <v>600</v>
+      </c>
       <c r="Q237" t="s">
         <v>27</v>
       </c>
@@ -13684,7 +13950,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="238" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A238" s="2">
         <v>2390004</v>
       </c>
@@ -13724,6 +13990,9 @@
       <c r="M238" t="s">
         <v>26</v>
       </c>
+      <c r="N238" t="s">
+        <v>600</v>
+      </c>
       <c r="Q238" t="s">
         <v>27</v>
       </c>
@@ -13731,7 +14000,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="239" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A239" s="2">
         <v>2390009</v>
       </c>
@@ -13771,6 +14040,9 @@
       <c r="M239" t="s">
         <v>26</v>
       </c>
+      <c r="N239" t="s">
+        <v>601</v>
+      </c>
       <c r="Q239" t="s">
         <v>27</v>
       </c>
@@ -13778,7 +14050,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="240" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A240" s="2">
         <v>2390009</v>
       </c>
@@ -13818,6 +14090,9 @@
       <c r="M240" t="s">
         <v>26</v>
       </c>
+      <c r="N240" t="s">
+        <v>602</v>
+      </c>
       <c r="Q240" t="s">
         <v>27</v>
       </c>
@@ -13825,7 +14100,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="241" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A241" s="2">
         <v>2390009</v>
       </c>
@@ -13865,6 +14140,9 @@
       <c r="M241" t="s">
         <v>26</v>
       </c>
+      <c r="N241" t="s">
+        <v>602</v>
+      </c>
       <c r="Q241" t="s">
         <v>27</v>
       </c>
@@ -13872,7 +14150,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="242" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A242" s="2">
         <v>2390013</v>
       </c>
@@ -13909,6 +14187,9 @@
       <c r="M242" t="s">
         <v>26</v>
       </c>
+      <c r="N242" t="s">
+        <v>587</v>
+      </c>
       <c r="Q242" t="s">
         <v>27</v>
       </c>
@@ -13916,7 +14197,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="243" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A243" s="2">
         <v>2390013</v>
       </c>
@@ -13953,6 +14234,9 @@
       <c r="M243" t="s">
         <v>26</v>
       </c>
+      <c r="N243" t="s">
+        <v>588</v>
+      </c>
       <c r="Q243" t="s">
         <v>27</v>
       </c>
@@ -13960,7 +14244,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="244" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A244" s="2">
         <v>2390013</v>
       </c>
@@ -13997,6 +14281,9 @@
       <c r="M244" t="s">
         <v>26</v>
       </c>
+      <c r="N244" t="s">
+        <v>588</v>
+      </c>
       <c r="Q244" t="s">
         <v>27</v>
       </c>
@@ -14004,7 +14291,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="252" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="L252" s="1"/>
     </row>
   </sheetData>

--- a/POD_2026-27_11-5-2026.xlsx
+++ b/POD_2026-27_11-5-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\misael.marriaga\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94AEE75B-CF8A-4758-BFE0-1B61F613C496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA07D8F0-6552-493D-9472-941D82970228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="POD" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3108" uniqueCount="603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3113" uniqueCount="605">
   <si>
     <t>POD_2026-27_11-5-2026</t>
   </si>
@@ -1845,6 +1845,12 @@
   </si>
   <si>
     <t>Tayomara Borsich (12)</t>
+  </si>
+  <si>
+    <t>Miguel Ángel Rivas (10)</t>
+  </si>
+  <si>
+    <t>Miguel Ángel Rivas (4)</t>
   </si>
 </sst>
 </file>
@@ -6631,6 +6637,9 @@
       <c r="N90" t="s">
         <v>568</v>
       </c>
+      <c r="O90" t="s">
+        <v>603</v>
+      </c>
       <c r="Q90" t="s">
         <v>27</v>
       </c>
@@ -13143,6 +13152,9 @@
       <c r="N221" s="6" t="s">
         <v>507</v>
       </c>
+      <c r="O221" s="6" t="s">
+        <v>604</v>
+      </c>
       <c r="Q221" t="s">
         <v>27</v>
       </c>
@@ -13243,6 +13255,9 @@
       <c r="N223" s="6" t="s">
         <v>507</v>
       </c>
+      <c r="O223" s="6" t="s">
+        <v>604</v>
+      </c>
       <c r="Q223" t="s">
         <v>27</v>
       </c>
@@ -13593,6 +13608,9 @@
       <c r="N230" s="6" t="s">
         <v>594</v>
       </c>
+      <c r="O230" s="6" t="s">
+        <v>604</v>
+      </c>
       <c r="Q230" t="s">
         <v>27</v>
       </c>
@@ -13642,6 +13660,9 @@
       </c>
       <c r="N231" s="6" t="s">
         <v>594</v>
+      </c>
+      <c r="O231" s="6" t="s">
+        <v>604</v>
       </c>
       <c r="Q231" t="s">
         <v>27</v>

--- a/POD_2026-27_11-5-2026.xlsx
+++ b/POD_2026-27_11-5-2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10811"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\misael.marriaga\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guillermo.vera/Desktop/POD2627/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA07D8F0-6552-493D-9472-941D82970228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{591172C4-32AD-084E-8988-BD031E514157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="POD" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3113" uniqueCount="605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3119" uniqueCount="610">
   <si>
     <t>POD_2026-27_11-5-2026</t>
   </si>
@@ -1851,6 +1851,21 @@
   </si>
   <si>
     <t>Miguel Ángel Rivas (4)</t>
+  </si>
+  <si>
+    <t>FRANCISCO JAVIER MARÍN (10)</t>
+  </si>
+  <si>
+    <t>HÉCTOR RODRIGO IGLESIAS (6)</t>
+  </si>
+  <si>
+    <t>HÉCTOR RODRIGO IGLESIAS (24)</t>
+  </si>
+  <si>
+    <t>HÉCTOR RODRIGO IGLESIAS (10)</t>
+  </si>
+  <si>
+    <t>HÉCTOR RODRIGO IGLESIAS (21)</t>
   </si>
 </sst>
 </file>
@@ -1947,9 +1962,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1987,7 +2002,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2093,7 +2108,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2235,7 +2250,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2244,30 +2259,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S252"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="71.36328125" customWidth="1"/>
+    <col min="2" max="2" width="71.33203125" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="9.1796875" customWidth="1"/>
-    <col min="5" max="5" width="20.1796875" customWidth="1"/>
-    <col min="6" max="6" width="64.1796875" customWidth="1"/>
-    <col min="7" max="7" width="20.81640625" customWidth="1"/>
-    <col min="8" max="8" width="6.453125" customWidth="1"/>
-    <col min="9" max="9" width="7.81640625" customWidth="1"/>
-    <col min="10" max="10" width="6.453125" customWidth="1"/>
-    <col min="11" max="11" width="107.1796875" customWidth="1"/>
-    <col min="12" max="12" width="53.6328125" customWidth="1"/>
-    <col min="13" max="13" width="12.6328125" customWidth="1"/>
-    <col min="14" max="14" width="36.453125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="36.453125" customWidth="1"/>
-    <col min="16" max="16" width="20.81640625" customWidth="1"/>
+    <col min="4" max="4" width="9.1640625" customWidth="1"/>
+    <col min="5" max="5" width="20.1640625" customWidth="1"/>
+    <col min="6" max="6" width="64.1640625" customWidth="1"/>
+    <col min="7" max="7" width="20.83203125" customWidth="1"/>
+    <col min="8" max="8" width="6.5" customWidth="1"/>
+    <col min="9" max="9" width="7.83203125" customWidth="1"/>
+    <col min="10" max="10" width="6.5" customWidth="1"/>
+    <col min="11" max="11" width="107.1640625" customWidth="1"/>
+    <col min="12" max="12" width="53.6640625" customWidth="1"/>
+    <col min="13" max="13" width="12.6640625" customWidth="1"/>
+    <col min="14" max="14" width="36.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="36.5" customWidth="1"/>
+    <col min="16" max="16" width="20.83203125" customWidth="1"/>
     <col min="17" max="17" width="52" customWidth="1"/>
-    <col min="18" max="18" width="32.453125" customWidth="1"/>
-    <col min="19" max="19" width="16.81640625" customWidth="1"/>
+    <col min="18" max="18" width="32.5" customWidth="1"/>
+    <col min="19" max="19" width="16.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -2290,7 +2305,7 @@
       <c r="R1" s="10"/>
       <c r="S1" s="10"/>
     </row>
-    <row r="2" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2349,7 +2364,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>2291005</v>
       </c>
@@ -2393,7 +2408,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>2291009</v>
       </c>
@@ -2437,7 +2452,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>2240005</v>
       </c>
@@ -2484,7 +2499,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>2240009</v>
       </c>
@@ -2531,7 +2546,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>2251011</v>
       </c>
@@ -2575,7 +2590,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>2327002</v>
       </c>
@@ -2622,7 +2637,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>2327002</v>
       </c>
@@ -2669,7 +2684,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>2327002</v>
       </c>
@@ -2716,7 +2731,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>2327007</v>
       </c>
@@ -2766,7 +2781,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>2327007</v>
       </c>
@@ -2816,7 +2831,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>2327007</v>
       </c>
@@ -2866,7 +2881,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>2327015</v>
       </c>
@@ -2913,7 +2928,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>2327015</v>
       </c>
@@ -2960,7 +2975,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>2327015</v>
       </c>
@@ -3007,7 +3022,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>2360001</v>
       </c>
@@ -3054,7 +3069,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>2360002</v>
       </c>
@@ -3101,7 +3116,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>2382005</v>
       </c>
@@ -3151,7 +3166,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>2382005</v>
       </c>
@@ -3201,7 +3216,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>2382005</v>
       </c>
@@ -3251,7 +3266,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>2382005</v>
       </c>
@@ -3301,7 +3316,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>2382005</v>
       </c>
@@ -3351,7 +3366,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>2382005</v>
       </c>
@@ -3401,7 +3416,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>2382010</v>
       </c>
@@ -3451,7 +3466,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>2382010</v>
       </c>
@@ -3501,7 +3516,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>2382010</v>
       </c>
@@ -3551,7 +3566,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>2382010</v>
       </c>
@@ -3601,7 +3616,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>2382010</v>
       </c>
@@ -3648,7 +3663,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>2382010</v>
       </c>
@@ -3698,7 +3713,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>2383001</v>
       </c>
@@ -3748,7 +3763,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>2383001</v>
       </c>
@@ -3795,7 +3810,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>2383001</v>
       </c>
@@ -3842,7 +3857,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>2383001</v>
       </c>
@@ -3892,7 +3907,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>2383001</v>
       </c>
@@ -3942,7 +3957,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>2383001</v>
       </c>
@@ -3992,7 +4007,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>2383002</v>
       </c>
@@ -4042,7 +4057,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>2383002</v>
       </c>
@@ -4089,7 +4104,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>2383002</v>
       </c>
@@ -4136,7 +4151,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>2383002</v>
       </c>
@@ -4186,7 +4201,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>2383002</v>
       </c>
@@ -4236,7 +4251,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>2383002</v>
       </c>
@@ -4286,7 +4301,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:18" ht="48" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>2383007</v>
       </c>
@@ -4339,7 +4354,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:18" ht="48" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>2383007</v>
       </c>
@@ -4392,7 +4407,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>2384001</v>
       </c>
@@ -4442,7 +4457,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>2384001</v>
       </c>
@@ -4492,7 +4507,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>2384001</v>
       </c>
@@ -4542,7 +4557,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
         <v>2384005</v>
       </c>
@@ -4592,7 +4607,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
         <v>2384005</v>
       </c>
@@ -4642,7 +4657,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
         <v>2384005</v>
       </c>
@@ -4692,7 +4707,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="51" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
         <v>2385001</v>
       </c>
@@ -4742,7 +4757,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="52" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
         <v>2385001</v>
       </c>
@@ -4792,7 +4807,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="53" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
         <v>2385001</v>
       </c>
@@ -4842,7 +4857,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
         <v>2385005</v>
       </c>
@@ -4892,7 +4907,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
         <v>2385005</v>
       </c>
@@ -4942,7 +4957,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="56" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
         <v>2385005</v>
       </c>
@@ -4992,7 +5007,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="57" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
         <v>2386001</v>
       </c>
@@ -5042,7 +5057,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="58" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
         <v>2386001</v>
       </c>
@@ -5092,7 +5107,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="59" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
         <v>2386001</v>
       </c>
@@ -5139,7 +5154,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="60" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
         <v>2386001</v>
       </c>
@@ -5189,7 +5204,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="61" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
         <v>2386001</v>
       </c>
@@ -5239,7 +5254,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="62" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
         <v>2386001</v>
       </c>
@@ -5286,7 +5301,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="63" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
         <v>2386002</v>
       </c>
@@ -5336,7 +5351,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="64" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
         <v>2386002</v>
       </c>
@@ -5389,7 +5404,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="65" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
         <v>2387009</v>
       </c>
@@ -5439,7 +5454,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="66" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
         <v>2387009</v>
       </c>
@@ -5489,7 +5504,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="67" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
         <v>2387009</v>
       </c>
@@ -5539,7 +5554,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="68" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
         <v>2387016</v>
       </c>
@@ -5586,7 +5601,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="69" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
         <v>2387016</v>
       </c>
@@ -5633,7 +5648,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="70" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
         <v>2387016</v>
       </c>
@@ -5680,7 +5695,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="71" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
         <v>2265020</v>
       </c>
@@ -5730,7 +5745,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="72" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
         <v>2029018</v>
       </c>
@@ -5777,7 +5792,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="73" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
         <v>2030013</v>
       </c>
@@ -5824,7 +5839,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="74" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
         <v>2031001</v>
       </c>
@@ -5868,7 +5883,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="75" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
         <v>2032001</v>
       </c>
@@ -5918,7 +5933,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="76" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
         <v>2032007</v>
       </c>
@@ -5968,7 +5983,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="77" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
         <v>2032009</v>
       </c>
@@ -6008,6 +6023,9 @@
       <c r="N77" s="6" t="s">
         <v>513</v>
       </c>
+      <c r="O77" s="6" t="s">
+        <v>605</v>
+      </c>
       <c r="Q77" t="s">
         <v>27</v>
       </c>
@@ -6015,7 +6033,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="78" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
         <v>2033001</v>
       </c>
@@ -6065,7 +6083,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="79" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
         <v>2033002</v>
       </c>
@@ -6118,7 +6136,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="80" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
         <v>2033006</v>
       </c>
@@ -6168,7 +6186,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="81" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
         <v>2034001</v>
       </c>
@@ -6218,7 +6236,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="82" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
         <v>2034002</v>
       </c>
@@ -6271,7 +6289,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="83" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
         <v>2034006</v>
       </c>
@@ -6321,7 +6339,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="84" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
         <v>2061001</v>
       </c>
@@ -6365,7 +6383,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="85" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
         <v>2061002</v>
       </c>
@@ -6412,7 +6430,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="86" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
         <v>2061006</v>
       </c>
@@ -6456,7 +6474,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="87" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
         <v>2107013</v>
       </c>
@@ -6503,7 +6521,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="88" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
         <v>2143016</v>
       </c>
@@ -6550,7 +6568,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="89" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
         <v>2148011</v>
       </c>
@@ -6594,7 +6612,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="90" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
         <v>2175020</v>
       </c>
@@ -6647,7 +6665,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="91" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
         <v>2285005</v>
       </c>
@@ -6697,7 +6715,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="92" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
         <v>2285006</v>
       </c>
@@ -6744,7 +6762,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="93" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
         <v>2285007</v>
       </c>
@@ -6791,7 +6809,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="94" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
         <v>2286015</v>
       </c>
@@ -6835,7 +6853,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="95" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
         <v>2338044</v>
       </c>
@@ -6879,7 +6897,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="96" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
         <v>2342014</v>
       </c>
@@ -6926,7 +6944,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="97" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
         <v>5</v>
       </c>
@@ -6966,7 +6984,9 @@
       <c r="N97" s="5" t="s">
         <v>494</v>
       </c>
-      <c r="O97" s="3"/>
+      <c r="O97" s="5" t="s">
+        <v>608</v>
+      </c>
       <c r="Q97" t="s">
         <v>27</v>
       </c>
@@ -6974,7 +6994,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="98" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
         <v>2343027</v>
       </c>
@@ -7014,7 +7034,9 @@
       <c r="N98" s="5" t="s">
         <v>495</v>
       </c>
-      <c r="O98" s="3"/>
+      <c r="O98" s="5" t="s">
+        <v>607</v>
+      </c>
       <c r="Q98" t="s">
         <v>27</v>
       </c>
@@ -7022,7 +7044,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="99" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
         <v>2343027</v>
       </c>
@@ -7069,7 +7091,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="100" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
         <v>2343027</v>
       </c>
@@ -7106,7 +7128,9 @@
       <c r="M100" t="s">
         <v>211</v>
       </c>
-      <c r="N100" s="3"/>
+      <c r="N100" s="5" t="s">
+        <v>606</v>
+      </c>
       <c r="O100" s="3"/>
       <c r="Q100" t="s">
         <v>27</v>
@@ -7115,7 +7139,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="101" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
         <v>2347001</v>
       </c>
@@ -7165,7 +7189,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="102" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
         <v>2347003</v>
       </c>
@@ -7215,7 +7239,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="103" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
         <v>2347005</v>
       </c>
@@ -7266,7 +7290,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="104" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A104" s="2">
         <v>2347006</v>
       </c>
@@ -7316,7 +7340,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="105" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A105" s="2">
         <v>2347007</v>
       </c>
@@ -7367,7 +7391,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="106" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A106" s="2">
         <v>2347013</v>
       </c>
@@ -7417,7 +7441,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="107" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A107" s="2">
         <v>2347014</v>
       </c>
@@ -7467,7 +7491,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="108" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A108" s="2">
         <v>2347017</v>
       </c>
@@ -7517,7 +7541,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="109" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A109" s="2">
         <v>2347030</v>
       </c>
@@ -7568,7 +7592,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="110" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A110" s="2">
         <v>2347021</v>
       </c>
@@ -7618,7 +7642,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="111" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A111" s="2">
         <v>2347022</v>
       </c>
@@ -7670,7 +7694,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="112" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A112" s="2">
         <v>2347024</v>
       </c>
@@ -7720,7 +7744,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="113" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A113" s="2">
         <v>2347026</v>
       </c>
@@ -7771,7 +7795,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="114" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A114" s="2">
         <v>2347027</v>
       </c>
@@ -7814,7 +7838,9 @@
       <c r="N114" s="5" t="s">
         <v>483</v>
       </c>
-      <c r="O114" s="5"/>
+      <c r="O114" s="5" t="s">
+        <v>606</v>
+      </c>
       <c r="Q114" t="s">
         <v>27</v>
       </c>
@@ -7822,7 +7848,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="115" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A115" s="2">
         <v>2347029</v>
       </c>
@@ -7872,7 +7898,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="116" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A116" s="2">
         <v>2347031</v>
       </c>
@@ -7922,7 +7948,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="117" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A117" s="2">
         <v>2347038</v>
       </c>
@@ -7973,7 +7999,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="118" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A118" s="2">
         <v>2361002</v>
       </c>
@@ -8020,7 +8046,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="119" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A119" s="2">
         <v>2361002</v>
       </c>
@@ -8067,7 +8093,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="120" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A120" s="2">
         <v>2361002</v>
       </c>
@@ -8111,7 +8137,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="121" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A121" s="2">
         <v>2361004</v>
       </c>
@@ -8158,7 +8184,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="122" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A122" s="2">
         <v>2393002</v>
       </c>
@@ -8208,7 +8234,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="123" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A123" s="2">
         <v>2393002</v>
       </c>
@@ -8258,7 +8284,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="124" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A124" s="2">
         <v>2393002</v>
       </c>
@@ -8308,7 +8334,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="125" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A125" s="2">
         <v>2394004</v>
       </c>
@@ -8358,7 +8384,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="126" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A126" s="2">
         <v>2394004</v>
       </c>
@@ -8408,7 +8434,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="127" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A127" s="2">
         <v>2394004</v>
       </c>
@@ -8458,7 +8484,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="128" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A128" s="2">
         <v>2395003</v>
       </c>
@@ -8508,7 +8534,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="129" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A129" s="2">
         <v>2395003</v>
       </c>
@@ -8558,7 +8584,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="130" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A130" s="2">
         <v>2395003</v>
       </c>
@@ -8608,7 +8634,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="131" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A131" s="2">
         <v>2396001</v>
       </c>
@@ -8658,7 +8684,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="132" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A132" s="2">
         <v>2396001</v>
       </c>
@@ -8708,7 +8734,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="133" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A133" s="2">
         <v>2396001</v>
       </c>
@@ -8758,7 +8784,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="134" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A134" s="2">
         <v>2397003</v>
       </c>
@@ -8808,7 +8834,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="135" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A135" s="2">
         <v>2397003</v>
       </c>
@@ -8858,7 +8884,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="136" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A136" s="2">
         <v>2397003</v>
       </c>
@@ -8908,7 +8934,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="137" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A137" s="2">
         <v>2397008</v>
       </c>
@@ -8958,7 +8984,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="138" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A138" s="2">
         <v>2397008</v>
       </c>
@@ -9008,7 +9034,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="139" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A139" s="2">
         <v>2397008</v>
       </c>
@@ -9058,7 +9084,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="140" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A140" s="2">
         <v>2398001</v>
       </c>
@@ -9108,7 +9134,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="141" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A141" s="2">
         <v>2398001</v>
       </c>
@@ -9159,7 +9185,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="142" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A142" s="2">
         <v>2398001</v>
       </c>
@@ -9210,7 +9236,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="143" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A143" s="2">
         <v>2398006</v>
       </c>
@@ -9260,7 +9286,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="144" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A144" s="2">
         <v>2398006</v>
       </c>
@@ -9310,7 +9336,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="145" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A145" s="2">
         <v>2398006</v>
       </c>
@@ -9360,7 +9386,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="146" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A146" s="2">
         <v>2398013</v>
       </c>
@@ -9410,7 +9436,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="147" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A147" s="2">
         <v>2398013</v>
       </c>
@@ -9460,7 +9486,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="148" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A148" s="2">
         <v>2398013</v>
       </c>
@@ -9507,7 +9533,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="149" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A149" s="2">
         <v>2399003</v>
       </c>
@@ -9560,7 +9586,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="150" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A150" s="2">
         <v>2399003</v>
       </c>
@@ -9613,7 +9639,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="151" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A151" s="2">
         <v>2399003</v>
       </c>
@@ -9666,7 +9692,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="152" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A152" s="2">
         <v>2399010</v>
       </c>
@@ -9716,7 +9742,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="153" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A153" s="2">
         <v>2399010</v>
       </c>
@@ -9766,7 +9792,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="154" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A154" s="2">
         <v>2399010</v>
       </c>
@@ -9816,7 +9842,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="155" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A155" s="2">
         <v>2399014</v>
       </c>
@@ -9866,7 +9892,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="156" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A156" s="2">
         <v>2399014</v>
       </c>
@@ -9916,7 +9942,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="157" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A157" s="2">
         <v>2399014</v>
       </c>
@@ -9963,7 +9989,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="158" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A158" s="2">
         <v>2400003</v>
       </c>
@@ -10013,7 +10039,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="159" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A159" s="2">
         <v>2400003</v>
       </c>
@@ -10063,7 +10089,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="160" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A160" s="2">
         <v>2400003</v>
       </c>
@@ -10113,7 +10139,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="161" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A161" s="2">
         <v>2400008</v>
       </c>
@@ -10163,7 +10189,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="162" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A162" s="2">
         <v>2400008</v>
       </c>
@@ -10213,7 +10239,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="163" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A163" s="2">
         <v>2400008</v>
       </c>
@@ -10263,7 +10289,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="164" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A164" s="2">
         <v>2400012</v>
       </c>
@@ -10313,7 +10339,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="165" spans="1:18" ht="29" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:18" ht="32" x14ac:dyDescent="0.2">
       <c r="A165" s="2">
         <v>2400012</v>
       </c>
@@ -10363,7 +10389,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="166" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A166" s="2">
         <v>2400012</v>
       </c>
@@ -10410,7 +10436,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="167" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A167" s="2">
         <v>2401001</v>
       </c>
@@ -10460,7 +10486,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="168" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A168" s="2">
         <v>2401001</v>
       </c>
@@ -10510,7 +10536,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="169" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A169" s="2">
         <v>2401001</v>
       </c>
@@ -10560,7 +10586,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="170" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A170" s="2">
         <v>2401007</v>
       </c>
@@ -10610,7 +10636,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="171" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A171" s="2">
         <v>2401007</v>
       </c>
@@ -10660,7 +10686,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="172" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A172" s="2">
         <v>2401007</v>
       </c>
@@ -10710,7 +10736,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="173" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A173" s="2">
         <v>2401013</v>
       </c>
@@ -10760,7 +10786,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="174" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A174" s="2">
         <v>2401013</v>
       </c>
@@ -10810,7 +10836,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="175" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A175" s="2">
         <v>2401013</v>
       </c>
@@ -10860,7 +10886,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="176" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A176" s="2">
         <v>2401018</v>
       </c>
@@ -10910,7 +10936,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="177" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A177" s="2">
         <v>2401018</v>
       </c>
@@ -10960,7 +10986,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="178" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A178" s="2">
         <v>2401018</v>
       </c>
@@ -11007,7 +11033,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="179" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A179" s="2">
         <v>2401018</v>
       </c>
@@ -11057,7 +11083,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="180" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A180" s="2">
         <v>2401018</v>
       </c>
@@ -11104,7 +11130,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="181" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A181" s="2">
         <v>2401018</v>
       </c>
@@ -11151,7 +11177,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="182" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A182" s="2">
         <v>2401018</v>
       </c>
@@ -11198,7 +11224,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="183" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A183" s="2">
         <v>2402003</v>
       </c>
@@ -11249,7 +11275,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="184" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A184" s="2">
         <v>2402003</v>
       </c>
@@ -11300,7 +11326,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="185" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A185" s="2">
         <v>2402003</v>
       </c>
@@ -11351,7 +11377,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="186" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A186" s="2">
         <v>2402008</v>
       </c>
@@ -11404,7 +11430,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="187" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A187" s="2">
         <v>2402008</v>
       </c>
@@ -11457,7 +11483,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="188" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A188" s="2">
         <v>2402008</v>
       </c>
@@ -11510,7 +11536,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="189" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A189" s="2">
         <v>2402015</v>
       </c>
@@ -11557,7 +11583,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="190" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A190" s="2">
         <v>2402015</v>
       </c>
@@ -11604,7 +11630,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="191" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A191" s="2">
         <v>2402015</v>
       </c>
@@ -11641,7 +11667,9 @@
       <c r="M191" t="s">
         <v>26</v>
       </c>
-      <c r="N191" s="3"/>
+      <c r="N191" s="5" t="s">
+        <v>609</v>
+      </c>
       <c r="O191" s="3"/>
       <c r="Q191" t="s">
         <v>27</v>
@@ -11650,7 +11678,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="192" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A192" s="2">
         <v>2403004</v>
       </c>
@@ -11701,7 +11729,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="193" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A193" s="2">
         <v>2403004</v>
       </c>
@@ -11752,7 +11780,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="194" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A194" s="2">
         <v>2403004</v>
       </c>
@@ -11803,7 +11831,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="195" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A195" s="2">
         <v>2403009</v>
       </c>
@@ -11856,7 +11884,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="196" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A196" s="2">
         <v>2403009</v>
       </c>
@@ -11909,7 +11937,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="197" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A197" s="2">
         <v>2403009</v>
       </c>
@@ -11962,7 +11990,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="198" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A198" s="2">
         <v>2403013</v>
       </c>
@@ -12009,7 +12037,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="199" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A199" s="2">
         <v>2403013</v>
       </c>
@@ -12056,7 +12084,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="200" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A200" s="2">
         <v>2403013</v>
       </c>
@@ -12103,7 +12131,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="201" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A201" s="2">
         <v>2404001</v>
       </c>
@@ -12153,7 +12181,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="202" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A202" s="2">
         <v>2404001</v>
       </c>
@@ -12203,7 +12231,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="203" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A203" s="2">
         <v>2404001</v>
       </c>
@@ -12253,7 +12281,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="204" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A204" s="2">
         <v>2404006</v>
       </c>
@@ -12303,7 +12331,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="205" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A205" s="2">
         <v>2404006</v>
       </c>
@@ -12353,7 +12381,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="206" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A206" s="2">
         <v>2404006</v>
       </c>
@@ -12403,7 +12431,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="207" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A207" s="2">
         <v>2404015</v>
       </c>
@@ -12453,7 +12481,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="208" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A208" s="2">
         <v>2404015</v>
       </c>
@@ -12503,7 +12531,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="209" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A209" s="2">
         <v>2404015</v>
       </c>
@@ -12553,7 +12581,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="210" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A210" s="2">
         <v>2405001</v>
       </c>
@@ -12603,7 +12631,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="211" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A211" s="2">
         <v>2405001</v>
       </c>
@@ -12653,7 +12681,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="212" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A212" s="2">
         <v>2405001</v>
       </c>
@@ -12703,7 +12731,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="213" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A213" s="2">
         <v>2405006</v>
       </c>
@@ -12756,7 +12784,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="214" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A214" s="2">
         <v>2405006</v>
       </c>
@@ -12809,7 +12837,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="215" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A215" s="2">
         <v>2405006</v>
       </c>
@@ -12862,7 +12890,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="216" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A216" s="2">
         <v>2405015</v>
       </c>
@@ -12912,7 +12940,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="217" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A217" s="2">
         <v>2405015</v>
       </c>
@@ -12962,7 +12990,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="218" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A218" s="2">
         <v>2405015</v>
       </c>
@@ -13009,7 +13037,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="219" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A219" s="2">
         <v>2406004</v>
       </c>
@@ -13059,7 +13087,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="220" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A220" s="2">
         <v>2406004</v>
       </c>
@@ -13109,7 +13137,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="221" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A221" s="2">
         <v>2406004</v>
       </c>
@@ -13162,7 +13190,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="222" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A222" s="2">
         <v>2406004</v>
       </c>
@@ -13212,7 +13240,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="223" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A223" s="2">
         <v>2406004</v>
       </c>
@@ -13265,7 +13293,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="224" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A224" s="2">
         <v>2406009</v>
       </c>
@@ -13315,7 +13343,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="225" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A225" s="2">
         <v>2406009</v>
       </c>
@@ -13365,7 +13393,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="226" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A226" s="2">
         <v>2406009</v>
       </c>
@@ -13415,7 +13443,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="227" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A227" s="2">
         <v>2406009</v>
       </c>
@@ -13465,7 +13493,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="228" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A228" s="2">
         <v>2406009</v>
       </c>
@@ -13515,7 +13543,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="229" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A229" s="2">
         <v>2406012</v>
       </c>
@@ -13565,7 +13593,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="230" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A230" s="2">
         <v>2406012</v>
       </c>
@@ -13618,7 +13646,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="231" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A231" s="2">
         <v>2406012</v>
       </c>
@@ -13671,7 +13699,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="232" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A232" s="2">
         <v>2059001</v>
       </c>
@@ -13721,7 +13749,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="233" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A233" s="2">
         <v>2059002</v>
       </c>
@@ -13774,7 +13802,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="234" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A234" s="2">
         <v>2059006</v>
       </c>
@@ -13824,7 +13852,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="235" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A235" s="2">
         <v>2140011</v>
       </c>
@@ -13871,7 +13899,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="236" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A236" s="2">
         <v>2390004</v>
       </c>
@@ -13921,7 +13949,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="237" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A237" s="2">
         <v>2390004</v>
       </c>
@@ -13971,7 +13999,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="238" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A238" s="2">
         <v>2390004</v>
       </c>
@@ -14021,7 +14049,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="239" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A239" s="2">
         <v>2390009</v>
       </c>
@@ -14071,7 +14099,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="240" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A240" s="2">
         <v>2390009</v>
       </c>
@@ -14121,7 +14149,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="241" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A241" s="2">
         <v>2390009</v>
       </c>
@@ -14171,7 +14199,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="242" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A242" s="2">
         <v>2390013</v>
       </c>
@@ -14218,7 +14246,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="243" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A243" s="2">
         <v>2390013</v>
       </c>
@@ -14265,7 +14293,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="244" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A244" s="2">
         <v>2390013</v>
       </c>
@@ -14312,7 +14340,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="252" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="L252" s="1"/>
     </row>
   </sheetData>

--- a/POD_2026-27_11-5-2026.xlsx
+++ b/POD_2026-27_11-5-2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr showInkAnnotation="0" autoCompressPictures="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guillermo.vera/Desktop/POD2627/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guillermo.vera/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{591172C4-32AD-084E-8988-BD031E514157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40FB5FA1-041E-BE4C-B2E5-7B999FCA8279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3119" uniqueCount="610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3125" uniqueCount="612">
   <si>
     <t>POD_2026-27_11-5-2026</t>
   </si>
@@ -1866,6 +1866,12 @@
   </si>
   <si>
     <t>HÉCTOR RODRIGO IGLESIAS (21)</t>
+  </si>
+  <si>
+    <t>ELENA CARRERAS (10)</t>
+  </si>
+  <si>
+    <t>FRANCISCO JAVIER MARÍN (16)</t>
   </si>
 </sst>
 </file>
@@ -5147,6 +5153,9 @@
       <c r="M59" t="s">
         <v>26</v>
       </c>
+      <c r="N59" s="6" t="s">
+        <v>611</v>
+      </c>
       <c r="Q59" t="s">
         <v>27</v>
       </c>
@@ -5294,6 +5303,9 @@
       <c r="M62" t="s">
         <v>26</v>
       </c>
+      <c r="N62" s="6" t="s">
+        <v>611</v>
+      </c>
       <c r="Q62" t="s">
         <v>27</v>
       </c>
@@ -5344,6 +5356,9 @@
       <c r="N63" t="s">
         <v>556</v>
       </c>
+      <c r="O63" s="6" t="s">
+        <v>611</v>
+      </c>
       <c r="Q63" t="s">
         <v>27</v>
       </c>
@@ -6076,6 +6091,9 @@
       <c r="N78" s="6" t="s">
         <v>537</v>
       </c>
+      <c r="O78" s="6" t="s">
+        <v>610</v>
+      </c>
       <c r="Q78" t="s">
         <v>27</v>
       </c>
@@ -6229,6 +6247,9 @@
       <c r="N81" s="6" t="s">
         <v>559</v>
       </c>
+      <c r="O81" s="6" t="s">
+        <v>610</v>
+      </c>
       <c r="Q81" t="s">
         <v>27</v>
       </c>
@@ -6331,6 +6352,9 @@
       </c>
       <c r="N83" s="6" t="s">
         <v>523</v>
+      </c>
+      <c r="O83" s="6" t="s">
+        <v>610</v>
       </c>
       <c r="Q83" t="s">
         <v>27</v>

--- a/POD_2026-27_11-5-2026.xlsx
+++ b/POD_2026-27_11-5-2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr showInkAnnotation="0" autoCompressPictures="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guillermo.vera/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guillermo.vera/Desktop/POD2627/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40FB5FA1-041E-BE4C-B2E5-7B999FCA8279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AF0CB16-D932-EE49-95FB-94367CC2B115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3125" uniqueCount="612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3119" uniqueCount="610">
   <si>
     <t>POD_2026-27_11-5-2026</t>
   </si>
@@ -1805,9 +1805,6 @@
     <t>Rubén Carrillo (21)</t>
   </si>
   <si>
-    <t>Lorenzo Martini (14)</t>
-  </si>
-  <si>
     <t>Lorenzo Martini (16)</t>
   </si>
   <si>
@@ -1868,10 +1865,7 @@
     <t>HÉCTOR RODRIGO IGLESIAS (21)</t>
   </si>
   <si>
-    <t>ELENA CARRERAS (10)</t>
-  </si>
-  <si>
-    <t>FRANCISCO JAVIER MARÍN (16)</t>
+    <t>Lorenzo Martini (12)</t>
   </si>
 </sst>
 </file>
@@ -5153,9 +5147,6 @@
       <c r="M59" t="s">
         <v>26</v>
       </c>
-      <c r="N59" s="6" t="s">
-        <v>611</v>
-      </c>
       <c r="Q59" t="s">
         <v>27</v>
       </c>
@@ -5303,9 +5294,6 @@
       <c r="M62" t="s">
         <v>26</v>
       </c>
-      <c r="N62" s="6" t="s">
-        <v>611</v>
-      </c>
       <c r="Q62" t="s">
         <v>27</v>
       </c>
@@ -5356,9 +5344,6 @@
       <c r="N63" t="s">
         <v>556</v>
       </c>
-      <c r="O63" s="6" t="s">
-        <v>611</v>
-      </c>
       <c r="Q63" t="s">
         <v>27</v>
       </c>
@@ -6039,7 +6024,7 @@
         <v>513</v>
       </c>
       <c r="O77" s="6" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="Q77" t="s">
         <v>27</v>
@@ -6091,9 +6076,6 @@
       <c r="N78" s="6" t="s">
         <v>537</v>
       </c>
-      <c r="O78" s="6" t="s">
-        <v>610</v>
-      </c>
       <c r="Q78" t="s">
         <v>27</v>
       </c>
@@ -6247,9 +6229,6 @@
       <c r="N81" s="6" t="s">
         <v>559</v>
       </c>
-      <c r="O81" s="6" t="s">
-        <v>610</v>
-      </c>
       <c r="Q81" t="s">
         <v>27</v>
       </c>
@@ -6353,9 +6332,6 @@
       <c r="N83" s="6" t="s">
         <v>523</v>
       </c>
-      <c r="O83" s="6" t="s">
-        <v>610</v>
-      </c>
       <c r="Q83" t="s">
         <v>27</v>
       </c>
@@ -6680,7 +6656,7 @@
         <v>568</v>
       </c>
       <c r="O90" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="Q90" t="s">
         <v>27</v>
@@ -7009,7 +6985,7 @@
         <v>494</v>
       </c>
       <c r="O97" s="5" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="Q97" t="s">
         <v>27</v>
@@ -7059,7 +7035,7 @@
         <v>495</v>
       </c>
       <c r="O98" s="5" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q98" t="s">
         <v>27</v>
@@ -7153,7 +7129,7 @@
         <v>211</v>
       </c>
       <c r="N100" s="5" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="O100" s="3"/>
       <c r="Q100" t="s">
@@ -7863,7 +7839,7 @@
         <v>483</v>
       </c>
       <c r="O114" s="5" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="Q114" t="s">
         <v>27</v>
@@ -11692,7 +11668,7 @@
         <v>26</v>
       </c>
       <c r="N191" s="5" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="O191" s="3"/>
       <c r="Q191" t="s">
@@ -12495,8 +12471,8 @@
       <c r="N207" t="s">
         <v>423</v>
       </c>
-      <c r="O207" t="s">
-        <v>589</v>
+      <c r="O207" s="6" t="s">
+        <v>609</v>
       </c>
       <c r="Q207" t="s">
         <v>27</v>
@@ -12546,7 +12522,7 @@
         <v>510</v>
       </c>
       <c r="O208" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="Q208" t="s">
         <v>27</v>
@@ -12596,7 +12572,7 @@
         <v>510</v>
       </c>
       <c r="O209" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="Q209" t="s">
         <v>27</v>
@@ -12799,7 +12775,7 @@
         <v>499</v>
       </c>
       <c r="O213" s="6" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="Q213" t="s">
         <v>27</v>
@@ -12852,7 +12828,7 @@
         <v>500</v>
       </c>
       <c r="O214" s="6" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="Q214" t="s">
         <v>27</v>
@@ -12905,7 +12881,7 @@
         <v>500</v>
       </c>
       <c r="O215" s="6" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="Q215" t="s">
         <v>27</v>
@@ -13205,7 +13181,7 @@
         <v>507</v>
       </c>
       <c r="O221" s="6" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="Q221" t="s">
         <v>27</v>
@@ -13308,7 +13284,7 @@
         <v>507</v>
       </c>
       <c r="O223" s="6" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="Q223" t="s">
         <v>27</v>
@@ -13608,7 +13584,7 @@
         <v>26</v>
       </c>
       <c r="N229" s="6" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="Q229" t="s">
         <v>27</v>
@@ -13658,10 +13634,10 @@
         <v>26</v>
       </c>
       <c r="N230" s="6" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="O230" s="6" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="Q230" t="s">
         <v>27</v>
@@ -13711,10 +13687,10 @@
         <v>26</v>
       </c>
       <c r="N231" s="6" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="O231" s="6" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="Q231" t="s">
         <v>27</v>
@@ -13764,7 +13740,7 @@
         <v>26</v>
       </c>
       <c r="N232" s="6" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="Q232" t="s">
         <v>27</v>
@@ -13814,10 +13790,10 @@
         <v>26</v>
       </c>
       <c r="N233" s="6" t="s">
+        <v>595</v>
+      </c>
+      <c r="O233" s="6" t="s">
         <v>596</v>
-      </c>
-      <c r="O233" s="6" t="s">
-        <v>597</v>
       </c>
       <c r="Q233" t="s">
         <v>27</v>
@@ -13867,7 +13843,7 @@
         <v>26</v>
       </c>
       <c r="N234" s="6" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="Q234" t="s">
         <v>27</v>
@@ -13964,7 +13940,7 @@
         <v>26</v>
       </c>
       <c r="N236" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="Q236" t="s">
         <v>27</v>
@@ -14014,7 +13990,7 @@
         <v>26</v>
       </c>
       <c r="N237" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="Q237" t="s">
         <v>27</v>
@@ -14064,7 +14040,7 @@
         <v>26</v>
       </c>
       <c r="N238" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="Q238" t="s">
         <v>27</v>
@@ -14114,7 +14090,7 @@
         <v>26</v>
       </c>
       <c r="N239" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="Q239" t="s">
         <v>27</v>
@@ -14164,7 +14140,7 @@
         <v>26</v>
       </c>
       <c r="N240" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="Q240" t="s">
         <v>27</v>
@@ -14214,7 +14190,7 @@
         <v>26</v>
       </c>
       <c r="N241" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="Q241" t="s">
         <v>27</v>

--- a/POD_2026-27_11-5-2026.xlsx
+++ b/POD_2026-27_11-5-2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr showInkAnnotation="0" autoCompressPictures="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guillermo.vera/Desktop/POD2627/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guillermo.vera/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AF0CB16-D932-EE49-95FB-94367CC2B115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FA87C84-60ED-764A-A83B-B2ACFCF30C20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3119" uniqueCount="610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3125" uniqueCount="612">
   <si>
     <t>POD_2026-27_11-5-2026</t>
   </si>
@@ -1863,6 +1863,12 @@
   </si>
   <si>
     <t>HÉCTOR RODRIGO IGLESIAS (21)</t>
+  </si>
+  <si>
+    <t>ELENA CARRERAS (10)</t>
+  </si>
+  <si>
+    <t>FRANCISCO JAVIER MARÍN (16)</t>
   </si>
   <si>
     <t>Lorenzo Martini (12)</t>
@@ -5147,6 +5153,9 @@
       <c r="M59" t="s">
         <v>26</v>
       </c>
+      <c r="N59" s="6" t="s">
+        <v>610</v>
+      </c>
       <c r="Q59" t="s">
         <v>27</v>
       </c>
@@ -5294,6 +5303,9 @@
       <c r="M62" t="s">
         <v>26</v>
       </c>
+      <c r="N62" s="6" t="s">
+        <v>610</v>
+      </c>
       <c r="Q62" t="s">
         <v>27</v>
       </c>
@@ -5344,6 +5356,9 @@
       <c r="N63" t="s">
         <v>556</v>
       </c>
+      <c r="O63" s="6" t="s">
+        <v>610</v>
+      </c>
       <c r="Q63" t="s">
         <v>27</v>
       </c>
@@ -6076,6 +6091,9 @@
       <c r="N78" s="6" t="s">
         <v>537</v>
       </c>
+      <c r="O78" s="6" t="s">
+        <v>609</v>
+      </c>
       <c r="Q78" t="s">
         <v>27</v>
       </c>
@@ -6229,6 +6247,9 @@
       <c r="N81" s="6" t="s">
         <v>559</v>
       </c>
+      <c r="O81" s="6" t="s">
+        <v>609</v>
+      </c>
       <c r="Q81" t="s">
         <v>27</v>
       </c>
@@ -6332,6 +6353,9 @@
       <c r="N83" s="6" t="s">
         <v>523</v>
       </c>
+      <c r="O83" s="6" t="s">
+        <v>609</v>
+      </c>
       <c r="Q83" t="s">
         <v>27</v>
       </c>
@@ -12472,7 +12496,7 @@
         <v>423</v>
       </c>
       <c r="O207" s="6" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="Q207" t="s">
         <v>27</v>

--- a/POD_2026-27_11-5-2026.xlsx
+++ b/POD_2026-27_11-5-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guillermo.vera/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FA87C84-60ED-764A-A83B-B2ACFCF30C20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{308F942D-C8D7-8F43-899F-8045A104B9DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1790,9 +1790,6 @@
     <t>Daniel Rodríguez (32)</t>
   </si>
   <si>
-    <t>Daniel Rodríguez (4)</t>
-  </si>
-  <si>
     <t>Rubén Carrillo (24)</t>
   </si>
   <si>
@@ -1872,6 +1869,9 @@
   </si>
   <si>
     <t>Lorenzo Martini (12)</t>
+  </si>
+  <si>
+    <t>Daniel Rodríguez (8)</t>
   </si>
 </sst>
 </file>
@@ -5154,7 +5154,7 @@
         <v>26</v>
       </c>
       <c r="N59" s="6" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q59" t="s">
         <v>27</v>
@@ -5304,7 +5304,7 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q62" t="s">
         <v>27</v>
@@ -5357,7 +5357,7 @@
         <v>556</v>
       </c>
       <c r="O63" s="6" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q63" t="s">
         <v>27</v>
@@ -6039,7 +6039,7 @@
         <v>513</v>
       </c>
       <c r="O77" s="6" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="Q77" t="s">
         <v>27</v>
@@ -6092,7 +6092,7 @@
         <v>537</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q78" t="s">
         <v>27</v>
@@ -6248,7 +6248,7 @@
         <v>559</v>
       </c>
       <c r="O81" s="6" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q81" t="s">
         <v>27</v>
@@ -6354,7 +6354,7 @@
         <v>523</v>
       </c>
       <c r="O83" s="6" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q83" t="s">
         <v>27</v>
@@ -6680,7 +6680,7 @@
         <v>568</v>
       </c>
       <c r="O90" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="Q90" t="s">
         <v>27</v>
@@ -7009,7 +7009,7 @@
         <v>494</v>
       </c>
       <c r="O97" s="5" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="Q97" t="s">
         <v>27</v>
@@ -7059,7 +7059,7 @@
         <v>495</v>
       </c>
       <c r="O98" s="5" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="Q98" t="s">
         <v>27</v>
@@ -7153,7 +7153,7 @@
         <v>211</v>
       </c>
       <c r="N100" s="5" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="O100" s="3"/>
       <c r="Q100" t="s">
@@ -7863,7 +7863,7 @@
         <v>483</v>
       </c>
       <c r="O114" s="5" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="Q114" t="s">
         <v>27</v>
@@ -11497,8 +11497,8 @@
       <c r="N187" t="s">
         <v>390</v>
       </c>
-      <c r="O187" t="s">
-        <v>584</v>
+      <c r="O187" s="6" t="s">
+        <v>611</v>
       </c>
       <c r="Q187" t="s">
         <v>27</v>
@@ -11550,8 +11550,8 @@
       <c r="N188" t="s">
         <v>390</v>
       </c>
-      <c r="O188" t="s">
-        <v>584</v>
+      <c r="O188" s="6" t="s">
+        <v>611</v>
       </c>
       <c r="Q188" t="s">
         <v>27</v>
@@ -11692,7 +11692,7 @@
         <v>26</v>
       </c>
       <c r="N191" s="5" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O191" s="3"/>
       <c r="Q191" t="s">
@@ -11899,7 +11899,7 @@
         <v>551</v>
       </c>
       <c r="O195" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="Q195" t="s">
         <v>27</v>
@@ -11952,7 +11952,7 @@
         <v>552</v>
       </c>
       <c r="O196" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="Q196" t="s">
         <v>27</v>
@@ -12005,7 +12005,7 @@
         <v>552</v>
       </c>
       <c r="O197" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="Q197" t="s">
         <v>27</v>
@@ -12496,7 +12496,7 @@
         <v>423</v>
       </c>
       <c r="O207" s="6" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q207" t="s">
         <v>27</v>
@@ -12546,7 +12546,7 @@
         <v>510</v>
       </c>
       <c r="O208" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="Q208" t="s">
         <v>27</v>
@@ -12596,7 +12596,7 @@
         <v>510</v>
       </c>
       <c r="O209" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="Q209" t="s">
         <v>27</v>
@@ -12799,7 +12799,7 @@
         <v>499</v>
       </c>
       <c r="O213" s="6" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="Q213" t="s">
         <v>27</v>
@@ -12852,7 +12852,7 @@
         <v>500</v>
       </c>
       <c r="O214" s="6" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="Q214" t="s">
         <v>27</v>
@@ -12905,7 +12905,7 @@
         <v>500</v>
       </c>
       <c r="O215" s="6" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="Q215" t="s">
         <v>27</v>
@@ -13205,7 +13205,7 @@
         <v>507</v>
       </c>
       <c r="O221" s="6" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="Q221" t="s">
         <v>27</v>
@@ -13308,7 +13308,7 @@
         <v>507</v>
       </c>
       <c r="O223" s="6" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="Q223" t="s">
         <v>27</v>
@@ -13608,7 +13608,7 @@
         <v>26</v>
       </c>
       <c r="N229" s="6" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="Q229" t="s">
         <v>27</v>
@@ -13658,10 +13658,10 @@
         <v>26</v>
       </c>
       <c r="N230" s="6" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="O230" s="6" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="Q230" t="s">
         <v>27</v>
@@ -13711,10 +13711,10 @@
         <v>26</v>
       </c>
       <c r="N231" s="6" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="O231" s="6" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="Q231" t="s">
         <v>27</v>
@@ -13764,7 +13764,7 @@
         <v>26</v>
       </c>
       <c r="N232" s="6" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="Q232" t="s">
         <v>27</v>
@@ -13814,10 +13814,10 @@
         <v>26</v>
       </c>
       <c r="N233" s="6" t="s">
+        <v>594</v>
+      </c>
+      <c r="O233" s="6" t="s">
         <v>595</v>
-      </c>
-      <c r="O233" s="6" t="s">
-        <v>596</v>
       </c>
       <c r="Q233" t="s">
         <v>27</v>
@@ -13867,7 +13867,7 @@
         <v>26</v>
       </c>
       <c r="N234" s="6" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="Q234" t="s">
         <v>27</v>
@@ -13964,7 +13964,7 @@
         <v>26</v>
       </c>
       <c r="N236" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="Q236" t="s">
         <v>27</v>
@@ -14014,7 +14014,7 @@
         <v>26</v>
       </c>
       <c r="N237" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="Q237" t="s">
         <v>27</v>
@@ -14064,7 +14064,7 @@
         <v>26</v>
       </c>
       <c r="N238" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="Q238" t="s">
         <v>27</v>
@@ -14114,7 +14114,7 @@
         <v>26</v>
       </c>
       <c r="N239" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="Q239" t="s">
         <v>27</v>
@@ -14164,7 +14164,7 @@
         <v>26</v>
       </c>
       <c r="N240" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="Q240" t="s">
         <v>27</v>
@@ -14214,7 +14214,7 @@
         <v>26</v>
       </c>
       <c r="N241" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="Q241" t="s">
         <v>27</v>
@@ -14261,7 +14261,7 @@
         <v>26</v>
       </c>
       <c r="N242" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="Q242" t="s">
         <v>27</v>
@@ -14308,7 +14308,7 @@
         <v>26</v>
       </c>
       <c r="N243" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="Q243" t="s">
         <v>27</v>
@@ -14355,7 +14355,7 @@
         <v>26</v>
       </c>
       <c r="N244" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="Q244" t="s">
         <v>27</v>

--- a/POD_2026-27_11-5-2026.xlsx
+++ b/POD_2026-27_11-5-2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr showInkAnnotation="0" autoCompressPictures="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guillermo.vera/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guillermo.vera/Desktop/POD2627/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{308F942D-C8D7-8F43-899F-8045A104B9DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A0CF233-1C62-7443-BB28-C73371E60034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3125" uniqueCount="612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3126" uniqueCount="612">
   <si>
     <t>POD_2026-27_11-5-2026</t>
   </si>
@@ -6197,6 +6197,9 @@
       <c r="N80" t="s">
         <v>177</v>
       </c>
+      <c r="O80" s="6" t="s">
+        <v>608</v>
+      </c>
       <c r="Q80" t="s">
         <v>27</v>
       </c>

--- a/POD_2026-27_11-5-2026.xlsx
+++ b/POD_2026-27_11-5-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guillermo.vera/Desktop/POD2627/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A0CF233-1C62-7443-BB28-C73371E60034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15CF2EE8-A44E-F745-A779-CCB68D157AC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3126" uniqueCount="612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3128" uniqueCount="612">
   <si>
     <t>POD_2026-27_11-5-2026</t>
   </si>
@@ -482,9 +482,6 @@
     <t>L(17:00 - 19:00), J(17:00 - 19:00)</t>
   </si>
   <si>
-    <t>CHRISTIAN VANHILLE (35)</t>
-  </si>
-  <si>
     <t>(2029) GRADO EN INGENIERIA DE LA ENERGIA (MOSTOLES)</t>
   </si>
   <si>
@@ -1739,9 +1736,6 @@
     <t>Guille Carrión (16)</t>
   </si>
   <si>
-    <t>Lorenzo Martini (35)</t>
-  </si>
-  <si>
     <t>Lorenzo Martini (60)</t>
   </si>
   <si>
@@ -1872,6 +1866,12 @@
   </si>
   <si>
     <t>Daniel Rodríguez (8)</t>
+  </si>
+  <si>
+    <t>CHRISTIAN VANHILLE (30)</t>
+  </si>
+  <si>
+    <t>Lorenzo Martini (30)</t>
   </si>
 </sst>
 </file>
@@ -2355,10 +2355,10 @@
         <v>14</v>
       </c>
       <c r="O2" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>484</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>485</v>
       </c>
       <c r="Q2" s="1" t="s">
         <v>15</v>
@@ -2634,7 +2634,7 @@
         <v>26</v>
       </c>
       <c r="N8" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="Q8" t="s">
         <v>27</v>
@@ -2681,7 +2681,7 @@
         <v>26</v>
       </c>
       <c r="N9" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="Q9" t="s">
         <v>27</v>
@@ -2728,7 +2728,7 @@
         <v>26</v>
       </c>
       <c r="N10" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="Q10" t="s">
         <v>27</v>
@@ -2775,10 +2775,10 @@
         <v>26</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="Q11" t="s">
         <v>27</v>
@@ -2825,10 +2825,10 @@
         <v>26</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="Q12" t="s">
         <v>27</v>
@@ -2875,10 +2875,10 @@
         <v>26</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="O13" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="Q13" t="s">
         <v>27</v>
@@ -2925,7 +2925,7 @@
         <v>26</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="Q14" t="s">
         <v>27</v>
@@ -2972,7 +2972,7 @@
         <v>26</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="Q15" t="s">
         <v>27</v>
@@ -3019,7 +3019,7 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="Q16" t="s">
         <v>27</v>
@@ -3066,7 +3066,7 @@
         <v>26</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="Q17" t="s">
         <v>27</v>
@@ -3113,7 +3113,7 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="Q18" t="s">
         <v>27</v>
@@ -3163,7 +3163,7 @@
         <v>26</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="Q19" t="s">
         <v>27</v>
@@ -3213,7 +3213,7 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="Q20" t="s">
         <v>27</v>
@@ -3263,7 +3263,7 @@
         <v>26</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="Q21" t="s">
         <v>27</v>
@@ -3313,7 +3313,7 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="Q22" t="s">
         <v>27</v>
@@ -3363,7 +3363,7 @@
         <v>26</v>
       </c>
       <c r="N23" s="6" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="Q23" t="s">
         <v>27</v>
@@ -3413,7 +3413,7 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="Q24" t="s">
         <v>27</v>
@@ -3463,7 +3463,7 @@
         <v>26</v>
       </c>
       <c r="N25" s="6" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="Q25" t="s">
         <v>27</v>
@@ -3513,7 +3513,7 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="Q26" t="s">
         <v>27</v>
@@ -3563,7 +3563,7 @@
         <v>26</v>
       </c>
       <c r="N27" s="6" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="Q27" t="s">
         <v>27</v>
@@ -3613,7 +3613,7 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="Q28" t="s">
         <v>27</v>
@@ -3660,7 +3660,7 @@
         <v>26</v>
       </c>
       <c r="N29" s="7" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="Q29" t="s">
         <v>27</v>
@@ -3710,7 +3710,7 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="Q30" t="s">
         <v>27</v>
@@ -3760,7 +3760,7 @@
         <v>26</v>
       </c>
       <c r="N31" s="6" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="Q31" t="s">
         <v>27</v>
@@ -3807,7 +3807,7 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="Q32" t="s">
         <v>27</v>
@@ -3854,7 +3854,7 @@
         <v>26</v>
       </c>
       <c r="N33" s="6" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="Q33" t="s">
         <v>27</v>
@@ -3904,7 +3904,7 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="Q34" t="s">
         <v>27</v>
@@ -3954,7 +3954,7 @@
         <v>26</v>
       </c>
       <c r="N35" s="6" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="Q35" t="s">
         <v>27</v>
@@ -4004,7 +4004,7 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="Q36" t="s">
         <v>27</v>
@@ -4054,7 +4054,7 @@
         <v>26</v>
       </c>
       <c r="N37" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="Q37" t="s">
         <v>27</v>
@@ -4101,7 +4101,7 @@
         <v>26</v>
       </c>
       <c r="N38" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="Q38" t="s">
         <v>27</v>
@@ -4148,7 +4148,7 @@
         <v>26</v>
       </c>
       <c r="N39" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="Q39" t="s">
         <v>27</v>
@@ -4198,7 +4198,7 @@
         <v>26</v>
       </c>
       <c r="N40" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="Q40" t="s">
         <v>27</v>
@@ -4248,7 +4248,7 @@
         <v>26</v>
       </c>
       <c r="N41" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="Q41" t="s">
         <v>27</v>
@@ -4298,7 +4298,7 @@
         <v>26</v>
       </c>
       <c r="N42" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="Q42" t="s">
         <v>27</v>
@@ -4348,10 +4348,10 @@
         <v>26</v>
       </c>
       <c r="N43" t="s">
+        <v>552</v>
+      </c>
+      <c r="O43" t="s">
         <v>553</v>
-      </c>
-      <c r="O43" t="s">
-        <v>554</v>
       </c>
       <c r="Q43" t="s">
         <v>27</v>
@@ -4401,10 +4401,10 @@
         <v>26</v>
       </c>
       <c r="N44" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="O44" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="Q44" t="s">
         <v>27</v>
@@ -4454,7 +4454,7 @@
         <v>26</v>
       </c>
       <c r="N45" s="6" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q45" t="s">
         <v>27</v>
@@ -4504,7 +4504,7 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="Q46" t="s">
         <v>27</v>
@@ -4554,7 +4554,7 @@
         <v>26</v>
       </c>
       <c r="N47" s="6" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="Q47" t="s">
         <v>27</v>
@@ -4604,7 +4604,7 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="Q48" t="s">
         <v>27</v>
@@ -4654,7 +4654,7 @@
         <v>26</v>
       </c>
       <c r="N49" s="6" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="Q49" t="s">
         <v>27</v>
@@ -4704,7 +4704,7 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="Q50" t="s">
         <v>27</v>
@@ -4754,7 +4754,7 @@
         <v>26</v>
       </c>
       <c r="N51" s="6" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q51" t="s">
         <v>27</v>
@@ -4804,7 +4804,7 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="Q52" t="s">
         <v>27</v>
@@ -4854,7 +4854,7 @@
         <v>26</v>
       </c>
       <c r="N53" s="6" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="Q53" t="s">
         <v>27</v>
@@ -4904,7 +4904,7 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="Q54" t="s">
         <v>27</v>
@@ -4954,7 +4954,7 @@
         <v>26</v>
       </c>
       <c r="N55" s="6" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="Q55" t="s">
         <v>27</v>
@@ -5004,7 +5004,7 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="Q56" t="s">
         <v>27</v>
@@ -5054,7 +5054,7 @@
         <v>26</v>
       </c>
       <c r="N57" s="6" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="Q57" t="s">
         <v>27</v>
@@ -5095,7 +5095,7 @@
         <v>41</v>
       </c>
       <c r="K58" s="6" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="L58" t="s">
         <v>130</v>
@@ -5104,7 +5104,7 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="Q58" t="s">
         <v>27</v>
@@ -5145,7 +5145,7 @@
         <v>41</v>
       </c>
       <c r="K59" s="6" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="L59" t="s">
         <v>130</v>
@@ -5154,7 +5154,7 @@
         <v>26</v>
       </c>
       <c r="N59" s="6" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="Q59" t="s">
         <v>27</v>
@@ -5204,7 +5204,7 @@
         <v>26</v>
       </c>
       <c r="N60" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="Q60" t="s">
         <v>27</v>
@@ -5245,7 +5245,7 @@
         <v>41</v>
       </c>
       <c r="K61" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="L61" t="s">
         <v>133</v>
@@ -5254,7 +5254,7 @@
         <v>26</v>
       </c>
       <c r="N61" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="Q61" t="s">
         <v>27</v>
@@ -5295,7 +5295,7 @@
         <v>41</v>
       </c>
       <c r="K62" s="6" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="L62" t="s">
         <v>133</v>
@@ -5304,7 +5304,7 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="Q62" t="s">
         <v>27</v>
@@ -5354,10 +5354,10 @@
         <v>26</v>
       </c>
       <c r="N63" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="O63" s="6" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="Q63" t="s">
         <v>27</v>
@@ -5407,10 +5407,10 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="Q64" t="s">
         <v>27</v>
@@ -5460,7 +5460,7 @@
         <v>26</v>
       </c>
       <c r="N65" s="6" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="Q65" t="s">
         <v>27</v>
@@ -5501,7 +5501,7 @@
         <v>41</v>
       </c>
       <c r="K66" s="6" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="L66" t="s">
         <v>142</v>
@@ -5510,7 +5510,7 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="Q66" t="s">
         <v>27</v>
@@ -5551,7 +5551,7 @@
         <v>41</v>
       </c>
       <c r="K67" s="6" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="L67" t="s">
         <v>142</v>
@@ -5560,7 +5560,7 @@
         <v>26</v>
       </c>
       <c r="N67" s="6" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="Q67" t="s">
         <v>27</v>
@@ -5607,7 +5607,7 @@
         <v>26</v>
       </c>
       <c r="N68" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="Q68" t="s">
         <v>27</v>
@@ -5648,13 +5648,13 @@
         <v>24</v>
       </c>
       <c r="K69" s="6" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="M69" t="s">
         <v>26</v>
       </c>
       <c r="N69" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="Q69" t="s">
         <v>27</v>
@@ -5695,13 +5695,13 @@
         <v>24</v>
       </c>
       <c r="K70" s="6" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="M70" t="s">
         <v>26</v>
       </c>
       <c r="N70" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="Q70" t="s">
         <v>27</v>
@@ -5747,11 +5747,14 @@
       <c r="M71" t="s">
         <v>26</v>
       </c>
-      <c r="N71" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="O71" s="3" t="s">
-        <v>567</v>
+      <c r="N71" s="5" t="s">
+        <v>610</v>
+      </c>
+      <c r="O71" s="5" t="s">
+        <v>611</v>
+      </c>
+      <c r="P71" s="6" t="s">
+        <v>606</v>
       </c>
       <c r="Q71" t="s">
         <v>27</v>
@@ -5765,10 +5768,10 @@
         <v>2029018</v>
       </c>
       <c r="B72" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C72" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D72" s="2">
         <v>2</v>
@@ -5777,7 +5780,7 @@
         <v>20</v>
       </c>
       <c r="F72" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G72" t="s">
         <v>39</v>
@@ -5792,10 +5795,10 @@
         <v>24</v>
       </c>
       <c r="K72" t="s">
+        <v>151</v>
+      </c>
+      <c r="L72" t="s">
         <v>152</v>
-      </c>
-      <c r="L72" t="s">
-        <v>153</v>
       </c>
       <c r="M72" t="s">
         <v>26</v>
@@ -5812,10 +5815,10 @@
         <v>2030013</v>
       </c>
       <c r="B73" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C73" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D73" s="2">
         <v>2</v>
@@ -5824,7 +5827,7 @@
         <v>34</v>
       </c>
       <c r="F73" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G73" t="s">
         <v>22</v>
@@ -5839,10 +5842,10 @@
         <v>24</v>
       </c>
       <c r="K73" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L73" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M73" t="s">
         <v>26</v>
@@ -5859,19 +5862,19 @@
         <v>2031001</v>
       </c>
       <c r="B74" t="s">
+        <v>156</v>
+      </c>
+      <c r="C74" t="s">
+        <v>149</v>
+      </c>
+      <c r="D74" s="2">
+        <v>1</v>
+      </c>
+      <c r="E74" t="s">
         <v>157</v>
       </c>
-      <c r="C74" t="s">
-        <v>150</v>
-      </c>
-      <c r="D74" s="2">
-        <v>1</v>
-      </c>
-      <c r="E74" t="s">
+      <c r="F74" t="s">
         <v>158</v>
-      </c>
-      <c r="F74" t="s">
-        <v>159</v>
       </c>
       <c r="G74" t="s">
         <v>22</v>
@@ -5903,19 +5906,19 @@
         <v>2032001</v>
       </c>
       <c r="B75" t="s">
+        <v>159</v>
+      </c>
+      <c r="C75" t="s">
+        <v>149</v>
+      </c>
+      <c r="D75" s="2">
+        <v>1</v>
+      </c>
+      <c r="E75" t="s">
+        <v>20</v>
+      </c>
+      <c r="F75" t="s">
         <v>160</v>
-      </c>
-      <c r="C75" t="s">
-        <v>150</v>
-      </c>
-      <c r="D75" s="2">
-        <v>1</v>
-      </c>
-      <c r="E75" t="s">
-        <v>20</v>
-      </c>
-      <c r="F75" t="s">
-        <v>161</v>
       </c>
       <c r="G75" t="s">
         <v>22</v>
@@ -5930,16 +5933,19 @@
         <v>41</v>
       </c>
       <c r="K75" t="s">
+        <v>161</v>
+      </c>
+      <c r="L75" t="s">
         <v>162</v>
       </c>
-      <c r="L75" t="s">
-        <v>163</v>
-      </c>
       <c r="M75" t="s">
         <v>26</v>
       </c>
       <c r="N75" s="6" t="s">
-        <v>504</v>
+        <v>503</v>
+      </c>
+      <c r="O75" s="6" t="s">
+        <v>606</v>
       </c>
       <c r="Q75" t="s">
         <v>27</v>
@@ -5953,10 +5959,10 @@
         <v>2032007</v>
       </c>
       <c r="B76" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C76" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D76" s="2">
         <v>1</v>
@@ -5980,16 +5986,16 @@
         <v>41</v>
       </c>
       <c r="K76" t="s">
+        <v>163</v>
+      </c>
+      <c r="L76" t="s">
         <v>164</v>
       </c>
-      <c r="L76" t="s">
+      <c r="M76" t="s">
+        <v>26</v>
+      </c>
+      <c r="N76" t="s">
         <v>165</v>
-      </c>
-      <c r="M76" t="s">
-        <v>26</v>
-      </c>
-      <c r="N76" t="s">
-        <v>166</v>
       </c>
       <c r="Q76" t="s">
         <v>27</v>
@@ -6003,10 +6009,10 @@
         <v>2032009</v>
       </c>
       <c r="B77" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C77" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D77" s="2">
         <v>1</v>
@@ -6030,16 +6036,16 @@
         <v>41</v>
       </c>
       <c r="K77" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M77" t="s">
         <v>26</v>
       </c>
       <c r="N77" s="6" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="O77" s="6" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="Q77" t="s">
         <v>27</v>
@@ -6053,19 +6059,19 @@
         <v>2033001</v>
       </c>
       <c r="B78" t="s">
+        <v>167</v>
+      </c>
+      <c r="C78" t="s">
+        <v>149</v>
+      </c>
+      <c r="D78" s="2">
+        <v>1</v>
+      </c>
+      <c r="E78" t="s">
+        <v>20</v>
+      </c>
+      <c r="F78" t="s">
         <v>168</v>
-      </c>
-      <c r="C78" t="s">
-        <v>150</v>
-      </c>
-      <c r="D78" s="2">
-        <v>1</v>
-      </c>
-      <c r="E78" t="s">
-        <v>20</v>
-      </c>
-      <c r="F78" t="s">
-        <v>169</v>
       </c>
       <c r="G78" t="s">
         <v>22</v>
@@ -6080,19 +6086,19 @@
         <v>41</v>
       </c>
       <c r="K78" t="s">
+        <v>169</v>
+      </c>
+      <c r="L78" t="s">
         <v>170</v>
       </c>
-      <c r="L78" t="s">
-        <v>171</v>
-      </c>
       <c r="M78" t="s">
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="Q78" t="s">
         <v>27</v>
@@ -6106,10 +6112,10 @@
         <v>2033002</v>
       </c>
       <c r="B79" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C79" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D79" s="2">
         <v>1</v>
@@ -6118,7 +6124,7 @@
         <v>20</v>
       </c>
       <c r="F79" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G79" t="s">
         <v>22</v>
@@ -6133,19 +6139,19 @@
         <v>41</v>
       </c>
       <c r="K79" t="s">
+        <v>172</v>
+      </c>
+      <c r="L79" t="s">
         <v>173</v>
       </c>
-      <c r="L79" t="s">
-        <v>174</v>
-      </c>
       <c r="M79" t="s">
         <v>26</v>
       </c>
       <c r="N79" s="5" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="O79" s="5" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Q79" t="s">
         <v>27</v>
@@ -6159,10 +6165,10 @@
         <v>2033006</v>
       </c>
       <c r="B80" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C80" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D80" s="2">
         <v>1</v>
@@ -6186,19 +6192,19 @@
         <v>41</v>
       </c>
       <c r="K80" t="s">
+        <v>174</v>
+      </c>
+      <c r="L80" t="s">
         <v>175</v>
       </c>
-      <c r="L80" t="s">
+      <c r="M80" t="s">
+        <v>26</v>
+      </c>
+      <c r="N80" t="s">
         <v>176</v>
       </c>
-      <c r="M80" t="s">
-        <v>26</v>
-      </c>
-      <c r="N80" t="s">
-        <v>177</v>
-      </c>
       <c r="O80" s="6" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="Q80" t="s">
         <v>27</v>
@@ -6212,10 +6218,10 @@
         <v>2034001</v>
       </c>
       <c r="B81" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C81" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D81" s="2">
         <v>1</v>
@@ -6224,7 +6230,7 @@
         <v>20</v>
       </c>
       <c r="F81" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G81" t="s">
         <v>22</v>
@@ -6239,19 +6245,19 @@
         <v>41</v>
       </c>
       <c r="K81" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L81" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M81" t="s">
         <v>26</v>
       </c>
       <c r="N81" s="6" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="O81" s="6" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="Q81" t="s">
         <v>27</v>
@@ -6265,10 +6271,10 @@
         <v>2034002</v>
       </c>
       <c r="B82" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C82" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D82" s="2">
         <v>1</v>
@@ -6277,7 +6283,7 @@
         <v>20</v>
       </c>
       <c r="F82" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G82" t="s">
         <v>22</v>
@@ -6292,19 +6298,19 @@
         <v>41</v>
       </c>
       <c r="K82" t="s">
+        <v>179</v>
+      </c>
+      <c r="L82" t="s">
         <v>180</v>
       </c>
-      <c r="L82" t="s">
-        <v>181</v>
-      </c>
       <c r="M82" t="s">
         <v>26</v>
       </c>
       <c r="N82" s="5" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="O82" s="5" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="Q82" t="s">
         <v>27</v>
@@ -6318,10 +6324,10 @@
         <v>2034006</v>
       </c>
       <c r="B83" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C83" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D83" s="2">
         <v>1</v>
@@ -6345,19 +6351,19 @@
         <v>41</v>
       </c>
       <c r="K83" t="s">
+        <v>181</v>
+      </c>
+      <c r="L83" t="s">
         <v>182</v>
       </c>
-      <c r="L83" t="s">
-        <v>183</v>
-      </c>
       <c r="M83" t="s">
         <v>26</v>
       </c>
       <c r="N83" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="O83" s="6" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="Q83" t="s">
         <v>27</v>
@@ -6371,10 +6377,10 @@
         <v>2061001</v>
       </c>
       <c r="B84" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C84" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D84" s="2">
         <v>1</v>
@@ -6383,7 +6389,7 @@
         <v>20</v>
       </c>
       <c r="F84" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G84" t="s">
         <v>22</v>
@@ -6415,10 +6421,10 @@
         <v>2061002</v>
       </c>
       <c r="B85" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C85" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D85" s="2">
         <v>1</v>
@@ -6427,7 +6433,7 @@
         <v>20</v>
       </c>
       <c r="F85" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G85" t="s">
         <v>22</v>
@@ -6448,7 +6454,7 @@
         <v>26</v>
       </c>
       <c r="N85" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q85" t="s">
         <v>27</v>
@@ -6462,10 +6468,10 @@
         <v>2061006</v>
       </c>
       <c r="B86" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C86" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D86" s="2">
         <v>1</v>
@@ -6506,10 +6512,10 @@
         <v>2107013</v>
       </c>
       <c r="B87" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C87" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D87" s="2">
         <v>2</v>
@@ -6518,7 +6524,7 @@
         <v>20</v>
       </c>
       <c r="F87" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G87" t="s">
         <v>39</v>
@@ -6533,10 +6539,10 @@
         <v>24</v>
       </c>
       <c r="K87" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L87" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M87" t="s">
         <v>26</v>
@@ -6553,10 +6559,10 @@
         <v>2143016</v>
       </c>
       <c r="B88" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C88" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D88" s="2">
         <v>2</v>
@@ -6565,7 +6571,7 @@
         <v>20</v>
       </c>
       <c r="F88" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G88" t="s">
         <v>39</v>
@@ -6580,10 +6586,10 @@
         <v>24</v>
       </c>
       <c r="K88" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L88" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="M88" t="s">
         <v>26</v>
@@ -6600,10 +6606,10 @@
         <v>2148011</v>
       </c>
       <c r="B89" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C89" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D89" s="2">
         <v>2</v>
@@ -6612,7 +6618,7 @@
         <v>20</v>
       </c>
       <c r="F89" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G89" t="s">
         <v>39</v>
@@ -6627,7 +6633,7 @@
         <v>24</v>
       </c>
       <c r="K89" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M89" t="s">
         <v>26</v>
@@ -6644,10 +6650,10 @@
         <v>2175020</v>
       </c>
       <c r="B90" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C90" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D90" s="2">
         <v>2</v>
@@ -6671,19 +6677,19 @@
         <v>24</v>
       </c>
       <c r="K90" t="s">
+        <v>194</v>
+      </c>
+      <c r="L90" t="s">
         <v>195</v>
       </c>
-      <c r="L90" t="s">
-        <v>196</v>
-      </c>
       <c r="M90" t="s">
         <v>26</v>
       </c>
       <c r="N90" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="O90" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="Q90" t="s">
         <v>27</v>
@@ -6697,10 +6703,10 @@
         <v>2285005</v>
       </c>
       <c r="B91" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C91" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D91" s="2">
         <v>1</v>
@@ -6709,7 +6715,7 @@
         <v>20</v>
       </c>
       <c r="F91" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G91" t="s">
         <v>22</v>
@@ -6724,16 +6730,16 @@
         <v>41</v>
       </c>
       <c r="K91" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="M91" t="s">
         <v>26</v>
       </c>
       <c r="N91" s="5" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="O91" s="5" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="Q91" t="s">
         <v>27</v>
@@ -6747,10 +6753,10 @@
         <v>2285006</v>
       </c>
       <c r="B92" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C92" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D92" s="2">
         <v>1</v>
@@ -6774,13 +6780,13 @@
         <v>41</v>
       </c>
       <c r="K92" t="s">
+        <v>197</v>
+      </c>
+      <c r="M92" t="s">
+        <v>26</v>
+      </c>
+      <c r="N92" t="s">
         <v>198</v>
-      </c>
-      <c r="M92" t="s">
-        <v>26</v>
-      </c>
-      <c r="N92" t="s">
-        <v>199</v>
       </c>
       <c r="Q92" t="s">
         <v>27</v>
@@ -6794,10 +6800,10 @@
         <v>2285007</v>
       </c>
       <c r="B93" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C93" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D93" s="2">
         <v>1</v>
@@ -6806,7 +6812,7 @@
         <v>34</v>
       </c>
       <c r="F93" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G93" t="s">
         <v>39</v>
@@ -6821,13 +6827,13 @@
         <v>41</v>
       </c>
       <c r="K93" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="M93" t="s">
         <v>26</v>
       </c>
       <c r="N93" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q93" t="s">
         <v>27</v>
@@ -6841,10 +6847,10 @@
         <v>2286015</v>
       </c>
       <c r="B94" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C94" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D94" s="2">
         <v>2</v>
@@ -6853,7 +6859,7 @@
         <v>20</v>
       </c>
       <c r="F94" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G94" t="s">
         <v>39</v>
@@ -6868,7 +6874,7 @@
         <v>24</v>
       </c>
       <c r="K94" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M94" t="s">
         <v>26</v>
@@ -6885,10 +6891,10 @@
         <v>2338044</v>
       </c>
       <c r="B95" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C95" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D95" s="2">
         <v>1</v>
@@ -6929,10 +6935,10 @@
         <v>2342014</v>
       </c>
       <c r="B96" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C96" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D96" s="2">
         <v>2</v>
@@ -6941,7 +6947,7 @@
         <v>20</v>
       </c>
       <c r="F96" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G96" t="s">
         <v>39</v>
@@ -6956,13 +6962,13 @@
         <v>41</v>
       </c>
       <c r="K96" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M96" t="s">
         <v>26</v>
       </c>
       <c r="N96" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q96" t="s">
         <v>27</v>
@@ -6976,10 +6982,10 @@
         <v>5</v>
       </c>
       <c r="B97" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C97" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D97" s="2">
         <v>4</v>
@@ -6988,7 +6994,7 @@
         <v>20</v>
       </c>
       <c r="F97" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G97" t="s">
         <v>39</v>
@@ -7003,16 +7009,16 @@
         <v>41</v>
       </c>
       <c r="K97" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="M97" t="s">
         <v>26</v>
       </c>
       <c r="N97" s="5" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="O97" s="5" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="Q97" t="s">
         <v>27</v>
@@ -7026,10 +7032,10 @@
         <v>2343027</v>
       </c>
       <c r="B98" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C98" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D98" s="2">
         <v>3</v>
@@ -7038,7 +7044,7 @@
         <v>34</v>
       </c>
       <c r="F98" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G98" t="s">
         <v>39</v>
@@ -7053,16 +7059,16 @@
         <v>24</v>
       </c>
       <c r="K98" t="s">
+        <v>209</v>
+      </c>
+      <c r="M98" t="s">
         <v>210</v>
       </c>
-      <c r="M98" t="s">
-        <v>211</v>
-      </c>
       <c r="N98" s="5" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O98" s="5" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="Q98" t="s">
         <v>27</v>
@@ -7076,10 +7082,10 @@
         <v>2343027</v>
       </c>
       <c r="B99" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C99" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D99" s="2">
         <v>3</v>
@@ -7088,7 +7094,7 @@
         <v>34</v>
       </c>
       <c r="F99" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G99" t="s">
         <v>39</v>
@@ -7103,13 +7109,13 @@
         <v>24</v>
       </c>
       <c r="K99" t="s">
+        <v>211</v>
+      </c>
+      <c r="M99" t="s">
+        <v>210</v>
+      </c>
+      <c r="N99" t="s">
         <v>212</v>
-      </c>
-      <c r="M99" t="s">
-        <v>211</v>
-      </c>
-      <c r="N99" t="s">
-        <v>213</v>
       </c>
       <c r="Q99" t="s">
         <v>27</v>
@@ -7123,10 +7129,10 @@
         <v>2343027</v>
       </c>
       <c r="B100" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C100" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D100" s="2">
         <v>3</v>
@@ -7135,7 +7141,7 @@
         <v>34</v>
       </c>
       <c r="F100" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G100" t="s">
         <v>39</v>
@@ -7150,13 +7156,13 @@
         <v>24</v>
       </c>
       <c r="K100" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="M100" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N100" s="5" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="O100" s="3"/>
       <c r="Q100" t="s">
@@ -7171,10 +7177,10 @@
         <v>2347001</v>
       </c>
       <c r="B101" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C101" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D101" s="2">
         <v>1</v>
@@ -7198,16 +7204,16 @@
         <v>41</v>
       </c>
       <c r="K101" t="s">
+        <v>214</v>
+      </c>
+      <c r="L101" t="s">
         <v>215</v>
       </c>
-      <c r="L101" t="s">
+      <c r="M101" t="s">
+        <v>26</v>
+      </c>
+      <c r="N101" t="s">
         <v>216</v>
-      </c>
-      <c r="M101" t="s">
-        <v>26</v>
-      </c>
-      <c r="N101" t="s">
-        <v>217</v>
       </c>
       <c r="Q101" t="s">
         <v>27</v>
@@ -7221,10 +7227,10 @@
         <v>2347003</v>
       </c>
       <c r="B102" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C102" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D102" s="2">
         <v>1</v>
@@ -7233,7 +7239,7 @@
         <v>20</v>
       </c>
       <c r="F102" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G102" t="s">
         <v>39</v>
@@ -7248,16 +7254,16 @@
         <v>41</v>
       </c>
       <c r="K102" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L102" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="M102" t="s">
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="Q102" t="s">
         <v>27</v>
@@ -7271,10 +7277,10 @@
         <v>2347005</v>
       </c>
       <c r="B103" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C103" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D103" s="2">
         <v>1</v>
@@ -7283,7 +7289,7 @@
         <v>20</v>
       </c>
       <c r="F103" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G103" t="s">
         <v>39</v>
@@ -7298,16 +7304,16 @@
         <v>41</v>
       </c>
       <c r="K103" t="s">
+        <v>219</v>
+      </c>
+      <c r="L103" t="s">
         <v>220</v>
       </c>
-      <c r="L103" t="s">
+      <c r="M103" t="s">
+        <v>26</v>
+      </c>
+      <c r="N103" s="3" t="s">
         <v>221</v>
-      </c>
-      <c r="M103" t="s">
-        <v>26</v>
-      </c>
-      <c r="N103" s="3" t="s">
-        <v>222</v>
       </c>
       <c r="O103" s="3"/>
       <c r="Q103" t="s">
@@ -7322,10 +7328,10 @@
         <v>2347006</v>
       </c>
       <c r="B104" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C104" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D104" s="2">
         <v>1</v>
@@ -7334,7 +7340,7 @@
         <v>34</v>
       </c>
       <c r="F104" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G104" t="s">
         <v>39</v>
@@ -7349,16 +7355,16 @@
         <v>41</v>
       </c>
       <c r="K104" t="s">
+        <v>223</v>
+      </c>
+      <c r="L104" t="s">
         <v>224</v>
       </c>
-      <c r="L104" t="s">
-        <v>225</v>
-      </c>
       <c r="M104" t="s">
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="Q104" t="s">
         <v>27</v>
@@ -7372,10 +7378,10 @@
         <v>2347007</v>
       </c>
       <c r="B105" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C105" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D105" s="2">
         <v>1</v>
@@ -7399,16 +7405,16 @@
         <v>41</v>
       </c>
       <c r="K105" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="L105" t="s">
+        <v>225</v>
+      </c>
+      <c r="M105" t="s">
+        <v>26</v>
+      </c>
+      <c r="N105" s="3" t="s">
         <v>226</v>
-      </c>
-      <c r="M105" t="s">
-        <v>26</v>
-      </c>
-      <c r="N105" s="3" t="s">
-        <v>227</v>
       </c>
       <c r="O105" s="3"/>
       <c r="Q105" t="s">
@@ -7423,10 +7429,10 @@
         <v>2347013</v>
       </c>
       <c r="B106" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C106" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D106" s="2">
         <v>2</v>
@@ -7435,7 +7441,7 @@
         <v>20</v>
       </c>
       <c r="F106" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G106" t="s">
         <v>39</v>
@@ -7450,16 +7456,16 @@
         <v>41</v>
       </c>
       <c r="K106" t="s">
+        <v>228</v>
+      </c>
+      <c r="L106" t="s">
         <v>229</v>
       </c>
-      <c r="L106" t="s">
-        <v>230</v>
-      </c>
       <c r="M106" t="s">
         <v>26</v>
       </c>
       <c r="N106" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Q106" t="s">
         <v>27</v>
@@ -7473,10 +7479,10 @@
         <v>2347014</v>
       </c>
       <c r="B107" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C107" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D107" s="2">
         <v>2</v>
@@ -7485,7 +7491,7 @@
         <v>34</v>
       </c>
       <c r="F107" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G107" t="s">
         <v>39</v>
@@ -7500,16 +7506,16 @@
         <v>41</v>
       </c>
       <c r="K107" t="s">
+        <v>231</v>
+      </c>
+      <c r="L107" t="s">
         <v>232</v>
       </c>
-      <c r="L107" t="s">
-        <v>233</v>
-      </c>
       <c r="M107" t="s">
         <v>26</v>
       </c>
       <c r="N107" s="3" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="Q107" t="s">
         <v>27</v>
@@ -7523,10 +7529,10 @@
         <v>2347017</v>
       </c>
       <c r="B108" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C108" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D108" s="2">
         <v>2</v>
@@ -7535,7 +7541,7 @@
         <v>34</v>
       </c>
       <c r="F108" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G108" t="s">
         <v>22</v>
@@ -7550,16 +7556,16 @@
         <v>41</v>
       </c>
       <c r="K108" t="s">
+        <v>234</v>
+      </c>
+      <c r="L108" t="s">
         <v>235</v>
       </c>
-      <c r="L108" t="s">
+      <c r="M108" t="s">
+        <v>26</v>
+      </c>
+      <c r="N108" t="s">
         <v>236</v>
-      </c>
-      <c r="M108" t="s">
-        <v>26</v>
-      </c>
-      <c r="N108" t="s">
-        <v>237</v>
       </c>
       <c r="Q108" t="s">
         <v>27</v>
@@ -7573,10 +7579,10 @@
         <v>2347030</v>
       </c>
       <c r="B109" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C109" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D109" s="2">
         <v>2</v>
@@ -7585,7 +7591,7 @@
         <v>34</v>
       </c>
       <c r="F109" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G109" t="s">
         <v>39</v>
@@ -7600,16 +7606,16 @@
         <v>41</v>
       </c>
       <c r="K109" t="s">
+        <v>238</v>
+      </c>
+      <c r="L109" t="s">
         <v>239</v>
       </c>
-      <c r="L109" t="s">
-        <v>240</v>
-      </c>
       <c r="M109" t="s">
         <v>26</v>
       </c>
       <c r="N109" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="O109" s="3"/>
       <c r="Q109" t="s">
@@ -7624,10 +7630,10 @@
         <v>2347021</v>
       </c>
       <c r="B110" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C110" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D110" s="2">
         <v>3</v>
@@ -7636,7 +7642,7 @@
         <v>20</v>
       </c>
       <c r="F110" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G110" t="s">
         <v>39</v>
@@ -7651,16 +7657,16 @@
         <v>41</v>
       </c>
       <c r="K110" t="s">
+        <v>241</v>
+      </c>
+      <c r="L110" t="s">
         <v>242</v>
       </c>
-      <c r="L110" t="s">
-        <v>243</v>
-      </c>
       <c r="M110" t="s">
         <v>26</v>
       </c>
       <c r="N110" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q110" t="s">
         <v>27</v>
@@ -7674,10 +7680,10 @@
         <v>2347022</v>
       </c>
       <c r="B111" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C111" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D111" s="2">
         <v>3</v>
@@ -7686,7 +7692,7 @@
         <v>20</v>
       </c>
       <c r="F111" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G111" t="s">
         <v>39</v>
@@ -7701,16 +7707,16 @@
         <v>41</v>
       </c>
       <c r="K111" t="s">
+        <v>244</v>
+      </c>
+      <c r="L111" t="s">
         <v>245</v>
       </c>
-      <c r="L111" t="s">
+      <c r="M111" t="s">
+        <v>26</v>
+      </c>
+      <c r="N111" s="3" t="s">
         <v>246</v>
-      </c>
-      <c r="M111" t="s">
-        <v>26</v>
-      </c>
-      <c r="N111" s="3" t="s">
-        <v>247</v>
       </c>
       <c r="O111" s="3"/>
       <c r="P111" s="1"/>
@@ -7726,10 +7732,10 @@
         <v>2347024</v>
       </c>
       <c r="B112" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C112" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D112" s="2">
         <v>3</v>
@@ -7738,7 +7744,7 @@
         <v>20</v>
       </c>
       <c r="F112" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G112" t="s">
         <v>39</v>
@@ -7753,16 +7759,16 @@
         <v>41</v>
       </c>
       <c r="K112" t="s">
+        <v>248</v>
+      </c>
+      <c r="L112" t="s">
         <v>249</v>
       </c>
-      <c r="L112" t="s">
-        <v>250</v>
-      </c>
       <c r="M112" t="s">
         <v>26</v>
       </c>
       <c r="N112" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q112" t="s">
         <v>27</v>
@@ -7776,10 +7782,10 @@
         <v>2347026</v>
       </c>
       <c r="B113" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C113" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D113" s="2">
         <v>3</v>
@@ -7788,7 +7794,7 @@
         <v>34</v>
       </c>
       <c r="F113" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G113" t="s">
         <v>39</v>
@@ -7803,16 +7809,16 @@
         <v>41</v>
       </c>
       <c r="K113" t="s">
+        <v>251</v>
+      </c>
+      <c r="L113" t="s">
         <v>252</v>
       </c>
-      <c r="L113" t="s">
-        <v>253</v>
-      </c>
       <c r="M113" t="s">
         <v>26</v>
       </c>
       <c r="N113" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O113" s="3"/>
       <c r="Q113" t="s">
@@ -7827,10 +7833,10 @@
         <v>2347027</v>
       </c>
       <c r="B114" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C114" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D114" s="2">
         <v>3</v>
@@ -7839,7 +7845,7 @@
         <v>34</v>
       </c>
       <c r="F114" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G114" t="s">
         <v>39</v>
@@ -7854,19 +7860,19 @@
         <v>41</v>
       </c>
       <c r="K114" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="L114" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="M114" t="s">
         <v>26</v>
       </c>
       <c r="N114" s="5" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="O114" s="5" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="Q114" t="s">
         <v>27</v>
@@ -7880,10 +7886,10 @@
         <v>2347029</v>
       </c>
       <c r="B115" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C115" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D115" s="2">
         <v>3</v>
@@ -7892,7 +7898,7 @@
         <v>34</v>
       </c>
       <c r="F115" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G115" t="s">
         <v>39</v>
@@ -7907,16 +7913,16 @@
         <v>41</v>
       </c>
       <c r="K115" t="s">
+        <v>256</v>
+      </c>
+      <c r="L115" t="s">
         <v>257</v>
       </c>
-      <c r="L115" t="s">
+      <c r="M115" t="s">
+        <v>210</v>
+      </c>
+      <c r="N115" t="s">
         <v>258</v>
-      </c>
-      <c r="M115" t="s">
-        <v>211</v>
-      </c>
-      <c r="N115" t="s">
-        <v>259</v>
       </c>
       <c r="Q115" t="s">
         <v>27</v>
@@ -7930,10 +7936,10 @@
         <v>2347031</v>
       </c>
       <c r="B116" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C116" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D116" s="2">
         <v>4</v>
@@ -7942,7 +7948,7 @@
         <v>20</v>
       </c>
       <c r="F116" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G116" t="s">
         <v>39</v>
@@ -7957,16 +7963,16 @@
         <v>41</v>
       </c>
       <c r="K116" t="s">
+        <v>260</v>
+      </c>
+      <c r="L116" t="s">
         <v>261</v>
       </c>
-      <c r="L116" t="s">
-        <v>262</v>
-      </c>
       <c r="M116" t="s">
         <v>26</v>
       </c>
       <c r="N116" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Q116" t="s">
         <v>27</v>
@@ -7980,10 +7986,10 @@
         <v>2347038</v>
       </c>
       <c r="B117" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C117" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D117" s="2">
         <v>4</v>
@@ -7992,10 +7998,10 @@
         <v>20</v>
       </c>
       <c r="F117" t="s">
+        <v>262</v>
+      </c>
+      <c r="G117" t="s">
         <v>263</v>
-      </c>
-      <c r="G117" t="s">
-        <v>264</v>
       </c>
       <c r="H117" s="2">
         <v>60</v>
@@ -8007,16 +8013,16 @@
         <v>41</v>
       </c>
       <c r="K117" t="s">
+        <v>264</v>
+      </c>
+      <c r="L117" t="s">
         <v>265</v>
       </c>
-      <c r="L117" t="s">
-        <v>266</v>
-      </c>
       <c r="M117" t="s">
         <v>26</v>
       </c>
       <c r="N117" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O117" s="3"/>
       <c r="Q117" t="s">
@@ -8031,10 +8037,10 @@
         <v>2361002</v>
       </c>
       <c r="B118" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C118" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D118" s="2">
         <v>1</v>
@@ -8058,13 +8064,13 @@
         <v>41</v>
       </c>
       <c r="K118" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="M118" t="s">
         <v>26</v>
       </c>
       <c r="N118" s="3" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Q118" t="s">
         <v>27</v>
@@ -8078,10 +8084,10 @@
         <v>2361002</v>
       </c>
       <c r="B119" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C119" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D119" s="2">
         <v>1</v>
@@ -8105,13 +8111,13 @@
         <v>41</v>
       </c>
       <c r="K119" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="M119" t="s">
         <v>26</v>
       </c>
       <c r="N119" s="3" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Q119" t="s">
         <v>27</v>
@@ -8125,10 +8131,10 @@
         <v>2361002</v>
       </c>
       <c r="B120" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C120" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D120" s="2">
         <v>1</v>
@@ -8152,7 +8158,7 @@
         <v>41</v>
       </c>
       <c r="K120" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="M120" t="s">
         <v>26</v>
@@ -8169,10 +8175,10 @@
         <v>2361004</v>
       </c>
       <c r="B121" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C121" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D121" s="2">
         <v>1</v>
@@ -8181,7 +8187,7 @@
         <v>20</v>
       </c>
       <c r="F121" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G121" t="s">
         <v>22</v>
@@ -8196,13 +8202,13 @@
         <v>41</v>
       </c>
       <c r="K121" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="M121" t="s">
         <v>26</v>
       </c>
       <c r="N121" s="6" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="Q121" t="s">
         <v>27</v>
@@ -8216,10 +8222,10 @@
         <v>2393002</v>
       </c>
       <c r="B122" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C122" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D122" s="2">
         <v>1</v>
@@ -8228,7 +8234,7 @@
         <v>20</v>
       </c>
       <c r="F122" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G122" t="s">
         <v>22</v>
@@ -8243,16 +8249,16 @@
         <v>41</v>
       </c>
       <c r="K122" t="s">
+        <v>271</v>
+      </c>
+      <c r="L122" t="s">
         <v>272</v>
       </c>
-      <c r="L122" t="s">
-        <v>273</v>
-      </c>
       <c r="M122" t="s">
         <v>26</v>
       </c>
       <c r="N122" s="3" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="Q122" t="s">
         <v>27</v>
@@ -8266,10 +8272,10 @@
         <v>2393002</v>
       </c>
       <c r="B123" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C123" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D123" s="2">
         <v>1</v>
@@ -8278,7 +8284,7 @@
         <v>20</v>
       </c>
       <c r="F123" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G123" t="s">
         <v>22</v>
@@ -8287,22 +8293,22 @@
         <v>20</v>
       </c>
       <c r="I123" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J123" t="s">
         <v>41</v>
       </c>
       <c r="K123" t="s">
+        <v>274</v>
+      </c>
+      <c r="L123" t="s">
         <v>275</v>
       </c>
-      <c r="L123" t="s">
-        <v>276</v>
-      </c>
       <c r="M123" t="s">
         <v>26</v>
       </c>
       <c r="N123" s="3" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="Q123" t="s">
         <v>27</v>
@@ -8316,10 +8322,10 @@
         <v>2393002</v>
       </c>
       <c r="B124" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C124" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D124" s="2">
         <v>1</v>
@@ -8328,7 +8334,7 @@
         <v>20</v>
       </c>
       <c r="F124" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G124" t="s">
         <v>22</v>
@@ -8337,22 +8343,22 @@
         <v>20</v>
       </c>
       <c r="I124" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J124" t="s">
         <v>41</v>
       </c>
       <c r="K124" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="L124" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M124" t="s">
         <v>26</v>
       </c>
       <c r="N124" s="3" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="Q124" t="s">
         <v>27</v>
@@ -8366,10 +8372,10 @@
         <v>2394004</v>
       </c>
       <c r="B125" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C125" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D125" s="2">
         <v>1</v>
@@ -8378,7 +8384,7 @@
         <v>20</v>
       </c>
       <c r="F125" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G125" t="s">
         <v>22</v>
@@ -8393,16 +8399,16 @@
         <v>24</v>
       </c>
       <c r="K125" t="s">
+        <v>279</v>
+      </c>
+      <c r="L125" t="s">
         <v>280</v>
       </c>
-      <c r="L125" t="s">
-        <v>281</v>
-      </c>
       <c r="M125" t="s">
         <v>26</v>
       </c>
       <c r="N125" s="3" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="Q125" t="s">
         <v>27</v>
@@ -8416,10 +8422,10 @@
         <v>2394004</v>
       </c>
       <c r="B126" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C126" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D126" s="2">
         <v>1</v>
@@ -8428,7 +8434,7 @@
         <v>20</v>
       </c>
       <c r="F126" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G126" t="s">
         <v>22</v>
@@ -8443,16 +8449,16 @@
         <v>24</v>
       </c>
       <c r="K126" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L126" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="M126" t="s">
         <v>26</v>
       </c>
       <c r="N126" s="3" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="Q126" t="s">
         <v>27</v>
@@ -8466,10 +8472,10 @@
         <v>2394004</v>
       </c>
       <c r="B127" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C127" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D127" s="2">
         <v>1</v>
@@ -8478,7 +8484,7 @@
         <v>20</v>
       </c>
       <c r="F127" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G127" t="s">
         <v>22</v>
@@ -8493,16 +8499,16 @@
         <v>24</v>
       </c>
       <c r="K127" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L127" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="M127" t="s">
         <v>26</v>
       </c>
       <c r="N127" s="3" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="Q127" t="s">
         <v>27</v>
@@ -8516,10 +8522,10 @@
         <v>2395003</v>
       </c>
       <c r="B128" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C128" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D128" s="2">
         <v>1</v>
@@ -8528,7 +8534,7 @@
         <v>20</v>
       </c>
       <c r="F128" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G128" t="s">
         <v>22</v>
@@ -8543,16 +8549,16 @@
         <v>41</v>
       </c>
       <c r="K128" t="s">
+        <v>284</v>
+      </c>
+      <c r="L128" t="s">
         <v>285</v>
       </c>
-      <c r="L128" t="s">
-        <v>286</v>
-      </c>
       <c r="M128" t="s">
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="Q128" t="s">
         <v>27</v>
@@ -8566,10 +8572,10 @@
         <v>2395003</v>
       </c>
       <c r="B129" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C129" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D129" s="2">
         <v>1</v>
@@ -8578,7 +8584,7 @@
         <v>20</v>
       </c>
       <c r="F129" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G129" t="s">
         <v>22</v>
@@ -8593,16 +8599,16 @@
         <v>41</v>
       </c>
       <c r="K129" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="L129" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="M129" t="s">
         <v>26</v>
       </c>
       <c r="N129" s="6" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="Q129" t="s">
         <v>27</v>
@@ -8616,10 +8622,10 @@
         <v>2395003</v>
       </c>
       <c r="B130" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C130" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D130" s="2">
         <v>1</v>
@@ -8628,7 +8634,7 @@
         <v>20</v>
       </c>
       <c r="F130" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G130" t="s">
         <v>22</v>
@@ -8643,16 +8649,16 @@
         <v>41</v>
       </c>
       <c r="K130" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L130" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="M130" t="s">
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="Q130" t="s">
         <v>27</v>
@@ -8666,10 +8672,10 @@
         <v>2396001</v>
       </c>
       <c r="B131" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C131" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D131" s="2">
         <v>1</v>
@@ -8678,7 +8684,7 @@
         <v>20</v>
       </c>
       <c r="F131" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G131" t="s">
         <v>22</v>
@@ -8693,16 +8699,16 @@
         <v>24</v>
       </c>
       <c r="K131" t="s">
+        <v>289</v>
+      </c>
+      <c r="L131" t="s">
         <v>290</v>
       </c>
-      <c r="L131" t="s">
-        <v>291</v>
-      </c>
       <c r="M131" t="s">
         <v>26</v>
       </c>
       <c r="N131" s="6" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="Q131" t="s">
         <v>27</v>
@@ -8716,10 +8722,10 @@
         <v>2396001</v>
       </c>
       <c r="B132" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C132" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D132" s="2">
         <v>1</v>
@@ -8728,7 +8734,7 @@
         <v>20</v>
       </c>
       <c r="F132" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G132" t="s">
         <v>22</v>
@@ -8743,16 +8749,16 @@
         <v>24</v>
       </c>
       <c r="K132" t="s">
+        <v>291</v>
+      </c>
+      <c r="L132" t="s">
         <v>292</v>
       </c>
-      <c r="L132" t="s">
-        <v>293</v>
-      </c>
       <c r="M132" t="s">
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="Q132" t="s">
         <v>27</v>
@@ -8766,10 +8772,10 @@
         <v>2396001</v>
       </c>
       <c r="B133" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C133" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D133" s="2">
         <v>1</v>
@@ -8778,7 +8784,7 @@
         <v>20</v>
       </c>
       <c r="F133" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G133" t="s">
         <v>22</v>
@@ -8793,16 +8799,16 @@
         <v>24</v>
       </c>
       <c r="K133" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="L133" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="M133" t="s">
         <v>26</v>
       </c>
       <c r="N133" s="6" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="Q133" t="s">
         <v>27</v>
@@ -8816,10 +8822,10 @@
         <v>2397003</v>
       </c>
       <c r="B134" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C134" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D134" s="2">
         <v>1</v>
@@ -8843,16 +8849,16 @@
         <v>24</v>
       </c>
       <c r="K134" t="s">
+        <v>295</v>
+      </c>
+      <c r="L134" t="s">
         <v>296</v>
       </c>
-      <c r="L134" t="s">
+      <c r="M134" t="s">
+        <v>26</v>
+      </c>
+      <c r="N134" t="s">
         <v>297</v>
-      </c>
-      <c r="M134" t="s">
-        <v>26</v>
-      </c>
-      <c r="N134" t="s">
-        <v>298</v>
       </c>
       <c r="Q134" t="s">
         <v>27</v>
@@ -8866,10 +8872,10 @@
         <v>2397003</v>
       </c>
       <c r="B135" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C135" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D135" s="2">
         <v>1</v>
@@ -8893,16 +8899,16 @@
         <v>24</v>
       </c>
       <c r="K135" t="s">
+        <v>298</v>
+      </c>
+      <c r="L135" t="s">
         <v>299</v>
       </c>
-      <c r="L135" t="s">
+      <c r="M135" t="s">
+        <v>26</v>
+      </c>
+      <c r="N135" t="s">
         <v>300</v>
-      </c>
-      <c r="M135" t="s">
-        <v>26</v>
-      </c>
-      <c r="N135" t="s">
-        <v>301</v>
       </c>
       <c r="Q135" t="s">
         <v>27</v>
@@ -8916,10 +8922,10 @@
         <v>2397003</v>
       </c>
       <c r="B136" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C136" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D136" s="2">
         <v>1</v>
@@ -8943,16 +8949,16 @@
         <v>24</v>
       </c>
       <c r="K136" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L136" t="s">
+        <v>299</v>
+      </c>
+      <c r="M136" t="s">
+        <v>26</v>
+      </c>
+      <c r="N136" t="s">
         <v>300</v>
-      </c>
-      <c r="M136" t="s">
-        <v>26</v>
-      </c>
-      <c r="N136" t="s">
-        <v>301</v>
       </c>
       <c r="Q136" t="s">
         <v>27</v>
@@ -8966,10 +8972,10 @@
         <v>2397008</v>
       </c>
       <c r="B137" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C137" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D137" s="2">
         <v>1</v>
@@ -8993,16 +8999,16 @@
         <v>24</v>
       </c>
       <c r="K137" t="s">
+        <v>302</v>
+      </c>
+      <c r="L137" t="s">
         <v>303</v>
       </c>
-      <c r="L137" t="s">
-        <v>304</v>
-      </c>
       <c r="M137" t="s">
         <v>26</v>
       </c>
       <c r="N137" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="Q137" t="s">
         <v>27</v>
@@ -9016,10 +9022,10 @@
         <v>2397008</v>
       </c>
       <c r="B138" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C138" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D138" s="2">
         <v>1</v>
@@ -9043,16 +9049,16 @@
         <v>24</v>
       </c>
       <c r="K138" t="s">
+        <v>304</v>
+      </c>
+      <c r="L138" t="s">
         <v>305</v>
       </c>
-      <c r="L138" t="s">
-        <v>306</v>
-      </c>
       <c r="M138" t="s">
         <v>26</v>
       </c>
       <c r="N138" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="Q138" t="s">
         <v>27</v>
@@ -9066,10 +9072,10 @@
         <v>2397008</v>
       </c>
       <c r="B139" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C139" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D139" s="2">
         <v>1</v>
@@ -9093,16 +9099,16 @@
         <v>24</v>
       </c>
       <c r="K139" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L139" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="M139" t="s">
         <v>26</v>
       </c>
       <c r="N139" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="Q139" t="s">
         <v>27</v>
@@ -9116,10 +9122,10 @@
         <v>2398001</v>
       </c>
       <c r="B140" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C140" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D140" s="2">
         <v>1</v>
@@ -9143,16 +9149,16 @@
         <v>41</v>
       </c>
       <c r="K140" t="s">
+        <v>308</v>
+      </c>
+      <c r="L140" t="s">
         <v>309</v>
       </c>
-      <c r="L140" t="s">
+      <c r="M140" t="s">
+        <v>26</v>
+      </c>
+      <c r="N140" t="s">
         <v>310</v>
-      </c>
-      <c r="M140" t="s">
-        <v>26</v>
-      </c>
-      <c r="N140" t="s">
-        <v>311</v>
       </c>
       <c r="Q140" t="s">
         <v>27</v>
@@ -9166,10 +9172,10 @@
         <v>2398001</v>
       </c>
       <c r="B141" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C141" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D141" s="2">
         <v>1</v>
@@ -9193,16 +9199,16 @@
         <v>41</v>
       </c>
       <c r="K141" t="s">
+        <v>311</v>
+      </c>
+      <c r="L141" t="s">
+        <v>309</v>
+      </c>
+      <c r="M141" t="s">
+        <v>26</v>
+      </c>
+      <c r="N141" s="4" t="s">
         <v>312</v>
-      </c>
-      <c r="L141" t="s">
-        <v>310</v>
-      </c>
-      <c r="M141" t="s">
-        <v>26</v>
-      </c>
-      <c r="N141" s="4" t="s">
-        <v>313</v>
       </c>
       <c r="O141" s="4"/>
       <c r="Q141" t="s">
@@ -9217,10 +9223,10 @@
         <v>2398001</v>
       </c>
       <c r="B142" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C142" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D142" s="2">
         <v>1</v>
@@ -9244,16 +9250,16 @@
         <v>41</v>
       </c>
       <c r="K142" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="L142" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="M142" t="s">
         <v>26</v>
       </c>
       <c r="N142" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O142" s="4"/>
       <c r="Q142" t="s">
@@ -9268,10 +9274,10 @@
         <v>2398006</v>
       </c>
       <c r="B143" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C143" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D143" s="2">
         <v>1</v>
@@ -9295,16 +9301,16 @@
         <v>41</v>
       </c>
       <c r="K143" t="s">
+        <v>314</v>
+      </c>
+      <c r="L143" t="s">
         <v>315</v>
       </c>
-      <c r="L143" t="s">
-        <v>316</v>
-      </c>
       <c r="M143" t="s">
         <v>26</v>
       </c>
       <c r="N143" s="6" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="Q143" t="s">
         <v>27</v>
@@ -9318,10 +9324,10 @@
         <v>2398006</v>
       </c>
       <c r="B144" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C144" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D144" s="2">
         <v>1</v>
@@ -9345,16 +9351,16 @@
         <v>41</v>
       </c>
       <c r="K144" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="L144" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M144" t="s">
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="Q144" t="s">
         <v>27</v>
@@ -9368,10 +9374,10 @@
         <v>2398006</v>
       </c>
       <c r="B145" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C145" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D145" s="2">
         <v>1</v>
@@ -9395,16 +9401,16 @@
         <v>41</v>
       </c>
       <c r="K145" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="L145" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="M145" t="s">
         <v>26</v>
       </c>
       <c r="N145" s="6" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="Q145" t="s">
         <v>27</v>
@@ -9418,10 +9424,10 @@
         <v>2398013</v>
       </c>
       <c r="B146" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C146" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D146" s="2">
         <v>2</v>
@@ -9430,7 +9436,7 @@
         <v>20</v>
       </c>
       <c r="F146" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G146" t="s">
         <v>22</v>
@@ -9445,16 +9451,16 @@
         <v>24</v>
       </c>
       <c r="K146" t="s">
+        <v>318</v>
+      </c>
+      <c r="L146" t="s">
         <v>319</v>
       </c>
-      <c r="L146" t="s">
-        <v>320</v>
-      </c>
       <c r="M146" t="s">
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="Q146" t="s">
         <v>27</v>
@@ -9468,10 +9474,10 @@
         <v>2398013</v>
       </c>
       <c r="B147" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C147" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D147" s="2">
         <v>2</v>
@@ -9480,7 +9486,7 @@
         <v>20</v>
       </c>
       <c r="F147" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G147" t="s">
         <v>22</v>
@@ -9495,16 +9501,16 @@
         <v>24</v>
       </c>
       <c r="K147" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="L147" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="M147" t="s">
         <v>26</v>
       </c>
       <c r="N147" s="6" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="Q147" t="s">
         <v>27</v>
@@ -9518,10 +9524,10 @@
         <v>2398013</v>
       </c>
       <c r="B148" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C148" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D148" s="2">
         <v>2</v>
@@ -9530,7 +9536,7 @@
         <v>20</v>
       </c>
       <c r="F148" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G148" t="s">
         <v>22</v>
@@ -9545,13 +9551,13 @@
         <v>24</v>
       </c>
       <c r="K148" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="M148" t="s">
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="Q148" t="s">
         <v>27</v>
@@ -9565,10 +9571,10 @@
         <v>2399003</v>
       </c>
       <c r="B149" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C149" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D149" s="2">
         <v>1</v>
@@ -9592,19 +9598,19 @@
         <v>41</v>
       </c>
       <c r="K149" t="s">
+        <v>323</v>
+      </c>
+      <c r="L149" t="s">
         <v>324</v>
       </c>
-      <c r="L149" t="s">
-        <v>325</v>
-      </c>
       <c r="M149" t="s">
         <v>26</v>
       </c>
       <c r="N149" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="O149" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="Q149" t="s">
         <v>27</v>
@@ -9618,10 +9624,10 @@
         <v>2399003</v>
       </c>
       <c r="B150" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C150" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D150" s="2">
         <v>1</v>
@@ -9645,19 +9651,19 @@
         <v>41</v>
       </c>
       <c r="K150" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L150" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="M150" t="s">
         <v>26</v>
       </c>
       <c r="N150" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="O150" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="Q150" t="s">
         <v>27</v>
@@ -9671,10 +9677,10 @@
         <v>2399003</v>
       </c>
       <c r="B151" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C151" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D151" s="2">
         <v>1</v>
@@ -9698,19 +9704,19 @@
         <v>41</v>
       </c>
       <c r="K151" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="L151" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="M151" t="s">
         <v>26</v>
       </c>
       <c r="N151" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="O151" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="Q151" t="s">
         <v>27</v>
@@ -9724,10 +9730,10 @@
         <v>2399010</v>
       </c>
       <c r="B152" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C152" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D152" s="2">
         <v>1</v>
@@ -9751,16 +9757,16 @@
         <v>41</v>
       </c>
       <c r="K152" t="s">
+        <v>327</v>
+      </c>
+      <c r="L152" t="s">
         <v>328</v>
       </c>
-      <c r="L152" t="s">
-        <v>329</v>
-      </c>
       <c r="M152" t="s">
         <v>26</v>
       </c>
       <c r="N152" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="Q152" t="s">
         <v>27</v>
@@ -9774,10 +9780,10 @@
         <v>2399010</v>
       </c>
       <c r="B153" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C153" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D153" s="2">
         <v>1</v>
@@ -9801,16 +9807,16 @@
         <v>41</v>
       </c>
       <c r="K153" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="L153" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="M153" t="s">
         <v>26</v>
       </c>
       <c r="N153" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="Q153" t="s">
         <v>27</v>
@@ -9824,10 +9830,10 @@
         <v>2399010</v>
       </c>
       <c r="B154" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C154" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D154" s="2">
         <v>1</v>
@@ -9851,16 +9857,16 @@
         <v>41</v>
       </c>
       <c r="K154" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="L154" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="M154" t="s">
         <v>26</v>
       </c>
       <c r="N154" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="Q154" t="s">
         <v>27</v>
@@ -9874,10 +9880,10 @@
         <v>2399014</v>
       </c>
       <c r="B155" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C155" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D155" s="2">
         <v>2</v>
@@ -9886,7 +9892,7 @@
         <v>20</v>
       </c>
       <c r="F155" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G155" t="s">
         <v>22</v>
@@ -9901,16 +9907,16 @@
         <v>24</v>
       </c>
       <c r="K155" t="s">
+        <v>331</v>
+      </c>
+      <c r="L155" t="s">
         <v>332</v>
       </c>
-      <c r="L155" t="s">
-        <v>333</v>
-      </c>
       <c r="M155" t="s">
         <v>26</v>
       </c>
       <c r="N155" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="Q155" t="s">
         <v>27</v>
@@ -9924,10 +9930,10 @@
         <v>2399014</v>
       </c>
       <c r="B156" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C156" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D156" s="2">
         <v>2</v>
@@ -9936,7 +9942,7 @@
         <v>20</v>
       </c>
       <c r="F156" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G156" t="s">
         <v>22</v>
@@ -9951,16 +9957,16 @@
         <v>24</v>
       </c>
       <c r="K156" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="L156" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="M156" t="s">
         <v>26</v>
       </c>
       <c r="N156" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="Q156" t="s">
         <v>27</v>
@@ -9974,10 +9980,10 @@
         <v>2399014</v>
       </c>
       <c r="B157" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C157" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D157" s="2">
         <v>2</v>
@@ -9986,7 +9992,7 @@
         <v>20</v>
       </c>
       <c r="F157" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G157" t="s">
         <v>22</v>
@@ -10001,13 +10007,13 @@
         <v>24</v>
       </c>
       <c r="K157" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="M157" t="s">
         <v>26</v>
       </c>
       <c r="N157" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="Q157" t="s">
         <v>27</v>
@@ -10021,10 +10027,10 @@
         <v>2400003</v>
       </c>
       <c r="B158" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C158" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D158" s="2">
         <v>1</v>
@@ -10048,16 +10054,16 @@
         <v>41</v>
       </c>
       <c r="K158" t="s">
+        <v>336</v>
+      </c>
+      <c r="L158" t="s">
         <v>337</v>
       </c>
-      <c r="L158" t="s">
-        <v>338</v>
-      </c>
       <c r="M158" t="s">
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="Q158" t="s">
         <v>27</v>
@@ -10071,10 +10077,10 @@
         <v>2400003</v>
       </c>
       <c r="B159" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C159" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D159" s="2">
         <v>1</v>
@@ -10098,16 +10104,16 @@
         <v>41</v>
       </c>
       <c r="K159" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="L159" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="M159" t="s">
         <v>26</v>
       </c>
       <c r="N159" s="6" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="Q159" t="s">
         <v>27</v>
@@ -10121,10 +10127,10 @@
         <v>2400003</v>
       </c>
       <c r="B160" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C160" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D160" s="2">
         <v>1</v>
@@ -10148,16 +10154,16 @@
         <v>41</v>
       </c>
       <c r="K160" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="L160" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="M160" t="s">
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="Q160" t="s">
         <v>27</v>
@@ -10171,10 +10177,10 @@
         <v>2400008</v>
       </c>
       <c r="B161" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C161" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D161" s="2">
         <v>1</v>
@@ -10198,16 +10204,16 @@
         <v>41</v>
       </c>
       <c r="K161" t="s">
+        <v>340</v>
+      </c>
+      <c r="L161" t="s">
         <v>341</v>
       </c>
-      <c r="L161" t="s">
-        <v>342</v>
-      </c>
       <c r="M161" t="s">
         <v>26</v>
       </c>
       <c r="N161" s="6" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="Q161" t="s">
         <v>27</v>
@@ -10221,10 +10227,10 @@
         <v>2400008</v>
       </c>
       <c r="B162" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C162" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D162" s="2">
         <v>1</v>
@@ -10248,16 +10254,16 @@
         <v>41</v>
       </c>
       <c r="K162" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="L162" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="M162" t="s">
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="Q162" t="s">
         <v>27</v>
@@ -10271,10 +10277,10 @@
         <v>2400008</v>
       </c>
       <c r="B163" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C163" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D163" s="2">
         <v>1</v>
@@ -10298,16 +10304,16 @@
         <v>41</v>
       </c>
       <c r="K163" t="s">
+        <v>343</v>
+      </c>
+      <c r="L163" t="s">
         <v>344</v>
       </c>
-      <c r="L163" t="s">
-        <v>345</v>
-      </c>
       <c r="M163" t="s">
         <v>26</v>
       </c>
       <c r="N163" s="6" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="Q163" t="s">
         <v>27</v>
@@ -10321,10 +10327,10 @@
         <v>2400012</v>
       </c>
       <c r="B164" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C164" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D164" s="2">
         <v>2</v>
@@ -10333,7 +10339,7 @@
         <v>20</v>
       </c>
       <c r="F164" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G164" t="s">
         <v>22</v>
@@ -10348,16 +10354,16 @@
         <v>24</v>
       </c>
       <c r="K164" t="s">
+        <v>345</v>
+      </c>
+      <c r="L164" t="s">
         <v>346</v>
       </c>
-      <c r="L164" t="s">
+      <c r="M164" t="s">
+        <v>26</v>
+      </c>
+      <c r="N164" t="s">
         <v>347</v>
-      </c>
-      <c r="M164" t="s">
-        <v>26</v>
-      </c>
-      <c r="N164" t="s">
-        <v>348</v>
       </c>
       <c r="Q164" t="s">
         <v>27</v>
@@ -10371,10 +10377,10 @@
         <v>2400012</v>
       </c>
       <c r="B165" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C165" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D165" s="2">
         <v>2</v>
@@ -10383,7 +10389,7 @@
         <v>20</v>
       </c>
       <c r="F165" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G165" t="s">
         <v>22</v>
@@ -10398,16 +10404,16 @@
         <v>24</v>
       </c>
       <c r="K165" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="L165" t="s">
+        <v>346</v>
+      </c>
+      <c r="M165" t="s">
+        <v>26</v>
+      </c>
+      <c r="N165" t="s">
         <v>349</v>
-      </c>
-      <c r="L165" t="s">
-        <v>347</v>
-      </c>
-      <c r="M165" t="s">
-        <v>26</v>
-      </c>
-      <c r="N165" t="s">
-        <v>350</v>
       </c>
       <c r="Q165" t="s">
         <v>27</v>
@@ -10421,10 +10427,10 @@
         <v>2400012</v>
       </c>
       <c r="B166" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C166" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D166" s="2">
         <v>2</v>
@@ -10433,7 +10439,7 @@
         <v>20</v>
       </c>
       <c r="F166" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G166" t="s">
         <v>22</v>
@@ -10448,13 +10454,13 @@
         <v>24</v>
       </c>
       <c r="K166" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M166" t="s">
         <v>26</v>
       </c>
       <c r="N166" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="Q166" t="s">
         <v>27</v>
@@ -10468,10 +10474,10 @@
         <v>2401001</v>
       </c>
       <c r="B167" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C167" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D167" s="2">
         <v>1</v>
@@ -10495,16 +10501,16 @@
         <v>24</v>
       </c>
       <c r="K167" t="s">
+        <v>352</v>
+      </c>
+      <c r="L167" t="s">
         <v>353</v>
       </c>
-      <c r="L167" t="s">
-        <v>354</v>
-      </c>
       <c r="M167" t="s">
         <v>26</v>
       </c>
       <c r="N167" s="6" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="Q167" t="s">
         <v>27</v>
@@ -10518,10 +10524,10 @@
         <v>2401001</v>
       </c>
       <c r="B168" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C168" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D168" s="2">
         <v>1</v>
@@ -10545,16 +10551,16 @@
         <v>24</v>
       </c>
       <c r="K168" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="L168" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="M168" t="s">
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="Q168" t="s">
         <v>27</v>
@@ -10568,10 +10574,10 @@
         <v>2401001</v>
       </c>
       <c r="B169" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C169" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D169" s="2">
         <v>1</v>
@@ -10595,16 +10601,16 @@
         <v>24</v>
       </c>
       <c r="K169" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="L169" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="M169" t="s">
         <v>26</v>
       </c>
       <c r="N169" s="6" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="Q169" t="s">
         <v>27</v>
@@ -10618,10 +10624,10 @@
         <v>2401007</v>
       </c>
       <c r="B170" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C170" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D170" s="2">
         <v>1</v>
@@ -10645,16 +10651,16 @@
         <v>24</v>
       </c>
       <c r="K170" t="s">
+        <v>356</v>
+      </c>
+      <c r="L170" t="s">
         <v>357</v>
       </c>
-      <c r="L170" t="s">
-        <v>358</v>
-      </c>
       <c r="M170" t="s">
         <v>26</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="Q170" t="s">
         <v>27</v>
@@ -10668,10 +10674,10 @@
         <v>2401007</v>
       </c>
       <c r="B171" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C171" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D171" s="2">
         <v>1</v>
@@ -10695,16 +10701,16 @@
         <v>24</v>
       </c>
       <c r="K171" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="L171" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="M171" t="s">
         <v>26</v>
       </c>
       <c r="N171" s="6" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="Q171" t="s">
         <v>27</v>
@@ -10718,10 +10724,10 @@
         <v>2401007</v>
       </c>
       <c r="B172" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C172" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D172" s="2">
         <v>1</v>
@@ -10745,16 +10751,16 @@
         <v>24</v>
       </c>
       <c r="K172" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="L172" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="M172" t="s">
         <v>26</v>
       </c>
       <c r="N172" s="6" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="Q172" t="s">
         <v>27</v>
@@ -10768,10 +10774,10 @@
         <v>2401013</v>
       </c>
       <c r="B173" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C173" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D173" s="2">
         <v>2</v>
@@ -10780,7 +10786,7 @@
         <v>20</v>
       </c>
       <c r="F173" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G173" t="s">
         <v>39</v>
@@ -10795,16 +10801,16 @@
         <v>41</v>
       </c>
       <c r="K173" t="s">
+        <v>361</v>
+      </c>
+      <c r="L173" t="s">
         <v>362</v>
       </c>
-      <c r="L173" t="s">
+      <c r="M173" t="s">
+        <v>26</v>
+      </c>
+      <c r="N173" t="s">
         <v>363</v>
-      </c>
-      <c r="M173" t="s">
-        <v>26</v>
-      </c>
-      <c r="N173" t="s">
-        <v>364</v>
       </c>
       <c r="Q173" t="s">
         <v>27</v>
@@ -10818,10 +10824,10 @@
         <v>2401013</v>
       </c>
       <c r="B174" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C174" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D174" s="2">
         <v>2</v>
@@ -10830,7 +10836,7 @@
         <v>20</v>
       </c>
       <c r="F174" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G174" t="s">
         <v>39</v>
@@ -10845,16 +10851,16 @@
         <v>41</v>
       </c>
       <c r="K174" t="s">
+        <v>364</v>
+      </c>
+      <c r="L174" t="s">
+        <v>362</v>
+      </c>
+      <c r="M174" t="s">
+        <v>26</v>
+      </c>
+      <c r="N174" t="s">
         <v>365</v>
-      </c>
-      <c r="L174" t="s">
-        <v>363</v>
-      </c>
-      <c r="M174" t="s">
-        <v>26</v>
-      </c>
-      <c r="N174" t="s">
-        <v>366</v>
       </c>
       <c r="Q174" t="s">
         <v>27</v>
@@ -10868,10 +10874,10 @@
         <v>2401013</v>
       </c>
       <c r="B175" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C175" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D175" s="2">
         <v>2</v>
@@ -10880,7 +10886,7 @@
         <v>20</v>
       </c>
       <c r="F175" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G175" t="s">
         <v>39</v>
@@ -10895,16 +10901,16 @@
         <v>41</v>
       </c>
       <c r="K175" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="L175" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="M175" t="s">
         <v>26</v>
       </c>
       <c r="N175" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="Q175" t="s">
         <v>27</v>
@@ -10918,10 +10924,10 @@
         <v>2401018</v>
       </c>
       <c r="B176" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C176" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D176" s="2">
         <v>2</v>
@@ -10930,7 +10936,7 @@
         <v>34</v>
       </c>
       <c r="F176" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G176" t="s">
         <v>39</v>
@@ -10945,16 +10951,16 @@
         <v>41</v>
       </c>
       <c r="K176" t="s">
+        <v>368</v>
+      </c>
+      <c r="L176" t="s">
         <v>369</v>
       </c>
-      <c r="L176" t="s">
-        <v>370</v>
-      </c>
       <c r="M176" t="s">
         <v>26</v>
       </c>
       <c r="N176" s="6" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="Q176" t="s">
         <v>27</v>
@@ -10968,10 +10974,10 @@
         <v>2401018</v>
       </c>
       <c r="B177" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C177" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D177" s="2">
         <v>2</v>
@@ -10980,7 +10986,7 @@
         <v>34</v>
       </c>
       <c r="F177" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G177" t="s">
         <v>39</v>
@@ -10995,16 +11001,16 @@
         <v>41</v>
       </c>
       <c r="K177" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="L177" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M177" t="s">
         <v>26</v>
       </c>
       <c r="N177" s="6" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="Q177" t="s">
         <v>27</v>
@@ -11018,10 +11024,10 @@
         <v>2401018</v>
       </c>
       <c r="B178" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C178" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D178" s="2">
         <v>2</v>
@@ -11030,7 +11036,7 @@
         <v>34</v>
       </c>
       <c r="F178" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G178" t="s">
         <v>39</v>
@@ -11039,16 +11045,16 @@
         <v>4</v>
       </c>
       <c r="I178" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="J178" t="s">
         <v>41</v>
       </c>
       <c r="K178" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="L178" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M178" t="s">
         <v>26</v>
@@ -11065,10 +11071,10 @@
         <v>2401018</v>
       </c>
       <c r="B179" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C179" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D179" s="2">
         <v>2</v>
@@ -11077,7 +11083,7 @@
         <v>34</v>
       </c>
       <c r="F179" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G179" t="s">
         <v>39</v>
@@ -11092,16 +11098,16 @@
         <v>41</v>
       </c>
       <c r="K179" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="L179" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M179" t="s">
         <v>26</v>
       </c>
       <c r="N179" s="6" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="Q179" t="s">
         <v>27</v>
@@ -11115,10 +11121,10 @@
         <v>2401018</v>
       </c>
       <c r="B180" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C180" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D180" s="2">
         <v>2</v>
@@ -11127,7 +11133,7 @@
         <v>34</v>
       </c>
       <c r="F180" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G180" t="s">
         <v>39</v>
@@ -11136,16 +11142,16 @@
         <v>4</v>
       </c>
       <c r="I180" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="J180" t="s">
         <v>41</v>
       </c>
       <c r="K180" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L180" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M180" t="s">
         <v>26</v>
@@ -11162,10 +11168,10 @@
         <v>2401018</v>
       </c>
       <c r="B181" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C181" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D181" s="2">
         <v>2</v>
@@ -11174,7 +11180,7 @@
         <v>34</v>
       </c>
       <c r="F181" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G181" t="s">
         <v>39</v>
@@ -11183,16 +11189,16 @@
         <v>4</v>
       </c>
       <c r="I181" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J181" t="s">
         <v>41</v>
       </c>
       <c r="K181" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="L181" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M181" t="s">
         <v>26</v>
@@ -11209,10 +11215,10 @@
         <v>2401018</v>
       </c>
       <c r="B182" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C182" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D182" s="2">
         <v>2</v>
@@ -11221,7 +11227,7 @@
         <v>34</v>
       </c>
       <c r="F182" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G182" t="s">
         <v>39</v>
@@ -11230,16 +11236,16 @@
         <v>4</v>
       </c>
       <c r="I182" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="J182" t="s">
         <v>41</v>
       </c>
       <c r="K182" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="L182" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M182" t="s">
         <v>26</v>
@@ -11256,10 +11262,10 @@
         <v>2402003</v>
       </c>
       <c r="B183" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C183" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D183" s="2">
         <v>1</v>
@@ -11283,16 +11289,16 @@
         <v>24</v>
       </c>
       <c r="K183" t="s">
+        <v>381</v>
+      </c>
+      <c r="L183" t="s">
         <v>382</v>
       </c>
-      <c r="L183" t="s">
-        <v>383</v>
-      </c>
       <c r="M183" t="s">
         <v>26</v>
       </c>
       <c r="N183" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="O183" s="4"/>
       <c r="Q183" t="s">
@@ -11307,10 +11313,10 @@
         <v>2402003</v>
       </c>
       <c r="B184" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C184" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D184" s="2">
         <v>1</v>
@@ -11334,16 +11340,16 @@
         <v>24</v>
       </c>
       <c r="K184" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="L184" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="M184" t="s">
         <v>26</v>
       </c>
       <c r="N184" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O184" s="4"/>
       <c r="Q184" t="s">
@@ -11358,10 +11364,10 @@
         <v>2402003</v>
       </c>
       <c r="B185" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C185" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D185" s="2">
         <v>1</v>
@@ -11385,16 +11391,16 @@
         <v>24</v>
       </c>
       <c r="K185" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L185" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="M185" t="s">
         <v>26</v>
       </c>
       <c r="N185" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O185" s="4"/>
       <c r="Q185" t="s">
@@ -11409,10 +11415,10 @@
         <v>2402008</v>
       </c>
       <c r="B186" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C186" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D186" s="2">
         <v>1</v>
@@ -11436,19 +11442,19 @@
         <v>24</v>
       </c>
       <c r="K186" t="s">
+        <v>385</v>
+      </c>
+      <c r="L186" t="s">
         <v>386</v>
       </c>
-      <c r="L186" t="s">
+      <c r="M186" t="s">
+        <v>26</v>
+      </c>
+      <c r="N186" t="s">
         <v>387</v>
       </c>
-      <c r="M186" t="s">
-        <v>26</v>
-      </c>
-      <c r="N186" t="s">
-        <v>388</v>
-      </c>
       <c r="O186" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="Q186" t="s">
         <v>27</v>
@@ -11462,10 +11468,10 @@
         <v>2402008</v>
       </c>
       <c r="B187" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C187" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D187" s="2">
         <v>1</v>
@@ -11489,19 +11495,19 @@
         <v>24</v>
       </c>
       <c r="K187" t="s">
+        <v>388</v>
+      </c>
+      <c r="L187" t="s">
+        <v>386</v>
+      </c>
+      <c r="M187" t="s">
+        <v>26</v>
+      </c>
+      <c r="N187" t="s">
         <v>389</v>
       </c>
-      <c r="L187" t="s">
-        <v>387</v>
-      </c>
-      <c r="M187" t="s">
-        <v>26</v>
-      </c>
-      <c r="N187" t="s">
-        <v>390</v>
-      </c>
       <c r="O187" s="6" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="Q187" t="s">
         <v>27</v>
@@ -11515,10 +11521,10 @@
         <v>2402008</v>
       </c>
       <c r="B188" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C188" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D188" s="2">
         <v>1</v>
@@ -11542,19 +11548,19 @@
         <v>24</v>
       </c>
       <c r="K188" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="L188" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="M188" t="s">
         <v>26</v>
       </c>
       <c r="N188" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="O188" s="6" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="Q188" t="s">
         <v>27</v>
@@ -11568,10 +11574,10 @@
         <v>2402015</v>
       </c>
       <c r="B189" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C189" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D189" s="2">
         <v>2</v>
@@ -11580,7 +11586,7 @@
         <v>20</v>
       </c>
       <c r="F189" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G189" t="s">
         <v>22</v>
@@ -11595,13 +11601,13 @@
         <v>41</v>
       </c>
       <c r="K189" t="s">
+        <v>391</v>
+      </c>
+      <c r="M189" t="s">
+        <v>26</v>
+      </c>
+      <c r="N189" t="s">
         <v>392</v>
-      </c>
-      <c r="M189" t="s">
-        <v>26</v>
-      </c>
-      <c r="N189" t="s">
-        <v>393</v>
       </c>
       <c r="Q189" t="s">
         <v>27</v>
@@ -11615,10 +11621,10 @@
         <v>2402015</v>
       </c>
       <c r="B190" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C190" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D190" s="2">
         <v>2</v>
@@ -11627,7 +11633,7 @@
         <v>20</v>
       </c>
       <c r="F190" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G190" t="s">
         <v>22</v>
@@ -11642,13 +11648,13 @@
         <v>41</v>
       </c>
       <c r="K190" t="s">
+        <v>393</v>
+      </c>
+      <c r="M190" t="s">
+        <v>26</v>
+      </c>
+      <c r="N190" t="s">
         <v>394</v>
-      </c>
-      <c r="M190" t="s">
-        <v>26</v>
-      </c>
-      <c r="N190" t="s">
-        <v>395</v>
       </c>
       <c r="Q190" t="s">
         <v>27</v>
@@ -11662,10 +11668,10 @@
         <v>2402015</v>
       </c>
       <c r="B191" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C191" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D191" s="2">
         <v>2</v>
@@ -11674,7 +11680,7 @@
         <v>20</v>
       </c>
       <c r="F191" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G191" t="s">
         <v>22</v>
@@ -11689,13 +11695,13 @@
         <v>41</v>
       </c>
       <c r="K191" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="M191" t="s">
         <v>26</v>
       </c>
       <c r="N191" s="5" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="O191" s="3"/>
       <c r="Q191" t="s">
@@ -11710,10 +11716,10 @@
         <v>2403004</v>
       </c>
       <c r="B192" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C192" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D192" s="2">
         <v>1</v>
@@ -11737,16 +11743,16 @@
         <v>41</v>
       </c>
       <c r="K192" t="s">
+        <v>397</v>
+      </c>
+      <c r="L192" t="s">
         <v>398</v>
       </c>
-      <c r="L192" t="s">
-        <v>399</v>
-      </c>
       <c r="M192" t="s">
         <v>26</v>
       </c>
       <c r="N192" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="O192" s="4"/>
       <c r="Q192" t="s">
@@ -11761,10 +11767,10 @@
         <v>2403004</v>
       </c>
       <c r="B193" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C193" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D193" s="2">
         <v>1</v>
@@ -11788,16 +11794,16 @@
         <v>41</v>
       </c>
       <c r="K193" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="L193" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="M193" t="s">
         <v>26</v>
       </c>
       <c r="N193" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O193" s="4"/>
       <c r="Q193" t="s">
@@ -11812,10 +11818,10 @@
         <v>2403004</v>
       </c>
       <c r="B194" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C194" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D194" s="2">
         <v>1</v>
@@ -11839,16 +11845,16 @@
         <v>41</v>
       </c>
       <c r="K194" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="L194" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="M194" t="s">
         <v>26</v>
       </c>
       <c r="N194" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O194" s="4"/>
       <c r="Q194" t="s">
@@ -11863,10 +11869,10 @@
         <v>2403009</v>
       </c>
       <c r="B195" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C195" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D195" s="2">
         <v>1</v>
@@ -11890,19 +11896,19 @@
         <v>41</v>
       </c>
       <c r="K195" t="s">
+        <v>401</v>
+      </c>
+      <c r="L195" t="s">
         <v>402</v>
       </c>
-      <c r="L195" t="s">
-        <v>403</v>
-      </c>
       <c r="M195" t="s">
         <v>26</v>
       </c>
       <c r="N195" s="8" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="O195" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Q195" t="s">
         <v>27</v>
@@ -11916,10 +11922,10 @@
         <v>2403009</v>
       </c>
       <c r="B196" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C196" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D196" s="2">
         <v>1</v>
@@ -11943,19 +11949,19 @@
         <v>41</v>
       </c>
       <c r="K196" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="L196" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="M196" t="s">
         <v>26</v>
       </c>
       <c r="N196" s="8" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="O196" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="Q196" t="s">
         <v>27</v>
@@ -11969,10 +11975,10 @@
         <v>2403009</v>
       </c>
       <c r="B197" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C197" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D197" s="2">
         <v>1</v>
@@ -11996,19 +12002,19 @@
         <v>41</v>
       </c>
       <c r="K197" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="L197" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="M197" t="s">
         <v>26</v>
       </c>
       <c r="N197" s="8" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="O197" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="Q197" t="s">
         <v>27</v>
@@ -12022,10 +12028,10 @@
         <v>2403013</v>
       </c>
       <c r="B198" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C198" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D198" s="2">
         <v>2</v>
@@ -12034,7 +12040,7 @@
         <v>20</v>
       </c>
       <c r="F198" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G198" t="s">
         <v>22</v>
@@ -12049,13 +12055,13 @@
         <v>24</v>
       </c>
       <c r="K198" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="M198" t="s">
         <v>26</v>
       </c>
       <c r="N198" s="6" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="Q198" t="s">
         <v>27</v>
@@ -12069,10 +12075,10 @@
         <v>2403013</v>
       </c>
       <c r="B199" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C199" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D199" s="2">
         <v>2</v>
@@ -12081,7 +12087,7 @@
         <v>20</v>
       </c>
       <c r="F199" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G199" t="s">
         <v>22</v>
@@ -12096,13 +12102,13 @@
         <v>24</v>
       </c>
       <c r="K199" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="M199" t="s">
         <v>26</v>
       </c>
       <c r="N199" s="6" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="Q199" t="s">
         <v>27</v>
@@ -12116,10 +12122,10 @@
         <v>2403013</v>
       </c>
       <c r="B200" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C200" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D200" s="2">
         <v>2</v>
@@ -12128,7 +12134,7 @@
         <v>20</v>
       </c>
       <c r="F200" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G200" t="s">
         <v>22</v>
@@ -12143,13 +12149,13 @@
         <v>24</v>
       </c>
       <c r="K200" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="M200" t="s">
         <v>26</v>
       </c>
       <c r="N200" s="6" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="Q200" t="s">
         <v>27</v>
@@ -12163,10 +12169,10 @@
         <v>2404001</v>
       </c>
       <c r="B201" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C201" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D201" s="2">
         <v>1</v>
@@ -12190,16 +12196,16 @@
         <v>41</v>
       </c>
       <c r="K201" t="s">
+        <v>409</v>
+      </c>
+      <c r="L201" t="s">
         <v>410</v>
       </c>
-      <c r="L201" t="s">
+      <c r="M201" t="s">
+        <v>26</v>
+      </c>
+      <c r="N201" t="s">
         <v>411</v>
-      </c>
-      <c r="M201" t="s">
-        <v>26</v>
-      </c>
-      <c r="N201" t="s">
-        <v>412</v>
       </c>
       <c r="Q201" t="s">
         <v>27</v>
@@ -12213,10 +12219,10 @@
         <v>2404001</v>
       </c>
       <c r="B202" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C202" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D202" s="2">
         <v>1</v>
@@ -12240,16 +12246,16 @@
         <v>41</v>
       </c>
       <c r="K202" t="s">
+        <v>412</v>
+      </c>
+      <c r="L202" t="s">
+        <v>410</v>
+      </c>
+      <c r="M202" t="s">
+        <v>26</v>
+      </c>
+      <c r="N202" t="s">
         <v>413</v>
-      </c>
-      <c r="L202" t="s">
-        <v>411</v>
-      </c>
-      <c r="M202" t="s">
-        <v>26</v>
-      </c>
-      <c r="N202" t="s">
-        <v>414</v>
       </c>
       <c r="Q202" t="s">
         <v>27</v>
@@ -12263,10 +12269,10 @@
         <v>2404001</v>
       </c>
       <c r="B203" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C203" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D203" s="2">
         <v>1</v>
@@ -12290,16 +12296,16 @@
         <v>41</v>
       </c>
       <c r="K203" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="L203" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="M203" t="s">
         <v>26</v>
       </c>
       <c r="N203" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="Q203" t="s">
         <v>27</v>
@@ -12313,10 +12319,10 @@
         <v>2404006</v>
       </c>
       <c r="B204" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C204" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D204" s="2">
         <v>1</v>
@@ -12340,16 +12346,16 @@
         <v>41</v>
       </c>
       <c r="K204" t="s">
+        <v>415</v>
+      </c>
+      <c r="L204" t="s">
         <v>416</v>
       </c>
-      <c r="L204" t="s">
+      <c r="M204" t="s">
+        <v>26</v>
+      </c>
+      <c r="N204" t="s">
         <v>417</v>
-      </c>
-      <c r="M204" t="s">
-        <v>26</v>
-      </c>
-      <c r="N204" t="s">
-        <v>418</v>
       </c>
       <c r="Q204" t="s">
         <v>27</v>
@@ -12363,10 +12369,10 @@
         <v>2404006</v>
       </c>
       <c r="B205" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C205" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D205" s="2">
         <v>1</v>
@@ -12390,16 +12396,16 @@
         <v>41</v>
       </c>
       <c r="K205" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="L205" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="M205" t="s">
         <v>26</v>
       </c>
       <c r="N205" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="Q205" t="s">
         <v>27</v>
@@ -12413,10 +12419,10 @@
         <v>2404006</v>
       </c>
       <c r="B206" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C206" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D206" s="2">
         <v>1</v>
@@ -12440,16 +12446,16 @@
         <v>41</v>
       </c>
       <c r="K206" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="L206" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="M206" t="s">
         <v>26</v>
       </c>
       <c r="N206" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="Q206" t="s">
         <v>27</v>
@@ -12463,10 +12469,10 @@
         <v>2404015</v>
       </c>
       <c r="B207" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C207" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D207" s="2">
         <v>2</v>
@@ -12475,7 +12481,7 @@
         <v>20</v>
       </c>
       <c r="F207" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G207" t="s">
         <v>39</v>
@@ -12490,16 +12496,16 @@
         <v>24</v>
       </c>
       <c r="K207" t="s">
+        <v>421</v>
+      </c>
+      <c r="M207" t="s">
+        <v>26</v>
+      </c>
+      <c r="N207" t="s">
         <v>422</v>
       </c>
-      <c r="M207" t="s">
-        <v>26</v>
-      </c>
-      <c r="N207" t="s">
-        <v>423</v>
-      </c>
       <c r="O207" s="6" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="Q207" t="s">
         <v>27</v>
@@ -12513,10 +12519,10 @@
         <v>2404015</v>
       </c>
       <c r="B208" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C208" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D208" s="2">
         <v>2</v>
@@ -12525,7 +12531,7 @@
         <v>20</v>
       </c>
       <c r="F208" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G208" t="s">
         <v>39</v>
@@ -12534,22 +12540,22 @@
         <v>32</v>
       </c>
       <c r="I208" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="J208" t="s">
         <v>24</v>
       </c>
       <c r="K208" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="M208" t="s">
         <v>26</v>
       </c>
       <c r="N208" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="O208" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="Q208" t="s">
         <v>27</v>
@@ -12563,10 +12569,10 @@
         <v>2404015</v>
       </c>
       <c r="B209" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C209" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D209" s="2">
         <v>2</v>
@@ -12575,7 +12581,7 @@
         <v>20</v>
       </c>
       <c r="F209" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G209" t="s">
         <v>39</v>
@@ -12584,22 +12590,22 @@
         <v>32</v>
       </c>
       <c r="I209" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="J209" t="s">
         <v>24</v>
       </c>
       <c r="K209" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="M209" t="s">
         <v>26</v>
       </c>
       <c r="N209" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="O209" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="Q209" t="s">
         <v>27</v>
@@ -12613,10 +12619,10 @@
         <v>2405001</v>
       </c>
       <c r="B210" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C210" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D210" s="2">
         <v>1</v>
@@ -12640,16 +12646,16 @@
         <v>41</v>
       </c>
       <c r="K210" t="s">
+        <v>428</v>
+      </c>
+      <c r="L210" t="s">
         <v>429</v>
       </c>
-      <c r="L210" t="s">
-        <v>430</v>
-      </c>
       <c r="M210" t="s">
         <v>26</v>
       </c>
       <c r="N210" s="6" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="Q210" t="s">
         <v>27</v>
@@ -12663,10 +12669,10 @@
         <v>2405001</v>
       </c>
       <c r="B211" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C211" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D211" s="2">
         <v>1</v>
@@ -12690,16 +12696,16 @@
         <v>41</v>
       </c>
       <c r="K211" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="L211" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="M211" t="s">
         <v>26</v>
       </c>
       <c r="N211" s="6" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="Q211" t="s">
         <v>27</v>
@@ -12713,10 +12719,10 @@
         <v>2405001</v>
       </c>
       <c r="B212" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C212" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D212" s="2">
         <v>1</v>
@@ -12740,16 +12746,16 @@
         <v>41</v>
       </c>
       <c r="K212" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="L212" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="M212" t="s">
         <v>26</v>
       </c>
       <c r="N212" s="6" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="Q212" t="s">
         <v>27</v>
@@ -12763,10 +12769,10 @@
         <v>2405006</v>
       </c>
       <c r="B213" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C213" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D213" s="2">
         <v>1</v>
@@ -12790,19 +12796,19 @@
         <v>41</v>
       </c>
       <c r="K213" t="s">
+        <v>432</v>
+      </c>
+      <c r="L213" t="s">
         <v>433</v>
       </c>
-      <c r="L213" t="s">
-        <v>434</v>
-      </c>
       <c r="M213" t="s">
         <v>26</v>
       </c>
       <c r="N213" s="6" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="O213" s="6" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="Q213" t="s">
         <v>27</v>
@@ -12816,10 +12822,10 @@
         <v>2405006</v>
       </c>
       <c r="B214" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C214" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D214" s="2">
         <v>1</v>
@@ -12843,19 +12849,19 @@
         <v>41</v>
       </c>
       <c r="K214" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="L214" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="M214" t="s">
         <v>26</v>
       </c>
       <c r="N214" s="6" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="O214" s="6" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="Q214" t="s">
         <v>27</v>
@@ -12869,10 +12875,10 @@
         <v>2405006</v>
       </c>
       <c r="B215" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C215" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D215" s="2">
         <v>1</v>
@@ -12896,19 +12902,19 @@
         <v>41</v>
       </c>
       <c r="K215" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="L215" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="M215" t="s">
         <v>26</v>
       </c>
       <c r="N215" s="6" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="O215" s="6" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="Q215" t="s">
         <v>27</v>
@@ -12922,10 +12928,10 @@
         <v>2405015</v>
       </c>
       <c r="B216" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C216" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D216" s="2">
         <v>2</v>
@@ -12934,7 +12940,7 @@
         <v>20</v>
       </c>
       <c r="F216" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G216" t="s">
         <v>22</v>
@@ -12949,16 +12955,16 @@
         <v>24</v>
       </c>
       <c r="K216" t="s">
+        <v>436</v>
+      </c>
+      <c r="L216" t="s">
         <v>437</v>
       </c>
-      <c r="L216" t="s">
+      <c r="M216" t="s">
+        <v>26</v>
+      </c>
+      <c r="N216" t="s">
         <v>438</v>
-      </c>
-      <c r="M216" t="s">
-        <v>26</v>
-      </c>
-      <c r="N216" t="s">
-        <v>439</v>
       </c>
       <c r="Q216" t="s">
         <v>27</v>
@@ -12972,10 +12978,10 @@
         <v>2405015</v>
       </c>
       <c r="B217" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C217" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D217" s="2">
         <v>2</v>
@@ -12984,7 +12990,7 @@
         <v>20</v>
       </c>
       <c r="F217" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G217" t="s">
         <v>22</v>
@@ -12999,16 +13005,16 @@
         <v>24</v>
       </c>
       <c r="K217" t="s">
+        <v>439</v>
+      </c>
+      <c r="L217" t="s">
+        <v>437</v>
+      </c>
+      <c r="M217" t="s">
+        <v>26</v>
+      </c>
+      <c r="N217" t="s">
         <v>440</v>
-      </c>
-      <c r="L217" t="s">
-        <v>438</v>
-      </c>
-      <c r="M217" t="s">
-        <v>26</v>
-      </c>
-      <c r="N217" t="s">
-        <v>441</v>
       </c>
       <c r="Q217" t="s">
         <v>27</v>
@@ -13022,10 +13028,10 @@
         <v>2405015</v>
       </c>
       <c r="B218" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C218" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D218" s="2">
         <v>2</v>
@@ -13034,7 +13040,7 @@
         <v>20</v>
       </c>
       <c r="F218" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G218" t="s">
         <v>22</v>
@@ -13049,13 +13055,13 @@
         <v>24</v>
       </c>
       <c r="K218" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="M218" t="s">
         <v>26</v>
       </c>
       <c r="N218" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q218" t="s">
         <v>27</v>
@@ -13069,10 +13075,10 @@
         <v>2406004</v>
       </c>
       <c r="B219" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C219" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D219" s="2">
         <v>1</v>
@@ -13096,16 +13102,16 @@
         <v>24</v>
       </c>
       <c r="K219" t="s">
+        <v>443</v>
+      </c>
+      <c r="L219" t="s">
         <v>444</v>
       </c>
-      <c r="L219" t="s">
-        <v>445</v>
-      </c>
       <c r="M219" t="s">
         <v>26</v>
       </c>
       <c r="N219" s="6" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="Q219" t="s">
         <v>27</v>
@@ -13119,10 +13125,10 @@
         <v>2406004</v>
       </c>
       <c r="B220" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C220" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D220" s="2">
         <v>1</v>
@@ -13146,16 +13152,16 @@
         <v>24</v>
       </c>
       <c r="K220" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="L220" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="M220" t="s">
         <v>26</v>
       </c>
       <c r="N220" s="6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="Q220" t="s">
         <v>27</v>
@@ -13169,10 +13175,10 @@
         <v>2406004</v>
       </c>
       <c r="B221" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C221" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D221" s="2">
         <v>1</v>
@@ -13190,25 +13196,25 @@
         <v>8</v>
       </c>
       <c r="I221" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="J221" t="s">
         <v>24</v>
       </c>
       <c r="K221" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="L221" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="M221" t="s">
         <v>26</v>
       </c>
       <c r="N221" s="6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="O221" s="6" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="Q221" t="s">
         <v>27</v>
@@ -13222,10 +13228,10 @@
         <v>2406004</v>
       </c>
       <c r="B222" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C222" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D222" s="2">
         <v>1</v>
@@ -13249,16 +13255,16 @@
         <v>24</v>
       </c>
       <c r="K222" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="L222" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="M222" t="s">
         <v>26</v>
       </c>
       <c r="N222" s="6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="Q222" t="s">
         <v>27</v>
@@ -13272,10 +13278,10 @@
         <v>2406004</v>
       </c>
       <c r="B223" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C223" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D223" s="2">
         <v>1</v>
@@ -13293,25 +13299,25 @@
         <v>8</v>
       </c>
       <c r="I223" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="J223" t="s">
         <v>24</v>
       </c>
       <c r="K223" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="L223" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="M223" t="s">
         <v>26</v>
       </c>
       <c r="N223" s="6" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="O223" s="6" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="Q223" t="s">
         <v>27</v>
@@ -13325,10 +13331,10 @@
         <v>2406009</v>
       </c>
       <c r="B224" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C224" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D224" s="2">
         <v>1</v>
@@ -13352,16 +13358,16 @@
         <v>24</v>
       </c>
       <c r="K224" t="s">
+        <v>447</v>
+      </c>
+      <c r="L224" t="s">
         <v>448</v>
       </c>
-      <c r="L224" t="s">
-        <v>449</v>
-      </c>
       <c r="M224" t="s">
         <v>26</v>
       </c>
       <c r="N224" s="6" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="Q224" t="s">
         <v>27</v>
@@ -13375,10 +13381,10 @@
         <v>2406009</v>
       </c>
       <c r="B225" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C225" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D225" s="2">
         <v>1</v>
@@ -13402,16 +13408,16 @@
         <v>24</v>
       </c>
       <c r="K225" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="L225" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="M225" t="s">
         <v>26</v>
       </c>
       <c r="N225" s="6" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="Q225" t="s">
         <v>27</v>
@@ -13425,10 +13431,10 @@
         <v>2406009</v>
       </c>
       <c r="B226" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C226" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D226" s="2">
         <v>1</v>
@@ -13446,22 +13452,22 @@
         <v>8</v>
       </c>
       <c r="I226" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="J226" t="s">
         <v>24</v>
       </c>
       <c r="K226" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="L226" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="M226" t="s">
         <v>26</v>
       </c>
       <c r="N226" s="6" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="Q226" t="s">
         <v>27</v>
@@ -13475,10 +13481,10 @@
         <v>2406009</v>
       </c>
       <c r="B227" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C227" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D227" s="2">
         <v>1</v>
@@ -13502,16 +13508,16 @@
         <v>24</v>
       </c>
       <c r="K227" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="L227" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="M227" t="s">
         <v>26</v>
       </c>
       <c r="N227" s="6" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="Q227" t="s">
         <v>27</v>
@@ -13525,10 +13531,10 @@
         <v>2406009</v>
       </c>
       <c r="B228" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C228" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D228" s="2">
         <v>1</v>
@@ -13546,22 +13552,22 @@
         <v>8</v>
       </c>
       <c r="I228" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="J228" t="s">
         <v>24</v>
       </c>
       <c r="K228" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="L228" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="M228" t="s">
         <v>26</v>
       </c>
       <c r="N228" s="6" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="Q228" t="s">
         <v>27</v>
@@ -13575,10 +13581,10 @@
         <v>2406012</v>
       </c>
       <c r="B229" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C229" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D229" s="2">
         <v>2</v>
@@ -13587,7 +13593,7 @@
         <v>20</v>
       </c>
       <c r="F229" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G229" t="s">
         <v>39</v>
@@ -13602,16 +13608,16 @@
         <v>41</v>
       </c>
       <c r="K229" t="s">
+        <v>454</v>
+      </c>
+      <c r="L229" t="s">
         <v>455</v>
       </c>
-      <c r="L229" t="s">
-        <v>456</v>
-      </c>
       <c r="M229" t="s">
         <v>26</v>
       </c>
       <c r="N229" s="6" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="Q229" t="s">
         <v>27</v>
@@ -13625,10 +13631,10 @@
         <v>2406012</v>
       </c>
       <c r="B230" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C230" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D230" s="2">
         <v>2</v>
@@ -13637,7 +13643,7 @@
         <v>20</v>
       </c>
       <c r="F230" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G230" t="s">
         <v>39</v>
@@ -13646,25 +13652,25 @@
         <v>8</v>
       </c>
       <c r="I230" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="J230" t="s">
         <v>41</v>
       </c>
       <c r="K230" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="L230" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="M230" t="s">
         <v>26</v>
       </c>
       <c r="N230" s="6" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="O230" s="6" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="Q230" t="s">
         <v>27</v>
@@ -13678,10 +13684,10 @@
         <v>2406012</v>
       </c>
       <c r="B231" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C231" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D231" s="2">
         <v>2</v>
@@ -13690,7 +13696,7 @@
         <v>20</v>
       </c>
       <c r="F231" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G231" t="s">
         <v>39</v>
@@ -13699,25 +13705,25 @@
         <v>8</v>
       </c>
       <c r="I231" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="J231" t="s">
         <v>41</v>
       </c>
       <c r="K231" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L231" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="M231" t="s">
         <v>26</v>
       </c>
       <c r="N231" s="6" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="O231" s="6" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="Q231" t="s">
         <v>27</v>
@@ -13731,11 +13737,11 @@
         <v>2059001</v>
       </c>
       <c r="B232" t="s">
+        <v>458</v>
+      </c>
+      <c r="C232" t="s">
         <v>459</v>
       </c>
-      <c r="C232" t="s">
-        <v>460</v>
-      </c>
       <c r="D232" s="2">
         <v>1</v>
       </c>
@@ -13743,7 +13749,7 @@
         <v>20</v>
       </c>
       <c r="F232" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G232" t="s">
         <v>22</v>
@@ -13758,16 +13764,16 @@
         <v>41</v>
       </c>
       <c r="K232" t="s">
+        <v>460</v>
+      </c>
+      <c r="L232" t="s">
         <v>461</v>
       </c>
-      <c r="L232" t="s">
-        <v>462</v>
-      </c>
       <c r="M232" t="s">
         <v>26</v>
       </c>
       <c r="N232" s="6" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="Q232" t="s">
         <v>27</v>
@@ -13781,11 +13787,11 @@
         <v>2059002</v>
       </c>
       <c r="B233" t="s">
+        <v>458</v>
+      </c>
+      <c r="C233" t="s">
         <v>459</v>
       </c>
-      <c r="C233" t="s">
-        <v>460</v>
-      </c>
       <c r="D233" s="2">
         <v>1</v>
       </c>
@@ -13793,7 +13799,7 @@
         <v>20</v>
       </c>
       <c r="F233" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G233" t="s">
         <v>22</v>
@@ -13808,19 +13814,19 @@
         <v>41</v>
       </c>
       <c r="K233" t="s">
+        <v>462</v>
+      </c>
+      <c r="L233" t="s">
         <v>463</v>
       </c>
-      <c r="L233" t="s">
-        <v>464</v>
-      </c>
       <c r="M233" t="s">
         <v>26</v>
       </c>
       <c r="N233" s="6" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="O233" s="6" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="Q233" t="s">
         <v>27</v>
@@ -13834,10 +13840,10 @@
         <v>2059006</v>
       </c>
       <c r="B234" t="s">
+        <v>458</v>
+      </c>
+      <c r="C234" t="s">
         <v>459</v>
-      </c>
-      <c r="C234" t="s">
-        <v>460</v>
       </c>
       <c r="D234" s="2">
         <v>1</v>
@@ -13861,16 +13867,16 @@
         <v>41</v>
       </c>
       <c r="K234" t="s">
+        <v>464</v>
+      </c>
+      <c r="L234" t="s">
         <v>465</v>
       </c>
-      <c r="L234" t="s">
-        <v>466</v>
-      </c>
       <c r="M234" t="s">
         <v>26</v>
       </c>
       <c r="N234" s="6" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="Q234" t="s">
         <v>27</v>
@@ -13884,10 +13890,10 @@
         <v>2140011</v>
       </c>
       <c r="B235" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C235" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D235" s="2">
         <v>2</v>
@@ -13896,7 +13902,7 @@
         <v>20</v>
       </c>
       <c r="F235" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G235" t="s">
         <v>39</v>
@@ -13911,10 +13917,10 @@
         <v>41</v>
       </c>
       <c r="K235" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L235" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="M235" t="s">
         <v>26</v>
@@ -13931,10 +13937,10 @@
         <v>2390004</v>
       </c>
       <c r="B236" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C236" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D236" s="2">
         <v>1</v>
@@ -13958,16 +13964,16 @@
         <v>24</v>
       </c>
       <c r="K236" t="s">
+        <v>469</v>
+      </c>
+      <c r="L236" t="s">
         <v>470</v>
       </c>
-      <c r="L236" t="s">
-        <v>471</v>
-      </c>
       <c r="M236" t="s">
         <v>26</v>
       </c>
       <c r="N236" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="Q236" t="s">
         <v>27</v>
@@ -13981,10 +13987,10 @@
         <v>2390004</v>
       </c>
       <c r="B237" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C237" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D237" s="2">
         <v>1</v>
@@ -14008,16 +14014,16 @@
         <v>24</v>
       </c>
       <c r="K237" t="s">
+        <v>471</v>
+      </c>
+      <c r="L237" t="s">
         <v>472</v>
       </c>
-      <c r="L237" t="s">
-        <v>473</v>
-      </c>
       <c r="M237" t="s">
         <v>26</v>
       </c>
       <c r="N237" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="Q237" t="s">
         <v>27</v>
@@ -14031,10 +14037,10 @@
         <v>2390004</v>
       </c>
       <c r="B238" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C238" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D238" s="2">
         <v>1</v>
@@ -14058,16 +14064,16 @@
         <v>24</v>
       </c>
       <c r="K238" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="L238" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="M238" t="s">
         <v>26</v>
       </c>
       <c r="N238" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="Q238" t="s">
         <v>27</v>
@@ -14081,10 +14087,10 @@
         <v>2390009</v>
       </c>
       <c r="B239" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C239" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D239" s="2">
         <v>1</v>
@@ -14108,16 +14114,16 @@
         <v>24</v>
       </c>
       <c r="K239" t="s">
+        <v>474</v>
+      </c>
+      <c r="L239" t="s">
         <v>475</v>
       </c>
-      <c r="L239" t="s">
-        <v>476</v>
-      </c>
       <c r="M239" t="s">
         <v>26</v>
       </c>
       <c r="N239" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="Q239" t="s">
         <v>27</v>
@@ -14131,10 +14137,10 @@
         <v>2390009</v>
       </c>
       <c r="B240" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C240" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D240" s="2">
         <v>1</v>
@@ -14158,16 +14164,16 @@
         <v>24</v>
       </c>
       <c r="K240" t="s">
+        <v>476</v>
+      </c>
+      <c r="L240" t="s">
         <v>477</v>
       </c>
-      <c r="L240" t="s">
-        <v>478</v>
-      </c>
       <c r="M240" t="s">
         <v>26</v>
       </c>
       <c r="N240" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="Q240" t="s">
         <v>27</v>
@@ -14181,10 +14187,10 @@
         <v>2390009</v>
       </c>
       <c r="B241" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C241" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D241" s="2">
         <v>1</v>
@@ -14208,16 +14214,16 @@
         <v>24</v>
       </c>
       <c r="K241" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="L241" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="M241" t="s">
         <v>26</v>
       </c>
       <c r="N241" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="Q241" t="s">
         <v>27</v>
@@ -14231,10 +14237,10 @@
         <v>2390013</v>
       </c>
       <c r="B242" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C242" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D242" s="2">
         <v>2</v>
@@ -14243,7 +14249,7 @@
         <v>20</v>
       </c>
       <c r="F242" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G242" t="s">
         <v>22</v>
@@ -14258,13 +14264,13 @@
         <v>41</v>
       </c>
       <c r="K242" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="M242" t="s">
         <v>26</v>
       </c>
       <c r="N242" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="Q242" t="s">
         <v>27</v>
@@ -14278,10 +14284,10 @@
         <v>2390013</v>
       </c>
       <c r="B243" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C243" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D243" s="2">
         <v>2</v>
@@ -14290,7 +14296,7 @@
         <v>20</v>
       </c>
       <c r="F243" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G243" t="s">
         <v>22</v>
@@ -14305,13 +14311,13 @@
         <v>41</v>
       </c>
       <c r="K243" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="M243" t="s">
         <v>26</v>
       </c>
       <c r="N243" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="Q243" t="s">
         <v>27</v>
@@ -14325,10 +14331,10 @@
         <v>2390013</v>
       </c>
       <c r="B244" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C244" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D244" s="2">
         <v>2</v>
@@ -14337,7 +14343,7 @@
         <v>20</v>
       </c>
       <c r="F244" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G244" t="s">
         <v>22</v>
@@ -14352,13 +14358,13 @@
         <v>41</v>
       </c>
       <c r="K244" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="M244" t="s">
         <v>26</v>
       </c>
       <c r="N244" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="Q244" t="s">
         <v>27</v>

--- a/POD_2026-27_11-5-2026.xlsx
+++ b/POD_2026-27_11-5-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guillermo.vera/Desktop/POD2627/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15CF2EE8-A44E-F745-A779-CCB68D157AC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E88AE84-4E77-B641-A702-1FA7B74F8A3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3128" uniqueCount="612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3131" uniqueCount="613">
   <si>
     <t>POD_2026-27_11-5-2026</t>
   </si>
@@ -1872,6 +1872,9 @@
   </si>
   <si>
     <t>Lorenzo Martini (30)</t>
+  </si>
+  <si>
+    <t>RAZVAN IAGAR (4)</t>
   </si>
 </sst>
 </file>
@@ -3115,6 +3118,9 @@
       <c r="N18" s="6" t="s">
         <v>522</v>
       </c>
+      <c r="O18" s="6" t="s">
+        <v>258</v>
+      </c>
       <c r="Q18" t="s">
         <v>27</v>
       </c>
@@ -13469,6 +13475,9 @@
       <c r="N226" s="6" t="s">
         <v>542</v>
       </c>
+      <c r="O226" s="6" t="s">
+        <v>612</v>
+      </c>
       <c r="Q226" t="s">
         <v>27</v>
       </c>
@@ -13568,6 +13577,9 @@
       </c>
       <c r="N228" s="6" t="s">
         <v>542</v>
+      </c>
+      <c r="O228" s="6" t="s">
+        <v>612</v>
       </c>
       <c r="Q228" t="s">
         <v>27</v>

--- a/POD_2026-27_11-5-2026.xlsx
+++ b/POD_2026-27_11-5-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guillermo.vera/Desktop/POD2627/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E88AE84-4E77-B641-A702-1FA7B74F8A3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E2695C4-1069-E24A-82CF-9991040F9DA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3131" uniqueCount="613">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3129" uniqueCount="612">
   <si>
     <t>POD_2026-27_11-5-2026</t>
   </si>
@@ -1304,9 +1304,6 @@
     <t>M=&gt;(15:00-17:00)[15/09/26, 22/09/26, 29/09/26, 06/10/26, 13/10/26, 20/10/26, 27/10/26, 03/11/26, 10/11/26, 17/11/26, 24/11/26, 01/12/26], L=&gt;(17:00-19:00)[14/09/26, 21/09/26, 28/09/26, 05/10/26, 19/10/26, 26/10/26, 09/11/26, 16/11/26, 23/11/26, 30/11/26]</t>
   </si>
   <si>
-    <t>PILAR RUIZ (32)</t>
-  </si>
-  <si>
     <t>ATG1P4</t>
   </si>
   <si>
@@ -1565,9 +1562,6 @@
     <t>J=&gt;(21:00-22:00)[10/09/26, 17/09/26, 24/09/26, 01/10/26, 08/10/26, 15/10/26, 22/10/26, 29/10/26]</t>
   </si>
   <si>
-    <t>PILAR RUIZ (8)</t>
-  </si>
-  <si>
     <t>DAVID ALEJA (44)</t>
   </si>
   <si>
@@ -1862,9 +1856,6 @@
     <t>FRANCISCO JAVIER MARÍN (16)</t>
   </si>
   <si>
-    <t>Lorenzo Martini (12)</t>
-  </si>
-  <si>
     <t>Daniel Rodríguez (8)</t>
   </si>
   <si>
@@ -1875,6 +1866,12 @@
   </si>
   <si>
     <t>RAZVAN IAGAR (4)</t>
+  </si>
+  <si>
+    <t>PILAR RUIZ (40)</t>
+  </si>
+  <si>
+    <t>Lorenzo Martini (4)</t>
   </si>
 </sst>
 </file>
@@ -2358,10 +2355,10 @@
         <v>14</v>
       </c>
       <c r="O2" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>483</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>484</v>
       </c>
       <c r="Q2" s="1" t="s">
         <v>15</v>
@@ -2637,7 +2634,7 @@
         <v>26</v>
       </c>
       <c r="N8" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="Q8" t="s">
         <v>27</v>
@@ -2684,7 +2681,7 @@
         <v>26</v>
       </c>
       <c r="N9" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="Q9" t="s">
         <v>27</v>
@@ -2731,7 +2728,7 @@
         <v>26</v>
       </c>
       <c r="N10" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="Q10" t="s">
         <v>27</v>
@@ -2778,10 +2775,10 @@
         <v>26</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q11" t="s">
         <v>27</v>
@@ -2828,10 +2825,10 @@
         <v>26</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="Q12" t="s">
         <v>27</v>
@@ -2878,10 +2875,10 @@
         <v>26</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="O13" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="Q13" t="s">
         <v>27</v>
@@ -2928,7 +2925,7 @@
         <v>26</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="Q14" t="s">
         <v>27</v>
@@ -2975,7 +2972,7 @@
         <v>26</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="Q15" t="s">
         <v>27</v>
@@ -3022,7 +3019,7 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="Q16" t="s">
         <v>27</v>
@@ -3069,7 +3066,7 @@
         <v>26</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="Q17" t="s">
         <v>27</v>
@@ -3116,7 +3113,7 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>258</v>
@@ -3169,7 +3166,7 @@
         <v>26</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="Q19" t="s">
         <v>27</v>
@@ -3219,7 +3216,7 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="Q20" t="s">
         <v>27</v>
@@ -3269,7 +3266,7 @@
         <v>26</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="Q21" t="s">
         <v>27</v>
@@ -3319,7 +3316,7 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="Q22" t="s">
         <v>27</v>
@@ -3369,7 +3366,7 @@
         <v>26</v>
       </c>
       <c r="N23" s="6" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="Q23" t="s">
         <v>27</v>
@@ -3419,7 +3416,7 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="Q24" t="s">
         <v>27</v>
@@ -3469,7 +3466,7 @@
         <v>26</v>
       </c>
       <c r="N25" s="6" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="Q25" t="s">
         <v>27</v>
@@ -3519,7 +3516,7 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="Q26" t="s">
         <v>27</v>
@@ -3569,7 +3566,7 @@
         <v>26</v>
       </c>
       <c r="N27" s="6" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="Q27" t="s">
         <v>27</v>
@@ -3619,7 +3616,7 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="Q28" t="s">
         <v>27</v>
@@ -3666,7 +3663,7 @@
         <v>26</v>
       </c>
       <c r="N29" s="7" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="Q29" t="s">
         <v>27</v>
@@ -3716,7 +3713,7 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="Q30" t="s">
         <v>27</v>
@@ -3766,7 +3763,7 @@
         <v>26</v>
       </c>
       <c r="N31" s="6" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="Q31" t="s">
         <v>27</v>
@@ -3813,7 +3810,7 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="Q32" t="s">
         <v>27</v>
@@ -3860,7 +3857,7 @@
         <v>26</v>
       </c>
       <c r="N33" s="6" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="Q33" t="s">
         <v>27</v>
@@ -3910,7 +3907,7 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="Q34" t="s">
         <v>27</v>
@@ -3960,7 +3957,7 @@
         <v>26</v>
       </c>
       <c r="N35" s="6" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="Q35" t="s">
         <v>27</v>
@@ -4010,7 +4007,7 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="Q36" t="s">
         <v>27</v>
@@ -4060,7 +4057,7 @@
         <v>26</v>
       </c>
       <c r="N37" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="Q37" t="s">
         <v>27</v>
@@ -4107,7 +4104,7 @@
         <v>26</v>
       </c>
       <c r="N38" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="Q38" t="s">
         <v>27</v>
@@ -4154,7 +4151,7 @@
         <v>26</v>
       </c>
       <c r="N39" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="Q39" t="s">
         <v>27</v>
@@ -4204,7 +4201,7 @@
         <v>26</v>
       </c>
       <c r="N40" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="Q40" t="s">
         <v>27</v>
@@ -4254,7 +4251,7 @@
         <v>26</v>
       </c>
       <c r="N41" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="Q41" t="s">
         <v>27</v>
@@ -4304,7 +4301,7 @@
         <v>26</v>
       </c>
       <c r="N42" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="Q42" t="s">
         <v>27</v>
@@ -4354,10 +4351,10 @@
         <v>26</v>
       </c>
       <c r="N43" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="O43" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="Q43" t="s">
         <v>27</v>
@@ -4410,7 +4407,7 @@
         <v>176</v>
       </c>
       <c r="O44" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="Q44" t="s">
         <v>27</v>
@@ -4460,7 +4457,7 @@
         <v>26</v>
       </c>
       <c r="N45" s="6" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="Q45" t="s">
         <v>27</v>
@@ -4510,7 +4507,7 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q46" t="s">
         <v>27</v>
@@ -4560,7 +4557,7 @@
         <v>26</v>
       </c>
       <c r="N47" s="6" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q47" t="s">
         <v>27</v>
@@ -4610,7 +4607,7 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="Q48" t="s">
         <v>27</v>
@@ -4660,7 +4657,7 @@
         <v>26</v>
       </c>
       <c r="N49" s="6" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="Q49" t="s">
         <v>27</v>
@@ -4710,7 +4707,7 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="Q50" t="s">
         <v>27</v>
@@ -4760,7 +4757,7 @@
         <v>26</v>
       </c>
       <c r="N51" s="6" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="Q51" t="s">
         <v>27</v>
@@ -4810,7 +4807,7 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q52" t="s">
         <v>27</v>
@@ -4860,7 +4857,7 @@
         <v>26</v>
       </c>
       <c r="N53" s="6" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q53" t="s">
         <v>27</v>
@@ -4910,7 +4907,7 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="Q54" t="s">
         <v>27</v>
@@ -4960,7 +4957,7 @@
         <v>26</v>
       </c>
       <c r="N55" s="6" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="Q55" t="s">
         <v>27</v>
@@ -5010,7 +5007,7 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="Q56" t="s">
         <v>27</v>
@@ -5060,7 +5057,7 @@
         <v>26</v>
       </c>
       <c r="N57" s="6" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="Q57" t="s">
         <v>27</v>
@@ -5101,7 +5098,7 @@
         <v>41</v>
       </c>
       <c r="K58" s="6" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="L58" t="s">
         <v>130</v>
@@ -5110,7 +5107,7 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="Q58" t="s">
         <v>27</v>
@@ -5151,7 +5148,7 @@
         <v>41</v>
       </c>
       <c r="K59" s="6" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="L59" t="s">
         <v>130</v>
@@ -5160,7 +5157,7 @@
         <v>26</v>
       </c>
       <c r="N59" s="6" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="Q59" t="s">
         <v>27</v>
@@ -5210,7 +5207,7 @@
         <v>26</v>
       </c>
       <c r="N60" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="Q60" t="s">
         <v>27</v>
@@ -5251,7 +5248,7 @@
         <v>41</v>
       </c>
       <c r="K61" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="L61" t="s">
         <v>133</v>
@@ -5260,7 +5257,7 @@
         <v>26</v>
       </c>
       <c r="N61" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="Q61" t="s">
         <v>27</v>
@@ -5301,7 +5298,7 @@
         <v>41</v>
       </c>
       <c r="K62" s="6" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="L62" t="s">
         <v>133</v>
@@ -5310,7 +5307,7 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="Q62" t="s">
         <v>27</v>
@@ -5360,10 +5357,10 @@
         <v>26</v>
       </c>
       <c r="N63" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="O63" s="6" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="Q63" t="s">
         <v>27</v>
@@ -5413,10 +5410,10 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="Q64" t="s">
         <v>27</v>
@@ -5466,7 +5463,7 @@
         <v>26</v>
       </c>
       <c r="N65" s="6" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="Q65" t="s">
         <v>27</v>
@@ -5507,7 +5504,7 @@
         <v>41</v>
       </c>
       <c r="K66" s="6" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="L66" t="s">
         <v>142</v>
@@ -5516,7 +5513,7 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="Q66" t="s">
         <v>27</v>
@@ -5557,7 +5554,7 @@
         <v>41</v>
       </c>
       <c r="K67" s="6" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="L67" t="s">
         <v>142</v>
@@ -5566,7 +5563,7 @@
         <v>26</v>
       </c>
       <c r="N67" s="6" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="Q67" t="s">
         <v>27</v>
@@ -5613,7 +5610,7 @@
         <v>26</v>
       </c>
       <c r="N68" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="Q68" t="s">
         <v>27</v>
@@ -5654,13 +5651,13 @@
         <v>24</v>
       </c>
       <c r="K69" s="6" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="M69" t="s">
         <v>26</v>
       </c>
       <c r="N69" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="Q69" t="s">
         <v>27</v>
@@ -5701,13 +5698,13 @@
         <v>24</v>
       </c>
       <c r="K70" s="6" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="M70" t="s">
         <v>26</v>
       </c>
       <c r="N70" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="Q70" t="s">
         <v>27</v>
@@ -5754,13 +5751,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="5" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="O71" s="5" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="P71" s="6" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="Q71" t="s">
         <v>27</v>
@@ -5948,10 +5945,10 @@
         <v>26</v>
       </c>
       <c r="N75" s="6" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="O75" s="6" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="Q75" t="s">
         <v>27</v>
@@ -6048,10 +6045,10 @@
         <v>26</v>
       </c>
       <c r="N77" s="6" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="O77" s="6" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="Q77" t="s">
         <v>27</v>
@@ -6101,10 +6098,10 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="Q78" t="s">
         <v>27</v>
@@ -6154,10 +6151,10 @@
         <v>26</v>
       </c>
       <c r="N79" s="5" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="O79" s="5" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="Q79" t="s">
         <v>27</v>
@@ -6210,7 +6207,7 @@
         <v>176</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="Q80" t="s">
         <v>27</v>
@@ -6260,10 +6257,10 @@
         <v>26</v>
       </c>
       <c r="N81" s="6" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="O81" s="6" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="Q81" t="s">
         <v>27</v>
@@ -6313,10 +6310,10 @@
         <v>26</v>
       </c>
       <c r="N82" s="5" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="O82" s="5" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="Q82" t="s">
         <v>27</v>
@@ -6366,10 +6363,10 @@
         <v>26</v>
       </c>
       <c r="N83" s="6" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="O83" s="6" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="Q83" t="s">
         <v>27</v>
@@ -6692,10 +6689,10 @@
         <v>26</v>
       </c>
       <c r="N90" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="O90" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="Q90" t="s">
         <v>27</v>
@@ -6742,10 +6739,10 @@
         <v>26</v>
       </c>
       <c r="N91" s="5" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="O91" s="5" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="Q91" t="s">
         <v>27</v>
@@ -7021,10 +7018,10 @@
         <v>26</v>
       </c>
       <c r="N97" s="5" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="O97" s="5" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="Q97" t="s">
         <v>27</v>
@@ -7071,10 +7068,10 @@
         <v>210</v>
       </c>
       <c r="N98" s="5" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="O98" s="5" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="Q98" t="s">
         <v>27</v>
@@ -7168,7 +7165,7 @@
         <v>210</v>
       </c>
       <c r="N100" s="5" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="O100" s="3"/>
       <c r="Q100" t="s">
@@ -7269,7 +7266,7 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="Q102" t="s">
         <v>27</v>
@@ -7370,7 +7367,7 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="Q104" t="s">
         <v>27</v>
@@ -7521,7 +7518,7 @@
         <v>26</v>
       </c>
       <c r="N107" s="3" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="Q107" t="s">
         <v>27</v>
@@ -7875,10 +7872,10 @@
         <v>26</v>
       </c>
       <c r="N114" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="O114" s="5" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="Q114" t="s">
         <v>27</v>
@@ -8076,7 +8073,7 @@
         <v>26</v>
       </c>
       <c r="N118" s="3" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="Q118" t="s">
         <v>27</v>
@@ -8123,7 +8120,7 @@
         <v>26</v>
       </c>
       <c r="N119" s="3" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="Q119" t="s">
         <v>27</v>
@@ -8214,7 +8211,7 @@
         <v>26</v>
       </c>
       <c r="N121" s="6" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="Q121" t="s">
         <v>27</v>
@@ -8264,7 +8261,7 @@
         <v>26</v>
       </c>
       <c r="N122" s="3" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="Q122" t="s">
         <v>27</v>
@@ -8314,7 +8311,7 @@
         <v>26</v>
       </c>
       <c r="N123" s="3" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="Q123" t="s">
         <v>27</v>
@@ -8364,7 +8361,7 @@
         <v>26</v>
       </c>
       <c r="N124" s="3" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="Q124" t="s">
         <v>27</v>
@@ -8414,7 +8411,7 @@
         <v>26</v>
       </c>
       <c r="N125" s="3" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="Q125" t="s">
         <v>27</v>
@@ -8464,7 +8461,7 @@
         <v>26</v>
       </c>
       <c r="N126" s="3" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="Q126" t="s">
         <v>27</v>
@@ -8514,7 +8511,7 @@
         <v>26</v>
       </c>
       <c r="N127" s="3" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="Q127" t="s">
         <v>27</v>
@@ -8564,7 +8561,7 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="Q128" t="s">
         <v>27</v>
@@ -8614,7 +8611,7 @@
         <v>26</v>
       </c>
       <c r="N129" s="6" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="Q129" t="s">
         <v>27</v>
@@ -8664,7 +8661,7 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="Q130" t="s">
         <v>27</v>
@@ -8714,7 +8711,7 @@
         <v>26</v>
       </c>
       <c r="N131" s="6" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="Q131" t="s">
         <v>27</v>
@@ -8764,7 +8761,7 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="Q132" t="s">
         <v>27</v>
@@ -8814,7 +8811,7 @@
         <v>26</v>
       </c>
       <c r="N133" s="6" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="Q133" t="s">
         <v>27</v>
@@ -9014,7 +9011,7 @@
         <v>26</v>
       </c>
       <c r="N137" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="Q137" t="s">
         <v>27</v>
@@ -9064,7 +9061,7 @@
         <v>26</v>
       </c>
       <c r="N138" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="Q138" t="s">
         <v>27</v>
@@ -9114,7 +9111,7 @@
         <v>26</v>
       </c>
       <c r="N139" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="Q139" t="s">
         <v>27</v>
@@ -9316,7 +9313,7 @@
         <v>26</v>
       </c>
       <c r="N143" s="6" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="Q143" t="s">
         <v>27</v>
@@ -9366,7 +9363,7 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="Q144" t="s">
         <v>27</v>
@@ -9416,7 +9413,7 @@
         <v>26</v>
       </c>
       <c r="N145" s="6" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="Q145" t="s">
         <v>27</v>
@@ -9466,7 +9463,7 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="Q146" t="s">
         <v>27</v>
@@ -9516,7 +9513,7 @@
         <v>26</v>
       </c>
       <c r="N147" s="6" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="Q147" t="s">
         <v>27</v>
@@ -9563,7 +9560,7 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="Q148" t="s">
         <v>27</v>
@@ -9613,10 +9610,10 @@
         <v>26</v>
       </c>
       <c r="N149" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="O149" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="Q149" t="s">
         <v>27</v>
@@ -9666,10 +9663,10 @@
         <v>26</v>
       </c>
       <c r="N150" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="O150" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="Q150" t="s">
         <v>27</v>
@@ -9719,10 +9716,10 @@
         <v>26</v>
       </c>
       <c r="N151" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="O151" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="Q151" t="s">
         <v>27</v>
@@ -9772,7 +9769,7 @@
         <v>26</v>
       </c>
       <c r="N152" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="Q152" t="s">
         <v>27</v>
@@ -9822,7 +9819,7 @@
         <v>26</v>
       </c>
       <c r="N153" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="Q153" t="s">
         <v>27</v>
@@ -9872,7 +9869,7 @@
         <v>26</v>
       </c>
       <c r="N154" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="Q154" t="s">
         <v>27</v>
@@ -9922,7 +9919,7 @@
         <v>26</v>
       </c>
       <c r="N155" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="Q155" t="s">
         <v>27</v>
@@ -9972,7 +9969,7 @@
         <v>26</v>
       </c>
       <c r="N156" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="Q156" t="s">
         <v>27</v>
@@ -10019,7 +10016,7 @@
         <v>26</v>
       </c>
       <c r="N157" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="Q157" t="s">
         <v>27</v>
@@ -10069,7 +10066,7 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="Q158" t="s">
         <v>27</v>
@@ -10119,7 +10116,7 @@
         <v>26</v>
       </c>
       <c r="N159" s="6" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="Q159" t="s">
         <v>27</v>
@@ -10169,7 +10166,7 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="Q160" t="s">
         <v>27</v>
@@ -10219,7 +10216,7 @@
         <v>26</v>
       </c>
       <c r="N161" s="6" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="Q161" t="s">
         <v>27</v>
@@ -10269,7 +10266,7 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="Q162" t="s">
         <v>27</v>
@@ -10319,7 +10316,7 @@
         <v>26</v>
       </c>
       <c r="N163" s="6" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="Q163" t="s">
         <v>27</v>
@@ -10516,7 +10513,7 @@
         <v>26</v>
       </c>
       <c r="N167" s="6" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="Q167" t="s">
         <v>27</v>
@@ -10566,7 +10563,7 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="Q168" t="s">
         <v>27</v>
@@ -10616,7 +10613,7 @@
         <v>26</v>
       </c>
       <c r="N169" s="6" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="Q169" t="s">
         <v>27</v>
@@ -10666,7 +10663,7 @@
         <v>26</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="Q170" t="s">
         <v>27</v>
@@ -10716,7 +10713,7 @@
         <v>26</v>
       </c>
       <c r="N171" s="6" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="Q171" t="s">
         <v>27</v>
@@ -10766,7 +10763,7 @@
         <v>26</v>
       </c>
       <c r="N172" s="6" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="Q172" t="s">
         <v>27</v>
@@ -10966,7 +10963,7 @@
         <v>26</v>
       </c>
       <c r="N176" s="6" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="Q176" t="s">
         <v>27</v>
@@ -11016,7 +11013,7 @@
         <v>26</v>
       </c>
       <c r="N177" s="6" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="Q177" t="s">
         <v>27</v>
@@ -11113,7 +11110,7 @@
         <v>26</v>
       </c>
       <c r="N179" s="6" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="Q179" t="s">
         <v>27</v>
@@ -11460,7 +11457,7 @@
         <v>387</v>
       </c>
       <c r="O186" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="Q186" t="s">
         <v>27</v>
@@ -11513,7 +11510,7 @@
         <v>389</v>
       </c>
       <c r="O187" s="6" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="Q187" t="s">
         <v>27</v>
@@ -11566,7 +11563,7 @@
         <v>389</v>
       </c>
       <c r="O188" s="6" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="Q188" t="s">
         <v>27</v>
@@ -11707,7 +11704,7 @@
         <v>26</v>
       </c>
       <c r="N191" s="5" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="O191" s="3"/>
       <c r="Q191" t="s">
@@ -11911,10 +11908,10 @@
         <v>26</v>
       </c>
       <c r="N195" s="8" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="O195" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="Q195" t="s">
         <v>27</v>
@@ -11964,10 +11961,10 @@
         <v>26</v>
       </c>
       <c r="N196" s="8" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="O196" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="Q196" t="s">
         <v>27</v>
@@ -12017,10 +12014,10 @@
         <v>26</v>
       </c>
       <c r="N197" s="8" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="O197" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="Q197" t="s">
         <v>27</v>
@@ -12067,7 +12064,7 @@
         <v>26</v>
       </c>
       <c r="N198" s="6" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="Q198" t="s">
         <v>27</v>
@@ -12114,7 +12111,7 @@
         <v>26</v>
       </c>
       <c r="N199" s="6" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="Q199" t="s">
         <v>27</v>
@@ -12161,7 +12158,7 @@
         <v>26</v>
       </c>
       <c r="N200" s="6" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="Q200" t="s">
         <v>27</v>
@@ -12507,11 +12504,11 @@
       <c r="M207" t="s">
         <v>26</v>
       </c>
-      <c r="N207" t="s">
-        <v>422</v>
+      <c r="N207" s="6" t="s">
+        <v>610</v>
       </c>
       <c r="O207" s="6" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="Q207" t="s">
         <v>27</v>
@@ -12546,22 +12543,19 @@
         <v>32</v>
       </c>
       <c r="I208" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="J208" t="s">
         <v>24</v>
       </c>
       <c r="K208" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="M208" t="s">
         <v>26</v>
       </c>
-      <c r="N208" t="s">
-        <v>509</v>
-      </c>
-      <c r="O208" t="s">
-        <v>586</v>
+      <c r="N208" s="6" t="s">
+        <v>584</v>
       </c>
       <c r="Q208" t="s">
         <v>27</v>
@@ -12596,22 +12590,19 @@
         <v>32</v>
       </c>
       <c r="I209" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="J209" t="s">
         <v>24</v>
       </c>
       <c r="K209" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="M209" t="s">
         <v>26</v>
       </c>
-      <c r="N209" t="s">
-        <v>509</v>
-      </c>
-      <c r="O209" t="s">
-        <v>586</v>
+      <c r="N209" s="6" t="s">
+        <v>584</v>
       </c>
       <c r="Q209" t="s">
         <v>27</v>
@@ -12625,7 +12616,7 @@
         <v>2405001</v>
       </c>
       <c r="B210" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C210" t="s">
         <v>149</v>
@@ -12652,16 +12643,16 @@
         <v>41</v>
       </c>
       <c r="K210" t="s">
+        <v>427</v>
+      </c>
+      <c r="L210" t="s">
         <v>428</v>
       </c>
-      <c r="L210" t="s">
-        <v>429</v>
-      </c>
       <c r="M210" t="s">
         <v>26</v>
       </c>
       <c r="N210" s="6" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="Q210" t="s">
         <v>27</v>
@@ -12675,7 +12666,7 @@
         <v>2405001</v>
       </c>
       <c r="B211" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C211" t="s">
         <v>149</v>
@@ -12702,16 +12693,16 @@
         <v>41</v>
       </c>
       <c r="K211" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="L211" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="M211" t="s">
         <v>26</v>
       </c>
       <c r="N211" s="6" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="Q211" t="s">
         <v>27</v>
@@ -12725,7 +12716,7 @@
         <v>2405001</v>
       </c>
       <c r="B212" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C212" t="s">
         <v>149</v>
@@ -12752,16 +12743,16 @@
         <v>41</v>
       </c>
       <c r="K212" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="L212" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="M212" t="s">
         <v>26</v>
       </c>
       <c r="N212" s="6" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="Q212" t="s">
         <v>27</v>
@@ -12775,7 +12766,7 @@
         <v>2405006</v>
       </c>
       <c r="B213" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C213" t="s">
         <v>149</v>
@@ -12802,19 +12793,19 @@
         <v>41</v>
       </c>
       <c r="K213" t="s">
+        <v>431</v>
+      </c>
+      <c r="L213" t="s">
         <v>432</v>
       </c>
-      <c r="L213" t="s">
-        <v>433</v>
-      </c>
       <c r="M213" t="s">
         <v>26</v>
       </c>
       <c r="N213" s="6" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="O213" s="6" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="Q213" t="s">
         <v>27</v>
@@ -12828,7 +12819,7 @@
         <v>2405006</v>
       </c>
       <c r="B214" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C214" t="s">
         <v>149</v>
@@ -12855,19 +12846,19 @@
         <v>41</v>
       </c>
       <c r="K214" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="L214" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="M214" t="s">
         <v>26</v>
       </c>
       <c r="N214" s="6" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="O214" s="6" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="Q214" t="s">
         <v>27</v>
@@ -12881,7 +12872,7 @@
         <v>2405006</v>
       </c>
       <c r="B215" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C215" t="s">
         <v>149</v>
@@ -12908,19 +12899,19 @@
         <v>41</v>
       </c>
       <c r="K215" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="L215" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="M215" t="s">
         <v>26</v>
       </c>
       <c r="N215" s="6" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="O215" s="6" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="Q215" t="s">
         <v>27</v>
@@ -12934,7 +12925,7 @@
         <v>2405015</v>
       </c>
       <c r="B216" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C216" t="s">
         <v>149</v>
@@ -12961,16 +12952,16 @@
         <v>24</v>
       </c>
       <c r="K216" t="s">
+        <v>435</v>
+      </c>
+      <c r="L216" t="s">
         <v>436</v>
       </c>
-      <c r="L216" t="s">
+      <c r="M216" t="s">
+        <v>26</v>
+      </c>
+      <c r="N216" t="s">
         <v>437</v>
-      </c>
-      <c r="M216" t="s">
-        <v>26</v>
-      </c>
-      <c r="N216" t="s">
-        <v>438</v>
       </c>
       <c r="Q216" t="s">
         <v>27</v>
@@ -12984,7 +12975,7 @@
         <v>2405015</v>
       </c>
       <c r="B217" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C217" t="s">
         <v>149</v>
@@ -13011,16 +13002,16 @@
         <v>24</v>
       </c>
       <c r="K217" t="s">
+        <v>438</v>
+      </c>
+      <c r="L217" t="s">
+        <v>436</v>
+      </c>
+      <c r="M217" t="s">
+        <v>26</v>
+      </c>
+      <c r="N217" t="s">
         <v>439</v>
-      </c>
-      <c r="L217" t="s">
-        <v>437</v>
-      </c>
-      <c r="M217" t="s">
-        <v>26</v>
-      </c>
-      <c r="N217" t="s">
-        <v>440</v>
       </c>
       <c r="Q217" t="s">
         <v>27</v>
@@ -13034,7 +13025,7 @@
         <v>2405015</v>
       </c>
       <c r="B218" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C218" t="s">
         <v>149</v>
@@ -13061,13 +13052,13 @@
         <v>24</v>
       </c>
       <c r="K218" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="M218" t="s">
         <v>26</v>
       </c>
       <c r="N218" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="Q218" t="s">
         <v>27</v>
@@ -13081,7 +13072,7 @@
         <v>2406004</v>
       </c>
       <c r="B219" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C219" t="s">
         <v>149</v>
@@ -13108,16 +13099,16 @@
         <v>24</v>
       </c>
       <c r="K219" t="s">
+        <v>442</v>
+      </c>
+      <c r="L219" t="s">
         <v>443</v>
       </c>
-      <c r="L219" t="s">
-        <v>444</v>
-      </c>
       <c r="M219" t="s">
         <v>26</v>
       </c>
       <c r="N219" s="6" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="Q219" t="s">
         <v>27</v>
@@ -13131,7 +13122,7 @@
         <v>2406004</v>
       </c>
       <c r="B220" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C220" t="s">
         <v>149</v>
@@ -13158,16 +13149,16 @@
         <v>24</v>
       </c>
       <c r="K220" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="L220" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="M220" t="s">
         <v>26</v>
       </c>
       <c r="N220" s="6" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="Q220" t="s">
         <v>27</v>
@@ -13181,7 +13172,7 @@
         <v>2406004</v>
       </c>
       <c r="B221" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C221" t="s">
         <v>149</v>
@@ -13202,25 +13193,25 @@
         <v>8</v>
       </c>
       <c r="I221" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="J221" t="s">
         <v>24</v>
       </c>
       <c r="K221" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="L221" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="M221" t="s">
         <v>26</v>
       </c>
       <c r="N221" s="6" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="O221" s="6" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="Q221" t="s">
         <v>27</v>
@@ -13234,7 +13225,7 @@
         <v>2406004</v>
       </c>
       <c r="B222" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C222" t="s">
         <v>149</v>
@@ -13261,16 +13252,16 @@
         <v>24</v>
       </c>
       <c r="K222" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="L222" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="M222" t="s">
         <v>26</v>
       </c>
       <c r="N222" s="6" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="Q222" t="s">
         <v>27</v>
@@ -13284,7 +13275,7 @@
         <v>2406004</v>
       </c>
       <c r="B223" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C223" t="s">
         <v>149</v>
@@ -13305,25 +13296,25 @@
         <v>8</v>
       </c>
       <c r="I223" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="J223" t="s">
         <v>24</v>
       </c>
       <c r="K223" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="L223" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="M223" t="s">
         <v>26</v>
       </c>
       <c r="N223" s="6" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="O223" s="6" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="Q223" t="s">
         <v>27</v>
@@ -13337,7 +13328,7 @@
         <v>2406009</v>
       </c>
       <c r="B224" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C224" t="s">
         <v>149</v>
@@ -13364,16 +13355,16 @@
         <v>24</v>
       </c>
       <c r="K224" t="s">
+        <v>446</v>
+      </c>
+      <c r="L224" t="s">
         <v>447</v>
       </c>
-      <c r="L224" t="s">
-        <v>448</v>
-      </c>
       <c r="M224" t="s">
         <v>26</v>
       </c>
       <c r="N224" s="6" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="Q224" t="s">
         <v>27</v>
@@ -13387,7 +13378,7 @@
         <v>2406009</v>
       </c>
       <c r="B225" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C225" t="s">
         <v>149</v>
@@ -13414,16 +13405,16 @@
         <v>24</v>
       </c>
       <c r="K225" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="L225" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="M225" t="s">
         <v>26</v>
       </c>
       <c r="N225" s="6" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="Q225" t="s">
         <v>27</v>
@@ -13437,7 +13428,7 @@
         <v>2406009</v>
       </c>
       <c r="B226" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C226" t="s">
         <v>149</v>
@@ -13458,25 +13449,25 @@
         <v>8</v>
       </c>
       <c r="I226" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="J226" t="s">
         <v>24</v>
       </c>
       <c r="K226" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="L226" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="M226" t="s">
         <v>26</v>
       </c>
       <c r="N226" s="6" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="O226" s="6" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="Q226" t="s">
         <v>27</v>
@@ -13490,7 +13481,7 @@
         <v>2406009</v>
       </c>
       <c r="B227" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C227" t="s">
         <v>149</v>
@@ -13517,16 +13508,16 @@
         <v>24</v>
       </c>
       <c r="K227" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="L227" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="M227" t="s">
         <v>26</v>
       </c>
       <c r="N227" s="6" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="Q227" t="s">
         <v>27</v>
@@ -13540,7 +13531,7 @@
         <v>2406009</v>
       </c>
       <c r="B228" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C228" t="s">
         <v>149</v>
@@ -13561,25 +13552,25 @@
         <v>8</v>
       </c>
       <c r="I228" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="J228" t="s">
         <v>24</v>
       </c>
       <c r="K228" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="L228" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="M228" t="s">
         <v>26</v>
       </c>
       <c r="N228" s="6" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="O228" s="6" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="Q228" t="s">
         <v>27</v>
@@ -13593,7 +13584,7 @@
         <v>2406012</v>
       </c>
       <c r="B229" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C229" t="s">
         <v>149</v>
@@ -13605,7 +13596,7 @@
         <v>20</v>
       </c>
       <c r="F229" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="G229" t="s">
         <v>39</v>
@@ -13620,16 +13611,16 @@
         <v>41</v>
       </c>
       <c r="K229" t="s">
+        <v>453</v>
+      </c>
+      <c r="L229" t="s">
         <v>454</v>
       </c>
-      <c r="L229" t="s">
-        <v>455</v>
-      </c>
       <c r="M229" t="s">
         <v>26</v>
       </c>
       <c r="N229" s="6" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="Q229" t="s">
         <v>27</v>
@@ -13643,7 +13634,7 @@
         <v>2406012</v>
       </c>
       <c r="B230" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C230" t="s">
         <v>149</v>
@@ -13655,7 +13646,7 @@
         <v>20</v>
       </c>
       <c r="F230" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="G230" t="s">
         <v>39</v>
@@ -13670,19 +13661,19 @@
         <v>41</v>
       </c>
       <c r="K230" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L230" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="M230" t="s">
         <v>26</v>
       </c>
       <c r="N230" s="6" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="O230" s="6" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="Q230" t="s">
         <v>27</v>
@@ -13696,7 +13687,7 @@
         <v>2406012</v>
       </c>
       <c r="B231" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C231" t="s">
         <v>149</v>
@@ -13708,7 +13699,7 @@
         <v>20</v>
       </c>
       <c r="F231" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="G231" t="s">
         <v>39</v>
@@ -13723,19 +13714,19 @@
         <v>41</v>
       </c>
       <c r="K231" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="L231" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="M231" t="s">
         <v>26</v>
       </c>
       <c r="N231" s="6" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="O231" s="6" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="Q231" t="s">
         <v>27</v>
@@ -13749,10 +13740,10 @@
         <v>2059001</v>
       </c>
       <c r="B232" t="s">
+        <v>457</v>
+      </c>
+      <c r="C232" t="s">
         <v>458</v>
-      </c>
-      <c r="C232" t="s">
-        <v>459</v>
       </c>
       <c r="D232" s="2">
         <v>1</v>
@@ -13776,16 +13767,16 @@
         <v>41</v>
       </c>
       <c r="K232" t="s">
+        <v>459</v>
+      </c>
+      <c r="L232" t="s">
         <v>460</v>
       </c>
-      <c r="L232" t="s">
-        <v>461</v>
-      </c>
       <c r="M232" t="s">
         <v>26</v>
       </c>
       <c r="N232" s="6" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="Q232" t="s">
         <v>27</v>
@@ -13799,10 +13790,10 @@
         <v>2059002</v>
       </c>
       <c r="B233" t="s">
+        <v>457</v>
+      </c>
+      <c r="C233" t="s">
         <v>458</v>
-      </c>
-      <c r="C233" t="s">
-        <v>459</v>
       </c>
       <c r="D233" s="2">
         <v>1</v>
@@ -13826,19 +13817,19 @@
         <v>41</v>
       </c>
       <c r="K233" t="s">
+        <v>461</v>
+      </c>
+      <c r="L233" t="s">
         <v>462</v>
       </c>
-      <c r="L233" t="s">
-        <v>463</v>
-      </c>
       <c r="M233" t="s">
         <v>26</v>
       </c>
       <c r="N233" s="6" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="O233" s="6" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="Q233" t="s">
         <v>27</v>
@@ -13852,10 +13843,10 @@
         <v>2059006</v>
       </c>
       <c r="B234" t="s">
+        <v>457</v>
+      </c>
+      <c r="C234" t="s">
         <v>458</v>
-      </c>
-      <c r="C234" t="s">
-        <v>459</v>
       </c>
       <c r="D234" s="2">
         <v>1</v>
@@ -13879,16 +13870,16 @@
         <v>41</v>
       </c>
       <c r="K234" t="s">
+        <v>463</v>
+      </c>
+      <c r="L234" t="s">
         <v>464</v>
       </c>
-      <c r="L234" t="s">
-        <v>465</v>
-      </c>
       <c r="M234" t="s">
         <v>26</v>
       </c>
       <c r="N234" s="6" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="Q234" t="s">
         <v>27</v>
@@ -13902,10 +13893,10 @@
         <v>2140011</v>
       </c>
       <c r="B235" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C235" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D235" s="2">
         <v>2</v>
@@ -13932,7 +13923,7 @@
         <v>151</v>
       </c>
       <c r="L235" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="M235" t="s">
         <v>26</v>
@@ -13949,10 +13940,10 @@
         <v>2390004</v>
       </c>
       <c r="B236" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C236" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D236" s="2">
         <v>1</v>
@@ -13976,16 +13967,16 @@
         <v>24</v>
       </c>
       <c r="K236" t="s">
+        <v>468</v>
+      </c>
+      <c r="L236" t="s">
         <v>469</v>
       </c>
-      <c r="L236" t="s">
-        <v>470</v>
-      </c>
       <c r="M236" t="s">
         <v>26</v>
       </c>
       <c r="N236" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="Q236" t="s">
         <v>27</v>
@@ -13999,10 +13990,10 @@
         <v>2390004</v>
       </c>
       <c r="B237" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C237" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D237" s="2">
         <v>1</v>
@@ -14026,16 +14017,16 @@
         <v>24</v>
       </c>
       <c r="K237" t="s">
+        <v>470</v>
+      </c>
+      <c r="L237" t="s">
         <v>471</v>
       </c>
-      <c r="L237" t="s">
-        <v>472</v>
-      </c>
       <c r="M237" t="s">
         <v>26</v>
       </c>
       <c r="N237" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="Q237" t="s">
         <v>27</v>
@@ -14049,10 +14040,10 @@
         <v>2390004</v>
       </c>
       <c r="B238" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C238" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D238" s="2">
         <v>1</v>
@@ -14076,16 +14067,16 @@
         <v>24</v>
       </c>
       <c r="K238" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L238" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="M238" t="s">
         <v>26</v>
       </c>
       <c r="N238" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="Q238" t="s">
         <v>27</v>
@@ -14099,10 +14090,10 @@
         <v>2390009</v>
       </c>
       <c r="B239" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C239" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D239" s="2">
         <v>1</v>
@@ -14126,16 +14117,16 @@
         <v>24</v>
       </c>
       <c r="K239" t="s">
+        <v>473</v>
+      </c>
+      <c r="L239" t="s">
         <v>474</v>
       </c>
-      <c r="L239" t="s">
-        <v>475</v>
-      </c>
       <c r="M239" t="s">
         <v>26</v>
       </c>
       <c r="N239" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="Q239" t="s">
         <v>27</v>
@@ -14149,10 +14140,10 @@
         <v>2390009</v>
       </c>
       <c r="B240" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C240" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D240" s="2">
         <v>1</v>
@@ -14176,16 +14167,16 @@
         <v>24</v>
       </c>
       <c r="K240" t="s">
+        <v>475</v>
+      </c>
+      <c r="L240" t="s">
         <v>476</v>
       </c>
-      <c r="L240" t="s">
-        <v>477</v>
-      </c>
       <c r="M240" t="s">
         <v>26</v>
       </c>
       <c r="N240" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="Q240" t="s">
         <v>27</v>
@@ -14199,10 +14190,10 @@
         <v>2390009</v>
       </c>
       <c r="B241" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C241" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D241" s="2">
         <v>1</v>
@@ -14226,16 +14217,16 @@
         <v>24</v>
       </c>
       <c r="K241" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="L241" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M241" t="s">
         <v>26</v>
       </c>
       <c r="N241" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="Q241" t="s">
         <v>27</v>
@@ -14249,10 +14240,10 @@
         <v>2390013</v>
       </c>
       <c r="B242" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C242" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D242" s="2">
         <v>2</v>
@@ -14276,13 +14267,13 @@
         <v>41</v>
       </c>
       <c r="K242" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="M242" t="s">
         <v>26</v>
       </c>
       <c r="N242" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="Q242" t="s">
         <v>27</v>
@@ -14296,10 +14287,10 @@
         <v>2390013</v>
       </c>
       <c r="B243" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C243" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D243" s="2">
         <v>2</v>
@@ -14323,13 +14314,13 @@
         <v>41</v>
       </c>
       <c r="K243" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="M243" t="s">
         <v>26</v>
       </c>
       <c r="N243" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="Q243" t="s">
         <v>27</v>
@@ -14343,10 +14334,10 @@
         <v>2390013</v>
       </c>
       <c r="B244" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C244" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D244" s="2">
         <v>2</v>
@@ -14370,13 +14361,13 @@
         <v>41</v>
       </c>
       <c r="K244" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="M244" t="s">
         <v>26</v>
       </c>
       <c r="N244" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="Q244" t="s">
         <v>27</v>

--- a/POD_2026-27_11-5-2026.xlsx
+++ b/POD_2026-27_11-5-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guillermo.vera/Desktop/POD2627/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E2695C4-1069-E24A-82CF-9991040F9DA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{111AF960-C394-A74E-864D-0D16C17878E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3129" uniqueCount="612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3130" uniqueCount="613">
   <si>
     <t>POD_2026-27_11-5-2026</t>
   </si>
@@ -1872,6 +1872,9 @@
   </si>
   <si>
     <t>Lorenzo Martini (4)</t>
+  </si>
+  <si>
+    <t>ÁNGEL PÉREZ (20)</t>
   </si>
 </sst>
 </file>
@@ -6838,6 +6841,9 @@
       <c r="N93" s="6" t="s">
         <v>176</v>
       </c>
+      <c r="O93" s="6" t="s">
+        <v>612</v>
+      </c>
       <c r="Q93" t="s">
         <v>27</v>
       </c>

--- a/POD_2026-27_11-5-2026.xlsx
+++ b/POD_2026-27_11-5-2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guillermo.vera/Desktop/POD2627/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guillermo.vera\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{111AF960-C394-A74E-864D-0D16C17878E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8BE26F4-75E2-4031-8C00-7AC115C7C137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="POD" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3130" uniqueCount="613">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3126" uniqueCount="614">
   <si>
     <t>POD_2026-27_11-5-2026</t>
   </si>
@@ -1679,9 +1679,6 @@
     <t>Enrique Benito Matías (44)</t>
   </si>
   <si>
-    <t>Enrique Benito Matías (16)</t>
-  </si>
-  <si>
     <t>Enrique Benito Matías (24)</t>
   </si>
   <si>
@@ -1875,6 +1872,12 @@
   </si>
   <si>
     <t>ÁNGEL PÉREZ (20)</t>
+  </si>
+  <si>
+    <t>ALEJANDRO GARCÍA DEL AMO (24)</t>
+  </si>
+  <si>
+    <t>ALEJANDRO GARCÍA DEL AMO (6)</t>
   </si>
 </sst>
 </file>
@@ -1971,9 +1974,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2011,7 +2014,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2117,7 +2120,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2259,7 +2262,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2268,30 +2271,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S252"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="71.33203125" customWidth="1"/>
+    <col min="2" max="2" width="71.28515625" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" customWidth="1"/>
-    <col min="5" max="5" width="20.1640625" customWidth="1"/>
-    <col min="6" max="6" width="64.1640625" customWidth="1"/>
-    <col min="7" max="7" width="20.83203125" customWidth="1"/>
-    <col min="8" max="8" width="6.5" customWidth="1"/>
-    <col min="9" max="9" width="7.83203125" customWidth="1"/>
-    <col min="10" max="10" width="6.5" customWidth="1"/>
-    <col min="11" max="11" width="107.1640625" customWidth="1"/>
-    <col min="12" max="12" width="53.6640625" customWidth="1"/>
-    <col min="13" max="13" width="12.6640625" customWidth="1"/>
-    <col min="14" max="14" width="36.5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="36.5" customWidth="1"/>
-    <col min="16" max="16" width="20.83203125" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" customWidth="1"/>
+    <col min="5" max="5" width="20.140625" customWidth="1"/>
+    <col min="6" max="6" width="64.140625" customWidth="1"/>
+    <col min="7" max="7" width="20.85546875" customWidth="1"/>
+    <col min="8" max="8" width="6.42578125" customWidth="1"/>
+    <col min="9" max="9" width="7.85546875" customWidth="1"/>
+    <col min="10" max="10" width="6.42578125" customWidth="1"/>
+    <col min="11" max="11" width="107.140625" customWidth="1"/>
+    <col min="12" max="12" width="53.7109375" customWidth="1"/>
+    <col min="13" max="13" width="12.7109375" customWidth="1"/>
+    <col min="14" max="14" width="36.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="36.42578125" customWidth="1"/>
+    <col min="16" max="16" width="20.85546875" customWidth="1"/>
     <col min="17" max="17" width="52" customWidth="1"/>
-    <col min="18" max="18" width="32.5" customWidth="1"/>
-    <col min="19" max="19" width="16.83203125" customWidth="1"/>
+    <col min="18" max="18" width="32.42578125" customWidth="1"/>
+    <col min="19" max="19" width="16.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -2314,7 +2317,7 @@
       <c r="R1" s="10"/>
       <c r="S1" s="10"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2373,7 +2376,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2291005</v>
       </c>
@@ -2417,7 +2420,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>2291009</v>
       </c>
@@ -2461,7 +2464,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>2240005</v>
       </c>
@@ -2508,7 +2511,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>2240009</v>
       </c>
@@ -2555,7 +2558,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>2251011</v>
       </c>
@@ -2599,7 +2602,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>2327002</v>
       </c>
@@ -2646,7 +2649,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9"